--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="AH1" s="4" t="inlineStr">
         <is>
-          <t>최종 업데이트: 2025-10-16 03:50:19</t>
+          <t>최종 업데이트: 2025-10-16 05:18:52</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       <c r="AD2" s="9" t="inlineStr"/>
       <c r="AE2" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:01</t>
+          <t>2025-10-16 05:18:34</t>
         </is>
       </c>
       <c r="AF2" s="11" t="n">
@@ -827,7 +827,7 @@
       <c r="AD3" s="9" t="inlineStr"/>
       <c r="AE3" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:01</t>
+          <t>2025-10-16 05:18:34</t>
         </is>
       </c>
       <c r="AF3" s="11" t="n">
@@ -911,7 +911,7 @@
       <c r="AD4" s="9" t="inlineStr"/>
       <c r="AE4" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:01</t>
+          <t>2025-10-16 05:18:34</t>
         </is>
       </c>
       <c r="AF4" s="11" t="n">
@@ -995,7 +995,7 @@
       <c r="AD5" s="9" t="inlineStr"/>
       <c r="AE5" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:01</t>
+          <t>2025-10-16 05:18:35</t>
         </is>
       </c>
       <c r="AF5" s="11" t="n">
@@ -1079,7 +1079,7 @@
       <c r="AD6" s="9" t="inlineStr"/>
       <c r="AE6" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:02</t>
+          <t>2025-10-16 05:18:35</t>
         </is>
       </c>
       <c r="AF6" s="11" t="n">
@@ -1163,7 +1163,7 @@
       <c r="AD7" s="9" t="inlineStr"/>
       <c r="AE7" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:02</t>
+          <t>2025-10-16 05:18:35</t>
         </is>
       </c>
       <c r="AF7" s="11" t="n">
@@ -1247,7 +1247,7 @@
       <c r="AD8" s="9" t="inlineStr"/>
       <c r="AE8" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:02</t>
+          <t>2025-10-16 05:18:35</t>
         </is>
       </c>
       <c r="AF8" s="11" t="n">
@@ -1331,7 +1331,7 @@
       <c r="AD9" s="9" t="inlineStr"/>
       <c r="AE9" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:02</t>
+          <t>2025-10-16 05:18:36</t>
         </is>
       </c>
       <c r="AF9" s="11" t="n">
@@ -1415,7 +1415,7 @@
       <c r="AD10" s="9" t="inlineStr"/>
       <c r="AE10" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:03</t>
+          <t>2025-10-16 05:18:36</t>
         </is>
       </c>
       <c r="AF10" s="11" t="n">
@@ -1499,7 +1499,7 @@
       <c r="AD11" s="9" t="inlineStr"/>
       <c r="AE11" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:03</t>
+          <t>2025-10-16 05:18:36</t>
         </is>
       </c>
       <c r="AF11" s="11" t="n">
@@ -1583,7 +1583,7 @@
       <c r="AD12" s="9" t="inlineStr"/>
       <c r="AE12" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:03</t>
+          <t>2025-10-16 05:18:37</t>
         </is>
       </c>
       <c r="AF12" s="11" t="n">
@@ -1667,7 +1667,7 @@
       <c r="AD13" s="9" t="inlineStr"/>
       <c r="AE13" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:04</t>
+          <t>2025-10-16 05:18:37</t>
         </is>
       </c>
       <c r="AF13" s="11" t="n">
@@ -1751,7 +1751,7 @@
       <c r="AD14" s="9" t="inlineStr"/>
       <c r="AE14" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:04</t>
+          <t>2025-10-16 05:18:37</t>
         </is>
       </c>
       <c r="AF14" s="11" t="n">
@@ -1835,7 +1835,7 @@
       <c r="AD15" s="9" t="inlineStr"/>
       <c r="AE15" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:04</t>
+          <t>2025-10-16 05:18:37</t>
         </is>
       </c>
       <c r="AF15" s="11" t="n">
@@ -1919,7 +1919,7 @@
       <c r="AD16" s="9" t="inlineStr"/>
       <c r="AE16" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:04</t>
+          <t>2025-10-16 05:18:38</t>
         </is>
       </c>
       <c r="AF16" s="11" t="n">
@@ -2003,7 +2003,7 @@
       <c r="AD17" s="9" t="inlineStr"/>
       <c r="AE17" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:05</t>
+          <t>2025-10-16 05:18:38</t>
         </is>
       </c>
       <c r="AF17" s="11" t="n">
@@ -2087,7 +2087,7 @@
       <c r="AD18" s="9" t="inlineStr"/>
       <c r="AE18" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:05</t>
+          <t>2025-10-16 05:18:38</t>
         </is>
       </c>
       <c r="AF18" s="11" t="n">
@@ -2171,7 +2171,7 @@
       <c r="AD19" s="9" t="inlineStr"/>
       <c r="AE19" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:05</t>
+          <t>2025-10-16 05:18:38</t>
         </is>
       </c>
       <c r="AF19" s="11" t="n">
@@ -2255,7 +2255,7 @@
       <c r="AD20" s="9" t="inlineStr"/>
       <c r="AE20" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:05</t>
+          <t>2025-10-16 05:18:39</t>
         </is>
       </c>
       <c r="AF20" s="11" t="n">
@@ -2339,7 +2339,7 @@
       <c r="AD21" s="9" t="inlineStr"/>
       <c r="AE21" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:06</t>
+          <t>2025-10-16 05:18:39</t>
         </is>
       </c>
       <c r="AF21" s="11" t="n">
@@ -2423,7 +2423,7 @@
       <c r="AD22" s="9" t="inlineStr"/>
       <c r="AE22" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:06</t>
+          <t>2025-10-16 05:18:39</t>
         </is>
       </c>
       <c r="AF22" s="11" t="n">
@@ -2507,7 +2507,7 @@
       <c r="AD23" s="9" t="inlineStr"/>
       <c r="AE23" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:06</t>
+          <t>2025-10-16 05:18:40</t>
         </is>
       </c>
       <c r="AF23" s="11" t="n">
@@ -2591,7 +2591,7 @@
       <c r="AD24" s="9" t="inlineStr"/>
       <c r="AE24" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:07</t>
+          <t>2025-10-16 05:18:40</t>
         </is>
       </c>
       <c r="AF24" s="11" t="n">
@@ -2675,7 +2675,7 @@
       <c r="AD25" s="9" t="inlineStr"/>
       <c r="AE25" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:07</t>
+          <t>2025-10-16 05:18:40</t>
         </is>
       </c>
       <c r="AF25" s="11" t="n">
@@ -2759,7 +2759,7 @@
       <c r="AD26" s="9" t="inlineStr"/>
       <c r="AE26" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:07</t>
+          <t>2025-10-16 05:18:40</t>
         </is>
       </c>
       <c r="AF26" s="11" t="n">
@@ -2843,7 +2843,7 @@
       <c r="AD27" s="9" t="inlineStr"/>
       <c r="AE27" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:07</t>
+          <t>2025-10-16 05:18:41</t>
         </is>
       </c>
       <c r="AF27" s="11" t="n">
@@ -2927,7 +2927,7 @@
       <c r="AD28" s="9" t="inlineStr"/>
       <c r="AE28" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:08</t>
+          <t>2025-10-16 05:18:41</t>
         </is>
       </c>
       <c r="AF28" s="11" t="n">
@@ -3011,7 +3011,7 @@
       <c r="AD29" s="9" t="inlineStr"/>
       <c r="AE29" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:08</t>
+          <t>2025-10-16 05:18:41</t>
         </is>
       </c>
       <c r="AF29" s="11" t="n">
@@ -3095,7 +3095,7 @@
       <c r="AD30" s="9" t="inlineStr"/>
       <c r="AE30" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:08</t>
+          <t>2025-10-16 05:18:41</t>
         </is>
       </c>
       <c r="AF30" s="11" t="n">
@@ -3179,7 +3179,7 @@
       <c r="AD31" s="9" t="inlineStr"/>
       <c r="AE31" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:08</t>
+          <t>2025-10-16 05:18:42</t>
         </is>
       </c>
       <c r="AF31" s="11" t="n">
@@ -3263,7 +3263,7 @@
       <c r="AD32" s="9" t="inlineStr"/>
       <c r="AE32" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:09</t>
+          <t>2025-10-16 05:18:42</t>
         </is>
       </c>
       <c r="AF32" s="11" t="n">
@@ -3347,7 +3347,7 @@
       <c r="AD33" s="9" t="inlineStr"/>
       <c r="AE33" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:09</t>
+          <t>2025-10-16 05:18:42</t>
         </is>
       </c>
       <c r="AF33" s="11" t="n">
@@ -3431,7 +3431,7 @@
       <c r="AD34" s="9" t="inlineStr"/>
       <c r="AE34" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:09</t>
+          <t>2025-10-16 05:18:43</t>
         </is>
       </c>
       <c r="AF34" s="11" t="n">
@@ -3515,7 +3515,7 @@
       <c r="AD35" s="9" t="inlineStr"/>
       <c r="AE35" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:10</t>
+          <t>2025-10-16 05:18:43</t>
         </is>
       </c>
       <c r="AF35" s="11" t="n">
@@ -3599,7 +3599,7 @@
       <c r="AD36" s="9" t="inlineStr"/>
       <c r="AE36" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:10</t>
+          <t>2025-10-16 05:18:43</t>
         </is>
       </c>
       <c r="AF36" s="11" t="n">
@@ -3683,7 +3683,7 @@
       <c r="AD37" s="9" t="inlineStr"/>
       <c r="AE37" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:10</t>
+          <t>2025-10-16 05:18:43</t>
         </is>
       </c>
       <c r="AF37" s="11" t="n">
@@ -3767,7 +3767,7 @@
       <c r="AD38" s="9" t="inlineStr"/>
       <c r="AE38" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:10</t>
+          <t>2025-10-16 05:18:44</t>
         </is>
       </c>
       <c r="AF38" s="11" t="n">
@@ -3851,7 +3851,7 @@
       <c r="AD39" s="9" t="inlineStr"/>
       <c r="AE39" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:11</t>
+          <t>2025-10-16 05:18:44</t>
         </is>
       </c>
       <c r="AF39" s="11" t="n">
@@ -3935,7 +3935,7 @@
       <c r="AD40" s="9" t="inlineStr"/>
       <c r="AE40" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:11</t>
+          <t>2025-10-16 05:18:44</t>
         </is>
       </c>
       <c r="AF40" s="11" t="n">
@@ -4019,7 +4019,7 @@
       <c r="AD41" s="9" t="inlineStr"/>
       <c r="AE41" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:11</t>
+          <t>2025-10-16 05:18:44</t>
         </is>
       </c>
       <c r="AF41" s="11" t="n">
@@ -4103,7 +4103,7 @@
       <c r="AD42" s="9" t="inlineStr"/>
       <c r="AE42" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:11</t>
+          <t>2025-10-16 05:18:45</t>
         </is>
       </c>
       <c r="AF42" s="11" t="n">
@@ -4187,7 +4187,7 @@
       <c r="AD43" s="9" t="inlineStr"/>
       <c r="AE43" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:12</t>
+          <t>2025-10-16 05:18:45</t>
         </is>
       </c>
       <c r="AF43" s="11" t="n">
@@ -4271,7 +4271,7 @@
       <c r="AD44" s="9" t="inlineStr"/>
       <c r="AE44" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:12</t>
+          <t>2025-10-16 05:18:45</t>
         </is>
       </c>
       <c r="AF44" s="11" t="n">
@@ -4355,7 +4355,7 @@
       <c r="AD45" s="9" t="inlineStr"/>
       <c r="AE45" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:12</t>
+          <t>2025-10-16 05:18:46</t>
         </is>
       </c>
       <c r="AF45" s="11" t="n">
@@ -4439,7 +4439,7 @@
       <c r="AD46" s="9" t="inlineStr"/>
       <c r="AE46" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:13</t>
+          <t>2025-10-16 05:18:46</t>
         </is>
       </c>
       <c r="AF46" s="11" t="n">
@@ -4523,7 +4523,7 @@
       <c r="AD47" s="9" t="inlineStr"/>
       <c r="AE47" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:13</t>
+          <t>2025-10-16 05:18:46</t>
         </is>
       </c>
       <c r="AF47" s="11" t="n">
@@ -4607,7 +4607,7 @@
       <c r="AD48" s="9" t="inlineStr"/>
       <c r="AE48" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:13</t>
+          <t>2025-10-16 05:18:46</t>
         </is>
       </c>
       <c r="AF48" s="11" t="n">
@@ -4691,7 +4691,7 @@
       <c r="AD49" s="9" t="inlineStr"/>
       <c r="AE49" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:13</t>
+          <t>2025-10-16 05:18:47</t>
         </is>
       </c>
       <c r="AF49" s="11" t="n">
@@ -4775,7 +4775,7 @@
       <c r="AD50" s="9" t="inlineStr"/>
       <c r="AE50" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:14</t>
+          <t>2025-10-16 05:18:47</t>
         </is>
       </c>
       <c r="AF50" s="11" t="n">
@@ -4859,7 +4859,7 @@
       <c r="AD51" s="9" t="inlineStr"/>
       <c r="AE51" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:14</t>
+          <t>2025-10-16 05:18:47</t>
         </is>
       </c>
       <c r="AF51" s="11" t="n">
@@ -4943,7 +4943,7 @@
       <c r="AD52" s="9" t="inlineStr"/>
       <c r="AE52" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:14</t>
+          <t>2025-10-16 05:18:47</t>
         </is>
       </c>
       <c r="AF52" s="11" t="n">
@@ -5027,7 +5027,7 @@
       <c r="AD53" s="9" t="inlineStr"/>
       <c r="AE53" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:14</t>
+          <t>2025-10-16 05:18:48</t>
         </is>
       </c>
       <c r="AF53" s="11" t="n">
@@ -5111,7 +5111,7 @@
       <c r="AD54" s="9" t="inlineStr"/>
       <c r="AE54" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:15</t>
+          <t>2025-10-16 05:18:48</t>
         </is>
       </c>
       <c r="AF54" s="11" t="n">
@@ -5195,7 +5195,7 @@
       <c r="AD55" s="9" t="inlineStr"/>
       <c r="AE55" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:15</t>
+          <t>2025-10-16 05:18:48</t>
         </is>
       </c>
       <c r="AF55" s="11" t="n">
@@ -5279,7 +5279,7 @@
       <c r="AD56" s="9" t="inlineStr"/>
       <c r="AE56" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:15</t>
+          <t>2025-10-16 05:18:49</t>
         </is>
       </c>
       <c r="AF56" s="11" t="n">
@@ -5363,7 +5363,7 @@
       <c r="AD57" s="9" t="inlineStr"/>
       <c r="AE57" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:16</t>
+          <t>2025-10-16 05:18:49</t>
         </is>
       </c>
       <c r="AF57" s="11" t="n">
@@ -5447,7 +5447,7 @@
       <c r="AD58" s="9" t="inlineStr"/>
       <c r="AE58" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:16</t>
+          <t>2025-10-16 05:18:49</t>
         </is>
       </c>
       <c r="AF58" s="11" t="n">
@@ -5531,7 +5531,7 @@
       <c r="AD59" s="9" t="inlineStr"/>
       <c r="AE59" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:16</t>
+          <t>2025-10-16 05:18:49</t>
         </is>
       </c>
       <c r="AF59" s="11" t="n">
@@ -5615,7 +5615,7 @@
       <c r="AD60" s="9" t="inlineStr"/>
       <c r="AE60" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:16</t>
+          <t>2025-10-16 05:18:50</t>
         </is>
       </c>
       <c r="AF60" s="11" t="n">
@@ -5699,7 +5699,7 @@
       <c r="AD61" s="9" t="inlineStr"/>
       <c r="AE61" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:17</t>
+          <t>2025-10-16 05:18:50</t>
         </is>
       </c>
       <c r="AF61" s="11" t="n">
@@ -5783,7 +5783,7 @@
       <c r="AD62" s="9" t="inlineStr"/>
       <c r="AE62" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:17</t>
+          <t>2025-10-16 05:18:50</t>
         </is>
       </c>
       <c r="AF62" s="11" t="n">
@@ -5867,7 +5867,7 @@
       <c r="AD63" s="9" t="inlineStr"/>
       <c r="AE63" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:17</t>
+          <t>2025-10-16 05:18:51</t>
         </is>
       </c>
       <c r="AF63" s="11" t="n">
@@ -5951,7 +5951,7 @@
       <c r="AD64" s="9" t="inlineStr"/>
       <c r="AE64" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:18</t>
+          <t>2025-10-16 05:18:51</t>
         </is>
       </c>
       <c r="AF64" s="11" t="n">
@@ -6035,7 +6035,7 @@
       <c r="AD65" s="9" t="inlineStr"/>
       <c r="AE65" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:18</t>
+          <t>2025-10-16 05:18:51</t>
         </is>
       </c>
       <c r="AF65" s="11" t="n">
@@ -6119,7 +6119,7 @@
       <c r="AD66" s="9" t="inlineStr"/>
       <c r="AE66" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:18</t>
+          <t>2025-10-16 05:18:51</t>
         </is>
       </c>
       <c r="AF66" s="11" t="n">
@@ -6203,7 +6203,7 @@
       <c r="AD67" s="9" t="inlineStr"/>
       <c r="AE67" s="10" t="inlineStr">
         <is>
-          <t>2025-10-16 03:50:18</t>
+          <t>2025-10-16 05:18:52</t>
         </is>
       </c>
       <c r="AF67" s="11" t="n">
@@ -6257,7 +6257,7 @@
         <v>34276</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>1.349048897187536e-13</v>
+        <v>1.349048897187536e-15</v>
       </c>
       <c r="M68" s="9" t="inlineStr"/>
       <c r="N68" s="9" t="inlineStr"/>
@@ -6265,7 +6265,7 @@
         <v>30848.4</v>
       </c>
       <c r="P68" s="8" t="n">
-        <v>2.610054330208374e-13</v>
+        <v>2.610054330208374e-15</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="9" t="inlineStr"/>
@@ -6273,7 +6273,7 @@
         <v>27763.56</v>
       </c>
       <c r="T68" s="8" t="n">
-        <v>4.011171478009304e-13</v>
+        <v>4.011171478009304e-15</v>
       </c>
       <c r="U68" s="9" t="inlineStr"/>
       <c r="V68" s="9" t="inlineStr"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH70"/>
+  <dimension ref="A1:AH73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>최종 업데이트: 2025-10-17 13:37:17</t>
+          <t>최종 업데이트: 2025-10-18 10:13:23</t>
         </is>
       </c>
     </row>
@@ -679,45 +679,45 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.1%</t>
+          <t>1차 매수선까지 38.9%</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>97900</v>
+        <v>96300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>94900</v>
+        <v>94400</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>99100</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>86635</v>
+        <v>86555</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>69308</v>
+        <v>69244</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>69408</v>
+        <v>69344</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>41.05002305209774</v>
+        <v>38.87286571296723</v>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="6" t="n">
-        <v>62567.2</v>
+        <v>62509.6</v>
       </c>
       <c r="P2" s="7" t="n">
-        <v>56.47176156196856</v>
+        <v>54.056336946645</v>
       </c>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="6" t="n">
-        <v>56410.48</v>
+        <v>56358.64</v>
       </c>
       <c r="T2" s="7" t="n">
-        <v>73.54931211363561</v>
+        <v>70.86998550710237</v>
       </c>
       <c r="U2" s="8" t="inlineStr"/>
       <c r="V2" s="8" t="inlineStr"/>
@@ -731,7 +731,7 @@
       <c r="AD2" s="8" t="inlineStr"/>
       <c r="AE2" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:57</t>
+          <t>2025-10-18 10:13:03</t>
         </is>
       </c>
       <c r="AF2" s="8" t="inlineStr"/>
@@ -759,45 +759,45 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 53.8%</t>
+          <t>1차 매수선까지 50.6%</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>465000</v>
+        <v>454500</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>443500</v>
+        <v>440500</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>475000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>377225</v>
+        <v>376700</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>301780</v>
+        <v>301360</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>302280</v>
+        <v>301860</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>53.8308852719333</v>
+        <v>50.5664877757901</v>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="6" t="n">
-        <v>272552</v>
+        <v>272174</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>70.60964513193812</v>
+        <v>66.98876454033082</v>
       </c>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="6" t="n">
-        <v>245796.8</v>
+        <v>245456.6</v>
       </c>
       <c r="T3" s="7" t="n">
-        <v>89.18065654231462</v>
+        <v>85.16511676605965</v>
       </c>
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr"/>
@@ -811,7 +811,7 @@
       <c r="AD3" s="8" t="inlineStr"/>
       <c r="AE3" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:57</t>
+          <t>2025-10-18 10:13:03</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr"/>
@@ -839,45 +839,45 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.1%</t>
+          <t>1차 매수선까지 46.8%</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>81500</v>
+        <v>79600</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>80600</v>
+        <v>76200</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>83600</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>67755</v>
+        <v>67660</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>54204</v>
+        <v>54128</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>54304</v>
+        <v>54228</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>50.08102533883324</v>
+        <v>46.78763738290182</v>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="6" t="n">
-        <v>48923.6</v>
+        <v>48855.2</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>66.58626920341104</v>
+        <v>62.93045571402838</v>
       </c>
       <c r="Q4" s="8" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="6" t="n">
-        <v>44081.24</v>
+        <v>44019.68000000001</v>
       </c>
       <c r="T4" s="7" t="n">
-        <v>84.88590611334891</v>
+        <v>80.82821138181828</v>
       </c>
       <c r="U4" s="8" t="inlineStr"/>
       <c r="V4" s="8" t="inlineStr"/>
@@ -891,7 +891,7 @@
       <c r="AD4" s="8" t="inlineStr"/>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:58</t>
+          <t>2025-10-18 10:13:03</t>
         </is>
       </c>
       <c r="AF4" s="8" t="inlineStr"/>
@@ -919,45 +919,45 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.2%</t>
+          <t>1차 매수선까지 25.1%</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>257000</v>
+        <v>250500</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>254500</v>
+        <v>245000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>262500</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>249925</v>
+        <v>249600</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>199940</v>
+        <v>199680</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>200440</v>
+        <v>200180</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>28.21792057473558</v>
+        <v>25.13737636127485</v>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="6" t="n">
-        <v>180896</v>
+        <v>180662</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>42.07058199186272</v>
+        <v>38.65671807020846</v>
       </c>
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="6" t="n">
-        <v>163306.4</v>
+        <v>163095.8</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>57.37288924377735</v>
+        <v>53.59071171667203</v>
       </c>
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
@@ -971,7 +971,7 @@
       <c r="AD5" s="8" t="inlineStr"/>
       <c r="AE5" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:58</t>
+          <t>2025-10-18 10:13:04</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr"/>
@@ -999,45 +999,45 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 69.0%</t>
+          <t>1차 매수선까지 64.1%</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>143900</v>
+        <v>139500</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>140900</v>
+        <v>131700</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>147900</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>106330</v>
+        <v>106110</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>85064</v>
+        <v>84888</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>85164</v>
+        <v>84988</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>68.96810859048425</v>
+        <v>64.14081988045372</v>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="6" t="n">
-        <v>76747.60000000001</v>
+        <v>76589.2</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>87.49771979840411</v>
+        <v>82.14056289920772</v>
       </c>
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="6" t="n">
-        <v>69172.84000000001</v>
+        <v>69030.28</v>
       </c>
       <c r="T6" s="7" t="n">
-        <v>108.0296255004131</v>
+        <v>102.0852298440626</v>
       </c>
       <c r="U6" s="8" t="inlineStr"/>
       <c r="V6" s="8" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       <c r="AD6" s="8" t="inlineStr"/>
       <c r="AE6" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:58</t>
+          <t>2025-10-18 10:13:04</t>
         </is>
       </c>
       <c r="AF6" s="8" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.0%</t>
+          <t>1차 매수선까지 57.2%</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>163200</v>
+        <v>152900</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>138600</v>
@@ -1092,32 +1092,32 @@
         <v>167400</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>122000</v>
+        <v>121485</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>97600</v>
+        <v>97188</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>97700</v>
+        <v>97288</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>67.04196519959058</v>
+        <v>57.16223994737275</v>
       </c>
       <c r="M7" s="8" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="6" t="n">
-        <v>88030</v>
+        <v>87659.2</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>85.39134386004771</v>
+        <v>74.42550240020444</v>
       </c>
       <c r="Q7" s="8" t="inlineStr"/>
       <c r="R7" s="8" t="inlineStr"/>
       <c r="S7" s="6" t="n">
-        <v>79327</v>
+        <v>78993.28</v>
       </c>
       <c r="T7" s="7" t="n">
-        <v>105.7307095944634</v>
+        <v>93.56076871349057</v>
       </c>
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       <c r="AD7" s="8" t="inlineStr"/>
       <c r="AE7" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:59</t>
+          <t>2025-10-18 10:13:04</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr"/>
@@ -1159,45 +1159,45 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 49.9%</t>
+          <t>1차 매수선까지 46.6%</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>255000</v>
+        <v>249000</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>228000</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>257500</v>
+        <v>259500</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>212000</v>
+        <v>211700</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>169600</v>
+        <v>169360</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>170100</v>
+        <v>169860</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>49.91181657848324</v>
+        <v>46.59131049099258</v>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="6" t="n">
-        <v>153590</v>
+        <v>153374</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>66.02643401263103</v>
+        <v>62.34824676933509</v>
       </c>
       <c r="Q8" s="8" t="inlineStr"/>
       <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="6" t="n">
-        <v>138731</v>
+        <v>138536.6</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>83.80895401892872</v>
+        <v>79.73589650677148</v>
       </c>
       <c r="U8" s="8" t="inlineStr"/>
       <c r="V8" s="8" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       <c r="AD8" s="8" t="inlineStr"/>
       <c r="AE8" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:59</t>
+          <t>2025-10-18 10:13:04</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr"/>
@@ -1219,12 +1219,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>086520</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1239,45 +1239,45 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.3%</t>
+          <t>1차 매수선까지 74.3%</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>11210</v>
+        <v>70800</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>11050</v>
+        <v>58600</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>12250</v>
+        <v>73900</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>8516</v>
+        <v>50715</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>6812.8</v>
+        <v>40572</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>6822.8</v>
+        <v>40622</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>64.30204608078795</v>
+        <v>74.28979370784305</v>
       </c>
       <c r="M9" s="8" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="6" t="n">
-        <v>6150.52</v>
+        <v>36609.8</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>82.26101207702762</v>
+        <v>93.39084070385523</v>
       </c>
       <c r="Q9" s="8" t="inlineStr"/>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="6" t="n">
-        <v>5545.468000000001</v>
+        <v>32998.82000000001</v>
       </c>
       <c r="T9" s="7" t="n">
-        <v>102.1470505284676</v>
+        <v>114.5531264451274</v>
       </c>
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       <c r="AD9" s="8" t="inlineStr"/>
       <c r="AE9" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:36:59</t>
+          <t>2025-10-18 10:13:05</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr"/>
@@ -1299,12 +1299,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>086520</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1319,45 +1319,45 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 78.9%</t>
+          <t>1차 매수선까지 50.7%</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>72800</v>
+        <v>61700</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>58600</v>
+        <v>58700</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>73500</v>
+        <v>69200</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>50815</v>
+        <v>51130</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>40652</v>
+        <v>40904</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>40702</v>
+        <v>40954</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>78.86098963195913</v>
+        <v>50.65683449724081</v>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="6" t="n">
-        <v>36681.8</v>
+        <v>36908.6</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>98.46354322852203</v>
+        <v>67.16971112423663</v>
       </c>
       <c r="Q10" s="8" t="inlineStr"/>
       <c r="R10" s="8" t="inlineStr"/>
       <c r="S10" s="6" t="n">
-        <v>33063.62</v>
+        <v>33267.74</v>
       </c>
       <c r="T10" s="7" t="n">
-        <v>120.1815772138683</v>
+        <v>85.4649579442427</v>
       </c>
       <c r="U10" s="8" t="inlineStr"/>
       <c r="V10" s="8" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="AD10" s="8" t="inlineStr"/>
       <c r="AE10" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:00</t>
+          <t>2025-10-18 10:13:05</t>
         </is>
       </c>
       <c r="AF10" s="8" t="inlineStr"/>
@@ -1379,12 +1379,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1399,45 +1399,45 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 61.6%</t>
+          <t>1차 매수선까지 44.8%</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>66500</v>
+        <v>421500</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>60900</v>
+        <v>406000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>69200</v>
+        <v>443000</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>51370</v>
+        <v>363350</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>41096</v>
+        <v>290680</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>41146</v>
+        <v>291180</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>61.61959850289214</v>
+        <v>44.75582114156192</v>
       </c>
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="6" t="n">
-        <v>37081.4</v>
+        <v>262562</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>79.33519230665507</v>
+        <v>60.53351208476474</v>
       </c>
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="6" t="n">
-        <v>33423.26</v>
+        <v>236805.8</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>98.9632369792773</v>
+        <v>77.99395116166917</v>
       </c>
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       <c r="AD11" s="8" t="inlineStr"/>
       <c r="AE11" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:00</t>
+          <t>2025-10-18 10:13:05</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr"/>
@@ -1459,12 +1459,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1479,45 +1479,45 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.4%</t>
+          <t>1차 매수선까지 22.6%</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>432750</v>
+        <v>107300</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>406500</v>
+        <v>103700</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>443000</v>
+        <v>113700</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>363912.5</v>
+        <v>109295</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>291130</v>
+        <v>87436</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>291630</v>
+        <v>87536</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>48.39008332476083</v>
+        <v>22.57813927983915</v>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="6" t="n">
-        <v>262967</v>
+        <v>78882.40000000001</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>64.56437499762328</v>
+        <v>36.02527306471404</v>
       </c>
       <c r="Q12" s="8" t="inlineStr"/>
       <c r="R12" s="8" t="inlineStr"/>
       <c r="S12" s="6" t="n">
-        <v>237170.3</v>
+        <v>71094.16</v>
       </c>
       <c r="T12" s="7" t="n">
-        <v>82.4638245176567</v>
+        <v>50.92660212878244</v>
       </c>
       <c r="U12" s="8" t="inlineStr"/>
       <c r="V12" s="8" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="AD12" s="8" t="inlineStr"/>
       <c r="AE12" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:00</t>
+          <t>2025-10-18 10:13:06</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr"/>
@@ -1539,12 +1539,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1559,45 +1559,45 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 61.2%</t>
+          <t>1차 매수선까지 41.3%</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>41700</v>
+        <v>41850</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>41450</v>
+        <v>39450</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>45000</v>
+        <v>43300</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>32265</v>
+        <v>36962.5</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>25812</v>
+        <v>29570</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>25862</v>
+        <v>29620</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>61.24042997447994</v>
+        <v>41.2896691424713</v>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="6" t="n">
-        <v>23325.8</v>
+        <v>26708</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>78.77200353256909</v>
+        <v>56.69462333383256</v>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
       <c r="S13" s="6" t="n">
-        <v>21043.22</v>
+        <v>24087.2</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>98.16358903247696</v>
+        <v>73.74373111029924</v>
       </c>
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       <c r="AD13" s="8" t="inlineStr"/>
       <c r="AE13" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:00</t>
+          <t>2025-10-18 10:13:06</t>
         </is>
       </c>
       <c r="AF13" s="8" t="inlineStr"/>
@@ -1619,12 +1619,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1639,45 +1639,45 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 57.1%</t>
+          <t>1차 매수선까지 36.3%</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>193800</v>
+        <v>240500</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>191600</v>
+        <v>230000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>202500</v>
+        <v>246000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>153529.4</v>
+        <v>219950</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>122823.52</v>
+        <v>175960</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>123323.52</v>
+        <v>176460</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>57.14763899051859</v>
+        <v>36.29151082398277</v>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="6" t="n">
-        <v>111491.168</v>
+        <v>159314</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>73.82542803749261</v>
+        <v>50.9597398847559</v>
       </c>
       <c r="Q14" s="8" t="inlineStr"/>
       <c r="R14" s="8" t="inlineStr"/>
       <c r="S14" s="6" t="n">
-        <v>100842.0512</v>
+        <v>143882.6</v>
       </c>
       <c r="T14" s="7" t="n">
-        <v>92.18173142436039</v>
+        <v>67.15016270209185</v>
       </c>
       <c r="U14" s="8" t="inlineStr"/>
       <c r="V14" s="8" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       <c r="AD14" s="8" t="inlineStr"/>
       <c r="AE14" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:01</t>
+          <t>2025-10-18 10:13:06</t>
         </is>
       </c>
       <c r="AF14" s="8" t="inlineStr"/>
@@ -1699,12 +1699,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1719,45 +1719,45 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.2%</t>
+          <t>1차 매수선까지 53.9%</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>75100</v>
+        <v>185400</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>74400</v>
+        <v>170000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>76000</v>
+        <v>201000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>68290</v>
+        <v>149940</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>54632</v>
+        <v>119952</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>54732</v>
+        <v>120452</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>37.21406124387926</v>
+        <v>53.92023378607246</v>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="6" t="n">
-        <v>49308.8</v>
+        <v>108906.8</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>52.30547082873645</v>
+        <v>70.23730382308541</v>
       </c>
       <c r="Q15" s="8" t="inlineStr"/>
       <c r="R15" s="8" t="inlineStr"/>
       <c r="S15" s="6" t="n">
-        <v>44427.92000000001</v>
+        <v>98116.12000000001</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>69.0378482719875</v>
+        <v>88.95977541712817</v>
       </c>
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       <c r="AD15" s="8" t="inlineStr"/>
       <c r="AE15" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:01</t>
+          <t>2025-10-18 10:13:06</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr"/>
@@ -1779,12 +1779,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1794,50 +1794,50 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 2.2% (접근 중!)</t>
+          <t>1차 매수선까지 66.9%</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>21800</v>
+        <v>11400</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>21650</v>
+        <v>11050</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>22850</v>
+        <v>12250</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>26602.5</v>
+        <v>8525.5</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>21282</v>
+        <v>6820.400000000001</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>21332</v>
+        <v>6830.400000000001</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>2.193887117944871</v>
+        <v>66.90091356289528</v>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="6" t="n">
-        <v>19248.8</v>
+        <v>6157.360000000001</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>13.25381322472051</v>
+        <v>85.14428261462703</v>
       </c>
       <c r="Q16" s="8" t="inlineStr"/>
       <c r="R16" s="8" t="inlineStr"/>
       <c r="S16" s="6" t="n">
-        <v>17373.92</v>
+        <v>5551.624000000001</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>25.47542523506499</v>
+        <v>105.3453187751908</v>
       </c>
       <c r="U16" s="8" t="inlineStr"/>
       <c r="V16" s="8" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="AD16" s="8" t="inlineStr"/>
       <c r="AE16" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:01</t>
+          <t>2025-10-18 10:13:07</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr"/>
@@ -1859,12 +1859,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1874,50 +1874,50 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 6.4% (접근 중!)</t>
+          <t>1차 매수선까지 41.5%</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>9190</v>
+        <v>331500</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>9070</v>
+        <v>303500</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>9870</v>
+        <v>350000</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>10786</v>
+        <v>292275</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>8628.800000000001</v>
+        <v>233820</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>8638.800000000001</v>
+        <v>234320</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>6.380515812381336</v>
+        <v>41.47319904404234</v>
       </c>
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="6" t="n">
-        <v>7784.920000000001</v>
+        <v>211388</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>18.04874038525764</v>
+        <v>56.82063314852309</v>
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
       <c r="S17" s="6" t="n">
-        <v>7016.428000000001</v>
+        <v>190749.2</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>30.97832686375459</v>
+        <v>73.78840907327526</v>
       </c>
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       <c r="AD17" s="8" t="inlineStr"/>
       <c r="AE17" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:02</t>
+          <t>2025-10-18 10:13:07</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr"/>
@@ -1939,12 +1939,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1959,45 +1959,45 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.1%</t>
+          <t>1차 매수선까지 68.6%</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>16630</v>
+        <v>105100</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>16610</v>
+        <v>95100</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>17290</v>
+        <v>114600</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>16688.5</v>
+        <v>77785</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>13350.8</v>
+        <v>62228</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>13400.8</v>
+        <v>62328</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>24.09706883171153</v>
+        <v>68.62405339494289</v>
       </c>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="6" t="n">
-        <v>12110.72</v>
+        <v>56195.2</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>37.31636104211805</v>
+        <v>87.02664996298614</v>
       </c>
       <c r="Q18" s="8" t="inlineStr"/>
       <c r="R18" s="8" t="inlineStr"/>
       <c r="S18" s="6" t="n">
-        <v>10949.648</v>
+        <v>50675.68000000001</v>
       </c>
       <c r="T18" s="7" t="n">
-        <v>51.87702837570668</v>
+        <v>107.397315635429</v>
       </c>
       <c r="U18" s="8" t="inlineStr"/>
       <c r="V18" s="8" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       <c r="AD18" s="8" t="inlineStr"/>
       <c r="AE18" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:02</t>
+          <t>2025-10-18 10:13:07</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr"/>
@@ -2019,12 +2019,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2039,45 +2039,45 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.5%</t>
+          <t>1차 매수선까지 43.0%</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>58100</v>
+        <v>678000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>58000</v>
+        <v>598000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>59500</v>
+        <v>722000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>61755</v>
+        <v>592150</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>49404</v>
+        <v>473720</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>49454</v>
+        <v>474220</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>17.48291341448619</v>
+        <v>42.97161654928092</v>
       </c>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="6" t="n">
-        <v>44558.6</v>
+        <v>427298</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>30.39009304601132</v>
+        <v>58.67146581542624</v>
       </c>
       <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="6" t="n">
-        <v>40152.74</v>
+        <v>385068.2</v>
       </c>
       <c r="T19" s="7" t="n">
-        <v>44.69747270049317</v>
+        <v>76.07270608167592</v>
       </c>
       <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       <c r="AD19" s="8" t="inlineStr"/>
       <c r="AE19" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:02</t>
+          <t>2025-10-18 10:13:07</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr"/>
@@ -2099,12 +2099,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2119,45 +2119,45 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.6%</t>
+          <t>1차 매수선까지 61.6%</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>332500</v>
+        <v>41800</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>332500</v>
+        <v>41450</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>347000</v>
+        <v>45000</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>315225</v>
+        <v>32270</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>252180</v>
+        <v>25816</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>252680</v>
+        <v>25866</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>31.58936203894254</v>
+        <v>61.60210314698833</v>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="6" t="n">
-        <v>227912</v>
+        <v>23329.4</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>45.88964161606233</v>
+        <v>79.17306060164427</v>
       </c>
       <c r="Q20" s="8" t="inlineStr"/>
       <c r="R20" s="8" t="inlineStr"/>
       <c r="S20" s="6" t="n">
-        <v>205620.8</v>
+        <v>21046.46</v>
       </c>
       <c r="T20" s="7" t="n">
-        <v>61.70543057900756</v>
+        <v>98.60822200027935</v>
       </c>
       <c r="U20" s="8" t="inlineStr"/>
       <c r="V20" s="8" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       <c r="AD20" s="8" t="inlineStr"/>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:02</t>
+          <t>2025-10-18 10:13:08</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr"/>
@@ -2179,12 +2179,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2199,45 +2199,45 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.4%</t>
+          <t>1차 매수선까지 55.9%</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>436500</v>
+        <v>192200</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>426000</v>
+        <v>190900</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>448000</v>
+        <v>202500</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>464275</v>
+        <v>153449.4</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>371420</v>
+        <v>122759.52</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>371920</v>
+        <v>123259.52</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>17.36394923639492</v>
+        <v>55.93116053023734</v>
       </c>
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="6" t="n">
-        <v>335228</v>
+        <v>111433.568</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>30.20988700227905</v>
+        <v>72.47944533194881</v>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="6" t="n">
-        <v>302205.2</v>
+        <v>100790.2112</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>44.43828233266667</v>
+        <v>90.69312159552256</v>
       </c>
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       <c r="AD21" s="8" t="inlineStr"/>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:03</t>
+          <t>2025-10-18 10:13:08</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr"/>
@@ -2259,12 +2259,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2279,45 +2279,45 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.9%</t>
+          <t>1차 매수선까지 37.0%</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>175400</v>
+        <v>75000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>173050</v>
+        <v>74400</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>176500</v>
+        <v>76000</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>173485</v>
+        <v>68285</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>138788</v>
+        <v>54628</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>139288</v>
+        <v>54728</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>25.92613864798116</v>
+        <v>37.04136822102032</v>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="6" t="n">
-        <v>125859.2</v>
+        <v>49305.2</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>39.36208080140348</v>
+        <v>52.11377298946155</v>
       </c>
       <c r="Q22" s="8" t="inlineStr"/>
       <c r="R22" s="8" t="inlineStr"/>
       <c r="S22" s="6" t="n">
-        <v>113773.28</v>
+        <v>44424.68000000001</v>
       </c>
       <c r="T22" s="7" t="n">
-        <v>54.1662506345954</v>
+        <v>68.82507651152464</v>
       </c>
       <c r="U22" s="8" t="inlineStr"/>
       <c r="V22" s="8" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="AD22" s="8" t="inlineStr"/>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:03</t>
+          <t>2025-10-18 10:13:08</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2359,45 +2359,45 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.6% (접근 중!)</t>
+          <t>1차 매수선까지 2.6% (접근 중!)</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>162500</v>
+        <v>21900</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>161700</v>
+        <v>21500</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>172900</v>
+        <v>22850</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>184735</v>
+        <v>26607.5</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>147788</v>
+        <v>21286</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>148288</v>
+        <v>21336</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>9.584052654294346</v>
+        <v>2.643419572553431</v>
       </c>
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="6" t="n">
-        <v>133959.2</v>
+        <v>19252.4</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>21.30559155324904</v>
+        <v>13.75205169225654</v>
       </c>
       <c r="Q23" s="8" t="inlineStr"/>
       <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="6" t="n">
-        <v>121063.28</v>
+        <v>17377.16</v>
       </c>
       <c r="T23" s="7" t="n">
-        <v>34.22732309912633</v>
+        <v>26.02749816425696</v>
       </c>
       <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr"/>
@@ -2411,7 +2411,7 @@
       <c r="AD23" s="8" t="inlineStr"/>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:03</t>
+          <t>2025-10-18 10:13:09</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr"/>
@@ -2419,12 +2419,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2434,50 +2434,50 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.6%</t>
+          <t>1차 매수선까지 4.4% (접근 중!)</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>199500</v>
+        <v>9010</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>197000</v>
+        <v>8870</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>204500</v>
+        <v>9870</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>218800</v>
+        <v>10777</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>175040</v>
+        <v>8621.6</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>175540</v>
+        <v>8631.6</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>13.64931069841631</v>
+        <v>4.383891746605491</v>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="6" t="n">
-        <v>158486</v>
+        <v>7778.440000000001</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>25.87862650328735</v>
+        <v>15.83299479072924</v>
       </c>
       <c r="Q24" s="8" t="inlineStr"/>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="6" t="n">
-        <v>143137.4</v>
+        <v>7010.596</v>
       </c>
       <c r="T24" s="7" t="n">
-        <v>39.37657104292798</v>
+        <v>28.5197435424891</v>
       </c>
       <c r="U24" s="8" t="inlineStr"/>
       <c r="V24" s="8" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       <c r="AD24" s="8" t="inlineStr"/>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:04</t>
+          <t>2025-10-18 10:13:09</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr"/>
@@ -2499,12 +2499,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2519,45 +2519,45 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.5%</t>
+          <t>1차 매수선까지 18.8%</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>9040</v>
+        <v>15890</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>9030</v>
+        <v>15680</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9470</v>
+        <v>17290</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>9773</v>
+        <v>16651.5</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>7818.400000000001</v>
+        <v>13321.2</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>7828.400000000001</v>
+        <v>13371.2</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>15.47698124776454</v>
+        <v>18.83750149575206</v>
       </c>
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="6" t="n">
-        <v>7055.56</v>
+        <v>12084.08</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>28.12590354273792</v>
+        <v>31.49532277177905</v>
       </c>
       <c r="Q25" s="8" t="inlineStr"/>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="6" t="n">
-        <v>6360.004000000001</v>
+        <v>10925.672</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>42.13827538473245</v>
+        <v>45.43727836603549</v>
       </c>
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="AD25" s="8" t="inlineStr"/>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:04</t>
+          <t>2025-10-18 10:13:09</t>
         </is>
       </c>
       <c r="AF25" s="8" t="inlineStr"/>
@@ -2579,12 +2579,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2599,45 +2599,45 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.0%</t>
+          <t>1차 매수선까지 16.9%</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>203500</v>
+        <v>57800</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>202000</v>
+        <v>56900</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>209500</v>
+        <v>59500</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>216850</v>
+        <v>61740</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>173480</v>
+        <v>49392</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>173980</v>
+        <v>49442</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>16.96746752500287</v>
+        <v>16.9046559605194</v>
       </c>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
       <c r="O26" s="6" t="n">
-        <v>157082</v>
+        <v>44547.8</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>29.55017124813791</v>
+        <v>29.74827039719132</v>
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
       <c r="R26" s="8" t="inlineStr"/>
       <c r="S26" s="6" t="n">
-        <v>141873.8</v>
+        <v>40143.02</v>
       </c>
       <c r="T26" s="7" t="n">
-        <v>43.43733656249425</v>
+        <v>43.98518098538673</v>
       </c>
       <c r="U26" s="8" t="inlineStr"/>
       <c r="V26" s="8" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="AD26" s="8" t="inlineStr"/>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:04</t>
+          <t>2025-10-18 10:13:09</t>
         </is>
       </c>
       <c r="AF26" s="8" t="inlineStr"/>
@@ -2659,12 +2659,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2679,45 +2679,45 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 66.7%</t>
+          <t>1차 매수선까지 29.1%</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>65400</v>
+        <v>326000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>65100</v>
+        <v>319000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>70800</v>
+        <v>347000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>48982.5</v>
+        <v>314900</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>39186</v>
+        <v>251920</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>39236</v>
+        <v>252420</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>66.68365786522581</v>
+        <v>29.14982964899771</v>
       </c>
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr"/>
       <c r="O27" s="6" t="n">
-        <v>35362.4</v>
+        <v>227678</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>84.94219849331492</v>
+        <v>43.18467309094422</v>
       </c>
       <c r="Q27" s="8" t="inlineStr"/>
       <c r="R27" s="8" t="inlineStr"/>
       <c r="S27" s="6" t="n">
-        <v>31876.16</v>
+        <v>205410.2</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>105.1690040456567</v>
+        <v>58.70682176444986</v>
       </c>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       <c r="AD27" s="8" t="inlineStr"/>
       <c r="AE27" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:04</t>
+          <t>2025-10-18 10:13:10</t>
         </is>
       </c>
       <c r="AF27" s="8" t="inlineStr"/>
@@ -2739,12 +2739,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2759,45 +2759,45 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.5%</t>
+          <t>1차 매수선까지 15.1%</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>96300</v>
+        <v>427500</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>95100</v>
+        <v>415000</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>99600</v>
+        <v>448000</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>105005</v>
+        <v>463825</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>84004</v>
+        <v>371060</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>84104</v>
+        <v>371560</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>14.50109388376296</v>
+        <v>15.05544192055119</v>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
       <c r="O28" s="6" t="n">
-        <v>75793.60000000001</v>
+        <v>334904</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>27.05558252939561</v>
+        <v>27.64852017294508</v>
       </c>
       <c r="Q28" s="8" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="6" t="n">
-        <v>68314.24000000001</v>
+        <v>301913.6</v>
       </c>
       <c r="T28" s="7" t="n">
-        <v>40.9662172923244</v>
+        <v>41.59680120405307</v>
       </c>
       <c r="U28" s="8" t="inlineStr"/>
       <c r="V28" s="8" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       <c r="AD28" s="8" t="inlineStr"/>
       <c r="AE28" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:05</t>
+          <t>2025-10-18 10:13:10</t>
         </is>
       </c>
       <c r="AF28" s="8" t="inlineStr"/>
@@ -2819,12 +2819,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2839,45 +2839,45 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.4%</t>
+          <t>1차 매수선까지 24.7%</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>109000</v>
+        <v>173600</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>105500</v>
+        <v>171400</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>113700</v>
+        <v>176500</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>109380</v>
+        <v>173395</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>87504</v>
+        <v>138716</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>87604</v>
+        <v>139216</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>24.42354230400438</v>
+        <v>24.6983105390185</v>
       </c>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="6" t="n">
-        <v>78943.60000000001</v>
+        <v>125794.4</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>38.07325736348481</v>
+        <v>38.00296356594569</v>
       </c>
       <c r="Q29" s="8" t="inlineStr"/>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="6" t="n">
-        <v>71149.24000000001</v>
+        <v>113714.96</v>
       </c>
       <c r="T29" s="7" t="n">
-        <v>53.19910655405453</v>
+        <v>52.66241134851561</v>
       </c>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       <c r="AD29" s="8" t="inlineStr"/>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:05</t>
+          <t>2025-10-18 10:13:10</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr"/>
@@ -2899,12 +2899,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2919,45 +2919,45 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 3.0% (접근 중!)</t>
+          <t>1차 매수선까지 8.6% (접근 중!)</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>169900</v>
+        <v>161000</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>168000</v>
+        <v>159800</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>179300</v>
+        <v>172900</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>205600</v>
+        <v>184660</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>164480</v>
+        <v>147728</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>164980</v>
+        <v>148228</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>2.982179658140381</v>
+        <v>8.616455730361334</v>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="6" t="n">
-        <v>148982</v>
+        <v>133905.2</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>14.04062235706327</v>
+        <v>20.23431502286691</v>
       </c>
       <c r="Q30" s="8" t="inlineStr"/>
       <c r="R30" s="8" t="inlineStr"/>
       <c r="S30" s="6" t="n">
-        <v>134583.8</v>
+        <v>121014.68</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>26.24104832825346</v>
+        <v>33.04171031150931</v>
       </c>
       <c r="U30" s="8" t="inlineStr"/>
       <c r="V30" s="8" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       <c r="AD30" s="8" t="inlineStr"/>
       <c r="AE30" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:05</t>
+          <t>2025-10-18 10:13:10</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr"/>
@@ -2979,12 +2979,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2999,45 +2999,45 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.9%</t>
+          <t>1차 매수선까지 13.6%</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>430000</v>
+        <v>199500</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>424000</v>
+        <v>195500</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>435000</v>
+        <v>204500</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>451600</v>
+        <v>218800</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>361280</v>
+        <v>175040</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>361780</v>
+        <v>175540</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>18.85676377909227</v>
+        <v>13.64931069841631</v>
       </c>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="6" t="n">
-        <v>326102</v>
+        <v>158486</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>31.86058349841461</v>
+        <v>25.87862650328735</v>
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="6" t="n">
-        <v>293991.8</v>
+        <v>143137.4</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>46.26258283394299</v>
+        <v>39.37657104292798</v>
       </c>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
       <c r="AD31" s="8" t="inlineStr"/>
       <c r="AE31" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:05</t>
+          <t>2025-10-18 10:13:11</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr"/>
@@ -3059,12 +3059,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3074,50 +3074,50 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 6.3% (접근 중!)</t>
+          <t>1차 매수선까지 14.3%</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>21150</v>
+        <v>8940</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>20900</v>
+        <v>8920</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>22500</v>
+        <v>9470</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>24817.5</v>
+        <v>9768</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>19854</v>
+        <v>7814.400000000001</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>19904</v>
+        <v>7824.400000000001</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>6.260048231511255</v>
+        <v>14.25796227186748</v>
       </c>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="8" t="inlineStr"/>
       <c r="O32" s="6" t="n">
-        <v>17963.6</v>
+        <v>7051.960000000001</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>17.73809258723194</v>
+        <v>26.77326587218303</v>
       </c>
       <c r="Q32" s="8" t="inlineStr"/>
       <c r="R32" s="8" t="inlineStr"/>
       <c r="S32" s="6" t="n">
-        <v>16217.24</v>
+        <v>6356.764000000001</v>
       </c>
       <c r="T32" s="7" t="n">
-        <v>30.41676635481745</v>
+        <v>40.63759485172012</v>
       </c>
       <c r="U32" s="8" t="inlineStr"/>
       <c r="V32" s="8" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       <c r="AD32" s="8" t="inlineStr"/>
       <c r="AE32" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:06</t>
+          <t>2025-10-18 10:13:11</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr"/>
@@ -3139,12 +3139,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3159,45 +3159,45 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.6%</t>
+          <t>1차 매수선까지 15.6%</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>25250</v>
+        <v>201000</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>25100</v>
+        <v>199800</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>27750</v>
+        <v>209500</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>27722.5</v>
+        <v>216725</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>22178</v>
+        <v>173380</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>22228</v>
+        <v>173880</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>13.59546517905344</v>
+        <v>15.59696342305038</v>
       </c>
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
       <c r="O33" s="6" t="n">
-        <v>20055.2</v>
+        <v>156992</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>25.90250907495312</v>
+        <v>28.03200163065634</v>
       </c>
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
       <c r="S33" s="6" t="n">
-        <v>18099.68</v>
+        <v>141792.8</v>
       </c>
       <c r="T33" s="7" t="n">
-        <v>39.50522882172503</v>
+        <v>41.75613994504656</v>
       </c>
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AD33" s="8" t="inlineStr"/>
       <c r="AE33" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:06</t>
+          <t>2025-10-18 10:13:11</t>
         </is>
       </c>
       <c r="AF33" s="8" t="inlineStr"/>
@@ -3219,12 +3219,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3239,45 +3239,45 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.6%</t>
+          <t>1차 매수선까지 64.3%</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>20200</v>
+        <v>64400</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>20050</v>
+        <v>63700</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>22200</v>
+        <v>70800</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>21599.5</v>
+        <v>48932.5</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>17279.6</v>
+        <v>39146</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>17329.6</v>
+        <v>39196</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>16.56356753762347</v>
+        <v>64.30247984488213</v>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
       <c r="O34" s="6" t="n">
-        <v>15646.64</v>
+        <v>35326.4</v>
       </c>
       <c r="P34" s="7" t="n">
-        <v>29.10120000204514</v>
+        <v>82.29992300375922</v>
       </c>
       <c r="Q34" s="8" t="inlineStr"/>
       <c r="R34" s="8" t="inlineStr"/>
       <c r="S34" s="6" t="n">
-        <v>14131.976</v>
+        <v>31843.76</v>
       </c>
       <c r="T34" s="7" t="n">
-        <v>42.93825576833697</v>
+        <v>102.2374242237725</v>
       </c>
       <c r="U34" s="8" t="inlineStr"/>
       <c r="V34" s="8" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       <c r="AD34" s="8" t="inlineStr"/>
       <c r="AE34" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:06</t>
+          <t>2025-10-18 10:13:12</t>
         </is>
       </c>
       <c r="AF34" s="8" t="inlineStr"/>
@@ -3299,12 +3299,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3319,45 +3319,45 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.9%</t>
+          <t>1차 매수선까지 13.5%</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>50400</v>
+        <v>95400</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>49600</v>
+        <v>94600</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>57700</v>
+        <v>99600</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>54755</v>
+        <v>104960</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>43804</v>
+        <v>83968</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>43854</v>
+        <v>84068</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>14.9268025721713</v>
+        <v>13.47956416234477</v>
       </c>
       <c r="M35" s="8" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
       <c r="O35" s="6" t="n">
-        <v>39518.6</v>
+        <v>75761.2</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>27.53488230858381</v>
+        <v>25.9219758926733</v>
       </c>
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="6" t="n">
-        <v>35616.74</v>
+        <v>68285.08</v>
       </c>
       <c r="T35" s="7" t="n">
-        <v>41.5064938565405</v>
+        <v>39.70841068063477</v>
       </c>
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       <c r="AD35" s="8" t="inlineStr"/>
       <c r="AE35" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:07</t>
+          <t>2025-10-18 10:13:12</t>
         </is>
       </c>
       <c r="AF35" s="8" t="inlineStr"/>
@@ -3379,12 +3379,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3394,50 +3394,50 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.3%</t>
+          <t>1차 매수선까지 0.9% (접근 중!)</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47000</v>
+        <v>166300</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>46350</v>
+        <v>166000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>49250</v>
+        <v>179300</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>45025</v>
+        <v>205420</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>36020</v>
+        <v>164336</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>36070</v>
+        <v>164836</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>30.30219018574993</v>
+        <v>0.8881555000121333</v>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="6" t="n">
-        <v>32513</v>
+        <v>148852.4</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>44.55756159074832</v>
+        <v>11.72140993359866</v>
       </c>
       <c r="Q36" s="8" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
       <c r="S36" s="6" t="n">
-        <v>29311.7</v>
+        <v>134467.16</v>
       </c>
       <c r="T36" s="7" t="n">
-        <v>60.34552755384368</v>
+        <v>23.67331919555674</v>
       </c>
       <c r="U36" s="8" t="inlineStr"/>
       <c r="V36" s="8" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="AD36" s="8" t="inlineStr"/>
       <c r="AE36" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:07</t>
+          <t>2025-10-18 10:13:12</t>
         </is>
       </c>
       <c r="AF36" s="8" t="inlineStr"/>
@@ -3459,12 +3459,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3474,50 +3474,50 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.8% (접근 중!)</t>
+          <t>1차 매수선까지 17.4%</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>22600</v>
+        <v>424500</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>22500</v>
+        <v>420000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>23900</v>
+        <v>435000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>25667.5</v>
+        <v>451325</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>20534</v>
+        <v>361060</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>20584</v>
+        <v>361560</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>9.794014768752429</v>
+        <v>17.40789910388317</v>
       </c>
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="6" t="n">
-        <v>18575.6</v>
+        <v>325904</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>21.66497986606084</v>
+        <v>30.25308066178998</v>
       </c>
       <c r="Q37" s="8" t="inlineStr"/>
       <c r="R37" s="8" t="inlineStr"/>
       <c r="S37" s="6" t="n">
-        <v>16768.04</v>
+        <v>293813.6</v>
       </c>
       <c r="T37" s="7" t="n">
-        <v>34.78021283346175</v>
+        <v>44.4793569800717</v>
       </c>
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="AD37" s="8" t="inlineStr"/>
       <c r="AE37" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:07</t>
+          <t>2025-10-18 10:13:12</t>
         </is>
       </c>
       <c r="AF37" s="8" t="inlineStr"/>
@@ -3539,12 +3539,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3554,50 +3554,50 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.1%</t>
+          <t>1차 매수선까지 7.5% (접근 중!)</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>422500</v>
+        <v>21400</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>420500</v>
+        <v>20900</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>434500</v>
+        <v>22500</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>411575</v>
+        <v>24830</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>329260</v>
+        <v>19864</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>329760</v>
+        <v>19914</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>28.12348374575449</v>
+        <v>7.46208697398815</v>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
       <c r="O38" s="6" t="n">
-        <v>297284</v>
+        <v>17972.6</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>42.11999300332342</v>
+        <v>19.07014010215549</v>
       </c>
       <c r="Q38" s="8" t="inlineStr"/>
       <c r="R38" s="8" t="inlineStr"/>
       <c r="S38" s="6" t="n">
-        <v>268055.6</v>
+        <v>16225.34</v>
       </c>
       <c r="T38" s="7" t="n">
-        <v>57.61655417756613</v>
+        <v>31.89245957249585</v>
       </c>
       <c r="U38" s="8" t="inlineStr"/>
       <c r="V38" s="8" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       <c r="AD38" s="8" t="inlineStr"/>
       <c r="AE38" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:08</t>
+          <t>2025-10-18 10:13:13</t>
         </is>
       </c>
       <c r="AF38" s="8" t="inlineStr"/>
@@ -3619,12 +3619,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3639,45 +3639,45 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.6%</t>
+          <t>1차 매수선까지 15.3%</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>201000</v>
+        <v>25650</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>200000</v>
+        <v>25100</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>206000</v>
+        <v>27750</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>199390</v>
+        <v>27742.5</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>159512</v>
+        <v>22194</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>160012</v>
+        <v>22244</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>25.61557883158763</v>
+        <v>15.31199424563927</v>
       </c>
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="6" t="n">
-        <v>144510.8</v>
+        <v>20069.6</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>39.08995037049132</v>
+        <v>27.80523777255151</v>
       </c>
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
       <c r="S39" s="6" t="n">
-        <v>130559.72</v>
+        <v>18112.64</v>
       </c>
       <c r="T39" s="7" t="n">
-        <v>53.95253605016921</v>
+        <v>41.61381223278327</v>
       </c>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
       <c r="AD39" s="8" t="inlineStr"/>
       <c r="AE39" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:08</t>
+          <t>2025-10-18 10:13:13</t>
         </is>
       </c>
       <c r="AF39" s="8" t="inlineStr"/>
@@ -3699,12 +3699,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3719,45 +3719,45 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.6%</t>
+          <t>1차 매수선까지 16.0%</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>22600</v>
+        <v>20100</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>21950</v>
+        <v>20050</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>22700</v>
+        <v>22200</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>21730</v>
+        <v>21594.5</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>17384</v>
+        <v>17275.6</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>17434</v>
+        <v>17325.6</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>29.63175404382242</v>
+        <v>16.01329824075355</v>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="6" t="n">
-        <v>15740.6</v>
+        <v>15643.04</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>43.57775434227412</v>
+        <v>28.49164868209758</v>
       </c>
       <c r="Q40" s="8" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
       <c r="S40" s="6" t="n">
-        <v>14216.54</v>
+        <v>14128.736</v>
       </c>
       <c r="T40" s="7" t="n">
-        <v>58.96976338827871</v>
+        <v>42.26325695377135</v>
       </c>
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="8" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       <c r="AD40" s="8" t="inlineStr"/>
       <c r="AE40" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:08</t>
+          <t>2025-10-18 10:13:13</t>
         </is>
       </c>
       <c r="AF40" s="8" t="inlineStr"/>
@@ -3779,12 +3779,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3799,45 +3799,45 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.6%</t>
+          <t>1차 매수선까지 10.1%</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1575000</v>
+        <v>48200</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1570000</v>
+        <v>47000</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1625000</v>
+        <v>57700</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1429650</v>
+        <v>54645</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1143720</v>
+        <v>43716</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>1144720</v>
+        <v>43766</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>37.58823118317143</v>
+        <v>10.1311520358269</v>
       </c>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
       <c r="O41" s="6" t="n">
-        <v>1031248</v>
+        <v>39439.4</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>52.72756892619428</v>
+        <v>22.21281256814251</v>
       </c>
       <c r="Q41" s="8" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
       <c r="S41" s="6" t="n">
-        <v>929123.2000000001</v>
+        <v>35545.46</v>
       </c>
       <c r="T41" s="7" t="n">
-        <v>69.51465639863474</v>
+        <v>35.60100220956488</v>
       </c>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       <c r="AD41" s="8" t="inlineStr"/>
       <c r="AE41" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:08</t>
+          <t>2025-10-18 10:13:14</t>
         </is>
       </c>
       <c r="AF41" s="8" t="inlineStr"/>
@@ -3859,12 +3859,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3874,50 +3874,50 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.6% (접근 중!)</t>
+          <t>1차 매수선까지 28.9%</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>431500</v>
+        <v>46450</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>430500</v>
+        <v>46200</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>452000</v>
+        <v>49250</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>491550</v>
+        <v>44997.5</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>393240</v>
+        <v>35998</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>393740</v>
+        <v>36048</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>9.590084827551177</v>
+        <v>28.85596981802042</v>
       </c>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="8" t="inlineStr"/>
       <c r="O42" s="6" t="n">
-        <v>354866</v>
+        <v>32493.2</v>
       </c>
       <c r="P42" s="7" t="n">
-        <v>21.59519367874071</v>
+        <v>42.95298708652887</v>
       </c>
       <c r="Q42" s="8" t="inlineStr"/>
       <c r="R42" s="8" t="inlineStr"/>
       <c r="S42" s="6" t="n">
-        <v>319879.4</v>
+        <v>29293.88</v>
       </c>
       <c r="T42" s="7" t="n">
-        <v>34.89458839800248</v>
+        <v>58.56554338312302</v>
       </c>
       <c r="U42" s="8" t="inlineStr"/>
       <c r="V42" s="8" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       <c r="AD42" s="8" t="inlineStr"/>
       <c r="AE42" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:09</t>
+          <t>2025-10-18 10:13:14</t>
         </is>
       </c>
       <c r="AF42" s="8" t="inlineStr"/>
@@ -3939,12 +3939,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3954,50 +3954,50 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.9%</t>
+          <t>1차 매수선까지 9.6% (접근 중!)</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>40400</v>
+        <v>22550</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>40150</v>
+        <v>22500</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>42350</v>
+        <v>23900</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>41717.5</v>
+        <v>25665</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>33374</v>
+        <v>20532</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>33424</v>
+        <v>20582</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>20.87123025370991</v>
+        <v>9.561752988047809</v>
       </c>
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="6" t="n">
-        <v>30131.6</v>
+        <v>18573.8</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>34.07850894077977</v>
+        <v>21.40757410976753</v>
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="6" t="n">
-        <v>27168.44</v>
+        <v>16766.42</v>
       </c>
       <c r="T43" s="7" t="n">
-        <v>48.70194976229772</v>
+        <v>34.49502040387872</v>
       </c>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       <c r="AD43" s="8" t="inlineStr"/>
       <c r="AE43" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:09</t>
+          <t>2025-10-18 10:13:14</t>
         </is>
       </c>
       <c r="AF43" s="8" t="inlineStr"/>
@@ -4019,12 +4019,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4034,50 +4034,50 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 7.7% (접근 중!)</t>
+          <t>1차 매수선까지 25.5%</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>16020</v>
+        <v>413500</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>15950</v>
+        <v>408500</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>16540</v>
+        <v>434500</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>18537.5</v>
+        <v>411125</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>14830</v>
+        <v>328900</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>14880</v>
+        <v>329400</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>7.661290322580645</v>
+        <v>25.53126897389192</v>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="6" t="n">
-        <v>13442</v>
+        <v>296960</v>
       </c>
       <c r="P44" s="7" t="n">
-        <v>19.17869364677875</v>
+        <v>39.24434267241379</v>
       </c>
       <c r="Q44" s="8" t="inlineStr"/>
       <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="6" t="n">
-        <v>12147.8</v>
+        <v>267764</v>
       </c>
       <c r="T44" s="7" t="n">
-        <v>31.87573058496188</v>
+        <v>54.42703276019181</v>
       </c>
       <c r="U44" s="8" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       <c r="AD44" s="8" t="inlineStr"/>
       <c r="AE44" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:09</t>
+          <t>2025-10-18 10:13:14</t>
         </is>
       </c>
       <c r="AF44" s="8" t="inlineStr"/>
@@ -4099,12 +4099,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4119,45 +4119,45 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 12.1%</t>
+          <t>1차 매수선까지 24.7%</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>86500</v>
+        <v>199500</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>84600</v>
+        <v>194100</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>89400</v>
+        <v>206000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>96300</v>
+        <v>199315</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>77040</v>
+        <v>159452</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>77140</v>
+        <v>159952</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>12.1337827326938</v>
+        <v>24.72491747524257</v>
       </c>
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="6" t="n">
-        <v>69526</v>
+        <v>144456.8</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>24.41388832954578</v>
+        <v>38.10357144834994</v>
       </c>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
       <c r="S45" s="6" t="n">
-        <v>62673.4</v>
+        <v>130511.12</v>
       </c>
       <c r="T45" s="7" t="n">
-        <v>38.01708539827104</v>
+        <v>52.86053786068188</v>
       </c>
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       <c r="AD45" s="8" t="inlineStr"/>
       <c r="AE45" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:09</t>
+          <t>2025-10-18 10:13:15</t>
         </is>
       </c>
       <c r="AF45" s="8" t="inlineStr"/>
@@ -4179,12 +4179,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4199,45 +4199,45 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.3%</t>
+          <t>1차 매수선까지 27.5%</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>14310</v>
+        <v>22200</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>14120</v>
+        <v>21600</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>14470</v>
+        <v>22700</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>13985</v>
+        <v>21710</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>11188</v>
+        <v>17368</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>11238</v>
+        <v>17418</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>27.33582487987186</v>
+        <v>27.45435756114365</v>
       </c>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="6" t="n">
-        <v>10164.2</v>
+        <v>15726.2</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>40.78825682296687</v>
+        <v>41.1656980071473</v>
       </c>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="6" t="n">
-        <v>9157.780000000001</v>
+        <v>14203.58</v>
       </c>
       <c r="T46" s="7" t="n">
-        <v>56.26057843713214</v>
+        <v>56.29862330482877</v>
       </c>
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       <c r="AD46" s="8" t="inlineStr"/>
       <c r="AE46" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:10</t>
+          <t>2025-10-18 10:13:15</t>
         </is>
       </c>
       <c r="AF46" s="8" t="inlineStr"/>
@@ -4259,12 +4259,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4279,45 +4279,45 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.6%</t>
+          <t>1차 매수선까지 38.0%</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>42900</v>
+        <v>1580000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>39450</v>
+        <v>1544000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>43300</v>
+        <v>1625000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>37015</v>
+        <v>1429900</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>29612</v>
+        <v>1143920</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>29662</v>
+        <v>1144920</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>44.62949227968445</v>
+        <v>38.00090836040946</v>
       </c>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="6" t="n">
-        <v>26745.8</v>
+        <v>1031428</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>60.39901592025664</v>
+        <v>53.18568043528003</v>
       </c>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
       <c r="S47" s="6" t="n">
-        <v>24121.22</v>
+        <v>929285.2000000001</v>
       </c>
       <c r="T47" s="7" t="n">
-        <v>77.85170070170579</v>
+        <v>70.02315327953139</v>
       </c>
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       <c r="AD47" s="8" t="inlineStr"/>
       <c r="AE47" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:10</t>
+          <t>2025-10-18 10:13:15</t>
         </is>
       </c>
       <c r="AF47" s="8" t="inlineStr"/>
@@ -4339,12 +4339,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4354,50 +4354,50 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.6%</t>
+          <t>1차 매수선까지 9.8% (접근 중!)</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>75700</v>
+        <v>432500</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>75500</v>
+        <v>429000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>78250</v>
+        <v>452000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>79635</v>
+        <v>491600</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>63708</v>
+        <v>393280</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>63808</v>
+        <v>393780</v>
       </c>
       <c r="L48" s="7" t="n">
-        <v>18.63716148445336</v>
+        <v>9.832901620194017</v>
       </c>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
       <c r="O48" s="6" t="n">
-        <v>57527.2</v>
+        <v>354902</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>31.58992615667023</v>
+        <v>21.86462741827321</v>
       </c>
       <c r="Q48" s="8" t="inlineStr"/>
       <c r="R48" s="8" t="inlineStr"/>
       <c r="S48" s="6" t="n">
-        <v>51874.48</v>
+        <v>319911.8</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>45.92917365147563</v>
+        <v>35.19351271194123</v>
       </c>
       <c r="U48" s="8" t="inlineStr"/>
       <c r="V48" s="8" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
       <c r="AD48" s="8" t="inlineStr"/>
       <c r="AE48" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:10</t>
+          <t>2025-10-18 10:13:15</t>
         </is>
       </c>
       <c r="AF48" s="8" t="inlineStr"/>
@@ -4419,12 +4419,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4439,45 +4439,45 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 20.0%</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>241500</v>
+        <v>40100</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>234500</v>
+        <v>40100</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>245500</v>
+        <v>42350</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>235425</v>
+        <v>41702.5</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>188340</v>
+        <v>33362</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>188840</v>
+        <v>33412</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>27.88604109298877</v>
+        <v>20.01676044534898</v>
       </c>
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="6" t="n">
-        <v>170456</v>
+        <v>30120.8</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>41.67879100765007</v>
+        <v>33.13059414092587</v>
       </c>
       <c r="Q49" s="8" t="inlineStr"/>
       <c r="R49" s="8" t="inlineStr"/>
       <c r="S49" s="6" t="n">
-        <v>153910.4</v>
+        <v>27158.72</v>
       </c>
       <c r="T49" s="7" t="n">
-        <v>56.90947460340562</v>
+        <v>47.65055201423336</v>
       </c>
       <c r="U49" s="8" t="inlineStr"/>
       <c r="V49" s="8" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       <c r="AD49" s="8" t="inlineStr"/>
       <c r="AE49" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:11</t>
+          <t>2025-10-18 10:13:16</t>
         </is>
       </c>
       <c r="AF49" s="8" t="inlineStr"/>
@@ -4499,12 +4499,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4514,50 +4514,50 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.4%</t>
+          <t>1차 매수선까지 7.7% (접근 중!)</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>101900</v>
+        <v>16020</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>100700</v>
+        <v>15950</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>103500</v>
+        <v>16540</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>105680</v>
+        <v>18537.5</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>84544</v>
+        <v>14830</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>84644</v>
+        <v>14880</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>20.3865601814659</v>
+        <v>7.661290322580645</v>
       </c>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
       <c r="O50" s="6" t="n">
-        <v>76279.60000000001</v>
+        <v>13442</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>33.5874860382068</v>
+        <v>19.17869364677875</v>
       </c>
       <c r="Q50" s="8" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="6" t="n">
-        <v>68751.64000000001</v>
+        <v>12147.8</v>
       </c>
       <c r="T50" s="7" t="n">
-        <v>48.21464622516638</v>
+        <v>31.87573058496188</v>
       </c>
       <c r="U50" s="8" t="inlineStr"/>
       <c r="V50" s="8" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       <c r="AD50" s="8" t="inlineStr"/>
       <c r="AE50" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:11</t>
+          <t>2025-10-18 10:13:16</t>
         </is>
       </c>
       <c r="AF50" s="8" t="inlineStr"/>
@@ -4579,12 +4579,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4599,45 +4599,45 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 11.9%</t>
+          <t>1차 매수선까지 10.2%</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>915000</v>
+        <v>84900</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>912000</v>
+        <v>82300</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>947000</v>
+        <v>89400</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1020800</v>
+        <v>96220</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>816640</v>
+        <v>76976</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>817640</v>
+        <v>77076</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>11.90744092754758</v>
+        <v>10.15101977269189</v>
       </c>
       <c r="M51" s="8" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="6" t="n">
-        <v>736876</v>
+        <v>69468.40000000001</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>24.17285947703548</v>
+        <v>22.21384111336952</v>
       </c>
       <c r="Q51" s="8" t="inlineStr"/>
       <c r="R51" s="8" t="inlineStr"/>
       <c r="S51" s="6" t="n">
-        <v>664188.4</v>
+        <v>62621.56000000001</v>
       </c>
       <c r="T51" s="7" t="n">
-        <v>37.76211689333929</v>
+        <v>35.57630950107276</v>
       </c>
       <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       <c r="AD51" s="8" t="inlineStr"/>
       <c r="AE51" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:11</t>
+          <t>2025-10-18 10:13:16</t>
         </is>
       </c>
       <c r="AF51" s="8" t="inlineStr"/>
@@ -4659,12 +4659,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4679,45 +4679,45 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.1%</t>
+          <t>1차 매수선까지 26.4%</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>242000</v>
+        <v>14200</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>239000</v>
+        <v>14020</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>246000</v>
+        <v>14470</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>220025</v>
+        <v>13979.5</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>176020</v>
+        <v>11183.6</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>176520</v>
+        <v>11233.6</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>37.09494674824382</v>
+        <v>26.40649480131035</v>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
       <c r="O52" s="6" t="n">
-        <v>159368</v>
+        <v>10160.24</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>51.84980673660961</v>
+        <v>39.76047809894255</v>
       </c>
       <c r="Q52" s="8" t="inlineStr"/>
       <c r="R52" s="8" t="inlineStr"/>
       <c r="S52" s="6" t="n">
-        <v>143931.2</v>
+        <v>9154.216</v>
       </c>
       <c r="T52" s="7" t="n">
-        <v>68.13588714608089</v>
+        <v>55.11978305952142</v>
       </c>
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
       <c r="AD52" s="8" t="inlineStr"/>
       <c r="AE52" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:11</t>
+          <t>2025-10-18 10:13:17</t>
         </is>
       </c>
       <c r="AF52" s="8" t="inlineStr"/>
@@ -4739,12 +4739,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4759,45 +4759,45 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 12.1%</t>
+          <t>1차 매수선까지 19.1%</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>51600</v>
+        <v>76000</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>51100</v>
+        <v>75400</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>53600</v>
+        <v>78250</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>57495</v>
+        <v>79650</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>45996</v>
+        <v>63720</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>46046</v>
+        <v>63820</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>12.06185119228597</v>
+        <v>19.08492635537449</v>
       </c>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
       <c r="O53" s="6" t="n">
-        <v>41491.4</v>
+        <v>57538</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>24.36312103231031</v>
+        <v>32.0866210156766</v>
       </c>
       <c r="Q53" s="8" t="inlineStr"/>
       <c r="R53" s="8" t="inlineStr"/>
       <c r="S53" s="6" t="n">
-        <v>37392.26</v>
+        <v>51884.2</v>
       </c>
       <c r="T53" s="7" t="n">
-        <v>37.99647306688603</v>
+        <v>46.48004594847756</v>
       </c>
       <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       <c r="AD53" s="8" t="inlineStr"/>
       <c r="AE53" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:12</t>
+          <t>2025-10-18 10:13:17</t>
         </is>
       </c>
       <c r="AF53" s="8" t="inlineStr"/>
@@ -4819,12 +4819,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4839,45 +4839,45 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.5%</t>
+          <t>1차 매수선까지 25.6%</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>29900</v>
+        <v>237000</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>29100</v>
+        <v>225000</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>30200</v>
+        <v>245500</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>29255</v>
+        <v>235200</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>23404</v>
+        <v>188160</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>23454</v>
+        <v>188660</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>27.48358488957108</v>
+        <v>25.62281352697975</v>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
       <c r="O54" s="6" t="n">
-        <v>21158.6</v>
+        <v>170294</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>41.31369750361554</v>
+        <v>39.1710806017828</v>
       </c>
       <c r="Q54" s="8" t="inlineStr"/>
       <c r="R54" s="8" t="inlineStr"/>
       <c r="S54" s="6" t="n">
-        <v>19092.74</v>
+        <v>153764.6</v>
       </c>
       <c r="T54" s="7" t="n">
-        <v>56.60402854697648</v>
+        <v>54.13170521693549</v>
       </c>
       <c r="U54" s="8" t="inlineStr"/>
       <c r="V54" s="8" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       <c r="AD54" s="8" t="inlineStr"/>
       <c r="AE54" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:12</t>
+          <t>2025-10-18 10:13:17</t>
         </is>
       </c>
       <c r="AF54" s="8" t="inlineStr"/>
@@ -4899,12 +4899,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.3%</t>
+          <t>1차 매수선까지 19.0%</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>206000</v>
+        <v>100700</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>197500</v>
+        <v>100100</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>208000</v>
+        <v>103500</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>198475</v>
+        <v>105620</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>158780</v>
+        <v>84496</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>159280</v>
+        <v>84596</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>29.33199397287795</v>
+        <v>19.03636105726039</v>
       </c>
       <c r="M55" s="8" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
       <c r="O55" s="6" t="n">
-        <v>143852</v>
+        <v>76236.40000000001</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>43.20273614548286</v>
+        <v>32.08913327491853</v>
       </c>
       <c r="Q55" s="8" t="inlineStr"/>
       <c r="R55" s="8" t="inlineStr"/>
       <c r="S55" s="6" t="n">
-        <v>129966.8</v>
+        <v>68712.76000000001</v>
       </c>
       <c r="T55" s="7" t="n">
-        <v>58.50201743829962</v>
+        <v>46.55211055413869</v>
       </c>
       <c r="U55" s="8" t="inlineStr"/>
       <c r="V55" s="8" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       <c r="AD55" s="8" t="inlineStr"/>
       <c r="AE55" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:12</t>
+          <t>2025-10-18 10:13:17</t>
         </is>
       </c>
       <c r="AF55" s="8" t="inlineStr"/>
@@ -4979,12 +4979,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4999,45 +4999,45 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.8%</t>
+          <t>1차 매수선까지 12.0%</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>51500</v>
+        <v>916000</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>51000</v>
+        <v>905000</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>52500</v>
+        <v>947000</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>55990</v>
+        <v>1020850</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>44792</v>
+        <v>816680</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>44842</v>
+        <v>817680</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>14.847687435886</v>
+        <v>12.02426377066823</v>
       </c>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
       <c r="O56" s="6" t="n">
-        <v>40407.8</v>
+        <v>736912</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>27.45064071788119</v>
+        <v>24.30249473478516</v>
       </c>
       <c r="Q56" s="8" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
       <c r="S56" s="6" t="n">
-        <v>36417.02</v>
+        <v>664220.8</v>
       </c>
       <c r="T56" s="7" t="n">
-        <v>41.41739219738461</v>
+        <v>37.90594934696414</v>
       </c>
       <c r="U56" s="8" t="inlineStr"/>
       <c r="V56" s="8" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       <c r="AD56" s="8" t="inlineStr"/>
       <c r="AE56" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:12</t>
+          <t>2025-10-18 10:13:18</t>
         </is>
       </c>
       <c r="AF56" s="8" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5079,45 +5079,45 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.6%</t>
+          <t>1차 매수선까지 11.4%</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>14800</v>
+        <v>51300</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>14640</v>
+        <v>51000</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>15970</v>
+        <v>53600</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>15402</v>
+        <v>57480</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>12321.6</v>
+        <v>45984</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>12371.6</v>
+        <v>46034</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>19.62882731417116</v>
+        <v>11.43937089976973</v>
       </c>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
       <c r="O57" s="6" t="n">
-        <v>11184.44</v>
+        <v>41480.6</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>32.32669673224586</v>
+        <v>23.67227089289933</v>
       </c>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
       <c r="S57" s="6" t="n">
-        <v>10115.996</v>
+        <v>37382.54</v>
       </c>
       <c r="T57" s="7" t="n">
-        <v>46.30294436652603</v>
+        <v>37.22984045492895</v>
       </c>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       <c r="AD57" s="8" t="inlineStr"/>
       <c r="AE57" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:13</t>
+          <t>2025-10-18 10:13:18</t>
         </is>
       </c>
       <c r="AF57" s="8" t="inlineStr"/>
@@ -5139,12 +5139,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5159,45 +5159,45 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.8%</t>
+          <t>1차 매수선까지 25.5%</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>30700</v>
+        <v>29400</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>28800</v>
+        <v>28500</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>31000</v>
+        <v>30200</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>30440</v>
+        <v>29230</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>24352</v>
+        <v>23384</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>24402</v>
+        <v>23434</v>
       </c>
       <c r="L58" s="7" t="n">
-        <v>25.80935988853373</v>
+        <v>25.45873517111889</v>
       </c>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="6" t="n">
-        <v>22011.8</v>
+        <v>21140.6</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>39.47064756176233</v>
+        <v>39.0689005988477</v>
       </c>
       <c r="Q58" s="8" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="6" t="n">
-        <v>19860.62</v>
+        <v>19076.54</v>
       </c>
       <c r="T58" s="7" t="n">
-        <v>54.57724884721625</v>
+        <v>54.11599797447545</v>
       </c>
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       <c r="AD58" s="8" t="inlineStr"/>
       <c r="AE58" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:13</t>
+          <t>2025-10-18 10:13:18</t>
         </is>
       </c>
       <c r="AF58" s="8" t="inlineStr"/>
@@ -5219,12 +5219,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5239,45 +5239,45 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.3%</t>
+          <t>1차 매수선까지 27.2%</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2620</v>
+        <v>202500</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>2540</v>
+        <v>196000</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>2855</v>
+        <v>208000</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>2628.75</v>
+        <v>198300</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>2103</v>
+        <v>158640</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>2108</v>
+        <v>159140</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>24.28842504743833</v>
+        <v>27.24644966695991</v>
       </c>
       <c r="M59" s="8" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="6" t="n">
-        <v>1902.2</v>
+        <v>143726</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>37.73525391651771</v>
+        <v>40.8930882373405</v>
       </c>
       <c r="Q59" s="8" t="inlineStr"/>
       <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="6" t="n">
-        <v>1716.98</v>
+        <v>129853.4</v>
       </c>
       <c r="T59" s="7" t="n">
-        <v>52.59350720451025</v>
+        <v>55.94508884634518</v>
       </c>
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
@@ -5291,7 +5291,7 @@
       <c r="AD59" s="8" t="inlineStr"/>
       <c r="AE59" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:13</t>
+          <t>2025-10-18 10:13:19</t>
         </is>
       </c>
       <c r="AF59" s="8" t="inlineStr"/>
@@ -5299,12 +5299,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5314,50 +5314,50 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 5.3% (접근 중!)</t>
+          <t>1차 매수선까지 13.6%</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>6570</v>
+        <v>50900</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>6510</v>
+        <v>50200</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>6710</v>
+        <v>52500</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>7787.5</v>
+        <v>55960</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>6230</v>
+        <v>44768</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>6240</v>
+        <v>44818</v>
       </c>
       <c r="L60" s="7" t="n">
-        <v>5.288461538461538</v>
+        <v>13.57044044803427</v>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
       <c r="O60" s="6" t="n">
-        <v>5626</v>
+        <v>40386.2</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>16.77923924635621</v>
+        <v>26.03314993735483</v>
       </c>
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="6" t="n">
-        <v>5073.400000000001</v>
+        <v>36397.58</v>
       </c>
       <c r="T60" s="7" t="n">
-        <v>29.49895533567232</v>
+        <v>39.84446218677175</v>
       </c>
       <c r="U60" s="8" t="inlineStr"/>
       <c r="V60" s="8" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
       <c r="AD60" s="8" t="inlineStr"/>
       <c r="AE60" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:14</t>
+          <t>2025-10-18 10:13:19</t>
         </is>
       </c>
       <c r="AF60" s="8" t="inlineStr"/>
@@ -5379,12 +5379,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -5399,45 +5399,45 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 61.4%</t>
+          <t>1차 매수선까지 18.7%</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>195000</v>
+        <v>14680</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>185000</v>
+        <v>14300</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>201000</v>
+        <v>15970</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>150420</v>
+        <v>15396</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>120336</v>
+        <v>12316.8</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>120836</v>
+        <v>12366.8</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>61.37574894898871</v>
+        <v>18.70491962350809</v>
       </c>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="6" t="n">
-        <v>109252.4</v>
+        <v>11180.12</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>78.48578154804837</v>
+        <v>31.30449404836441</v>
       </c>
       <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="6" t="n">
-        <v>98427.16</v>
+        <v>10112.108</v>
       </c>
       <c r="T61" s="7" t="n">
-        <v>98.11604845654391</v>
+        <v>45.17250013548114</v>
       </c>
       <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
@@ -5451,7 +5451,7 @@
       <c r="AD61" s="8" t="inlineStr"/>
       <c r="AE61" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:14</t>
+          <t>2025-10-18 10:13:19</t>
         </is>
       </c>
       <c r="AF61" s="8" t="inlineStr"/>
@@ -5459,12 +5459,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -5479,45 +5479,45 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 11.4%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>132100</v>
+        <v>30200</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>131200</v>
+        <v>28800</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>137200</v>
+        <v>31000</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>147665</v>
+        <v>30415</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>118132</v>
+        <v>24332</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>118632</v>
+        <v>24382</v>
       </c>
       <c r="L62" s="7" t="n">
-        <v>11.352754737339</v>
+        <v>23.86186531047494</v>
       </c>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
       <c r="O62" s="6" t="n">
-        <v>107268.8</v>
+        <v>21993.8</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>23.14857628686067</v>
+        <v>37.31142412861807</v>
       </c>
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="6" t="n">
-        <v>96641.92</v>
+        <v>19844.42</v>
       </c>
       <c r="T62" s="7" t="n">
-        <v>36.6901650960577</v>
+        <v>52.18383807639631</v>
       </c>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       <c r="AD62" s="8" t="inlineStr"/>
       <c r="AE62" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:14</t>
+          <t>2025-10-18 10:13:19</t>
         </is>
       </c>
       <c r="AF62" s="8" t="inlineStr"/>
@@ -5539,12 +5539,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5559,45 +5559,45 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.2%</t>
+          <t>1차 매수선까지 23.8%</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>37550</v>
+        <v>2610</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>37200</v>
+        <v>2540</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>38550</v>
+        <v>2855</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>38337.5</v>
+        <v>2628.25</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>30670</v>
+        <v>2102.6</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>30720</v>
+        <v>2107.6</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>22.23307291666666</v>
+        <v>23.83754033023344</v>
       </c>
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
       <c r="O63" s="6" t="n">
-        <v>27698</v>
+        <v>1901.84</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>35.56935518810022</v>
+        <v>37.23551928658563</v>
       </c>
       <c r="Q63" s="8" t="inlineStr"/>
       <c r="R63" s="8" t="inlineStr"/>
       <c r="S63" s="6" t="n">
-        <v>24978.2</v>
+        <v>1716.656</v>
       </c>
       <c r="T63" s="7" t="n">
-        <v>50.33108870935455</v>
+        <v>52.03977966465034</v>
       </c>
       <c r="U63" s="8" t="inlineStr"/>
       <c r="V63" s="8" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       <c r="AD63" s="8" t="inlineStr"/>
       <c r="AE63" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:14</t>
+          <t>2025-10-18 10:13:20</t>
         </is>
       </c>
       <c r="AF63" s="8" t="inlineStr"/>
@@ -5619,12 +5619,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -5639,45 +5639,45 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 8.4% (접근 중!)</t>
+          <t>1차 매수선까지 5.0% (접근 중!)</t>
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>9650</v>
+        <v>6550</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>9650</v>
+        <v>6510</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>10080</v>
+        <v>6710</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>11118.5</v>
+        <v>7786.5</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>8894.800000000001</v>
+        <v>6229.200000000001</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>8904.800000000001</v>
+        <v>6239.200000000001</v>
       </c>
       <c r="L64" s="7" t="n">
-        <v>8.368520348576036</v>
+        <v>4.981407872804193</v>
       </c>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="6" t="n">
-        <v>8024.320000000002</v>
+        <v>5625.280000000001</v>
       </c>
       <c r="P64" s="7" t="n">
-        <v>20.25941138937627</v>
+        <v>16.43864838728026</v>
       </c>
       <c r="Q64" s="8" t="inlineStr"/>
       <c r="R64" s="8" t="inlineStr"/>
       <c r="S64" s="6" t="n">
-        <v>7231.888000000002</v>
+        <v>5072.752</v>
       </c>
       <c r="T64" s="7" t="n">
-        <v>33.43680101240503</v>
+        <v>29.1212343911155</v>
       </c>
       <c r="U64" s="8" t="inlineStr"/>
       <c r="V64" s="8" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       <c r="AD64" s="8" t="inlineStr"/>
       <c r="AE64" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:15</t>
+          <t>2025-10-18 10:13:20</t>
         </is>
       </c>
       <c r="AF64" s="8" t="inlineStr"/>
@@ -5699,12 +5699,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -5714,50 +5714,50 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.5%</t>
+          <t>1차 매수선까지 10.0% (접근 중!)</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>258000</v>
+        <v>130400</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>250500</v>
+        <v>125100</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>267000</v>
+        <v>137200</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>221095</v>
+        <v>147580</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>176876</v>
+        <v>118064</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>177376</v>
+        <v>118564</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>45.45372541944796</v>
+        <v>9.982794102763066</v>
       </c>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="6" t="n">
-        <v>160138.4</v>
+        <v>107207.6</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>61.1106392970081</v>
+        <v>21.63316779780537</v>
       </c>
       <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="6" t="n">
-        <v>144624.56</v>
+        <v>96586.84000000001</v>
       </c>
       <c r="T65" s="7" t="n">
-        <v>78.39293685664455</v>
+        <v>35.00804043283742</v>
       </c>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       <c r="AD65" s="8" t="inlineStr"/>
       <c r="AE65" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:15</t>
+          <t>2025-10-18 10:13:20</t>
         </is>
       </c>
       <c r="AF65" s="8" t="inlineStr"/>
@@ -5779,12 +5779,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5799,45 +5799,45 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.6%</t>
+          <t>1차 매수선까지 20.2%</t>
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>295000</v>
+        <v>36900</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>281500</v>
+        <v>36800</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>300000</v>
+        <v>38550</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>279650</v>
+        <v>38305</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>223720</v>
+        <v>30644</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>224220</v>
+        <v>30694</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>31.56721077513157</v>
+        <v>20.21893529680068</v>
       </c>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
       <c r="O66" s="6" t="n">
-        <v>202298</v>
+        <v>27674.6</v>
       </c>
       <c r="P66" s="7" t="n">
-        <v>45.82447676200456</v>
+        <v>33.33526049156988</v>
       </c>
       <c r="Q66" s="8" t="inlineStr"/>
       <c r="R66" s="8" t="inlineStr"/>
       <c r="S66" s="6" t="n">
-        <v>182568.2</v>
+        <v>24957.14</v>
       </c>
       <c r="T66" s="7" t="n">
-        <v>61.58345210173513</v>
+        <v>47.85348000612248</v>
       </c>
       <c r="U66" s="8" t="inlineStr"/>
       <c r="V66" s="8" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       <c r="AD66" s="8" t="inlineStr"/>
       <c r="AE66" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:15</t>
+          <t>2025-10-18 10:13:21</t>
         </is>
       </c>
       <c r="AF66" s="8" t="inlineStr"/>
@@ -5859,12 +5859,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5874,50 +5874,50 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.9%</t>
+          <t>1차 매수선까지 7.6% (접근 중!)</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>93800</v>
+        <v>9580</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>93800</v>
+        <v>9550</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>98900</v>
+        <v>10080</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>95310</v>
+        <v>11115</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>76248</v>
+        <v>8892</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>76348</v>
+        <v>8902</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>22.8584900717766</v>
+        <v>7.616266007638734</v>
       </c>
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="6" t="n">
-        <v>68813.2</v>
+        <v>8021.8</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>36.3110565996059</v>
+        <v>19.42456805205814</v>
       </c>
       <c r="Q67" s="8" t="inlineStr"/>
       <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="6" t="n">
-        <v>62031.88</v>
+        <v>7229.62</v>
       </c>
       <c r="T67" s="7" t="n">
-        <v>51.21257005268905</v>
+        <v>32.51042240117738</v>
       </c>
       <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       <c r="AD67" s="8" t="inlineStr"/>
       <c r="AE67" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:15</t>
+          <t>2025-10-18 10:13:21</t>
         </is>
       </c>
       <c r="AF67" s="8" t="inlineStr"/>
@@ -5939,12 +5939,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5959,45 +5959,45 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.7%</t>
+          <t>1차 매수선까지 44.4%</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>83300</v>
+        <v>256000</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>81700</v>
+        <v>244000</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>85400</v>
+        <v>267000</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>86855</v>
+        <v>220995</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>69484</v>
+        <v>176796</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>69584</v>
+        <v>177296</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>19.71142791446309</v>
+        <v>44.39130042414944</v>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="6" t="n">
-        <v>62725.6</v>
+        <v>160066.4</v>
       </c>
       <c r="P68" s="7" t="n">
-        <v>32.80064279975002</v>
+        <v>59.93362754456901</v>
       </c>
       <c r="Q68" s="8" t="inlineStr"/>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="6" t="n">
-        <v>56553.04</v>
+        <v>144559.76</v>
       </c>
       <c r="T68" s="7" t="n">
-        <v>47.29535317641633</v>
+        <v>77.08939195803866</v>
       </c>
       <c r="U68" s="8" t="inlineStr"/>
       <c r="V68" s="8" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="AD68" s="8" t="inlineStr"/>
       <c r="AE68" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:16</t>
+          <t>2025-10-18 10:13:21</t>
         </is>
       </c>
       <c r="AF68" s="8" t="inlineStr"/>
@@ -6019,12 +6019,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -6039,45 +6039,45 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.7%</t>
+          <t>1차 매수선까지 29.0%</t>
         </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>221000</v>
+        <v>289000</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>216000</v>
+        <v>281500</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>227000</v>
+        <v>300000</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>220975</v>
+        <v>279350</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>176780</v>
+        <v>223480</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>177280</v>
+        <v>223980</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>24.6615523465704</v>
+        <v>29.02937762300206</v>
       </c>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="6" t="n">
-        <v>160052</v>
+        <v>202082</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>38.08012395971309</v>
+        <v>43.01125285775081</v>
       </c>
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="6" t="n">
-        <v>144546.8</v>
+        <v>182373.8</v>
       </c>
       <c r="T69" s="7" t="n">
-        <v>52.89165861852353</v>
+        <v>58.46574453128682</v>
       </c>
       <c r="U69" s="8" t="inlineStr"/>
       <c r="V69" s="8" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       <c r="AD69" s="8" t="inlineStr"/>
       <c r="AE69" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:16</t>
+          <t>2025-10-18 10:13:21</t>
         </is>
       </c>
       <c r="AF69" s="8" t="inlineStr"/>
@@ -6099,12 +6099,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -6119,45 +6119,45 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.3%</t>
+          <t>1차 매수선까지 23.6%</t>
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>116600</v>
+        <v>94400</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>111900</v>
+        <v>93200</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>119000</v>
+        <v>98900</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>105275</v>
+        <v>95340</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>84220</v>
+        <v>76272</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>84320</v>
+        <v>76372</v>
       </c>
       <c r="L70" s="7" t="n">
-        <v>38.28273244781784</v>
+        <v>23.60550987272823</v>
       </c>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
       <c r="O70" s="6" t="n">
-        <v>75988</v>
+        <v>68834.8</v>
       </c>
       <c r="P70" s="7" t="n">
-        <v>53.44528083381586</v>
+        <v>37.13993503286128</v>
       </c>
       <c r="Q70" s="8" t="inlineStr"/>
       <c r="R70" s="8" t="inlineStr"/>
       <c r="S70" s="6" t="n">
-        <v>68489.2</v>
+        <v>62051.32000000001</v>
       </c>
       <c r="T70" s="7" t="n">
-        <v>70.24581977888485</v>
+        <v>52.13213836546908</v>
       </c>
       <c r="U70" s="8" t="inlineStr"/>
       <c r="V70" s="8" t="inlineStr"/>
@@ -6171,10 +6171,250 @@
       <c r="AD70" s="8" t="inlineStr"/>
       <c r="AE70" s="9" t="inlineStr">
         <is>
-          <t>2025-10-17 13:37:16</t>
+          <t>2025-10-18 10:13:22</t>
         </is>
       </c>
       <c r="AF70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>000880</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 17.7%</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>81800</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>81200</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>85400</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>86780</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>69424</v>
+      </c>
+      <c r="K71" s="6" t="n">
+        <v>69524</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>17.65721189804959</v>
+      </c>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr"/>
+      <c r="O71" s="6" t="n">
+        <v>62671.6</v>
+      </c>
+      <c r="P71" s="7" t="n">
+        <v>30.5216397858041</v>
+      </c>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="6" t="n">
+        <v>56504.44</v>
+      </c>
+      <c r="T71" s="7" t="n">
+        <v>44.76738465154242</v>
+      </c>
+      <c r="U71" s="8" t="inlineStr"/>
+      <c r="V71" s="8" t="inlineStr"/>
+      <c r="W71" s="8" t="inlineStr"/>
+      <c r="X71" s="8" t="inlineStr"/>
+      <c r="Y71" s="8" t="inlineStr"/>
+      <c r="Z71" s="8" t="inlineStr"/>
+      <c r="AA71" s="8" t="inlineStr"/>
+      <c r="AB71" s="8" t="inlineStr"/>
+      <c r="AC71" s="8" t="inlineStr"/>
+      <c r="AD71" s="8" t="inlineStr"/>
+      <c r="AE71" s="9" t="inlineStr">
+        <is>
+          <t>2025-10-18 10:13:22</t>
+        </is>
+      </c>
+      <c r="AF71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>034730</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 22.2%</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>216500</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>213000</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>227000</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>220750</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>176600</v>
+      </c>
+      <c r="K72" s="6" t="n">
+        <v>177100</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>22.24731789949181</v>
+      </c>
+      <c r="M72" s="8" t="inlineStr"/>
+      <c r="N72" s="8" t="inlineStr"/>
+      <c r="O72" s="6" t="n">
+        <v>159890</v>
+      </c>
+      <c r="P72" s="7" t="n">
+        <v>35.40559134404903</v>
+      </c>
+      <c r="Q72" s="8" t="inlineStr"/>
+      <c r="R72" s="8" t="inlineStr"/>
+      <c r="S72" s="6" t="n">
+        <v>144401</v>
+      </c>
+      <c r="T72" s="7" t="n">
+        <v>49.92970962804966</v>
+      </c>
+      <c r="U72" s="8" t="inlineStr"/>
+      <c r="V72" s="8" t="inlineStr"/>
+      <c r="W72" s="8" t="inlineStr"/>
+      <c r="X72" s="8" t="inlineStr"/>
+      <c r="Y72" s="8" t="inlineStr"/>
+      <c r="Z72" s="8" t="inlineStr"/>
+      <c r="AA72" s="8" t="inlineStr"/>
+      <c r="AB72" s="8" t="inlineStr"/>
+      <c r="AC72" s="8" t="inlineStr"/>
+      <c r="AD72" s="8" t="inlineStr"/>
+      <c r="AE72" s="9" t="inlineStr">
+        <is>
+          <t>2025-10-18 10:13:22</t>
+        </is>
+      </c>
+      <c r="AF72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 35.3%</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>113900</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>111800</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>119000</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>105140</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>84112</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>84212</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>35.2538830570465</v>
+      </c>
+      <c r="M73" s="8" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr"/>
+      <c r="O73" s="6" t="n">
+        <v>75890.8</v>
+      </c>
+      <c r="P73" s="7" t="n">
+        <v>50.08406816109462</v>
+      </c>
+      <c r="Q73" s="8" t="inlineStr"/>
+      <c r="R73" s="8" t="inlineStr"/>
+      <c r="S73" s="6" t="n">
+        <v>68401.72</v>
+      </c>
+      <c r="T73" s="7" t="n">
+        <v>66.51628058475723</v>
+      </c>
+      <c r="U73" s="8" t="inlineStr"/>
+      <c r="V73" s="8" t="inlineStr"/>
+      <c r="W73" s="8" t="inlineStr"/>
+      <c r="X73" s="8" t="inlineStr"/>
+      <c r="Y73" s="8" t="inlineStr"/>
+      <c r="Z73" s="8" t="inlineStr"/>
+      <c r="AA73" s="8" t="inlineStr"/>
+      <c r="AB73" s="8" t="inlineStr"/>
+      <c r="AC73" s="8" t="inlineStr"/>
+      <c r="AD73" s="8" t="inlineStr"/>
+      <c r="AE73" s="9" t="inlineStr">
+        <is>
+          <t>2025-10-18 10:13:22</t>
+        </is>
+      </c>
+      <c r="AF73" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>최종 업데이트: 2025-10-18 10:13:23</t>
+          <t>최종 업데이트: 2025-10-18 10:45:51</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       <c r="AD2" s="8" t="inlineStr"/>
       <c r="AE2" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:03</t>
+          <t>2025-10-18 10:45:27</t>
         </is>
       </c>
       <c r="AF2" s="8" t="inlineStr"/>
@@ -811,7 +811,7 @@
       <c r="AD3" s="8" t="inlineStr"/>
       <c r="AE3" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:03</t>
+          <t>2025-10-18 10:45:27</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr"/>
@@ -891,7 +891,7 @@
       <c r="AD4" s="8" t="inlineStr"/>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:03</t>
+          <t>2025-10-18 10:45:27</t>
         </is>
       </c>
       <c r="AF4" s="8" t="inlineStr"/>
@@ -971,7 +971,7 @@
       <c r="AD5" s="8" t="inlineStr"/>
       <c r="AE5" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:04</t>
+          <t>2025-10-18 10:45:28</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       <c r="AD6" s="8" t="inlineStr"/>
       <c r="AE6" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:04</t>
+          <t>2025-10-18 10:45:28</t>
         </is>
       </c>
       <c r="AF6" s="8" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       <c r="AD7" s="8" t="inlineStr"/>
       <c r="AE7" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:04</t>
+          <t>2025-10-18 10:45:28</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       <c r="AD8" s="8" t="inlineStr"/>
       <c r="AE8" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:04</t>
+          <t>2025-10-18 10:45:29</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       <c r="AD9" s="8" t="inlineStr"/>
       <c r="AE9" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:05</t>
+          <t>2025-10-18 10:45:29</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="AD10" s="8" t="inlineStr"/>
       <c r="AE10" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:05</t>
+          <t>2025-10-18 10:45:29</t>
         </is>
       </c>
       <c r="AF10" s="8" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       <c r="AD11" s="8" t="inlineStr"/>
       <c r="AE11" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:05</t>
+          <t>2025-10-18 10:45:30</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="AD12" s="8" t="inlineStr"/>
       <c r="AE12" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:06</t>
+          <t>2025-10-18 10:45:30</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       <c r="AD13" s="8" t="inlineStr"/>
       <c r="AE13" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:06</t>
+          <t>2025-10-18 10:45:31</t>
         </is>
       </c>
       <c r="AF13" s="8" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       <c r="AD14" s="8" t="inlineStr"/>
       <c r="AE14" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:06</t>
+          <t>2025-10-18 10:45:31</t>
         </is>
       </c>
       <c r="AF14" s="8" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       <c r="AD15" s="8" t="inlineStr"/>
       <c r="AE15" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:06</t>
+          <t>2025-10-18 10:45:31</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="AD16" s="8" t="inlineStr"/>
       <c r="AE16" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:07</t>
+          <t>2025-10-18 10:45:31</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       <c r="AD17" s="8" t="inlineStr"/>
       <c r="AE17" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:07</t>
+          <t>2025-10-18 10:45:32</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       <c r="AD18" s="8" t="inlineStr"/>
       <c r="AE18" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:07</t>
+          <t>2025-10-18 10:45:32</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       <c r="AD19" s="8" t="inlineStr"/>
       <c r="AE19" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:07</t>
+          <t>2025-10-18 10:45:32</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       <c r="AD20" s="8" t="inlineStr"/>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:08</t>
+          <t>2025-10-18 10:45:33</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       <c r="AD21" s="8" t="inlineStr"/>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:08</t>
+          <t>2025-10-18 10:45:33</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="AD22" s="8" t="inlineStr"/>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:08</t>
+          <t>2025-10-18 10:45:33</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr"/>
@@ -2411,7 +2411,7 @@
       <c r="AD23" s="8" t="inlineStr"/>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:09</t>
+          <t>2025-10-18 10:45:34</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       <c r="AD24" s="8" t="inlineStr"/>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:09</t>
+          <t>2025-10-18 10:45:34</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="AD25" s="8" t="inlineStr"/>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:09</t>
+          <t>2025-10-18 10:45:34</t>
         </is>
       </c>
       <c r="AF25" s="8" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="AD26" s="8" t="inlineStr"/>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:09</t>
+          <t>2025-10-18 10:45:35</t>
         </is>
       </c>
       <c r="AF26" s="8" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       <c r="AD27" s="8" t="inlineStr"/>
       <c r="AE27" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:10</t>
+          <t>2025-10-18 10:45:35</t>
         </is>
       </c>
       <c r="AF27" s="8" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       <c r="AD28" s="8" t="inlineStr"/>
       <c r="AE28" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:10</t>
+          <t>2025-10-18 10:45:35</t>
         </is>
       </c>
       <c r="AF28" s="8" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       <c r="AD29" s="8" t="inlineStr"/>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:10</t>
+          <t>2025-10-18 10:45:36</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       <c r="AD30" s="8" t="inlineStr"/>
       <c r="AE30" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:10</t>
+          <t>2025-10-18 10:45:36</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
       <c r="AD31" s="8" t="inlineStr"/>
       <c r="AE31" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:11</t>
+          <t>2025-10-18 10:45:36</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       <c r="AD32" s="8" t="inlineStr"/>
       <c r="AE32" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:11</t>
+          <t>2025-10-18 10:45:37</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AD33" s="8" t="inlineStr"/>
       <c r="AE33" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:11</t>
+          <t>2025-10-18 10:45:37</t>
         </is>
       </c>
       <c r="AF33" s="8" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       <c r="AD34" s="8" t="inlineStr"/>
       <c r="AE34" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:12</t>
+          <t>2025-10-18 10:45:38</t>
         </is>
       </c>
       <c r="AF34" s="8" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       <c r="AD35" s="8" t="inlineStr"/>
       <c r="AE35" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:12</t>
+          <t>2025-10-18 10:45:38</t>
         </is>
       </c>
       <c r="AF35" s="8" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="AD36" s="8" t="inlineStr"/>
       <c r="AE36" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:12</t>
+          <t>2025-10-18 10:45:38</t>
         </is>
       </c>
       <c r="AF36" s="8" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="AD37" s="8" t="inlineStr"/>
       <c r="AE37" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:12</t>
+          <t>2025-10-18 10:45:39</t>
         </is>
       </c>
       <c r="AF37" s="8" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       <c r="AD38" s="8" t="inlineStr"/>
       <c r="AE38" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:13</t>
+          <t>2025-10-18 10:45:39</t>
         </is>
       </c>
       <c r="AF38" s="8" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
       <c r="AD39" s="8" t="inlineStr"/>
       <c r="AE39" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:13</t>
+          <t>2025-10-18 10:45:39</t>
         </is>
       </c>
       <c r="AF39" s="8" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       <c r="AD40" s="8" t="inlineStr"/>
       <c r="AE40" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:13</t>
+          <t>2025-10-18 10:45:40</t>
         </is>
       </c>
       <c r="AF40" s="8" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       <c r="AD41" s="8" t="inlineStr"/>
       <c r="AE41" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:14</t>
+          <t>2025-10-18 10:45:40</t>
         </is>
       </c>
       <c r="AF41" s="8" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       <c r="AD42" s="8" t="inlineStr"/>
       <c r="AE42" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:14</t>
+          <t>2025-10-18 10:45:40</t>
         </is>
       </c>
       <c r="AF42" s="8" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       <c r="AD43" s="8" t="inlineStr"/>
       <c r="AE43" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:14</t>
+          <t>2025-10-18 10:45:41</t>
         </is>
       </c>
       <c r="AF43" s="8" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       <c r="AD44" s="8" t="inlineStr"/>
       <c r="AE44" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:14</t>
+          <t>2025-10-18 10:45:41</t>
         </is>
       </c>
       <c r="AF44" s="8" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       <c r="AD45" s="8" t="inlineStr"/>
       <c r="AE45" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:15</t>
+          <t>2025-10-18 10:45:41</t>
         </is>
       </c>
       <c r="AF45" s="8" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       <c r="AD46" s="8" t="inlineStr"/>
       <c r="AE46" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:15</t>
+          <t>2025-10-18 10:45:42</t>
         </is>
       </c>
       <c r="AF46" s="8" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       <c r="AD47" s="8" t="inlineStr"/>
       <c r="AE47" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:15</t>
+          <t>2025-10-18 10:45:42</t>
         </is>
       </c>
       <c r="AF47" s="8" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
       <c r="AD48" s="8" t="inlineStr"/>
       <c r="AE48" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:15</t>
+          <t>2025-10-18 10:45:42</t>
         </is>
       </c>
       <c r="AF48" s="8" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       <c r="AD49" s="8" t="inlineStr"/>
       <c r="AE49" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:16</t>
+          <t>2025-10-18 10:45:43</t>
         </is>
       </c>
       <c r="AF49" s="8" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       <c r="AD50" s="8" t="inlineStr"/>
       <c r="AE50" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:16</t>
+          <t>2025-10-18 10:45:43</t>
         </is>
       </c>
       <c r="AF50" s="8" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       <c r="AD51" s="8" t="inlineStr"/>
       <c r="AE51" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:16</t>
+          <t>2025-10-18 10:45:43</t>
         </is>
       </c>
       <c r="AF51" s="8" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
       <c r="AD52" s="8" t="inlineStr"/>
       <c r="AE52" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:17</t>
+          <t>2025-10-18 10:45:44</t>
         </is>
       </c>
       <c r="AF52" s="8" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       <c r="AD53" s="8" t="inlineStr"/>
       <c r="AE53" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:17</t>
+          <t>2025-10-18 10:45:44</t>
         </is>
       </c>
       <c r="AF53" s="8" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       <c r="AD54" s="8" t="inlineStr"/>
       <c r="AE54" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:17</t>
+          <t>2025-10-18 10:45:44</t>
         </is>
       </c>
       <c r="AF54" s="8" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       <c r="AD55" s="8" t="inlineStr"/>
       <c r="AE55" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:17</t>
+          <t>2025-10-18 10:45:44</t>
         </is>
       </c>
       <c r="AF55" s="8" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       <c r="AD56" s="8" t="inlineStr"/>
       <c r="AE56" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:18</t>
+          <t>2025-10-18 10:45:45</t>
         </is>
       </c>
       <c r="AF56" s="8" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       <c r="AD57" s="8" t="inlineStr"/>
       <c r="AE57" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:18</t>
+          <t>2025-10-18 10:45:45</t>
         </is>
       </c>
       <c r="AF57" s="8" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       <c r="AD58" s="8" t="inlineStr"/>
       <c r="AE58" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:18</t>
+          <t>2025-10-18 10:45:45</t>
         </is>
       </c>
       <c r="AF58" s="8" t="inlineStr"/>
@@ -5291,7 +5291,7 @@
       <c r="AD59" s="8" t="inlineStr"/>
       <c r="AE59" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:19</t>
+          <t>2025-10-18 10:45:46</t>
         </is>
       </c>
       <c r="AF59" s="8" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
       <c r="AD60" s="8" t="inlineStr"/>
       <c r="AE60" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:19</t>
+          <t>2025-10-18 10:45:46</t>
         </is>
       </c>
       <c r="AF60" s="8" t="inlineStr"/>
@@ -5451,7 +5451,7 @@
       <c r="AD61" s="8" t="inlineStr"/>
       <c r="AE61" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:19</t>
+          <t>2025-10-18 10:45:46</t>
         </is>
       </c>
       <c r="AF61" s="8" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       <c r="AD62" s="8" t="inlineStr"/>
       <c r="AE62" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:19</t>
+          <t>2025-10-18 10:45:47</t>
         </is>
       </c>
       <c r="AF62" s="8" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       <c r="AD63" s="8" t="inlineStr"/>
       <c r="AE63" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:20</t>
+          <t>2025-10-18 10:45:47</t>
         </is>
       </c>
       <c r="AF63" s="8" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       <c r="AD64" s="8" t="inlineStr"/>
       <c r="AE64" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:20</t>
+          <t>2025-10-18 10:45:47</t>
         </is>
       </c>
       <c r="AF64" s="8" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       <c r="AD65" s="8" t="inlineStr"/>
       <c r="AE65" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:20</t>
+          <t>2025-10-18 10:45:48</t>
         </is>
       </c>
       <c r="AF65" s="8" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       <c r="AD66" s="8" t="inlineStr"/>
       <c r="AE66" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:21</t>
+          <t>2025-10-18 10:45:48</t>
         </is>
       </c>
       <c r="AF66" s="8" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       <c r="AD67" s="8" t="inlineStr"/>
       <c r="AE67" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:21</t>
+          <t>2025-10-18 10:45:49</t>
         </is>
       </c>
       <c r="AF67" s="8" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="AD68" s="8" t="inlineStr"/>
       <c r="AE68" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:21</t>
+          <t>2025-10-18 10:45:49</t>
         </is>
       </c>
       <c r="AF68" s="8" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       <c r="AD69" s="8" t="inlineStr"/>
       <c r="AE69" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:21</t>
+          <t>2025-10-18 10:45:49</t>
         </is>
       </c>
       <c r="AF69" s="8" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
       <c r="AD70" s="8" t="inlineStr"/>
       <c r="AE70" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:22</t>
+          <t>2025-10-18 10:45:50</t>
         </is>
       </c>
       <c r="AF70" s="8" t="inlineStr"/>
@@ -6251,7 +6251,7 @@
       <c r="AD71" s="8" t="inlineStr"/>
       <c r="AE71" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:22</t>
+          <t>2025-10-18 10:45:50</t>
         </is>
       </c>
       <c r="AF71" s="8" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
       <c r="AD72" s="8" t="inlineStr"/>
       <c r="AE72" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:22</t>
+          <t>2025-10-18 10:45:50</t>
         </is>
       </c>
       <c r="AF72" s="8" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       <c r="AD73" s="8" t="inlineStr"/>
       <c r="AE73" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:13:22</t>
+          <t>2025-10-18 10:45:51</t>
         </is>
       </c>
       <c r="AF73" s="8" t="inlineStr"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>최종 업데이트: 2025-10-18 10:45:51</t>
+          <t>최종 업데이트: 2025-10-18 11:06:03</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       <c r="AD2" s="8" t="inlineStr"/>
       <c r="AE2" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:27</t>
+          <t>2025-10-18 11:05:39</t>
         </is>
       </c>
       <c r="AF2" s="8" t="inlineStr"/>
@@ -811,7 +811,7 @@
       <c r="AD3" s="8" t="inlineStr"/>
       <c r="AE3" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:27</t>
+          <t>2025-10-18 11:05:39</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr"/>
@@ -891,7 +891,7 @@
       <c r="AD4" s="8" t="inlineStr"/>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:27</t>
+          <t>2025-10-18 11:05:39</t>
         </is>
       </c>
       <c r="AF4" s="8" t="inlineStr"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.1%</t>
+          <t>1차 매수선까지 25.4%</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -938,26 +938,26 @@
         <v>199680</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>200180</v>
+        <v>199780</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>25.13737636127485</v>
+        <v>25.38792671939133</v>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="6" t="n">
-        <v>180662</v>
+        <v>179902</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>38.65671807020846</v>
+        <v>39.24247645940568</v>
       </c>
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="6" t="n">
-        <v>163095.8</v>
+        <v>162011.8</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>53.59071171667203</v>
+        <v>54.61836730410992</v>
       </c>
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
@@ -971,7 +971,7 @@
       <c r="AD5" s="8" t="inlineStr"/>
       <c r="AE5" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:28</t>
+          <t>2025-10-18 11:05:40</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       <c r="AD6" s="8" t="inlineStr"/>
       <c r="AE6" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:28</t>
+          <t>2025-10-18 11:05:40</t>
         </is>
       </c>
       <c r="AF6" s="8" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       <c r="AD7" s="8" t="inlineStr"/>
       <c r="AE7" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:28</t>
+          <t>2025-10-18 11:05:40</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.6%</t>
+          <t>1차 매수선까지 46.9%</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -1178,26 +1178,26 @@
         <v>169360</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>169860</v>
+        <v>169460</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>46.59131049099258</v>
+        <v>46.93733034344388</v>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="6" t="n">
-        <v>153374</v>
+        <v>152614</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>62.34824676933509</v>
+        <v>63.15672218800372</v>
       </c>
       <c r="Q8" s="8" t="inlineStr"/>
       <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="6" t="n">
-        <v>138536.6</v>
+        <v>137452.6</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>79.73589650677148</v>
+        <v>81.15335759381779</v>
       </c>
       <c r="U8" s="8" t="inlineStr"/>
       <c r="V8" s="8" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       <c r="AD8" s="8" t="inlineStr"/>
       <c r="AE8" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:29</t>
+          <t>2025-10-18 11:05:41</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       <c r="AD9" s="8" t="inlineStr"/>
       <c r="AE9" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:29</t>
+          <t>2025-10-18 11:05:41</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="AD10" s="8" t="inlineStr"/>
       <c r="AE10" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:29</t>
+          <t>2025-10-18 11:05:41</t>
         </is>
       </c>
       <c r="AF10" s="8" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       <c r="AD11" s="8" t="inlineStr"/>
       <c r="AE11" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:30</t>
+          <t>2025-10-18 11:05:42</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="AD12" s="8" t="inlineStr"/>
       <c r="AE12" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:30</t>
+          <t>2025-10-18 11:05:42</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       <c r="AD13" s="8" t="inlineStr"/>
       <c r="AE13" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:31</t>
+          <t>2025-10-18 11:05:42</t>
         </is>
       </c>
       <c r="AF13" s="8" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.3%</t>
+          <t>1차 매수선까지 36.6%</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1658,26 +1658,26 @@
         <v>175960</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>176460</v>
+        <v>176060</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>36.29151082398277</v>
+        <v>36.60115869589913</v>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="6" t="n">
-        <v>159314</v>
+        <v>158554</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>50.9597398847559</v>
+        <v>51.68333816869962</v>
       </c>
       <c r="Q14" s="8" t="inlineStr"/>
       <c r="R14" s="8" t="inlineStr"/>
       <c r="S14" s="6" t="n">
-        <v>143882.6</v>
+        <v>142798.6</v>
       </c>
       <c r="T14" s="7" t="n">
-        <v>67.15016270209185</v>
+        <v>68.41901811362295</v>
       </c>
       <c r="U14" s="8" t="inlineStr"/>
       <c r="V14" s="8" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       <c r="AD14" s="8" t="inlineStr"/>
       <c r="AE14" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:31</t>
+          <t>2025-10-18 11:05:43</t>
         </is>
       </c>
       <c r="AF14" s="8" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 53.9%</t>
+          <t>1차 매수선까지 54.4%</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1738,26 +1738,26 @@
         <v>119952</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>120452</v>
+        <v>120052</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>53.92023378607246</v>
+        <v>54.4330789991004</v>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="6" t="n">
-        <v>108906.8</v>
+        <v>108146.8</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>70.23730382308541</v>
+        <v>71.4336438988486</v>
       </c>
       <c r="Q15" s="8" t="inlineStr"/>
       <c r="R15" s="8" t="inlineStr"/>
       <c r="S15" s="6" t="n">
-        <v>98116.12000000001</v>
+        <v>97432.12000000001</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>88.95977541712817</v>
+        <v>90.2863244687686</v>
       </c>
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       <c r="AD15" s="8" t="inlineStr"/>
       <c r="AE15" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:31</t>
+          <t>2025-10-18 11:05:43</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="AD16" s="8" t="inlineStr"/>
       <c r="AE16" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:31</t>
+          <t>2025-10-18 11:05:43</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
       <c r="S17" s="6" t="n">
-        <v>190749.2</v>
+        <v>190349.2</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>73.78840907327526</v>
+        <v>74.15360821059399</v>
       </c>
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       <c r="AD17" s="8" t="inlineStr"/>
       <c r="AE17" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:32</t>
+          <t>2025-10-18 11:05:44</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       <c r="AD18" s="8" t="inlineStr"/>
       <c r="AE18" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:32</t>
+          <t>2025-10-18 11:05:44</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       <c r="AD19" s="8" t="inlineStr"/>
       <c r="AE19" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:32</t>
+          <t>2025-10-18 11:05:44</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       <c r="AD20" s="8" t="inlineStr"/>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:33</t>
+          <t>2025-10-18 11:05:45</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 55.9%</t>
+          <t>1차 매수선까지 56.4%</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -2218,26 +2218,26 @@
         <v>122759.52</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>123259.52</v>
+        <v>122859.52</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>55.93116053023734</v>
+        <v>56.43883355559259</v>
       </c>
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="6" t="n">
-        <v>111433.568</v>
+        <v>110673.568</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>72.47944533194881</v>
+        <v>73.66386886523799</v>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="6" t="n">
-        <v>100790.2112</v>
+        <v>99706.21120000001</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>90.69312159552256</v>
+        <v>92.76632587559399</v>
       </c>
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       <c r="AD21" s="8" t="inlineStr"/>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:33</t>
+          <t>2025-10-18 11:05:45</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="AD22" s="8" t="inlineStr"/>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:33</t>
+          <t>2025-10-18 11:05:45</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr"/>
@@ -2386,18 +2386,18 @@
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="6" t="n">
-        <v>19252.4</v>
+        <v>19212.4</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>13.75205169225654</v>
+        <v>13.98888218025857</v>
       </c>
       <c r="Q23" s="8" t="inlineStr"/>
       <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="6" t="n">
-        <v>17377.16</v>
+        <v>17301.16</v>
       </c>
       <c r="T23" s="7" t="n">
-        <v>26.02749816425696</v>
+        <v>26.5811078563518</v>
       </c>
       <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr"/>
@@ -2411,7 +2411,7 @@
       <c r="AD23" s="8" t="inlineStr"/>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:34</t>
+          <t>2025-10-18 11:05:46</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       <c r="AD24" s="8" t="inlineStr"/>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:34</t>
+          <t>2025-10-18 11:05:46</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.8%</t>
+          <t>1차 매수선까지 19.2%</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2538,26 +2538,26 @@
         <v>13321.2</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>13371.2</v>
+        <v>13331.2</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>18.83750149575206</v>
+        <v>19.19407105136821</v>
       </c>
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="6" t="n">
-        <v>12084.08</v>
+        <v>12008.08</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>31.49532277177905</v>
+        <v>32.32756610548896</v>
       </c>
       <c r="Q25" s="8" t="inlineStr"/>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="6" t="n">
-        <v>10925.672</v>
+        <v>10817.272</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>45.43727836603549</v>
+        <v>46.89470690946845</v>
       </c>
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="AD25" s="8" t="inlineStr"/>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:34</t>
+          <t>2025-10-18 11:05:46</t>
         </is>
       </c>
       <c r="AF25" s="8" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="AD26" s="8" t="inlineStr"/>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:35</t>
+          <t>2025-10-18 11:05:47</t>
         </is>
       </c>
       <c r="AF26" s="8" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       <c r="AD27" s="8" t="inlineStr"/>
       <c r="AE27" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:35</t>
+          <t>2025-10-18 11:05:47</t>
         </is>
       </c>
       <c r="AF27" s="8" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       <c r="AD28" s="8" t="inlineStr"/>
       <c r="AE28" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:35</t>
+          <t>2025-10-18 11:05:48</t>
         </is>
       </c>
       <c r="AF28" s="8" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.7%</t>
+          <t>1차 매수선까지 25.1%</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2858,26 +2858,26 @@
         <v>138716</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>139216</v>
+        <v>138816</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>24.6983105390185</v>
+        <v>25.05763024435224</v>
       </c>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="6" t="n">
-        <v>125794.4</v>
+        <v>125034.4</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>38.00296356594569</v>
+        <v>38.84179073918857</v>
       </c>
       <c r="Q29" s="8" t="inlineStr"/>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="6" t="n">
-        <v>113714.96</v>
+        <v>112630.96</v>
       </c>
       <c r="T29" s="7" t="n">
-        <v>52.66241134851561</v>
+        <v>54.13168812553848</v>
       </c>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       <c r="AD29" s="8" t="inlineStr"/>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:36</t>
+          <t>2025-10-18 11:05:48</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 8.6% (접근 중!)</t>
+          <t>1차 매수선까지 8.9% (접근 중!)</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -2938,26 +2938,26 @@
         <v>147728</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>148228</v>
+        <v>147828</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>8.616455730361334</v>
+        <v>8.91035527775523</v>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="6" t="n">
-        <v>133905.2</v>
+        <v>133145.2</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>20.23431502286691</v>
+        <v>20.92061899339967</v>
       </c>
       <c r="Q30" s="8" t="inlineStr"/>
       <c r="R30" s="8" t="inlineStr"/>
       <c r="S30" s="6" t="n">
-        <v>121014.68</v>
+        <v>119930.68</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>33.04171031150931</v>
+        <v>34.24421507490826</v>
       </c>
       <c r="U30" s="8" t="inlineStr"/>
       <c r="V30" s="8" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       <c r="AD30" s="8" t="inlineStr"/>
       <c r="AE30" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:36</t>
+          <t>2025-10-18 11:05:48</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.6%</t>
+          <t>1차 매수선까지 13.9%</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
@@ -3018,26 +3018,26 @@
         <v>175040</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>175540</v>
+        <v>175140</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>13.64931069841631</v>
+        <v>13.90887290167866</v>
       </c>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="6" t="n">
-        <v>158486</v>
+        <v>157726</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>25.87862650328735</v>
+        <v>26.48517048552553</v>
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="6" t="n">
-        <v>143137.4</v>
+        <v>142053.4</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>39.37657104292798</v>
+        <v>40.4401443400862</v>
       </c>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
       <c r="AD31" s="8" t="inlineStr"/>
       <c r="AE31" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:36</t>
+          <t>2025-10-18 11:05:49</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       <c r="AD32" s="8" t="inlineStr"/>
       <c r="AE32" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:37</t>
+          <t>2025-10-18 11:05:49</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.6%</t>
+          <t>1차 매수선까지 15.9%</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -3178,26 +3178,26 @@
         <v>173380</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>173880</v>
+        <v>173480</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>15.59696342305038</v>
+        <v>15.86350011528707</v>
       </c>
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
       <c r="O33" s="6" t="n">
-        <v>156992</v>
+        <v>156232</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>28.03200163065634</v>
+        <v>28.65482103538328</v>
       </c>
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
       <c r="S33" s="6" t="n">
-        <v>141792.8</v>
+        <v>140708.8</v>
       </c>
       <c r="T33" s="7" t="n">
-        <v>41.75613994504656</v>
+        <v>42.84820849868663</v>
       </c>
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AD33" s="8" t="inlineStr"/>
       <c r="AE33" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:37</t>
+          <t>2025-10-18 11:05:49</t>
         </is>
       </c>
       <c r="AF33" s="8" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       <c r="AD34" s="8" t="inlineStr"/>
       <c r="AE34" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:38</t>
+          <t>2025-10-18 11:05:50</t>
         </is>
       </c>
       <c r="AF34" s="8" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       <c r="AD35" s="8" t="inlineStr"/>
       <c r="AE35" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:38</t>
+          <t>2025-10-18 11:05:50</t>
         </is>
       </c>
       <c r="AF35" s="8" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 0.9% (접근 중!)</t>
+          <t>1차 매수선까지 1.1% (접근 중!)</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -3418,26 +3418,26 @@
         <v>164336</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>164836</v>
+        <v>164436</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.8881555000121333</v>
+        <v>1.133571723953392</v>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="6" t="n">
-        <v>148852.4</v>
+        <v>148092.4</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>11.72140993359866</v>
+        <v>12.29475651687731</v>
       </c>
       <c r="Q36" s="8" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
       <c r="S36" s="6" t="n">
-        <v>134467.16</v>
+        <v>133383.16</v>
       </c>
       <c r="T36" s="7" t="n">
-        <v>23.67331919555674</v>
+        <v>24.67840767905033</v>
       </c>
       <c r="U36" s="8" t="inlineStr"/>
       <c r="V36" s="8" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="AD36" s="8" t="inlineStr"/>
       <c r="AE36" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:38</t>
+          <t>2025-10-18 11:05:50</t>
         </is>
       </c>
       <c r="AF36" s="8" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="AD37" s="8" t="inlineStr"/>
       <c r="AE37" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:39</t>
+          <t>2025-10-18 11:05:51</t>
         </is>
       </c>
       <c r="AF37" s="8" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 7.5% (접근 중!)</t>
+          <t>1차 매수선까지 7.7% (접근 중!)</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -3578,26 +3578,26 @@
         <v>19864</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19914</v>
+        <v>19874</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>7.46208697398815</v>
+        <v>7.678373754654322</v>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
       <c r="O38" s="6" t="n">
-        <v>17972.6</v>
+        <v>17896.6</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>19.07014010215549</v>
+        <v>19.57578534470233</v>
       </c>
       <c r="Q38" s="8" t="inlineStr"/>
       <c r="R38" s="8" t="inlineStr"/>
       <c r="S38" s="6" t="n">
-        <v>16225.34</v>
+        <v>16116.94</v>
       </c>
       <c r="T38" s="7" t="n">
-        <v>31.89245957249585</v>
+        <v>32.77954748233844</v>
       </c>
       <c r="U38" s="8" t="inlineStr"/>
       <c r="V38" s="8" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       <c r="AD38" s="8" t="inlineStr"/>
       <c r="AE38" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:39</t>
+          <t>2025-10-18 11:05:51</t>
         </is>
       </c>
       <c r="AF38" s="8" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
       <c r="S39" s="6" t="n">
-        <v>18112.64</v>
+        <v>18072.64</v>
       </c>
       <c r="T39" s="7" t="n">
-        <v>41.61381223278327</v>
+        <v>41.92724471908916</v>
       </c>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
       <c r="AD39" s="8" t="inlineStr"/>
       <c r="AE39" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:39</t>
+          <t>2025-10-18 11:05:51</t>
         </is>
       </c>
       <c r="AF39" s="8" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.0%</t>
+          <t>1차 매수선까지 16.3%</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
@@ -3738,26 +3738,26 @@
         <v>17275.6</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>17325.6</v>
+        <v>17285.6</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>16.01329824075355</v>
+        <v>16.28176054056554</v>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="6" t="n">
-        <v>15643.04</v>
+        <v>15567.04</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>28.49164868209758</v>
+        <v>29.11895903138937</v>
       </c>
       <c r="Q40" s="8" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
       <c r="S40" s="6" t="n">
-        <v>14128.736</v>
+        <v>14020.336</v>
       </c>
       <c r="T40" s="7" t="n">
-        <v>42.26325695377135</v>
+        <v>43.36318330744709</v>
       </c>
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="8" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       <c r="AD40" s="8" t="inlineStr"/>
       <c r="AE40" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:40</t>
+          <t>2025-10-18 11:05:52</t>
         </is>
       </c>
       <c r="AF40" s="8" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       <c r="AD41" s="8" t="inlineStr"/>
       <c r="AE41" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:40</t>
+          <t>2025-10-18 11:05:52</t>
         </is>
       </c>
       <c r="AF41" s="8" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       <c r="AD42" s="8" t="inlineStr"/>
       <c r="AE42" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:40</t>
+          <t>2025-10-18 11:05:52</t>
         </is>
       </c>
       <c r="AF42" s="8" t="inlineStr"/>
@@ -3986,18 +3986,18 @@
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="6" t="n">
-        <v>18573.8</v>
+        <v>18533.8</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>21.40757410976753</v>
+        <v>21.66959824752615</v>
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="6" t="n">
-        <v>16766.42</v>
+        <v>16690.42</v>
       </c>
       <c r="T43" s="7" t="n">
-        <v>34.49502040387872</v>
+        <v>35.1074448695719</v>
       </c>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       <c r="AD43" s="8" t="inlineStr"/>
       <c r="AE43" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:41</t>
+          <t>2025-10-18 11:05:53</t>
         </is>
       </c>
       <c r="AF43" s="8" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       <c r="AD44" s="8" t="inlineStr"/>
       <c r="AE44" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:41</t>
+          <t>2025-10-18 11:05:53</t>
         </is>
       </c>
       <c r="AF44" s="8" t="inlineStr"/>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.7%</t>
+          <t>1차 매수선까지 25.0%</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -4138,26 +4138,26 @@
         <v>159452</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>159952</v>
+        <v>159552</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>24.72491747524257</v>
+        <v>25.03760529482551</v>
       </c>
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="6" t="n">
-        <v>144456.8</v>
+        <v>143696.8</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>38.10357144834994</v>
+        <v>38.83398934423033</v>
       </c>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
       <c r="S45" s="6" t="n">
-        <v>130511.12</v>
+        <v>129427.12</v>
       </c>
       <c r="T45" s="7" t="n">
-        <v>52.86053786068188</v>
+        <v>54.14080140236448</v>
       </c>
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       <c r="AD45" s="8" t="inlineStr"/>
       <c r="AE45" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:41</t>
+          <t>2025-10-18 11:05:53</t>
         </is>
       </c>
       <c r="AF45" s="8" t="inlineStr"/>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.5%</t>
+          <t>1차 매수선까지 27.7%</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
@@ -4218,26 +4218,26 @@
         <v>17368</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>17418</v>
+        <v>17378</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>27.45435756114365</v>
+        <v>27.74772701116354</v>
       </c>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="6" t="n">
-        <v>15726.2</v>
+        <v>15650.2</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>41.1656980071473</v>
+        <v>41.85122234859618</v>
       </c>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="6" t="n">
-        <v>14203.58</v>
+        <v>14095.18</v>
       </c>
       <c r="T46" s="7" t="n">
-        <v>56.29862330482877</v>
+        <v>57.50064915808098</v>
       </c>
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       <c r="AD46" s="8" t="inlineStr"/>
       <c r="AE46" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:42</t>
+          <t>2025-10-18 11:05:54</t>
         </is>
       </c>
       <c r="AF46" s="8" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       <c r="AD47" s="8" t="inlineStr"/>
       <c r="AE47" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:42</t>
+          <t>2025-10-18 11:05:54</t>
         </is>
       </c>
       <c r="AF47" s="8" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
       <c r="AD48" s="8" t="inlineStr"/>
       <c r="AE48" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:42</t>
+          <t>2025-10-18 11:05:54</t>
         </is>
       </c>
       <c r="AF48" s="8" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       <c r="AD49" s="8" t="inlineStr"/>
       <c r="AE49" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:43</t>
+          <t>2025-10-18 11:05:55</t>
         </is>
       </c>
       <c r="AF49" s="8" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 7.7% (접근 중!)</t>
+          <t>1차 매수선까지 8.0% (접근 중!)</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -4538,26 +4538,26 @@
         <v>14830</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>14880</v>
+        <v>14840</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>7.661290322580645</v>
+        <v>7.951482479784366</v>
       </c>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
       <c r="O50" s="6" t="n">
-        <v>13442</v>
+        <v>13366</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>19.17869364677875</v>
+        <v>19.85635193775251</v>
       </c>
       <c r="Q50" s="8" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="6" t="n">
-        <v>12147.8</v>
+        <v>12039.4</v>
       </c>
       <c r="T50" s="7" t="n">
-        <v>31.87573058496188</v>
+        <v>33.06310945728193</v>
       </c>
       <c r="U50" s="8" t="inlineStr"/>
       <c r="V50" s="8" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       <c r="AD50" s="8" t="inlineStr"/>
       <c r="AE50" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:43</t>
+          <t>2025-10-18 11:05:55</t>
         </is>
       </c>
       <c r="AF50" s="8" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       <c r="AD51" s="8" t="inlineStr"/>
       <c r="AE51" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:43</t>
+          <t>2025-10-18 11:05:55</t>
         </is>
       </c>
       <c r="AF51" s="8" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.4%</t>
+          <t>1차 매수선까지 26.9%</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
@@ -4698,26 +4698,26 @@
         <v>11183.6</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>11233.6</v>
+        <v>11193.6</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>26.40649480131035</v>
+        <v>26.85820468839336</v>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
       <c r="O52" s="6" t="n">
-        <v>10160.24</v>
+        <v>10084.24</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>39.76047809894255</v>
+        <v>40.81378467787359</v>
       </c>
       <c r="Q52" s="8" t="inlineStr"/>
       <c r="R52" s="8" t="inlineStr"/>
       <c r="S52" s="6" t="n">
-        <v>9154.216</v>
+        <v>9085.816000000001</v>
       </c>
       <c r="T52" s="7" t="n">
-        <v>55.11978305952142</v>
+        <v>56.28755854179744</v>
       </c>
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
       <c r="AD52" s="8" t="inlineStr"/>
       <c r="AE52" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:44</t>
+          <t>2025-10-18 11:05:56</t>
         </is>
       </c>
       <c r="AF52" s="8" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       <c r="AD53" s="8" t="inlineStr"/>
       <c r="AE53" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:44</t>
+          <t>2025-10-18 11:05:56</t>
         </is>
       </c>
       <c r="AF53" s="8" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.6%</t>
+          <t>1차 매수선까지 25.9%</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
@@ -4858,26 +4858,26 @@
         <v>188160</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>188660</v>
+        <v>188260</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>25.62281352697975</v>
+        <v>25.88972697333475</v>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
       <c r="O54" s="6" t="n">
-        <v>170294</v>
+        <v>169534</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>39.1710806017828</v>
+        <v>39.79496738117428</v>
       </c>
       <c r="Q54" s="8" t="inlineStr"/>
       <c r="R54" s="8" t="inlineStr"/>
       <c r="S54" s="6" t="n">
-        <v>153764.6</v>
+        <v>152680.6</v>
       </c>
       <c r="T54" s="7" t="n">
-        <v>54.13170521693549</v>
+        <v>55.22600775737061</v>
       </c>
       <c r="U54" s="8" t="inlineStr"/>
       <c r="V54" s="8" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       <c r="AD54" s="8" t="inlineStr"/>
       <c r="AE54" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:44</t>
+          <t>2025-10-18 11:05:56</t>
         </is>
       </c>
       <c r="AF54" s="8" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       <c r="AD55" s="8" t="inlineStr"/>
       <c r="AE55" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:44</t>
+          <t>2025-10-18 11:05:57</t>
         </is>
       </c>
       <c r="AF55" s="8" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       <c r="AD56" s="8" t="inlineStr"/>
       <c r="AE56" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:45</t>
+          <t>2025-10-18 11:05:57</t>
         </is>
       </c>
       <c r="AF56" s="8" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       <c r="AD57" s="8" t="inlineStr"/>
       <c r="AE57" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:45</t>
+          <t>2025-10-18 11:05:57</t>
         </is>
       </c>
       <c r="AF57" s="8" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
       <c r="Q58" s="8" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="6" t="n">
-        <v>19076.54</v>
+        <v>19036.54</v>
       </c>
       <c r="T58" s="7" t="n">
-        <v>54.11599797447545</v>
+        <v>54.43982992707708</v>
       </c>
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       <c r="AD58" s="8" t="inlineStr"/>
       <c r="AE58" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:45</t>
+          <t>2025-10-18 11:05:58</t>
         </is>
       </c>
       <c r="AF58" s="8" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.2%</t>
+          <t>1차 매수선까지 27.6%</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
@@ -5258,26 +5258,26 @@
         <v>158640</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>159140</v>
+        <v>158740</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>27.24644966695991</v>
+        <v>27.5670908403679</v>
       </c>
       <c r="M59" s="8" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="6" t="n">
-        <v>143726</v>
+        <v>142966</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>40.8930882373405</v>
+        <v>41.64206874361736</v>
       </c>
       <c r="Q59" s="8" t="inlineStr"/>
       <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="6" t="n">
-        <v>129853.4</v>
+        <v>128769.4</v>
       </c>
       <c r="T59" s="7" t="n">
-        <v>55.94508884634518</v>
+        <v>57.25785784510915</v>
       </c>
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
@@ -5291,7 +5291,7 @@
       <c r="AD59" s="8" t="inlineStr"/>
       <c r="AE59" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:46</t>
+          <t>2025-10-18 11:05:58</t>
         </is>
       </c>
       <c r="AF59" s="8" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
       <c r="AD60" s="8" t="inlineStr"/>
       <c r="AE60" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:46</t>
+          <t>2025-10-18 11:05:58</t>
         </is>
       </c>
       <c r="AF60" s="8" t="inlineStr"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.7%</t>
+          <t>1차 매수선까지 19.1%</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
@@ -5418,26 +5418,26 @@
         <v>12316.8</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>12366.8</v>
+        <v>12326.8</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>18.70491962350809</v>
+        <v>19.0901126001882</v>
       </c>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="6" t="n">
-        <v>11180.12</v>
+        <v>11104.12</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>31.30449404836441</v>
+        <v>32.20318224226683</v>
       </c>
       <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="6" t="n">
-        <v>10112.108</v>
+        <v>10003.708</v>
       </c>
       <c r="T61" s="7" t="n">
-        <v>45.17250013548114</v>
+        <v>46.74558673643812</v>
       </c>
       <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
@@ -5451,7 +5451,7 @@
       <c r="AD61" s="8" t="inlineStr"/>
       <c r="AE61" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:46</t>
+          <t>2025-10-18 11:05:59</t>
         </is>
       </c>
       <c r="AF61" s="8" t="inlineStr"/>
@@ -5514,10 +5514,10 @@
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="6" t="n">
-        <v>19844.42</v>
+        <v>19804.42</v>
       </c>
       <c r="T62" s="7" t="n">
-        <v>52.18383807639631</v>
+        <v>52.49121155782397</v>
       </c>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       <c r="AD62" s="8" t="inlineStr"/>
       <c r="AE62" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:47</t>
+          <t>2025-10-18 11:05:59</t>
         </is>
       </c>
       <c r="AF62" s="8" t="inlineStr"/>
@@ -5586,18 +5586,18 @@
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
       <c r="O63" s="6" t="n">
-        <v>1901.84</v>
+        <v>1897.84</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>37.23551928658563</v>
+        <v>37.52476499599545</v>
       </c>
       <c r="Q63" s="8" t="inlineStr"/>
       <c r="R63" s="8" t="inlineStr"/>
       <c r="S63" s="6" t="n">
-        <v>1716.656</v>
+        <v>1709.056</v>
       </c>
       <c r="T63" s="7" t="n">
-        <v>52.03977966465034</v>
+        <v>52.71588526063511</v>
       </c>
       <c r="U63" s="8" t="inlineStr"/>
       <c r="V63" s="8" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       <c r="AD63" s="8" t="inlineStr"/>
       <c r="AE63" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:47</t>
+          <t>2025-10-18 11:05:59</t>
         </is>
       </c>
       <c r="AF63" s="8" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       <c r="AD64" s="8" t="inlineStr"/>
       <c r="AE64" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:47</t>
+          <t>2025-10-18 11:06:00</t>
         </is>
       </c>
       <c r="AF64" s="8" t="inlineStr"/>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.0% (접근 중!)</t>
+          <t>1차 매수선까지 10.4%</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
@@ -5738,26 +5738,26 @@
         <v>118064</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>118564</v>
+        <v>118164</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>9.982794102763066</v>
+        <v>10.35509969195356</v>
       </c>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="6" t="n">
-        <v>107207.6</v>
+        <v>106447.6</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>21.63316779780537</v>
+        <v>22.50158763560662</v>
       </c>
       <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="6" t="n">
-        <v>96586.84000000001</v>
+        <v>95902.84000000001</v>
       </c>
       <c r="T65" s="7" t="n">
-        <v>35.00804043283742</v>
+        <v>35.97094726287562</v>
       </c>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       <c r="AD65" s="8" t="inlineStr"/>
       <c r="AE65" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:48</t>
+          <t>2025-10-18 11:06:00</t>
         </is>
       </c>
       <c r="AF65" s="8" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       <c r="AD66" s="8" t="inlineStr"/>
       <c r="AE66" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:48</t>
+          <t>2025-10-18 11:06:00</t>
         </is>
       </c>
       <c r="AF66" s="8" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       <c r="AD67" s="8" t="inlineStr"/>
       <c r="AE67" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:49</t>
+          <t>2025-10-18 11:06:01</t>
         </is>
       </c>
       <c r="AF67" s="8" t="inlineStr"/>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.4%</t>
+          <t>1차 매수선까지 44.7%</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
@@ -5978,26 +5978,26 @@
         <v>176796</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>177296</v>
+        <v>176896</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>44.39130042414944</v>
+        <v>44.7178002894356</v>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="6" t="n">
-        <v>160066.4</v>
+        <v>159306.4</v>
       </c>
       <c r="P68" s="7" t="n">
-        <v>59.93362754456901</v>
+        <v>60.69661984703691</v>
       </c>
       <c r="Q68" s="8" t="inlineStr"/>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="6" t="n">
-        <v>144559.76</v>
+        <v>143475.76</v>
       </c>
       <c r="T68" s="7" t="n">
-        <v>77.08939195803866</v>
+        <v>78.42735246706481</v>
       </c>
       <c r="U68" s="8" t="inlineStr"/>
       <c r="V68" s="8" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="AD68" s="8" t="inlineStr"/>
       <c r="AE68" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:49</t>
+          <t>2025-10-18 11:06:01</t>
         </is>
       </c>
       <c r="AF68" s="8" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="6" t="n">
-        <v>182373.8</v>
+        <v>181973.8</v>
       </c>
       <c r="T69" s="7" t="n">
-        <v>58.46574453128682</v>
+        <v>58.81407103659976</v>
       </c>
       <c r="U69" s="8" t="inlineStr"/>
       <c r="V69" s="8" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       <c r="AD69" s="8" t="inlineStr"/>
       <c r="AE69" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:49</t>
+          <t>2025-10-18 11:06:01</t>
         </is>
       </c>
       <c r="AF69" s="8" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
       <c r="AD70" s="8" t="inlineStr"/>
       <c r="AE70" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:50</t>
+          <t>2025-10-18 11:06:02</t>
         </is>
       </c>
       <c r="AF70" s="8" t="inlineStr"/>
@@ -6251,7 +6251,7 @@
       <c r="AD71" s="8" t="inlineStr"/>
       <c r="AE71" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:50</t>
+          <t>2025-10-18 11:06:02</t>
         </is>
       </c>
       <c r="AF71" s="8" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.2%</t>
+          <t>1차 매수선까지 22.5%</t>
         </is>
       </c>
       <c r="F72" s="6" t="n">
@@ -6298,26 +6298,26 @@
         <v>176600</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>177100</v>
+        <v>176700</v>
       </c>
       <c r="L72" s="7" t="n">
-        <v>22.24731789949181</v>
+        <v>22.52405206564799</v>
       </c>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
       <c r="O72" s="6" t="n">
-        <v>159890</v>
+        <v>159130</v>
       </c>
       <c r="P72" s="7" t="n">
-        <v>35.40559134404903</v>
+        <v>36.05228429585873</v>
       </c>
       <c r="Q72" s="8" t="inlineStr"/>
       <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="6" t="n">
-        <v>144401</v>
+        <v>143317</v>
       </c>
       <c r="T72" s="7" t="n">
-        <v>49.92970962804966</v>
+        <v>51.06372586643594</v>
       </c>
       <c r="U72" s="8" t="inlineStr"/>
       <c r="V72" s="8" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
       <c r="AD72" s="8" t="inlineStr"/>
       <c r="AE72" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:50</t>
+          <t>2025-10-18 11:06:02</t>
         </is>
       </c>
       <c r="AF72" s="8" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       <c r="AD73" s="8" t="inlineStr"/>
       <c r="AE73" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 10:45:51</t>
+          <t>2025-10-18 11:06:03</t>
         </is>
       </c>
       <c r="AF73" s="8" t="inlineStr"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>최종 업데이트: 2025-10-18 11:06:03</t>
+          <t>최종 업데이트: 2025-10-18 11:08:39</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.9%</t>
+          <t>1차 매수선까지 39.0%</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -698,26 +698,26 @@
         <v>69244</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>69344</v>
+        <v>69300</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>38.87286571296723</v>
+        <v>38.96103896103897</v>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="6" t="n">
-        <v>62509.6</v>
+        <v>62500</v>
       </c>
       <c r="P2" s="7" t="n">
-        <v>54.056336946645</v>
+        <v>54.08</v>
       </c>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="6" t="n">
-        <v>56358.64</v>
+        <v>56300</v>
       </c>
       <c r="T2" s="7" t="n">
-        <v>70.86998550710237</v>
+        <v>71.04795737122558</v>
       </c>
       <c r="U2" s="8" t="inlineStr"/>
       <c r="V2" s="8" t="inlineStr"/>
@@ -731,7 +731,7 @@
       <c r="AD2" s="8" t="inlineStr"/>
       <c r="AE2" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:39</t>
+          <t>2025-10-18 11:08:18</t>
         </is>
       </c>
       <c r="AF2" s="8" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.6%</t>
+          <t>1차 매수선까지 50.5%</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -778,26 +778,26 @@
         <v>301360</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>301860</v>
+        <v>302000</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>50.5664877757901</v>
+        <v>50.49668874172185</v>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="6" t="n">
-        <v>272174</v>
+        <v>272500</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>66.98876454033082</v>
+        <v>66.78899082568807</v>
       </c>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="6" t="n">
-        <v>245456.6</v>
+        <v>245500</v>
       </c>
       <c r="T3" s="7" t="n">
-        <v>85.16511676605965</v>
+        <v>85.13238289205702</v>
       </c>
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr"/>
@@ -811,7 +811,7 @@
       <c r="AD3" s="8" t="inlineStr"/>
       <c r="AE3" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:39</t>
+          <t>2025-10-18 11:08:19</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr"/>
@@ -839,7 +839,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.8%</t>
+          <t>1차 매수선까지 46.9%</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -858,26 +858,26 @@
         <v>54128</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>54228</v>
+        <v>54200</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>46.78763738290182</v>
+        <v>46.86346863468634</v>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="6" t="n">
-        <v>48855.2</v>
+        <v>48850</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>62.93045571402838</v>
+        <v>62.94779938587512</v>
       </c>
       <c r="Q4" s="8" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="6" t="n">
-        <v>44019.68000000001</v>
+        <v>44000</v>
       </c>
       <c r="T4" s="7" t="n">
-        <v>80.82821138181828</v>
+        <v>80.90909090909091</v>
       </c>
       <c r="U4" s="8" t="inlineStr"/>
       <c r="V4" s="8" t="inlineStr"/>
@@ -891,7 +891,7 @@
       <c r="AD4" s="8" t="inlineStr"/>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:39</t>
+          <t>2025-10-18 11:08:19</t>
         </is>
       </c>
       <c r="AF4" s="8" t="inlineStr"/>
@@ -938,26 +938,26 @@
         <v>199680</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>199780</v>
+        <v>199800</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>25.38792671939133</v>
+        <v>25.37537537537538</v>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="6" t="n">
-        <v>179902</v>
+        <v>179900</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>39.24247645940568</v>
+        <v>39.24402445803224</v>
       </c>
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="6" t="n">
-        <v>162011.8</v>
+        <v>162000</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>54.61836730410992</v>
+        <v>54.62962962962963</v>
       </c>
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
@@ -971,7 +971,7 @@
       <c r="AD5" s="8" t="inlineStr"/>
       <c r="AE5" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:40</t>
+          <t>2025-10-18 11:08:20</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr"/>
@@ -1018,26 +1018,26 @@
         <v>84888</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>84988</v>
+        <v>85000</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>64.14081988045372</v>
+        <v>64.11764705882354</v>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="6" t="n">
-        <v>76589.2</v>
+        <v>76600</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>82.14056289920772</v>
+        <v>82.11488250652742</v>
       </c>
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="6" t="n">
-        <v>69030.28</v>
+        <v>69000</v>
       </c>
       <c r="T6" s="7" t="n">
-        <v>102.0852298440626</v>
+        <v>102.1739130434783</v>
       </c>
       <c r="U6" s="8" t="inlineStr"/>
       <c r="V6" s="8" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       <c r="AD6" s="8" t="inlineStr"/>
       <c r="AE6" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:40</t>
+          <t>2025-10-18 11:08:20</t>
         </is>
       </c>
       <c r="AF6" s="8" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 57.2%</t>
+          <t>1차 매수선까지 57.1%</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -1098,26 +1098,26 @@
         <v>97188</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>97288</v>
+        <v>97300</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>57.16223994737275</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="M7" s="8" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="6" t="n">
-        <v>87659.2</v>
+        <v>87700</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>74.42550240020444</v>
+        <v>74.34435575826683</v>
       </c>
       <c r="Q7" s="8" t="inlineStr"/>
       <c r="R7" s="8" t="inlineStr"/>
       <c r="S7" s="6" t="n">
-        <v>78993.28</v>
+        <v>79000</v>
       </c>
       <c r="T7" s="7" t="n">
-        <v>93.56076871349057</v>
+        <v>93.54430379746836</v>
       </c>
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       <c r="AD7" s="8" t="inlineStr"/>
       <c r="AE7" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:40</t>
+          <t>2025-10-18 11:08:20</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr"/>
@@ -1178,26 +1178,26 @@
         <v>169360</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>169460</v>
+        <v>169500</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>46.93733034344388</v>
+        <v>46.90265486725664</v>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="6" t="n">
-        <v>152614</v>
+        <v>152700</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>63.15672218800372</v>
+        <v>63.0648330058939</v>
       </c>
       <c r="Q8" s="8" t="inlineStr"/>
       <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="6" t="n">
-        <v>137452.6</v>
+        <v>137500</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>81.15335759381779</v>
+        <v>81.09090909090909</v>
       </c>
       <c r="U8" s="8" t="inlineStr"/>
       <c r="V8" s="8" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       <c r="AD8" s="8" t="inlineStr"/>
       <c r="AE8" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:41</t>
+          <t>2025-10-18 11:08:21</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 74.3%</t>
+          <t>1차 매수선까지 74.4%</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1258,26 +1258,26 @@
         <v>40572</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>40622</v>
+        <v>40600</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>74.28979370784305</v>
+        <v>74.38423645320196</v>
       </c>
       <c r="M9" s="8" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="6" t="n">
-        <v>36609.8</v>
+        <v>36600</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>93.39084070385523</v>
+        <v>93.44262295081968</v>
       </c>
       <c r="Q9" s="8" t="inlineStr"/>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="6" t="n">
-        <v>32998.82000000001</v>
+        <v>33000</v>
       </c>
       <c r="T9" s="7" t="n">
-        <v>114.5531264451274</v>
+        <v>114.5454545454545</v>
       </c>
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       <c r="AD9" s="8" t="inlineStr"/>
       <c r="AE9" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:41</t>
+          <t>2025-10-18 11:08:21</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr"/>
@@ -1338,26 +1338,26 @@
         <v>40904</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>40954</v>
+        <v>40950</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>50.65683449724081</v>
+        <v>50.67155067155067</v>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="6" t="n">
-        <v>36908.6</v>
+        <v>36900</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>67.16971112423663</v>
+        <v>67.20867208672087</v>
       </c>
       <c r="Q10" s="8" t="inlineStr"/>
       <c r="R10" s="8" t="inlineStr"/>
       <c r="S10" s="6" t="n">
-        <v>33267.74</v>
+        <v>33250</v>
       </c>
       <c r="T10" s="7" t="n">
-        <v>85.4649579442427</v>
+        <v>85.56390977443608</v>
       </c>
       <c r="U10" s="8" t="inlineStr"/>
       <c r="V10" s="8" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="AD10" s="8" t="inlineStr"/>
       <c r="AE10" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:41</t>
+          <t>2025-10-18 11:08:21</t>
         </is>
       </c>
       <c r="AF10" s="8" t="inlineStr"/>
@@ -1418,26 +1418,26 @@
         <v>290680</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>291180</v>
+        <v>291000</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>44.75582114156192</v>
+        <v>44.84536082474227</v>
       </c>
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="6" t="n">
-        <v>262562</v>
+        <v>262500</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>60.53351208476474</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="6" t="n">
-        <v>236805.8</v>
+        <v>236500</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>77.99395116166917</v>
+        <v>78.22410147991543</v>
       </c>
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       <c r="AD11" s="8" t="inlineStr"/>
       <c r="AE11" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:42</t>
+          <t>2025-10-18 11:08:21</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr"/>
@@ -1498,26 +1498,26 @@
         <v>87436</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>87536</v>
+        <v>87500</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>22.57813927983915</v>
+        <v>22.62857142857143</v>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="6" t="n">
-        <v>78882.40000000001</v>
+        <v>78900</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>36.02527306471404</v>
+        <v>35.99493029150824</v>
       </c>
       <c r="Q12" s="8" t="inlineStr"/>
       <c r="R12" s="8" t="inlineStr"/>
       <c r="S12" s="6" t="n">
-        <v>71094.16</v>
+        <v>71100</v>
       </c>
       <c r="T12" s="7" t="n">
-        <v>50.92660212878244</v>
+        <v>50.91420534458509</v>
       </c>
       <c r="U12" s="8" t="inlineStr"/>
       <c r="V12" s="8" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="AD12" s="8" t="inlineStr"/>
       <c r="AE12" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:42</t>
+          <t>2025-10-18 11:08:22</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.3%</t>
+          <t>1차 매수선까지 41.4%</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1578,26 +1578,26 @@
         <v>29570</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>29620</v>
+        <v>29600</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>41.2896691424713</v>
+        <v>41.38513513513514</v>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="6" t="n">
-        <v>26708</v>
+        <v>26700</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>56.69462333383256</v>
+        <v>56.74157303370787</v>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
       <c r="S13" s="6" t="n">
-        <v>24087.2</v>
+        <v>24100</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>73.74373111029924</v>
+        <v>73.65145228215768</v>
       </c>
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       <c r="AD13" s="8" t="inlineStr"/>
       <c r="AE13" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:42</t>
+          <t>2025-10-18 11:08:22</t>
         </is>
       </c>
       <c r="AF13" s="8" t="inlineStr"/>
@@ -1658,26 +1658,26 @@
         <v>175960</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>176060</v>
+        <v>176100</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>36.60115869589913</v>
+        <v>36.57013060760931</v>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="6" t="n">
-        <v>158554</v>
+        <v>158600</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>51.68333816869962</v>
+        <v>51.63934426229508</v>
       </c>
       <c r="Q14" s="8" t="inlineStr"/>
       <c r="R14" s="8" t="inlineStr"/>
       <c r="S14" s="6" t="n">
-        <v>142798.6</v>
+        <v>142800</v>
       </c>
       <c r="T14" s="7" t="n">
-        <v>68.41901811362295</v>
+        <v>68.41736694677871</v>
       </c>
       <c r="U14" s="8" t="inlineStr"/>
       <c r="V14" s="8" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       <c r="AD14" s="8" t="inlineStr"/>
       <c r="AE14" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:43</t>
+          <t>2025-10-18 11:08:22</t>
         </is>
       </c>
       <c r="AF14" s="8" t="inlineStr"/>
@@ -1738,26 +1738,26 @@
         <v>119952</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>120052</v>
+        <v>120100</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>54.4330789991004</v>
+        <v>54.3713572023314</v>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="6" t="n">
-        <v>108146.8</v>
+        <v>108200</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>71.4336438988486</v>
+        <v>71.34935304990758</v>
       </c>
       <c r="Q15" s="8" t="inlineStr"/>
       <c r="R15" s="8" t="inlineStr"/>
       <c r="S15" s="6" t="n">
-        <v>97432.12000000001</v>
+        <v>97500</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>90.2863244687686</v>
+        <v>90.15384615384615</v>
       </c>
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       <c r="AD15" s="8" t="inlineStr"/>
       <c r="AE15" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:43</t>
+          <t>2025-10-18 11:08:23</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr"/>
@@ -1818,26 +1818,26 @@
         <v>6820.400000000001</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>6830.400000000001</v>
+        <v>6830</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>66.90091356289528</v>
+        <v>66.91068814055637</v>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="6" t="n">
-        <v>6157.360000000001</v>
+        <v>6160</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>85.14428261462703</v>
+        <v>85.06493506493507</v>
       </c>
       <c r="Q16" s="8" t="inlineStr"/>
       <c r="R16" s="8" t="inlineStr"/>
       <c r="S16" s="6" t="n">
-        <v>5551.624000000001</v>
+        <v>5550</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>105.3453187751908</v>
+        <v>105.4054054054054</v>
       </c>
       <c r="U16" s="8" t="inlineStr"/>
       <c r="V16" s="8" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="AD16" s="8" t="inlineStr"/>
       <c r="AE16" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:43</t>
+          <t>2025-10-18 11:08:23</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.5%</t>
+          <t>1차 매수선까지 41.4%</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1898,26 +1898,26 @@
         <v>233820</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>234320</v>
+        <v>234500</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>41.47319904404234</v>
+        <v>41.36460554371002</v>
       </c>
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="6" t="n">
-        <v>211388</v>
+        <v>211500</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>56.82063314852309</v>
+        <v>56.73758865248227</v>
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
       <c r="S17" s="6" t="n">
-        <v>190349.2</v>
+        <v>190500</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>74.15360821059399</v>
+        <v>74.01574803149606</v>
       </c>
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       <c r="AD17" s="8" t="inlineStr"/>
       <c r="AE17" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:44</t>
+          <t>2025-10-18 11:08:23</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 68.6%</t>
+          <t>1차 매수선까지 68.7%</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1978,26 +1978,26 @@
         <v>62228</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>62328</v>
+        <v>62300</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>68.62405339494289</v>
+        <v>68.69983948635634</v>
       </c>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="6" t="n">
-        <v>56195.2</v>
+        <v>56200</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>87.02664996298614</v>
+        <v>87.01067615658363</v>
       </c>
       <c r="Q18" s="8" t="inlineStr"/>
       <c r="R18" s="8" t="inlineStr"/>
       <c r="S18" s="6" t="n">
-        <v>50675.68000000001</v>
+        <v>50700</v>
       </c>
       <c r="T18" s="7" t="n">
-        <v>107.397315635429</v>
+        <v>107.2978303747534</v>
       </c>
       <c r="U18" s="8" t="inlineStr"/>
       <c r="V18" s="8" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       <c r="AD18" s="8" t="inlineStr"/>
       <c r="AE18" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:44</t>
+          <t>2025-10-18 11:08:23</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr"/>
@@ -2058,26 +2058,26 @@
         <v>473720</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>474220</v>
+        <v>474000</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>42.97161654928092</v>
+        <v>43.03797468354431</v>
       </c>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="6" t="n">
-        <v>427298</v>
+        <v>427000</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>58.67146581542624</v>
+        <v>58.78220140515222</v>
       </c>
       <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="6" t="n">
-        <v>385068.2</v>
+        <v>385000</v>
       </c>
       <c r="T19" s="7" t="n">
-        <v>76.07270608167592</v>
+        <v>76.1038961038961</v>
       </c>
       <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       <c r="AD19" s="8" t="inlineStr"/>
       <c r="AE19" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:44</t>
+          <t>2025-10-18 11:08:24</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 61.6%</t>
+          <t>1차 매수선까지 61.7%</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -2138,26 +2138,26 @@
         <v>25816</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>25866</v>
+        <v>25850</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>61.60210314698833</v>
+        <v>61.70212765957447</v>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="6" t="n">
-        <v>23329.4</v>
+        <v>23300</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>79.17306060164427</v>
+        <v>79.39914163090128</v>
       </c>
       <c r="Q20" s="8" t="inlineStr"/>
       <c r="R20" s="8" t="inlineStr"/>
       <c r="S20" s="6" t="n">
-        <v>21046.46</v>
+        <v>21000</v>
       </c>
       <c r="T20" s="7" t="n">
-        <v>98.60822200027935</v>
+        <v>99.04761904761905</v>
       </c>
       <c r="U20" s="8" t="inlineStr"/>
       <c r="V20" s="8" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       <c r="AD20" s="8" t="inlineStr"/>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:45</t>
+          <t>2025-10-18 11:08:24</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr"/>
@@ -2218,26 +2218,26 @@
         <v>122759.52</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>122859.52</v>
+        <v>122900</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>56.43883355559259</v>
+        <v>56.3873067534581</v>
       </c>
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="6" t="n">
-        <v>110673.568</v>
+        <v>110700</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>73.66386886523799</v>
+        <v>73.62240289069557</v>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="6" t="n">
-        <v>99706.21120000001</v>
+        <v>99700</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>92.76632587559399</v>
+        <v>92.77833500501504</v>
       </c>
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       <c r="AD21" s="8" t="inlineStr"/>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:45</t>
+          <t>2025-10-18 11:08:24</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.0%</t>
+          <t>1차 매수선까지 37.1%</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -2298,26 +2298,26 @@
         <v>54628</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>54728</v>
+        <v>54700</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>37.04136822102032</v>
+        <v>37.11151736745887</v>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="6" t="n">
-        <v>49305.2</v>
+        <v>49300</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>52.11377298946155</v>
+        <v>52.12981744421906</v>
       </c>
       <c r="Q22" s="8" t="inlineStr"/>
       <c r="R22" s="8" t="inlineStr"/>
       <c r="S22" s="6" t="n">
-        <v>44424.68000000001</v>
+        <v>44400</v>
       </c>
       <c r="T22" s="7" t="n">
-        <v>68.82507651152464</v>
+        <v>68.91891891891892</v>
       </c>
       <c r="U22" s="8" t="inlineStr"/>
       <c r="V22" s="8" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="AD22" s="8" t="inlineStr"/>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:45</t>
+          <t>2025-10-18 11:08:24</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr"/>
@@ -2378,26 +2378,26 @@
         <v>21286</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>21336</v>
+        <v>21350</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>2.643419572553431</v>
+        <v>2.576112412177986</v>
       </c>
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="6" t="n">
-        <v>19212.4</v>
+        <v>19230</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>13.98888218025857</v>
+        <v>13.88455538221529</v>
       </c>
       <c r="Q23" s="8" t="inlineStr"/>
       <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="6" t="n">
-        <v>17301.16</v>
+        <v>17320</v>
       </c>
       <c r="T23" s="7" t="n">
-        <v>26.5811078563518</v>
+        <v>26.44341801385681</v>
       </c>
       <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr"/>
@@ -2411,7 +2411,7 @@
       <c r="AD23" s="8" t="inlineStr"/>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:46</t>
+          <t>2025-10-18 11:08:25</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr"/>
@@ -2458,26 +2458,26 @@
         <v>8621.6</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>8631.6</v>
+        <v>8630</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>4.383891746605491</v>
+        <v>4.40324449594438</v>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="6" t="n">
-        <v>7778.440000000001</v>
+        <v>7780</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>15.83299479072924</v>
+        <v>15.80976863753213</v>
       </c>
       <c r="Q24" s="8" t="inlineStr"/>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="6" t="n">
-        <v>7010.596</v>
+        <v>7010</v>
       </c>
       <c r="T24" s="7" t="n">
-        <v>28.5197435424891</v>
+        <v>28.53067047075606</v>
       </c>
       <c r="U24" s="8" t="inlineStr"/>
       <c r="V24" s="8" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       <c r="AD24" s="8" t="inlineStr"/>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:46</t>
+          <t>2025-10-18 11:08:25</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr"/>
@@ -2538,26 +2538,26 @@
         <v>13321.2</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>13331.2</v>
+        <v>13330</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>19.19407105136821</v>
+        <v>19.20480120030007</v>
       </c>
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="6" t="n">
-        <v>12008.08</v>
+        <v>12010</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>32.32756610548896</v>
+        <v>32.30641132389675</v>
       </c>
       <c r="Q25" s="8" t="inlineStr"/>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="6" t="n">
-        <v>10817.272</v>
+        <v>10820</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>46.89470690946845</v>
+        <v>46.85767097966728</v>
       </c>
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="AD25" s="8" t="inlineStr"/>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:46</t>
+          <t>2025-10-18 11:08:25</t>
         </is>
       </c>
       <c r="AF25" s="8" t="inlineStr"/>
@@ -2618,26 +2618,26 @@
         <v>49392</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>49442</v>
+        <v>49450</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>16.9046559605194</v>
+        <v>16.88574317492417</v>
       </c>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
       <c r="O26" s="6" t="n">
-        <v>44547.8</v>
+        <v>44550</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>29.74827039719132</v>
+        <v>29.74186307519641</v>
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
       <c r="R26" s="8" t="inlineStr"/>
       <c r="S26" s="6" t="n">
-        <v>40143.02</v>
+        <v>40150</v>
       </c>
       <c r="T26" s="7" t="n">
-        <v>43.98518098538673</v>
+        <v>43.96014943960149</v>
       </c>
       <c r="U26" s="8" t="inlineStr"/>
       <c r="V26" s="8" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="AD26" s="8" t="inlineStr"/>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:47</t>
+          <t>2025-10-18 11:08:26</t>
         </is>
       </c>
       <c r="AF26" s="8" t="inlineStr"/>
@@ -2698,26 +2698,26 @@
         <v>251920</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>252420</v>
+        <v>252500</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>29.14982964899771</v>
+        <v>29.10891089108911</v>
       </c>
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr"/>
       <c r="O27" s="6" t="n">
-        <v>227678</v>
+        <v>227500</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>43.18467309094422</v>
+        <v>43.2967032967033</v>
       </c>
       <c r="Q27" s="8" t="inlineStr"/>
       <c r="R27" s="8" t="inlineStr"/>
       <c r="S27" s="6" t="n">
-        <v>205410.2</v>
+        <v>205500</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>58.70682176444986</v>
+        <v>58.63746958637469</v>
       </c>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       <c r="AD27" s="8" t="inlineStr"/>
       <c r="AE27" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:47</t>
+          <t>2025-10-18 11:08:26</t>
         </is>
       </c>
       <c r="AF27" s="8" t="inlineStr"/>
@@ -2778,26 +2778,26 @@
         <v>371060</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>371560</v>
+        <v>371500</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>15.05544192055119</v>
+        <v>15.07402422611036</v>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
       <c r="O28" s="6" t="n">
-        <v>334904</v>
+        <v>335000</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>27.64852017294508</v>
+        <v>27.61194029850746</v>
       </c>
       <c r="Q28" s="8" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="6" t="n">
-        <v>301913.6</v>
+        <v>302000</v>
       </c>
       <c r="T28" s="7" t="n">
-        <v>41.59680120405307</v>
+        <v>41.55629139072848</v>
       </c>
       <c r="U28" s="8" t="inlineStr"/>
       <c r="V28" s="8" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       <c r="AD28" s="8" t="inlineStr"/>
       <c r="AE28" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:48</t>
+          <t>2025-10-18 11:08:26</t>
         </is>
       </c>
       <c r="AF28" s="8" t="inlineStr"/>
@@ -2858,26 +2858,26 @@
         <v>138716</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>138816</v>
+        <v>138800</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>25.05763024435224</v>
+        <v>25.07204610951009</v>
       </c>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="6" t="n">
-        <v>125034.4</v>
+        <v>125000</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>38.84179073918857</v>
+        <v>38.88</v>
       </c>
       <c r="Q29" s="8" t="inlineStr"/>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="6" t="n">
-        <v>112630.96</v>
+        <v>112600</v>
       </c>
       <c r="T29" s="7" t="n">
-        <v>54.13168812553848</v>
+        <v>54.17406749555951</v>
       </c>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       <c r="AD29" s="8" t="inlineStr"/>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:48</t>
+          <t>2025-10-18 11:08:26</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr"/>
@@ -2938,26 +2938,26 @@
         <v>147728</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>147828</v>
+        <v>147800</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>8.91035527775523</v>
+        <v>8.930987821380242</v>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="6" t="n">
-        <v>133145.2</v>
+        <v>133100</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>20.92061899339967</v>
+        <v>20.96168294515402</v>
       </c>
       <c r="Q30" s="8" t="inlineStr"/>
       <c r="R30" s="8" t="inlineStr"/>
       <c r="S30" s="6" t="n">
-        <v>119930.68</v>
+        <v>119900</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>34.24421507490826</v>
+        <v>34.27856547122602</v>
       </c>
       <c r="U30" s="8" t="inlineStr"/>
       <c r="V30" s="8" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       <c r="AD30" s="8" t="inlineStr"/>
       <c r="AE30" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:48</t>
+          <t>2025-10-18 11:08:27</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr"/>
@@ -3018,26 +3018,26 @@
         <v>175040</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>175140</v>
+        <v>175100</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>13.90887290167866</v>
+        <v>13.93489434608795</v>
       </c>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="6" t="n">
-        <v>157726</v>
+        <v>157700</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>26.48517048552553</v>
+        <v>26.50602409638554</v>
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="6" t="n">
-        <v>142053.4</v>
+        <v>142000</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>40.4401443400862</v>
+        <v>40.49295774647887</v>
       </c>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
       <c r="AD31" s="8" t="inlineStr"/>
       <c r="AE31" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:49</t>
+          <t>2025-10-18 11:08:27</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr"/>
@@ -3098,26 +3098,26 @@
         <v>7814.400000000001</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>7824.400000000001</v>
+        <v>7820</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>14.25796227186748</v>
+        <v>14.32225063938619</v>
       </c>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="8" t="inlineStr"/>
       <c r="O32" s="6" t="n">
-        <v>7051.960000000001</v>
+        <v>7050</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>26.77326587218303</v>
+        <v>26.80851063829787</v>
       </c>
       <c r="Q32" s="8" t="inlineStr"/>
       <c r="R32" s="8" t="inlineStr"/>
       <c r="S32" s="6" t="n">
-        <v>6356.764000000001</v>
+        <v>6350</v>
       </c>
       <c r="T32" s="7" t="n">
-        <v>40.63759485172012</v>
+        <v>40.78740157480315</v>
       </c>
       <c r="U32" s="8" t="inlineStr"/>
       <c r="V32" s="8" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       <c r="AD32" s="8" t="inlineStr"/>
       <c r="AE32" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:49</t>
+          <t>2025-10-18 11:08:27</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr"/>
@@ -3178,26 +3178,26 @@
         <v>173380</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>173480</v>
+        <v>173500</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>15.86350011528707</v>
+        <v>15.85014409221902</v>
       </c>
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
       <c r="O33" s="6" t="n">
-        <v>156232</v>
+        <v>156300</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>28.65482103538328</v>
+        <v>28.59884836852207</v>
       </c>
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
       <c r="S33" s="6" t="n">
-        <v>140708.8</v>
+        <v>140800</v>
       </c>
       <c r="T33" s="7" t="n">
-        <v>42.84820849868663</v>
+        <v>42.75568181818182</v>
       </c>
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AD33" s="8" t="inlineStr"/>
       <c r="AE33" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:49</t>
+          <t>2025-10-18 11:08:27</t>
         </is>
       </c>
       <c r="AF33" s="8" t="inlineStr"/>
@@ -3258,26 +3258,26 @@
         <v>39146</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>39196</v>
+        <v>39200</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>64.30247984488213</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
       <c r="O34" s="6" t="n">
-        <v>35326.4</v>
+        <v>35350</v>
       </c>
       <c r="P34" s="7" t="n">
-        <v>82.29992300375922</v>
+        <v>82.17821782178217</v>
       </c>
       <c r="Q34" s="8" t="inlineStr"/>
       <c r="R34" s="8" t="inlineStr"/>
       <c r="S34" s="6" t="n">
-        <v>31843.76</v>
+        <v>31850</v>
       </c>
       <c r="T34" s="7" t="n">
-        <v>102.2374242237725</v>
+        <v>102.1978021978022</v>
       </c>
       <c r="U34" s="8" t="inlineStr"/>
       <c r="V34" s="8" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       <c r="AD34" s="8" t="inlineStr"/>
       <c r="AE34" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:50</t>
+          <t>2025-10-18 11:08:28</t>
         </is>
       </c>
       <c r="AF34" s="8" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.5%</t>
+          <t>1차 매수선까지 13.4%</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -3338,26 +3338,26 @@
         <v>83968</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>84068</v>
+        <v>84100</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>13.47956416234477</v>
+        <v>13.43638525564804</v>
       </c>
       <c r="M35" s="8" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
       <c r="O35" s="6" t="n">
-        <v>75761.2</v>
+        <v>75800</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>25.9219758926733</v>
+        <v>25.8575197889182</v>
       </c>
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="6" t="n">
-        <v>68285.08</v>
+        <v>68300</v>
       </c>
       <c r="T35" s="7" t="n">
-        <v>39.70841068063477</v>
+        <v>39.67789165446559</v>
       </c>
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       <c r="AD35" s="8" t="inlineStr"/>
       <c r="AE35" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:50</t>
+          <t>2025-10-18 11:08:28</t>
         </is>
       </c>
       <c r="AF35" s="8" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 1.1% (접근 중!)</t>
+          <t>1차 매수선까지 1.2% (접근 중!)</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -3418,26 +3418,26 @@
         <v>164336</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>164436</v>
+        <v>164400</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>1.133571723953392</v>
+        <v>1.155717761557178</v>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="6" t="n">
-        <v>148092.4</v>
+        <v>148100</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>12.29475651687731</v>
+        <v>12.28899392302498</v>
       </c>
       <c r="Q36" s="8" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
       <c r="S36" s="6" t="n">
-        <v>133383.16</v>
+        <v>133400</v>
       </c>
       <c r="T36" s="7" t="n">
-        <v>24.67840767905033</v>
+        <v>24.66266866566717</v>
       </c>
       <c r="U36" s="8" t="inlineStr"/>
       <c r="V36" s="8" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="AD36" s="8" t="inlineStr"/>
       <c r="AE36" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:50</t>
+          <t>2025-10-18 11:08:28</t>
         </is>
       </c>
       <c r="AF36" s="8" t="inlineStr"/>
@@ -3498,26 +3498,26 @@
         <v>361060</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>361560</v>
+        <v>361500</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>17.40789910388317</v>
+        <v>17.42738589211618</v>
       </c>
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="6" t="n">
-        <v>325904</v>
+        <v>326000</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>30.25308066178998</v>
+        <v>30.21472392638037</v>
       </c>
       <c r="Q37" s="8" t="inlineStr"/>
       <c r="R37" s="8" t="inlineStr"/>
       <c r="S37" s="6" t="n">
-        <v>293813.6</v>
+        <v>294000</v>
       </c>
       <c r="T37" s="7" t="n">
-        <v>44.4793569800717</v>
+        <v>44.38775510204081</v>
       </c>
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="AD37" s="8" t="inlineStr"/>
       <c r="AE37" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:51</t>
+          <t>2025-10-18 11:08:29</t>
         </is>
       </c>
       <c r="AF37" s="8" t="inlineStr"/>
@@ -3578,26 +3578,26 @@
         <v>19864</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19874</v>
+        <v>19870</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>7.678373754654322</v>
+        <v>7.700050327126321</v>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
       <c r="O38" s="6" t="n">
-        <v>17896.6</v>
+        <v>17890</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>19.57578534470233</v>
+        <v>19.61989938513136</v>
       </c>
       <c r="Q38" s="8" t="inlineStr"/>
       <c r="R38" s="8" t="inlineStr"/>
       <c r="S38" s="6" t="n">
-        <v>16116.94</v>
+        <v>16110</v>
       </c>
       <c r="T38" s="7" t="n">
-        <v>32.77954748233844</v>
+        <v>32.83674736188703</v>
       </c>
       <c r="U38" s="8" t="inlineStr"/>
       <c r="V38" s="8" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       <c r="AD38" s="8" t="inlineStr"/>
       <c r="AE38" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:51</t>
+          <t>2025-10-18 11:08:29</t>
         </is>
       </c>
       <c r="AF38" s="8" t="inlineStr"/>
@@ -3658,26 +3658,26 @@
         <v>22194</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>22244</v>
+        <v>22250</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>15.31199424563927</v>
+        <v>15.28089887640449</v>
       </c>
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="6" t="n">
-        <v>20069.6</v>
+        <v>20050</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>27.80523777255151</v>
+        <v>27.93017456359102</v>
       </c>
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
       <c r="S39" s="6" t="n">
-        <v>18072.64</v>
+        <v>18050</v>
       </c>
       <c r="T39" s="7" t="n">
-        <v>41.92724471908916</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
       <c r="AD39" s="8" t="inlineStr"/>
       <c r="AE39" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:51</t>
+          <t>2025-10-18 11:08:29</t>
         </is>
       </c>
       <c r="AF39" s="8" t="inlineStr"/>
@@ -3738,26 +3738,26 @@
         <v>17275.6</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>17285.6</v>
+        <v>17290</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>16.28176054056554</v>
+        <v>16.25216888374783</v>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="6" t="n">
-        <v>15567.04</v>
+        <v>15570</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>29.11895903138937</v>
+        <v>29.09441233140655</v>
       </c>
       <c r="Q40" s="8" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
       <c r="S40" s="6" t="n">
-        <v>14020.336</v>
+        <v>14020</v>
       </c>
       <c r="T40" s="7" t="n">
-        <v>43.36318330744709</v>
+        <v>43.36661911554921</v>
       </c>
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="8" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       <c r="AD40" s="8" t="inlineStr"/>
       <c r="AE40" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:52</t>
+          <t>2025-10-18 11:08:29</t>
         </is>
       </c>
       <c r="AF40" s="8" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.1%</t>
+          <t>1차 매수선까지 10.2%</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -3818,26 +3818,26 @@
         <v>43716</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>43766</v>
+        <v>43750</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>10.1311520358269</v>
+        <v>10.17142857142857</v>
       </c>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
       <c r="O41" s="6" t="n">
-        <v>39439.4</v>
+        <v>39450</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>22.21281256814251</v>
+        <v>22.17997465145754</v>
       </c>
       <c r="Q41" s="8" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
       <c r="S41" s="6" t="n">
-        <v>35545.46</v>
+        <v>35550</v>
       </c>
       <c r="T41" s="7" t="n">
-        <v>35.60100220956488</v>
+        <v>35.58368495077356</v>
       </c>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       <c r="AD41" s="8" t="inlineStr"/>
       <c r="AE41" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:52</t>
+          <t>2025-10-18 11:08:30</t>
         </is>
       </c>
       <c r="AF41" s="8" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.9%</t>
+          <t>1차 매수선까지 28.8%</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3898,26 +3898,26 @@
         <v>35998</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>36048</v>
+        <v>36050</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>28.85596981802042</v>
+        <v>28.84882108183079</v>
       </c>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="8" t="inlineStr"/>
       <c r="O42" s="6" t="n">
-        <v>32493.2</v>
+        <v>32500</v>
       </c>
       <c r="P42" s="7" t="n">
-        <v>42.95298708652887</v>
+        <v>42.92307692307693</v>
       </c>
       <c r="Q42" s="8" t="inlineStr"/>
       <c r="R42" s="8" t="inlineStr"/>
       <c r="S42" s="6" t="n">
-        <v>29293.88</v>
+        <v>29300</v>
       </c>
       <c r="T42" s="7" t="n">
-        <v>58.56554338312302</v>
+        <v>58.53242320819113</v>
       </c>
       <c r="U42" s="8" t="inlineStr"/>
       <c r="V42" s="8" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       <c r="AD42" s="8" t="inlineStr"/>
       <c r="AE42" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:52</t>
+          <t>2025-10-18 11:08:30</t>
         </is>
       </c>
       <c r="AF42" s="8" t="inlineStr"/>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.6% (접근 중!)</t>
+          <t>1차 매수선까지 9.5% (접근 중!)</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3978,26 +3978,26 @@
         <v>20532</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>20582</v>
+        <v>20600</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>9.561752988047809</v>
+        <v>9.466019417475728</v>
       </c>
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="6" t="n">
-        <v>18533.8</v>
+        <v>18550</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>21.66959824752615</v>
+        <v>21.5633423180593</v>
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="6" t="n">
-        <v>16690.42</v>
+        <v>16710</v>
       </c>
       <c r="T43" s="7" t="n">
-        <v>35.1074448695719</v>
+        <v>34.94913225613405</v>
       </c>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       <c r="AD43" s="8" t="inlineStr"/>
       <c r="AE43" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:53</t>
+          <t>2025-10-18 11:08:30</t>
         </is>
       </c>
       <c r="AF43" s="8" t="inlineStr"/>
@@ -4058,26 +4058,26 @@
         <v>328900</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>329400</v>
+        <v>329500</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>25.53126897389192</v>
+        <v>25.49317147192716</v>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="6" t="n">
-        <v>296960</v>
+        <v>297000</v>
       </c>
       <c r="P44" s="7" t="n">
-        <v>39.24434267241379</v>
+        <v>39.22558922558922</v>
       </c>
       <c r="Q44" s="8" t="inlineStr"/>
       <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="6" t="n">
-        <v>267764</v>
+        <v>268000</v>
       </c>
       <c r="T44" s="7" t="n">
-        <v>54.42703276019181</v>
+        <v>54.2910447761194</v>
       </c>
       <c r="U44" s="8" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       <c r="AD44" s="8" t="inlineStr"/>
       <c r="AE44" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:53</t>
+          <t>2025-10-18 11:08:31</t>
         </is>
       </c>
       <c r="AF44" s="8" t="inlineStr"/>
@@ -4138,26 +4138,26 @@
         <v>159452</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>159552</v>
+        <v>159600</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>25.03760529482551</v>
+        <v>25</v>
       </c>
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="6" t="n">
-        <v>143696.8</v>
+        <v>143700</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>38.83398934423033</v>
+        <v>38.83089770354906</v>
       </c>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
       <c r="S45" s="6" t="n">
-        <v>129427.12</v>
+        <v>129400</v>
       </c>
       <c r="T45" s="7" t="n">
-        <v>54.14080140236448</v>
+        <v>54.17310664605873</v>
       </c>
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       <c r="AD45" s="8" t="inlineStr"/>
       <c r="AE45" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:53</t>
+          <t>2025-10-18 11:08:31</t>
         </is>
       </c>
       <c r="AF45" s="8" t="inlineStr"/>
@@ -4218,26 +4218,26 @@
         <v>17368</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>17378</v>
+        <v>17380</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>27.74772701116354</v>
+        <v>27.73302646720368</v>
       </c>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="6" t="n">
-        <v>15650.2</v>
+        <v>15650</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>41.85122234859618</v>
+        <v>41.85303514376997</v>
       </c>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="6" t="n">
-        <v>14095.18</v>
+        <v>14090</v>
       </c>
       <c r="T46" s="7" t="n">
-        <v>57.50064915808098</v>
+        <v>57.55855216465579</v>
       </c>
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       <c r="AD46" s="8" t="inlineStr"/>
       <c r="AE46" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:54</t>
+          <t>2025-10-18 11:08:31</t>
         </is>
       </c>
       <c r="AF46" s="8" t="inlineStr"/>
@@ -4298,26 +4298,26 @@
         <v>1143920</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1144920</v>
+        <v>1145000</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>38.00090836040946</v>
+        <v>37.99126637554585</v>
       </c>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="6" t="n">
-        <v>1031428</v>
+        <v>1031000</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>53.18568043528003</v>
+        <v>53.24927255092143</v>
       </c>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
       <c r="S47" s="6" t="n">
-        <v>929285.2000000001</v>
+        <v>929000</v>
       </c>
       <c r="T47" s="7" t="n">
-        <v>70.02315327953139</v>
+        <v>70.07534983853606</v>
       </c>
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       <c r="AD47" s="8" t="inlineStr"/>
       <c r="AE47" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:54</t>
+          <t>2025-10-18 11:08:31</t>
         </is>
       </c>
       <c r="AF47" s="8" t="inlineStr"/>
@@ -4378,26 +4378,26 @@
         <v>393280</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>393780</v>
+        <v>394000</v>
       </c>
       <c r="L48" s="7" t="n">
-        <v>9.832901620194017</v>
+        <v>9.771573604060913</v>
       </c>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
       <c r="O48" s="6" t="n">
-        <v>354902</v>
+        <v>355000</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>21.86462741827321</v>
+        <v>21.83098591549296</v>
       </c>
       <c r="Q48" s="8" t="inlineStr"/>
       <c r="R48" s="8" t="inlineStr"/>
       <c r="S48" s="6" t="n">
-        <v>319911.8</v>
+        <v>320000</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>35.19351271194123</v>
+        <v>35.15625</v>
       </c>
       <c r="U48" s="8" t="inlineStr"/>
       <c r="V48" s="8" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
       <c r="AD48" s="8" t="inlineStr"/>
       <c r="AE48" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:54</t>
+          <t>2025-10-18 11:08:32</t>
         </is>
       </c>
       <c r="AF48" s="8" t="inlineStr"/>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.0%</t>
+          <t>1차 매수선까지 20.1%</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -4458,26 +4458,26 @@
         <v>33362</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>33412</v>
+        <v>33400</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>20.01676044534898</v>
+        <v>20.05988023952096</v>
       </c>
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="6" t="n">
-        <v>30120.8</v>
+        <v>30100</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>33.13059414092587</v>
+        <v>33.22259136212624</v>
       </c>
       <c r="Q49" s="8" t="inlineStr"/>
       <c r="R49" s="8" t="inlineStr"/>
       <c r="S49" s="6" t="n">
-        <v>27158.72</v>
+        <v>27150</v>
       </c>
       <c r="T49" s="7" t="n">
-        <v>47.65055201423336</v>
+        <v>47.69797421731123</v>
       </c>
       <c r="U49" s="8" t="inlineStr"/>
       <c r="V49" s="8" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       <c r="AD49" s="8" t="inlineStr"/>
       <c r="AE49" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:55</t>
+          <t>2025-10-18 11:08:32</t>
         </is>
       </c>
       <c r="AF49" s="8" t="inlineStr"/>
@@ -4546,18 +4546,18 @@
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
       <c r="O50" s="6" t="n">
-        <v>13366</v>
+        <v>13370</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>19.85635193775251</v>
+        <v>19.82049364248317</v>
       </c>
       <c r="Q50" s="8" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="6" t="n">
-        <v>12039.4</v>
+        <v>12040</v>
       </c>
       <c r="T50" s="7" t="n">
-        <v>33.06310945728193</v>
+        <v>33.05647840531562</v>
       </c>
       <c r="U50" s="8" t="inlineStr"/>
       <c r="V50" s="8" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       <c r="AD50" s="8" t="inlineStr"/>
       <c r="AE50" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:55</t>
+          <t>2025-10-18 11:08:32</t>
         </is>
       </c>
       <c r="AF50" s="8" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.2%</t>
+          <t>1차 매수선까지 10.1%</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -4618,26 +4618,26 @@
         <v>76976</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>77076</v>
+        <v>77100</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>10.15101977269189</v>
+        <v>10.11673151750973</v>
       </c>
       <c r="M51" s="8" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="6" t="n">
-        <v>69468.40000000001</v>
+        <v>69500</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>22.21384111336952</v>
+        <v>22.15827338129496</v>
       </c>
       <c r="Q51" s="8" t="inlineStr"/>
       <c r="R51" s="8" t="inlineStr"/>
       <c r="S51" s="6" t="n">
-        <v>62621.56000000001</v>
+        <v>62700</v>
       </c>
       <c r="T51" s="7" t="n">
-        <v>35.57630950107276</v>
+        <v>35.40669856459331</v>
       </c>
       <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       <c r="AD51" s="8" t="inlineStr"/>
       <c r="AE51" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:55</t>
+          <t>2025-10-18 11:08:32</t>
         </is>
       </c>
       <c r="AF51" s="8" t="inlineStr"/>
@@ -4698,26 +4698,26 @@
         <v>11183.6</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>11193.6</v>
+        <v>11190</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>26.85820468839336</v>
+        <v>26.89901697944593</v>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
       <c r="O52" s="6" t="n">
-        <v>10084.24</v>
+        <v>10080</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>40.81378467787359</v>
+        <v>40.87301587301587</v>
       </c>
       <c r="Q52" s="8" t="inlineStr"/>
       <c r="R52" s="8" t="inlineStr"/>
       <c r="S52" s="6" t="n">
-        <v>9085.816000000001</v>
+        <v>9080</v>
       </c>
       <c r="T52" s="7" t="n">
-        <v>56.28755854179744</v>
+        <v>56.38766519823789</v>
       </c>
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
       <c r="AD52" s="8" t="inlineStr"/>
       <c r="AE52" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:56</t>
+          <t>2025-10-18 11:08:33</t>
         </is>
       </c>
       <c r="AF52" s="8" t="inlineStr"/>
@@ -4778,26 +4778,26 @@
         <v>63720</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>63820</v>
+        <v>63800</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>19.08492635537449</v>
+        <v>19.12225705329153</v>
       </c>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
       <c r="O53" s="6" t="n">
-        <v>57538</v>
+        <v>57500</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>32.0866210156766</v>
+        <v>32.17391304347826</v>
       </c>
       <c r="Q53" s="8" t="inlineStr"/>
       <c r="R53" s="8" t="inlineStr"/>
       <c r="S53" s="6" t="n">
-        <v>51884.2</v>
+        <v>51900</v>
       </c>
       <c r="T53" s="7" t="n">
-        <v>46.48004594847756</v>
+        <v>46.4354527938343</v>
       </c>
       <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       <c r="AD53" s="8" t="inlineStr"/>
       <c r="AE53" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:56</t>
+          <t>2025-10-18 11:08:33</t>
         </is>
       </c>
       <c r="AF53" s="8" t="inlineStr"/>
@@ -4858,26 +4858,26 @@
         <v>188160</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>188260</v>
+        <v>188300</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>25.88972697333475</v>
+        <v>25.86298459904408</v>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
       <c r="O54" s="6" t="n">
-        <v>169534</v>
+        <v>169600</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>39.79496738117428</v>
+        <v>39.74056603773585</v>
       </c>
       <c r="Q54" s="8" t="inlineStr"/>
       <c r="R54" s="8" t="inlineStr"/>
       <c r="S54" s="6" t="n">
-        <v>152680.6</v>
+        <v>152700</v>
       </c>
       <c r="T54" s="7" t="n">
-        <v>55.22600775737061</v>
+        <v>55.20628683693517</v>
       </c>
       <c r="U54" s="8" t="inlineStr"/>
       <c r="V54" s="8" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       <c r="AD54" s="8" t="inlineStr"/>
       <c r="AE54" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:56</t>
+          <t>2025-10-18 11:08:33</t>
         </is>
       </c>
       <c r="AF54" s="8" t="inlineStr"/>
@@ -4938,26 +4938,26 @@
         <v>84496</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>84596</v>
+        <v>84600</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>19.03636105726039</v>
+        <v>19.03073286052009</v>
       </c>
       <c r="M55" s="8" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
       <c r="O55" s="6" t="n">
-        <v>76236.40000000001</v>
+        <v>76200</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>32.08913327491853</v>
+        <v>32.15223097112861</v>
       </c>
       <c r="Q55" s="8" t="inlineStr"/>
       <c r="R55" s="8" t="inlineStr"/>
       <c r="S55" s="6" t="n">
-        <v>68712.76000000001</v>
+        <v>68700</v>
       </c>
       <c r="T55" s="7" t="n">
-        <v>46.55211055413869</v>
+        <v>46.57933042212518</v>
       </c>
       <c r="U55" s="8" t="inlineStr"/>
       <c r="V55" s="8" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       <c r="AD55" s="8" t="inlineStr"/>
       <c r="AE55" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:57</t>
+          <t>2025-10-18 11:08:34</t>
         </is>
       </c>
       <c r="AF55" s="8" t="inlineStr"/>
@@ -5018,26 +5018,26 @@
         <v>816680</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>817680</v>
+        <v>818000</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>12.02426377066823</v>
+        <v>11.98044009779951</v>
       </c>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
       <c r="O56" s="6" t="n">
-        <v>736912</v>
+        <v>737000</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>24.30249473478516</v>
+        <v>24.2876526458616</v>
       </c>
       <c r="Q56" s="8" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
       <c r="S56" s="6" t="n">
-        <v>664220.8</v>
+        <v>664000</v>
       </c>
       <c r="T56" s="7" t="n">
-        <v>37.90594934696414</v>
+        <v>37.95180722891566</v>
       </c>
       <c r="U56" s="8" t="inlineStr"/>
       <c r="V56" s="8" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       <c r="AD56" s="8" t="inlineStr"/>
       <c r="AE56" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:57</t>
+          <t>2025-10-18 11:08:34</t>
         </is>
       </c>
       <c r="AF56" s="8" t="inlineStr"/>
@@ -5098,26 +5098,26 @@
         <v>45984</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>46034</v>
+        <v>46050</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>11.43937089976973</v>
+        <v>11.40065146579805</v>
       </c>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
       <c r="O57" s="6" t="n">
-        <v>41480.6</v>
+        <v>41500</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>23.67227089289933</v>
+        <v>23.6144578313253</v>
       </c>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
       <c r="S57" s="6" t="n">
-        <v>37382.54</v>
+        <v>37400</v>
       </c>
       <c r="T57" s="7" t="n">
-        <v>37.22984045492895</v>
+        <v>37.16577540106952</v>
       </c>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       <c r="AD57" s="8" t="inlineStr"/>
       <c r="AE57" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:57</t>
+          <t>2025-10-18 11:08:34</t>
         </is>
       </c>
       <c r="AF57" s="8" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.5%</t>
+          <t>1차 매수선까지 25.4%</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
@@ -5178,26 +5178,26 @@
         <v>23384</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>23434</v>
+        <v>23450</v>
       </c>
       <c r="L58" s="7" t="n">
-        <v>25.45873517111889</v>
+        <v>25.37313432835821</v>
       </c>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="6" t="n">
-        <v>21140.6</v>
+        <v>21150</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>39.0689005988477</v>
+        <v>39.00709219858156</v>
       </c>
       <c r="Q58" s="8" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="6" t="n">
-        <v>19036.54</v>
+        <v>19050</v>
       </c>
       <c r="T58" s="7" t="n">
-        <v>54.43982992707708</v>
+        <v>54.33070866141733</v>
       </c>
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       <c r="AD58" s="8" t="inlineStr"/>
       <c r="AE58" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:58</t>
+          <t>2025-10-18 11:08:34</t>
         </is>
       </c>
       <c r="AF58" s="8" t="inlineStr"/>
@@ -5258,26 +5258,26 @@
         <v>158640</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>158740</v>
+        <v>158700</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>27.5670908403679</v>
+        <v>27.59924385633271</v>
       </c>
       <c r="M59" s="8" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="6" t="n">
-        <v>142966</v>
+        <v>142900</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>41.64206874361736</v>
+        <v>41.7074877536739</v>
       </c>
       <c r="Q59" s="8" t="inlineStr"/>
       <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="6" t="n">
-        <v>128769.4</v>
+        <v>128700</v>
       </c>
       <c r="T59" s="7" t="n">
-        <v>57.25785784510915</v>
+        <v>57.34265734265735</v>
       </c>
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
@@ -5291,7 +5291,7 @@
       <c r="AD59" s="8" t="inlineStr"/>
       <c r="AE59" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:58</t>
+          <t>2025-10-18 11:08:35</t>
         </is>
       </c>
       <c r="AF59" s="8" t="inlineStr"/>
@@ -5338,26 +5338,26 @@
         <v>44768</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>44818</v>
+        <v>44800</v>
       </c>
       <c r="L60" s="7" t="n">
-        <v>13.57044044803427</v>
+        <v>13.61607142857143</v>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
       <c r="O60" s="6" t="n">
-        <v>40386.2</v>
+        <v>40350</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>26.03314993735483</v>
+        <v>26.14622057001239</v>
       </c>
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="6" t="n">
-        <v>36397.58</v>
+        <v>36350</v>
       </c>
       <c r="T60" s="7" t="n">
-        <v>39.84446218677175</v>
+        <v>40.02751031636863</v>
       </c>
       <c r="U60" s="8" t="inlineStr"/>
       <c r="V60" s="8" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
       <c r="AD60" s="8" t="inlineStr"/>
       <c r="AE60" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:58</t>
+          <t>2025-10-18 11:08:35</t>
         </is>
       </c>
       <c r="AF60" s="8" t="inlineStr"/>
@@ -5418,26 +5418,26 @@
         <v>12316.8</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>12326.8</v>
+        <v>12330</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>19.0901126001882</v>
+        <v>19.05920519059205</v>
       </c>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="6" t="n">
-        <v>11104.12</v>
+        <v>11110</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>32.20318224226683</v>
+        <v>32.13321332133214</v>
       </c>
       <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="6" t="n">
-        <v>10003.708</v>
+        <v>10010</v>
       </c>
       <c r="T61" s="7" t="n">
-        <v>46.74558673643812</v>
+        <v>46.65334665334665</v>
       </c>
       <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
@@ -5451,7 +5451,7 @@
       <c r="AD61" s="8" t="inlineStr"/>
       <c r="AE61" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:59</t>
+          <t>2025-10-18 11:08:35</t>
         </is>
       </c>
       <c r="AF61" s="8" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 23.8%</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
@@ -5498,26 +5498,26 @@
         <v>24332</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>24382</v>
+        <v>24400</v>
       </c>
       <c r="L62" s="7" t="n">
-        <v>23.86186531047494</v>
+        <v>23.77049180327869</v>
       </c>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
       <c r="O62" s="6" t="n">
-        <v>21993.8</v>
+        <v>22000</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>37.31142412861807</v>
+        <v>37.27272727272727</v>
       </c>
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="6" t="n">
-        <v>19804.42</v>
+        <v>19810</v>
       </c>
       <c r="T62" s="7" t="n">
-        <v>52.49121155782397</v>
+        <v>52.44825845532559</v>
       </c>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       <c r="AD62" s="8" t="inlineStr"/>
       <c r="AE62" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:59</t>
+          <t>2025-10-18 11:08:35</t>
         </is>
       </c>
       <c r="AF62" s="8" t="inlineStr"/>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.8%</t>
+          <t>1차 매수선까지 23.7%</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
@@ -5578,26 +5578,26 @@
         <v>2102.6</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>2107.6</v>
+        <v>2110</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>23.83754033023344</v>
+        <v>23.69668246445498</v>
       </c>
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
       <c r="O63" s="6" t="n">
-        <v>1897.84</v>
+        <v>1900</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>37.52476499599545</v>
+        <v>37.36842105263158</v>
       </c>
       <c r="Q63" s="8" t="inlineStr"/>
       <c r="R63" s="8" t="inlineStr"/>
       <c r="S63" s="6" t="n">
-        <v>1709.056</v>
+        <v>1711</v>
       </c>
       <c r="T63" s="7" t="n">
-        <v>52.71588526063511</v>
+        <v>52.54237288135594</v>
       </c>
       <c r="U63" s="8" t="inlineStr"/>
       <c r="V63" s="8" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       <c r="AD63" s="8" t="inlineStr"/>
       <c r="AE63" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:05:59</t>
+          <t>2025-10-18 11:08:36</t>
         </is>
       </c>
       <c r="AF63" s="8" t="inlineStr"/>
@@ -5658,26 +5658,26 @@
         <v>6229.200000000001</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>6239.200000000001</v>
+        <v>6240</v>
       </c>
       <c r="L64" s="7" t="n">
-        <v>4.981407872804193</v>
+        <v>4.967948717948718</v>
       </c>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="6" t="n">
-        <v>5625.280000000001</v>
+        <v>5630</v>
       </c>
       <c r="P64" s="7" t="n">
-        <v>16.43864838728026</v>
+        <v>16.34103019538188</v>
       </c>
       <c r="Q64" s="8" t="inlineStr"/>
       <c r="R64" s="8" t="inlineStr"/>
       <c r="S64" s="6" t="n">
-        <v>5072.752</v>
+        <v>5080</v>
       </c>
       <c r="T64" s="7" t="n">
-        <v>29.1212343911155</v>
+        <v>28.93700787401575</v>
       </c>
       <c r="U64" s="8" t="inlineStr"/>
       <c r="V64" s="8" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       <c r="AD64" s="8" t="inlineStr"/>
       <c r="AE64" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:00</t>
+          <t>2025-10-18 11:08:36</t>
         </is>
       </c>
       <c r="AF64" s="8" t="inlineStr"/>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.4%</t>
+          <t>1차 매수선까지 10.3%</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
@@ -5738,26 +5738,26 @@
         <v>118064</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>118164</v>
+        <v>118200</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>10.35509969195356</v>
+        <v>10.32148900169205</v>
       </c>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="6" t="n">
-        <v>106447.6</v>
+        <v>106500</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>22.50158763560662</v>
+        <v>22.44131455399061</v>
       </c>
       <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="6" t="n">
-        <v>95902.84000000001</v>
+        <v>95900</v>
       </c>
       <c r="T65" s="7" t="n">
-        <v>35.97094726287562</v>
+        <v>35.97497393117831</v>
       </c>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       <c r="AD65" s="8" t="inlineStr"/>
       <c r="AE65" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:00</t>
+          <t>2025-10-18 11:08:36</t>
         </is>
       </c>
       <c r="AF65" s="8" t="inlineStr"/>
@@ -5818,26 +5818,26 @@
         <v>30644</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>30694</v>
+        <v>30700</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>20.21893529680068</v>
+        <v>20.19543973941368</v>
       </c>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
       <c r="O66" s="6" t="n">
-        <v>27674.6</v>
+        <v>27700</v>
       </c>
       <c r="P66" s="7" t="n">
-        <v>33.33526049156988</v>
+        <v>33.2129963898917</v>
       </c>
       <c r="Q66" s="8" t="inlineStr"/>
       <c r="R66" s="8" t="inlineStr"/>
       <c r="S66" s="6" t="n">
-        <v>24957.14</v>
+        <v>25000</v>
       </c>
       <c r="T66" s="7" t="n">
-        <v>47.85348000612248</v>
+        <v>47.59999999999999</v>
       </c>
       <c r="U66" s="8" t="inlineStr"/>
       <c r="V66" s="8" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       <c r="AD66" s="8" t="inlineStr"/>
       <c r="AE66" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:00</t>
+          <t>2025-10-18 11:08:37</t>
         </is>
       </c>
       <c r="AF66" s="8" t="inlineStr"/>
@@ -5898,26 +5898,26 @@
         <v>8892</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>8902</v>
+        <v>8900</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>7.616266007638734</v>
+        <v>7.640449438202247</v>
       </c>
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="6" t="n">
-        <v>8021.8</v>
+        <v>8020</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>19.42456805205814</v>
+        <v>19.45137157107232</v>
       </c>
       <c r="Q67" s="8" t="inlineStr"/>
       <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="6" t="n">
-        <v>7229.62</v>
+        <v>7230</v>
       </c>
       <c r="T67" s="7" t="n">
-        <v>32.51042240117738</v>
+        <v>32.50345781466113</v>
       </c>
       <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       <c r="AD67" s="8" t="inlineStr"/>
       <c r="AE67" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:01</t>
+          <t>2025-10-18 11:08:37</t>
         </is>
       </c>
       <c r="AF67" s="8" t="inlineStr"/>
@@ -5978,26 +5978,26 @@
         <v>176796</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>176896</v>
+        <v>176900</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>44.7178002894356</v>
+        <v>44.71452798191068</v>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="6" t="n">
-        <v>159306.4</v>
+        <v>159300</v>
       </c>
       <c r="P68" s="7" t="n">
-        <v>60.69661984703691</v>
+        <v>60.70307595731325</v>
       </c>
       <c r="Q68" s="8" t="inlineStr"/>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="6" t="n">
-        <v>143475.76</v>
+        <v>143500</v>
       </c>
       <c r="T68" s="7" t="n">
-        <v>78.42735246706481</v>
+        <v>78.39721254355401</v>
       </c>
       <c r="U68" s="8" t="inlineStr"/>
       <c r="V68" s="8" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="AD68" s="8" t="inlineStr"/>
       <c r="AE68" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:01</t>
+          <t>2025-10-18 11:08:37</t>
         </is>
       </c>
       <c r="AF68" s="8" t="inlineStr"/>
@@ -6058,26 +6058,26 @@
         <v>223480</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>223980</v>
+        <v>224000</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>29.02937762300206</v>
+        <v>29.01785714285715</v>
       </c>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="6" t="n">
-        <v>202082</v>
+        <v>202000</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>43.01125285775081</v>
+        <v>43.06930693069307</v>
       </c>
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="6" t="n">
-        <v>181973.8</v>
+        <v>181900</v>
       </c>
       <c r="T69" s="7" t="n">
-        <v>58.81407103659976</v>
+        <v>58.87850467289719</v>
       </c>
       <c r="U69" s="8" t="inlineStr"/>
       <c r="V69" s="8" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       <c r="AD69" s="8" t="inlineStr"/>
       <c r="AE69" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:01</t>
+          <t>2025-10-18 11:08:37</t>
         </is>
       </c>
       <c r="AF69" s="8" t="inlineStr"/>
@@ -6138,26 +6138,26 @@
         <v>76272</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>76372</v>
+        <v>76400</v>
       </c>
       <c r="L70" s="7" t="n">
-        <v>23.60550987272823</v>
+        <v>23.56020942408377</v>
       </c>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
       <c r="O70" s="6" t="n">
-        <v>68834.8</v>
+        <v>68900</v>
       </c>
       <c r="P70" s="7" t="n">
-        <v>37.13993503286128</v>
+        <v>37.01015965166908</v>
       </c>
       <c r="Q70" s="8" t="inlineStr"/>
       <c r="R70" s="8" t="inlineStr"/>
       <c r="S70" s="6" t="n">
-        <v>62051.32000000001</v>
+        <v>62100</v>
       </c>
       <c r="T70" s="7" t="n">
-        <v>52.13213836546908</v>
+        <v>52.01288244766506</v>
       </c>
       <c r="U70" s="8" t="inlineStr"/>
       <c r="V70" s="8" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
       <c r="AD70" s="8" t="inlineStr"/>
       <c r="AE70" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:02</t>
+          <t>2025-10-18 11:08:38</t>
         </is>
       </c>
       <c r="AF70" s="8" t="inlineStr"/>
@@ -6218,26 +6218,26 @@
         <v>69424</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>69524</v>
+        <v>69500</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>17.65721189804959</v>
+        <v>17.69784172661871</v>
       </c>
       <c r="M71" s="8" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
       <c r="O71" s="6" t="n">
-        <v>62671.6</v>
+        <v>62700</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>30.5216397858041</v>
+        <v>30.46251993620415</v>
       </c>
       <c r="Q71" s="8" t="inlineStr"/>
       <c r="R71" s="8" t="inlineStr"/>
       <c r="S71" s="6" t="n">
-        <v>56504.44</v>
+        <v>56500</v>
       </c>
       <c r="T71" s="7" t="n">
-        <v>44.76738465154242</v>
+        <v>44.7787610619469</v>
       </c>
       <c r="U71" s="8" t="inlineStr"/>
       <c r="V71" s="8" t="inlineStr"/>
@@ -6251,7 +6251,7 @@
       <c r="AD71" s="8" t="inlineStr"/>
       <c r="AE71" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:02</t>
+          <t>2025-10-18 11:08:38</t>
         </is>
       </c>
       <c r="AF71" s="8" t="inlineStr"/>
@@ -6306,18 +6306,18 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
       <c r="O72" s="6" t="n">
-        <v>159130</v>
+        <v>159100</v>
       </c>
       <c r="P72" s="7" t="n">
-        <v>36.05228429585873</v>
+        <v>36.0779384035198</v>
       </c>
       <c r="Q72" s="8" t="inlineStr"/>
       <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="6" t="n">
-        <v>143317</v>
+        <v>143300</v>
       </c>
       <c r="T72" s="7" t="n">
-        <v>51.06372586643594</v>
+        <v>51.08164689462665</v>
       </c>
       <c r="U72" s="8" t="inlineStr"/>
       <c r="V72" s="8" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
       <c r="AD72" s="8" t="inlineStr"/>
       <c r="AE72" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:02</t>
+          <t>2025-10-18 11:08:38</t>
         </is>
       </c>
       <c r="AF72" s="8" t="inlineStr"/>
@@ -6378,26 +6378,26 @@
         <v>84112</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>84212</v>
+        <v>84200</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>35.2538830570465</v>
+        <v>35.27315914489311</v>
       </c>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="6" t="n">
-        <v>75890.8</v>
+        <v>75900</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>50.08406816109462</v>
+        <v>50.06587615283268</v>
       </c>
       <c r="Q73" s="8" t="inlineStr"/>
       <c r="R73" s="8" t="inlineStr"/>
       <c r="S73" s="6" t="n">
-        <v>68401.72</v>
+        <v>68400</v>
       </c>
       <c r="T73" s="7" t="n">
-        <v>66.51628058475723</v>
+        <v>66.52046783625731</v>
       </c>
       <c r="U73" s="8" t="inlineStr"/>
       <c r="V73" s="8" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       <c r="AD73" s="8" t="inlineStr"/>
       <c r="AE73" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:06:03</t>
+          <t>2025-10-18 11:08:38</t>
         </is>
       </c>
       <c r="AF73" s="8" t="inlineStr"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>최종 업데이트: 2025-10-18 11:08:39</t>
+          <t>최종 업데이트: 2025-10-18 11:11:39</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.0%</t>
+          <t>1차 매수선까지 38.8%</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -698,26 +698,26 @@
         <v>69244</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>69300</v>
+        <v>69400</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>38.96103896103897</v>
+        <v>38.76080691642652</v>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="6" t="n">
-        <v>62500</v>
+        <v>62600</v>
       </c>
       <c r="P2" s="7" t="n">
-        <v>54.08</v>
+        <v>53.83386581469649</v>
       </c>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="6" t="n">
-        <v>56300</v>
+        <v>56500</v>
       </c>
       <c r="T2" s="7" t="n">
-        <v>71.04795737122558</v>
+        <v>70.4424778761062</v>
       </c>
       <c r="U2" s="8" t="inlineStr"/>
       <c r="V2" s="8" t="inlineStr"/>
@@ -731,7 +731,7 @@
       <c r="AD2" s="8" t="inlineStr"/>
       <c r="AE2" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:18</t>
+          <t>2025-10-18 11:11:16</t>
         </is>
       </c>
       <c r="AF2" s="8" t="inlineStr"/>
@@ -794,10 +794,10 @@
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="6" t="n">
-        <v>245500</v>
+        <v>246000</v>
       </c>
       <c r="T3" s="7" t="n">
-        <v>85.13238289205702</v>
+        <v>84.7560975609756</v>
       </c>
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr"/>
@@ -811,7 +811,7 @@
       <c r="AD3" s="8" t="inlineStr"/>
       <c r="AE3" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:19</t>
+          <t>2025-10-18 11:11:16</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr"/>
@@ -839,7 +839,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.9%</t>
+          <t>1차 매수선까지 46.6%</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -858,26 +858,26 @@
         <v>54128</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>54200</v>
+        <v>54300</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>46.86346863468634</v>
+        <v>46.59300184162063</v>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="6" t="n">
-        <v>48850</v>
+        <v>48950</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>62.94779938587512</v>
+        <v>62.61491317671093</v>
       </c>
       <c r="Q4" s="8" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="6" t="n">
-        <v>44000</v>
+        <v>44150</v>
       </c>
       <c r="T4" s="7" t="n">
-        <v>80.90909090909091</v>
+        <v>80.29445073612685</v>
       </c>
       <c r="U4" s="8" t="inlineStr"/>
       <c r="V4" s="8" t="inlineStr"/>
@@ -891,7 +891,7 @@
       <c r="AD4" s="8" t="inlineStr"/>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:19</t>
+          <t>2025-10-18 11:11:17</t>
         </is>
       </c>
       <c r="AF4" s="8" t="inlineStr"/>
@@ -946,18 +946,18 @@
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="6" t="n">
-        <v>179900</v>
+        <v>180000</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>39.24402445803224</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="6" t="n">
-        <v>162000</v>
+        <v>162100</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>54.62962962962963</v>
+        <v>54.53423812461443</v>
       </c>
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
@@ -971,7 +971,7 @@
       <c r="AD5" s="8" t="inlineStr"/>
       <c r="AE5" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:20</t>
+          <t>2025-10-18 11:11:17</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="6" t="n">
-        <v>69000</v>
+        <v>69100</v>
       </c>
       <c r="T6" s="7" t="n">
-        <v>102.1739130434783</v>
+        <v>101.8813314037627</v>
       </c>
       <c r="U6" s="8" t="inlineStr"/>
       <c r="V6" s="8" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       <c r="AD6" s="8" t="inlineStr"/>
       <c r="AE6" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:20</t>
+          <t>2025-10-18 11:11:18</t>
         </is>
       </c>
       <c r="AF6" s="8" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
       <c r="Q7" s="8" t="inlineStr"/>
       <c r="R7" s="8" t="inlineStr"/>
       <c r="S7" s="6" t="n">
-        <v>79000</v>
+        <v>79100</v>
       </c>
       <c r="T7" s="7" t="n">
-        <v>93.54430379746836</v>
+        <v>93.29962073324906</v>
       </c>
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       <c r="AD7" s="8" t="inlineStr"/>
       <c r="AE7" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:20</t>
+          <t>2025-10-18 11:11:18</t>
         </is>
       </c>
       <c r="AF7" s="8" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
       <c r="Q8" s="8" t="inlineStr"/>
       <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="6" t="n">
-        <v>137500</v>
+        <v>137600</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>81.09090909090909</v>
+        <v>80.95930232558139</v>
       </c>
       <c r="U8" s="8" t="inlineStr"/>
       <c r="V8" s="8" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       <c r="AD8" s="8" t="inlineStr"/>
       <c r="AE8" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:21</t>
+          <t>2025-10-18 11:11:18</t>
         </is>
       </c>
       <c r="AF8" s="8" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 74.4%</t>
+          <t>1차 매수선까지 74.2%</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1258,26 +1258,26 @@
         <v>40572</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>40600</v>
+        <v>40650</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>74.38423645320196</v>
+        <v>74.16974169741697</v>
       </c>
       <c r="M9" s="8" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="6" t="n">
-        <v>36600</v>
+        <v>36650</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>93.44262295081968</v>
+        <v>93.17871759890861</v>
       </c>
       <c r="Q9" s="8" t="inlineStr"/>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="6" t="n">
-        <v>33000</v>
+        <v>33050</v>
       </c>
       <c r="T9" s="7" t="n">
-        <v>114.5454545454545</v>
+        <v>114.2208774583964</v>
       </c>
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       <c r="AD9" s="8" t="inlineStr"/>
       <c r="AE9" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:21</t>
+          <t>2025-10-18 11:11:19</t>
         </is>
       </c>
       <c r="AF9" s="8" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.7%</t>
+          <t>1차 매수선까지 50.5%</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1338,26 +1338,26 @@
         <v>40904</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>40950</v>
+        <v>41000</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>50.67155067155067</v>
+        <v>50.48780487804878</v>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="6" t="n">
-        <v>36900</v>
+        <v>36950</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>67.20867208672087</v>
+        <v>66.98240866035182</v>
       </c>
       <c r="Q10" s="8" t="inlineStr"/>
       <c r="R10" s="8" t="inlineStr"/>
       <c r="S10" s="6" t="n">
-        <v>33250</v>
+        <v>33350</v>
       </c>
       <c r="T10" s="7" t="n">
-        <v>85.56390977443608</v>
+        <v>85.00749625187406</v>
       </c>
       <c r="U10" s="8" t="inlineStr"/>
       <c r="V10" s="8" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="AD10" s="8" t="inlineStr"/>
       <c r="AE10" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:21</t>
+          <t>2025-10-18 11:11:19</t>
         </is>
       </c>
       <c r="AF10" s="8" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.8%</t>
+          <t>1차 매수선까지 44.6%</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -1418,26 +1418,26 @@
         <v>290680</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>291000</v>
+        <v>291500</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>44.84536082474227</v>
+        <v>44.59691252144082</v>
       </c>
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="6" t="n">
-        <v>262500</v>
+        <v>263000</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>60.57142857142858</v>
+        <v>60.26615969581749</v>
       </c>
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="6" t="n">
-        <v>236500</v>
+        <v>237500</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>78.22410147991543</v>
+        <v>77.47368421052632</v>
       </c>
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       <c r="AD11" s="8" t="inlineStr"/>
       <c r="AE11" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:21</t>
+          <t>2025-10-18 11:11:19</t>
         </is>
       </c>
       <c r="AF11" s="8" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.6%</t>
+          <t>1차 매수선까지 22.5%</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1498,26 +1498,26 @@
         <v>87436</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>87500</v>
+        <v>87600</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>22.62857142857143</v>
+        <v>22.48858447488584</v>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="6" t="n">
-        <v>78900</v>
+        <v>79000</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>35.99493029150824</v>
+        <v>35.82278481012658</v>
       </c>
       <c r="Q12" s="8" t="inlineStr"/>
       <c r="R12" s="8" t="inlineStr"/>
       <c r="S12" s="6" t="n">
-        <v>71100</v>
+        <v>71200</v>
       </c>
       <c r="T12" s="7" t="n">
-        <v>50.91420534458509</v>
+        <v>50.70224719101124</v>
       </c>
       <c r="U12" s="8" t="inlineStr"/>
       <c r="V12" s="8" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="AD12" s="8" t="inlineStr"/>
       <c r="AE12" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:22</t>
+          <t>2025-10-18 11:11:20</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.4%</t>
+          <t>1차 매수선까지 41.1%</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1578,26 +1578,26 @@
         <v>29570</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>29600</v>
+        <v>29650</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>41.38513513513514</v>
+        <v>41.14671163575042</v>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="6" t="n">
-        <v>26700</v>
+        <v>26750</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>56.74157303370787</v>
+        <v>56.44859813084112</v>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
       <c r="S13" s="6" t="n">
-        <v>24100</v>
+        <v>24150</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>73.65145228215768</v>
+        <v>73.29192546583852</v>
       </c>
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       <c r="AD13" s="8" t="inlineStr"/>
       <c r="AE13" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:22</t>
+          <t>2025-10-18 11:11:20</t>
         </is>
       </c>
       <c r="AF13" s="8" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
       <c r="Q14" s="8" t="inlineStr"/>
       <c r="R14" s="8" t="inlineStr"/>
       <c r="S14" s="6" t="n">
-        <v>142800</v>
+        <v>142900</v>
       </c>
       <c r="T14" s="7" t="n">
-        <v>68.41736694677871</v>
+        <v>68.29951014695591</v>
       </c>
       <c r="U14" s="8" t="inlineStr"/>
       <c r="V14" s="8" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       <c r="AD14" s="8" t="inlineStr"/>
       <c r="AE14" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:22</t>
+          <t>2025-10-18 11:11:20</t>
         </is>
       </c>
       <c r="AF14" s="8" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       <c r="AD15" s="8" t="inlineStr"/>
       <c r="AE15" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:23</t>
+          <t>2025-10-18 11:11:21</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 66.9%</t>
+          <t>1차 매수선까지 66.7%</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1818,26 +1818,26 @@
         <v>6820.400000000001</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>6830</v>
+        <v>6840</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>66.91068814055637</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="6" t="n">
-        <v>6160</v>
+        <v>6170</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>85.06493506493507</v>
+        <v>84.76499189627229</v>
       </c>
       <c r="Q16" s="8" t="inlineStr"/>
       <c r="R16" s="8" t="inlineStr"/>
       <c r="S16" s="6" t="n">
-        <v>5550</v>
+        <v>5570</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>105.4054054054054</v>
+        <v>104.6678635547576</v>
       </c>
       <c r="U16" s="8" t="inlineStr"/>
       <c r="V16" s="8" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="AD16" s="8" t="inlineStr"/>
       <c r="AE16" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:23</t>
+          <t>2025-10-18 11:11:21</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr"/>
@@ -1906,18 +1906,18 @@
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="6" t="n">
-        <v>211500</v>
+        <v>212000</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>56.73758865248227</v>
+        <v>56.36792452830188</v>
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
       <c r="S17" s="6" t="n">
-        <v>190500</v>
+        <v>190900</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>74.01574803149606</v>
+        <v>73.65112624410686</v>
       </c>
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       <c r="AD17" s="8" t="inlineStr"/>
       <c r="AE17" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:23</t>
+          <t>2025-10-18 11:11:21</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 68.7%</t>
+          <t>1차 매수선까지 68.4%</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1978,26 +1978,26 @@
         <v>62228</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>62300</v>
+        <v>62400</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>68.69983948635634</v>
+        <v>68.42948717948718</v>
       </c>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="6" t="n">
-        <v>56200</v>
+        <v>56300</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>87.01067615658363</v>
+        <v>86.67850799289521</v>
       </c>
       <c r="Q18" s="8" t="inlineStr"/>
       <c r="R18" s="8" t="inlineStr"/>
       <c r="S18" s="6" t="n">
-        <v>50700</v>
+        <v>50800</v>
       </c>
       <c r="T18" s="7" t="n">
-        <v>107.2978303747534</v>
+        <v>106.8897637795276</v>
       </c>
       <c r="U18" s="8" t="inlineStr"/>
       <c r="V18" s="8" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       <c r="AD18" s="8" t="inlineStr"/>
       <c r="AE18" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:23</t>
+          <t>2025-10-18 11:11:22</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.0%</t>
+          <t>1차 매수선까지 42.9%</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -2058,26 +2058,26 @@
         <v>473720</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>474000</v>
+        <v>474500</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>43.03797468354431</v>
+        <v>42.8872497365648</v>
       </c>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="6" t="n">
-        <v>427000</v>
+        <v>428000</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>58.78220140515222</v>
+        <v>58.41121495327103</v>
       </c>
       <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="6" t="n">
-        <v>385000</v>
+        <v>386000</v>
       </c>
       <c r="T19" s="7" t="n">
-        <v>76.1038961038961</v>
+        <v>75.64766839378238</v>
       </c>
       <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       <c r="AD19" s="8" t="inlineStr"/>
       <c r="AE19" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:24</t>
+          <t>2025-10-18 11:11:22</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 61.7%</t>
+          <t>1차 매수선까지 61.4%</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -2138,26 +2138,26 @@
         <v>25816</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>25850</v>
+        <v>25900</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>61.70212765957447</v>
+        <v>61.38996138996139</v>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="6" t="n">
-        <v>23300</v>
+        <v>23400</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>79.39914163090128</v>
+        <v>78.63247863247864</v>
       </c>
       <c r="Q20" s="8" t="inlineStr"/>
       <c r="R20" s="8" t="inlineStr"/>
       <c r="S20" s="6" t="n">
-        <v>21000</v>
+        <v>21150</v>
       </c>
       <c r="T20" s="7" t="n">
-        <v>99.04761904761905</v>
+        <v>97.63593380614657</v>
       </c>
       <c r="U20" s="8" t="inlineStr"/>
       <c r="V20" s="8" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       <c r="AD20" s="8" t="inlineStr"/>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:24</t>
+          <t>2025-10-18 11:11:22</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr"/>
@@ -2226,18 +2226,18 @@
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="6" t="n">
-        <v>110700</v>
+        <v>110800</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>73.62240289069557</v>
+        <v>73.46570397111914</v>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="6" t="n">
-        <v>99700</v>
+        <v>99900</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>92.77833500501504</v>
+        <v>92.3923923923924</v>
       </c>
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       <c r="AD21" s="8" t="inlineStr"/>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:24</t>
+          <t>2025-10-18 11:11:23</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.1%</t>
+          <t>1차 매수선까지 36.9%</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -2298,26 +2298,26 @@
         <v>54628</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>54700</v>
+        <v>54800</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>37.11151736745887</v>
+        <v>36.86131386861314</v>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="6" t="n">
-        <v>49300</v>
+        <v>49400</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>52.12981744421906</v>
+        <v>51.82186234817814</v>
       </c>
       <c r="Q22" s="8" t="inlineStr"/>
       <c r="R22" s="8" t="inlineStr"/>
       <c r="S22" s="6" t="n">
-        <v>44400</v>
+        <v>44550</v>
       </c>
       <c r="T22" s="7" t="n">
-        <v>68.91891891891892</v>
+        <v>68.35016835016835</v>
       </c>
       <c r="U22" s="8" t="inlineStr"/>
       <c r="V22" s="8" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="AD22" s="8" t="inlineStr"/>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:24</t>
+          <t>2025-10-18 11:11:23</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr"/>
@@ -2411,7 +2411,7 @@
       <c r="AD23" s="8" t="inlineStr"/>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:25</t>
+          <t>2025-10-18 11:11:23</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr"/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 4.4% (접근 중!)</t>
+          <t>1차 매수선까지 4.3% (접근 중!)</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2458,26 +2458,26 @@
         <v>8621.6</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>8630</v>
+        <v>8640</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>4.40324449594438</v>
+        <v>4.282407407407407</v>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="6" t="n">
-        <v>7780</v>
+        <v>7790</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>15.80976863753213</v>
+        <v>15.66110397946085</v>
       </c>
       <c r="Q24" s="8" t="inlineStr"/>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="6" t="n">
-        <v>7010</v>
+        <v>7030</v>
       </c>
       <c r="T24" s="7" t="n">
-        <v>28.53067047075606</v>
+        <v>28.16500711237553</v>
       </c>
       <c r="U24" s="8" t="inlineStr"/>
       <c r="V24" s="8" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       <c r="AD24" s="8" t="inlineStr"/>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:25</t>
+          <t>2025-10-18 11:11:24</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.2%</t>
+          <t>1차 매수선까지 19.1%</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2538,26 +2538,26 @@
         <v>13321.2</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>13330</v>
+        <v>13340</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>19.20480120030007</v>
+        <v>19.11544227886057</v>
       </c>
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="6" t="n">
-        <v>12010</v>
+        <v>12020</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>32.30641132389675</v>
+        <v>32.1963394342762</v>
       </c>
       <c r="Q25" s="8" t="inlineStr"/>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="6" t="n">
-        <v>10820</v>
+        <v>10830</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>46.85767097966728</v>
+        <v>46.72206832871652</v>
       </c>
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="AD25" s="8" t="inlineStr"/>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:25</t>
+          <t>2025-10-18 11:11:24</t>
         </is>
       </c>
       <c r="AF25" s="8" t="inlineStr"/>
@@ -2626,18 +2626,18 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
       <c r="O26" s="6" t="n">
-        <v>44550</v>
+        <v>44600</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>29.74186307519641</v>
+        <v>29.59641255605381</v>
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
       <c r="R26" s="8" t="inlineStr"/>
       <c r="S26" s="6" t="n">
-        <v>40150</v>
+        <v>40200</v>
       </c>
       <c r="T26" s="7" t="n">
-        <v>43.96014943960149</v>
+        <v>43.78109452736319</v>
       </c>
       <c r="U26" s="8" t="inlineStr"/>
       <c r="V26" s="8" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="AD26" s="8" t="inlineStr"/>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:26</t>
+          <t>2025-10-18 11:11:24</t>
         </is>
       </c>
       <c r="AF26" s="8" t="inlineStr"/>
@@ -2706,18 +2706,18 @@
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr"/>
       <c r="O27" s="6" t="n">
-        <v>227500</v>
+        <v>228000</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>43.2967032967033</v>
+        <v>42.98245614035088</v>
       </c>
       <c r="Q27" s="8" t="inlineStr"/>
       <c r="R27" s="8" t="inlineStr"/>
       <c r="S27" s="6" t="n">
-        <v>205500</v>
+        <v>206000</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>58.63746958637469</v>
+        <v>58.25242718446601</v>
       </c>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       <c r="AD27" s="8" t="inlineStr"/>
       <c r="AE27" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:26</t>
+          <t>2025-10-18 11:11:25</t>
         </is>
       </c>
       <c r="AF27" s="8" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.1%</t>
+          <t>1차 매수선까지 14.9%</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
@@ -2778,26 +2778,26 @@
         <v>371060</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>371500</v>
+        <v>372000</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>15.07402422611036</v>
+        <v>14.91935483870968</v>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
       <c r="O28" s="6" t="n">
-        <v>335000</v>
+        <v>335500</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>27.61194029850746</v>
+        <v>27.42175856929955</v>
       </c>
       <c r="Q28" s="8" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="6" t="n">
-        <v>302000</v>
+        <v>302500</v>
       </c>
       <c r="T28" s="7" t="n">
-        <v>41.55629139072848</v>
+        <v>41.32231404958678</v>
       </c>
       <c r="U28" s="8" t="inlineStr"/>
       <c r="V28" s="8" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       <c r="AD28" s="8" t="inlineStr"/>
       <c r="AE28" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:26</t>
+          <t>2025-10-18 11:11:25</t>
         </is>
       </c>
       <c r="AF28" s="8" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.1%</t>
+          <t>1차 매수선까지 25.0%</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2858,26 +2858,26 @@
         <v>138716</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>138800</v>
+        <v>138900</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>25.07204610951009</v>
+        <v>24.98200143988481</v>
       </c>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="6" t="n">
-        <v>125000</v>
+        <v>125200</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>38.88</v>
+        <v>38.65814696485623</v>
       </c>
       <c r="Q29" s="8" t="inlineStr"/>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="6" t="n">
-        <v>112600</v>
+        <v>112800</v>
       </c>
       <c r="T29" s="7" t="n">
-        <v>54.17406749555951</v>
+        <v>53.90070921985816</v>
       </c>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       <c r="AD29" s="8" t="inlineStr"/>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:26</t>
+          <t>2025-10-18 11:11:26</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr"/>
@@ -2938,26 +2938,26 @@
         <v>147728</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>147800</v>
+        <v>147900</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>8.930987821380242</v>
+        <v>8.857336037863421</v>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="6" t="n">
-        <v>133100</v>
+        <v>133300</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>20.96168294515402</v>
+        <v>20.78019504876219</v>
       </c>
       <c r="Q30" s="8" t="inlineStr"/>
       <c r="R30" s="8" t="inlineStr"/>
       <c r="S30" s="6" t="n">
-        <v>119900</v>
+        <v>120100</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>34.27856547122602</v>
+        <v>34.05495420482931</v>
       </c>
       <c r="U30" s="8" t="inlineStr"/>
       <c r="V30" s="8" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       <c r="AD30" s="8" t="inlineStr"/>
       <c r="AE30" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:27</t>
+          <t>2025-10-18 11:11:26</t>
         </is>
       </c>
       <c r="AF30" s="8" t="inlineStr"/>
@@ -3018,26 +3018,26 @@
         <v>175040</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>175100</v>
+        <v>175200</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>13.93489434608795</v>
+        <v>13.86986301369863</v>
       </c>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="6" t="n">
-        <v>157700</v>
+        <v>157800</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>26.50602409638554</v>
+        <v>26.42585551330798</v>
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="6" t="n">
-        <v>142000</v>
+        <v>142200</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>40.49295774647887</v>
+        <v>40.29535864978903</v>
       </c>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
       <c r="AD31" s="8" t="inlineStr"/>
       <c r="AE31" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:27</t>
+          <t>2025-10-18 11:11:26</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.3%</t>
+          <t>1차 매수선까지 14.2%</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -3098,26 +3098,26 @@
         <v>7814.400000000001</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>7820</v>
+        <v>7830</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>14.32225063938619</v>
+        <v>14.17624521072797</v>
       </c>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="8" t="inlineStr"/>
       <c r="O32" s="6" t="n">
-        <v>7050</v>
+        <v>7060</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>26.80851063829787</v>
+        <v>26.62889518413597</v>
       </c>
       <c r="Q32" s="8" t="inlineStr"/>
       <c r="R32" s="8" t="inlineStr"/>
       <c r="S32" s="6" t="n">
-        <v>6350</v>
+        <v>6370</v>
       </c>
       <c r="T32" s="7" t="n">
-        <v>40.78740157480315</v>
+        <v>40.34536891679748</v>
       </c>
       <c r="U32" s="8" t="inlineStr"/>
       <c r="V32" s="8" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       <c r="AD32" s="8" t="inlineStr"/>
       <c r="AE32" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:27</t>
+          <t>2025-10-18 11:11:27</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AD33" s="8" t="inlineStr"/>
       <c r="AE33" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:27</t>
+          <t>2025-10-18 11:11:27</t>
         </is>
       </c>
       <c r="AF33" s="8" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
       <c r="Q34" s="8" t="inlineStr"/>
       <c r="R34" s="8" t="inlineStr"/>
       <c r="S34" s="6" t="n">
-        <v>31850</v>
+        <v>31900</v>
       </c>
       <c r="T34" s="7" t="n">
-        <v>102.1978021978022</v>
+        <v>101.8808777429467</v>
       </c>
       <c r="U34" s="8" t="inlineStr"/>
       <c r="V34" s="8" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       <c r="AD34" s="8" t="inlineStr"/>
       <c r="AE34" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:28</t>
+          <t>2025-10-18 11:11:27</t>
         </is>
       </c>
       <c r="AF34" s="8" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="6" t="n">
-        <v>68300</v>
+        <v>68400</v>
       </c>
       <c r="T35" s="7" t="n">
-        <v>39.67789165446559</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       <c r="AD35" s="8" t="inlineStr"/>
       <c r="AE35" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:28</t>
+          <t>2025-10-18 11:11:28</t>
         </is>
       </c>
       <c r="AF35" s="8" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 1.2% (접근 중!)</t>
+          <t>1차 매수선까지 1.1% (접근 중!)</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -3418,26 +3418,26 @@
         <v>164336</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>164400</v>
+        <v>164500</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>1.155717761557178</v>
+        <v>1.094224924012158</v>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="6" t="n">
-        <v>148100</v>
+        <v>148200</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>12.28899392302498</v>
+        <v>12.21322537112011</v>
       </c>
       <c r="Q36" s="8" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
       <c r="S36" s="6" t="n">
-        <v>133400</v>
+        <v>133500</v>
       </c>
       <c r="T36" s="7" t="n">
-        <v>24.66266866566717</v>
+        <v>24.56928838951311</v>
       </c>
       <c r="U36" s="8" t="inlineStr"/>
       <c r="V36" s="8" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="AD36" s="8" t="inlineStr"/>
       <c r="AE36" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:28</t>
+          <t>2025-10-18 11:11:28</t>
         </is>
       </c>
       <c r="AF36" s="8" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.4%</t>
+          <t>1차 매수선까지 17.3%</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -3498,26 +3498,26 @@
         <v>361060</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>361500</v>
+        <v>362000</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>17.42738589211618</v>
+        <v>17.26519337016575</v>
       </c>
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="6" t="n">
-        <v>326000</v>
+        <v>326500</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>30.21472392638037</v>
+        <v>30.01531393568147</v>
       </c>
       <c r="Q37" s="8" t="inlineStr"/>
       <c r="R37" s="8" t="inlineStr"/>
       <c r="S37" s="6" t="n">
-        <v>294000</v>
+        <v>294500</v>
       </c>
       <c r="T37" s="7" t="n">
-        <v>44.38775510204081</v>
+        <v>44.14261460101868</v>
       </c>
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="AD37" s="8" t="inlineStr"/>
       <c r="AE37" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:29</t>
+          <t>2025-10-18 11:11:28</t>
         </is>
       </c>
       <c r="AF37" s="8" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 7.7% (접근 중!)</t>
+          <t>1차 매수선까지 7.6% (접근 중!)</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -3578,26 +3578,26 @@
         <v>19864</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19870</v>
+        <v>19880</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>7.700050327126321</v>
+        <v>7.645875251509055</v>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
       <c r="O38" s="6" t="n">
-        <v>17890</v>
+        <v>17910</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>19.61989938513136</v>
+        <v>19.48632049134562</v>
       </c>
       <c r="Q38" s="8" t="inlineStr"/>
       <c r="R38" s="8" t="inlineStr"/>
       <c r="S38" s="6" t="n">
-        <v>16110</v>
+        <v>16130</v>
       </c>
       <c r="T38" s="7" t="n">
-        <v>32.83674736188703</v>
+        <v>32.67203967761934</v>
       </c>
       <c r="U38" s="8" t="inlineStr"/>
       <c r="V38" s="8" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       <c r="AD38" s="8" t="inlineStr"/>
       <c r="AE38" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:29</t>
+          <t>2025-10-18 11:11:29</t>
         </is>
       </c>
       <c r="AF38" s="8" t="inlineStr"/>
@@ -3666,18 +3666,18 @@
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="6" t="n">
-        <v>20050</v>
+        <v>20100</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>27.93017456359102</v>
+        <v>27.61194029850746</v>
       </c>
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
       <c r="S39" s="6" t="n">
-        <v>18050</v>
+        <v>18100</v>
       </c>
       <c r="T39" s="7" t="n">
-        <v>42.10526315789473</v>
+        <v>41.71270718232044</v>
       </c>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
       <c r="AD39" s="8" t="inlineStr"/>
       <c r="AE39" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:29</t>
+          <t>2025-10-18 11:11:29</t>
         </is>
       </c>
       <c r="AF39" s="8" t="inlineStr"/>
@@ -3746,18 +3746,18 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="6" t="n">
-        <v>15570</v>
+        <v>15580</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>29.09441233140655</v>
+        <v>29.01155327342747</v>
       </c>
       <c r="Q40" s="8" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
       <c r="S40" s="6" t="n">
-        <v>14020</v>
+        <v>14040</v>
       </c>
       <c r="T40" s="7" t="n">
-        <v>43.36661911554921</v>
+        <v>43.16239316239317</v>
       </c>
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="8" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       <c r="AD40" s="8" t="inlineStr"/>
       <c r="AE40" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:29</t>
+          <t>2025-10-18 11:11:29</t>
         </is>
       </c>
       <c r="AF40" s="8" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.2%</t>
+          <t>1차 매수선까지 10.0%</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -3818,26 +3818,26 @@
         <v>43716</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>43750</v>
+        <v>43800</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>10.17142857142857</v>
+        <v>10.04566210045662</v>
       </c>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
       <c r="O41" s="6" t="n">
-        <v>39450</v>
+        <v>39500</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>22.17997465145754</v>
+        <v>22.0253164556962</v>
       </c>
       <c r="Q41" s="8" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
       <c r="S41" s="6" t="n">
-        <v>35550</v>
+        <v>35600</v>
       </c>
       <c r="T41" s="7" t="n">
-        <v>35.58368495077356</v>
+        <v>35.39325842696629</v>
       </c>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       <c r="AD41" s="8" t="inlineStr"/>
       <c r="AE41" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:30</t>
+          <t>2025-10-18 11:11:30</t>
         </is>
       </c>
       <c r="AF41" s="8" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       <c r="AD42" s="8" t="inlineStr"/>
       <c r="AE42" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:30</t>
+          <t>2025-10-18 11:11:30</t>
         </is>
       </c>
       <c r="AF42" s="8" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       <c r="AD43" s="8" t="inlineStr"/>
       <c r="AE43" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:30</t>
+          <t>2025-10-18 11:11:30</t>
         </is>
       </c>
       <c r="AF43" s="8" t="inlineStr"/>
@@ -4066,18 +4066,18 @@
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="6" t="n">
-        <v>297000</v>
+        <v>297500</v>
       </c>
       <c r="P44" s="7" t="n">
-        <v>39.22558922558922</v>
+        <v>38.99159663865547</v>
       </c>
       <c r="Q44" s="8" t="inlineStr"/>
       <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="6" t="n">
-        <v>268000</v>
+        <v>268500</v>
       </c>
       <c r="T44" s="7" t="n">
-        <v>54.2910447761194</v>
+        <v>54.00372439478585</v>
       </c>
       <c r="U44" s="8" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       <c r="AD44" s="8" t="inlineStr"/>
       <c r="AE44" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:31</t>
+          <t>2025-10-18 11:11:31</t>
         </is>
       </c>
       <c r="AF44" s="8" t="inlineStr"/>
@@ -4146,18 +4146,18 @@
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="6" t="n">
-        <v>143700</v>
+        <v>143800</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>38.83089770354906</v>
+        <v>38.73435326842837</v>
       </c>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
       <c r="S45" s="6" t="n">
-        <v>129400</v>
+        <v>129600</v>
       </c>
       <c r="T45" s="7" t="n">
-        <v>54.17310664605873</v>
+        <v>53.93518518518518</v>
       </c>
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       <c r="AD45" s="8" t="inlineStr"/>
       <c r="AE45" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:31</t>
+          <t>2025-10-18 11:11:31</t>
         </is>
       </c>
       <c r="AF45" s="8" t="inlineStr"/>
@@ -4226,18 +4226,18 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="6" t="n">
-        <v>15650</v>
+        <v>15660</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>41.85303514376997</v>
+        <v>41.7624521072797</v>
       </c>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="6" t="n">
-        <v>14090</v>
+        <v>14110</v>
       </c>
       <c r="T46" s="7" t="n">
-        <v>57.55855216465579</v>
+        <v>57.33522324592487</v>
       </c>
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       <c r="AD46" s="8" t="inlineStr"/>
       <c r="AE46" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:31</t>
+          <t>2025-10-18 11:11:31</t>
         </is>
       </c>
       <c r="AF46" s="8" t="inlineStr"/>
@@ -4306,18 +4306,18 @@
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="6" t="n">
-        <v>1031000</v>
+        <v>1032000</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>53.24927255092143</v>
+        <v>53.10077519379846</v>
       </c>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
       <c r="S47" s="6" t="n">
-        <v>929000</v>
+        <v>930000</v>
       </c>
       <c r="T47" s="7" t="n">
-        <v>70.07534983853606</v>
+        <v>69.89247311827957</v>
       </c>
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       <c r="AD47" s="8" t="inlineStr"/>
       <c r="AE47" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:31</t>
+          <t>2025-10-18 11:11:32</t>
         </is>
       </c>
       <c r="AF47" s="8" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
       <c r="O48" s="6" t="n">
-        <v>355000</v>
+        <v>355500</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>21.83098591549296</v>
+        <v>21.65963431786217</v>
       </c>
       <c r="Q48" s="8" t="inlineStr"/>
       <c r="R48" s="8" t="inlineStr"/>
       <c r="S48" s="6" t="n">
-        <v>320000</v>
+        <v>320500</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>35.15625</v>
+        <v>34.94539781591264</v>
       </c>
       <c r="U48" s="8" t="inlineStr"/>
       <c r="V48" s="8" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
       <c r="AD48" s="8" t="inlineStr"/>
       <c r="AE48" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:32</t>
+          <t>2025-10-18 11:11:32</t>
         </is>
       </c>
       <c r="AF48" s="8" t="inlineStr"/>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.1%</t>
+          <t>1차 매수선까지 19.9%</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -4458,26 +4458,26 @@
         <v>33362</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>33400</v>
+        <v>33450</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>20.05988023952096</v>
+        <v>19.88041853512706</v>
       </c>
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="6" t="n">
-        <v>30100</v>
+        <v>30200</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>33.22259136212624</v>
+        <v>32.78145695364238</v>
       </c>
       <c r="Q49" s="8" t="inlineStr"/>
       <c r="R49" s="8" t="inlineStr"/>
       <c r="S49" s="6" t="n">
-        <v>27150</v>
+        <v>27250</v>
       </c>
       <c r="T49" s="7" t="n">
-        <v>47.69797421731123</v>
+        <v>47.1559633027523</v>
       </c>
       <c r="U49" s="8" t="inlineStr"/>
       <c r="V49" s="8" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       <c r="AD49" s="8" t="inlineStr"/>
       <c r="AE49" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:32</t>
+          <t>2025-10-18 11:11:32</t>
         </is>
       </c>
       <c r="AF49" s="8" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
       <c r="Q50" s="8" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="6" t="n">
-        <v>12040</v>
+        <v>12050</v>
       </c>
       <c r="T50" s="7" t="n">
-        <v>33.05647840531562</v>
+        <v>32.9460580912863</v>
       </c>
       <c r="U50" s="8" t="inlineStr"/>
       <c r="V50" s="8" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       <c r="AD50" s="8" t="inlineStr"/>
       <c r="AE50" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:32</t>
+          <t>2025-10-18 11:11:32</t>
         </is>
       </c>
       <c r="AF50" s="8" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       <c r="AD51" s="8" t="inlineStr"/>
       <c r="AE51" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:32</t>
+          <t>2025-10-18 11:11:33</t>
         </is>
       </c>
       <c r="AF51" s="8" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.9%</t>
+          <t>1차 매수선까지 26.8%</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
@@ -4698,26 +4698,26 @@
         <v>11183.6</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>11190</v>
+        <v>11200</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>26.89901697944593</v>
+        <v>26.78571428571428</v>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
       <c r="O52" s="6" t="n">
-        <v>10080</v>
+        <v>10090</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>40.87301587301587</v>
+        <v>40.73339940535183</v>
       </c>
       <c r="Q52" s="8" t="inlineStr"/>
       <c r="R52" s="8" t="inlineStr"/>
       <c r="S52" s="6" t="n">
-        <v>9080</v>
+        <v>9100</v>
       </c>
       <c r="T52" s="7" t="n">
-        <v>56.38766519823789</v>
+        <v>56.04395604395604</v>
       </c>
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
       <c r="AD52" s="8" t="inlineStr"/>
       <c r="AE52" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:33</t>
+          <t>2025-10-18 11:11:33</t>
         </is>
       </c>
       <c r="AF52" s="8" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.1%</t>
+          <t>1차 매수선까지 18.9%</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -4778,26 +4778,26 @@
         <v>63720</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>63800</v>
+        <v>63900</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>19.12225705329153</v>
+        <v>18.9358372456964</v>
       </c>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
       <c r="O53" s="6" t="n">
-        <v>57500</v>
+        <v>57700</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>32.17391304347826</v>
+        <v>31.7157712305026</v>
       </c>
       <c r="Q53" s="8" t="inlineStr"/>
       <c r="R53" s="8" t="inlineStr"/>
       <c r="S53" s="6" t="n">
-        <v>51900</v>
+        <v>52100</v>
       </c>
       <c r="T53" s="7" t="n">
-        <v>46.4354527938343</v>
+        <v>45.87332053742802</v>
       </c>
       <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       <c r="AD53" s="8" t="inlineStr"/>
       <c r="AE53" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:33</t>
+          <t>2025-10-18 11:11:33</t>
         </is>
       </c>
       <c r="AF53" s="8" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
       <c r="Q54" s="8" t="inlineStr"/>
       <c r="R54" s="8" t="inlineStr"/>
       <c r="S54" s="6" t="n">
-        <v>152700</v>
+        <v>152800</v>
       </c>
       <c r="T54" s="7" t="n">
-        <v>55.20628683693517</v>
+        <v>55.10471204188482</v>
       </c>
       <c r="U54" s="8" t="inlineStr"/>
       <c r="V54" s="8" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       <c r="AD54" s="8" t="inlineStr"/>
       <c r="AE54" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:33</t>
+          <t>2025-10-18 11:11:34</t>
         </is>
       </c>
       <c r="AF54" s="8" t="inlineStr"/>
@@ -4946,18 +4946,18 @@
       <c r="M55" s="8" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
       <c r="O55" s="6" t="n">
-        <v>76200</v>
+        <v>76300</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>32.15223097112861</v>
+        <v>31.97903014416776</v>
       </c>
       <c r="Q55" s="8" t="inlineStr"/>
       <c r="R55" s="8" t="inlineStr"/>
       <c r="S55" s="6" t="n">
-        <v>68700</v>
+        <v>68800</v>
       </c>
       <c r="T55" s="7" t="n">
-        <v>46.57933042212518</v>
+        <v>46.36627906976744</v>
       </c>
       <c r="U55" s="8" t="inlineStr"/>
       <c r="V55" s="8" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       <c r="AD55" s="8" t="inlineStr"/>
       <c r="AE55" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:34</t>
+          <t>2025-10-18 11:11:34</t>
         </is>
       </c>
       <c r="AF55" s="8" t="inlineStr"/>
@@ -5026,18 +5026,18 @@
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
       <c r="O56" s="6" t="n">
-        <v>737000</v>
+        <v>738000</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>24.2876526458616</v>
+        <v>24.11924119241192</v>
       </c>
       <c r="Q56" s="8" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
       <c r="S56" s="6" t="n">
-        <v>664000</v>
+        <v>666000</v>
       </c>
       <c r="T56" s="7" t="n">
-        <v>37.95180722891566</v>
+        <v>37.53753753753754</v>
       </c>
       <c r="U56" s="8" t="inlineStr"/>
       <c r="V56" s="8" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       <c r="AD56" s="8" t="inlineStr"/>
       <c r="AE56" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:34</t>
+          <t>2025-10-18 11:11:34</t>
         </is>
       </c>
       <c r="AF56" s="8" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       <c r="AD57" s="8" t="inlineStr"/>
       <c r="AE57" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:34</t>
+          <t>2025-10-18 11:11:34</t>
         </is>
       </c>
       <c r="AF57" s="8" t="inlineStr"/>
@@ -5186,18 +5186,18 @@
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="6" t="n">
-        <v>21150</v>
+        <v>21200</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>39.00709219858156</v>
+        <v>38.67924528301887</v>
       </c>
       <c r="Q58" s="8" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="6" t="n">
-        <v>19050</v>
+        <v>19090</v>
       </c>
       <c r="T58" s="7" t="n">
-        <v>54.33070866141733</v>
+        <v>54.00733368255631</v>
       </c>
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       <c r="AD58" s="8" t="inlineStr"/>
       <c r="AE58" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:34</t>
+          <t>2025-10-18 11:11:35</t>
         </is>
       </c>
       <c r="AF58" s="8" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.6%</t>
+          <t>1차 매수선까지 27.5%</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
@@ -5258,26 +5258,26 @@
         <v>158640</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>158700</v>
+        <v>158800</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>27.59924385633271</v>
+        <v>27.51889168765743</v>
       </c>
       <c r="M59" s="8" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="6" t="n">
-        <v>142900</v>
+        <v>143100</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>41.7074877536739</v>
+        <v>41.50943396226415</v>
       </c>
       <c r="Q59" s="8" t="inlineStr"/>
       <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="6" t="n">
-        <v>128700</v>
+        <v>128900</v>
       </c>
       <c r="T59" s="7" t="n">
-        <v>57.34265734265735</v>
+        <v>57.09852598913887</v>
       </c>
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
@@ -5291,7 +5291,7 @@
       <c r="AD59" s="8" t="inlineStr"/>
       <c r="AE59" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:35</t>
+          <t>2025-10-18 11:11:35</t>
         </is>
       </c>
       <c r="AF59" s="8" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.6%</t>
+          <t>1차 매수선까지 13.5%</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
@@ -5338,26 +5338,26 @@
         <v>44768</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>44800</v>
+        <v>44850</v>
       </c>
       <c r="L60" s="7" t="n">
-        <v>13.61607142857143</v>
+        <v>13.48940914158306</v>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
       <c r="O60" s="6" t="n">
-        <v>40350</v>
+        <v>40450</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>26.14622057001239</v>
+        <v>25.83436341161928</v>
       </c>
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="6" t="n">
-        <v>36350</v>
+        <v>36500</v>
       </c>
       <c r="T60" s="7" t="n">
-        <v>40.02751031636863</v>
+        <v>39.45205479452055</v>
       </c>
       <c r="U60" s="8" t="inlineStr"/>
       <c r="V60" s="8" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
       <c r="AD60" s="8" t="inlineStr"/>
       <c r="AE60" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:35</t>
+          <t>2025-10-18 11:11:35</t>
         </is>
       </c>
       <c r="AF60" s="8" t="inlineStr"/>
@@ -5451,7 +5451,7 @@
       <c r="AD61" s="8" t="inlineStr"/>
       <c r="AE61" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:35</t>
+          <t>2025-10-18 11:11:36</t>
         </is>
       </c>
       <c r="AF61" s="8" t="inlineStr"/>
@@ -5506,18 +5506,18 @@
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
       <c r="O62" s="6" t="n">
-        <v>22000</v>
+        <v>22050</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>37.27272727272727</v>
+        <v>36.96145124716553</v>
       </c>
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="6" t="n">
-        <v>19810</v>
+        <v>19860</v>
       </c>
       <c r="T62" s="7" t="n">
-        <v>52.44825845532559</v>
+        <v>52.06445115810675</v>
       </c>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       <c r="AD62" s="8" t="inlineStr"/>
       <c r="AE62" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:35</t>
+          <t>2025-10-18 11:11:36</t>
         </is>
       </c>
       <c r="AF62" s="8" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       <c r="AD63" s="8" t="inlineStr"/>
       <c r="AE63" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:36</t>
+          <t>2025-10-18 11:11:36</t>
         </is>
       </c>
       <c r="AF63" s="8" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       <c r="AD64" s="8" t="inlineStr"/>
       <c r="AE64" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:36</t>
+          <t>2025-10-18 11:11:36</t>
         </is>
       </c>
       <c r="AF64" s="8" t="inlineStr"/>
@@ -5754,10 +5754,10 @@
       <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="6" t="n">
-        <v>95900</v>
+        <v>96000</v>
       </c>
       <c r="T65" s="7" t="n">
-        <v>35.97497393117831</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       <c r="AD65" s="8" t="inlineStr"/>
       <c r="AE65" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:36</t>
+          <t>2025-10-18 11:11:37</t>
         </is>
       </c>
       <c r="AF65" s="8" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       <c r="AD66" s="8" t="inlineStr"/>
       <c r="AE66" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:37</t>
+          <t>2025-10-18 11:11:37</t>
         </is>
       </c>
       <c r="AF66" s="8" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 7.6% (접근 중!)</t>
+          <t>1차 매수선까지 7.5% (접근 중!)</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
@@ -5898,26 +5898,26 @@
         <v>8892</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>8900</v>
+        <v>8910</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>7.640449438202247</v>
+        <v>7.519640852974187</v>
       </c>
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="6" t="n">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>19.45137157107232</v>
+        <v>19.30261519302615</v>
       </c>
       <c r="Q67" s="8" t="inlineStr"/>
       <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="6" t="n">
-        <v>7230</v>
+        <v>7240</v>
       </c>
       <c r="T67" s="7" t="n">
-        <v>32.50345781466113</v>
+        <v>32.32044198895028</v>
       </c>
       <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       <c r="AD67" s="8" t="inlineStr"/>
       <c r="AE67" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:37</t>
+          <t>2025-10-18 11:11:37</t>
         </is>
       </c>
       <c r="AF67" s="8" t="inlineStr"/>
@@ -5986,18 +5986,18 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="6" t="n">
-        <v>159300</v>
+        <v>159400</v>
       </c>
       <c r="P68" s="7" t="n">
-        <v>60.70307595731325</v>
+        <v>60.60225846925973</v>
       </c>
       <c r="Q68" s="8" t="inlineStr"/>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="6" t="n">
-        <v>143500</v>
+        <v>143600</v>
       </c>
       <c r="T68" s="7" t="n">
-        <v>78.39721254355401</v>
+        <v>78.27298050139275</v>
       </c>
       <c r="U68" s="8" t="inlineStr"/>
       <c r="V68" s="8" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="AD68" s="8" t="inlineStr"/>
       <c r="AE68" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:37</t>
+          <t>2025-10-18 11:11:37</t>
         </is>
       </c>
       <c r="AF68" s="8" t="inlineStr"/>
@@ -6066,18 +6066,18 @@
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="6" t="n">
-        <v>202000</v>
+        <v>202500</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>43.06930693069307</v>
+        <v>42.71604938271605</v>
       </c>
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="6" t="n">
-        <v>181900</v>
+        <v>182400</v>
       </c>
       <c r="T69" s="7" t="n">
-        <v>58.87850467289719</v>
+        <v>58.44298245614035</v>
       </c>
       <c r="U69" s="8" t="inlineStr"/>
       <c r="V69" s="8" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       <c r="AD69" s="8" t="inlineStr"/>
       <c r="AE69" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:37</t>
+          <t>2025-10-18 11:11:38</t>
         </is>
       </c>
       <c r="AF69" s="8" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
       <c r="Q70" s="8" t="inlineStr"/>
       <c r="R70" s="8" t="inlineStr"/>
       <c r="S70" s="6" t="n">
-        <v>62100</v>
+        <v>62200</v>
       </c>
       <c r="T70" s="7" t="n">
-        <v>52.01288244766506</v>
+        <v>51.76848874598071</v>
       </c>
       <c r="U70" s="8" t="inlineStr"/>
       <c r="V70" s="8" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
       <c r="AD70" s="8" t="inlineStr"/>
       <c r="AE70" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:38</t>
+          <t>2025-10-18 11:11:38</t>
         </is>
       </c>
       <c r="AF70" s="8" t="inlineStr"/>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.7%</t>
+          <t>1차 매수선까지 17.5%</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
@@ -6218,26 +6218,26 @@
         <v>69424</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>69500</v>
+        <v>69600</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>17.69784172661871</v>
+        <v>17.52873563218391</v>
       </c>
       <c r="M71" s="8" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
       <c r="O71" s="6" t="n">
-        <v>62700</v>
+        <v>62800</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>30.46251993620415</v>
+        <v>30.25477707006369</v>
       </c>
       <c r="Q71" s="8" t="inlineStr"/>
       <c r="R71" s="8" t="inlineStr"/>
       <c r="S71" s="6" t="n">
-        <v>56500</v>
+        <v>56700</v>
       </c>
       <c r="T71" s="7" t="n">
-        <v>44.7787610619469</v>
+        <v>44.26807760141093</v>
       </c>
       <c r="U71" s="8" t="inlineStr"/>
       <c r="V71" s="8" t="inlineStr"/>
@@ -6251,7 +6251,7 @@
       <c r="AD71" s="8" t="inlineStr"/>
       <c r="AE71" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:38</t>
+          <t>2025-10-18 11:11:38</t>
         </is>
       </c>
       <c r="AF71" s="8" t="inlineStr"/>
@@ -6306,18 +6306,18 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
       <c r="O72" s="6" t="n">
-        <v>159100</v>
+        <v>159200</v>
       </c>
       <c r="P72" s="7" t="n">
-        <v>36.0779384035198</v>
+        <v>35.99246231155779</v>
       </c>
       <c r="Q72" s="8" t="inlineStr"/>
       <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="6" t="n">
-        <v>143300</v>
+        <v>143400</v>
       </c>
       <c r="T72" s="7" t="n">
-        <v>51.08164689462665</v>
+        <v>50.976290097629</v>
       </c>
       <c r="U72" s="8" t="inlineStr"/>
       <c r="V72" s="8" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
       <c r="AD72" s="8" t="inlineStr"/>
       <c r="AE72" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:38</t>
+          <t>2025-10-18 11:11:39</t>
         </is>
       </c>
       <c r="AF72" s="8" t="inlineStr"/>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>1차 매수선까지 35.3%</t>
+          <t>1차 매수선까지 35.1%</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
@@ -6378,26 +6378,26 @@
         <v>84112</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>84200</v>
+        <v>84300</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>35.27315914489311</v>
+        <v>35.11269276393831</v>
       </c>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="6" t="n">
-        <v>75900</v>
+        <v>76000</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>50.06587615283268</v>
+        <v>49.86842105263158</v>
       </c>
       <c r="Q73" s="8" t="inlineStr"/>
       <c r="R73" s="8" t="inlineStr"/>
       <c r="S73" s="6" t="n">
-        <v>68400</v>
+        <v>68500</v>
       </c>
       <c r="T73" s="7" t="n">
-        <v>66.52046783625731</v>
+        <v>66.27737226277372</v>
       </c>
       <c r="U73" s="8" t="inlineStr"/>
       <c r="V73" s="8" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       <c r="AD73" s="8" t="inlineStr"/>
       <c r="AE73" s="9" t="inlineStr">
         <is>
-          <t>2025-10-18 11:08:38</t>
+          <t>2025-10-18 11:11:39</t>
         </is>
       </c>
       <c r="AF73" s="8" t="inlineStr"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -79,6 +80,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -654,45 +658,45 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.6%</t>
+          <t>1차 매수선까지 33.9%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>96300</v>
+        <v>96400</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>94400</v>
+        <v>95200</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>99100</v>
+        <v>98500</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>86555</v>
+        <v>90345</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>69244</v>
+        <v>72276</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>69000</v>
+        <v>72000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>39.56521739130434</v>
+        <v>33.88888888888889</v>
       </c>
       <c r="M2" s="7" t="inlineStr"/>
       <c r="N2" s="7" t="inlineStr"/>
       <c r="O2" s="5" t="n">
-        <v>62200</v>
+        <v>64900</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>54.82315112540193</v>
+        <v>48.53620955315871</v>
       </c>
       <c r="Q2" s="7" t="inlineStr"/>
       <c r="R2" s="7" t="inlineStr"/>
       <c r="S2" s="5" t="n">
-        <v>56100</v>
+        <v>58600</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>71.65775401069519</v>
+        <v>64.50511945392492</v>
       </c>
       <c r="U2" s="7" t="inlineStr"/>
       <c r="V2" s="7" t="inlineStr"/>
@@ -728,45 +732,45 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 51.2%</t>
+          <t>1차 매수선까지 47.7%</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>454500</v>
+        <v>477000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>440500</v>
+        <v>468000</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>475000</v>
+        <v>488500</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>376700</v>
+        <v>404875</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>301360</v>
+        <v>323900</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>300500</v>
+        <v>323000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>51.24792013311148</v>
+        <v>47.6780185758514</v>
       </c>
       <c r="M3" s="7" t="inlineStr"/>
       <c r="N3" s="7" t="inlineStr"/>
       <c r="O3" s="5" t="n">
-        <v>271000</v>
+        <v>291500</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>67.71217712177122</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="5" t="n">
-        <v>244500</v>
+        <v>263000</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>85.88957055214725</v>
+        <v>81.36882129277566</v>
       </c>
       <c r="U3" s="7" t="inlineStr"/>
       <c r="V3" s="7" t="inlineStr"/>
@@ -802,45 +806,45 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.4%</t>
+          <t>1차 매수선까지 34.4%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>79600</v>
+        <v>76500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>76200</v>
+        <v>75500</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>83600</v>
+        <v>78200</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>67660</v>
+        <v>71310</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>54128</v>
+        <v>57048</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>54000</v>
+        <v>56900</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>47.40740740740741</v>
+        <v>34.44639718804921</v>
       </c>
       <c r="M4" s="7" t="inlineStr"/>
       <c r="N4" s="7" t="inlineStr"/>
       <c r="O4" s="5" t="n">
-        <v>48650</v>
+        <v>51400</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>63.61767728674204</v>
+        <v>48.83268482490272</v>
       </c>
       <c r="Q4" s="7" t="inlineStr"/>
       <c r="R4" s="7" t="inlineStr"/>
       <c r="S4" s="5" t="n">
-        <v>43850</v>
+        <v>46350</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>81.52793614595211</v>
+        <v>65.0485436893204</v>
       </c>
       <c r="U4" s="7" t="inlineStr"/>
       <c r="V4" s="7" t="inlineStr"/>
@@ -876,45 +880,45 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.3%</t>
+          <t>1차 매수선까지 20.6%</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>250500</v>
+        <v>243000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>245000</v>
+        <v>242000</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>262500</v>
+        <v>255000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>249600</v>
+        <v>253075</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>199680</v>
+        <v>202460</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>198300</v>
+        <v>201500</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>26.32375189107413</v>
+        <v>20.59553349875931</v>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="5" t="n">
-        <v>178600</v>
+        <v>181500</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>40.25755879059351</v>
+        <v>33.88429752066116</v>
       </c>
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="5" t="n">
-        <v>160900</v>
+        <v>163500</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>55.68676196395277</v>
+        <v>48.62385321100918</v>
       </c>
       <c r="U5" s="7" t="inlineStr"/>
       <c r="V5" s="7" t="inlineStr"/>
@@ -950,45 +954,45 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.7%</t>
+          <t>1차 매수선까지 57.7%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>139500</v>
+        <v>148600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>131700</v>
+        <v>144700</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>147900</v>
+        <v>152900</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>106110</v>
+        <v>117620</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>84888</v>
+        <v>94096</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>84700</v>
+        <v>94200</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>64.69893742621015</v>
+        <v>57.74946921443737</v>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="5" t="n">
-        <v>76400</v>
+        <v>84900</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>82.59162303664922</v>
+        <v>75.02944640753827</v>
       </c>
       <c r="Q6" s="7" t="inlineStr"/>
       <c r="R6" s="7" t="inlineStr"/>
       <c r="S6" s="5" t="n">
-        <v>68900</v>
+        <v>76600</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>102.467343976778</v>
+        <v>93.99477806788512</v>
       </c>
       <c r="U6" s="7" t="inlineStr"/>
       <c r="V6" s="7" t="inlineStr"/>
@@ -1004,12 +1008,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>247540</t>
+          <t>086520</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1024,45 +1028,45 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 58.9%</t>
+          <t>1차 매수선까지 79.7%</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>152900</v>
+        <v>81500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>138600</v>
+        <v>81500</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>167400</v>
+        <v>87200</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>121485</v>
+        <v>56875</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>97188</v>
+        <v>45500</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>96200</v>
+        <v>45350</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>58.93970893970894</v>
+        <v>79.71334068357223</v>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="5" t="n">
-        <v>86700</v>
+        <v>40900</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>76.35524798154556</v>
+        <v>99.26650366748166</v>
       </c>
       <c r="Q7" s="7" t="inlineStr"/>
       <c r="R7" s="7" t="inlineStr"/>
       <c r="S7" s="5" t="n">
-        <v>78200</v>
+        <v>36900</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>95.52429667519181</v>
+        <v>120.8672086720867</v>
       </c>
       <c r="U7" s="7" t="inlineStr"/>
       <c r="V7" s="7" t="inlineStr"/>
@@ -1078,12 +1082,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1098,45 +1102,45 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.2%</t>
+          <t>1차 매수선까지 51.9%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>249000</v>
+        <v>135000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>228000</v>
+        <v>128600</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>259500</v>
+        <v>139700</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>211700</v>
+        <v>112155</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>169360</v>
+        <v>89724</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>168000</v>
+        <v>88900</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>48.21428571428572</v>
+        <v>51.85601799775028</v>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="5" t="n">
-        <v>151300</v>
+        <v>80200</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>64.57369464639788</v>
+        <v>68.3291770573566</v>
       </c>
       <c r="Q8" s="7" t="inlineStr"/>
       <c r="R8" s="7" t="inlineStr"/>
       <c r="S8" s="5" t="n">
-        <v>136300</v>
+        <v>72300</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>82.68525311812179</v>
+        <v>86.72199170124482</v>
       </c>
       <c r="U8" s="7" t="inlineStr"/>
       <c r="V8" s="7" t="inlineStr"/>
@@ -1152,12 +1156,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>086520</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1172,45 +1176,45 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 76.1%</t>
+          <t>1차 매수선까지 38.5%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>70800</v>
+        <v>250500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>58600</v>
+        <v>250000</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>73900</v>
+        <v>260000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>50715</v>
+        <v>227750</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>40572</v>
+        <v>182200</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>40200</v>
+        <v>180900</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>76.11940298507463</v>
+        <v>38.47429519071311</v>
       </c>
       <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="5" t="n">
-        <v>36250</v>
+        <v>163000</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>95.31034482758621</v>
+        <v>53.68098159509203</v>
       </c>
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="5" t="n">
-        <v>32700</v>
+        <v>146800</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>116.5137614678899</v>
+        <v>70.64032697547684</v>
       </c>
       <c r="U9" s="7" t="inlineStr"/>
       <c r="V9" s="7" t="inlineStr"/>
@@ -1226,12 +1230,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>247540</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1246,45 +1250,45 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 52.5%</t>
+          <t>1차 매수선까지 53.6%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61700</v>
+        <v>157900</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>58700</v>
+        <v>157500</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>69200</v>
+        <v>167800</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>51130</v>
+        <v>129250</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>40904</v>
+        <v>103400</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>40450</v>
+        <v>102800</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>52.53399258343634</v>
+        <v>53.59922178988327</v>
       </c>
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="5" t="n">
-        <v>36500</v>
+        <v>92700</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>69.04109589041096</v>
+        <v>70.33441208198489</v>
       </c>
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="5" t="n">
-        <v>32900</v>
+        <v>83600</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>87.53799392097264</v>
+        <v>88.8755980861244</v>
       </c>
       <c r="U10" s="7" t="inlineStr"/>
       <c r="V10" s="7" t="inlineStr"/>
@@ -1300,12 +1304,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1320,45 +1324,45 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.4%</t>
+          <t>1차 매수선까지 45.3%</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>421500</v>
+        <v>257500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>406000</v>
+        <v>257000</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>443000</v>
+        <v>264500</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>363350</v>
+        <v>222825</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>290680</v>
+        <v>178260</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>288000</v>
+        <v>177200</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>46.35416666666667</v>
+        <v>45.31602708803612</v>
       </c>
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="5" t="n">
-        <v>260000</v>
+        <v>159600</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>62.11538461538461</v>
+        <v>61.34085213032582</v>
       </c>
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="5" t="n">
-        <v>234500</v>
+        <v>143800</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>79.74413646055437</v>
+        <v>79.06815020862309</v>
       </c>
       <c r="U11" s="7" t="inlineStr"/>
       <c r="V11" s="7" t="inlineStr"/>
@@ -1374,12 +1378,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1394,45 +1398,45 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 56.8%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>107300</v>
+        <v>382500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>103700</v>
+        <v>378000</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>113700</v>
+        <v>415000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>109295</v>
+        <v>307275</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>87436</v>
+        <v>245820</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>86600</v>
+        <v>244000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>23.90300230946882</v>
+        <v>56.76229508196722</v>
       </c>
       <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="5" t="n">
-        <v>78100</v>
+        <v>220500</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>37.38796414852753</v>
+        <v>73.46938775510205</v>
       </c>
       <c r="Q12" s="7" t="inlineStr"/>
       <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="5" t="n">
-        <v>70400</v>
+        <v>198600</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>52.41477272727273</v>
+        <v>92.59818731117825</v>
       </c>
       <c r="U12" s="7" t="inlineStr"/>
       <c r="V12" s="7" t="inlineStr"/>
@@ -1448,12 +1452,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1468,45 +1472,45 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.8%</t>
+          <t>1차 매수선까지 51.7%</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>41850</v>
+        <v>65100</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>39450</v>
+        <v>65000</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>43300</v>
+        <v>69200</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>36962.5</v>
+        <v>54010</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>29570</v>
+        <v>43208</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>29300</v>
+        <v>42900</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>42.83276450511945</v>
+        <v>51.74825174825175</v>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="5" t="n">
-        <v>26450</v>
+        <v>38700</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>58.22306238185255</v>
+        <v>68.21705426356588</v>
       </c>
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="5" t="n">
-        <v>23900</v>
+        <v>34900</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>75.10460251046025</v>
+        <v>86.53295128939828</v>
       </c>
       <c r="U13" s="7" t="inlineStr"/>
       <c r="V13" s="7" t="inlineStr"/>
@@ -1522,12 +1526,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1542,45 +1546,45 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.9%</t>
+          <t>1차 매수선까지 47.0%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>240500</v>
+        <v>446000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>230000</v>
+        <v>443000</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>246000</v>
+        <v>457000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>219950</v>
+        <v>381125</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>175960</v>
+        <v>304900</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>174400</v>
+        <v>303500</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>37.90137614678899</v>
+        <v>46.95222405271829</v>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="5" t="n">
-        <v>157100</v>
+        <v>274000</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>53.08720560152769</v>
+        <v>62.77372262773723</v>
       </c>
       <c r="Q14" s="7" t="inlineStr"/>
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="5" t="n">
-        <v>141500</v>
+        <v>247500</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>69.96466431095406</v>
+        <v>80.20202020202019</v>
       </c>
       <c r="U14" s="7" t="inlineStr"/>
       <c r="V14" s="7" t="inlineStr"/>
@@ -1596,12 +1600,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1616,45 +1620,45 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 55.3%</t>
+          <t>1차 매수선까지 38.8%</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>185400</v>
+        <v>42200</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>170000</v>
+        <v>41850</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>201000</v>
+        <v>43650</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>149940</v>
+        <v>38227.5</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>119952</v>
+        <v>30582</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>119400</v>
+        <v>30400</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>55.27638190954774</v>
+        <v>38.81578947368421</v>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="5" t="n">
-        <v>107600</v>
+        <v>27450</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>72.30483271375465</v>
+        <v>53.73406193078324</v>
       </c>
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="5" t="n">
-        <v>97000</v>
+        <v>24800</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>91.1340206185567</v>
+        <v>70.16129032258065</v>
       </c>
       <c r="U15" s="7" t="inlineStr"/>
       <c r="V15" s="7" t="inlineStr"/>
@@ -1670,12 +1674,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1690,45 +1694,45 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 66.9%</t>
+          <t>1차 매수선까지 54.4%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>11400</v>
+        <v>201000</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>11050</v>
+        <v>200000</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>12250</v>
+        <v>210500</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>8525.5</v>
+        <v>163185</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>6820.400000000001</v>
+        <v>130548</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6830</v>
+        <v>130200</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>66.91068814055637</v>
+        <v>54.37788018433179</v>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="5" t="n">
-        <v>6160</v>
+        <v>117300</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>85.06493506493507</v>
+        <v>71.35549872122762</v>
       </c>
       <c r="Q16" s="7" t="inlineStr"/>
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="5" t="n">
-        <v>5560</v>
+        <v>105700</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>105.0359712230216</v>
+        <v>90.1608325449385</v>
       </c>
       <c r="U16" s="7" t="inlineStr"/>
       <c r="V16" s="7" t="inlineStr"/>
@@ -1744,12 +1748,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1764,45 +1768,45 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.2%</t>
+          <t>1차 매수선까지 39.7%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>331500</v>
+        <v>241000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>303500</v>
+        <v>227500</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>350000</v>
+        <v>249500</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>292275</v>
+        <v>218350</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>233820</v>
+        <v>174680</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>231500</v>
+        <v>172500</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>43.19654427645789</v>
+        <v>39.71014492753623</v>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="5" t="n">
-        <v>209000</v>
+        <v>155400</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>58.61244019138756</v>
+        <v>55.08365508365508</v>
       </c>
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="5" t="n">
-        <v>188200</v>
+        <v>140000</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>76.1424017003188</v>
+        <v>72.14285714285714</v>
       </c>
       <c r="U17" s="7" t="inlineStr"/>
       <c r="V17" s="7" t="inlineStr"/>
@@ -1818,12 +1822,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1838,45 +1842,45 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 69.5%</t>
+          <t>1차 매수선까지 23.2%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>105100</v>
+        <v>59300</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>95100</v>
+        <v>59000</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>114600</v>
+        <v>60700</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>77785</v>
+        <v>61090</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>62228</v>
+        <v>48872</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>62000</v>
+        <v>48150</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>69.51612903225806</v>
+        <v>23.15680166147456</v>
       </c>
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="5" t="n">
-        <v>55900</v>
+        <v>43400</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>88.01431127012522</v>
+        <v>36.63594470046083</v>
       </c>
       <c r="Q18" s="7" t="inlineStr"/>
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="5" t="n">
-        <v>50500</v>
+        <v>39150</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>108.1188118811881</v>
+        <v>51.46871008939975</v>
       </c>
       <c r="U18" s="7" t="inlineStr"/>
       <c r="V18" s="7" t="inlineStr"/>
@@ -1892,12 +1896,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1912,45 +1916,45 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.9%</t>
+          <t>1차 매수선까지 64.7%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>678000</v>
+        <v>113000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>598000</v>
+        <v>112000</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>722000</v>
+        <v>119200</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>592150</v>
+        <v>85930</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>473720</v>
+        <v>68744</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>468000</v>
+        <v>68600</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>44.87179487179488</v>
+        <v>64.72303206997084</v>
       </c>
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="5" t="n">
-        <v>422000</v>
+        <v>61900</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>60.66350710900474</v>
+        <v>82.55250403877221</v>
       </c>
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="5" t="n">
-        <v>380500</v>
+        <v>55900</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>78.18659658344284</v>
+        <v>102.1466905187835</v>
       </c>
       <c r="U19" s="7" t="inlineStr"/>
       <c r="V19" s="7" t="inlineStr"/>
@@ -1966,12 +1970,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1986,45 +1990,45 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 62.0%</t>
+          <t>1차 매수선까지 57.4%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>41800</v>
+        <v>775000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>41450</v>
+        <v>773000</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>45000</v>
+        <v>808000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>32270</v>
+        <v>620500</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>25816</v>
+        <v>496400</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>25800</v>
+        <v>492500</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>62.01550387596899</v>
+        <v>57.36040609137056</v>
       </c>
       <c r="M20" s="7" t="inlineStr"/>
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="5" t="n">
-        <v>23300</v>
+        <v>444000</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>79.39914163090128</v>
+        <v>74.54954954954955</v>
       </c>
       <c r="Q20" s="7" t="inlineStr"/>
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="5" t="n">
-        <v>21050</v>
+        <v>400500</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>98.57482185273159</v>
+        <v>93.50811485642946</v>
       </c>
       <c r="U20" s="7" t="inlineStr"/>
       <c r="V20" s="7" t="inlineStr"/>
@@ -2040,12 +2044,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2060,45 +2064,45 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 55.4%</t>
+          <t>1차 매수선까지 72.5%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>192200</v>
+        <v>13350</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>190900</v>
+        <v>12350</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>202500</v>
+        <v>14190</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>153449.4</v>
+        <v>9628.5</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>122759.52</v>
+        <v>7702.8</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>123700</v>
+        <v>7740</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>55.37590945836701</v>
+        <v>72.48062015503875</v>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="5" t="n">
-        <v>111500</v>
+        <v>6980</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>72.37668161434978</v>
+        <v>91.26074498567334</v>
       </c>
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="5" t="n">
-        <v>100500</v>
+        <v>6300</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>91.24378109452736</v>
+        <v>111.9047619047619</v>
       </c>
       <c r="U21" s="7" t="inlineStr"/>
       <c r="V21" s="7" t="inlineStr"/>
@@ -2114,12 +2118,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2134,45 +2138,45 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.9%</t>
+          <t>1차 매수선까지 85.8%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>75000</v>
+        <v>6000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>74400</v>
+        <v>5750</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>76000</v>
+        <v>6580</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>68285</v>
+        <v>4050.25</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>54628</v>
+        <v>3240.2</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>54400</v>
+        <v>3230</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>37.86764705882353</v>
+        <v>85.75851393188854</v>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="5" t="n">
-        <v>49050</v>
+        <v>2915</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>52.90519877675841</v>
+        <v>105.8319039451115</v>
       </c>
       <c r="Q22" s="7" t="inlineStr"/>
       <c r="R22" s="7" t="inlineStr"/>
       <c r="S22" s="5" t="n">
-        <v>44200</v>
+        <v>2630</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>69.68325791855203</v>
+        <v>128.1368821292776</v>
       </c>
       <c r="U22" s="7" t="inlineStr"/>
       <c r="V22" s="7" t="inlineStr"/>
@@ -2188,12 +2192,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2203,50 +2207,50 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 3.1% (접근 중!)</t>
+          <t>1차 매수선까지 38.6%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>21900</v>
+        <v>38800</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>21500</v>
+        <v>38450</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>22850</v>
+        <v>41450</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>26607.5</v>
+        <v>35007.5</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>21286</v>
+        <v>28006</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>21250</v>
+        <v>28000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>3.058823529411765</v>
+        <v>38.57142857142858</v>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="5" t="n">
-        <v>19140</v>
+        <v>25250</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>14.42006269592476</v>
+        <v>53.66336633663366</v>
       </c>
       <c r="Q23" s="7" t="inlineStr"/>
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="5" t="n">
-        <v>17240</v>
+        <v>22800</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>27.03016241299304</v>
+        <v>70.17543859649122</v>
       </c>
       <c r="U23" s="7" t="inlineStr"/>
       <c r="V23" s="7" t="inlineStr"/>
@@ -2262,12 +2266,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2277,50 +2281,50 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 5.6% (접근 중!)</t>
+          <t>1차 매수선까지 36.4%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>9010</v>
+        <v>187000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>8870</v>
+        <v>178500</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>9870</v>
+        <v>202500</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>10777</v>
+        <v>171036.2</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>8621.6</v>
+        <v>136828.96</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>8530</v>
+        <v>137100</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>5.627198124267292</v>
+        <v>36.39679066374909</v>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="5" t="n">
-        <v>7690</v>
+        <v>123500</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>17.16514954486346</v>
+        <v>51.417004048583</v>
       </c>
       <c r="Q24" s="7" t="inlineStr"/>
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="5" t="n">
-        <v>6940</v>
+        <v>111300</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>29.82708933717579</v>
+        <v>68.01437556154536</v>
       </c>
       <c r="U24" s="7" t="inlineStr"/>
       <c r="V24" s="7" t="inlineStr"/>
@@ -2336,12 +2340,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2356,45 +2360,45 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.3%</t>
+          <t>1차 매수선까지 35.0%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>15890</v>
+        <v>76400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>15680</v>
+        <v>76400</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>17290</v>
+        <v>77900</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>16651.5</v>
+        <v>71055</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>13321.2</v>
+        <v>56844</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>13320</v>
+        <v>56600</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>19.2942942942943</v>
+        <v>34.98233215547703</v>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="5" t="n">
-        <v>12000</v>
+        <v>51100</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>32.41666666666666</v>
+        <v>49.51076320939335</v>
       </c>
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="5" t="n">
-        <v>10810</v>
+        <v>46050</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>46.99352451433857</v>
+        <v>65.90662323561347</v>
       </c>
       <c r="U25" s="7" t="inlineStr"/>
       <c r="V25" s="7" t="inlineStr"/>
@@ -2410,86 +2414,108 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>BOUGHT_1</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_SELL1</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.4%</t>
+          <t>+3% 매도선까지 5.0%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>57800</v>
+        <v>20600</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>56900</v>
+        <v>20500</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>59500</v>
+        <v>21450</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>61740</v>
+        <v>25677.5</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>49392</v>
+        <v>20542</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>48800</v>
+        <v>20150</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>18.44262295081967</v>
-      </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+        <v>2.233250620347394</v>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>21,050</t>
+        </is>
+      </c>
       <c r="O26" s="5" t="n">
-        <v>44000</v>
+        <v>18150</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>31.36363636363637</v>
+        <v>13.49862258953168</v>
       </c>
       <c r="Q26" s="7" t="inlineStr"/>
       <c r="R26" s="7" t="inlineStr"/>
       <c r="S26" s="5" t="n">
-        <v>39650</v>
+        <v>16350</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>45.77553593947037</v>
+        <v>25.99388379204893</v>
       </c>
       <c r="U26" s="7" t="inlineStr"/>
       <c r="V26" s="7" t="inlineStr"/>
-      <c r="W26" s="7" t="inlineStr"/>
-      <c r="X26" s="7" t="inlineStr"/>
-      <c r="Y26" s="7" t="inlineStr"/>
-      <c r="Z26" s="7" t="inlineStr"/>
-      <c r="AA26" s="7" t="inlineStr"/>
-      <c r="AB26" s="7" t="inlineStr"/>
-      <c r="AC26" s="7" t="inlineStr"/>
+      <c r="W26" s="5" t="n">
+        <v>21050</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>21681.5</v>
+      </c>
+      <c r="Y26" s="6" t="n">
+        <v>-4.98812351543943</v>
+      </c>
+      <c r="Z26" s="5" t="n">
+        <v>22102.5</v>
+      </c>
+      <c r="AA26" s="6" t="n">
+        <v>-6.797873543716775</v>
+      </c>
+      <c r="AB26" s="5" t="n">
+        <v>22523.5</v>
+      </c>
+      <c r="AC26" s="6" t="n">
+        <v>-8.539969365329544</v>
+      </c>
       <c r="AD26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2499,50 +2525,50 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.4%</t>
+          <t>1차 매수선까지 6.7% (접근 중!)</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>326000</v>
+        <v>8730</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>319000</v>
+        <v>8530</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>347000</v>
+        <v>9030</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>314900</v>
+        <v>10369.5</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>251920</v>
+        <v>8295.6</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>250000</v>
+        <v>8180</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>30.4</v>
+        <v>6.723716381418093</v>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="5" t="n">
-        <v>225500</v>
+        <v>7380</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>44.56762749445677</v>
+        <v>18.29268292682927</v>
       </c>
       <c r="Q27" s="7" t="inlineStr"/>
       <c r="R27" s="7" t="inlineStr"/>
       <c r="S27" s="5" t="n">
-        <v>203500</v>
+        <v>6660</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>60.1965601965602</v>
+        <v>31.08108108108108</v>
       </c>
       <c r="U27" s="7" t="inlineStr"/>
       <c r="V27" s="7" t="inlineStr"/>
@@ -2558,12 +2584,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2578,45 +2604,45 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.8%</t>
+          <t>1차 매수선까지 16.2%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>427500</v>
+        <v>15820</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>415000</v>
+        <v>15810</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>448000</v>
+        <v>16500</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>463825</v>
+        <v>17157.5</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>371060</v>
+        <v>13726</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>366000</v>
+        <v>13620</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.80327868852459</v>
+        <v>16.15271659324523</v>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="5" t="n">
-        <v>330000</v>
+        <v>12270</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>29.54545454545455</v>
+        <v>28.93235533822331</v>
       </c>
       <c r="Q28" s="7" t="inlineStr"/>
       <c r="R28" s="7" t="inlineStr"/>
       <c r="S28" s="5" t="n">
-        <v>297500</v>
+        <v>11060</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>43.69747899159664</v>
+        <v>43.03797468354431</v>
       </c>
       <c r="U28" s="7" t="inlineStr"/>
       <c r="V28" s="7" t="inlineStr"/>
@@ -2632,12 +2658,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2652,45 +2678,45 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.3%</t>
+          <t>1차 매수선까지 28.7%</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>173600</v>
+        <v>332000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>171400</v>
+        <v>330000</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>176500</v>
+        <v>342000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>173395</v>
+        <v>324625</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>138716</v>
+        <v>259700</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>137500</v>
+        <v>258000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>26.25454545454545</v>
+        <v>28.68217054263566</v>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="5" t="n">
-        <v>123900</v>
+        <v>233000</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>40.11299435028249</v>
+        <v>42.48927038626609</v>
       </c>
       <c r="Q29" s="7" t="inlineStr"/>
       <c r="R29" s="7" t="inlineStr"/>
       <c r="S29" s="5" t="n">
-        <v>111700</v>
+        <v>210500</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>55.41629364368846</v>
+        <v>57.71971496437055</v>
       </c>
       <c r="U29" s="7" t="inlineStr"/>
       <c r="V29" s="7" t="inlineStr"/>
@@ -2706,12 +2732,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2721,50 +2747,50 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.4% (접근 중!)</t>
+          <t>1차 매수선까지 25.2%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>161000</v>
+        <v>452500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>159800</v>
+        <v>448000</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>172900</v>
+        <v>461000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>184660</v>
+        <v>456875</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>147728</v>
+        <v>365500</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>147100</v>
+        <v>361500</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>9.449354180829369</v>
+        <v>25.17289073305671</v>
       </c>
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="5" t="n">
-        <v>132500</v>
+        <v>326000</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>21.50943396226415</v>
+        <v>38.80368098159509</v>
       </c>
       <c r="Q30" s="7" t="inlineStr"/>
       <c r="R30" s="7" t="inlineStr"/>
       <c r="S30" s="5" t="n">
-        <v>119400</v>
+        <v>294000</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>34.84087102177554</v>
+        <v>53.91156462585034</v>
       </c>
       <c r="U30" s="7" t="inlineStr"/>
       <c r="V30" s="7" t="inlineStr"/>
@@ -2780,12 +2806,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2800,45 +2826,45 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.9%</t>
+          <t>1차 매수선까지 24.7%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>199500</v>
+        <v>172900</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>195500</v>
+        <v>172600</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>204500</v>
+        <v>178300</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>218800</v>
+        <v>174930</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>175040</v>
+        <v>139944</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>173700</v>
+        <v>138700</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>14.85319516407599</v>
+        <v>24.65753424657534</v>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="5" t="n">
-        <v>156500</v>
+        <v>125000</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>27.47603833865815</v>
+        <v>38.32</v>
       </c>
       <c r="Q31" s="7" t="inlineStr"/>
       <c r="R31" s="7" t="inlineStr"/>
       <c r="S31" s="5" t="n">
-        <v>141000</v>
+        <v>112600</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>41.48936170212766</v>
+        <v>53.55239786856127</v>
       </c>
       <c r="U31" s="7" t="inlineStr"/>
       <c r="V31" s="7" t="inlineStr"/>
@@ -2854,12 +2880,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2874,45 +2900,45 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.1%</t>
+          <t>1차 매수선까지 14.5%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>8940</v>
+        <v>169700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>8920</v>
+        <v>168000</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>9470</v>
+        <v>173300</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>9768</v>
+        <v>186035</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>7814.400000000001</v>
+        <v>148828</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>7770</v>
+        <v>148200</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>15.05791505791506</v>
+        <v>14.50742240215924</v>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="5" t="n">
-        <v>7010</v>
+        <v>133500</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>27.5320970042796</v>
+        <v>27.11610486891386</v>
       </c>
       <c r="Q32" s="7" t="inlineStr"/>
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="5" t="n">
-        <v>6320</v>
+        <v>120300</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>41.45569620253164</v>
+        <v>41.06400665004156</v>
       </c>
       <c r="U32" s="7" t="inlineStr"/>
       <c r="V32" s="7" t="inlineStr"/>
@@ -2928,12 +2954,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2948,45 +2974,45 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.1%</t>
+          <t>1차 매수선까지 17.3%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>201000</v>
+        <v>200500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>199800</v>
+        <v>200000</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>209500</v>
+        <v>206000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>216725</v>
+        <v>216440</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>173380</v>
+        <v>173152</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>171700</v>
+        <v>171000</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>17.06464764123471</v>
+        <v>17.25146198830409</v>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="7" t="inlineStr"/>
       <c r="O33" s="5" t="n">
-        <v>154700</v>
+        <v>154000</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>29.92889463477699</v>
+        <v>30.1948051948052</v>
       </c>
       <c r="Q33" s="7" t="inlineStr"/>
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="5" t="n">
-        <v>139400</v>
+        <v>138700</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>44.18938307030129</v>
+        <v>44.55659697188176</v>
       </c>
       <c r="U33" s="7" t="inlineStr"/>
       <c r="V33" s="7" t="inlineStr"/>
@@ -3002,12 +3028,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3022,45 +3048,45 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.1%</t>
+          <t>1차 매수선까지 16.6%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>64400</v>
+        <v>8990</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>63700</v>
+        <v>8750</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>70800</v>
+        <v>9250</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>48932.5</v>
+        <v>9797.5</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>39146</v>
+        <v>7838</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>39250</v>
+        <v>7710</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>64.07643312101911</v>
+        <v>16.6018158236057</v>
       </c>
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="5" t="n">
-        <v>35400</v>
+        <v>6950</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>81.92090395480226</v>
+        <v>29.35251798561151</v>
       </c>
       <c r="Q34" s="7" t="inlineStr"/>
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="5" t="n">
-        <v>31950</v>
+        <v>6270</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>101.5649452269171</v>
+        <v>43.38118022328549</v>
       </c>
       <c r="U34" s="7" t="inlineStr"/>
       <c r="V34" s="7" t="inlineStr"/>
@@ -3076,12 +3102,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3096,45 +3122,45 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.4%</t>
+          <t>1차 매수선까지 53.8%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>95400</v>
+        <v>67600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>94600</v>
+        <v>66000</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>99600</v>
+        <v>70700</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>104960</v>
+        <v>55047.5</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>83968</v>
+        <v>44038</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>83400</v>
+        <v>43950</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>14.38848920863309</v>
+        <v>53.81114903299203</v>
       </c>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="5" t="n">
-        <v>75200</v>
+        <v>39650</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>26.86170212765958</v>
+        <v>70.49180327868852</v>
       </c>
       <c r="Q35" s="7" t="inlineStr"/>
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="5" t="n">
-        <v>67800</v>
+        <v>35750</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>40.70796460176992</v>
+        <v>89.09090909090909</v>
       </c>
       <c r="U35" s="7" t="inlineStr"/>
       <c r="V35" s="7" t="inlineStr"/>
@@ -3150,12 +3176,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3165,50 +3191,50 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 2.0% (접근 중!)</t>
+          <t>1차 매수선까지 23.5%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>166300</v>
+        <v>101400</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>166000</v>
+        <v>99600</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>179300</v>
+        <v>102500</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>205420</v>
+        <v>103970</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>164336</v>
+        <v>83176</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>163000</v>
+        <v>82100</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>2.024539877300614</v>
+        <v>23.50791717417783</v>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr"/>
       <c r="O36" s="5" t="n">
-        <v>146800</v>
+        <v>74000</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>13.28337874659401</v>
+        <v>37.02702702702702</v>
       </c>
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="5" t="n">
-        <v>132300</v>
+        <v>66700</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>25.69916855631141</v>
+        <v>52.023988005997</v>
       </c>
       <c r="U36" s="7" t="inlineStr"/>
       <c r="V36" s="7" t="inlineStr"/>
@@ -3224,12 +3250,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3244,45 +3270,45 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.4%</t>
+          <t>1차 매수선까지 15.8%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>424500</v>
+        <v>179700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>420000</v>
+        <v>171200</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>435000</v>
+        <v>183500</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>451325</v>
+        <v>198050</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>361060</v>
+        <v>158440</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>355500</v>
+        <v>155200</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>19.40928270042194</v>
+        <v>15.7860824742268</v>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr"/>
       <c r="O37" s="5" t="n">
-        <v>320500</v>
+        <v>139800</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>32.44929797191888</v>
+        <v>28.54077253218884</v>
       </c>
       <c r="Q37" s="7" t="inlineStr"/>
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="5" t="n">
-        <v>289000</v>
+        <v>126000</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>46.88581314878893</v>
+        <v>42.61904761904762</v>
       </c>
       <c r="U37" s="7" t="inlineStr"/>
       <c r="V37" s="7" t="inlineStr"/>
@@ -3298,12 +3324,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3313,50 +3339,50 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.7% (접근 중!)</t>
+          <t>1차 매수선까지 25.2%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>21400</v>
+        <v>435000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>20900</v>
+        <v>426000</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>22500</v>
+        <v>446500</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>24830</v>
+        <v>440500</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>19864</v>
+        <v>352400</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>19510</v>
+        <v>347500</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>9.687339825730394</v>
+        <v>25.17985611510791</v>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="7" t="inlineStr"/>
       <c r="O38" s="5" t="n">
-        <v>17570</v>
+        <v>313500</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>21.79852020489471</v>
+        <v>38.75598086124402</v>
       </c>
       <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="5" t="n">
-        <v>15830</v>
+        <v>283000</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>35.18635502210991</v>
+        <v>53.71024734982333</v>
       </c>
       <c r="U38" s="7" t="inlineStr"/>
       <c r="V38" s="7" t="inlineStr"/>
@@ -3372,12 +3398,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3392,45 +3418,45 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.9%</t>
+          <t>1차 매수선까지 19.7%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>25650</v>
+        <v>22350</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>25100</v>
+        <v>21350</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>27750</v>
+        <v>23750</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>27742.5</v>
+        <v>23672.5</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>22194</v>
+        <v>18938</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>21750</v>
+        <v>18670</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>17.93103448275862</v>
+        <v>19.71076593465452</v>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr"/>
       <c r="O39" s="5" t="n">
-        <v>19590</v>
+        <v>16820</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>30.93415007656968</v>
+        <v>32.87752675386444</v>
       </c>
       <c r="Q39" s="7" t="inlineStr"/>
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="5" t="n">
-        <v>17650</v>
+        <v>15150</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>45.3257790368272</v>
+        <v>47.52475247524752</v>
       </c>
       <c r="U39" s="7" t="inlineStr"/>
       <c r="V39" s="7" t="inlineStr"/>
@@ -3446,12 +3472,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3466,45 +3492,45 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.4%</t>
+          <t>1차 매수선까지 33.7%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>20100</v>
+        <v>28350</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>20050</v>
+        <v>26600</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>22200</v>
+        <v>29500</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>21594.5</v>
+        <v>26877.5</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>17275.6</v>
+        <v>21502</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>16980</v>
+        <v>21200</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>18.37455830388692</v>
+        <v>33.72641509433962</v>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="7" t="inlineStr"/>
       <c r="O40" s="5" t="n">
-        <v>15300</v>
+        <v>19090</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>31.37254901960784</v>
+        <v>48.50707176532216</v>
       </c>
       <c r="Q40" s="7" t="inlineStr"/>
       <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="5" t="n">
-        <v>13780</v>
+        <v>17200</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>45.86357039187228</v>
+        <v>64.82558139534885</v>
       </c>
       <c r="U40" s="7" t="inlineStr"/>
       <c r="V40" s="7" t="inlineStr"/>
@@ -3520,12 +3546,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3540,45 +3566,45 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 12.5%</t>
+          <t>1차 매수선까지 33.8%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>48200</v>
+        <v>22500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>47000</v>
+        <v>22500</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>57700</v>
+        <v>24075</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>54645</v>
+        <v>21322</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>43716</v>
+        <v>17057.6</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>42850</v>
+        <v>16820</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.48541423570595</v>
+        <v>33.769322235434</v>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr"/>
       <c r="O41" s="5" t="n">
-        <v>38650</v>
+        <v>15150</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>24.70892626131953</v>
+        <v>48.51485148514851</v>
       </c>
       <c r="Q41" s="7" t="inlineStr"/>
       <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="5" t="n">
-        <v>34850</v>
+        <v>13650</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>38.30703012912482</v>
+        <v>64.83516483516483</v>
       </c>
       <c r="U41" s="7" t="inlineStr"/>
       <c r="V41" s="7" t="inlineStr"/>
@@ -3594,12 +3620,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3614,45 +3640,45 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.3%</t>
+          <t>1차 매수선까지 24.9%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>46450</v>
+        <v>51600</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>46200</v>
+        <v>48800</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>49250</v>
+        <v>51800</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>44997.5</v>
+        <v>52250</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>35998</v>
+        <v>41800</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>35650</v>
+        <v>41300</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>30.2945301542777</v>
+        <v>24.93946731234867</v>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr"/>
       <c r="O42" s="5" t="n">
-        <v>32150</v>
+        <v>37250</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>44.47900466562986</v>
+        <v>38.52348993288591</v>
       </c>
       <c r="Q42" s="7" t="inlineStr"/>
       <c r="R42" s="7" t="inlineStr"/>
       <c r="S42" s="5" t="n">
-        <v>29000</v>
+        <v>33600</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>60.17241379310345</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="U42" s="7" t="inlineStr"/>
       <c r="V42" s="7" t="inlineStr"/>
@@ -3668,12 +3694,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3688,45 +3714,45 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 11.6%</t>
+          <t>1차 매수선까지 33.5%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>22550</v>
+        <v>48600</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>22500</v>
+        <v>47800</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>23900</v>
+        <v>49800</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>25665</v>
+        <v>45787.5</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>20532</v>
+        <v>36630</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>20200</v>
+        <v>36400</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>11.63366336633663</v>
+        <v>33.51648351648351</v>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr"/>
       <c r="O43" s="5" t="n">
-        <v>18190</v>
+        <v>32850</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>23.9692138537658</v>
+        <v>47.94520547945205</v>
       </c>
       <c r="Q43" s="7" t="inlineStr"/>
       <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="5" t="n">
-        <v>16390</v>
+        <v>29650</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>37.58389261744966</v>
+        <v>63.91231028667791</v>
       </c>
       <c r="U43" s="7" t="inlineStr"/>
       <c r="V43" s="7" t="inlineStr"/>
@@ -3742,12 +3768,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3762,45 +3788,45 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.0%</t>
+          <t>1차 매수선까지 17.0%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>413500</v>
+        <v>22750</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>408500</v>
+        <v>22500</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>434500</v>
+        <v>23600</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>411125</v>
+        <v>24685</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>328900</v>
+        <v>19748</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>325500</v>
+        <v>19440</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>27.03533026113671</v>
+        <v>17.02674897119341</v>
       </c>
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="7" t="inlineStr"/>
       <c r="O44" s="5" t="n">
-        <v>293500</v>
+        <v>17510</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>40.88586030664395</v>
+        <v>29.92575671045118</v>
       </c>
       <c r="Q44" s="7" t="inlineStr"/>
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="5" t="n">
-        <v>265000</v>
+        <v>15770</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>56.0377358490566</v>
+        <v>44.26125554850983</v>
       </c>
       <c r="U44" s="7" t="inlineStr"/>
       <c r="V44" s="7" t="inlineStr"/>
@@ -3816,12 +3842,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3836,45 +3862,45 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.3%</t>
+          <t>1차 매수선까지 35.9%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>199500</v>
+        <v>449000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>194100</v>
+        <v>446000</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>206000</v>
+        <v>460000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>199315</v>
+        <v>417000</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>159452</v>
+        <v>333600</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>158000</v>
+        <v>330500</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>26.26582278481013</v>
+        <v>35.85476550680787</v>
       </c>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr"/>
       <c r="O45" s="5" t="n">
-        <v>142300</v>
+        <v>298000</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>40.19676739283204</v>
+        <v>50.67114093959731</v>
       </c>
       <c r="Q45" s="7" t="inlineStr"/>
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="5" t="n">
-        <v>128200</v>
+        <v>269000</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>55.61622464898596</v>
+        <v>66.91449814126395</v>
       </c>
       <c r="U45" s="7" t="inlineStr"/>
       <c r="V45" s="7" t="inlineStr"/>
@@ -3890,12 +3916,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3910,45 +3936,45 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.1%</t>
+          <t>1차 매수선까지 41.4%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>22200</v>
+        <v>229500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>21600</v>
+        <v>225500</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>22700</v>
+        <v>235000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>21710</v>
+        <v>204510</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>17368</v>
+        <v>163608</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>17190</v>
+        <v>162300</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>29.14485165794066</v>
+        <v>41.40480591497228</v>
       </c>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr"/>
       <c r="O46" s="5" t="n">
-        <v>15490</v>
+        <v>146200</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>43.31826985151711</v>
+        <v>56.97674418604651</v>
       </c>
       <c r="Q46" s="7" t="inlineStr"/>
       <c r="R46" s="7" t="inlineStr"/>
       <c r="S46" s="5" t="n">
-        <v>13960</v>
+        <v>131700</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>59.02578796561605</v>
+        <v>74.25968109339408</v>
       </c>
       <c r="U46" s="7" t="inlineStr"/>
       <c r="V46" s="7" t="inlineStr"/>
@@ -3964,12 +3990,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3984,45 +4010,45 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.5%</t>
+          <t>1차 매수선까지 36.3%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1580000</v>
+        <v>23900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1544000</v>
+        <v>23450</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>1625000</v>
+        <v>24500</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>1429900</v>
+        <v>22112.5</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1143920</v>
+        <v>17690</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1133000</v>
+        <v>17540</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>39.45278022947926</v>
+        <v>36.25997719498289</v>
       </c>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
       <c r="O47" s="5" t="n">
-        <v>1021000</v>
+        <v>15800</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>54.75024485798237</v>
+        <v>51.26582278481012</v>
       </c>
       <c r="Q47" s="7" t="inlineStr"/>
       <c r="R47" s="7" t="inlineStr"/>
       <c r="S47" s="5" t="n">
-        <v>920000</v>
+        <v>14230</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>71.73913043478261</v>
+        <v>67.9550245959241</v>
       </c>
       <c r="U47" s="7" t="inlineStr"/>
       <c r="V47" s="7" t="inlineStr"/>
@@ -4038,12 +4064,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4058,45 +4084,45 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 11.2%</t>
+          <t>1차 매수선까지 54.5%</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>432500</v>
+        <v>1838000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>429000</v>
+        <v>1682000</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>452000</v>
+        <v>1863000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>491600</v>
+        <v>1497700</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>393280</v>
+        <v>1198160</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>389000</v>
+        <v>1190000</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>11.18251928020566</v>
+        <v>54.45378151260504</v>
       </c>
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="7" t="inlineStr"/>
       <c r="O48" s="5" t="n">
-        <v>351000</v>
+        <v>1072000</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>23.21937321937322</v>
+        <v>71.45522388059702</v>
       </c>
       <c r="Q48" s="7" t="inlineStr"/>
       <c r="R48" s="7" t="inlineStr"/>
       <c r="S48" s="5" t="n">
-        <v>316500</v>
+        <v>966000</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>36.65086887835703</v>
+        <v>90.26915113871635</v>
       </c>
       <c r="U48" s="7" t="inlineStr"/>
       <c r="V48" s="7" t="inlineStr"/>
@@ -4112,12 +4138,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4132,45 +4158,45 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.9%</t>
+          <t>1차 매수선까지 23.3%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>40100</v>
+        <v>465500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>40100</v>
+        <v>448500</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>42350</v>
+        <v>474000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>41702.5</v>
+        <v>478275</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>33362</v>
+        <v>382620</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>32900</v>
+        <v>377500</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>21.88449848024316</v>
+        <v>23.3112582781457</v>
       </c>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
       <c r="O49" s="5" t="n">
-        <v>29700</v>
+        <v>340500</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>35.01683501683502</v>
+        <v>36.71071953010279</v>
       </c>
       <c r="Q49" s="7" t="inlineStr"/>
       <c r="R49" s="7" t="inlineStr"/>
       <c r="S49" s="5" t="n">
-        <v>26800</v>
+        <v>307000</v>
       </c>
       <c r="T49" s="6" t="n">
-        <v>49.62686567164179</v>
+        <v>51.62866449511401</v>
       </c>
       <c r="U49" s="7" t="inlineStr"/>
       <c r="V49" s="7" t="inlineStr"/>
@@ -4186,12 +4212,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4206,45 +4232,45 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.2%</t>
+          <t>1차 매수선까지 30.3%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>16020</v>
+        <v>42800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>15950</v>
+        <v>42600</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>16540</v>
+        <v>44250</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>18537.5</v>
+        <v>41427.5</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>14830</v>
+        <v>33142</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>14540</v>
+        <v>32850</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>10.17881705639615</v>
+        <v>30.28919330289193</v>
       </c>
       <c r="M50" s="7" t="inlineStr"/>
       <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="5" t="n">
-        <v>13100</v>
+        <v>29650</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>22.29007633587786</v>
+        <v>44.35075885328836</v>
       </c>
       <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="7" t="inlineStr"/>
       <c r="S50" s="5" t="n">
-        <v>11800</v>
+        <v>26750</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>35.76271186440678</v>
+        <v>60</v>
       </c>
       <c r="U50" s="7" t="inlineStr"/>
       <c r="V50" s="7" t="inlineStr"/>
@@ -4260,12 +4286,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4280,45 +4306,45 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 11.9%</t>
+          <t>1차 매수선까지 22.5%</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>84900</v>
+        <v>17230</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>82300</v>
+        <v>17170</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>89400</v>
+        <v>18070</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>96220</v>
+        <v>17851</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>76976</v>
+        <v>14280.8</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>75900</v>
+        <v>14070</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>11.85770750988142</v>
+        <v>22.4591329068941</v>
       </c>
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="7" t="inlineStr"/>
       <c r="O51" s="5" t="n">
-        <v>68500</v>
+        <v>12680</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>23.94160583941606</v>
+        <v>35.88328075709779</v>
       </c>
       <c r="Q51" s="7" t="inlineStr"/>
       <c r="R51" s="7" t="inlineStr"/>
       <c r="S51" s="5" t="n">
-        <v>61800</v>
+        <v>11430</v>
       </c>
       <c r="T51" s="6" t="n">
-        <v>37.37864077669903</v>
+        <v>50.74365704286964</v>
       </c>
       <c r="U51" s="7" t="inlineStr"/>
       <c r="V51" s="7" t="inlineStr"/>
@@ -4334,12 +4360,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4354,45 +4380,45 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.6%</t>
+          <t>1차 매수선까지 16.4%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>14200</v>
+        <v>85300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>14020</v>
+        <v>84100</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>14470</v>
+        <v>87100</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>13979.5</v>
+        <v>93300</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>11183.6</v>
+        <v>74640</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>11130</v>
+        <v>73300</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>27.58310871518418</v>
+        <v>16.37107776261938</v>
       </c>
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="5" t="n">
-        <v>10030</v>
+        <v>66100</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>41.5752741774676</v>
+        <v>29.04689863842663</v>
       </c>
       <c r="Q52" s="7" t="inlineStr"/>
       <c r="R52" s="7" t="inlineStr"/>
       <c r="S52" s="5" t="n">
-        <v>9040</v>
+        <v>59600</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>57.07964601769911</v>
+        <v>43.12080536912752</v>
       </c>
       <c r="U52" s="7" t="inlineStr"/>
       <c r="V52" s="7" t="inlineStr"/>
@@ -4408,12 +4434,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4428,45 +4454,45 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.6%</t>
+          <t>1차 매수선까지 24.9%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>76000</v>
+        <v>14150</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>75400</v>
+        <v>13840</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>78250</v>
+        <v>14330</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>79650</v>
+        <v>14239.5</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>63720</v>
+        <v>11391.6</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>63000</v>
+        <v>11330</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>20.63492063492063</v>
+        <v>24.88967343336276</v>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="5" t="n">
-        <v>56800</v>
+        <v>10210</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>33.80281690140845</v>
+        <v>38.5896180215475</v>
       </c>
       <c r="Q53" s="7" t="inlineStr"/>
       <c r="R53" s="7" t="inlineStr"/>
       <c r="S53" s="5" t="n">
-        <v>51300</v>
+        <v>9200</v>
       </c>
       <c r="T53" s="6" t="n">
-        <v>48.14814814814815</v>
+        <v>53.80434782608695</v>
       </c>
       <c r="U53" s="7" t="inlineStr"/>
       <c r="V53" s="7" t="inlineStr"/>
@@ -4482,12 +4508,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4502,45 +4528,45 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.7%</t>
+          <t>1차 매수선까지 23.8%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>237000</v>
+        <v>77400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>225000</v>
+        <v>77100</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>245500</v>
+        <v>79100</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>235200</v>
+        <v>78920</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>188160</v>
+        <v>63136</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>187000</v>
+        <v>62500</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>26.7379679144385</v>
+        <v>23.84</v>
       </c>
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="7" t="inlineStr"/>
       <c r="O54" s="5" t="n">
-        <v>168400</v>
+        <v>56400</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>40.73634204275535</v>
+        <v>37.23404255319149</v>
       </c>
       <c r="Q54" s="7" t="inlineStr"/>
       <c r="R54" s="7" t="inlineStr"/>
       <c r="S54" s="5" t="n">
-        <v>151700</v>
+        <v>50900</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>56.22940013183916</v>
+        <v>52.06286836935167</v>
       </c>
       <c r="U54" s="7" t="inlineStr"/>
       <c r="V54" s="7" t="inlineStr"/>
@@ -4556,12 +4582,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4576,45 +4602,45 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.7%</t>
+          <t>1차 매수선까지 28.2%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>100700</v>
+        <v>244000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>100100</v>
+        <v>235000</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>103500</v>
+        <v>245000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>105620</v>
+        <v>239475</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>84496</v>
+        <v>191580</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>83400</v>
+        <v>190300</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>20.74340527577937</v>
+        <v>28.21860220704152</v>
       </c>
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="7" t="inlineStr"/>
       <c r="O55" s="5" t="n">
-        <v>75200</v>
+        <v>171400</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>33.9095744680851</v>
+        <v>42.35705950991832</v>
       </c>
       <c r="Q55" s="7" t="inlineStr"/>
       <c r="R55" s="7" t="inlineStr"/>
       <c r="S55" s="5" t="n">
-        <v>67800</v>
+        <v>154400</v>
       </c>
       <c r="T55" s="6" t="n">
-        <v>48.52507374631269</v>
+        <v>58.03108808290155</v>
       </c>
       <c r="U55" s="7" t="inlineStr"/>
       <c r="V55" s="7" t="inlineStr"/>
@@ -4630,12 +4656,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4650,45 +4676,45 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.1%</t>
+          <t>1차 매수선까지 28.3%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>916000</v>
+        <v>106200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>905000</v>
+        <v>106000</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>947000</v>
+        <v>109300</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1020850</v>
+        <v>104995</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>816680</v>
+        <v>83996</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>810000</v>
+        <v>82800</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>13.08641975308642</v>
+        <v>28.26086956521739</v>
       </c>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="5" t="n">
-        <v>730000</v>
+        <v>74700</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>25.47945205479452</v>
+        <v>42.16867469879519</v>
       </c>
       <c r="Q56" s="7" t="inlineStr"/>
       <c r="R56" s="7" t="inlineStr"/>
       <c r="S56" s="5" t="n">
-        <v>658000</v>
+        <v>67400</v>
       </c>
       <c r="T56" s="6" t="n">
-        <v>39.209726443769</v>
+        <v>57.56676557863501</v>
       </c>
       <c r="U56" s="7" t="inlineStr"/>
       <c r="V56" s="7" t="inlineStr"/>
@@ -4704,12 +4730,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4724,45 +4750,45 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 12.5%</t>
+          <t>1차 매수선까지 29.9%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>51300</v>
+        <v>1046000</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>51000</v>
+        <v>996000</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>53600</v>
+        <v>1063000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>57480</v>
+        <v>1016650</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>45984</v>
+        <v>813320</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>45600</v>
+        <v>805000</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>12.5</v>
+        <v>29.93788819875776</v>
       </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="5" t="n">
-        <v>41100</v>
+        <v>726000</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>24.81751824817518</v>
+        <v>44.0771349862259</v>
       </c>
       <c r="Q57" s="7" t="inlineStr"/>
       <c r="R57" s="7" t="inlineStr"/>
       <c r="S57" s="5" t="n">
-        <v>37050</v>
+        <v>655000</v>
       </c>
       <c r="T57" s="6" t="n">
-        <v>38.46153846153847</v>
+        <v>59.69465648854961</v>
       </c>
       <c r="U57" s="7" t="inlineStr"/>
       <c r="V57" s="7" t="inlineStr"/>
@@ -4778,12 +4804,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4798,45 +4824,45 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.3%</t>
+          <t>1차 매수선까지 24.6%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>29400</v>
+        <v>55900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>28500</v>
+        <v>54400</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>30200</v>
+        <v>57200</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>29230</v>
+        <v>56775</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>23384</v>
+        <v>45420</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>23100</v>
+        <v>44850</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>27.27272727272727</v>
+        <v>24.63768115942029</v>
       </c>
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="7" t="inlineStr"/>
       <c r="O58" s="5" t="n">
-        <v>20850</v>
+        <v>40450</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>41.00719424460431</v>
+        <v>38.19530284301607</v>
       </c>
       <c r="Q58" s="7" t="inlineStr"/>
       <c r="R58" s="7" t="inlineStr"/>
       <c r="S58" s="5" t="n">
-        <v>18780</v>
+        <v>36500</v>
       </c>
       <c r="T58" s="6" t="n">
-        <v>56.54952076677316</v>
+        <v>53.15068493150685</v>
       </c>
       <c r="U58" s="7" t="inlineStr"/>
       <c r="V58" s="7" t="inlineStr"/>
@@ -4852,12 +4878,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4872,45 +4898,45 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.7%</t>
+          <t>1차 매수선까지 32.5%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>202500</v>
+        <v>30600</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>196000</v>
+        <v>29650</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>208000</v>
+        <v>30650</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>198300</v>
+        <v>29172.5</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>158640</v>
+        <v>23338</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>157400</v>
+        <v>23100</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>28.65311308767471</v>
+        <v>32.46753246753246</v>
       </c>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="5" t="n">
-        <v>141800</v>
+        <v>20850</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>42.80677009873061</v>
+        <v>46.76258992805755</v>
       </c>
       <c r="Q59" s="7" t="inlineStr"/>
       <c r="R59" s="7" t="inlineStr"/>
       <c r="S59" s="5" t="n">
-        <v>127800</v>
+        <v>18780</v>
       </c>
       <c r="T59" s="6" t="n">
-        <v>58.45070422535211</v>
+        <v>62.93929712460064</v>
       </c>
       <c r="U59" s="7" t="inlineStr"/>
       <c r="V59" s="7" t="inlineStr"/>
@@ -4926,12 +4952,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4946,45 +4972,45 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.3%</t>
+          <t>1차 매수선까지 37.5%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>50900</v>
+        <v>221500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>50200</v>
+        <v>206500</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>52500</v>
+        <v>223500</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>55960</v>
+        <v>203085</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>44768</v>
+        <v>162468</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>44150</v>
+        <v>161100</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>15.28878822197056</v>
+        <v>37.49224084419615</v>
       </c>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
       <c r="O60" s="5" t="n">
-        <v>39800</v>
+        <v>145100</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>27.8894472361809</v>
+        <v>52.65334252239835</v>
       </c>
       <c r="Q60" s="7" t="inlineStr"/>
       <c r="R60" s="7" t="inlineStr"/>
       <c r="S60" s="5" t="n">
-        <v>35900</v>
+        <v>130700</v>
       </c>
       <c r="T60" s="6" t="n">
-        <v>41.78272980501393</v>
+        <v>69.47207345065034</v>
       </c>
       <c r="U60" s="7" t="inlineStr"/>
       <c r="V60" s="7" t="inlineStr"/>
@@ -5000,12 +5026,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5020,45 +5046,45 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.3%</t>
+          <t>1차 매수선까지 20.9%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>14680</v>
+        <v>51700</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>14300</v>
+        <v>51200</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>15970</v>
+        <v>52400</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>15396</v>
+        <v>54245</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>12316.8</v>
+        <v>43396</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>12200</v>
+        <v>42750</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>20.32786885245902</v>
+        <v>20.93567251461988</v>
       </c>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
       <c r="O61" s="5" t="n">
-        <v>10990</v>
+        <v>38550</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>33.57597816196542</v>
+        <v>34.11154345006485</v>
       </c>
       <c r="Q61" s="7" t="inlineStr"/>
       <c r="R61" s="7" t="inlineStr"/>
       <c r="S61" s="5" t="n">
-        <v>9910</v>
+        <v>34750</v>
       </c>
       <c r="T61" s="6" t="n">
-        <v>48.13319878910192</v>
+        <v>48.77697841726619</v>
       </c>
       <c r="U61" s="7" t="inlineStr"/>
       <c r="V61" s="7" t="inlineStr"/>
@@ -5074,12 +5100,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5094,45 +5120,45 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.8%</t>
+          <t>1차 매수선까지 39.7%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>30200</v>
+        <v>17020</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>28800</v>
+        <v>15400</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>31000</v>
+        <v>17270</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>30415</v>
+        <v>15447.5</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>24332</v>
+        <v>12358</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>24000</v>
+        <v>12180</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>25.83333333333334</v>
+        <v>39.73727422003284</v>
       </c>
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr"/>
       <c r="O62" s="5" t="n">
-        <v>21650</v>
+        <v>10980</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>39.4919168591224</v>
+        <v>55.00910746812387</v>
       </c>
       <c r="Q62" s="7" t="inlineStr"/>
       <c r="R62" s="7" t="inlineStr"/>
       <c r="S62" s="5" t="n">
-        <v>19500</v>
+        <v>9900</v>
       </c>
       <c r="T62" s="6" t="n">
-        <v>54.87179487179488</v>
+        <v>71.91919191919192</v>
       </c>
       <c r="U62" s="7" t="inlineStr"/>
       <c r="V62" s="7" t="inlineStr"/>
@@ -5148,12 +5174,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5168,45 +5194,45 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.1%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>2610</v>
+        <v>28750</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2540</v>
+        <v>28700</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>2855</v>
+        <v>29450</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>2628.25</v>
+        <v>29927.5</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>2102.6</v>
+        <v>23942</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>2070</v>
+        <v>23650</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>26.08695652173913</v>
+        <v>21.56448202959831</v>
       </c>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="7" t="inlineStr"/>
       <c r="O63" s="5" t="n">
-        <v>1864</v>
+        <v>21350</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>40.02145922746781</v>
+        <v>34.66042154566745</v>
       </c>
       <c r="Q63" s="7" t="inlineStr"/>
       <c r="R63" s="7" t="inlineStr"/>
       <c r="S63" s="5" t="n">
-        <v>1679</v>
+        <v>19230</v>
       </c>
       <c r="T63" s="6" t="n">
-        <v>55.44967242406194</v>
+        <v>49.50598023920957</v>
       </c>
       <c r="U63" s="7" t="inlineStr"/>
       <c r="V63" s="7" t="inlineStr"/>
@@ -5222,12 +5248,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5237,50 +5263,50 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 6.7% (접근 중!)</t>
+          <t>1차 매수선까지 33.0%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>6550</v>
+        <v>2720</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>6510</v>
+        <v>2680</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>6710</v>
+        <v>2870</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>7786.5</v>
+        <v>2585</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>6229.200000000001</v>
+        <v>2068</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>6140</v>
+        <v>2045</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6.677524429967427</v>
+        <v>33.00733496332519</v>
       </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="5" t="n">
-        <v>5540</v>
+        <v>1842</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>18.23104693140794</v>
+        <v>47.66558089033659</v>
       </c>
       <c r="Q64" s="7" t="inlineStr"/>
       <c r="R64" s="7" t="inlineStr"/>
       <c r="S64" s="5" t="n">
-        <v>4995</v>
+        <v>1659</v>
       </c>
       <c r="T64" s="6" t="n">
-        <v>31.13113113113113</v>
+        <v>63.95418927064497</v>
       </c>
       <c r="U64" s="7" t="inlineStr"/>
       <c r="V64" s="7" t="inlineStr"/>
@@ -5296,12 +5322,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5316,45 +5342,45 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 11.8%</t>
+          <t>1차 매수선까지 12.0%</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>130400</v>
+        <v>6510</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>125100</v>
+        <v>6490</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>137200</v>
+        <v>6710</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>147580</v>
+        <v>7395.5</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>118064</v>
+        <v>5916.400000000001</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>116600</v>
+        <v>5810</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>11.83533447684391</v>
+        <v>12.04819277108434</v>
       </c>
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="7" t="inlineStr"/>
       <c r="O65" s="5" t="n">
-        <v>105100</v>
+        <v>5240</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>24.07231208372978</v>
+        <v>24.23664122137404</v>
       </c>
       <c r="Q65" s="7" t="inlineStr"/>
       <c r="R65" s="7" t="inlineStr"/>
       <c r="S65" s="5" t="n">
-        <v>94700</v>
+        <v>4725</v>
       </c>
       <c r="T65" s="6" t="n">
-        <v>37.69799366420274</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="U65" s="7" t="inlineStr"/>
       <c r="V65" s="7" t="inlineStr"/>
@@ -5370,12 +5396,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5390,45 +5416,45 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 17.1%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>36900</v>
+        <v>133900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>36800</v>
+        <v>133600</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>38550</v>
+        <v>138000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>38305</v>
+        <v>144815</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>30644</v>
+        <v>115852</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>30350</v>
+        <v>114300</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>21.58154859967051</v>
+        <v>17.14785651793526</v>
       </c>
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="7" t="inlineStr"/>
       <c r="O66" s="5" t="n">
-        <v>27400</v>
+        <v>103000</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>34.67153284671533</v>
+        <v>30</v>
       </c>
       <c r="Q66" s="7" t="inlineStr"/>
       <c r="R66" s="7" t="inlineStr"/>
       <c r="S66" s="5" t="n">
-        <v>24750</v>
+        <v>92800</v>
       </c>
       <c r="T66" s="6" t="n">
-        <v>49.09090909090909</v>
+        <v>44.28879310344828</v>
       </c>
       <c r="U66" s="7" t="inlineStr"/>
       <c r="V66" s="7" t="inlineStr"/>
@@ -5444,12 +5470,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5459,50 +5485,50 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.5% (접근 중!)</t>
+          <t>1차 매수선까지 22.0%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>9580</v>
+        <v>37150</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>9550</v>
+        <v>36850</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>10080</v>
+        <v>38150</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>11115</v>
+        <v>38405</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>8892</v>
+        <v>30724</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>8750</v>
+        <v>30450</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>9.485714285714286</v>
+        <v>22.00328407224959</v>
       </c>
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="5" t="n">
-        <v>7890</v>
+        <v>27500</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>21.41951837769328</v>
+        <v>35.09090909090909</v>
       </c>
       <c r="Q67" s="7" t="inlineStr"/>
       <c r="R67" s="7" t="inlineStr"/>
       <c r="S67" s="5" t="n">
-        <v>7120</v>
+        <v>24800</v>
       </c>
       <c r="T67" s="6" t="n">
-        <v>34.55056179775281</v>
+        <v>49.79838709677419</v>
       </c>
       <c r="U67" s="7" t="inlineStr"/>
       <c r="V67" s="7" t="inlineStr"/>
@@ -5518,12 +5544,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5533,50 +5559,50 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.5%</t>
+          <t>1차 매수선까지 9.2% (접근 중!)</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>256000</v>
+        <v>9010</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>244000</v>
+        <v>8900</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>267000</v>
+        <v>9270</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>220995</v>
+        <v>10531</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>176796</v>
+        <v>8424.800000000001</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>175900</v>
+        <v>8250</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>45.53723706651506</v>
+        <v>9.212121212121211</v>
       </c>
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="7" t="inlineStr"/>
       <c r="O68" s="5" t="n">
-        <v>158500</v>
+        <v>7440</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>61.51419558359621</v>
+        <v>21.10215053763441</v>
       </c>
       <c r="Q68" s="7" t="inlineStr"/>
       <c r="R68" s="7" t="inlineStr"/>
       <c r="S68" s="5" t="n">
-        <v>142800</v>
+        <v>6710</v>
       </c>
       <c r="T68" s="6" t="n">
-        <v>79.27170868347339</v>
+        <v>34.27719821162444</v>
       </c>
       <c r="U68" s="7" t="inlineStr"/>
       <c r="V68" s="7" t="inlineStr"/>
@@ -5592,12 +5618,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5612,45 +5638,45 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.8%</t>
+          <t>1차 매수선까지 36.5%</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>289000</v>
+        <v>251500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>281500</v>
+        <v>242000</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>300000</v>
+        <v>258500</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>279350</v>
+        <v>231755</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>223480</v>
+        <v>185404</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>221000</v>
+        <v>184200</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>30.76923076923077</v>
+        <v>36.53637350705755</v>
       </c>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr"/>
       <c r="O69" s="5" t="n">
-        <v>199000</v>
+        <v>165900</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>45.22613065326633</v>
+        <v>51.59734779987944</v>
       </c>
       <c r="Q69" s="7" t="inlineStr"/>
       <c r="R69" s="7" t="inlineStr"/>
       <c r="S69" s="5" t="n">
-        <v>179200</v>
+        <v>149500</v>
       </c>
       <c r="T69" s="6" t="n">
-        <v>61.27232142857143</v>
+        <v>68.22742474916387</v>
       </c>
       <c r="U69" s="7" t="inlineStr"/>
       <c r="V69" s="7" t="inlineStr"/>
@@ -5666,12 +5692,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5686,45 +5712,45 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.9%</t>
+          <t>1차 매수선까지 36.6%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>94400</v>
+        <v>306000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>93200</v>
+        <v>304500</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>98900</v>
+        <v>317500</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>95340</v>
+        <v>282850</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>76272</v>
+        <v>226280</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>75600</v>
+        <v>224000</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>24.86772486772487</v>
+        <v>36.60714285714285</v>
       </c>
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="7" t="inlineStr"/>
       <c r="O70" s="5" t="n">
-        <v>68200</v>
+        <v>202500</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>38.41642228739003</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="Q70" s="7" t="inlineStr"/>
       <c r="R70" s="7" t="inlineStr"/>
       <c r="S70" s="5" t="n">
-        <v>61500</v>
+        <v>182400</v>
       </c>
       <c r="T70" s="6" t="n">
-        <v>53.49593495934959</v>
+        <v>67.76315789473685</v>
       </c>
       <c r="U70" s="7" t="inlineStr"/>
       <c r="V70" s="7" t="inlineStr"/>
@@ -5740,12 +5766,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5760,45 +5786,45 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.4%</t>
+          <t>1차 매수선까지 50.0%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>81800</v>
+        <v>114900</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>81200</v>
+        <v>101700</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>85400</v>
+        <v>117400</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>86780</v>
+        <v>96975</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>69424</v>
+        <v>77580</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>68500</v>
+        <v>76600</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>19.41605839416059</v>
+        <v>50</v>
       </c>
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr"/>
       <c r="O71" s="5" t="n">
-        <v>61800</v>
+        <v>69100</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>32.36245954692556</v>
+        <v>66.28075253256151</v>
       </c>
       <c r="Q71" s="7" t="inlineStr"/>
       <c r="R71" s="7" t="inlineStr"/>
       <c r="S71" s="5" t="n">
-        <v>55800</v>
+        <v>62300</v>
       </c>
       <c r="T71" s="6" t="n">
-        <v>46.59498207885305</v>
+        <v>84.43017656500803</v>
       </c>
       <c r="U71" s="7" t="inlineStr"/>
       <c r="V71" s="7" t="inlineStr"/>
@@ -5814,12 +5840,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5834,45 +5860,45 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.2%</t>
+          <t>1차 매수선까지 38.5%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>216500</v>
+        <v>94900</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>213000</v>
+        <v>91600</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>227000</v>
+        <v>97500</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>220750</v>
+        <v>86775</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>176600</v>
+        <v>69420</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>174300</v>
+        <v>68500</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>24.21113023522662</v>
+        <v>38.54014598540146</v>
       </c>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
       <c r="O72" s="5" t="n">
-        <v>157000</v>
+        <v>61800</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>37.89808917197453</v>
+        <v>53.55987055016181</v>
       </c>
       <c r="Q72" s="7" t="inlineStr"/>
       <c r="R72" s="7" t="inlineStr"/>
       <c r="S72" s="5" t="n">
-        <v>141400</v>
+        <v>55800</v>
       </c>
       <c r="T72" s="6" t="n">
-        <v>53.11173974540311</v>
+        <v>70.07168458781362</v>
       </c>
       <c r="U72" s="7" t="inlineStr"/>
       <c r="V72" s="7" t="inlineStr"/>
@@ -5888,12 +5914,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5908,45 +5934,45 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.9%</t>
+          <t>1차 매수선까지 32.0%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>113900</v>
+        <v>230000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>111800</v>
+        <v>227000</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>119000</v>
+        <v>235000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>105140</v>
+        <v>220375</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>84112</v>
+        <v>176300</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>83200</v>
+        <v>174200</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>36.89903846153847</v>
+        <v>32.03214695752009</v>
       </c>
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="5" t="n">
-        <v>75000</v>
+        <v>156900</v>
       </c>
       <c r="P73" s="6" t="n">
-        <v>51.86666666666667</v>
+        <v>46.59018483110262</v>
       </c>
       <c r="Q73" s="7" t="inlineStr"/>
       <c r="R73" s="7" t="inlineStr"/>
       <c r="S73" s="5" t="n">
-        <v>67600</v>
+        <v>141400</v>
       </c>
       <c r="T73" s="6" t="n">
-        <v>68.49112426035504</v>
+        <v>62.65912305516266</v>
       </c>
       <c r="U73" s="7" t="inlineStr"/>
       <c r="V73" s="7" t="inlineStr"/>
@@ -5958,6 +5984,80 @@
       <c r="AB73" s="7" t="inlineStr"/>
       <c r="AC73" s="7" t="inlineStr"/>
       <c r="AD73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 45.1%</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>125100</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>124000</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>128000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>108560</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>86848</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>86200</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>45.12761020881671</v>
+      </c>
+      <c r="M74" s="7" t="inlineStr"/>
+      <c r="N74" s="7" t="inlineStr"/>
+      <c r="O74" s="5" t="n">
+        <v>77700</v>
+      </c>
+      <c r="P74" s="6" t="n">
+        <v>61.003861003861</v>
+      </c>
+      <c r="Q74" s="7" t="inlineStr"/>
+      <c r="R74" s="7" t="inlineStr"/>
+      <c r="S74" s="5" t="n">
+        <v>70100</v>
+      </c>
+      <c r="T74" s="6" t="n">
+        <v>78.45934379457917</v>
+      </c>
+      <c r="U74" s="7" t="inlineStr"/>
+      <c r="V74" s="7" t="inlineStr"/>
+      <c r="W74" s="7" t="inlineStr"/>
+      <c r="X74" s="7" t="inlineStr"/>
+      <c r="Y74" s="7" t="inlineStr"/>
+      <c r="Z74" s="7" t="inlineStr"/>
+      <c r="AA74" s="7" t="inlineStr"/>
+      <c r="AB74" s="7" t="inlineStr"/>
+      <c r="AC74" s="7" t="inlineStr"/>
+      <c r="AD74" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5970,14 +6070,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="n"/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>티커</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>매수상태</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>알람상태</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>상태메시지</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>저가</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>고가</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>20일선</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>-20%엔벨로프</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수선</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수선이격도(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수일</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수가</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수선</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수선이격도(%)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수일</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수가</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수선</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수선이격도(%)</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수일</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수가</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>평균매수가</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>1차매도선(+3%)</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>1차매도선이격도(%)</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>2차매도선(+5%)</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>2차매도선이격도(%)</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>3차매도선(+7%)</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>3차매도선이격도(%)</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>최고도달선</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>종료사유</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>실현수익률(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>456160</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>매도 완료</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>170500</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>161600</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>196700</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>199815</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>159852</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>157600</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>8.185279187817258</v>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>159500</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>142000</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>20.07042253521127</v>
+      </c>
+      <c r="Q2" s="7" t="n"/>
+      <c r="R2" s="7" t="n"/>
+      <c r="S2" s="5" t="n">
+        <v>127900</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>33.30727130570759</v>
+      </c>
+      <c r="U2" s="7" t="n"/>
+      <c r="V2" s="7" t="n"/>
+      <c r="W2" s="5" t="n">
+        <v>159500</v>
+      </c>
+      <c r="X2" s="5" t="n">
+        <v>164285</v>
+      </c>
+      <c r="Y2" s="6" t="n">
+        <v>3.783059926347506</v>
+      </c>
+      <c r="Z2" s="5" t="n">
+        <v>167475</v>
+      </c>
+      <c r="AA2" s="6" t="n">
+        <v>1.80623973727422</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>170665</v>
+      </c>
+      <c r="AC2" s="6" t="n">
+        <v>-0.09668063164679343</v>
+      </c>
+      <c r="AD2" s="7" t="n"/>
+      <c r="AE2" s="8" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>매도 완료</t>
+        </is>
+      </c>
+      <c r="AG2" s="6" t="n">
+        <v>6.896551724137931</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,7 +58,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -80,9 +79,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD74"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -658,45 +654,45 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.9%</t>
+          <t>1차 매수선까지 36.3%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>96400</v>
+        <v>101700</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>95200</v>
+        <v>99100</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>98500</v>
+        <v>101700</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>90345</v>
+        <v>93740</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>72276</v>
+        <v>74992</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>72000</v>
+        <v>74600</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>33.88888888888889</v>
+        <v>36.32707774798928</v>
       </c>
       <c r="M2" s="7" t="inlineStr"/>
       <c r="N2" s="7" t="inlineStr"/>
       <c r="O2" s="5" t="n">
-        <v>64900</v>
+        <v>67300</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>48.53620955315871</v>
+        <v>51.11441307578009</v>
       </c>
       <c r="Q2" s="7" t="inlineStr"/>
       <c r="R2" s="7" t="inlineStr"/>
       <c r="S2" s="5" t="n">
-        <v>58600</v>
+        <v>60700</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>64.50511945392492</v>
+        <v>67.54530477759472</v>
       </c>
       <c r="U2" s="7" t="inlineStr"/>
       <c r="V2" s="7" t="inlineStr"/>
@@ -732,45 +728,45 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.7%</t>
+          <t>1차 매수선까지 60.9%</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>477000</v>
+        <v>568000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>468000</v>
+        <v>522000</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>488500</v>
+        <v>568000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>404875</v>
+        <v>441275</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>323900</v>
+        <v>353020</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>323000</v>
+        <v>353000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>47.6780185758514</v>
+        <v>60.90651558073654</v>
       </c>
       <c r="M3" s="7" t="inlineStr"/>
       <c r="N3" s="7" t="inlineStr"/>
       <c r="O3" s="5" t="n">
-        <v>291500</v>
+        <v>318500</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>63.63636363636363</v>
+        <v>78.33594976452119</v>
       </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="5" t="n">
-        <v>263000</v>
+        <v>287500</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>81.36882129277566</v>
+        <v>97.56521739130434</v>
       </c>
       <c r="U3" s="7" t="inlineStr"/>
       <c r="V3" s="7" t="inlineStr"/>
@@ -806,45 +802,45 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.4%</t>
+          <t>1차 매수선까지 53.8%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>76500</v>
+        <v>93200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>75500</v>
+        <v>87300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>78200</v>
+        <v>97400</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>71310</v>
+        <v>75825</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>57048</v>
+        <v>60660</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>56900</v>
+        <v>60600</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>34.44639718804921</v>
+        <v>53.79537953795379</v>
       </c>
       <c r="M4" s="7" t="inlineStr"/>
       <c r="N4" s="7" t="inlineStr"/>
       <c r="O4" s="5" t="n">
-        <v>51400</v>
+        <v>54700</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>48.83268482490272</v>
+        <v>70.38391224862889</v>
       </c>
       <c r="Q4" s="7" t="inlineStr"/>
       <c r="R4" s="7" t="inlineStr"/>
       <c r="S4" s="5" t="n">
-        <v>46350</v>
+        <v>49300</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>65.0485436893204</v>
+        <v>89.04665314401623</v>
       </c>
       <c r="U4" s="7" t="inlineStr"/>
       <c r="V4" s="7" t="inlineStr"/>
@@ -860,12 +856,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -880,45 +876,45 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.6%</t>
+          <t>1차 매수선까지 49.9%</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>243000</v>
+        <v>139900</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>242000</v>
+        <v>127200</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>255000</v>
+        <v>141100</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>253075</v>
+        <v>117395</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>202460</v>
+        <v>93916</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>201500</v>
+        <v>93300</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.59553349875931</v>
+        <v>49.94640943193998</v>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="5" t="n">
-        <v>181500</v>
+        <v>84100</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>33.88429752066116</v>
+        <v>66.34958382877527</v>
       </c>
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="5" t="n">
-        <v>163500</v>
+        <v>75800</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>48.62385321100918</v>
+        <v>84.56464379947229</v>
       </c>
       <c r="U5" s="7" t="inlineStr"/>
       <c r="V5" s="7" t="inlineStr"/>
@@ -934,12 +930,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>035420</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -954,45 +950,45 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 57.7%</t>
+          <t>1차 매수선까지 30.3%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>148600</v>
+        <v>266500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>144700</v>
+        <v>252500</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>152900</v>
+        <v>268500</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>117620</v>
+        <v>257600</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>94096</v>
+        <v>206080</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>94200</v>
+        <v>204500</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>57.74946921443737</v>
+        <v>30.31784841075795</v>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="5" t="n">
-        <v>84900</v>
+        <v>184200</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>75.02944640753827</v>
+        <v>44.67969598262758</v>
       </c>
       <c r="Q6" s="7" t="inlineStr"/>
       <c r="R6" s="7" t="inlineStr"/>
       <c r="S6" s="5" t="n">
-        <v>76600</v>
+        <v>165900</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>93.99477806788512</v>
+        <v>60.63893911995177</v>
       </c>
       <c r="U6" s="7" t="inlineStr"/>
       <c r="V6" s="7" t="inlineStr"/>
@@ -1008,12 +1004,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>086520</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1028,45 +1024,45 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 79.7%</t>
+          <t>1차 매수선까지 71.6%</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>81500</v>
+        <v>331500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>81500</v>
+        <v>305000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>87200</v>
+        <v>334000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>56875</v>
+        <v>242300</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>45500</v>
+        <v>193840</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>45350</v>
+        <v>193200</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>79.71334068357223</v>
+        <v>71.58385093167702</v>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="5" t="n">
-        <v>40900</v>
+        <v>174000</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>99.26650366748166</v>
+        <v>90.51724137931035</v>
       </c>
       <c r="Q7" s="7" t="inlineStr"/>
       <c r="R7" s="7" t="inlineStr"/>
       <c r="S7" s="5" t="n">
-        <v>36900</v>
+        <v>156700</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>120.8672086720867</v>
+        <v>111.5507338864071</v>
       </c>
       <c r="U7" s="7" t="inlineStr"/>
       <c r="V7" s="7" t="inlineStr"/>
@@ -1082,12 +1078,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1102,45 +1098,45 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 51.9%</t>
+          <t>1차 매수선까지 35.3%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>135000</v>
+        <v>138700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>128600</v>
+        <v>133300</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>139700</v>
+        <v>147400</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>112155</v>
+        <v>127645</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>89724</v>
+        <v>102116</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>88900</v>
+        <v>102500</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>51.85601799775028</v>
+        <v>35.3170731707317</v>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="5" t="n">
-        <v>80200</v>
+        <v>92400</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>68.3291770573566</v>
+        <v>50.10822510822511</v>
       </c>
       <c r="Q8" s="7" t="inlineStr"/>
       <c r="R8" s="7" t="inlineStr"/>
       <c r="S8" s="5" t="n">
-        <v>72300</v>
+        <v>83300</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>86.72199170124482</v>
+        <v>66.50660264105642</v>
       </c>
       <c r="U8" s="7" t="inlineStr"/>
       <c r="V8" s="7" t="inlineStr"/>
@@ -1176,45 +1172,45 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.5%</t>
+          <t>1차 매수선까지 51.7%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>250500</v>
+        <v>285500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>250000</v>
+        <v>251000</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>260000</v>
+        <v>290500</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>227750</v>
+        <v>236600</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>182200</v>
+        <v>189280</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>180900</v>
+        <v>188200</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>38.47429519071311</v>
+        <v>51.70031880977683</v>
       </c>
       <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="5" t="n">
-        <v>163000</v>
+        <v>169500</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>53.68098159509203</v>
+        <v>68.43657817109144</v>
       </c>
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="5" t="n">
-        <v>146800</v>
+        <v>152700</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>70.64032697547684</v>
+        <v>86.96791093647676</v>
       </c>
       <c r="U9" s="7" t="inlineStr"/>
       <c r="V9" s="7" t="inlineStr"/>
@@ -1230,12 +1226,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>247540</t>
+          <t>086520</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1250,45 +1246,45 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 53.6%</t>
+          <t>1차 매수선까지 75.4%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>157900</v>
+        <v>92100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>157500</v>
+        <v>90200</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>167800</v>
+        <v>96400</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>129250</v>
+        <v>65450</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>103400</v>
+        <v>52360</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>102800</v>
+        <v>52500</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>53.59922178988327</v>
+        <v>75.42857142857143</v>
       </c>
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="5" t="n">
-        <v>92700</v>
+        <v>47300</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>70.33441208198489</v>
+        <v>94.71458773784354</v>
       </c>
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="5" t="n">
-        <v>83600</v>
+        <v>42650</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>88.8755980861244</v>
+        <v>115.9437280187573</v>
       </c>
       <c r="U10" s="7" t="inlineStr"/>
       <c r="V10" s="7" t="inlineStr"/>
@@ -1304,12 +1300,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1324,45 +1320,45 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.3%</t>
+          <t>1차 매수선까지 59.8%</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>257500</v>
+        <v>234000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>257000</v>
+        <v>230000</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>264500</v>
+        <v>242500</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>222825</v>
+        <v>182835</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>178260</v>
+        <v>146268</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>177200</v>
+        <v>146400</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>45.31602708803612</v>
+        <v>59.83606557377049</v>
       </c>
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="5" t="n">
-        <v>159600</v>
+        <v>131900</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>61.34085213032582</v>
+        <v>77.40712661106899</v>
       </c>
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="5" t="n">
-        <v>143800</v>
+        <v>118900</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>79.06815020862309</v>
+        <v>96.8040370058873</v>
       </c>
       <c r="U11" s="7" t="inlineStr"/>
       <c r="V11" s="7" t="inlineStr"/>
@@ -1378,12 +1374,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>247540</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1398,45 +1394,45 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 56.8%</t>
+          <t>1차 매수선까지 52.4%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>382500</v>
+        <v>170500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>378000</v>
+        <v>169000</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>415000</v>
+        <v>176500</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>307275</v>
+        <v>140170</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>245820</v>
+        <v>112136</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>244000</v>
+        <v>111900</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>56.76229508196722</v>
+        <v>52.36818588025023</v>
       </c>
       <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="5" t="n">
-        <v>220500</v>
+        <v>100900</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>73.46938775510205</v>
+        <v>68.97918731417245</v>
       </c>
       <c r="Q12" s="7" t="inlineStr"/>
       <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="5" t="n">
-        <v>198600</v>
+        <v>91000</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>92.59818731117825</v>
+        <v>87.36263736263736</v>
       </c>
       <c r="U12" s="7" t="inlineStr"/>
       <c r="V12" s="7" t="inlineStr"/>
@@ -1452,12 +1448,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1472,45 +1468,45 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 51.7%</t>
+          <t>1차 매수선까지 68.0%</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>65100</v>
+        <v>31550</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>65000</v>
+        <v>29200</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>69200</v>
+        <v>31750</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>54010</v>
+        <v>23625</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>43208</v>
+        <v>18900</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>42900</v>
+        <v>18780</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>51.74825174825175</v>
+        <v>67.99787007454739</v>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="5" t="n">
-        <v>38700</v>
+        <v>16920</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>68.21705426356588</v>
+        <v>86.46572104018912</v>
       </c>
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="5" t="n">
-        <v>34900</v>
+        <v>15240</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>86.53295128939828</v>
+        <v>107.0209973753281</v>
       </c>
       <c r="U13" s="7" t="inlineStr"/>
       <c r="V13" s="7" t="inlineStr"/>
@@ -1526,12 +1522,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1546,45 +1542,45 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.0%</t>
+          <t>1차 매수선까지 41.8%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>446000</v>
+        <v>68000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>443000</v>
+        <v>62800</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>457000</v>
+        <v>69700</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>381125</v>
+        <v>60695</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>304900</v>
+        <v>48556</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>303500</v>
+        <v>47950</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>46.95222405271829</v>
+        <v>41.81438998957247</v>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="5" t="n">
-        <v>274000</v>
+        <v>43250</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>62.77372262773723</v>
+        <v>57.22543352601156</v>
       </c>
       <c r="Q14" s="7" t="inlineStr"/>
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="5" t="n">
-        <v>247500</v>
+        <v>39000</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>80.20202020202019</v>
+        <v>74.35897435897436</v>
       </c>
       <c r="U14" s="7" t="inlineStr"/>
       <c r="V14" s="7" t="inlineStr"/>
@@ -1600,12 +1596,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1620,45 +1616,45 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.8%</t>
+          <t>1차 매수선까지 58.0%</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>42200</v>
+        <v>415500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>41850</v>
+        <v>409000</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>43650</v>
+        <v>422000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>38227.5</v>
+        <v>330125</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>30582</v>
+        <v>264100</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>30400</v>
+        <v>263000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>38.81578947368421</v>
+        <v>57.98479087452472</v>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="5" t="n">
-        <v>27450</v>
+        <v>237500</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>53.73406193078324</v>
+        <v>74.94736842105263</v>
       </c>
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="5" t="n">
-        <v>24800</v>
+        <v>214500</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>70.16129032258065</v>
+        <v>93.70629370629371</v>
       </c>
       <c r="U15" s="7" t="inlineStr"/>
       <c r="V15" s="7" t="inlineStr"/>
@@ -1674,12 +1670,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1694,45 +1690,45 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 54.4%</t>
+          <t>1차 매수선까지 45.3%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>201000</v>
+        <v>66200</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>200000</v>
+        <v>65500</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>210500</v>
+        <v>68000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>163185</v>
+        <v>57190</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>130548</v>
+        <v>45752</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>130200</v>
+        <v>45550</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>54.37788018433179</v>
+        <v>45.33479692645444</v>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="5" t="n">
-        <v>117300</v>
+        <v>41050</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>71.35549872122762</v>
+        <v>61.26674786845311</v>
       </c>
       <c r="Q16" s="7" t="inlineStr"/>
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="5" t="n">
-        <v>105700</v>
+        <v>37000</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>90.1608325449385</v>
+        <v>78.91891891891892</v>
       </c>
       <c r="U16" s="7" t="inlineStr"/>
       <c r="V16" s="7" t="inlineStr"/>
@@ -1748,12 +1744,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1768,45 +1764,45 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.7%</t>
+          <t>1차 매수선까지 57.0%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>241000</v>
+        <v>515000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>227500</v>
+        <v>502000</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>249500</v>
+        <v>527000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>218350</v>
+        <v>411075</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>174680</v>
+        <v>328860</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>172500</v>
+        <v>328000</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>39.71014492753623</v>
+        <v>57.01219512195122</v>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="5" t="n">
-        <v>155400</v>
+        <v>296000</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>55.08365508365508</v>
+        <v>73.98648648648648</v>
       </c>
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="5" t="n">
-        <v>140000</v>
+        <v>267000</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>72.14285714285714</v>
+        <v>92.88389513108615</v>
       </c>
       <c r="U17" s="7" t="inlineStr"/>
       <c r="V17" s="7" t="inlineStr"/>
@@ -1822,12 +1818,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1842,45 +1838,45 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.2%</t>
+          <t>1차 매수선까지 42.2%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>59300</v>
+        <v>45000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>59000</v>
+        <v>43850</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>60700</v>
+        <v>45800</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>61090</v>
+        <v>39730</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>48872</v>
+        <v>31784</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>48150</v>
+        <v>31650</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>23.15680166147456</v>
+        <v>42.18009478672986</v>
       </c>
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="5" t="n">
-        <v>43400</v>
+        <v>28550</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>36.63594470046083</v>
+        <v>57.61821366024519</v>
       </c>
       <c r="Q18" s="7" t="inlineStr"/>
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="5" t="n">
-        <v>39150</v>
+        <v>25750</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>51.46871008939975</v>
+        <v>74.75728155339806</v>
       </c>
       <c r="U18" s="7" t="inlineStr"/>
       <c r="V18" s="7" t="inlineStr"/>
@@ -1896,12 +1892,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1916,45 +1912,45 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.7%</t>
+          <t>1차 매수선까지 65.4%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>113000</v>
+        <v>42600</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>112000</v>
+        <v>37450</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>119200</v>
+        <v>44000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>85930</v>
+        <v>32307.5</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>68744</v>
+        <v>25846</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>68600</v>
+        <v>25750</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>64.72303206997084</v>
+        <v>65.4368932038835</v>
       </c>
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="5" t="n">
-        <v>61900</v>
+        <v>23250</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>82.55250403877221</v>
+        <v>83.22580645161291</v>
       </c>
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="5" t="n">
-        <v>55900</v>
+        <v>21000</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>102.1466905187835</v>
+        <v>102.8571428571428</v>
       </c>
       <c r="U19" s="7" t="inlineStr"/>
       <c r="V19" s="7" t="inlineStr"/>
@@ -1970,12 +1966,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1990,45 +1986,45 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 57.4%</t>
+          <t>1차 매수선까지 50.8%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>775000</v>
+        <v>71500</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>773000</v>
+        <v>70700</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>808000</v>
+        <v>76400</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>620500</v>
+        <v>59620</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>496400</v>
+        <v>47696</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>492500</v>
+        <v>47400</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>57.36040609137056</v>
+        <v>50.84388185654009</v>
       </c>
       <c r="M20" s="7" t="inlineStr"/>
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="5" t="n">
-        <v>444000</v>
+        <v>42750</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>74.54954954954955</v>
+        <v>67.2514619883041</v>
       </c>
       <c r="Q20" s="7" t="inlineStr"/>
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="5" t="n">
-        <v>400500</v>
+        <v>38550</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>93.50811485642946</v>
+        <v>85.473411154345</v>
       </c>
       <c r="U20" s="7" t="inlineStr"/>
       <c r="V20" s="7" t="inlineStr"/>
@@ -2044,12 +2040,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2064,45 +2060,45 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 72.5%</t>
+          <t>1차 매수선까지 30.6%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>13350</v>
+        <v>470000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>12350</v>
+        <v>463000</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>14190</v>
+        <v>479000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>9628.5</v>
+        <v>454650</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>7702.8</v>
+        <v>363720</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>7740</v>
+        <v>360000</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>72.48062015503875</v>
+        <v>30.55555555555556</v>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="5" t="n">
-        <v>6980</v>
+        <v>324500</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>91.26074498567334</v>
+        <v>44.8382126348228</v>
       </c>
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="5" t="n">
-        <v>6300</v>
+        <v>293000</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>111.9047619047619</v>
+        <v>60.40955631399317</v>
       </c>
       <c r="U21" s="7" t="inlineStr"/>
       <c r="V21" s="7" t="inlineStr"/>
@@ -2118,12 +2114,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>090710</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2138,45 +2134,45 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 85.8%</t>
+          <t>1차 매수선까지 41.3%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>6000</v>
+        <v>30300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>5750</v>
+        <v>28650</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>6580</v>
+        <v>31500</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>4050.25</v>
+        <v>27090</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>3240.2</v>
+        <v>21672</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>3230</v>
+        <v>21450</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>85.75851393188854</v>
+        <v>41.25874125874126</v>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="5" t="n">
-        <v>2915</v>
+        <v>19320</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>105.8319039451115</v>
+        <v>56.83229813664597</v>
       </c>
       <c r="Q22" s="7" t="inlineStr"/>
       <c r="R22" s="7" t="inlineStr"/>
       <c r="S22" s="5" t="n">
-        <v>2630</v>
+        <v>17400</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>128.1368821292776</v>
+        <v>74.13793103448276</v>
       </c>
       <c r="U22" s="7" t="inlineStr"/>
       <c r="V22" s="7" t="inlineStr"/>
@@ -2192,12 +2188,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2212,45 +2208,45 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.6%</t>
+          <t>1차 매수선까지 33.0%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>38800</v>
+        <v>232000</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>38450</v>
+        <v>227500</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>41450</v>
+        <v>242500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>35007.5</v>
+        <v>220400</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>28006</v>
+        <v>176320</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>28000</v>
+        <v>174500</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>38.57142857142858</v>
+        <v>32.95128939828081</v>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="5" t="n">
-        <v>25250</v>
+        <v>157200</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>53.66336633663366</v>
+        <v>47.58269720101781</v>
       </c>
       <c r="Q23" s="7" t="inlineStr"/>
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="5" t="n">
-        <v>22800</v>
+        <v>141600</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>70.17543859649122</v>
+        <v>63.84180790960452</v>
       </c>
       <c r="U23" s="7" t="inlineStr"/>
       <c r="V23" s="7" t="inlineStr"/>
@@ -2266,12 +2262,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2286,45 +2282,45 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.4%</t>
+          <t>1차 매수선까지 80.9%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>187000</v>
+        <v>143300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>178500</v>
+        <v>142000</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>202500</v>
+        <v>149000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>171036.2</v>
+        <v>98865</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>136828.96</v>
+        <v>79092</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>137100</v>
+        <v>79200</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>36.39679066374909</v>
+        <v>80.93434343434343</v>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="5" t="n">
-        <v>123500</v>
+        <v>71400</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>51.417004048583</v>
+        <v>100.7002801120448</v>
       </c>
       <c r="Q24" s="7" t="inlineStr"/>
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="5" t="n">
-        <v>111300</v>
+        <v>64400</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>68.01437556154536</v>
+        <v>122.5155279503106</v>
       </c>
       <c r="U24" s="7" t="inlineStr"/>
       <c r="V24" s="7" t="inlineStr"/>
@@ -2340,12 +2336,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2360,45 +2356,45 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 35.0%</t>
+          <t>1차 매수선까지 79.0%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>76400</v>
+        <v>970000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>76400</v>
+        <v>882000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>77900</v>
+        <v>998000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>71055</v>
+        <v>678400</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>56844</v>
+        <v>542720</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>56600</v>
+        <v>542000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>34.98233215547703</v>
+        <v>78.96678966789668</v>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="5" t="n">
-        <v>51100</v>
+        <v>488500</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>49.51076320939335</v>
+        <v>98.56704196519959</v>
       </c>
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="5" t="n">
-        <v>46050</v>
+        <v>440500</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>65.90662323561347</v>
+        <v>120.2043132803632</v>
       </c>
       <c r="U25" s="7" t="inlineStr"/>
       <c r="V25" s="7" t="inlineStr"/>
@@ -2414,108 +2410,86 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>BOUGHT_1</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>READY_SELL1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>+3% 매도선까지 5.0%</t>
+          <t>1차 매수선까지 50.6%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>20600</v>
+        <v>12800</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>20500</v>
+        <v>12730</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>21450</v>
+        <v>13290</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>25677.5</v>
+        <v>10627.5</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>20542</v>
+        <v>8502</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>20150</v>
+        <v>8500</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>2.233250620347394</v>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>21,050</t>
-        </is>
-      </c>
+        <v>50.58823529411764</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="5" t="n">
-        <v>18150</v>
+        <v>7660</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>13.49862258953168</v>
+        <v>67.10182767624021</v>
       </c>
       <c r="Q26" s="7" t="inlineStr"/>
       <c r="R26" s="7" t="inlineStr"/>
       <c r="S26" s="5" t="n">
-        <v>16350</v>
+        <v>6910</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>25.99388379204893</v>
+        <v>85.23878437047757</v>
       </c>
       <c r="U26" s="7" t="inlineStr"/>
       <c r="V26" s="7" t="inlineStr"/>
-      <c r="W26" s="5" t="n">
-        <v>21050</v>
-      </c>
-      <c r="X26" s="5" t="n">
-        <v>21681.5</v>
-      </c>
-      <c r="Y26" s="6" t="n">
-        <v>-4.98812351543943</v>
-      </c>
-      <c r="Z26" s="5" t="n">
-        <v>22102.5</v>
-      </c>
-      <c r="AA26" s="6" t="n">
-        <v>-6.797873543716775</v>
-      </c>
-      <c r="AB26" s="5" t="n">
-        <v>22523.5</v>
-      </c>
-      <c r="AC26" s="6" t="n">
-        <v>-8.539969365329544</v>
-      </c>
+      <c r="W26" s="7" t="inlineStr"/>
+      <c r="X26" s="7" t="inlineStr"/>
+      <c r="Y26" s="7" t="inlineStr"/>
+      <c r="Z26" s="7" t="inlineStr"/>
+      <c r="AA26" s="7" t="inlineStr"/>
+      <c r="AB26" s="7" t="inlineStr"/>
+      <c r="AC26" s="7" t="inlineStr"/>
       <c r="AD26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2525,50 +2499,50 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 6.7% (접근 중!)</t>
+          <t>1차 매수선까지 54.4%</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>8730</v>
+        <v>21400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>8530</v>
+        <v>19770</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>9030</v>
+        <v>22000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>10369.5</v>
+        <v>17407.5</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>8295.6</v>
+        <v>13926</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8180</v>
+        <v>13860</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>6.723716381418093</v>
+        <v>54.40115440115441</v>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="5" t="n">
-        <v>7380</v>
+        <v>12490</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>18.29268292682927</v>
+        <v>71.33706965572458</v>
       </c>
       <c r="Q27" s="7" t="inlineStr"/>
       <c r="R27" s="7" t="inlineStr"/>
       <c r="S27" s="5" t="n">
-        <v>6660</v>
+        <v>11260</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>31.08108108108108</v>
+        <v>90.05328596802842</v>
       </c>
       <c r="U27" s="7" t="inlineStr"/>
       <c r="V27" s="7" t="inlineStr"/>
@@ -2584,12 +2558,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2604,45 +2578,45 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.2%</t>
+          <t>1차 매수선까지 46.1%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>15820</v>
+        <v>124500</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>15810</v>
+        <v>121200</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>16500</v>
+        <v>126300</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>17157.5</v>
+        <v>107215</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>13726</v>
+        <v>85772</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>13620</v>
+        <v>85200</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.15271659324523</v>
+        <v>46.12676056338028</v>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="5" t="n">
-        <v>12270</v>
+        <v>76800</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>28.93235533822331</v>
+        <v>62.109375</v>
       </c>
       <c r="Q28" s="7" t="inlineStr"/>
       <c r="R28" s="7" t="inlineStr"/>
       <c r="S28" s="5" t="n">
-        <v>11060</v>
+        <v>69300</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>43.03797468354431</v>
+        <v>79.65367965367966</v>
       </c>
       <c r="U28" s="7" t="inlineStr"/>
       <c r="V28" s="7" t="inlineStr"/>
@@ -2658,12 +2632,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2678,45 +2652,45 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.7%</t>
+          <t>1차 매수선까지 37.3%</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>332000</v>
+        <v>395500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>330000</v>
+        <v>390500</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>342000</v>
+        <v>413000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>324625</v>
+        <v>364250</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>259700</v>
+        <v>291400</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>258000</v>
+        <v>288000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>28.68217054263566</v>
+        <v>37.32638888888889</v>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="5" t="n">
-        <v>233000</v>
+        <v>260000</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>42.48927038626609</v>
+        <v>52.11538461538462</v>
       </c>
       <c r="Q29" s="7" t="inlineStr"/>
       <c r="R29" s="7" t="inlineStr"/>
       <c r="S29" s="5" t="n">
-        <v>210500</v>
+        <v>234500</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>57.71971496437055</v>
+        <v>68.65671641791045</v>
       </c>
       <c r="U29" s="7" t="inlineStr"/>
       <c r="V29" s="7" t="inlineStr"/>
@@ -2732,12 +2706,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2752,45 +2726,45 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.2%</t>
+          <t>1차 매수선까지 38.9%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>452500</v>
+        <v>309000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>448000</v>
+        <v>305250</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>461000</v>
+        <v>314500</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>456875</v>
+        <v>280500</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>365500</v>
+        <v>224400</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>361500</v>
+        <v>222500</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>25.17289073305671</v>
+        <v>38.87640449438202</v>
       </c>
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="5" t="n">
-        <v>326000</v>
+        <v>201000</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>38.80368098159509</v>
+        <v>53.73134328358209</v>
       </c>
       <c r="Q30" s="7" t="inlineStr"/>
       <c r="R30" s="7" t="inlineStr"/>
       <c r="S30" s="5" t="n">
-        <v>294000</v>
+        <v>181000</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>53.91156462585034</v>
+        <v>70.71823204419888</v>
       </c>
       <c r="U30" s="7" t="inlineStr"/>
       <c r="V30" s="7" t="inlineStr"/>
@@ -2806,12 +2780,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2826,45 +2800,45 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.7%</t>
+          <t>1차 매수선까지 67.9%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>172900</v>
+        <v>6180</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>172600</v>
+        <v>5930</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>178300</v>
+        <v>6240</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>174930</v>
+        <v>4574.75</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>139944</v>
+        <v>3659.8</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>138700</v>
+        <v>3680</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>24.65753424657534</v>
+        <v>67.93478260869566</v>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="5" t="n">
-        <v>125000</v>
+        <v>3320</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>38.32</v>
+        <v>86.14457831325302</v>
       </c>
       <c r="Q31" s="7" t="inlineStr"/>
       <c r="R31" s="7" t="inlineStr"/>
       <c r="S31" s="5" t="n">
-        <v>112600</v>
+        <v>2995</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>53.55239786856127</v>
+        <v>106.3439065108514</v>
       </c>
       <c r="U31" s="7" t="inlineStr"/>
       <c r="V31" s="7" t="inlineStr"/>
@@ -2880,12 +2854,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2900,45 +2874,45 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.5%</t>
+          <t>1차 매수선까지 32.8%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>169700</v>
+        <v>39100</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>168000</v>
+        <v>38050</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>173300</v>
+        <v>40150</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>186035</v>
+        <v>36915</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>148828</v>
+        <v>29532</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>148200</v>
+        <v>29450</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>14.50742240215924</v>
+        <v>32.76740237691001</v>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="5" t="n">
-        <v>133500</v>
+        <v>26600</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>27.11610486891386</v>
+        <v>46.99248120300752</v>
       </c>
       <c r="Q32" s="7" t="inlineStr"/>
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="5" t="n">
-        <v>120300</v>
+        <v>24000</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>41.06400665004156</v>
+        <v>62.91666666666666</v>
       </c>
       <c r="U32" s="7" t="inlineStr"/>
       <c r="V32" s="7" t="inlineStr"/>
@@ -2954,12 +2928,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2974,45 +2948,45 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.3%</t>
+          <t>1차 매수선까지 42.2%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>200500</v>
+        <v>206500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>200000</v>
+        <v>192300</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>206000</v>
+        <v>212000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>216440</v>
+        <v>181263.65</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>173152</v>
+        <v>145010.92</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>171000</v>
+        <v>145200</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>17.25146198830409</v>
+        <v>42.21763085399449</v>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="7" t="inlineStr"/>
       <c r="O33" s="5" t="n">
-        <v>154000</v>
+        <v>130800</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>30.1948051948052</v>
+        <v>57.87461773700306</v>
       </c>
       <c r="Q33" s="7" t="inlineStr"/>
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="5" t="n">
-        <v>138700</v>
+        <v>117900</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>44.55659697188176</v>
+        <v>75.14843087362172</v>
       </c>
       <c r="U33" s="7" t="inlineStr"/>
       <c r="V33" s="7" t="inlineStr"/>
@@ -3028,12 +3002,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3048,45 +3022,45 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.6%</t>
+          <t>1차 매수선까지 36.6%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>8990</v>
+        <v>79900</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>8750</v>
+        <v>77400</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>9250</v>
+        <v>79900</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>9797.5</v>
+        <v>73550</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>7838</v>
+        <v>58840</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>7710</v>
+        <v>58500</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>16.6018158236057</v>
+        <v>36.58119658119658</v>
       </c>
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="5" t="n">
-        <v>6950</v>
+        <v>52800</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>29.35251798561151</v>
+        <v>51.32575757575758</v>
       </c>
       <c r="Q34" s="7" t="inlineStr"/>
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="5" t="n">
-        <v>6270</v>
+        <v>47600</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>43.38118022328549</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="U34" s="7" t="inlineStr"/>
       <c r="V34" s="7" t="inlineStr"/>
@@ -3102,12 +3076,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3122,45 +3096,45 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 53.8%</t>
+          <t>1차 매수선까지 18.5%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>67600</v>
+        <v>23150</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>66000</v>
+        <v>22950</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>70700</v>
+        <v>24000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>55047.5</v>
+        <v>24715</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>44038</v>
+        <v>19772</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>43950</v>
+        <v>19530</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>53.81114903299203</v>
+        <v>18.53558627752176</v>
       </c>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="5" t="n">
-        <v>39650</v>
+        <v>17590</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>70.49180327868852</v>
+        <v>31.60886867538374</v>
       </c>
       <c r="Q35" s="7" t="inlineStr"/>
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="5" t="n">
-        <v>35750</v>
+        <v>15850</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>89.09090909090909</v>
+        <v>46.05678233438486</v>
       </c>
       <c r="U35" s="7" t="inlineStr"/>
       <c r="V35" s="7" t="inlineStr"/>
@@ -3176,12 +3150,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3196,45 +3170,45 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.5%</t>
+          <t>1차 매수선까지 20.1%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>101400</v>
+        <v>9500</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>99600</v>
+        <v>8990</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>102500</v>
+        <v>9800</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>103970</v>
+        <v>9990.5</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>83176</v>
+        <v>7992.400000000001</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>82100</v>
+        <v>7910</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>23.50791717417783</v>
+        <v>20.10113780025284</v>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr"/>
       <c r="O36" s="5" t="n">
-        <v>74000</v>
+        <v>7130</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>37.02702702702702</v>
+        <v>33.2398316970547</v>
       </c>
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="5" t="n">
-        <v>66700</v>
+        <v>6430</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>52.023988005997</v>
+        <v>47.74494556765163</v>
       </c>
       <c r="U36" s="7" t="inlineStr"/>
       <c r="V36" s="7" t="inlineStr"/>
@@ -3250,12 +3224,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3270,45 +3244,45 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.8%</t>
+          <t>1차 매수선까지 22.7%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>179700</v>
+        <v>16870</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>171200</v>
+        <v>16420</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>183500</v>
+        <v>17320</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>198050</v>
+        <v>17430.5</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>158440</v>
+        <v>13944.4</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>155200</v>
+        <v>13750</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>15.7860824742268</v>
+        <v>22.69090909090909</v>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr"/>
       <c r="O37" s="5" t="n">
-        <v>139800</v>
+        <v>12390</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>28.54077253218884</v>
+        <v>36.15819209039548</v>
       </c>
       <c r="Q37" s="7" t="inlineStr"/>
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="5" t="n">
-        <v>126000</v>
+        <v>11170</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>42.61904761904762</v>
+        <v>51.02954341987467</v>
       </c>
       <c r="U37" s="7" t="inlineStr"/>
       <c r="V37" s="7" t="inlineStr"/>
@@ -3324,12 +3298,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3344,45 +3318,45 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.2%</t>
+          <t>1차 매수선까지 30.9%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>435000</v>
+        <v>345000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>426000</v>
+        <v>338000</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>446500</v>
+        <v>347500</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>440500</v>
+        <v>331750</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>352400</v>
+        <v>265400</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>347500</v>
+        <v>263500</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>25.17985611510791</v>
+        <v>30.92979127134725</v>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="7" t="inlineStr"/>
       <c r="O38" s="5" t="n">
-        <v>313500</v>
+        <v>238000</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>38.75598086124402</v>
+        <v>44.95798319327731</v>
       </c>
       <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="5" t="n">
-        <v>283000</v>
+        <v>215000</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>53.71024734982333</v>
+        <v>60.46511627906976</v>
       </c>
       <c r="U38" s="7" t="inlineStr"/>
       <c r="V38" s="7" t="inlineStr"/>
@@ -3398,12 +3372,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3418,45 +3392,45 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.7%</t>
+          <t>1차 매수선까지 29.2%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>22350</v>
+        <v>179500</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>21350</v>
+        <v>176100</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>23750</v>
+        <v>181400</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>23672.5</v>
+        <v>175475</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>18938</v>
+        <v>140380</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>18670</v>
+        <v>138900</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>19.71076593465452</v>
+        <v>29.22966162706984</v>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr"/>
       <c r="O39" s="5" t="n">
-        <v>16820</v>
+        <v>125200</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>32.87752675386444</v>
+        <v>43.37060702875399</v>
       </c>
       <c r="Q39" s="7" t="inlineStr"/>
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="5" t="n">
-        <v>15150</v>
+        <v>112800</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>47.52475247524752</v>
+        <v>59.13120567375887</v>
       </c>
       <c r="U39" s="7" t="inlineStr"/>
       <c r="V39" s="7" t="inlineStr"/>
@@ -3472,12 +3446,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3492,45 +3466,45 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.7%</t>
+          <t>1차 매수선까지 36.0%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>28350</v>
+        <v>198600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>26600</v>
+        <v>181700</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>29500</v>
+        <v>214000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>26877.5</v>
+        <v>184520</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>21502</v>
+        <v>147616</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>21200</v>
+        <v>146000</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>33.72641509433962</v>
+        <v>36.02739726027397</v>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="7" t="inlineStr"/>
       <c r="O40" s="5" t="n">
-        <v>19090</v>
+        <v>131500</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>48.50707176532216</v>
+        <v>51.02661596958175</v>
       </c>
       <c r="Q40" s="7" t="inlineStr"/>
       <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="5" t="n">
-        <v>17200</v>
+        <v>118500</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>64.82558139534885</v>
+        <v>67.59493670886076</v>
       </c>
       <c r="U40" s="7" t="inlineStr"/>
       <c r="V40" s="7" t="inlineStr"/>
@@ -3546,12 +3520,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3566,45 +3540,45 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.8%</t>
+          <t>1차 매수선까지 33.7%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>22500</v>
+        <v>221500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>22500</v>
+        <v>214500</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>24075</v>
+        <v>224500</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>21322</v>
+        <v>210215</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>17057.6</v>
+        <v>168172</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>16820</v>
+        <v>165700</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>33.769322235434</v>
+        <v>33.67531683765842</v>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr"/>
       <c r="O41" s="5" t="n">
-        <v>15150</v>
+        <v>149300</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>48.51485148514851</v>
+        <v>48.35900870730074</v>
       </c>
       <c r="Q41" s="7" t="inlineStr"/>
       <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="5" t="n">
-        <v>13650</v>
+        <v>134500</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>64.83516483516483</v>
+        <v>64.68401486988847</v>
       </c>
       <c r="U41" s="7" t="inlineStr"/>
       <c r="V41" s="7" t="inlineStr"/>
@@ -3620,12 +3594,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3640,45 +3614,45 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.9%</t>
+          <t>1차 매수선까지 18.8%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>51600</v>
+        <v>8860</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>48800</v>
+        <v>8810</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>51800</v>
+        <v>9190</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>52250</v>
+        <v>9466</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>41800</v>
+        <v>7572.8</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>41300</v>
+        <v>7460</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>24.93946731234867</v>
+        <v>18.76675603217158</v>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr"/>
       <c r="O42" s="5" t="n">
-        <v>37250</v>
+        <v>6730</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>38.52348993288591</v>
+        <v>31.64933135215453</v>
       </c>
       <c r="Q42" s="7" t="inlineStr"/>
       <c r="R42" s="7" t="inlineStr"/>
       <c r="S42" s="5" t="n">
-        <v>33600</v>
+        <v>6070</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>53.57142857142857</v>
+        <v>45.96375617792422</v>
       </c>
       <c r="U42" s="7" t="inlineStr"/>
       <c r="V42" s="7" t="inlineStr"/>
@@ -3694,12 +3668,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3714,45 +3688,45 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.5%</t>
+          <t>1차 매수선까지 72.9%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>48600</v>
+        <v>85400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>47800</v>
+        <v>83900</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>49800</v>
+        <v>88300</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>45787.5</v>
+        <v>61660</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>36630</v>
+        <v>49328</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>36400</v>
+        <v>49400</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>33.51648351648351</v>
+        <v>72.8744939271255</v>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr"/>
       <c r="O43" s="5" t="n">
-        <v>32850</v>
+        <v>44550</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>47.94520547945205</v>
+        <v>91.69472502805837</v>
       </c>
       <c r="Q43" s="7" t="inlineStr"/>
       <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="5" t="n">
-        <v>29650</v>
+        <v>40150</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>63.91231028667791</v>
+        <v>112.7023661270237</v>
       </c>
       <c r="U43" s="7" t="inlineStr"/>
       <c r="V43" s="7" t="inlineStr"/>
@@ -3768,12 +3742,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3788,45 +3762,45 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.0%</t>
+          <t>1차 매수선까지 26.0%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>22750</v>
+        <v>102600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>22500</v>
+        <v>100600</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>23600</v>
+        <v>105500</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>24685</v>
+        <v>103060</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>19748</v>
+        <v>82448</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>19440</v>
+        <v>81400</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>17.02674897119341</v>
+        <v>26.04422604422604</v>
       </c>
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="7" t="inlineStr"/>
       <c r="O44" s="5" t="n">
-        <v>17510</v>
+        <v>73400</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>29.92575671045118</v>
+        <v>39.78201634877384</v>
       </c>
       <c r="Q44" s="7" t="inlineStr"/>
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="5" t="n">
-        <v>15770</v>
+        <v>66200</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>44.26125554850983</v>
+        <v>54.98489425981873</v>
       </c>
       <c r="U44" s="7" t="inlineStr"/>
       <c r="V44" s="7" t="inlineStr"/>
@@ -3842,12 +3816,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3862,45 +3836,45 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 35.9%</t>
+          <t>1차 매수선까지 18.4%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>449000</v>
+        <v>174000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>446000</v>
+        <v>172700</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>460000</v>
+        <v>182900</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>417000</v>
+        <v>186720</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>333600</v>
+        <v>149376</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>330500</v>
+        <v>146900</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>35.85476550680787</v>
+        <v>18.44792375765827</v>
       </c>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr"/>
       <c r="O45" s="5" t="n">
-        <v>298000</v>
+        <v>132400</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>50.67114093959731</v>
+        <v>31.41993957703927</v>
       </c>
       <c r="Q45" s="7" t="inlineStr"/>
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="5" t="n">
-        <v>269000</v>
+        <v>119300</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>66.91449814126395</v>
+        <v>45.85079631181894</v>
       </c>
       <c r="U45" s="7" t="inlineStr"/>
       <c r="V45" s="7" t="inlineStr"/>
@@ -3916,12 +3890,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3936,45 +3910,45 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.4%</t>
+          <t>1차 매수선까지 26.4%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>229500</v>
+        <v>435500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>225500</v>
+        <v>431000</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>235000</v>
+        <v>442000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>204510</v>
+        <v>435200</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>163608</v>
+        <v>348160</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>162300</v>
+        <v>344500</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>41.40480591497228</v>
+        <v>26.41509433962264</v>
       </c>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr"/>
       <c r="O46" s="5" t="n">
-        <v>146200</v>
+        <v>311000</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>56.97674418604651</v>
+        <v>40.03215434083602</v>
       </c>
       <c r="Q46" s="7" t="inlineStr"/>
       <c r="R46" s="7" t="inlineStr"/>
       <c r="S46" s="5" t="n">
-        <v>131700</v>
+        <v>280500</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>74.25968109339408</v>
+        <v>55.2584670231729</v>
       </c>
       <c r="U46" s="7" t="inlineStr"/>
       <c r="V46" s="7" t="inlineStr"/>
@@ -3990,12 +3964,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4010,45 +3984,45 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.3%</t>
+          <t>1차 매수선까지 21.5%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>23900</v>
+        <v>22000</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>23450</v>
+        <v>21300</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>24500</v>
+        <v>22450</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>22112.5</v>
+        <v>23000</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>17690</v>
+        <v>18400</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>17540</v>
+        <v>18110</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>36.25997719498289</v>
+        <v>21.47984538928769</v>
       </c>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
       <c r="O47" s="5" t="n">
-        <v>15800</v>
+        <v>16310</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>51.26582278481012</v>
+        <v>34.88657265481299</v>
       </c>
       <c r="Q47" s="7" t="inlineStr"/>
       <c r="R47" s="7" t="inlineStr"/>
       <c r="S47" s="5" t="n">
-        <v>14230</v>
+        <v>14690</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>67.9550245959241</v>
+        <v>49.76174268209667</v>
       </c>
       <c r="U47" s="7" t="inlineStr"/>
       <c r="V47" s="7" t="inlineStr"/>
@@ -4064,12 +4038,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4084,45 +4058,45 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 54.5%</t>
+          <t>1차 매수선까지 33.3%</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1838000</v>
+        <v>22800</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1682000</v>
+        <v>22050</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>1863000</v>
+        <v>23600</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>1497700</v>
+        <v>21542</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1198160</v>
+        <v>17233.6</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1190000</v>
+        <v>17100</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>54.45378151260504</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="7" t="inlineStr"/>
       <c r="O48" s="5" t="n">
-        <v>1072000</v>
+        <v>15400</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>71.45522388059702</v>
+        <v>48.05194805194805</v>
       </c>
       <c r="Q48" s="7" t="inlineStr"/>
       <c r="R48" s="7" t="inlineStr"/>
       <c r="S48" s="5" t="n">
-        <v>966000</v>
+        <v>13870</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>90.26915113871635</v>
+        <v>64.38356164383562</v>
       </c>
       <c r="U48" s="7" t="inlineStr"/>
       <c r="V48" s="7" t="inlineStr"/>
@@ -4138,12 +4112,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4158,45 +4132,45 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.3%</t>
+          <t>1차 매수선까지 29.4%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>465500</v>
+        <v>52100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>448500</v>
+        <v>52000</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>474000</v>
+        <v>54300</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>478275</v>
+        <v>51260</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>382620</v>
+        <v>41008</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>377500</v>
+        <v>40250</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>23.3112582781457</v>
+        <v>29.44099378881987</v>
       </c>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
       <c r="O49" s="5" t="n">
-        <v>340500</v>
+        <v>36300</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>36.71071953010279</v>
+        <v>43.52617079889807</v>
       </c>
       <c r="Q49" s="7" t="inlineStr"/>
       <c r="R49" s="7" t="inlineStr"/>
       <c r="S49" s="5" t="n">
-        <v>307000</v>
+        <v>32750</v>
       </c>
       <c r="T49" s="6" t="n">
-        <v>51.62866449511401</v>
+        <v>59.08396946564886</v>
       </c>
       <c r="U49" s="7" t="inlineStr"/>
       <c r="V49" s="7" t="inlineStr"/>
@@ -4212,12 +4186,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4232,45 +4206,45 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.3%</t>
+          <t>1차 매수선까지 31.6%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>42800</v>
+        <v>49150</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>42600</v>
+        <v>47500</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>44250</v>
+        <v>49850</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>41427.5</v>
+        <v>47002.5</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>33142</v>
+        <v>37602</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>32850</v>
+        <v>37350</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>30.28919330289193</v>
+        <v>31.59303882195448</v>
       </c>
       <c r="M50" s="7" t="inlineStr"/>
       <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="5" t="n">
-        <v>29650</v>
+        <v>33700</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>44.35075885328836</v>
+        <v>45.84569732937685</v>
       </c>
       <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="7" t="inlineStr"/>
       <c r="S50" s="5" t="n">
-        <v>26750</v>
+        <v>30400</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>60</v>
+        <v>61.67763157894737</v>
       </c>
       <c r="U50" s="7" t="inlineStr"/>
       <c r="V50" s="7" t="inlineStr"/>
@@ -4286,12 +4260,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4306,45 +4280,45 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.5%</t>
+          <t>1차 매수선까지 20.6%</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17230</v>
+        <v>22850</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>17170</v>
+        <v>22550</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>18070</v>
+        <v>23375</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>17851</v>
+        <v>24000</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>14280.8</v>
+        <v>19200</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>14070</v>
+        <v>18940</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>22.4591329068941</v>
+        <v>20.6441393875396</v>
       </c>
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="7" t="inlineStr"/>
       <c r="O51" s="5" t="n">
-        <v>12680</v>
+        <v>17060</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>35.88328075709779</v>
+        <v>33.9390386869871</v>
       </c>
       <c r="Q51" s="7" t="inlineStr"/>
       <c r="R51" s="7" t="inlineStr"/>
       <c r="S51" s="5" t="n">
-        <v>11430</v>
+        <v>15370</v>
       </c>
       <c r="T51" s="6" t="n">
-        <v>50.74365704286964</v>
+        <v>48.66623292127521</v>
       </c>
       <c r="U51" s="7" t="inlineStr"/>
       <c r="V51" s="7" t="inlineStr"/>
@@ -4360,12 +4334,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4380,45 +4354,45 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.4%</t>
+          <t>1차 매수선까지 40.2%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>85300</v>
+        <v>478000</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>84100</v>
+        <v>445500</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>87100</v>
+        <v>481500</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>93300</v>
+        <v>429300</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>74640</v>
+        <v>343440</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>73300</v>
+        <v>341000</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>16.37107776261938</v>
+        <v>40.17595307917888</v>
       </c>
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="5" t="n">
-        <v>66100</v>
+        <v>307500</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>29.04689863842663</v>
+        <v>55.44715447154471</v>
       </c>
       <c r="Q52" s="7" t="inlineStr"/>
       <c r="R52" s="7" t="inlineStr"/>
       <c r="S52" s="5" t="n">
-        <v>59600</v>
+        <v>277500</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>43.12080536912752</v>
+        <v>72.25225225225225</v>
       </c>
       <c r="U52" s="7" t="inlineStr"/>
       <c r="V52" s="7" t="inlineStr"/>
@@ -4434,12 +4408,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4454,45 +4428,45 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.9%</t>
+          <t>1차 매수선까지 46.1%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>14150</v>
+        <v>248000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>13840</v>
+        <v>230000</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>14330</v>
+        <v>249500</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>14239.5</v>
+        <v>213740</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>11391.6</v>
+        <v>170992</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>11330</v>
+        <v>169800</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>24.88967343336276</v>
+        <v>46.05418138987044</v>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="5" t="n">
-        <v>10210</v>
+        <v>153000</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>38.5896180215475</v>
+        <v>62.09150326797386</v>
       </c>
       <c r="Q53" s="7" t="inlineStr"/>
       <c r="R53" s="7" t="inlineStr"/>
       <c r="S53" s="5" t="n">
-        <v>9200</v>
+        <v>137800</v>
       </c>
       <c r="T53" s="6" t="n">
-        <v>53.80434782608695</v>
+        <v>79.97097242380261</v>
       </c>
       <c r="U53" s="7" t="inlineStr"/>
       <c r="V53" s="7" t="inlineStr"/>
@@ -4508,12 +4482,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4528,45 +4502,45 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.8%</t>
+          <t>1차 매수선까지 56.7%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>77400</v>
+        <v>2007000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>77100</v>
+        <v>1915000</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>79100</v>
+        <v>2015000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>78920</v>
+        <v>1604450</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>63136</v>
+        <v>1283560</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>62500</v>
+        <v>1281000</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>23.84</v>
+        <v>56.67447306791568</v>
       </c>
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="7" t="inlineStr"/>
       <c r="O54" s="5" t="n">
-        <v>56400</v>
+        <v>1154000</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>37.23404255319149</v>
+        <v>73.91681109185441</v>
       </c>
       <c r="Q54" s="7" t="inlineStr"/>
       <c r="R54" s="7" t="inlineStr"/>
       <c r="S54" s="5" t="n">
-        <v>50900</v>
+        <v>1040000</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>52.06286836935167</v>
+        <v>92.98076923076923</v>
       </c>
       <c r="U54" s="7" t="inlineStr"/>
       <c r="V54" s="7" t="inlineStr"/>
@@ -4582,12 +4556,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4602,45 +4576,45 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.2%</t>
+          <t>1차 매수선까지 34.7%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>244000</v>
+        <v>510000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>235000</v>
+        <v>500000</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>245000</v>
+        <v>519000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>239475</v>
+        <v>478450</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>191580</v>
+        <v>382760</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>190300</v>
+        <v>378500</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>28.21860220704152</v>
+        <v>34.74240422721268</v>
       </c>
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="7" t="inlineStr"/>
       <c r="O55" s="5" t="n">
-        <v>171400</v>
+        <v>341500</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>42.35705950991832</v>
+        <v>49.34114202049781</v>
       </c>
       <c r="Q55" s="7" t="inlineStr"/>
       <c r="R55" s="7" t="inlineStr"/>
       <c r="S55" s="5" t="n">
-        <v>154400</v>
+        <v>308000</v>
       </c>
       <c r="T55" s="6" t="n">
-        <v>58.03108808290155</v>
+        <v>65.58441558441559</v>
       </c>
       <c r="U55" s="7" t="inlineStr"/>
       <c r="V55" s="7" t="inlineStr"/>
@@ -4656,12 +4630,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4676,45 +4650,45 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.3%</t>
+          <t>1차 매수선까지 31.7%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>106200</v>
+        <v>43650</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>106000</v>
+        <v>42800</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>109300</v>
+        <v>45000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>104995</v>
+        <v>41857.5</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>83996</v>
+        <v>33486</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>82800</v>
+        <v>33150</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>28.26086956521739</v>
+        <v>31.67420814479638</v>
       </c>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="5" t="n">
-        <v>74700</v>
+        <v>29900</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>42.16867469879519</v>
+        <v>45.9866220735786</v>
       </c>
       <c r="Q56" s="7" t="inlineStr"/>
       <c r="R56" s="7" t="inlineStr"/>
       <c r="S56" s="5" t="n">
-        <v>67400</v>
+        <v>27000</v>
       </c>
       <c r="T56" s="6" t="n">
-        <v>57.56676557863501</v>
+        <v>61.66666666666667</v>
       </c>
       <c r="U56" s="7" t="inlineStr"/>
       <c r="V56" s="7" t="inlineStr"/>
@@ -4730,12 +4704,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4750,45 +4724,45 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.9%</t>
+          <t>1차 매수선까지 22.0%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>1046000</v>
+        <v>16660</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>996000</v>
+        <v>16410</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>1063000</v>
+        <v>17000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>1016650</v>
+        <v>17338.5</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>813320</v>
+        <v>13870.8</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>805000</v>
+        <v>13660</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>29.93788819875776</v>
+        <v>21.96193265007321</v>
       </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="5" t="n">
-        <v>726000</v>
+        <v>12310</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>44.0771349862259</v>
+        <v>35.33712428919578</v>
       </c>
       <c r="Q57" s="7" t="inlineStr"/>
       <c r="R57" s="7" t="inlineStr"/>
       <c r="S57" s="5" t="n">
-        <v>655000</v>
+        <v>11090</v>
       </c>
       <c r="T57" s="6" t="n">
-        <v>59.69465648854961</v>
+        <v>50.22542831379621</v>
       </c>
       <c r="U57" s="7" t="inlineStr"/>
       <c r="V57" s="7" t="inlineStr"/>
@@ -4804,12 +4778,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4824,45 +4798,45 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.6%</t>
+          <t>1차 매수선까지 30.4%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>55900</v>
+        <v>93600</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>54400</v>
+        <v>91800</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>57200</v>
+        <v>96000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>56775</v>
+        <v>90715</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>45420</v>
+        <v>72572</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>44850</v>
+        <v>71800</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>24.63768115942029</v>
+        <v>30.36211699164346</v>
       </c>
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="7" t="inlineStr"/>
       <c r="O58" s="5" t="n">
-        <v>40450</v>
+        <v>64800</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>38.19530284301607</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="Q58" s="7" t="inlineStr"/>
       <c r="R58" s="7" t="inlineStr"/>
       <c r="S58" s="5" t="n">
-        <v>36500</v>
+        <v>58500</v>
       </c>
       <c r="T58" s="6" t="n">
-        <v>53.15068493150685</v>
+        <v>60</v>
       </c>
       <c r="U58" s="7" t="inlineStr"/>
       <c r="V58" s="7" t="inlineStr"/>
@@ -4878,12 +4852,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4898,45 +4872,45 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.5%</t>
+          <t>1차 매수선까지 27.5%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>30600</v>
+        <v>14560</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>29650</v>
+        <v>14250</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>30650</v>
+        <v>14790</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>29172.5</v>
+        <v>14409.5</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>23338</v>
+        <v>11527.6</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>23100</v>
+        <v>11420</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>32.46753246753246</v>
+        <v>27.49562171628722</v>
       </c>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="5" t="n">
-        <v>20850</v>
+        <v>10290</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>46.76258992805755</v>
+        <v>41.49659863945578</v>
       </c>
       <c r="Q59" s="7" t="inlineStr"/>
       <c r="R59" s="7" t="inlineStr"/>
       <c r="S59" s="5" t="n">
-        <v>18780</v>
+        <v>9280</v>
       </c>
       <c r="T59" s="6" t="n">
-        <v>62.93929712460064</v>
+        <v>56.89655172413794</v>
       </c>
       <c r="U59" s="7" t="inlineStr"/>
       <c r="V59" s="7" t="inlineStr"/>
@@ -4952,12 +4926,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4972,45 +4946,45 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.5%</t>
+          <t>1차 매수선까지 25.2%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>221500</v>
+        <v>77600</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>206500</v>
+        <v>76900</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>223500</v>
+        <v>79300</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>203085</v>
+        <v>78365</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>162468</v>
+        <v>62692</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>161100</v>
+        <v>62000</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>37.49224084419615</v>
+        <v>25.16129032258064</v>
       </c>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
       <c r="O60" s="5" t="n">
-        <v>145100</v>
+        <v>55900</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>52.65334252239835</v>
+        <v>38.81932021466905</v>
       </c>
       <c r="Q60" s="7" t="inlineStr"/>
       <c r="R60" s="7" t="inlineStr"/>
       <c r="S60" s="5" t="n">
-        <v>130700</v>
+        <v>50500</v>
       </c>
       <c r="T60" s="6" t="n">
-        <v>69.47207345065034</v>
+        <v>53.66336633663366</v>
       </c>
       <c r="U60" s="7" t="inlineStr"/>
       <c r="V60" s="7" t="inlineStr"/>
@@ -5026,12 +5000,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5046,45 +5020,45 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.9%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>51700</v>
+        <v>240000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>51200</v>
+        <v>237000</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>52400</v>
+        <v>247500</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>54245</v>
+        <v>243650</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>43396</v>
+        <v>194920</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>42750</v>
+        <v>193700</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>20.93567251461988</v>
+        <v>23.902942694889</v>
       </c>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
       <c r="O61" s="5" t="n">
-        <v>38550</v>
+        <v>174500</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>34.11154345006485</v>
+        <v>37.53581661891118</v>
       </c>
       <c r="Q61" s="7" t="inlineStr"/>
       <c r="R61" s="7" t="inlineStr"/>
       <c r="S61" s="5" t="n">
-        <v>34750</v>
+        <v>157200</v>
       </c>
       <c r="T61" s="6" t="n">
-        <v>48.77697841726619</v>
+        <v>52.67175572519084</v>
       </c>
       <c r="U61" s="7" t="inlineStr"/>
       <c r="V61" s="7" t="inlineStr"/>
@@ -5100,12 +5074,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5120,45 +5094,45 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.7%</t>
+          <t>1차 매수선까지 41.3%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>17020</v>
+        <v>118400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>15400</v>
+        <v>113500</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>17270</v>
+        <v>118400</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>15447.5</v>
+        <v>105765</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>12358</v>
+        <v>84612</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>12180</v>
+        <v>83800</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>39.73727422003284</v>
+        <v>41.28878281622912</v>
       </c>
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr"/>
       <c r="O62" s="5" t="n">
-        <v>10980</v>
+        <v>75600</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>55.00910746812387</v>
+        <v>56.61375661375661</v>
       </c>
       <c r="Q62" s="7" t="inlineStr"/>
       <c r="R62" s="7" t="inlineStr"/>
       <c r="S62" s="5" t="n">
-        <v>9900</v>
+        <v>68200</v>
       </c>
       <c r="T62" s="6" t="n">
-        <v>71.91919191919192</v>
+        <v>73.60703812316716</v>
       </c>
       <c r="U62" s="7" t="inlineStr"/>
       <c r="V62" s="7" t="inlineStr"/>
@@ -5174,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5194,45 +5168,45 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 25.1%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>28750</v>
+        <v>1003000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>28700</v>
+        <v>980000</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>29450</v>
+        <v>1018000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>29927.5</v>
+        <v>1014650</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>23942</v>
+        <v>811720</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>23650</v>
+        <v>802000</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>21.56448202959831</v>
+        <v>25.06234413965087</v>
       </c>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="7" t="inlineStr"/>
       <c r="O63" s="5" t="n">
-        <v>21350</v>
+        <v>723000</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>34.66042154566745</v>
+        <v>38.72752420470263</v>
       </c>
       <c r="Q63" s="7" t="inlineStr"/>
       <c r="R63" s="7" t="inlineStr"/>
       <c r="S63" s="5" t="n">
-        <v>19230</v>
+        <v>652000</v>
       </c>
       <c r="T63" s="6" t="n">
-        <v>49.50598023920957</v>
+        <v>53.83435582822086</v>
       </c>
       <c r="U63" s="7" t="inlineStr"/>
       <c r="V63" s="7" t="inlineStr"/>
@@ -5248,12 +5222,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5268,45 +5242,45 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.0%</t>
+          <t>1차 매수선까지 26.9%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>2720</v>
+        <v>56300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>2680</v>
+        <v>54300</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>2870</v>
+        <v>56600</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>2585</v>
+        <v>56170</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>2068</v>
+        <v>44936</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>2045</v>
+        <v>44350</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>33.00733496332519</v>
+        <v>26.94475760992108</v>
       </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="5" t="n">
-        <v>1842</v>
+        <v>40000</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>47.66558089033659</v>
+        <v>40.75</v>
       </c>
       <c r="Q64" s="7" t="inlineStr"/>
       <c r="R64" s="7" t="inlineStr"/>
       <c r="S64" s="5" t="n">
-        <v>1659</v>
+        <v>36050</v>
       </c>
       <c r="T64" s="6" t="n">
-        <v>63.95418927064497</v>
+        <v>56.17198335644937</v>
       </c>
       <c r="U64" s="7" t="inlineStr"/>
       <c r="V64" s="7" t="inlineStr"/>
@@ -5322,12 +5296,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5342,45 +5316,45 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 12.0%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>6510</v>
+        <v>30900</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>6490</v>
+        <v>30550</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>6710</v>
+        <v>32600</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>7395.5</v>
+        <v>29615</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>5916.400000000001</v>
+        <v>23692</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>5810</v>
+        <v>23500</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>12.04819277108434</v>
+        <v>31.48936170212766</v>
       </c>
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="7" t="inlineStr"/>
       <c r="O65" s="5" t="n">
-        <v>5240</v>
+        <v>21200</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>24.23664122137404</v>
+        <v>45.75471698113208</v>
       </c>
       <c r="Q65" s="7" t="inlineStr"/>
       <c r="R65" s="7" t="inlineStr"/>
       <c r="S65" s="5" t="n">
-        <v>4725</v>
+        <v>19090</v>
       </c>
       <c r="T65" s="6" t="n">
-        <v>37.77777777777778</v>
+        <v>61.86485070717653</v>
       </c>
       <c r="U65" s="7" t="inlineStr"/>
       <c r="V65" s="7" t="inlineStr"/>
@@ -5396,12 +5370,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5416,45 +5390,45 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.1%</t>
+          <t>1차 매수선까지 40.0%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>133900</v>
+        <v>231500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>133600</v>
+        <v>224000</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>138000</v>
+        <v>240000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>144815</v>
+        <v>208325</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>115852</v>
+        <v>166660</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>114300</v>
+        <v>165400</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>17.14785651793526</v>
+        <v>39.96372430471584</v>
       </c>
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="7" t="inlineStr"/>
       <c r="O66" s="5" t="n">
-        <v>103000</v>
+        <v>149000</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>30</v>
+        <v>55.36912751677853</v>
       </c>
       <c r="Q66" s="7" t="inlineStr"/>
       <c r="R66" s="7" t="inlineStr"/>
       <c r="S66" s="5" t="n">
-        <v>92800</v>
+        <v>134200</v>
       </c>
       <c r="T66" s="6" t="n">
-        <v>44.28879310344828</v>
+        <v>72.50372578241431</v>
       </c>
       <c r="U66" s="7" t="inlineStr"/>
       <c r="V66" s="7" t="inlineStr"/>
@@ -5470,12 +5444,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5490,45 +5464,45 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.0%</t>
+          <t>1차 매수선까지 24.0%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>37150</v>
+        <v>52100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>36850</v>
+        <v>51700</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>38150</v>
+        <v>54000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>38405</v>
+        <v>53130</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>30724</v>
+        <v>42504</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>30450</v>
+        <v>42000</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>22.00328407224959</v>
+        <v>24.04761904761905</v>
       </c>
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="5" t="n">
-        <v>27500</v>
+        <v>37850</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>35.09090909090909</v>
+        <v>37.64861294583884</v>
       </c>
       <c r="Q67" s="7" t="inlineStr"/>
       <c r="R67" s="7" t="inlineStr"/>
       <c r="S67" s="5" t="n">
-        <v>24800</v>
+        <v>34150</v>
       </c>
       <c r="T67" s="6" t="n">
-        <v>49.79838709677419</v>
+        <v>52.56222547584187</v>
       </c>
       <c r="U67" s="7" t="inlineStr"/>
       <c r="V67" s="7" t="inlineStr"/>
@@ -5544,12 +5518,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5559,50 +5533,50 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.2% (접근 중!)</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>9010</v>
+        <v>17400</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>8900</v>
+        <v>16680</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>9270</v>
+        <v>18310</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>10531</v>
+        <v>15627.5</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>8424.800000000001</v>
+        <v>12502</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>8250</v>
+        <v>12380</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>9.212121212121211</v>
+        <v>40.54927302100161</v>
       </c>
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="7" t="inlineStr"/>
       <c r="O68" s="5" t="n">
-        <v>7440</v>
+        <v>11160</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>21.10215053763441</v>
+        <v>55.91397849462365</v>
       </c>
       <c r="Q68" s="7" t="inlineStr"/>
       <c r="R68" s="7" t="inlineStr"/>
       <c r="S68" s="5" t="n">
-        <v>6710</v>
+        <v>10060</v>
       </c>
       <c r="T68" s="6" t="n">
-        <v>34.27719821162444</v>
+        <v>72.96222664015905</v>
       </c>
       <c r="U68" s="7" t="inlineStr"/>
       <c r="V68" s="7" t="inlineStr"/>
@@ -5618,12 +5592,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5638,45 +5612,45 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.5%</t>
+          <t>1차 매수선까지 24.2%</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>251500</v>
+        <v>28950</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>242000</v>
+        <v>28650</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>258500</v>
+        <v>29950</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>231755</v>
+        <v>29482.5</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>185404</v>
+        <v>23586</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>184200</v>
+        <v>23300</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>36.53637350705755</v>
+        <v>24.24892703862661</v>
       </c>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr"/>
       <c r="O69" s="5" t="n">
-        <v>165900</v>
+        <v>21050</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>51.59734779987944</v>
+        <v>37.52969121140142</v>
       </c>
       <c r="Q69" s="7" t="inlineStr"/>
       <c r="R69" s="7" t="inlineStr"/>
       <c r="S69" s="5" t="n">
-        <v>149500</v>
+        <v>18960</v>
       </c>
       <c r="T69" s="6" t="n">
-        <v>68.22742474916387</v>
+        <v>52.68987341772152</v>
       </c>
       <c r="U69" s="7" t="inlineStr"/>
       <c r="V69" s="7" t="inlineStr"/>
@@ -5692,12 +5666,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5712,45 +5686,45 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.6%</t>
+          <t>1차 매수선까지 33.2%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>306000</v>
+        <v>2570</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>304500</v>
+        <v>2550</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>317500</v>
+        <v>2715</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>282850</v>
+        <v>2437.95</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>226280</v>
+        <v>1950.36</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>224000</v>
+        <v>1929</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>36.60714285714285</v>
+        <v>33.22965266977709</v>
       </c>
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="7" t="inlineStr"/>
       <c r="O70" s="5" t="n">
-        <v>202500</v>
+        <v>1738</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>51.11111111111111</v>
+        <v>47.87111622554661</v>
       </c>
       <c r="Q70" s="7" t="inlineStr"/>
       <c r="R70" s="7" t="inlineStr"/>
       <c r="S70" s="5" t="n">
-        <v>182400</v>
+        <v>1566</v>
       </c>
       <c r="T70" s="6" t="n">
-        <v>67.76315789473685</v>
+        <v>64.11238825031928</v>
       </c>
       <c r="U70" s="7" t="inlineStr"/>
       <c r="V70" s="7" t="inlineStr"/>
@@ -5766,12 +5740,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5786,45 +5760,45 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.0%</t>
+          <t>1차 매수선까지 28.6%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>114900</v>
+        <v>7200</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>101700</v>
+        <v>7060</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>117400</v>
+        <v>7400</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>96975</v>
+        <v>7106.5</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>77580</v>
+        <v>5685.200000000001</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>76600</v>
+        <v>5600</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>50</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr"/>
       <c r="O71" s="5" t="n">
-        <v>69100</v>
+        <v>5050</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>66.28075253256151</v>
+        <v>42.57425742574257</v>
       </c>
       <c r="Q71" s="7" t="inlineStr"/>
       <c r="R71" s="7" t="inlineStr"/>
       <c r="S71" s="5" t="n">
-        <v>62300</v>
+        <v>4550</v>
       </c>
       <c r="T71" s="6" t="n">
-        <v>84.43017656500803</v>
+        <v>58.24175824175825</v>
       </c>
       <c r="U71" s="7" t="inlineStr"/>
       <c r="V71" s="7" t="inlineStr"/>
@@ -5840,12 +5814,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5860,45 +5834,45 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.5%</t>
+          <t>1차 매수선까지 26.8%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>94900</v>
+        <v>142000</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>91600</v>
+        <v>139600</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>97500</v>
+        <v>145200</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>86775</v>
+        <v>141765</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>69420</v>
+        <v>113412</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>68500</v>
+        <v>112000</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>38.54014598540146</v>
+        <v>26.78571428571428</v>
       </c>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
       <c r="O72" s="5" t="n">
-        <v>61800</v>
+        <v>100900</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>53.55987055016181</v>
+        <v>40.73339940535183</v>
       </c>
       <c r="Q72" s="7" t="inlineStr"/>
       <c r="R72" s="7" t="inlineStr"/>
       <c r="S72" s="5" t="n">
-        <v>55800</v>
+        <v>91000</v>
       </c>
       <c r="T72" s="6" t="n">
-        <v>70.07168458781362</v>
+        <v>56.04395604395604</v>
       </c>
       <c r="U72" s="7" t="inlineStr"/>
       <c r="V72" s="7" t="inlineStr"/>
@@ -5914,12 +5888,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5934,45 +5908,45 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.0%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>230000</v>
+        <v>37150</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>227000</v>
+        <v>36950</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>235000</v>
+        <v>38000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>220375</v>
+        <v>38525</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>176300</v>
+        <v>30820</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>174200</v>
+        <v>30550</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>32.03214695752009</v>
+        <v>21.60392798690671</v>
       </c>
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="5" t="n">
-        <v>156900</v>
+        <v>27550</v>
       </c>
       <c r="P73" s="6" t="n">
-        <v>46.59018483110262</v>
+        <v>34.84573502722323</v>
       </c>
       <c r="Q73" s="7" t="inlineStr"/>
       <c r="R73" s="7" t="inlineStr"/>
       <c r="S73" s="5" t="n">
-        <v>141400</v>
+        <v>24850</v>
       </c>
       <c r="T73" s="6" t="n">
-        <v>62.65912305516266</v>
+        <v>49.49698189134809</v>
       </c>
       <c r="U73" s="7" t="inlineStr"/>
       <c r="V73" s="7" t="inlineStr"/>
@@ -5988,12 +5962,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -6008,45 +5982,45 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.1%</t>
+          <t>1차 매수선까지 14.6%</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>125100</v>
+        <v>9010</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>124000</v>
+        <v>8860</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>128000</v>
+        <v>9180</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>108560</v>
+        <v>9976</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>86848</v>
+        <v>7980.8</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>86200</v>
+        <v>7860</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>45.12761020881671</v>
+        <v>14.63104325699746</v>
       </c>
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr"/>
       <c r="O74" s="5" t="n">
-        <v>77700</v>
+        <v>7090</v>
       </c>
       <c r="P74" s="6" t="n">
-        <v>61.003861003861</v>
+        <v>27.08039492242595</v>
       </c>
       <c r="Q74" s="7" t="inlineStr"/>
       <c r="R74" s="7" t="inlineStr"/>
       <c r="S74" s="5" t="n">
-        <v>70100</v>
+        <v>6400</v>
       </c>
       <c r="T74" s="6" t="n">
-        <v>78.45934379457917</v>
+        <v>40.78125</v>
       </c>
       <c r="U74" s="7" t="inlineStr"/>
       <c r="V74" s="7" t="inlineStr"/>
@@ -6058,6 +6032,450 @@
       <c r="AB74" s="7" t="inlineStr"/>
       <c r="AC74" s="7" t="inlineStr"/>
       <c r="AD74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>402340</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 41.0%</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>266500</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>282000</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>244480</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>195584</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>195100</v>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>40.95335725269093</v>
+      </c>
+      <c r="M75" s="7" t="inlineStr"/>
+      <c r="N75" s="7" t="inlineStr"/>
+      <c r="O75" s="5" t="n">
+        <v>175700</v>
+      </c>
+      <c r="P75" s="6" t="n">
+        <v>56.51678998292545</v>
+      </c>
+      <c r="Q75" s="7" t="inlineStr"/>
+      <c r="R75" s="7" t="inlineStr"/>
+      <c r="S75" s="5" t="n">
+        <v>158300</v>
+      </c>
+      <c r="T75" s="6" t="n">
+        <v>73.72078332280481</v>
+      </c>
+      <c r="U75" s="7" t="inlineStr"/>
+      <c r="V75" s="7" t="inlineStr"/>
+      <c r="W75" s="7" t="inlineStr"/>
+      <c r="X75" s="7" t="inlineStr"/>
+      <c r="Y75" s="7" t="inlineStr"/>
+      <c r="Z75" s="7" t="inlineStr"/>
+      <c r="AA75" s="7" t="inlineStr"/>
+      <c r="AB75" s="7" t="inlineStr"/>
+      <c r="AC75" s="7" t="inlineStr"/>
+      <c r="AD75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>005490</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 41.7%</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>328000</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>320500</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>331500</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>291800</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>233440</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>231500</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>41.68466522678186</v>
+      </c>
+      <c r="M76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="inlineStr"/>
+      <c r="O76" s="5" t="n">
+        <v>209000</v>
+      </c>
+      <c r="P76" s="6" t="n">
+        <v>56.9377990430622</v>
+      </c>
+      <c r="Q76" s="7" t="inlineStr"/>
+      <c r="R76" s="7" t="inlineStr"/>
+      <c r="S76" s="5" t="n">
+        <v>188200</v>
+      </c>
+      <c r="T76" s="6" t="n">
+        <v>74.28267800212541</v>
+      </c>
+      <c r="U76" s="7" t="inlineStr"/>
+      <c r="V76" s="7" t="inlineStr"/>
+      <c r="W76" s="7" t="inlineStr"/>
+      <c r="X76" s="7" t="inlineStr"/>
+      <c r="Y76" s="7" t="inlineStr"/>
+      <c r="Z76" s="7" t="inlineStr"/>
+      <c r="AA76" s="7" t="inlineStr"/>
+      <c r="AB76" s="7" t="inlineStr"/>
+      <c r="AC76" s="7" t="inlineStr"/>
+      <c r="AD76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>267270</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>HD현대건설기계</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 41.7%</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>111400</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>108000</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>79312</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>78600</v>
+      </c>
+      <c r="L77" s="6" t="n">
+        <v>41.73027989821883</v>
+      </c>
+      <c r="M77" s="7" t="inlineStr"/>
+      <c r="N77" s="7" t="inlineStr"/>
+      <c r="O77" s="5" t="n">
+        <v>70900</v>
+      </c>
+      <c r="P77" s="6" t="n">
+        <v>57.12270803949225</v>
+      </c>
+      <c r="Q77" s="7" t="inlineStr"/>
+      <c r="R77" s="7" t="inlineStr"/>
+      <c r="S77" s="5" t="n">
+        <v>64000</v>
+      </c>
+      <c r="T77" s="6" t="n">
+        <v>74.0625</v>
+      </c>
+      <c r="U77" s="7" t="inlineStr"/>
+      <c r="V77" s="7" t="inlineStr"/>
+      <c r="W77" s="7" t="inlineStr"/>
+      <c r="X77" s="7" t="inlineStr"/>
+      <c r="Y77" s="7" t="inlineStr"/>
+      <c r="Z77" s="7" t="inlineStr"/>
+      <c r="AA77" s="7" t="inlineStr"/>
+      <c r="AB77" s="7" t="inlineStr"/>
+      <c r="AC77" s="7" t="inlineStr"/>
+      <c r="AD77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>000880</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 43.8%</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>101700</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>95900</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>101900</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>89025</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>71220</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>70700</v>
+      </c>
+      <c r="L78" s="6" t="n">
+        <v>43.84724186704385</v>
+      </c>
+      <c r="M78" s="7" t="inlineStr"/>
+      <c r="N78" s="7" t="inlineStr"/>
+      <c r="O78" s="5" t="n">
+        <v>63800</v>
+      </c>
+      <c r="P78" s="6" t="n">
+        <v>59.40438871473355</v>
+      </c>
+      <c r="Q78" s="7" t="inlineStr"/>
+      <c r="R78" s="7" t="inlineStr"/>
+      <c r="S78" s="5" t="n">
+        <v>57600</v>
+      </c>
+      <c r="T78" s="6" t="n">
+        <v>76.5625</v>
+      </c>
+      <c r="U78" s="7" t="inlineStr"/>
+      <c r="V78" s="7" t="inlineStr"/>
+      <c r="W78" s="7" t="inlineStr"/>
+      <c r="X78" s="7" t="inlineStr"/>
+      <c r="Y78" s="7" t="inlineStr"/>
+      <c r="Z78" s="7" t="inlineStr"/>
+      <c r="AA78" s="7" t="inlineStr"/>
+      <c r="AB78" s="7" t="inlineStr"/>
+      <c r="AC78" s="7" t="inlineStr"/>
+      <c r="AD78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>034730</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 40.6%</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>251500</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>242500</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>256000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>225100</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>180080</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>178900</v>
+      </c>
+      <c r="L79" s="6" t="n">
+        <v>40.58133035215204</v>
+      </c>
+      <c r="M79" s="7" t="inlineStr"/>
+      <c r="N79" s="7" t="inlineStr"/>
+      <c r="O79" s="5" t="n">
+        <v>161200</v>
+      </c>
+      <c r="P79" s="6" t="n">
+        <v>56.01736972704715</v>
+      </c>
+      <c r="Q79" s="7" t="inlineStr"/>
+      <c r="R79" s="7" t="inlineStr"/>
+      <c r="S79" s="5" t="n">
+        <v>145200</v>
+      </c>
+      <c r="T79" s="6" t="n">
+        <v>73.20936639118457</v>
+      </c>
+      <c r="U79" s="7" t="inlineStr"/>
+      <c r="V79" s="7" t="inlineStr"/>
+      <c r="W79" s="7" t="inlineStr"/>
+      <c r="X79" s="7" t="inlineStr"/>
+      <c r="Y79" s="7" t="inlineStr"/>
+      <c r="Z79" s="7" t="inlineStr"/>
+      <c r="AA79" s="7" t="inlineStr"/>
+      <c r="AB79" s="7" t="inlineStr"/>
+      <c r="AC79" s="7" t="inlineStr"/>
+      <c r="AD79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 49.7%</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>136500</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>131400</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>138300</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>114540</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>91632</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>91200</v>
+      </c>
+      <c r="L80" s="6" t="n">
+        <v>49.67105263157895</v>
+      </c>
+      <c r="M80" s="7" t="inlineStr"/>
+      <c r="N80" s="7" t="inlineStr"/>
+      <c r="O80" s="5" t="n">
+        <v>82200</v>
+      </c>
+      <c r="P80" s="6" t="n">
+        <v>66.05839416058394</v>
+      </c>
+      <c r="Q80" s="7" t="inlineStr"/>
+      <c r="R80" s="7" t="inlineStr"/>
+      <c r="S80" s="5" t="n">
+        <v>74100</v>
+      </c>
+      <c r="T80" s="6" t="n">
+        <v>84.21052631578947</v>
+      </c>
+      <c r="U80" s="7" t="inlineStr"/>
+      <c r="V80" s="7" t="inlineStr"/>
+      <c r="W80" s="7" t="inlineStr"/>
+      <c r="X80" s="7" t="inlineStr"/>
+      <c r="Y80" s="7" t="inlineStr"/>
+      <c r="Z80" s="7" t="inlineStr"/>
+      <c r="AA80" s="7" t="inlineStr"/>
+      <c r="AB80" s="7" t="inlineStr"/>
+      <c r="AC80" s="7" t="inlineStr"/>
+      <c r="AD80" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6070,315 +6488,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>티커</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>매수상태</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>알람상태</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>상태메시지</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>저가</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>고가</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>20일선</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>-20%엔벨로프</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1차매수선</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1차매수선이격도(%)</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1차매수일</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1차매수가</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>2차매수선</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>2차매수선이격도(%)</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>2차매수일</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>2차매수가</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>3차매수선</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>3차매수선이격도(%)</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>3차매수일</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>3차매수가</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>평균매수가</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1차매도선(+3%)</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1차매도선이격도(%)</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>2차매도선(+5%)</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>2차매도선이격도(%)</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>3차매도선(+7%)</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>3차매도선이격도(%)</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>최고도달선</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>종료일</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>종료사유</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>실현수익률(%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>456160</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>지투지바이오</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>매도 완료</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>170500</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>161600</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>196700</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>199815</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>159852</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>157600</v>
-      </c>
-      <c r="L2" s="6" t="n">
-        <v>8.185279187817258</v>
-      </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>159500</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>142000</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>20.07042253521127</v>
-      </c>
-      <c r="Q2" s="7" t="n"/>
-      <c r="R2" s="7" t="n"/>
-      <c r="S2" s="5" t="n">
-        <v>127900</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>33.30727130570759</v>
-      </c>
-      <c r="U2" s="7" t="n"/>
-      <c r="V2" s="7" t="n"/>
-      <c r="W2" s="5" t="n">
-        <v>159500</v>
-      </c>
-      <c r="X2" s="5" t="n">
-        <v>164285</v>
-      </c>
-      <c r="Y2" s="6" t="n">
-        <v>3.783059926347506</v>
-      </c>
-      <c r="Z2" s="5" t="n">
-        <v>167475</v>
-      </c>
-      <c r="AA2" s="6" t="n">
-        <v>1.80623973727422</v>
-      </c>
-      <c r="AB2" s="5" t="n">
-        <v>170665</v>
-      </c>
-      <c r="AC2" s="6" t="n">
-        <v>-0.09668063164679343</v>
-      </c>
-      <c r="AD2" s="7" t="n"/>
-      <c r="AE2" s="8" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AF2" s="3" t="inlineStr">
-        <is>
-          <t>매도 완료</t>
-        </is>
-      </c>
-      <c r="AG2" s="6" t="n">
-        <v>6.896551724137931</v>
-      </c>
+      <c r="A1" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -654,45 +654,45 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.3%</t>
+          <t>1차 매수선까지 40.8%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>101700</v>
+        <v>107700</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>99100</v>
+        <v>101500</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>101700</v>
+        <v>109200</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>93740</v>
+        <v>95910</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>74992</v>
+        <v>76728</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>74600</v>
+        <v>76500</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>36.32707774798928</v>
+        <v>40.78431372549019</v>
       </c>
       <c r="M2" s="7" t="inlineStr"/>
       <c r="N2" s="7" t="inlineStr"/>
       <c r="O2" s="5" t="n">
-        <v>67300</v>
+        <v>69000</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>51.11441307578009</v>
+        <v>56.08695652173913</v>
       </c>
       <c r="Q2" s="7" t="inlineStr"/>
       <c r="R2" s="7" t="inlineStr"/>
       <c r="S2" s="5" t="n">
-        <v>60700</v>
+        <v>62200</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>67.54530477759472</v>
+        <v>73.15112540192926</v>
       </c>
       <c r="U2" s="7" t="inlineStr"/>
       <c r="V2" s="7" t="inlineStr"/>
@@ -728,45 +728,45 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.9%</t>
+          <t>1차 매수선까지 50.7%</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>568000</v>
+        <v>560000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>522000</v>
+        <v>552000</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>568000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>441275</v>
+        <v>463025</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>353020</v>
+        <v>370420</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>353000</v>
+        <v>371500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>60.90651558073654</v>
+        <v>50.74024226110363</v>
       </c>
       <c r="M3" s="7" t="inlineStr"/>
       <c r="N3" s="7" t="inlineStr"/>
       <c r="O3" s="5" t="n">
-        <v>318500</v>
+        <v>335000</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>78.33594976452119</v>
+        <v>67.16417910447761</v>
       </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="5" t="n">
-        <v>287500</v>
+        <v>302000</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>97.56521739130434</v>
+        <v>85.43046357615894</v>
       </c>
       <c r="U3" s="7" t="inlineStr"/>
       <c r="V3" s="7" t="inlineStr"/>
@@ -802,45 +802,45 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 53.8%</t>
+          <t>1차 매수선까지 41.4%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>93200</v>
+        <v>88800</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>87300</v>
+        <v>88200</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>97400</v>
+        <v>91500</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>75825</v>
+        <v>78450</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>60660</v>
+        <v>62760</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>60600</v>
+        <v>62800</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>53.79537953795379</v>
+        <v>41.40127388535032</v>
       </c>
       <c r="M4" s="7" t="inlineStr"/>
       <c r="N4" s="7" t="inlineStr"/>
       <c r="O4" s="5" t="n">
-        <v>54700</v>
+        <v>56700</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>70.38391224862889</v>
+        <v>56.61375661375661</v>
       </c>
       <c r="Q4" s="7" t="inlineStr"/>
       <c r="R4" s="7" t="inlineStr"/>
       <c r="S4" s="5" t="n">
-        <v>49300</v>
+        <v>51200</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>89.04665314401623</v>
+        <v>73.4375</v>
       </c>
       <c r="U4" s="7" t="inlineStr"/>
       <c r="V4" s="7" t="inlineStr"/>
@@ -876,45 +876,45 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 49.9%</t>
+          <t>1차 매수선까지 43.3%</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>139900</v>
+        <v>137600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>127200</v>
+        <v>133700</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>141100</v>
+        <v>141600</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>117395</v>
+        <v>120490</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>93916</v>
+        <v>96392</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>93300</v>
+        <v>96000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>49.94640943193998</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="5" t="n">
-        <v>84100</v>
+        <v>86500</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>66.34958382877527</v>
+        <v>59.07514450867052</v>
       </c>
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="5" t="n">
-        <v>75800</v>
+        <v>78000</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>84.56464379947229</v>
+        <v>76.41025641025641</v>
       </c>
       <c r="U5" s="7" t="inlineStr"/>
       <c r="V5" s="7" t="inlineStr"/>
@@ -950,45 +950,45 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.3%</t>
+          <t>1차 매수선까지 32.6%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>266500</v>
+        <v>270500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>252500</v>
+        <v>255500</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>268500</v>
+        <v>273500</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>257600</v>
+        <v>258250</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>206080</v>
+        <v>206600</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>204500</v>
+        <v>204000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>30.31784841075795</v>
+        <v>32.59803921568628</v>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="5" t="n">
-        <v>184200</v>
+        <v>183700</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>44.67969598262758</v>
+        <v>47.2509526401742</v>
       </c>
       <c r="Q6" s="7" t="inlineStr"/>
       <c r="R6" s="7" t="inlineStr"/>
       <c r="S6" s="5" t="n">
-        <v>165900</v>
+        <v>165500</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>60.63893911995177</v>
+        <v>63.44410876132931</v>
       </c>
       <c r="U6" s="7" t="inlineStr"/>
       <c r="V6" s="7" t="inlineStr"/>
@@ -1024,45 +1024,45 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 71.6%</t>
+          <t>1차 매수선까지 59.0%</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>331500</v>
+        <v>323500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>305000</v>
+        <v>315500</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>334000</v>
+        <v>329000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>242300</v>
+        <v>253975</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>193840</v>
+        <v>203180</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>193200</v>
+        <v>203500</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>71.58385093167702</v>
+        <v>58.96805896805897</v>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="5" t="n">
-        <v>174000</v>
+        <v>183300</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>90.51724137931035</v>
+        <v>76.48663393344245</v>
       </c>
       <c r="Q7" s="7" t="inlineStr"/>
       <c r="R7" s="7" t="inlineStr"/>
       <c r="S7" s="5" t="n">
-        <v>156700</v>
+        <v>165100</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>111.5507338864071</v>
+        <v>95.94185342216839</v>
       </c>
       <c r="U7" s="7" t="inlineStr"/>
       <c r="V7" s="7" t="inlineStr"/>
@@ -1098,45 +1098,45 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 35.3%</t>
+          <t>1차 매수선까지 32.5%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>138700</v>
+        <v>141500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>133300</v>
+        <v>138900</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>147400</v>
+        <v>144800</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>127645</v>
+        <v>132670</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>102116</v>
+        <v>106136</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>102500</v>
+        <v>106800</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>35.3170731707317</v>
+        <v>32.49063670411985</v>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="5" t="n">
-        <v>92400</v>
+        <v>96300</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>50.10822510822511</v>
+        <v>46.93665628245067</v>
       </c>
       <c r="Q8" s="7" t="inlineStr"/>
       <c r="R8" s="7" t="inlineStr"/>
       <c r="S8" s="5" t="n">
-        <v>83300</v>
+        <v>86800</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>66.50660264105642</v>
+        <v>63.0184331797235</v>
       </c>
       <c r="U8" s="7" t="inlineStr"/>
       <c r="V8" s="7" t="inlineStr"/>
@@ -1172,45 +1172,45 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 51.7%</t>
+          <t>1차 매수선까지 48.8%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>285500</v>
+        <v>288000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>251000</v>
+        <v>267000</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>290500</v>
+        <v>294000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>236600</v>
+        <v>242925</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>189280</v>
+        <v>194340</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>188200</v>
+        <v>193500</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>51.70031880977683</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="5" t="n">
-        <v>169500</v>
+        <v>174300</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>68.43657817109144</v>
+        <v>65.23235800344234</v>
       </c>
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="5" t="n">
-        <v>152700</v>
+        <v>157000</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>86.96791093647676</v>
+        <v>83.43949044585987</v>
       </c>
       <c r="U9" s="7" t="inlineStr"/>
       <c r="V9" s="7" t="inlineStr"/>
@@ -1246,45 +1246,45 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 75.4%</t>
+          <t>1차 매수선까지 60.8%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>92100</v>
+        <v>89900</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>90200</v>
+        <v>85500</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>96400</v>
+        <v>92300</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>65450</v>
+        <v>69475</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>52360</v>
+        <v>55580</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>52500</v>
+        <v>55900</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>75.42857142857143</v>
+        <v>60.82289803220036</v>
       </c>
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="5" t="n">
-        <v>47300</v>
+        <v>50500</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>94.71458773784354</v>
+        <v>78.01980198019803</v>
       </c>
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="5" t="n">
-        <v>42650</v>
+        <v>45500</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>115.9437280187573</v>
+        <v>97.58241758241758</v>
       </c>
       <c r="U10" s="7" t="inlineStr"/>
       <c r="V10" s="7" t="inlineStr"/>
@@ -1300,12 +1300,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1320,45 +1320,45 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.8%</t>
+          <t>1차 매수선까지 51.7%</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>234000</v>
+        <v>29600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>230000</v>
+        <v>29100</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>242500</v>
+        <v>30300</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>182835</v>
+        <v>24470</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>146268</v>
+        <v>19576</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>146400</v>
+        <v>19510</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>59.83606557377049</v>
+        <v>51.71706817016914</v>
       </c>
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="5" t="n">
-        <v>131900</v>
+        <v>17570</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>77.40712661106899</v>
+        <v>68.4689812179852</v>
       </c>
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="5" t="n">
-        <v>118900</v>
+        <v>15830</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>96.8040370058873</v>
+        <v>86.98673404927352</v>
       </c>
       <c r="U11" s="7" t="inlineStr"/>
       <c r="V11" s="7" t="inlineStr"/>
@@ -1374,12 +1374,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>247540</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1394,45 +1394,45 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 52.4%</t>
+          <t>1차 매수선까지 35.5%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>170500</v>
+        <v>65500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>169000</v>
+        <v>62800</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>176500</v>
+        <v>66300</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>140170</v>
+        <v>61040</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>112136</v>
+        <v>48832</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>111900</v>
+        <v>48350</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>52.36818588025023</v>
+        <v>35.47052740434333</v>
       </c>
       <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="5" t="n">
-        <v>100900</v>
+        <v>43600</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>68.97918731417245</v>
+        <v>50.22935779816514</v>
       </c>
       <c r="Q12" s="7" t="inlineStr"/>
       <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="5" t="n">
-        <v>91000</v>
+        <v>39300</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>87.36263736263736</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="U12" s="7" t="inlineStr"/>
       <c r="V12" s="7" t="inlineStr"/>
@@ -1448,12 +1448,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1468,45 +1468,45 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 68.0%</t>
+          <t>1차 매수선까지 42.8%</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>31550</v>
+        <v>218000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>29200</v>
+        <v>212500</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>31750</v>
+        <v>223500</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>23625</v>
+        <v>190435</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>18900</v>
+        <v>152348</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>18780</v>
+        <v>152700</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>67.99787007454739</v>
+        <v>42.76358873608383</v>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="5" t="n">
-        <v>16920</v>
+        <v>137600</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>86.46572104018912</v>
+        <v>58.43023255813954</v>
       </c>
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="5" t="n">
-        <v>15240</v>
+        <v>124000</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>107.0209973753281</v>
+        <v>75.80645161290323</v>
       </c>
       <c r="U13" s="7" t="inlineStr"/>
       <c r="V13" s="7" t="inlineStr"/>
@@ -1522,12 +1522,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>247540</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1542,45 +1542,45 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.8%</t>
+          <t>1차 매수선까지 40.1%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68000</v>
+        <v>162200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>62800</v>
+        <v>157600</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>69700</v>
+        <v>164500</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>60695</v>
+        <v>144660</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>48556</v>
+        <v>115728</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>47950</v>
+        <v>115800</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>41.81438998957247</v>
+        <v>40.06908462867012</v>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="5" t="n">
-        <v>43250</v>
+        <v>104400</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>57.22543352601156</v>
+        <v>55.3639846743295</v>
       </c>
       <c r="Q14" s="7" t="inlineStr"/>
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="5" t="n">
-        <v>39000</v>
+        <v>94100</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>74.35897435897436</v>
+        <v>72.36981934112646</v>
       </c>
       <c r="U14" s="7" t="inlineStr"/>
       <c r="V14" s="7" t="inlineStr"/>
@@ -1596,12 +1596,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1616,45 +1616,45 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 58.0%</t>
+          <t>1차 매수선까지 39.9%</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>415500</v>
+        <v>473500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>409000</v>
+        <v>469500</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>422000</v>
+        <v>491500</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>330125</v>
+        <v>423625</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>264100</v>
+        <v>338900</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>263000</v>
+        <v>338500</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57.98479087452472</v>
+        <v>39.88183161004431</v>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="5" t="n">
-        <v>237500</v>
+        <v>305500</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>74.94736842105263</v>
+        <v>54.99181669394435</v>
       </c>
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="5" t="n">
-        <v>214500</v>
+        <v>275500</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>93.70629370629371</v>
+        <v>71.86932849364791</v>
       </c>
       <c r="U15" s="7" t="inlineStr"/>
       <c r="V15" s="7" t="inlineStr"/>
@@ -1670,12 +1670,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1690,45 +1690,45 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.3%</t>
+          <t>1차 매수선까지 47.4%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>66200</v>
+        <v>123100</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>65500</v>
+        <v>118200</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>68000</v>
+        <v>129100</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>57190</v>
+        <v>103790</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>45752</v>
+        <v>83032</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>45550</v>
+        <v>83500</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>45.33479692645444</v>
+        <v>47.4251497005988</v>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="5" t="n">
-        <v>41050</v>
+        <v>75300</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>61.26674786845311</v>
+        <v>63.47941567065073</v>
       </c>
       <c r="Q16" s="7" t="inlineStr"/>
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="5" t="n">
-        <v>37000</v>
+        <v>67900</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>78.91891891891892</v>
+        <v>81.2960235640648</v>
       </c>
       <c r="U16" s="7" t="inlineStr"/>
       <c r="V16" s="7" t="inlineStr"/>
@@ -1744,12 +1744,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1764,45 +1764,45 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 57.0%</t>
+          <t>1차 매수선까지 45.6%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>515000</v>
+        <v>397500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>502000</v>
+        <v>389000</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>527000</v>
+        <v>404000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>411075</v>
+        <v>341475</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>328860</v>
+        <v>273180</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>328000</v>
+        <v>273000</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>57.01219512195122</v>
+        <v>45.60439560439561</v>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="5" t="n">
-        <v>296000</v>
+        <v>246500</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>73.98648648648648</v>
+        <v>61.25760649087221</v>
       </c>
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="5" t="n">
-        <v>267000</v>
+        <v>222500</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>92.88389513108615</v>
+        <v>78.65168539325843</v>
       </c>
       <c r="U17" s="7" t="inlineStr"/>
       <c r="V17" s="7" t="inlineStr"/>
@@ -1818,12 +1818,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1838,45 +1838,45 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.2%</t>
+          <t>1차 매수선까지 36.2%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>45000</v>
+        <v>63800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>43850</v>
+        <v>62200</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>45800</v>
+        <v>64900</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>39730</v>
+        <v>58605</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>31784</v>
+        <v>46884</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>31650</v>
+        <v>46850</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>42.18009478672986</v>
+        <v>36.17929562433298</v>
       </c>
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="5" t="n">
-        <v>28550</v>
+        <v>42250</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>57.61821366024519</v>
+        <v>51.00591715976331</v>
       </c>
       <c r="Q18" s="7" t="inlineStr"/>
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="5" t="n">
-        <v>25750</v>
+        <v>38100</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>74.75728155339806</v>
+        <v>67.45406824146981</v>
       </c>
       <c r="U18" s="7" t="inlineStr"/>
       <c r="V18" s="7" t="inlineStr"/>
@@ -1892,12 +1892,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1912,45 +1912,45 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 65.4%</t>
+          <t>1차 매수선까지 32.8%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>42600</v>
+        <v>42700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>37450</v>
+        <v>42500</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>44000</v>
+        <v>43400</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>32307.5</v>
+        <v>40407.5</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>25846</v>
+        <v>32326</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>25750</v>
+        <v>32150</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>65.4368932038835</v>
+        <v>32.8149300155521</v>
       </c>
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="5" t="n">
-        <v>23250</v>
+        <v>29000</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>83.22580645161291</v>
+        <v>47.24137931034483</v>
       </c>
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="5" t="n">
-        <v>21000</v>
+        <v>26150</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>102.8571428571428</v>
+        <v>63.28871892925431</v>
       </c>
       <c r="U19" s="7" t="inlineStr"/>
       <c r="V19" s="7" t="inlineStr"/>
@@ -1966,12 +1966,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1986,45 +1986,45 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.8%</t>
+          <t>1차 매수선까지 45.9%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>71500</v>
+        <v>220500</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>70700</v>
+        <v>214000</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>76400</v>
+        <v>235000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>59620</v>
+        <v>189055</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>47696</v>
+        <v>151244</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>47400</v>
+        <v>151100</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>50.84388185654009</v>
+        <v>45.92984778292521</v>
       </c>
       <c r="M20" s="7" t="inlineStr"/>
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="5" t="n">
-        <v>42750</v>
+        <v>136100</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>67.2514619883041</v>
+        <v>62.01322556943424</v>
       </c>
       <c r="Q20" s="7" t="inlineStr"/>
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="5" t="n">
-        <v>38550</v>
+        <v>122600</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>85.473411154345</v>
+        <v>79.85318107667212</v>
       </c>
       <c r="U20" s="7" t="inlineStr"/>
       <c r="V20" s="7" t="inlineStr"/>
@@ -2040,12 +2040,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2060,45 +2060,45 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.6%</t>
+          <t>1차 매수선까지 40.7%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>470000</v>
+        <v>84400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>463000</v>
+        <v>82100</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>479000</v>
+        <v>84900</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>454650</v>
+        <v>75265</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>363720</v>
+        <v>60212</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>360000</v>
+        <v>60000</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>30.55555555555556</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="5" t="n">
-        <v>324500</v>
+        <v>54100</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>44.8382126348228</v>
+        <v>56.00739371534195</v>
       </c>
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="5" t="n">
-        <v>293000</v>
+        <v>48750</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>60.40955631399317</v>
+        <v>73.12820512820512</v>
       </c>
       <c r="U21" s="7" t="inlineStr"/>
       <c r="V21" s="7" t="inlineStr"/>
@@ -2114,12 +2114,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2134,45 +2134,45 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.3%</t>
+          <t>1차 매수선까지 34.3%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>30300</v>
+        <v>59900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>28650</v>
+        <v>58700</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>31500</v>
+        <v>64300</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>27090</v>
+        <v>56485</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>21672</v>
+        <v>45188</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>21450</v>
+        <v>44600</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>41.25874125874126</v>
+        <v>34.30493273542601</v>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="5" t="n">
-        <v>19320</v>
+        <v>40200</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>56.83229813664597</v>
+        <v>49.00497512437811</v>
       </c>
       <c r="Q22" s="7" t="inlineStr"/>
       <c r="R22" s="7" t="inlineStr"/>
       <c r="S22" s="5" t="n">
-        <v>17400</v>
+        <v>36250</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>74.13793103448276</v>
+        <v>65.24137931034483</v>
       </c>
       <c r="U22" s="7" t="inlineStr"/>
       <c r="V22" s="7" t="inlineStr"/>
@@ -2188,12 +2188,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2208,45 +2208,45 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.0%</t>
+          <t>1차 매수선까지 59.0%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>232000</v>
+        <v>42700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>227500</v>
+        <v>41700</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>242500</v>
+        <v>45000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>220400</v>
+        <v>33670</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>176320</v>
+        <v>26936</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>174500</v>
+        <v>26850</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>32.95128939828081</v>
+        <v>59.0316573556797</v>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="5" t="n">
-        <v>157200</v>
+        <v>24250</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>47.58269720101781</v>
+        <v>76.08247422680412</v>
       </c>
       <c r="Q23" s="7" t="inlineStr"/>
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="5" t="n">
-        <v>141600</v>
+        <v>21900</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>63.84180790960452</v>
+        <v>94.97716894977168</v>
       </c>
       <c r="U23" s="7" t="inlineStr"/>
       <c r="V23" s="7" t="inlineStr"/>
@@ -2262,12 +2262,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2282,45 +2282,45 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 80.9%</t>
+          <t>1차 매수선까지 44.7%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>143300</v>
+        <v>70300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>142000</v>
+        <v>67000</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>149000</v>
+        <v>72100</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>98865</v>
+        <v>61060</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>79092</v>
+        <v>48848</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>79200</v>
+        <v>48600</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>80.93434343434343</v>
+        <v>44.65020576131688</v>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="5" t="n">
-        <v>71400</v>
+        <v>43800</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>100.7002801120448</v>
+        <v>60.50228310502283</v>
       </c>
       <c r="Q24" s="7" t="inlineStr"/>
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="5" t="n">
-        <v>64400</v>
+        <v>39500</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>122.5155279503106</v>
+        <v>77.9746835443038</v>
       </c>
       <c r="U24" s="7" t="inlineStr"/>
       <c r="V24" s="7" t="inlineStr"/>
@@ -2336,12 +2336,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2356,45 +2356,45 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 79.0%</t>
+          <t>1차 매수선까지 34.8%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>970000</v>
+        <v>488000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>882000</v>
+        <v>472000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>998000</v>
+        <v>491500</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>678400</v>
+        <v>457625</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>542720</v>
+        <v>366100</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>542000</v>
+        <v>362000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>78.96678966789668</v>
+        <v>34.80662983425415</v>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="5" t="n">
-        <v>488500</v>
+        <v>326500</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>98.56704196519959</v>
+        <v>49.46401225114855</v>
       </c>
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="5" t="n">
-        <v>440500</v>
+        <v>294500</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>120.2043132803632</v>
+        <v>65.70458404074702</v>
       </c>
       <c r="U25" s="7" t="inlineStr"/>
       <c r="V25" s="7" t="inlineStr"/>
@@ -2410,12 +2410,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2430,45 +2430,45 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.6%</t>
+          <t>1차 매수선까지 29.8%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>12800</v>
+        <v>28100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>12730</v>
+        <v>27800</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>13290</v>
+        <v>29200</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>10627.5</v>
+        <v>27267.5</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>8502</v>
+        <v>21814</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>8500</v>
+        <v>21650</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>50.58823529411764</v>
+        <v>29.79214780600462</v>
       </c>
       <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="5" t="n">
-        <v>7660</v>
+        <v>19500</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>67.10182767624021</v>
+        <v>44.1025641025641</v>
       </c>
       <c r="Q26" s="7" t="inlineStr"/>
       <c r="R26" s="7" t="inlineStr"/>
       <c r="S26" s="5" t="n">
-        <v>6910</v>
+        <v>17560</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>85.23878437047757</v>
+        <v>60.02277904328018</v>
       </c>
       <c r="U26" s="7" t="inlineStr"/>
       <c r="V26" s="7" t="inlineStr"/>
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2504,45 +2504,45 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 54.4%</t>
+          <t>1차 매수선까지 31.7%</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>21400</v>
+        <v>232000</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>19770</v>
+        <v>226500</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>22000</v>
+        <v>238000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>17407.5</v>
+        <v>222000</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>13926</v>
+        <v>177600</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>13860</v>
+        <v>176100</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>54.40115440115441</v>
+        <v>31.74332765474163</v>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="5" t="n">
-        <v>12490</v>
+        <v>158600</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>71.33706965572458</v>
+        <v>46.27994955863809</v>
       </c>
       <c r="Q27" s="7" t="inlineStr"/>
       <c r="R27" s="7" t="inlineStr"/>
       <c r="S27" s="5" t="n">
-        <v>11260</v>
+        <v>142900</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>90.05328596802842</v>
+        <v>62.35129461161652</v>
       </c>
       <c r="U27" s="7" t="inlineStr"/>
       <c r="V27" s="7" t="inlineStr"/>
@@ -2558,12 +2558,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2578,45 +2578,45 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.1%</t>
+          <t>1차 매수선까지 67.4%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>124500</v>
+        <v>966000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>121200</v>
+        <v>912000</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>126300</v>
+        <v>968000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>107215</v>
+        <v>718100</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>85772</v>
+        <v>574480</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>85200</v>
+        <v>577000</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>46.12676056338028</v>
+        <v>67.41767764298093</v>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="5" t="n">
-        <v>76800</v>
+        <v>521000</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>62.109375</v>
+        <v>85.41266794625719</v>
       </c>
       <c r="Q28" s="7" t="inlineStr"/>
       <c r="R28" s="7" t="inlineStr"/>
       <c r="S28" s="5" t="n">
-        <v>69300</v>
+        <v>469500</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>79.65367965367966</v>
+        <v>105.7507987220447</v>
       </c>
       <c r="U28" s="7" t="inlineStr"/>
       <c r="V28" s="7" t="inlineStr"/>
@@ -2632,12 +2632,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2652,45 +2652,45 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.3%</t>
+          <t>1차 매수선까지 34.8%</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>395500</v>
+        <v>11820</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>390500</v>
+        <v>11590</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>413000</v>
+        <v>12770</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>364250</v>
+        <v>10962.5</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>291400</v>
+        <v>8770</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>288000</v>
+        <v>8770</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>37.32638888888889</v>
+        <v>34.77765108323831</v>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="5" t="n">
-        <v>260000</v>
+        <v>7910</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>52.11538461538462</v>
+        <v>49.43109987357775</v>
       </c>
       <c r="Q29" s="7" t="inlineStr"/>
       <c r="R29" s="7" t="inlineStr"/>
       <c r="S29" s="5" t="n">
-        <v>234500</v>
+        <v>7130</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>68.65671641791045</v>
+        <v>65.77840112201963</v>
       </c>
       <c r="U29" s="7" t="inlineStr"/>
       <c r="V29" s="7" t="inlineStr"/>
@@ -2706,12 +2706,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2726,45 +2726,45 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.9%</t>
+          <t>1차 매수선까지 37.0%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>309000</v>
+        <v>120400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>305250</v>
+        <v>116000</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>314500</v>
+        <v>122600</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>280500</v>
+        <v>110440</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>224400</v>
+        <v>88352</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>222500</v>
+        <v>87900</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>38.87640449438202</v>
+        <v>36.97383390216154</v>
       </c>
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="5" t="n">
-        <v>201000</v>
+        <v>79300</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>53.73134328358209</v>
+        <v>51.82849936948297</v>
       </c>
       <c r="Q30" s="7" t="inlineStr"/>
       <c r="R30" s="7" t="inlineStr"/>
       <c r="S30" s="5" t="n">
-        <v>181000</v>
+        <v>71500</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>70.71823204419888</v>
+        <v>68.3916083916084</v>
       </c>
       <c r="U30" s="7" t="inlineStr"/>
       <c r="V30" s="7" t="inlineStr"/>
@@ -2780,12 +2780,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>090710</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2800,45 +2800,45 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.9%</t>
+          <t>1차 매수선까지 67.6%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>6180</v>
+        <v>24300</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>5930</v>
+        <v>21050</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>6240</v>
+        <v>25400</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>4574.75</v>
+        <v>18154.5</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>3659.8</v>
+        <v>14523.6</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>3680</v>
+        <v>14500</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>67.93478260869566</v>
+        <v>67.58620689655173</v>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="5" t="n">
-        <v>3320</v>
+        <v>13060</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>86.14457831325302</v>
+        <v>86.06431852986218</v>
       </c>
       <c r="Q31" s="7" t="inlineStr"/>
       <c r="R31" s="7" t="inlineStr"/>
       <c r="S31" s="5" t="n">
-        <v>2995</v>
+        <v>11770</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>106.3439065108514</v>
+        <v>106.4570943075616</v>
       </c>
       <c r="U31" s="7" t="inlineStr"/>
       <c r="V31" s="7" t="inlineStr"/>
@@ -2854,12 +2854,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2874,45 +2874,45 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.8%</t>
+          <t>1차 매수선까지 45.4%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>39100</v>
+        <v>126600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>38050</v>
+        <v>114700</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>40150</v>
+        <v>131100</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>36915</v>
+        <v>109445</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>29532</v>
+        <v>87556</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>29450</v>
+        <v>87100</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>32.76740237691001</v>
+        <v>45.35017221584386</v>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="5" t="n">
-        <v>26600</v>
+        <v>78500</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>46.99248120300752</v>
+        <v>61.27388535031847</v>
       </c>
       <c r="Q32" s="7" t="inlineStr"/>
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="5" t="n">
-        <v>24000</v>
+        <v>70800</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>62.91666666666666</v>
+        <v>78.8135593220339</v>
       </c>
       <c r="U32" s="7" t="inlineStr"/>
       <c r="V32" s="7" t="inlineStr"/>
@@ -2928,12 +2928,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2948,45 +2948,45 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.2%</t>
+          <t>1차 매수선까지 46.6%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>206500</v>
+        <v>425000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>192300</v>
+        <v>389500</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>212000</v>
+        <v>435500</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>181263.65</v>
+        <v>367250</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>145010.92</v>
+        <v>293800</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>145200</v>
+        <v>290000</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>42.21763085399449</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="7" t="inlineStr"/>
       <c r="O33" s="5" t="n">
-        <v>130800</v>
+        <v>261500</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>57.87461773700306</v>
+        <v>62.52390057361377</v>
       </c>
       <c r="Q33" s="7" t="inlineStr"/>
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="5" t="n">
-        <v>117900</v>
+        <v>236000</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>75.14843087362172</v>
+        <v>80.08474576271186</v>
       </c>
       <c r="U33" s="7" t="inlineStr"/>
       <c r="V33" s="7" t="inlineStr"/>
@@ -3002,12 +3002,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3022,45 +3022,45 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.6%</t>
+          <t>1차 매수선까지 50.4%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>79900</v>
+        <v>343000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>77400</v>
+        <v>321500</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>79900</v>
+        <v>345000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>73550</v>
+        <v>286925</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>58840</v>
+        <v>229540</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>58500</v>
+        <v>228000</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>36.58119658119658</v>
+        <v>50.43859649122807</v>
       </c>
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="5" t="n">
-        <v>52800</v>
+        <v>206000</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>51.32575757575758</v>
+        <v>66.50485436893204</v>
       </c>
       <c r="Q34" s="7" t="inlineStr"/>
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="5" t="n">
-        <v>47600</v>
+        <v>185500</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>67.85714285714286</v>
+        <v>84.90566037735849</v>
       </c>
       <c r="U34" s="7" t="inlineStr"/>
       <c r="V34" s="7" t="inlineStr"/>
@@ -3076,12 +3076,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3096,45 +3096,45 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.5%</t>
+          <t>1차 매수선까지 64.1%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>23150</v>
+        <v>6450</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>22950</v>
+        <v>6090</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>24000</v>
+        <v>6500</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>24715</v>
+        <v>4876.5</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>19772</v>
+        <v>3901.2</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>19530</v>
+        <v>3930</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>18.53558627752176</v>
+        <v>64.12213740458014</v>
       </c>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="5" t="n">
-        <v>17590</v>
+        <v>3545</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>31.60886867538374</v>
+        <v>81.94640338504936</v>
       </c>
       <c r="Q35" s="7" t="inlineStr"/>
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="5" t="n">
-        <v>15850</v>
+        <v>3200</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>46.05678233438486</v>
+        <v>101.5625</v>
       </c>
       <c r="U35" s="7" t="inlineStr"/>
       <c r="V35" s="7" t="inlineStr"/>
@@ -3150,12 +3150,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3170,45 +3170,45 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.1%</t>
+          <t>1차 매수선까지 33.6%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>9500</v>
+        <v>40600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>8990</v>
+        <v>40550</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>9800</v>
+        <v>45600</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>9990.5</v>
+        <v>37910</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>7992.400000000001</v>
+        <v>30328</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>7910</v>
+        <v>30400</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>20.10113780025284</v>
+        <v>33.55263157894737</v>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr"/>
       <c r="O36" s="5" t="n">
-        <v>7130</v>
+        <v>27450</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>33.2398316970547</v>
+        <v>47.90528233151184</v>
       </c>
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="5" t="n">
-        <v>6430</v>
+        <v>24800</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>47.74494556765163</v>
+        <v>63.70967741935484</v>
       </c>
       <c r="U36" s="7" t="inlineStr"/>
       <c r="V36" s="7" t="inlineStr"/>
@@ -3224,12 +3224,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3244,45 +3244,45 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.7%</t>
+          <t>1차 매수선까지 24.2%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>16870</v>
+        <v>23500</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>16420</v>
+        <v>22550</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>17320</v>
+        <v>23800</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>17430.5</v>
+        <v>24397.5</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>13944.4</v>
+        <v>19518</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>13750</v>
+        <v>18920</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>22.69090909090909</v>
+        <v>24.20718816067653</v>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr"/>
       <c r="O37" s="5" t="n">
-        <v>12390</v>
+        <v>17040</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>36.15819209039548</v>
+        <v>37.91079812206573</v>
       </c>
       <c r="Q37" s="7" t="inlineStr"/>
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="5" t="n">
-        <v>11170</v>
+        <v>15350</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>51.02954341987467</v>
+        <v>53.09446254071661</v>
       </c>
       <c r="U37" s="7" t="inlineStr"/>
       <c r="V37" s="7" t="inlineStr"/>
@@ -3298,12 +3298,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3318,45 +3318,45 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.9%</t>
+          <t>1차 매수선까지 17.0%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>345000</v>
+        <v>9010</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>338000</v>
+        <v>8890</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>347500</v>
+        <v>9080</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>331750</v>
+        <v>9852.5</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>265400</v>
+        <v>7882</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>263500</v>
+        <v>7700</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>30.92979127134725</v>
+        <v>17.01298701298701</v>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="7" t="inlineStr"/>
       <c r="O38" s="5" t="n">
-        <v>238000</v>
+        <v>6940</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>44.95798319327731</v>
+        <v>29.82708933717579</v>
       </c>
       <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="5" t="n">
-        <v>215000</v>
+        <v>6260</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>60.46511627906976</v>
+        <v>43.9297124600639</v>
       </c>
       <c r="U38" s="7" t="inlineStr"/>
       <c r="V38" s="7" t="inlineStr"/>
@@ -3372,12 +3372,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3392,45 +3392,45 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.2%</t>
+          <t>1차 매수선까지 18.8%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>179500</v>
+        <v>15950</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>176100</v>
+        <v>15860</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>181400</v>
+        <v>16250</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>175475</v>
+        <v>17111.5</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>140380</v>
+        <v>13689.2</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>138900</v>
+        <v>13430</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>29.22966162706984</v>
+        <v>18.76396128071482</v>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr"/>
       <c r="O39" s="5" t="n">
-        <v>125200</v>
+        <v>12100</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>43.37060702875399</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="Q39" s="7" t="inlineStr"/>
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="5" t="n">
-        <v>112800</v>
+        <v>10900</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>59.13120567375887</v>
+        <v>46.3302752293578</v>
       </c>
       <c r="U39" s="7" t="inlineStr"/>
       <c r="V39" s="7" t="inlineStr"/>
@@ -3446,12 +3446,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3466,45 +3466,45 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.0%</t>
+          <t>1차 매수선까지 60.9%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>198600</v>
+        <v>434500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>181700</v>
+        <v>358000</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>214000</v>
+        <v>453500</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>184520</v>
+        <v>339700</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>147616</v>
+        <v>271760</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>146000</v>
+        <v>270000</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>36.02739726027397</v>
+        <v>60.92592592592593</v>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="7" t="inlineStr"/>
       <c r="O40" s="5" t="n">
-        <v>131500</v>
+        <v>243500</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>51.02661596958175</v>
+        <v>78.43942505133469</v>
       </c>
       <c r="Q40" s="7" t="inlineStr"/>
       <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="5" t="n">
-        <v>118500</v>
+        <v>220000</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>67.59493670886076</v>
+        <v>97.5</v>
       </c>
       <c r="U40" s="7" t="inlineStr"/>
       <c r="V40" s="7" t="inlineStr"/>
@@ -3520,12 +3520,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3540,45 +3540,45 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.7%</t>
+          <t>1차 매수선까지 26.7%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>221500</v>
+        <v>175800</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>214500</v>
+        <v>174500</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>224500</v>
+        <v>177300</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>210215</v>
+        <v>175300</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>168172</v>
+        <v>140240</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>165700</v>
+        <v>138700</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>33.67531683765842</v>
+        <v>26.74837779379957</v>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr"/>
       <c r="O41" s="5" t="n">
-        <v>149300</v>
+        <v>125000</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>48.35900870730074</v>
+        <v>40.64</v>
       </c>
       <c r="Q41" s="7" t="inlineStr"/>
       <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="5" t="n">
-        <v>134500</v>
+        <v>112600</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>64.68401486988847</v>
+        <v>56.12788632326821</v>
       </c>
       <c r="U41" s="7" t="inlineStr"/>
       <c r="V41" s="7" t="inlineStr"/>
@@ -3594,12 +3594,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3614,45 +3614,45 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.8%</t>
+          <t>1차 매수선까지 85.3%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>8860</v>
+        <v>278000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>8810</v>
+        <v>233500</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>9190</v>
+        <v>284500</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>9466</v>
+        <v>190200</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>7572.8</v>
+        <v>152160</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>7460</v>
+        <v>150000</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>18.76675603217158</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr"/>
       <c r="O42" s="5" t="n">
-        <v>6730</v>
+        <v>135100</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>31.64933135215453</v>
+        <v>105.7735011102887</v>
       </c>
       <c r="Q42" s="7" t="inlineStr"/>
       <c r="R42" s="7" t="inlineStr"/>
       <c r="S42" s="5" t="n">
-        <v>6070</v>
+        <v>121700</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>45.96375617792422</v>
+        <v>128.430566967954</v>
       </c>
       <c r="U42" s="7" t="inlineStr"/>
       <c r="V42" s="7" t="inlineStr"/>
@@ -3668,12 +3668,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3688,45 +3688,45 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 72.9%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>85400</v>
+        <v>234000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>83900</v>
+        <v>221000</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>88300</v>
+        <v>238500</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>61660</v>
+        <v>210815</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>49328</v>
+        <v>168652</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>49400</v>
+        <v>166600</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>72.8744939271255</v>
+        <v>40.45618247298919</v>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr"/>
       <c r="O43" s="5" t="n">
-        <v>44550</v>
+        <v>150100</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>91.69472502805837</v>
+        <v>55.89606928714191</v>
       </c>
       <c r="Q43" s="7" t="inlineStr"/>
       <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="5" t="n">
-        <v>40150</v>
+        <v>135200</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>112.7023661270237</v>
+        <v>73.07692307692307</v>
       </c>
       <c r="U43" s="7" t="inlineStr"/>
       <c r="V43" s="7" t="inlineStr"/>
@@ -3742,12 +3742,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3762,45 +3762,45 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.0%</t>
+          <t>1차 매수선까지 10.7%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>102600</v>
+        <v>8060</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>100600</v>
+        <v>8030</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>105500</v>
+        <v>8350</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>103060</v>
+        <v>9235.5</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>82448</v>
+        <v>7388.400000000001</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>81400</v>
+        <v>7280</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>26.04422604422604</v>
+        <v>10.71428571428571</v>
       </c>
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="7" t="inlineStr"/>
       <c r="O44" s="5" t="n">
-        <v>73400</v>
+        <v>6570</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>39.78201634877384</v>
+        <v>22.67884322678843</v>
       </c>
       <c r="Q44" s="7" t="inlineStr"/>
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="5" t="n">
-        <v>66200</v>
+        <v>5930</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>54.98489425981873</v>
+        <v>35.91905564924115</v>
       </c>
       <c r="U44" s="7" t="inlineStr"/>
       <c r="V44" s="7" t="inlineStr"/>
@@ -3816,12 +3816,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3836,45 +3836,45 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.4%</t>
+          <t>1차 매수선까지 64.3%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>174000</v>
+        <v>86900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>172700</v>
+        <v>84800</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>182900</v>
+        <v>90800</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>186720</v>
+        <v>65667.5</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>149376</v>
+        <v>52534</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>146900</v>
+        <v>52900</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>18.44792375765827</v>
+        <v>64.27221172022685</v>
       </c>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr"/>
       <c r="O45" s="5" t="n">
-        <v>132400</v>
+        <v>47700</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>31.41993957703927</v>
+        <v>82.18029350104821</v>
       </c>
       <c r="Q45" s="7" t="inlineStr"/>
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="5" t="n">
-        <v>119300</v>
+        <v>43000</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>45.85079631181894</v>
+        <v>102.0930232558139</v>
       </c>
       <c r="U45" s="7" t="inlineStr"/>
       <c r="V45" s="7" t="inlineStr"/>
@@ -3890,12 +3890,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3910,45 +3910,45 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.4%</t>
+          <t>1차 매수선까지 27.9%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>435500</v>
+        <v>103700</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>431000</v>
+        <v>102500</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>442000</v>
+        <v>108000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>435200</v>
+        <v>102710</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>348160</v>
+        <v>82168</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>344500</v>
+        <v>81100</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>26.41509433962264</v>
+        <v>27.86683107274969</v>
       </c>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr"/>
       <c r="O46" s="5" t="n">
-        <v>311000</v>
+        <v>73100</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>40.03215434083602</v>
+        <v>41.86046511627907</v>
       </c>
       <c r="Q46" s="7" t="inlineStr"/>
       <c r="R46" s="7" t="inlineStr"/>
       <c r="S46" s="5" t="n">
-        <v>280500</v>
+        <v>65900</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>55.2584670231729</v>
+        <v>57.35963581183612</v>
       </c>
       <c r="U46" s="7" t="inlineStr"/>
       <c r="V46" s="7" t="inlineStr"/>
@@ -3964,12 +3964,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3984,45 +3984,45 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.5%</t>
+          <t>1차 매수선까지 16.1%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>22000</v>
+        <v>167000</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>21300</v>
+        <v>165100</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>22450</v>
+        <v>172400</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>23000</v>
+        <v>182965</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>18400</v>
+        <v>146372</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>18110</v>
+        <v>143900</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>21.47984538928769</v>
+        <v>16.05281445448228</v>
       </c>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
       <c r="O47" s="5" t="n">
-        <v>16310</v>
+        <v>129700</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>34.88657265481299</v>
+        <v>28.75867386276022</v>
       </c>
       <c r="Q47" s="7" t="inlineStr"/>
       <c r="R47" s="7" t="inlineStr"/>
       <c r="S47" s="5" t="n">
-        <v>14690</v>
+        <v>116900</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>49.76174268209667</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="U47" s="7" t="inlineStr"/>
       <c r="V47" s="7" t="inlineStr"/>
@@ -4038,12 +4038,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4058,45 +4058,45 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.3%</t>
+          <t>1차 매수선까지 26.6%</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>22800</v>
+        <v>435500</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>22050</v>
+        <v>430000</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>23600</v>
+        <v>436500</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>21542</v>
+        <v>434500</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>17233.6</v>
+        <v>347600</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>17100</v>
+        <v>344000</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>33.33333333333333</v>
+        <v>26.59883720930232</v>
       </c>
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="7" t="inlineStr"/>
       <c r="O48" s="5" t="n">
-        <v>15400</v>
+        <v>310500</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>48.05194805194805</v>
+        <v>40.25764895330113</v>
       </c>
       <c r="Q48" s="7" t="inlineStr"/>
       <c r="R48" s="7" t="inlineStr"/>
       <c r="S48" s="5" t="n">
-        <v>13870</v>
+        <v>280000</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>64.38356164383562</v>
+        <v>55.53571428571429</v>
       </c>
       <c r="U48" s="7" t="inlineStr"/>
       <c r="V48" s="7" t="inlineStr"/>
@@ -4112,12 +4112,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4132,45 +4132,45 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.4%</t>
+          <t>1차 매수선까지 18.6%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>52100</v>
+        <v>21200</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>52000</v>
+        <v>21050</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>54300</v>
+        <v>21850</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>51260</v>
+        <v>22647.5</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>41008</v>
+        <v>18118</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>40250</v>
+        <v>17880</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>29.44099378881987</v>
+        <v>18.56823266219239</v>
       </c>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
       <c r="O49" s="5" t="n">
-        <v>36300</v>
+        <v>16110</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>43.52617079889807</v>
+        <v>31.59528243327126</v>
       </c>
       <c r="Q49" s="7" t="inlineStr"/>
       <c r="R49" s="7" t="inlineStr"/>
       <c r="S49" s="5" t="n">
-        <v>32750</v>
+        <v>14510</v>
       </c>
       <c r="T49" s="6" t="n">
-        <v>59.08396946564886</v>
+        <v>46.10613370089594</v>
       </c>
       <c r="U49" s="7" t="inlineStr"/>
       <c r="V49" s="7" t="inlineStr"/>
@@ -4186,12 +4186,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4206,45 +4206,45 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.6%</t>
+          <t>1차 매수선까지 27.9%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>49150</v>
+        <v>22050</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>47500</v>
+        <v>21500</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>49850</v>
+        <v>22350</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>47002.5</v>
+        <v>21717</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>37602</v>
+        <v>17373.6</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>37350</v>
+        <v>17240</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>31.59303882195448</v>
+        <v>27.90023201856148</v>
       </c>
       <c r="M50" s="7" t="inlineStr"/>
       <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="5" t="n">
-        <v>33700</v>
+        <v>15530</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>45.84569732937685</v>
+        <v>41.98325820991629</v>
       </c>
       <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="7" t="inlineStr"/>
       <c r="S50" s="5" t="n">
-        <v>30400</v>
+        <v>13990</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>61.67763157894737</v>
+        <v>57.61258041458185</v>
       </c>
       <c r="U50" s="7" t="inlineStr"/>
       <c r="V50" s="7" t="inlineStr"/>
@@ -4260,12 +4260,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4280,45 +4280,45 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.6%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>22850</v>
+        <v>53200</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>22550</v>
+        <v>52000</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>23375</v>
+        <v>54600</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>24000</v>
+        <v>51265</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>19200</v>
+        <v>41012</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>18940</v>
+        <v>40450</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>20.6441393875396</v>
+        <v>31.5203955500618</v>
       </c>
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="7" t="inlineStr"/>
       <c r="O51" s="5" t="n">
-        <v>17060</v>
+        <v>36500</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>33.9390386869871</v>
+        <v>45.75342465753425</v>
       </c>
       <c r="Q51" s="7" t="inlineStr"/>
       <c r="R51" s="7" t="inlineStr"/>
       <c r="S51" s="5" t="n">
-        <v>15370</v>
+        <v>32900</v>
       </c>
       <c r="T51" s="6" t="n">
-        <v>48.66623292127521</v>
+        <v>61.70212765957447</v>
       </c>
       <c r="U51" s="7" t="inlineStr"/>
       <c r="V51" s="7" t="inlineStr"/>
@@ -4334,12 +4334,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4354,45 +4354,45 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.2%</t>
+          <t>1차 매수선까지 30.0%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>478000</v>
+        <v>49400</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>445500</v>
+        <v>48250</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>481500</v>
+        <v>50400</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>429300</v>
+        <v>47672.5</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>343440</v>
+        <v>38138</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>341000</v>
+        <v>38000</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>40.17595307917888</v>
+        <v>30</v>
       </c>
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="5" t="n">
-        <v>307500</v>
+        <v>34250</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>55.44715447154471</v>
+        <v>44.23357664233576</v>
       </c>
       <c r="Q52" s="7" t="inlineStr"/>
       <c r="R52" s="7" t="inlineStr"/>
       <c r="S52" s="5" t="n">
-        <v>277500</v>
+        <v>30900</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>72.25225225225225</v>
+        <v>59.8705501618123</v>
       </c>
       <c r="U52" s="7" t="inlineStr"/>
       <c r="V52" s="7" t="inlineStr"/>
@@ -4408,12 +4408,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4428,45 +4428,45 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.1%</t>
+          <t>1차 매수선까지 21.3%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>248000</v>
+        <v>22700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>230000</v>
+        <v>22000</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>249500</v>
+        <v>23100</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>213740</v>
+        <v>23712.5</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>170992</v>
+        <v>18970</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>169800</v>
+        <v>18720</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>46.05418138987044</v>
+        <v>21.26068376068376</v>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="5" t="n">
-        <v>153000</v>
+        <v>16860</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>62.09150326797386</v>
+        <v>34.63819691577699</v>
       </c>
       <c r="Q53" s="7" t="inlineStr"/>
       <c r="R53" s="7" t="inlineStr"/>
       <c r="S53" s="5" t="n">
-        <v>137800</v>
+        <v>15190</v>
       </c>
       <c r="T53" s="6" t="n">
-        <v>79.97097242380261</v>
+        <v>49.44042132982226</v>
       </c>
       <c r="U53" s="7" t="inlineStr"/>
       <c r="V53" s="7" t="inlineStr"/>
@@ -4482,12 +4482,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4502,45 +4502,45 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 56.7%</t>
+          <t>1차 매수선까지 37.5%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>2007000</v>
+        <v>477000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1915000</v>
+        <v>451500</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>2015000</v>
+        <v>484000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>1604450</v>
+        <v>436325</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1283560</v>
+        <v>349060</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1281000</v>
+        <v>347000</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>56.67447306791568</v>
+        <v>37.46397694524496</v>
       </c>
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="7" t="inlineStr"/>
       <c r="O54" s="5" t="n">
-        <v>1154000</v>
+        <v>313000</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>73.91681109185441</v>
+        <v>52.39616613418531</v>
       </c>
       <c r="Q54" s="7" t="inlineStr"/>
       <c r="R54" s="7" t="inlineStr"/>
       <c r="S54" s="5" t="n">
-        <v>1040000</v>
+        <v>282500</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>92.98076923076923</v>
+        <v>68.84955752212389</v>
       </c>
       <c r="U54" s="7" t="inlineStr"/>
       <c r="V54" s="7" t="inlineStr"/>
@@ -4556,12 +4556,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4576,45 +4576,45 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.7%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>510000</v>
+        <v>244000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>500000</v>
+        <v>232000</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>519000</v>
+        <v>246000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>478450</v>
+        <v>218130</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>382760</v>
+        <v>174504</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>378500</v>
+        <v>173700</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>34.74240422721268</v>
+        <v>40.4720782959125</v>
       </c>
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="7" t="inlineStr"/>
       <c r="O55" s="5" t="n">
-        <v>341500</v>
+        <v>156500</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>49.34114202049781</v>
+        <v>55.91054313099042</v>
       </c>
       <c r="Q55" s="7" t="inlineStr"/>
       <c r="R55" s="7" t="inlineStr"/>
       <c r="S55" s="5" t="n">
-        <v>308000</v>
+        <v>141000</v>
       </c>
       <c r="T55" s="6" t="n">
-        <v>65.58441558441559</v>
+        <v>73.04964539007092</v>
       </c>
       <c r="U55" s="7" t="inlineStr"/>
       <c r="V55" s="7" t="inlineStr"/>
@@ -4630,12 +4630,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4650,45 +4650,45 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.7%</t>
+          <t>1차 매수선까지 69.9%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>43650</v>
+        <v>2300000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>42800</v>
+        <v>2102000</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>45000</v>
+        <v>2414000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>41857.5</v>
+        <v>1691500</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>33486</v>
+        <v>1353200</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>33150</v>
+        <v>1354000</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>31.67420814479638</v>
+        <v>69.86706056129985</v>
       </c>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="5" t="n">
-        <v>29900</v>
+        <v>1220000</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>45.9866220735786</v>
+        <v>88.52459016393442</v>
       </c>
       <c r="Q56" s="7" t="inlineStr"/>
       <c r="R56" s="7" t="inlineStr"/>
       <c r="S56" s="5" t="n">
-        <v>27000</v>
+        <v>1099000</v>
       </c>
       <c r="T56" s="6" t="n">
-        <v>61.66666666666667</v>
+        <v>109.2811646951774</v>
       </c>
       <c r="U56" s="7" t="inlineStr"/>
       <c r="V56" s="7" t="inlineStr"/>
@@ -4704,12 +4704,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4724,45 +4724,45 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.0%</t>
+          <t>1차 매수선까지 36.8%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>16660</v>
+        <v>519000</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>16410</v>
+        <v>510000</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>17000</v>
+        <v>534000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>17338.5</v>
+        <v>480675</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>13870.8</v>
+        <v>384540</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>13660</v>
+        <v>379500</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>21.96193265007321</v>
+        <v>36.75889328063241</v>
       </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="5" t="n">
-        <v>12310</v>
+        <v>342500</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>35.33712428919578</v>
+        <v>51.53284671532846</v>
       </c>
       <c r="Q57" s="7" t="inlineStr"/>
       <c r="R57" s="7" t="inlineStr"/>
       <c r="S57" s="5" t="n">
-        <v>11090</v>
+        <v>309000</v>
       </c>
       <c r="T57" s="6" t="n">
-        <v>50.22542831379621</v>
+        <v>67.96116504854369</v>
       </c>
       <c r="U57" s="7" t="inlineStr"/>
       <c r="V57" s="7" t="inlineStr"/>
@@ -4778,12 +4778,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4798,45 +4798,45 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.4%</t>
+          <t>1차 매수선까지 23.8%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>93600</v>
+        <v>41100</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>91800</v>
+        <v>40750</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>96000</v>
+        <v>42000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>90715</v>
+        <v>41845</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>72572</v>
+        <v>33476</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>71800</v>
+        <v>33200</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>30.36211699164346</v>
+        <v>23.79518072289157</v>
       </c>
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="7" t="inlineStr"/>
       <c r="O58" s="5" t="n">
-        <v>64800</v>
+        <v>29950</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>44.44444444444444</v>
+        <v>37.22871452420701</v>
       </c>
       <c r="Q58" s="7" t="inlineStr"/>
       <c r="R58" s="7" t="inlineStr"/>
       <c r="S58" s="5" t="n">
-        <v>58500</v>
+        <v>27050</v>
       </c>
       <c r="T58" s="6" t="n">
-        <v>60</v>
+        <v>51.94085027726432</v>
       </c>
       <c r="U58" s="7" t="inlineStr"/>
       <c r="V58" s="7" t="inlineStr"/>
@@ -4852,12 +4852,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.5%</t>
+          <t>1차 매수선까지 17.6%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>14560</v>
+        <v>15900</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>14250</v>
+        <v>15540</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>14790</v>
+        <v>16070</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>14409.5</v>
+        <v>17086.5</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>11527.6</v>
+        <v>13669.2</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>11420</v>
+        <v>13520</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>27.49562171628722</v>
+        <v>17.60355029585799</v>
       </c>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="5" t="n">
-        <v>10290</v>
+        <v>12180</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>41.49659863945578</v>
+        <v>30.54187192118227</v>
       </c>
       <c r="Q59" s="7" t="inlineStr"/>
       <c r="R59" s="7" t="inlineStr"/>
       <c r="S59" s="5" t="n">
-        <v>9280</v>
+        <v>10980</v>
       </c>
       <c r="T59" s="6" t="n">
-        <v>56.89655172413794</v>
+        <v>44.80874316939891</v>
       </c>
       <c r="U59" s="7" t="inlineStr"/>
       <c r="V59" s="7" t="inlineStr"/>
@@ -4926,12 +4926,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4946,45 +4946,45 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.2%</t>
+          <t>1차 매수선까지 39.9%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>77600</v>
+        <v>100900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>76900</v>
+        <v>92100</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>79300</v>
+        <v>101400</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>78365</v>
+        <v>91195</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>62692</v>
+        <v>72956</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>62000</v>
+        <v>72100</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>25.16129032258064</v>
+        <v>39.94452149791955</v>
       </c>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
       <c r="O60" s="5" t="n">
-        <v>55900</v>
+        <v>65000</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>38.81932021466905</v>
+        <v>55.23076923076923</v>
       </c>
       <c r="Q60" s="7" t="inlineStr"/>
       <c r="R60" s="7" t="inlineStr"/>
       <c r="S60" s="5" t="n">
-        <v>50500</v>
+        <v>58600</v>
       </c>
       <c r="T60" s="6" t="n">
-        <v>53.66336633663366</v>
+        <v>72.18430034129693</v>
       </c>
       <c r="U60" s="7" t="inlineStr"/>
       <c r="V60" s="7" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5020,45 +5020,45 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 28.5%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>240000</v>
+        <v>14680</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>237000</v>
+        <v>13830</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>247500</v>
+        <v>14950</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>243650</v>
+        <v>14425</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>194920</v>
+        <v>11540</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>193700</v>
+        <v>11420</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>23.902942694889</v>
+        <v>28.54640980735552</v>
       </c>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
       <c r="O61" s="5" t="n">
-        <v>174500</v>
+        <v>10290</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>37.53581661891118</v>
+        <v>42.66277939747328</v>
       </c>
       <c r="Q61" s="7" t="inlineStr"/>
       <c r="R61" s="7" t="inlineStr"/>
       <c r="S61" s="5" t="n">
-        <v>157200</v>
+        <v>9280</v>
       </c>
       <c r="T61" s="6" t="n">
-        <v>52.67175572519084</v>
+        <v>58.18965517241379</v>
       </c>
       <c r="U61" s="7" t="inlineStr"/>
       <c r="V61" s="7" t="inlineStr"/>
@@ -5074,12 +5074,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5094,45 +5094,45 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.3%</t>
+          <t>1차 매수선까지 20.1%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>118400</v>
+        <v>74100</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>113500</v>
+        <v>73900</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>118400</v>
+        <v>76400</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>105765</v>
+        <v>77930</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>84612</v>
+        <v>62344</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>83800</v>
+        <v>61700</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>41.28878281622912</v>
+        <v>20.09724473257699</v>
       </c>
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr"/>
       <c r="O62" s="5" t="n">
-        <v>75600</v>
+        <v>55700</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>56.61375661375661</v>
+        <v>33.03411131059246</v>
       </c>
       <c r="Q62" s="7" t="inlineStr"/>
       <c r="R62" s="7" t="inlineStr"/>
       <c r="S62" s="5" t="n">
-        <v>68200</v>
+        <v>50300</v>
       </c>
       <c r="T62" s="6" t="n">
-        <v>73.60703812316716</v>
+        <v>47.31610337972167</v>
       </c>
       <c r="U62" s="7" t="inlineStr"/>
       <c r="V62" s="7" t="inlineStr"/>
@@ -5148,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5168,45 +5168,45 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.1%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>1003000</v>
+        <v>257000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>980000</v>
+        <v>250500</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>1018000</v>
+        <v>262500</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>1014650</v>
+        <v>246825</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>811720</v>
+        <v>197460</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>802000</v>
+        <v>195400</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>25.06234413965087</v>
+        <v>31.52507676560901</v>
       </c>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="7" t="inlineStr"/>
       <c r="O63" s="5" t="n">
-        <v>723000</v>
+        <v>176000</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>38.72752420470263</v>
+        <v>46.02272727272727</v>
       </c>
       <c r="Q63" s="7" t="inlineStr"/>
       <c r="R63" s="7" t="inlineStr"/>
       <c r="S63" s="5" t="n">
-        <v>652000</v>
+        <v>158500</v>
       </c>
       <c r="T63" s="6" t="n">
-        <v>53.83435582822086</v>
+        <v>62.14511041009464</v>
       </c>
       <c r="U63" s="7" t="inlineStr"/>
       <c r="V63" s="7" t="inlineStr"/>
@@ -5222,12 +5222,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5242,45 +5242,45 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.9%</t>
+          <t>1차 매수선까지 36.5%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>56300</v>
+        <v>115900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>54300</v>
+        <v>113900</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>56600</v>
+        <v>118900</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>56170</v>
+        <v>106930</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>44936</v>
+        <v>85544</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>44350</v>
+        <v>84900</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>26.94475760992108</v>
+        <v>36.51354534746761</v>
       </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="5" t="n">
-        <v>40000</v>
+        <v>76600</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>40.75</v>
+        <v>51.30548302872062</v>
       </c>
       <c r="Q64" s="7" t="inlineStr"/>
       <c r="R64" s="7" t="inlineStr"/>
       <c r="S64" s="5" t="n">
-        <v>36050</v>
+        <v>69100</v>
       </c>
       <c r="T64" s="6" t="n">
-        <v>56.17198335644937</v>
+        <v>67.72793053545585</v>
       </c>
       <c r="U64" s="7" t="inlineStr"/>
       <c r="V64" s="7" t="inlineStr"/>
@@ -5296,12 +5296,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5316,45 +5316,45 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>30900</v>
+        <v>989000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>30550</v>
+        <v>976000</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>32600</v>
+        <v>1007000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>29615</v>
+        <v>1009350</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>23692</v>
+        <v>807480</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>23500</v>
+        <v>798000</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>31.48936170212766</v>
+        <v>23.93483709273183</v>
       </c>
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="7" t="inlineStr"/>
       <c r="O65" s="5" t="n">
-        <v>21200</v>
+        <v>720000</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>45.75471698113208</v>
+        <v>37.36111111111111</v>
       </c>
       <c r="Q65" s="7" t="inlineStr"/>
       <c r="R65" s="7" t="inlineStr"/>
       <c r="S65" s="5" t="n">
-        <v>19090</v>
+        <v>649000</v>
       </c>
       <c r="T65" s="6" t="n">
-        <v>61.86485070717653</v>
+        <v>52.38828967642527</v>
       </c>
       <c r="U65" s="7" t="inlineStr"/>
       <c r="V65" s="7" t="inlineStr"/>
@@ -5370,12 +5370,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5390,45 +5390,45 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.0%</t>
+          <t>1차 매수선까지 29.4%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>231500</v>
+        <v>30600</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>224000</v>
+        <v>29800</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>240000</v>
+        <v>31250</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>208325</v>
+        <v>29765</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>166660</v>
+        <v>23812</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>165400</v>
+        <v>23650</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>39.96372430471584</v>
+        <v>29.38689217758985</v>
       </c>
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="7" t="inlineStr"/>
       <c r="O66" s="5" t="n">
-        <v>149000</v>
+        <v>21350</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>55.36912751677853</v>
+        <v>43.32552693208431</v>
       </c>
       <c r="Q66" s="7" t="inlineStr"/>
       <c r="R66" s="7" t="inlineStr"/>
       <c r="S66" s="5" t="n">
-        <v>134200</v>
+        <v>19230</v>
       </c>
       <c r="T66" s="6" t="n">
-        <v>72.50372578241431</v>
+        <v>59.12636505460218</v>
       </c>
       <c r="U66" s="7" t="inlineStr"/>
       <c r="V66" s="7" t="inlineStr"/>
@@ -5444,12 +5444,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5464,45 +5464,45 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.0%</t>
+          <t>1차 매수선까지 43.4%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>52100</v>
+        <v>242000</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>51700</v>
+        <v>223500</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>54000</v>
+        <v>248000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>53130</v>
+        <v>212260</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>42504</v>
+        <v>169808</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>42000</v>
+        <v>168700</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>24.04761904761905</v>
+        <v>43.44991108476586</v>
       </c>
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="5" t="n">
-        <v>37850</v>
+        <v>152000</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>37.64861294583884</v>
+        <v>59.21052631578947</v>
       </c>
       <c r="Q67" s="7" t="inlineStr"/>
       <c r="R67" s="7" t="inlineStr"/>
       <c r="S67" s="5" t="n">
-        <v>34150</v>
+        <v>136900</v>
       </c>
       <c r="T67" s="6" t="n">
-        <v>52.56222547584187</v>
+        <v>76.77136596055514</v>
       </c>
       <c r="U67" s="7" t="inlineStr"/>
       <c r="V67" s="7" t="inlineStr"/>
@@ -5518,12 +5518,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5538,45 +5538,45 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 19.5%</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>17400</v>
+        <v>49950</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>16680</v>
+        <v>48850</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>18310</v>
+        <v>51500</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>15627.5</v>
+        <v>52782.5</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>12502</v>
+        <v>42226</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>12380</v>
+        <v>41800</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>40.54927302100161</v>
+        <v>19.49760765550239</v>
       </c>
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="7" t="inlineStr"/>
       <c r="O68" s="5" t="n">
-        <v>11160</v>
+        <v>37700</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>55.91397849462365</v>
+        <v>32.49336870026525</v>
       </c>
       <c r="Q68" s="7" t="inlineStr"/>
       <c r="R68" s="7" t="inlineStr"/>
       <c r="S68" s="5" t="n">
-        <v>10060</v>
+        <v>34000</v>
       </c>
       <c r="T68" s="6" t="n">
-        <v>72.96222664015905</v>
+        <v>46.91176470588236</v>
       </c>
       <c r="U68" s="7" t="inlineStr"/>
       <c r="V68" s="7" t="inlineStr"/>
@@ -5592,12 +5592,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5612,45 +5612,45 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.2%</t>
+          <t>1차 매수선까지 22.9%</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>28950</v>
+        <v>15250</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>28650</v>
+        <v>15070</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>29950</v>
+        <v>16400</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>29482.5</v>
+        <v>15643.5</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>23586</v>
+        <v>12514.8</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>23300</v>
+        <v>12410</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>24.24892703862661</v>
+        <v>22.88477034649476</v>
       </c>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr"/>
       <c r="O69" s="5" t="n">
-        <v>21050</v>
+        <v>11180</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>37.52969121140142</v>
+        <v>36.40429338103757</v>
       </c>
       <c r="Q69" s="7" t="inlineStr"/>
       <c r="R69" s="7" t="inlineStr"/>
       <c r="S69" s="5" t="n">
-        <v>18960</v>
+        <v>10080</v>
       </c>
       <c r="T69" s="6" t="n">
-        <v>52.68987341772152</v>
+        <v>51.28968253968254</v>
       </c>
       <c r="U69" s="7" t="inlineStr"/>
       <c r="V69" s="7" t="inlineStr"/>
@@ -5666,12 +5666,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5686,45 +5686,45 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.2%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>2570</v>
+        <v>28150</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>2550</v>
+        <v>27700</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>2715</v>
+        <v>28450</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>2437.95</v>
+        <v>29257.5</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>1950.36</v>
+        <v>23406</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>1929</v>
+        <v>23150</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>33.22965266977709</v>
+        <v>21.59827213822894</v>
       </c>
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="7" t="inlineStr"/>
       <c r="O70" s="5" t="n">
-        <v>1738</v>
+        <v>20900</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>47.87111622554661</v>
+        <v>34.688995215311</v>
       </c>
       <c r="Q70" s="7" t="inlineStr"/>
       <c r="R70" s="7" t="inlineStr"/>
       <c r="S70" s="5" t="n">
-        <v>1566</v>
+        <v>18820</v>
       </c>
       <c r="T70" s="6" t="n">
-        <v>64.11238825031928</v>
+        <v>49.57492029755579</v>
       </c>
       <c r="U70" s="7" t="inlineStr"/>
       <c r="V70" s="7" t="inlineStr"/>
@@ -5740,12 +5740,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5760,45 +5760,45 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.6%</t>
+          <t>1차 매수선까지 25.3%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>7200</v>
+        <v>2415</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>7060</v>
+        <v>2410</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>7400</v>
+        <v>2535</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>7106.5</v>
+        <v>2433</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>5685.200000000001</v>
+        <v>1946.4</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>5600</v>
+        <v>1927</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>28.57142857142857</v>
+        <v>25.32433834976648</v>
       </c>
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr"/>
       <c r="O71" s="5" t="n">
-        <v>5050</v>
+        <v>1736</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>42.57425742574257</v>
+        <v>39.11290322580645</v>
       </c>
       <c r="Q71" s="7" t="inlineStr"/>
       <c r="R71" s="7" t="inlineStr"/>
       <c r="S71" s="5" t="n">
-        <v>4550</v>
+        <v>1564</v>
       </c>
       <c r="T71" s="6" t="n">
-        <v>58.24175824175825</v>
+        <v>54.41176470588235</v>
       </c>
       <c r="U71" s="7" t="inlineStr"/>
       <c r="V71" s="7" t="inlineStr"/>
@@ -5814,12 +5814,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5834,45 +5834,45 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.8%</t>
+          <t>1차 매수선까지 28.1%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>142000</v>
+        <v>7110</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>139600</v>
+        <v>7030</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>145200</v>
+        <v>7480</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>141765</v>
+        <v>7043</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>113412</v>
+        <v>5634.400000000001</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>112000</v>
+        <v>5550</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>26.78571428571428</v>
+        <v>28.10810810810811</v>
       </c>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
       <c r="O72" s="5" t="n">
-        <v>100900</v>
+        <v>5000</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>40.73339940535183</v>
+        <v>42.2</v>
       </c>
       <c r="Q72" s="7" t="inlineStr"/>
       <c r="R72" s="7" t="inlineStr"/>
       <c r="S72" s="5" t="n">
-        <v>91000</v>
+        <v>4505</v>
       </c>
       <c r="T72" s="6" t="n">
-        <v>56.04395604395604</v>
+        <v>57.82463928967814</v>
       </c>
       <c r="U72" s="7" t="inlineStr"/>
       <c r="V72" s="7" t="inlineStr"/>
@@ -5888,12 +5888,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5908,45 +5908,45 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 30.8%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>37150</v>
+        <v>146800</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>36950</v>
+        <v>140500</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>38000</v>
+        <v>146800</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>38525</v>
+        <v>141755</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>30820</v>
+        <v>113404</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>30550</v>
+        <v>112200</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>21.60392798690671</v>
+        <v>30.83778966131907</v>
       </c>
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="5" t="n">
-        <v>27550</v>
+        <v>101100</v>
       </c>
       <c r="P73" s="6" t="n">
-        <v>34.84573502722323</v>
+        <v>45.20276953511375</v>
       </c>
       <c r="Q73" s="7" t="inlineStr"/>
       <c r="R73" s="7" t="inlineStr"/>
       <c r="S73" s="5" t="n">
-        <v>24850</v>
+        <v>91100</v>
       </c>
       <c r="T73" s="6" t="n">
-        <v>49.49698189134809</v>
+        <v>61.14160263446762</v>
       </c>
       <c r="U73" s="7" t="inlineStr"/>
       <c r="V73" s="7" t="inlineStr"/>
@@ -5962,12 +5962,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -5982,45 +5982,45 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 14.6%</t>
+          <t>1차 매수선까지 18.1%</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>9010</v>
+        <v>35300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>8860</v>
+        <v>35000</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>9180</v>
+        <v>36000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>9976</v>
+        <v>38007.5</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>7980.8</v>
+        <v>30406</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>7860</v>
+        <v>29900</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>14.63104325699746</v>
+        <v>18.06020066889632</v>
       </c>
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr"/>
       <c r="O74" s="5" t="n">
-        <v>7090</v>
+        <v>27000</v>
       </c>
       <c r="P74" s="6" t="n">
-        <v>27.08039492242595</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="Q74" s="7" t="inlineStr"/>
       <c r="R74" s="7" t="inlineStr"/>
       <c r="S74" s="5" t="n">
-        <v>6400</v>
+        <v>24350</v>
       </c>
       <c r="T74" s="6" t="n">
-        <v>40.78125</v>
+        <v>44.96919917864476</v>
       </c>
       <c r="U74" s="7" t="inlineStr"/>
       <c r="V74" s="7" t="inlineStr"/>
@@ -6036,12 +6036,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6056,45 +6056,45 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.0%</t>
+          <t>1차 매수선까지 13.7%</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>275000</v>
+        <v>8730</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>266500</v>
+        <v>8570</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>282000</v>
+        <v>8910</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>244480</v>
+        <v>9764</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>195584</v>
+        <v>7811.200000000001</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>195100</v>
+        <v>7680</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>40.95335725269093</v>
+        <v>13.671875</v>
       </c>
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="7" t="inlineStr"/>
       <c r="O75" s="5" t="n">
-        <v>175700</v>
+        <v>6930</v>
       </c>
       <c r="P75" s="6" t="n">
-        <v>56.51678998292545</v>
+        <v>25.97402597402597</v>
       </c>
       <c r="Q75" s="7" t="inlineStr"/>
       <c r="R75" s="7" t="inlineStr"/>
       <c r="S75" s="5" t="n">
-        <v>158300</v>
+        <v>6250</v>
       </c>
       <c r="T75" s="6" t="n">
-        <v>73.72078332280481</v>
+        <v>39.68</v>
       </c>
       <c r="U75" s="7" t="inlineStr"/>
       <c r="V75" s="7" t="inlineStr"/>
@@ -6110,12 +6110,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6130,45 +6130,45 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.7%</t>
+          <t>1차 매수선까지 29.0%</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>328000</v>
+        <v>260000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>320500</v>
+        <v>251500</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>331500</v>
+        <v>283500</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>291800</v>
+        <v>251340</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>233440</v>
+        <v>201072</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>231500</v>
+        <v>201500</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>41.68466522678186</v>
+        <v>29.03225806451613</v>
       </c>
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="7" t="inlineStr"/>
       <c r="O76" s="5" t="n">
-        <v>209000</v>
+        <v>181500</v>
       </c>
       <c r="P76" s="6" t="n">
-        <v>56.9377990430622</v>
+        <v>43.25068870523416</v>
       </c>
       <c r="Q76" s="7" t="inlineStr"/>
       <c r="R76" s="7" t="inlineStr"/>
       <c r="S76" s="5" t="n">
-        <v>188200</v>
+        <v>163500</v>
       </c>
       <c r="T76" s="6" t="n">
-        <v>74.28267800212541</v>
+        <v>59.02140672782875</v>
       </c>
       <c r="U76" s="7" t="inlineStr"/>
       <c r="V76" s="7" t="inlineStr"/>
@@ -6184,12 +6184,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -6204,45 +6204,45 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.7%</t>
+          <t>1차 매수선까지 32.6%</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>111400</v>
+        <v>311500</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>108000</v>
+        <v>310000</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>120000</v>
+        <v>318500</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>99140</v>
+        <v>295400</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>79312</v>
+        <v>236320</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>78600</v>
+        <v>235000</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>41.73027989821883</v>
+        <v>32.5531914893617</v>
       </c>
       <c r="M77" s="7" t="inlineStr"/>
       <c r="N77" s="7" t="inlineStr"/>
       <c r="O77" s="5" t="n">
-        <v>70900</v>
+        <v>212000</v>
       </c>
       <c r="P77" s="6" t="n">
-        <v>57.12270803949225</v>
+        <v>46.93396226415094</v>
       </c>
       <c r="Q77" s="7" t="inlineStr"/>
       <c r="R77" s="7" t="inlineStr"/>
       <c r="S77" s="5" t="n">
-        <v>64000</v>
+        <v>190900</v>
       </c>
       <c r="T77" s="6" t="n">
-        <v>74.0625</v>
+        <v>63.17443687794657</v>
       </c>
       <c r="U77" s="7" t="inlineStr"/>
       <c r="V77" s="7" t="inlineStr"/>
@@ -6258,12 +6258,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -6278,45 +6278,45 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.8%</t>
+          <t>1차 매수선까지 26.1%</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>101700</v>
+        <v>100000</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>95900</v>
+        <v>98900</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>101900</v>
+        <v>104400</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>89025</v>
+        <v>99740</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>71220</v>
+        <v>79792</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>70700</v>
+        <v>79300</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>43.84724186704385</v>
+        <v>26.10340479192938</v>
       </c>
       <c r="M78" s="7" t="inlineStr"/>
       <c r="N78" s="7" t="inlineStr"/>
       <c r="O78" s="5" t="n">
-        <v>63800</v>
+        <v>71500</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>59.40438871473355</v>
+        <v>39.86013986013986</v>
       </c>
       <c r="Q78" s="7" t="inlineStr"/>
       <c r="R78" s="7" t="inlineStr"/>
       <c r="S78" s="5" t="n">
-        <v>57600</v>
+        <v>64500</v>
       </c>
       <c r="T78" s="6" t="n">
-        <v>76.5625</v>
+        <v>55.03875968992248</v>
       </c>
       <c r="U78" s="7" t="inlineStr"/>
       <c r="V78" s="7" t="inlineStr"/>
@@ -6332,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6352,45 +6352,45 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.6%</t>
+          <t>1차 매수선까지 34.4%</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>251500</v>
+        <v>96400</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>242500</v>
+        <v>94500</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>256000</v>
+        <v>97900</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>225100</v>
+        <v>90180</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>180080</v>
+        <v>72144</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>178900</v>
+        <v>71700</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>40.58133035215204</v>
+        <v>34.44909344490934</v>
       </c>
       <c r="M79" s="7" t="inlineStr"/>
       <c r="N79" s="7" t="inlineStr"/>
       <c r="O79" s="5" t="n">
-        <v>161200</v>
+        <v>64700</v>
       </c>
       <c r="P79" s="6" t="n">
-        <v>56.01736972704715</v>
+        <v>48.99536321483771</v>
       </c>
       <c r="Q79" s="7" t="inlineStr"/>
       <c r="R79" s="7" t="inlineStr"/>
       <c r="S79" s="5" t="n">
-        <v>145200</v>
+        <v>58400</v>
       </c>
       <c r="T79" s="6" t="n">
-        <v>73.20936639118457</v>
+        <v>65.06849315068493</v>
       </c>
       <c r="U79" s="7" t="inlineStr"/>
       <c r="V79" s="7" t="inlineStr"/>
@@ -6406,12 +6406,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -6426,45 +6426,45 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 49.7%</t>
+          <t>1차 매수선까지 36.7%</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>136500</v>
+        <v>249000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>131400</v>
+        <v>243000</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>138300</v>
+        <v>250000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>114540</v>
+        <v>229025</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>91632</v>
+        <v>183220</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>91200</v>
+        <v>182200</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>49.67105263157895</v>
+        <v>36.66300768386389</v>
       </c>
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr"/>
       <c r="O80" s="5" t="n">
-        <v>82200</v>
+        <v>164100</v>
       </c>
       <c r="P80" s="6" t="n">
-        <v>66.05839416058394</v>
+        <v>51.73674588665448</v>
       </c>
       <c r="Q80" s="7" t="inlineStr"/>
       <c r="R80" s="7" t="inlineStr"/>
       <c r="S80" s="5" t="n">
-        <v>74100</v>
+        <v>147800</v>
       </c>
       <c r="T80" s="6" t="n">
-        <v>84.21052631578947</v>
+        <v>68.47090663058187</v>
       </c>
       <c r="U80" s="7" t="inlineStr"/>
       <c r="V80" s="7" t="inlineStr"/>
@@ -6476,6 +6476,80 @@
       <c r="AB80" s="7" t="inlineStr"/>
       <c r="AC80" s="7" t="inlineStr"/>
       <c r="AD80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 38.2%</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>129600</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>128500</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>137200</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>117585</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>94068</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>93800</v>
+      </c>
+      <c r="L81" s="6" t="n">
+        <v>38.16631130063966</v>
+      </c>
+      <c r="M81" s="7" t="inlineStr"/>
+      <c r="N81" s="7" t="inlineStr"/>
+      <c r="O81" s="5" t="n">
+        <v>84600</v>
+      </c>
+      <c r="P81" s="6" t="n">
+        <v>53.19148936170212</v>
+      </c>
+      <c r="Q81" s="7" t="inlineStr"/>
+      <c r="R81" s="7" t="inlineStr"/>
+      <c r="S81" s="5" t="n">
+        <v>76300</v>
+      </c>
+      <c r="T81" s="6" t="n">
+        <v>69.85583224115334</v>
+      </c>
+      <c r="U81" s="7" t="inlineStr"/>
+      <c r="V81" s="7" t="inlineStr"/>
+      <c r="W81" s="7" t="inlineStr"/>
+      <c r="X81" s="7" t="inlineStr"/>
+      <c r="Y81" s="7" t="inlineStr"/>
+      <c r="Z81" s="7" t="inlineStr"/>
+      <c r="AA81" s="7" t="inlineStr"/>
+      <c r="AB81" s="7" t="inlineStr"/>
+      <c r="AC81" s="7" t="inlineStr"/>
+      <c r="AD81" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AF82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,8 @@
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,110 +524,120 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>20일선</t>
+          <t>20일선(당일)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>-20%엔벨로프</t>
+          <t>20일선(익일)</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>1차매수선</t>
+          <t>-20%엔벨로프(당일)</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t>-20%엔벨로프(익일)</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수선(익일)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>1차매수선이격도(%)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>1차매수일</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1차매수가</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>2차매수선</t>
-        </is>
-      </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
+          <t>1차매수가(당일)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수선(익일)</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
           <t>2차매수선이격도(%)</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>2차매수일</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>2차매수가</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>3차매수선</t>
-        </is>
-      </c>
       <c r="T1" s="2" t="inlineStr">
         <is>
+          <t>2차매수가(당일)</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수선(익일)</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
           <t>3차매수선이격도(%)</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>3차매수일</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>3차매수가</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수가(당일)</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>평균매수가</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>1차매도선(+3%)</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>1차매도선이격도(%)</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>2차매도선(+5%)</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>2차매도선이격도(%)</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>3차매도선(+7%)</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>3차매도선이격도(%)</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>최고도달선</t>
         </is>
@@ -670,32 +682,36 @@
         <v>95910</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>97070</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>76728</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2" s="5" t="n">
+        <v>77656</v>
+      </c>
+      <c r="M2" s="5" t="n">
         <v>76500</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>40.78431372549019</v>
       </c>
-      <c r="M2" s="7" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
-      <c r="O2" s="5" t="n">
-        <v>69000</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>56.08695652173913</v>
-      </c>
-      <c r="Q2" s="7" t="inlineStr"/>
-      <c r="R2" s="7" t="inlineStr"/>
-      <c r="S2" s="5" t="n">
-        <v>62200</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>73.15112540192926</v>
-      </c>
-      <c r="U2" s="7" t="inlineStr"/>
-      <c r="V2" s="7" t="inlineStr"/>
+      <c r="O2" s="7" t="inlineStr"/>
+      <c r="P2" s="7" t="inlineStr"/>
+      <c r="Q2" s="5" t="n">
+        <v>68900</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>56.31349782293179</v>
+      </c>
+      <c r="S2" s="7" t="inlineStr"/>
+      <c r="T2" s="7" t="inlineStr"/>
+      <c r="U2" s="5" t="n">
+        <v>62100</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>73.42995169082126</v>
+      </c>
       <c r="W2" s="7" t="inlineStr"/>
       <c r="X2" s="7" t="inlineStr"/>
       <c r="Y2" s="7" t="inlineStr"/>
@@ -704,6 +720,8 @@
       <c r="AB2" s="7" t="inlineStr"/>
       <c r="AC2" s="7" t="inlineStr"/>
       <c r="AD2" s="7" t="inlineStr"/>
+      <c r="AE2" s="7" t="inlineStr"/>
+      <c r="AF2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -744,32 +762,36 @@
         <v>463025</v>
       </c>
       <c r="J3" s="5" t="n">
+        <v>473475</v>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>370420</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
+        <v>378780</v>
+      </c>
+      <c r="M3" s="5" t="n">
         <v>371500</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>50.74024226110363</v>
       </c>
-      <c r="M3" s="7" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="5" t="n">
-        <v>335000</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>67.16417910447761</v>
-      </c>
-      <c r="Q3" s="7" t="inlineStr"/>
-      <c r="R3" s="7" t="inlineStr"/>
-      <c r="S3" s="5" t="n">
-        <v>302000</v>
-      </c>
-      <c r="T3" s="6" t="n">
-        <v>85.43046357615894</v>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr"/>
+      <c r="Q3" s="5" t="n">
+        <v>334500</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>67.41405082212258</v>
+      </c>
+      <c r="S3" s="7" t="inlineStr"/>
+      <c r="T3" s="7" t="inlineStr"/>
+      <c r="U3" s="5" t="n">
+        <v>301500</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>85.7379767827529</v>
+      </c>
       <c r="W3" s="7" t="inlineStr"/>
       <c r="X3" s="7" t="inlineStr"/>
       <c r="Y3" s="7" t="inlineStr"/>
@@ -778,6 +800,8 @@
       <c r="AB3" s="7" t="inlineStr"/>
       <c r="AC3" s="7" t="inlineStr"/>
       <c r="AD3" s="7" t="inlineStr"/>
+      <c r="AE3" s="7" t="inlineStr"/>
+      <c r="AF3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -818,32 +842,36 @@
         <v>78450</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>79730</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>62760</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="L4" s="5" t="n">
+        <v>63784</v>
+      </c>
+      <c r="M4" s="5" t="n">
         <v>62800</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>41.40127388535032</v>
       </c>
-      <c r="M4" s="7" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
-      <c r="O4" s="5" t="n">
-        <v>56700</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>56.61375661375661</v>
-      </c>
-      <c r="Q4" s="7" t="inlineStr"/>
-      <c r="R4" s="7" t="inlineStr"/>
-      <c r="S4" s="5" t="n">
-        <v>51200</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>73.4375</v>
-      </c>
-      <c r="U4" s="7" t="inlineStr"/>
-      <c r="V4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr"/>
+      <c r="Q4" s="5" t="n">
+        <v>56600</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>56.8904593639576</v>
+      </c>
+      <c r="S4" s="7" t="inlineStr"/>
+      <c r="T4" s="7" t="inlineStr"/>
+      <c r="U4" s="5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>74.11764705882354</v>
+      </c>
       <c r="W4" s="7" t="inlineStr"/>
       <c r="X4" s="7" t="inlineStr"/>
       <c r="Y4" s="7" t="inlineStr"/>
@@ -852,6 +880,8 @@
       <c r="AB4" s="7" t="inlineStr"/>
       <c r="AC4" s="7" t="inlineStr"/>
       <c r="AD4" s="7" t="inlineStr"/>
+      <c r="AE4" s="7" t="inlineStr"/>
+      <c r="AF4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -892,32 +922,36 @@
         <v>120490</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>122010</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>96392</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5" s="5" t="n">
+        <v>97608</v>
+      </c>
+      <c r="M5" s="5" t="n">
         <v>96000</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>43.33333333333334</v>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="5" t="n">
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr"/>
+      <c r="Q5" s="5" t="n">
         <v>86500</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>59.07514450867052</v>
       </c>
-      <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
-      <c r="S5" s="5" t="n">
-        <v>78000</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>76.41025641025641</v>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
+      <c r="T5" s="7" t="inlineStr"/>
+      <c r="U5" s="5" t="n">
+        <v>77900</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>76.6367137355584</v>
+      </c>
       <c r="W5" s="7" t="inlineStr"/>
       <c r="X5" s="7" t="inlineStr"/>
       <c r="Y5" s="7" t="inlineStr"/>
@@ -926,6 +960,8 @@
       <c r="AB5" s="7" t="inlineStr"/>
       <c r="AC5" s="7" t="inlineStr"/>
       <c r="AD5" s="7" t="inlineStr"/>
+      <c r="AE5" s="7" t="inlineStr"/>
+      <c r="AF5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -966,32 +1002,36 @@
         <v>258250</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>257925</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>206600</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="L6" s="5" t="n">
+        <v>206340</v>
+      </c>
+      <c r="M6" s="5" t="n">
         <v>204000</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>32.59803921568628</v>
       </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-      <c r="O6" s="5" t="n">
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="5" t="n">
         <v>183700</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="R6" s="6" t="n">
         <v>47.2509526401742</v>
       </c>
-      <c r="Q6" s="7" t="inlineStr"/>
-      <c r="R6" s="7" t="inlineStr"/>
-      <c r="S6" s="5" t="n">
-        <v>165500</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>63.44410876132931</v>
-      </c>
-      <c r="U6" s="7" t="inlineStr"/>
-      <c r="V6" s="7" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="7" t="inlineStr"/>
+      <c r="U6" s="5" t="n">
+        <v>165400</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>63.54292623941959</v>
+      </c>
       <c r="W6" s="7" t="inlineStr"/>
       <c r="X6" s="7" t="inlineStr"/>
       <c r="Y6" s="7" t="inlineStr"/>
@@ -1000,6 +1040,8 @@
       <c r="AB6" s="7" t="inlineStr"/>
       <c r="AC6" s="7" t="inlineStr"/>
       <c r="AD6" s="7" t="inlineStr"/>
+      <c r="AE6" s="7" t="inlineStr"/>
+      <c r="AF6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1040,32 +1082,36 @@
         <v>253975</v>
       </c>
       <c r="J7" s="5" t="n">
+        <v>259825</v>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>203180</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
+        <v>207860</v>
+      </c>
+      <c r="M7" s="5" t="n">
         <v>203500</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>58.96805896805897</v>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="5" t="n">
-        <v>183300</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>76.48663393344245</v>
-      </c>
-      <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="5" t="n">
-        <v>165100</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>95.94185342216839</v>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="5" t="n">
+        <v>183200</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>76.58296943231441</v>
+      </c>
+      <c r="S7" s="7" t="inlineStr"/>
+      <c r="T7" s="7" t="inlineStr"/>
+      <c r="U7" s="5" t="n">
+        <v>164900</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>96.17950272892662</v>
+      </c>
       <c r="W7" s="7" t="inlineStr"/>
       <c r="X7" s="7" t="inlineStr"/>
       <c r="Y7" s="7" t="inlineStr"/>
@@ -1074,16 +1120,18 @@
       <c r="AB7" s="7" t="inlineStr"/>
       <c r="AC7" s="7" t="inlineStr"/>
       <c r="AD7" s="7" t="inlineStr"/>
+      <c r="AE7" s="7" t="inlineStr"/>
+      <c r="AF7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1098,48 +1146,52 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.5%</t>
+          <t>1차 매수선까지 48.8%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>141500</v>
+        <v>288000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>138900</v>
+        <v>267000</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>144800</v>
+        <v>294000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>132670</v>
+        <v>242925</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>106136</v>
+        <v>246550</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>106800</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>32.49063670411985</v>
-      </c>
-      <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="5" t="n">
-        <v>96300</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>46.93665628245067</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr"/>
-      <c r="R8" s="7" t="inlineStr"/>
-      <c r="S8" s="5" t="n">
-        <v>86800</v>
-      </c>
-      <c r="T8" s="6" t="n">
-        <v>63.0184331797235</v>
-      </c>
-      <c r="U8" s="7" t="inlineStr"/>
-      <c r="V8" s="7" t="inlineStr"/>
+        <v>194340</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>197240</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>193500</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>48.83720930232558</v>
+      </c>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="5" t="n">
+        <v>174200</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>65.32721010332951</v>
+      </c>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="5" t="n">
+        <v>156800</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>83.67346938775511</v>
+      </c>
       <c r="W8" s="7" t="inlineStr"/>
       <c r="X8" s="7" t="inlineStr"/>
       <c r="Y8" s="7" t="inlineStr"/>
@@ -1148,16 +1200,18 @@
       <c r="AB8" s="7" t="inlineStr"/>
       <c r="AC8" s="7" t="inlineStr"/>
       <c r="AD8" s="7" t="inlineStr"/>
+      <c r="AE8" s="7" t="inlineStr"/>
+      <c r="AF8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1172,48 +1226,52 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.8%</t>
+          <t>1차 매수선까지 32.5%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>288000</v>
+        <v>141500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>267000</v>
+        <v>138900</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>294000</v>
+        <v>144800</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>242925</v>
+        <v>132670</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>194340</v>
+        <v>135140</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>193500</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>48.83720930232558</v>
-      </c>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="5" t="n">
-        <v>174300</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>65.23235800344234</v>
-      </c>
-      <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="5" t="n">
-        <v>157000</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>83.43949044585987</v>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="inlineStr"/>
+        <v>106136</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>108112</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>106800</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>32.49063670411985</v>
+      </c>
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="5" t="n">
+        <v>96200</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>47.08939708939709</v>
+      </c>
+      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="5" t="n">
+        <v>86600</v>
+      </c>
+      <c r="V9" s="6" t="n">
+        <v>63.39491916859122</v>
+      </c>
       <c r="W9" s="7" t="inlineStr"/>
       <c r="X9" s="7" t="inlineStr"/>
       <c r="Y9" s="7" t="inlineStr"/>
@@ -1222,6 +1280,8 @@
       <c r="AB9" s="7" t="inlineStr"/>
       <c r="AC9" s="7" t="inlineStr"/>
       <c r="AD9" s="7" t="inlineStr"/>
+      <c r="AE9" s="7" t="inlineStr"/>
+      <c r="AF9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1262,32 +1322,36 @@
         <v>69475</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>71557.5</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>55580</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
+        <v>57246</v>
+      </c>
+      <c r="M10" s="5" t="n">
         <v>55900</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>60.82289803220036</v>
       </c>
-      <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
-      <c r="O10" s="5" t="n">
-        <v>50500</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>78.01980198019803</v>
-      </c>
-      <c r="Q10" s="7" t="inlineStr"/>
-      <c r="R10" s="7" t="inlineStr"/>
-      <c r="S10" s="5" t="n">
-        <v>45500</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>97.58241758241758</v>
-      </c>
-      <c r="U10" s="7" t="inlineStr"/>
-      <c r="V10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="5" t="n">
+        <v>50400</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>78.37301587301587</v>
+      </c>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr"/>
+      <c r="U10" s="5" t="n">
+        <v>45400</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>98.01762114537445</v>
+      </c>
       <c r="W10" s="7" t="inlineStr"/>
       <c r="X10" s="7" t="inlineStr"/>
       <c r="Y10" s="7" t="inlineStr"/>
@@ -1296,6 +1360,8 @@
       <c r="AB10" s="7" t="inlineStr"/>
       <c r="AC10" s="7" t="inlineStr"/>
       <c r="AD10" s="7" t="inlineStr"/>
+      <c r="AE10" s="7" t="inlineStr"/>
+      <c r="AF10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1336,32 +1402,36 @@
         <v>24470</v>
       </c>
       <c r="J11" s="5" t="n">
+        <v>24882.5</v>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>19576</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="L11" s="5" t="n">
+        <v>19906</v>
+      </c>
+      <c r="M11" s="5" t="n">
         <v>19510</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>51.71706817016914</v>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="5" t="n">
-        <v>17570</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>68.4689812179852</v>
-      </c>
-      <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="5" t="n">
-        <v>15830</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>86.98673404927352</v>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="5" t="n">
+        <v>17560</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>68.56492027334852</v>
+      </c>
+      <c r="S11" s="7" t="inlineStr"/>
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="5" t="n">
+        <v>15810</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>87.22327640733712</v>
+      </c>
       <c r="W11" s="7" t="inlineStr"/>
       <c r="X11" s="7" t="inlineStr"/>
       <c r="Y11" s="7" t="inlineStr"/>
@@ -1370,6 +1440,8 @@
       <c r="AB11" s="7" t="inlineStr"/>
       <c r="AC11" s="7" t="inlineStr"/>
       <c r="AD11" s="7" t="inlineStr"/>
+      <c r="AE11" s="7" t="inlineStr"/>
+      <c r="AF11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1410,32 +1482,36 @@
         <v>61040</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>61275</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>48832</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="L12" s="5" t="n">
+        <v>49020</v>
+      </c>
+      <c r="M12" s="5" t="n">
         <v>48350</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>35.47052740434333</v>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="5" t="n">
-        <v>43600</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>50.22935779816514</v>
-      </c>
-      <c r="Q12" s="7" t="inlineStr"/>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="5" t="n">
-        <v>39300</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="U12" s="7" t="inlineStr"/>
-      <c r="V12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="5" t="n">
+        <v>43550</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>50.40183696900115</v>
+      </c>
+      <c r="S12" s="7" t="inlineStr"/>
+      <c r="T12" s="7" t="inlineStr"/>
+      <c r="U12" s="5" t="n">
+        <v>39200</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>67.09183673469387</v>
+      </c>
       <c r="W12" s="7" t="inlineStr"/>
       <c r="X12" s="7" t="inlineStr"/>
       <c r="Y12" s="7" t="inlineStr"/>
@@ -1444,6 +1520,8 @@
       <c r="AB12" s="7" t="inlineStr"/>
       <c r="AC12" s="7" t="inlineStr"/>
       <c r="AD12" s="7" t="inlineStr"/>
+      <c r="AE12" s="7" t="inlineStr"/>
+      <c r="AF12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1484,32 +1562,36 @@
         <v>190435</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>194050</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>152348</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="L13" s="5" t="n">
+        <v>155240</v>
+      </c>
+      <c r="M13" s="5" t="n">
         <v>152700</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>42.76358873608383</v>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="5" t="n">
-        <v>137600</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>58.43023255813954</v>
-      </c>
-      <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="5" t="n">
-        <v>124000</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>75.80645161290323</v>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="5" t="n">
+        <v>137500</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>58.54545454545455</v>
+      </c>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="5" t="n">
+        <v>123800</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>76.09046849757674</v>
+      </c>
       <c r="W13" s="7" t="inlineStr"/>
       <c r="X13" s="7" t="inlineStr"/>
       <c r="Y13" s="7" t="inlineStr"/>
@@ -1518,6 +1600,8 @@
       <c r="AB13" s="7" t="inlineStr"/>
       <c r="AC13" s="7" t="inlineStr"/>
       <c r="AD13" s="7" t="inlineStr"/>
+      <c r="AE13" s="7" t="inlineStr"/>
+      <c r="AF13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1558,32 +1642,36 @@
         <v>144660</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>146980</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>115728</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="L14" s="5" t="n">
+        <v>117584</v>
+      </c>
+      <c r="M14" s="5" t="n">
         <v>115800</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>40.06908462867012</v>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="5" t="n">
-        <v>104400</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>55.3639846743295</v>
-      </c>
-      <c r="Q14" s="7" t="inlineStr"/>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="5" t="n">
-        <v>94100</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>72.36981934112646</v>
-      </c>
-      <c r="U14" s="7" t="inlineStr"/>
-      <c r="V14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="5" t="n">
+        <v>104300</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>55.51294343240652</v>
+      </c>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="5" t="n">
+        <v>93900</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>72.73695420660276</v>
+      </c>
       <c r="W14" s="7" t="inlineStr"/>
       <c r="X14" s="7" t="inlineStr"/>
       <c r="Y14" s="7" t="inlineStr"/>
@@ -1592,6 +1680,8 @@
       <c r="AB14" s="7" t="inlineStr"/>
       <c r="AC14" s="7" t="inlineStr"/>
       <c r="AD14" s="7" t="inlineStr"/>
+      <c r="AE14" s="7" t="inlineStr"/>
+      <c r="AF14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1632,32 +1722,36 @@
         <v>423625</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>429700</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>338900</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L15" s="5" t="n">
+        <v>343760</v>
+      </c>
+      <c r="M15" s="5" t="n">
         <v>338500</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>39.88183161004431</v>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="5" t="n">
-        <v>305500</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>54.99181669394435</v>
-      </c>
-      <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="5" t="n">
-        <v>275500</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>71.86932849364791</v>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="5" t="n">
+        <v>305000</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>55.24590163934426</v>
+      </c>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="5" t="n">
+        <v>275000</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>72.18181818181819</v>
+      </c>
       <c r="W15" s="7" t="inlineStr"/>
       <c r="X15" s="7" t="inlineStr"/>
       <c r="Y15" s="7" t="inlineStr"/>
@@ -1666,16 +1760,18 @@
       <c r="AB15" s="7" t="inlineStr"/>
       <c r="AC15" s="7" t="inlineStr"/>
       <c r="AD15" s="7" t="inlineStr"/>
+      <c r="AE15" s="7" t="inlineStr"/>
+      <c r="AF15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1690,48 +1786,52 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.4%</t>
+          <t>1차 매수선까지 40.7%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>123100</v>
+        <v>84400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>118200</v>
+        <v>82100</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>129100</v>
+        <v>84900</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>103790</v>
+        <v>75265</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>83032</v>
+        <v>76160</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>83500</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>47.4251497005988</v>
-      </c>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="5" t="n">
-        <v>75300</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>63.47941567065073</v>
-      </c>
-      <c r="Q16" s="7" t="inlineStr"/>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="5" t="n">
-        <v>67900</v>
-      </c>
-      <c r="T16" s="6" t="n">
-        <v>81.2960235640648</v>
-      </c>
-      <c r="U16" s="7" t="inlineStr"/>
-      <c r="V16" s="7" t="inlineStr"/>
+        <v>60212</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>60928</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>40.66666666666666</v>
+      </c>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="5" t="n">
+        <v>54100</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>56.00739371534195</v>
+      </c>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="5" t="n">
+        <v>48700</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <v>73.30595482546201</v>
+      </c>
       <c r="W16" s="7" t="inlineStr"/>
       <c r="X16" s="7" t="inlineStr"/>
       <c r="Y16" s="7" t="inlineStr"/>
@@ -1740,16 +1840,18 @@
       <c r="AB16" s="7" t="inlineStr"/>
       <c r="AC16" s="7" t="inlineStr"/>
       <c r="AD16" s="7" t="inlineStr"/>
+      <c r="AE16" s="7" t="inlineStr"/>
+      <c r="AF16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1764,48 +1866,52 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.6%</t>
+          <t>1차 매수선까지 47.4%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>397500</v>
+        <v>123100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>389000</v>
+        <v>118200</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>404000</v>
+        <v>129100</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>341475</v>
+        <v>103790</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>273180</v>
+        <v>106300</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>273000</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>45.60439560439561</v>
-      </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="5" t="n">
-        <v>246500</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>61.25760649087221</v>
-      </c>
-      <c r="Q17" s="7" t="inlineStr"/>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="5" t="n">
-        <v>222500</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>78.65168539325843</v>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="inlineStr"/>
+        <v>83032</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>85040</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>83500</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>47.4251497005988</v>
+      </c>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr"/>
+      <c r="Q17" s="5" t="n">
+        <v>75200</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>63.69680851063831</v>
+      </c>
+      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="5" t="n">
+        <v>67700</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>81.83161004431314</v>
+      </c>
       <c r="W17" s="7" t="inlineStr"/>
       <c r="X17" s="7" t="inlineStr"/>
       <c r="Y17" s="7" t="inlineStr"/>
@@ -1814,16 +1920,18 @@
       <c r="AB17" s="7" t="inlineStr"/>
       <c r="AC17" s="7" t="inlineStr"/>
       <c r="AD17" s="7" t="inlineStr"/>
+      <c r="AE17" s="7" t="inlineStr"/>
+      <c r="AF17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1838,48 +1946,52 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.2%</t>
+          <t>1차 매수선까지 45.6%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>63800</v>
+        <v>397500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>62200</v>
+        <v>389000</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>64900</v>
+        <v>404000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>58605</v>
+        <v>341475</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>46884</v>
+        <v>347275</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>46850</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>36.17929562433298</v>
-      </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="5" t="n">
-        <v>42250</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>51.00591715976331</v>
-      </c>
-      <c r="Q18" s="7" t="inlineStr"/>
-      <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="5" t="n">
-        <v>38100</v>
-      </c>
-      <c r="T18" s="6" t="n">
-        <v>67.45406824146981</v>
-      </c>
-      <c r="U18" s="7" t="inlineStr"/>
-      <c r="V18" s="7" t="inlineStr"/>
+        <v>273180</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>277820</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>273000</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>45.60439560439561</v>
+      </c>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="5" t="n">
+        <v>246000</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>61.58536585365854</v>
+      </c>
+      <c r="S18" s="7" t="inlineStr"/>
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="5" t="n">
+        <v>221500</v>
+      </c>
+      <c r="V18" s="6" t="n">
+        <v>79.45823927765237</v>
+      </c>
       <c r="W18" s="7" t="inlineStr"/>
       <c r="X18" s="7" t="inlineStr"/>
       <c r="Y18" s="7" t="inlineStr"/>
@@ -1888,16 +2000,18 @@
       <c r="AB18" s="7" t="inlineStr"/>
       <c r="AC18" s="7" t="inlineStr"/>
       <c r="AD18" s="7" t="inlineStr"/>
+      <c r="AE18" s="7" t="inlineStr"/>
+      <c r="AF18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1912,48 +2026,52 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.8%</t>
+          <t>1차 매수선까지 36.2%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>42700</v>
+        <v>63800</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>42500</v>
+        <v>62200</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>43400</v>
+        <v>64900</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>40407.5</v>
+        <v>58605</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>32326</v>
+        <v>59377.5</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>32150</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>32.8149300155521</v>
-      </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="5" t="n">
-        <v>29000</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>47.24137931034483</v>
-      </c>
-      <c r="Q19" s="7" t="inlineStr"/>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="5" t="n">
-        <v>26150</v>
-      </c>
-      <c r="T19" s="6" t="n">
-        <v>63.28871892925431</v>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="inlineStr"/>
+        <v>46884</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>47502</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>46850</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>36.17929562433298</v>
+      </c>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="5" t="n">
+        <v>42200</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>51.18483412322274</v>
+      </c>
+      <c r="S19" s="7" t="inlineStr"/>
+      <c r="T19" s="7" t="inlineStr"/>
+      <c r="U19" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>67.89473684210526</v>
+      </c>
       <c r="W19" s="7" t="inlineStr"/>
       <c r="X19" s="7" t="inlineStr"/>
       <c r="Y19" s="7" t="inlineStr"/>
@@ -1962,16 +2080,18 @@
       <c r="AB19" s="7" t="inlineStr"/>
       <c r="AC19" s="7" t="inlineStr"/>
       <c r="AD19" s="7" t="inlineStr"/>
+      <c r="AE19" s="7" t="inlineStr"/>
+      <c r="AF19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1986,48 +2106,52 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.9%</t>
+          <t>1차 매수선까지 32.8%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>220500</v>
+        <v>42700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>214000</v>
+        <v>42500</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>235000</v>
+        <v>43400</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>189055</v>
+        <v>40407.5</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>151244</v>
+        <v>40700</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>151100</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>45.92984778292521</v>
-      </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="5" t="n">
-        <v>136100</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>62.01322556943424</v>
-      </c>
-      <c r="Q20" s="7" t="inlineStr"/>
-      <c r="R20" s="7" t="inlineStr"/>
-      <c r="S20" s="5" t="n">
-        <v>122600</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>79.85318107667212</v>
-      </c>
-      <c r="U20" s="7" t="inlineStr"/>
-      <c r="V20" s="7" t="inlineStr"/>
+        <v>32326</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>32560</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>32150</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>32.8149300155521</v>
+      </c>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="5" t="n">
+        <v>28950</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>47.49568221070812</v>
+      </c>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="5" t="n">
+        <v>26100</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>63.60153256704982</v>
+      </c>
       <c r="W20" s="7" t="inlineStr"/>
       <c r="X20" s="7" t="inlineStr"/>
       <c r="Y20" s="7" t="inlineStr"/>
@@ -2036,16 +2160,18 @@
       <c r="AB20" s="7" t="inlineStr"/>
       <c r="AC20" s="7" t="inlineStr"/>
       <c r="AD20" s="7" t="inlineStr"/>
+      <c r="AE20" s="7" t="inlineStr"/>
+      <c r="AF20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2060,48 +2186,52 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.7%</t>
+          <t>1차 매수선까지 37.0%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>84400</v>
+        <v>120400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>82100</v>
+        <v>116000</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>84900</v>
+        <v>122600</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>75265</v>
+        <v>110440</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>60212</v>
+        <v>111410</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>60000</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>40.66666666666666</v>
-      </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="5" t="n">
-        <v>54100</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>56.00739371534195</v>
-      </c>
-      <c r="Q21" s="7" t="inlineStr"/>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="5" t="n">
-        <v>48750</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>73.12820512820512</v>
-      </c>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="inlineStr"/>
+        <v>88352</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>89128</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>87900</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>36.97383390216154</v>
+      </c>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="5" t="n">
+        <v>79200</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>52.02020202020202</v>
+      </c>
+      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="5" t="n">
+        <v>71300</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>68.86395511921458</v>
+      </c>
       <c r="W21" s="7" t="inlineStr"/>
       <c r="X21" s="7" t="inlineStr"/>
       <c r="Y21" s="7" t="inlineStr"/>
@@ -2110,16 +2240,18 @@
       <c r="AB21" s="7" t="inlineStr"/>
       <c r="AC21" s="7" t="inlineStr"/>
       <c r="AD21" s="7" t="inlineStr"/>
+      <c r="AE21" s="7" t="inlineStr"/>
+      <c r="AF21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2134,48 +2266,52 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.3%</t>
+          <t>1차 매수선까지 67.6%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>59900</v>
+        <v>24300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>58700</v>
+        <v>21050</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>64300</v>
+        <v>25400</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>56485</v>
+        <v>18154.5</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>45188</v>
+        <v>18613.5</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>44600</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>34.30493273542601</v>
-      </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-      <c r="O22" s="5" t="n">
-        <v>40200</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>49.00497512437811</v>
-      </c>
-      <c r="Q22" s="7" t="inlineStr"/>
-      <c r="R22" s="7" t="inlineStr"/>
-      <c r="S22" s="5" t="n">
-        <v>36250</v>
-      </c>
-      <c r="T22" s="6" t="n">
-        <v>65.24137931034483</v>
-      </c>
-      <c r="U22" s="7" t="inlineStr"/>
-      <c r="V22" s="7" t="inlineStr"/>
+        <v>14523.6</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>14890.8</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>14500</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>67.58620689655173</v>
+      </c>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="5" t="n">
+        <v>13060</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>86.06431852986218</v>
+      </c>
+      <c r="S22" s="7" t="inlineStr"/>
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="5" t="n">
+        <v>11760</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>106.6326530612245</v>
+      </c>
       <c r="W22" s="7" t="inlineStr"/>
       <c r="X22" s="7" t="inlineStr"/>
       <c r="Y22" s="7" t="inlineStr"/>
@@ -2184,16 +2320,18 @@
       <c r="AB22" s="7" t="inlineStr"/>
       <c r="AC22" s="7" t="inlineStr"/>
       <c r="AD22" s="7" t="inlineStr"/>
+      <c r="AE22" s="7" t="inlineStr"/>
+      <c r="AF22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2208,48 +2346,52 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.0%</t>
+          <t>1차 매수선까지 60.9%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>42700</v>
+        <v>434500</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>41700</v>
+        <v>358000</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>45000</v>
+        <v>453500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>33670</v>
+        <v>339700</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>26936</v>
+        <v>345725</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>26850</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>59.0316573556797</v>
-      </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="5" t="n">
-        <v>24250</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>76.08247422680412</v>
-      </c>
-      <c r="Q23" s="7" t="inlineStr"/>
-      <c r="R23" s="7" t="inlineStr"/>
-      <c r="S23" s="5" t="n">
-        <v>21900</v>
-      </c>
-      <c r="T23" s="6" t="n">
-        <v>94.97716894977168</v>
-      </c>
-      <c r="U23" s="7" t="inlineStr"/>
-      <c r="V23" s="7" t="inlineStr"/>
+        <v>271760</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>276580</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>270000</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>60.92592592592593</v>
+      </c>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="5" t="n">
+        <v>243500</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>78.43942505133469</v>
+      </c>
+      <c r="S23" s="7" t="inlineStr"/>
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="5" t="n">
+        <v>219500</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>97.9498861047836</v>
+      </c>
       <c r="W23" s="7" t="inlineStr"/>
       <c r="X23" s="7" t="inlineStr"/>
       <c r="Y23" s="7" t="inlineStr"/>
@@ -2258,16 +2400,18 @@
       <c r="AB23" s="7" t="inlineStr"/>
       <c r="AC23" s="7" t="inlineStr"/>
       <c r="AD23" s="7" t="inlineStr"/>
+      <c r="AE23" s="7" t="inlineStr"/>
+      <c r="AF23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2282,48 +2426,52 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.7%</t>
+          <t>1차 매수선까지 85.3%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>70300</v>
+        <v>278000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>67000</v>
+        <v>233500</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>72100</v>
+        <v>284500</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>61060</v>
+        <v>190200</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>48848</v>
+        <v>193850</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>48600</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>44.65020576131688</v>
-      </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-      <c r="O24" s="5" t="n">
-        <v>43800</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>60.50228310502283</v>
-      </c>
-      <c r="Q24" s="7" t="inlineStr"/>
-      <c r="R24" s="7" t="inlineStr"/>
-      <c r="S24" s="5" t="n">
-        <v>39500</v>
-      </c>
-      <c r="T24" s="6" t="n">
-        <v>77.9746835443038</v>
-      </c>
-      <c r="U24" s="7" t="inlineStr"/>
-      <c r="V24" s="7" t="inlineStr"/>
+        <v>152160</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>155080</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>85.33333333333334</v>
+      </c>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="5" t="n">
+        <v>135100</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>105.7735011102887</v>
+      </c>
+      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="5" t="n">
+        <v>121600</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>128.6184210526316</v>
+      </c>
       <c r="W24" s="7" t="inlineStr"/>
       <c r="X24" s="7" t="inlineStr"/>
       <c r="Y24" s="7" t="inlineStr"/>
@@ -2332,16 +2480,18 @@
       <c r="AB24" s="7" t="inlineStr"/>
       <c r="AC24" s="7" t="inlineStr"/>
       <c r="AD24" s="7" t="inlineStr"/>
+      <c r="AE24" s="7" t="inlineStr"/>
+      <c r="AF24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2356,48 +2506,52 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.8%</t>
+          <t>1차 매수선까지 45.9%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>488000</v>
+        <v>220500</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>472000</v>
+        <v>214000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>491500</v>
+        <v>235000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>457625</v>
+        <v>189055</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>366100</v>
+        <v>192275</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>362000</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>34.80662983425415</v>
-      </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-      <c r="O25" s="5" t="n">
-        <v>326500</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>49.46401225114855</v>
-      </c>
-      <c r="Q25" s="7" t="inlineStr"/>
-      <c r="R25" s="7" t="inlineStr"/>
-      <c r="S25" s="5" t="n">
-        <v>294500</v>
-      </c>
-      <c r="T25" s="6" t="n">
-        <v>65.70458404074702</v>
-      </c>
-      <c r="U25" s="7" t="inlineStr"/>
-      <c r="V25" s="7" t="inlineStr"/>
+        <v>151244</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>153820</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>151100</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>45.92984778292521</v>
+      </c>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="5" t="n">
+        <v>136000</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>62.13235294117647</v>
+      </c>
+      <c r="S25" s="7" t="inlineStr"/>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="5" t="n">
+        <v>122500</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>80</v>
+      </c>
       <c r="W25" s="7" t="inlineStr"/>
       <c r="X25" s="7" t="inlineStr"/>
       <c r="Y25" s="7" t="inlineStr"/>
@@ -2406,16 +2560,18 @@
       <c r="AB25" s="7" t="inlineStr"/>
       <c r="AC25" s="7" t="inlineStr"/>
       <c r="AD25" s="7" t="inlineStr"/>
+      <c r="AE25" s="7" t="inlineStr"/>
+      <c r="AF25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2430,48 +2586,52 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.8%</t>
+          <t>1차 매수선까지 34.3%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>28100</v>
+        <v>59900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>27800</v>
+        <v>58700</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>29200</v>
+        <v>64300</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>27267.5</v>
+        <v>56485</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>21814</v>
+        <v>56505</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>21650</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>29.79214780600462</v>
-      </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-      <c r="O26" s="5" t="n">
-        <v>19500</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>44.1025641025641</v>
-      </c>
-      <c r="Q26" s="7" t="inlineStr"/>
-      <c r="R26" s="7" t="inlineStr"/>
-      <c r="S26" s="5" t="n">
-        <v>17560</v>
-      </c>
-      <c r="T26" s="6" t="n">
-        <v>60.02277904328018</v>
-      </c>
-      <c r="U26" s="7" t="inlineStr"/>
-      <c r="V26" s="7" t="inlineStr"/>
+        <v>45188</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>45204</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>44600</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>34.30493273542601</v>
+      </c>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="5" t="n">
+        <v>40150</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>49.19053549190536</v>
+      </c>
+      <c r="S26" s="7" t="inlineStr"/>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="5" t="n">
+        <v>36150</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <v>65.69847856154909</v>
+      </c>
       <c r="W26" s="7" t="inlineStr"/>
       <c r="X26" s="7" t="inlineStr"/>
       <c r="Y26" s="7" t="inlineStr"/>
@@ -2480,16 +2640,18 @@
       <c r="AB26" s="7" t="inlineStr"/>
       <c r="AC26" s="7" t="inlineStr"/>
       <c r="AD26" s="7" t="inlineStr"/>
+      <c r="AE26" s="7" t="inlineStr"/>
+      <c r="AF26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2504,48 +2666,52 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.7%</t>
+          <t>1차 매수선까지 59.0%</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>232000</v>
+        <v>42700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>226500</v>
+        <v>41700</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>238000</v>
+        <v>45000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>222000</v>
+        <v>33670</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>177600</v>
+        <v>34347.5</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>176100</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>31.74332765474163</v>
-      </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-      <c r="O27" s="5" t="n">
-        <v>158600</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>46.27994955863809</v>
-      </c>
-      <c r="Q27" s="7" t="inlineStr"/>
-      <c r="R27" s="7" t="inlineStr"/>
-      <c r="S27" s="5" t="n">
-        <v>142900</v>
-      </c>
-      <c r="T27" s="6" t="n">
-        <v>62.35129461161652</v>
-      </c>
-      <c r="U27" s="7" t="inlineStr"/>
-      <c r="V27" s="7" t="inlineStr"/>
+        <v>26936</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>27478</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>26850</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>59.0316573556797</v>
+      </c>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="5" t="n">
+        <v>24200</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>76.44628099173553</v>
+      </c>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="5" t="n">
+        <v>21800</v>
+      </c>
+      <c r="V27" s="6" t="n">
+        <v>95.87155963302753</v>
+      </c>
       <c r="W27" s="7" t="inlineStr"/>
       <c r="X27" s="7" t="inlineStr"/>
       <c r="Y27" s="7" t="inlineStr"/>
@@ -2554,16 +2720,18 @@
       <c r="AB27" s="7" t="inlineStr"/>
       <c r="AC27" s="7" t="inlineStr"/>
       <c r="AD27" s="7" t="inlineStr"/>
+      <c r="AE27" s="7" t="inlineStr"/>
+      <c r="AF27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2578,48 +2746,52 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.4%</t>
+          <t>1차 매수선까지 44.7%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>966000</v>
+        <v>70300</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>912000</v>
+        <v>67000</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>968000</v>
+        <v>72100</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>718100</v>
+        <v>61060</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>574480</v>
+        <v>61830</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>577000</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>67.41767764298093</v>
-      </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-      <c r="O28" s="5" t="n">
-        <v>521000</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>85.41266794625719</v>
-      </c>
-      <c r="Q28" s="7" t="inlineStr"/>
-      <c r="R28" s="7" t="inlineStr"/>
-      <c r="S28" s="5" t="n">
-        <v>469500</v>
-      </c>
-      <c r="T28" s="6" t="n">
-        <v>105.7507987220447</v>
-      </c>
-      <c r="U28" s="7" t="inlineStr"/>
-      <c r="V28" s="7" t="inlineStr"/>
+        <v>48848</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>49464</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>48600</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>44.65020576131688</v>
+      </c>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
+      <c r="Q28" s="5" t="n">
+        <v>43750</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>60.68571428571429</v>
+      </c>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="7" t="inlineStr"/>
+      <c r="U28" s="5" t="n">
+        <v>39400</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>78.42639593908629</v>
+      </c>
       <c r="W28" s="7" t="inlineStr"/>
       <c r="X28" s="7" t="inlineStr"/>
       <c r="Y28" s="7" t="inlineStr"/>
@@ -2628,16 +2800,18 @@
       <c r="AB28" s="7" t="inlineStr"/>
       <c r="AC28" s="7" t="inlineStr"/>
       <c r="AD28" s="7" t="inlineStr"/>
+      <c r="AE28" s="7" t="inlineStr"/>
+      <c r="AF28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2656,44 +2830,48 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>11820</v>
+        <v>488000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>11590</v>
+        <v>472000</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>12770</v>
+        <v>491500</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>10962.5</v>
+        <v>457625</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>8770</v>
+        <v>458675</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>8770</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>34.77765108323831</v>
-      </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-      <c r="O29" s="5" t="n">
-        <v>7910</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>49.43109987357775</v>
-      </c>
-      <c r="Q29" s="7" t="inlineStr"/>
-      <c r="R29" s="7" t="inlineStr"/>
-      <c r="S29" s="5" t="n">
-        <v>7130</v>
-      </c>
-      <c r="T29" s="6" t="n">
-        <v>65.77840112201963</v>
-      </c>
-      <c r="U29" s="7" t="inlineStr"/>
-      <c r="V29" s="7" t="inlineStr"/>
+        <v>366100</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>366940</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>362000</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>34.80662983425415</v>
+      </c>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
+      <c r="Q29" s="5" t="n">
+        <v>326000</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>49.69325153374233</v>
+      </c>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="5" t="n">
+        <v>293500</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>66.26916524701873</v>
+      </c>
       <c r="W29" s="7" t="inlineStr"/>
       <c r="X29" s="7" t="inlineStr"/>
       <c r="Y29" s="7" t="inlineStr"/>
@@ -2702,16 +2880,18 @@
       <c r="AB29" s="7" t="inlineStr"/>
       <c r="AC29" s="7" t="inlineStr"/>
       <c r="AD29" s="7" t="inlineStr"/>
+      <c r="AE29" s="7" t="inlineStr"/>
+      <c r="AF29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2726,48 +2906,52 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.0%</t>
+          <t>1차 매수선까지 29.8%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>120400</v>
+        <v>28100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>116000</v>
+        <v>27800</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>122600</v>
+        <v>29200</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>110440</v>
+        <v>27267.5</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>88352</v>
+        <v>27377.5</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>87900</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>36.97383390216154</v>
-      </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-      <c r="O30" s="5" t="n">
-        <v>79300</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>51.82849936948297</v>
-      </c>
-      <c r="Q30" s="7" t="inlineStr"/>
-      <c r="R30" s="7" t="inlineStr"/>
-      <c r="S30" s="5" t="n">
-        <v>71500</v>
-      </c>
-      <c r="T30" s="6" t="n">
-        <v>68.3916083916084</v>
-      </c>
-      <c r="U30" s="7" t="inlineStr"/>
-      <c r="V30" s="7" t="inlineStr"/>
+        <v>21814</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>21902</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>21650</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>29.79214780600462</v>
+      </c>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="5" t="n">
+        <v>19490</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>44.17650076962545</v>
+      </c>
+      <c r="S30" s="7" t="inlineStr"/>
+      <c r="T30" s="7" t="inlineStr"/>
+      <c r="U30" s="5" t="n">
+        <v>17550</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>60.11396011396012</v>
+      </c>
       <c r="W30" s="7" t="inlineStr"/>
       <c r="X30" s="7" t="inlineStr"/>
       <c r="Y30" s="7" t="inlineStr"/>
@@ -2776,16 +2960,18 @@
       <c r="AB30" s="7" t="inlineStr"/>
       <c r="AC30" s="7" t="inlineStr"/>
       <c r="AD30" s="7" t="inlineStr"/>
+      <c r="AE30" s="7" t="inlineStr"/>
+      <c r="AF30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2800,48 +2986,52 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.6%</t>
+          <t>1차 매수선까지 31.7%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>24300</v>
+        <v>232000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>21050</v>
+        <v>226500</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>25400</v>
+        <v>238000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>18154.5</v>
+        <v>222000</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>14523.6</v>
+        <v>222825</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>14500</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>67.58620689655173</v>
-      </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" s="5" t="n">
-        <v>13060</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v>86.06431852986218</v>
-      </c>
-      <c r="Q31" s="7" t="inlineStr"/>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" s="5" t="n">
-        <v>11770</v>
-      </c>
-      <c r="T31" s="6" t="n">
-        <v>106.4570943075616</v>
-      </c>
-      <c r="U31" s="7" t="inlineStr"/>
-      <c r="V31" s="7" t="inlineStr"/>
+        <v>177600</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>178260</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>176100</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>31.74332765474163</v>
+      </c>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr"/>
+      <c r="Q31" s="5" t="n">
+        <v>158500</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>46.37223974763407</v>
+      </c>
+      <c r="S31" s="7" t="inlineStr"/>
+      <c r="T31" s="7" t="inlineStr"/>
+      <c r="U31" s="5" t="n">
+        <v>142700</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>62.57883672039243</v>
+      </c>
       <c r="W31" s="7" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr"/>
       <c r="Y31" s="7" t="inlineStr"/>
@@ -2850,16 +3040,18 @@
       <c r="AB31" s="7" t="inlineStr"/>
       <c r="AC31" s="7" t="inlineStr"/>
       <c r="AD31" s="7" t="inlineStr"/>
+      <c r="AE31" s="7" t="inlineStr"/>
+      <c r="AF31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2874,48 +3066,52 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.4%</t>
+          <t>1차 매수선까지 67.4%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>126600</v>
+        <v>966000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>114700</v>
+        <v>912000</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>131100</v>
+        <v>968000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>109445</v>
+        <v>718100</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>87556</v>
+        <v>739750</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>87100</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>45.35017221584386</v>
-      </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-      <c r="O32" s="5" t="n">
-        <v>78500</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>61.27388535031847</v>
-      </c>
-      <c r="Q32" s="7" t="inlineStr"/>
-      <c r="R32" s="7" t="inlineStr"/>
-      <c r="S32" s="5" t="n">
-        <v>70800</v>
-      </c>
-      <c r="T32" s="6" t="n">
-        <v>78.8135593220339</v>
-      </c>
-      <c r="U32" s="7" t="inlineStr"/>
-      <c r="V32" s="7" t="inlineStr"/>
+        <v>574480</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>591800</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>577000</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>67.41767764298093</v>
+      </c>
+      <c r="O32" s="7" t="inlineStr"/>
+      <c r="P32" s="7" t="inlineStr"/>
+      <c r="Q32" s="5" t="n">
+        <v>520000</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>85.76923076923076</v>
+      </c>
+      <c r="S32" s="7" t="inlineStr"/>
+      <c r="T32" s="7" t="inlineStr"/>
+      <c r="U32" s="5" t="n">
+        <v>468500</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>106.1899679829242</v>
+      </c>
       <c r="W32" s="7" t="inlineStr"/>
       <c r="X32" s="7" t="inlineStr"/>
       <c r="Y32" s="7" t="inlineStr"/>
@@ -2924,16 +3120,18 @@
       <c r="AB32" s="7" t="inlineStr"/>
       <c r="AC32" s="7" t="inlineStr"/>
       <c r="AD32" s="7" t="inlineStr"/>
+      <c r="AE32" s="7" t="inlineStr"/>
+      <c r="AF32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2948,48 +3146,52 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.6%</t>
+          <t>1차 매수선까지 34.8%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>425000</v>
+        <v>11820</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>389500</v>
+        <v>11590</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>435500</v>
+        <v>12770</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>367250</v>
+        <v>10962.5</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>293800</v>
+        <v>11111</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>290000</v>
-      </c>
-      <c r="L33" s="6" t="n">
-        <v>46.55172413793103</v>
-      </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" s="5" t="n">
-        <v>261500</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>62.52390057361377</v>
-      </c>
-      <c r="Q33" s="7" t="inlineStr"/>
-      <c r="R33" s="7" t="inlineStr"/>
-      <c r="S33" s="5" t="n">
-        <v>236000</v>
-      </c>
-      <c r="T33" s="6" t="n">
-        <v>80.08474576271186</v>
-      </c>
-      <c r="U33" s="7" t="inlineStr"/>
-      <c r="V33" s="7" t="inlineStr"/>
+        <v>8770</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>8888.800000000001</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>8770</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>34.77765108323831</v>
+      </c>
+      <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="7" t="inlineStr"/>
+      <c r="Q33" s="5" t="n">
+        <v>7900</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>49.62025316455696</v>
+      </c>
+      <c r="S33" s="7" t="inlineStr"/>
+      <c r="T33" s="7" t="inlineStr"/>
+      <c r="U33" s="5" t="n">
+        <v>7120</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>66.01123595505618</v>
+      </c>
       <c r="W33" s="7" t="inlineStr"/>
       <c r="X33" s="7" t="inlineStr"/>
       <c r="Y33" s="7" t="inlineStr"/>
@@ -2998,16 +3200,18 @@
       <c r="AB33" s="7" t="inlineStr"/>
       <c r="AC33" s="7" t="inlineStr"/>
       <c r="AD33" s="7" t="inlineStr"/>
+      <c r="AE33" s="7" t="inlineStr"/>
+      <c r="AF33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3022,48 +3226,52 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.4%</t>
+          <t>1차 매수선까지 66.8%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>343000</v>
+        <v>209500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>321500</v>
+        <v>163400</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>345000</v>
+        <v>209500</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>286925</v>
+        <v>158340</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>229540</v>
+        <v>161130</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>228000</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>50.43859649122807</v>
-      </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" s="5" t="n">
-        <v>206000</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>66.50485436893204</v>
-      </c>
-      <c r="Q34" s="7" t="inlineStr"/>
-      <c r="R34" s="7" t="inlineStr"/>
-      <c r="S34" s="5" t="n">
-        <v>185500</v>
-      </c>
-      <c r="T34" s="6" t="n">
-        <v>84.90566037735849</v>
-      </c>
-      <c r="U34" s="7" t="inlineStr"/>
-      <c r="V34" s="7" t="inlineStr"/>
+        <v>126672</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>128904</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>125600</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>66.79936305732484</v>
+      </c>
+      <c r="O34" s="7" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr"/>
+      <c r="Q34" s="5" t="n">
+        <v>113100</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>85.2343059239611</v>
+      </c>
+      <c r="S34" s="7" t="inlineStr"/>
+      <c r="T34" s="7" t="inlineStr"/>
+      <c r="U34" s="5" t="n">
+        <v>101800</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>105.7956777996071</v>
+      </c>
       <c r="W34" s="7" t="inlineStr"/>
       <c r="X34" s="7" t="inlineStr"/>
       <c r="Y34" s="7" t="inlineStr"/>
@@ -3072,16 +3280,18 @@
       <c r="AB34" s="7" t="inlineStr"/>
       <c r="AC34" s="7" t="inlineStr"/>
       <c r="AD34" s="7" t="inlineStr"/>
+      <c r="AE34" s="7" t="inlineStr"/>
+      <c r="AF34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>090710</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3096,48 +3306,52 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.1%</t>
+          <t>1차 매수선까지 45.4%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>6450</v>
+        <v>126600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>6090</v>
+        <v>114700</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>6500</v>
+        <v>131100</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>4876.5</v>
+        <v>109445</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>3901.2</v>
+        <v>110790</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>3930</v>
-      </c>
-      <c r="L35" s="6" t="n">
-        <v>64.12213740458014</v>
-      </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" s="5" t="n">
-        <v>3545</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v>81.94640338504936</v>
-      </c>
-      <c r="Q35" s="7" t="inlineStr"/>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" s="5" t="n">
-        <v>3200</v>
-      </c>
-      <c r="T35" s="6" t="n">
-        <v>101.5625</v>
-      </c>
-      <c r="U35" s="7" t="inlineStr"/>
-      <c r="V35" s="7" t="inlineStr"/>
+        <v>87556</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>88632</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>87100</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>45.35017221584386</v>
+      </c>
+      <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr"/>
+      <c r="Q35" s="5" t="n">
+        <v>78400</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>61.47959183673469</v>
+      </c>
+      <c r="S35" s="7" t="inlineStr"/>
+      <c r="T35" s="7" t="inlineStr"/>
+      <c r="U35" s="5" t="n">
+        <v>70600</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>79.3201133144476</v>
+      </c>
       <c r="W35" s="7" t="inlineStr"/>
       <c r="X35" s="7" t="inlineStr"/>
       <c r="Y35" s="7" t="inlineStr"/>
@@ -3146,16 +3360,18 @@
       <c r="AB35" s="7" t="inlineStr"/>
       <c r="AC35" s="7" t="inlineStr"/>
       <c r="AD35" s="7" t="inlineStr"/>
+      <c r="AE35" s="7" t="inlineStr"/>
+      <c r="AF35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3170,48 +3386,52 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.6%</t>
+          <t>1차 매수선까지 46.6%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>40600</v>
+        <v>425000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>40550</v>
+        <v>389500</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>45600</v>
+        <v>435500</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>37910</v>
+        <v>367250</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>30328</v>
+        <v>368700</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>30400</v>
-      </c>
-      <c r="L36" s="6" t="n">
-        <v>33.55263157894737</v>
-      </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-      <c r="O36" s="5" t="n">
-        <v>27450</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>47.90528233151184</v>
-      </c>
-      <c r="Q36" s="7" t="inlineStr"/>
-      <c r="R36" s="7" t="inlineStr"/>
-      <c r="S36" s="5" t="n">
-        <v>24800</v>
-      </c>
-      <c r="T36" s="6" t="n">
-        <v>63.70967741935484</v>
-      </c>
-      <c r="U36" s="7" t="inlineStr"/>
-      <c r="V36" s="7" t="inlineStr"/>
+        <v>293800</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>294960</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>290000</v>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>46.55172413793103</v>
+      </c>
+      <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr"/>
+      <c r="Q36" s="5" t="n">
+        <v>261500</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>62.52390057361377</v>
+      </c>
+      <c r="S36" s="7" t="inlineStr"/>
+      <c r="T36" s="7" t="inlineStr"/>
+      <c r="U36" s="5" t="n">
+        <v>235500</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>80.46709129511677</v>
+      </c>
       <c r="W36" s="7" t="inlineStr"/>
       <c r="X36" s="7" t="inlineStr"/>
       <c r="Y36" s="7" t="inlineStr"/>
@@ -3220,16 +3440,18 @@
       <c r="AB36" s="7" t="inlineStr"/>
       <c r="AC36" s="7" t="inlineStr"/>
       <c r="AD36" s="7" t="inlineStr"/>
+      <c r="AE36" s="7" t="inlineStr"/>
+      <c r="AF36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3244,48 +3466,52 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.2%</t>
+          <t>1차 매수선까지 50.4%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>23500</v>
+        <v>343000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>22550</v>
+        <v>321500</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>23800</v>
+        <v>345000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>24397.5</v>
+        <v>286925</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>19518</v>
+        <v>290550</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>18920</v>
-      </c>
-      <c r="L37" s="6" t="n">
-        <v>24.20718816067653</v>
-      </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" s="5" t="n">
-        <v>17040</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>37.91079812206573</v>
-      </c>
-      <c r="Q37" s="7" t="inlineStr"/>
-      <c r="R37" s="7" t="inlineStr"/>
-      <c r="S37" s="5" t="n">
-        <v>15350</v>
-      </c>
-      <c r="T37" s="6" t="n">
-        <v>53.09446254071661</v>
-      </c>
-      <c r="U37" s="7" t="inlineStr"/>
-      <c r="V37" s="7" t="inlineStr"/>
+        <v>229540</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>232440</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>228000</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>50.43859649122807</v>
+      </c>
+      <c r="O37" s="7" t="inlineStr"/>
+      <c r="P37" s="7" t="inlineStr"/>
+      <c r="Q37" s="5" t="n">
+        <v>205500</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>66.90997566909975</v>
+      </c>
+      <c r="S37" s="7" t="inlineStr"/>
+      <c r="T37" s="7" t="inlineStr"/>
+      <c r="U37" s="5" t="n">
+        <v>185000</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>85.4054054054054</v>
+      </c>
       <c r="W37" s="7" t="inlineStr"/>
       <c r="X37" s="7" t="inlineStr"/>
       <c r="Y37" s="7" t="inlineStr"/>
@@ -3294,16 +3520,18 @@
       <c r="AB37" s="7" t="inlineStr"/>
       <c r="AC37" s="7" t="inlineStr"/>
       <c r="AD37" s="7" t="inlineStr"/>
+      <c r="AE37" s="7" t="inlineStr"/>
+      <c r="AF37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3318,48 +3546,52 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.0%</t>
+          <t>1차 매수선까지 64.1%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>9010</v>
+        <v>6450</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>8890</v>
+        <v>6090</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>9080</v>
+        <v>6500</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>9852.5</v>
+        <v>4876.5</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>7882</v>
+        <v>5035</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>7700</v>
-      </c>
-      <c r="L38" s="6" t="n">
-        <v>17.01298701298701</v>
-      </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-      <c r="O38" s="5" t="n">
-        <v>6940</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v>29.82708933717579</v>
-      </c>
-      <c r="Q38" s="7" t="inlineStr"/>
-      <c r="R38" s="7" t="inlineStr"/>
-      <c r="S38" s="5" t="n">
-        <v>6260</v>
-      </c>
-      <c r="T38" s="6" t="n">
-        <v>43.9297124600639</v>
-      </c>
-      <c r="U38" s="7" t="inlineStr"/>
-      <c r="V38" s="7" t="inlineStr"/>
+        <v>3901.2</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>4028</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>3930</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>64.12213740458014</v>
+      </c>
+      <c r="O38" s="7" t="inlineStr"/>
+      <c r="P38" s="7" t="inlineStr"/>
+      <c r="Q38" s="5" t="n">
+        <v>3540</v>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v>82.20338983050848</v>
+      </c>
+      <c r="S38" s="7" t="inlineStr"/>
+      <c r="T38" s="7" t="inlineStr"/>
+      <c r="U38" s="5" t="n">
+        <v>3190</v>
+      </c>
+      <c r="V38" s="6" t="n">
+        <v>102.1943573667712</v>
+      </c>
       <c r="W38" s="7" t="inlineStr"/>
       <c r="X38" s="7" t="inlineStr"/>
       <c r="Y38" s="7" t="inlineStr"/>
@@ -3368,16 +3600,18 @@
       <c r="AB38" s="7" t="inlineStr"/>
       <c r="AC38" s="7" t="inlineStr"/>
       <c r="AD38" s="7" t="inlineStr"/>
+      <c r="AE38" s="7" t="inlineStr"/>
+      <c r="AF38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3392,48 +3626,52 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.8%</t>
+          <t>1차 매수선까지 33.6%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>15950</v>
+        <v>40600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>15860</v>
+        <v>40550</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>16250</v>
+        <v>45600</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>17111.5</v>
+        <v>37910</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>13689.2</v>
+        <v>38487.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>13430</v>
-      </c>
-      <c r="L39" s="6" t="n">
-        <v>18.76396128071482</v>
-      </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-      <c r="O39" s="5" t="n">
-        <v>12100</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>31.81818181818182</v>
-      </c>
-      <c r="Q39" s="7" t="inlineStr"/>
-      <c r="R39" s="7" t="inlineStr"/>
-      <c r="S39" s="5" t="n">
-        <v>10900</v>
-      </c>
-      <c r="T39" s="6" t="n">
-        <v>46.3302752293578</v>
-      </c>
-      <c r="U39" s="7" t="inlineStr"/>
-      <c r="V39" s="7" t="inlineStr"/>
+        <v>30328</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>30790</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>30400</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>33.55263157894737</v>
+      </c>
+      <c r="O39" s="7" t="inlineStr"/>
+      <c r="P39" s="7" t="inlineStr"/>
+      <c r="Q39" s="5" t="n">
+        <v>27400</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>48.17518248175183</v>
+      </c>
+      <c r="S39" s="7" t="inlineStr"/>
+      <c r="T39" s="7" t="inlineStr"/>
+      <c r="U39" s="5" t="n">
+        <v>24700</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>64.37246963562752</v>
+      </c>
       <c r="W39" s="7" t="inlineStr"/>
       <c r="X39" s="7" t="inlineStr"/>
       <c r="Y39" s="7" t="inlineStr"/>
@@ -3442,16 +3680,18 @@
       <c r="AB39" s="7" t="inlineStr"/>
       <c r="AC39" s="7" t="inlineStr"/>
       <c r="AD39" s="7" t="inlineStr"/>
+      <c r="AE39" s="7" t="inlineStr"/>
+      <c r="AF39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3466,48 +3706,52 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.9%</t>
+          <t>1차 매수선까지 24.2%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>434500</v>
+        <v>23500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>358000</v>
+        <v>22550</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>453500</v>
+        <v>23800</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>339700</v>
+        <v>24397.5</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>271760</v>
+        <v>23877.5</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>270000</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>60.92592592592593</v>
-      </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-      <c r="O40" s="5" t="n">
-        <v>243500</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>78.43942505133469</v>
-      </c>
-      <c r="Q40" s="7" t="inlineStr"/>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" s="5" t="n">
-        <v>220000</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="U40" s="7" t="inlineStr"/>
-      <c r="V40" s="7" t="inlineStr"/>
+        <v>19518</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>19102</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>18920</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>24.20718816067653</v>
+      </c>
+      <c r="O40" s="7" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr"/>
+      <c r="Q40" s="5" t="n">
+        <v>17030</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>37.99177921315326</v>
+      </c>
+      <c r="S40" s="7" t="inlineStr"/>
+      <c r="T40" s="7" t="inlineStr"/>
+      <c r="U40" s="5" t="n">
+        <v>15330</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>53.2941943900848</v>
+      </c>
       <c r="W40" s="7" t="inlineStr"/>
       <c r="X40" s="7" t="inlineStr"/>
       <c r="Y40" s="7" t="inlineStr"/>
@@ -3516,16 +3760,18 @@
       <c r="AB40" s="7" t="inlineStr"/>
       <c r="AC40" s="7" t="inlineStr"/>
       <c r="AD40" s="7" t="inlineStr"/>
+      <c r="AE40" s="7" t="inlineStr"/>
+      <c r="AF40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3540,48 +3786,52 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.7%</t>
+          <t>1차 매수선까지 17.0%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>175800</v>
+        <v>9010</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>174500</v>
+        <v>8890</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>177300</v>
+        <v>9080</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>175300</v>
+        <v>9852.5</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>140240</v>
+        <v>9685</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>138700</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>26.74837779379957</v>
-      </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-      <c r="O41" s="5" t="n">
-        <v>125000</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="Q41" s="7" t="inlineStr"/>
-      <c r="R41" s="7" t="inlineStr"/>
-      <c r="S41" s="5" t="n">
-        <v>112600</v>
-      </c>
-      <c r="T41" s="6" t="n">
-        <v>56.12788632326821</v>
-      </c>
-      <c r="U41" s="7" t="inlineStr"/>
-      <c r="V41" s="7" t="inlineStr"/>
+        <v>7882</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>7748</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>7700</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>17.01298701298701</v>
+      </c>
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr"/>
+      <c r="Q41" s="5" t="n">
+        <v>6940</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>29.82708933717579</v>
+      </c>
+      <c r="S41" s="7" t="inlineStr"/>
+      <c r="T41" s="7" t="inlineStr"/>
+      <c r="U41" s="5" t="n">
+        <v>6250</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>44.16</v>
+      </c>
       <c r="W41" s="7" t="inlineStr"/>
       <c r="X41" s="7" t="inlineStr"/>
       <c r="Y41" s="7" t="inlineStr"/>
@@ -3590,16 +3840,18 @@
       <c r="AB41" s="7" t="inlineStr"/>
       <c r="AC41" s="7" t="inlineStr"/>
       <c r="AD41" s="7" t="inlineStr"/>
+      <c r="AE41" s="7" t="inlineStr"/>
+      <c r="AF41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3614,48 +3866,52 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 85.3%</t>
+          <t>1차 매수선까지 18.8%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>278000</v>
+        <v>15950</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>233500</v>
+        <v>15860</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>284500</v>
+        <v>16250</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>190200</v>
+        <v>17111.5</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>152160</v>
+        <v>16909.5</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>85.33333333333334</v>
-      </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" s="5" t="n">
-        <v>135100</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v>105.7735011102887</v>
-      </c>
-      <c r="Q42" s="7" t="inlineStr"/>
-      <c r="R42" s="7" t="inlineStr"/>
-      <c r="S42" s="5" t="n">
-        <v>121700</v>
-      </c>
-      <c r="T42" s="6" t="n">
-        <v>128.430566967954</v>
-      </c>
-      <c r="U42" s="7" t="inlineStr"/>
-      <c r="V42" s="7" t="inlineStr"/>
+        <v>13689.2</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>13527.6</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>13430</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>18.76396128071482</v>
+      </c>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr"/>
+      <c r="Q42" s="5" t="n">
+        <v>12090</v>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v>31.92721257237386</v>
+      </c>
+      <c r="S42" s="7" t="inlineStr"/>
+      <c r="T42" s="7" t="inlineStr"/>
+      <c r="U42" s="5" t="n">
+        <v>10890</v>
+      </c>
+      <c r="V42" s="6" t="n">
+        <v>46.46464646464646</v>
+      </c>
       <c r="W42" s="7" t="inlineStr"/>
       <c r="X42" s="7" t="inlineStr"/>
       <c r="Y42" s="7" t="inlineStr"/>
@@ -3664,16 +3920,18 @@
       <c r="AB42" s="7" t="inlineStr"/>
       <c r="AC42" s="7" t="inlineStr"/>
       <c r="AD42" s="7" t="inlineStr"/>
+      <c r="AE42" s="7" t="inlineStr"/>
+      <c r="AF42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3688,48 +3946,52 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 26.7%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>234000</v>
+        <v>175800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>221000</v>
+        <v>174500</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>238500</v>
+        <v>177300</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>210815</v>
+        <v>175300</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>168652</v>
+        <v>175160</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>166600</v>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>40.45618247298919</v>
-      </c>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" s="5" t="n">
-        <v>150100</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>55.89606928714191</v>
-      </c>
-      <c r="Q43" s="7" t="inlineStr"/>
-      <c r="R43" s="7" t="inlineStr"/>
-      <c r="S43" s="5" t="n">
-        <v>135200</v>
-      </c>
-      <c r="T43" s="6" t="n">
-        <v>73.07692307692307</v>
-      </c>
-      <c r="U43" s="7" t="inlineStr"/>
-      <c r="V43" s="7" t="inlineStr"/>
+        <v>140240</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>140128</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>138700</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>26.74837779379957</v>
+      </c>
+      <c r="O43" s="7" t="inlineStr"/>
+      <c r="P43" s="7" t="inlineStr"/>
+      <c r="Q43" s="5" t="n">
+        <v>124900</v>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v>40.75260208166534</v>
+      </c>
+      <c r="S43" s="7" t="inlineStr"/>
+      <c r="T43" s="7" t="inlineStr"/>
+      <c r="U43" s="5" t="n">
+        <v>112500</v>
+      </c>
+      <c r="V43" s="6" t="n">
+        <v>56.26666666666667</v>
+      </c>
       <c r="W43" s="7" t="inlineStr"/>
       <c r="X43" s="7" t="inlineStr"/>
       <c r="Y43" s="7" t="inlineStr"/>
@@ -3738,16 +4000,18 @@
       <c r="AB43" s="7" t="inlineStr"/>
       <c r="AC43" s="7" t="inlineStr"/>
       <c r="AD43" s="7" t="inlineStr"/>
+      <c r="AE43" s="7" t="inlineStr"/>
+      <c r="AF43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3762,48 +4026,52 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.7%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>8060</v>
+        <v>234000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>8030</v>
+        <v>221000</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>8350</v>
+        <v>238500</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>9235.5</v>
+        <v>210815</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>7388.400000000001</v>
+        <v>211565</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>7280</v>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>10.71428571428571</v>
-      </c>
-      <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" s="5" t="n">
-        <v>6570</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>22.67884322678843</v>
-      </c>
-      <c r="Q44" s="7" t="inlineStr"/>
-      <c r="R44" s="7" t="inlineStr"/>
-      <c r="S44" s="5" t="n">
-        <v>5930</v>
-      </c>
-      <c r="T44" s="6" t="n">
-        <v>35.91905564924115</v>
-      </c>
-      <c r="U44" s="7" t="inlineStr"/>
-      <c r="V44" s="7" t="inlineStr"/>
+        <v>168652</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>169252</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>166600</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>40.45618247298919</v>
+      </c>
+      <c r="O44" s="7" t="inlineStr"/>
+      <c r="P44" s="7" t="inlineStr"/>
+      <c r="Q44" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="S44" s="7" t="inlineStr"/>
+      <c r="T44" s="7" t="inlineStr"/>
+      <c r="U44" s="5" t="n">
+        <v>135100</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>73.20503330866025</v>
+      </c>
       <c r="W44" s="7" t="inlineStr"/>
       <c r="X44" s="7" t="inlineStr"/>
       <c r="Y44" s="7" t="inlineStr"/>
@@ -3812,16 +4080,18 @@
       <c r="AB44" s="7" t="inlineStr"/>
       <c r="AC44" s="7" t="inlineStr"/>
       <c r="AD44" s="7" t="inlineStr"/>
+      <c r="AE44" s="7" t="inlineStr"/>
+      <c r="AF44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3836,48 +4106,52 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.3%</t>
+          <t>1차 매수선까지 10.7%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>86900</v>
+        <v>8060</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>84800</v>
+        <v>8030</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>90800</v>
+        <v>8350</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>65667.5</v>
+        <v>9235.5</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>52534</v>
+        <v>9131</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>52900</v>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>64.27221172022685</v>
-      </c>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" s="5" t="n">
-        <v>47700</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>82.18029350104821</v>
-      </c>
-      <c r="Q45" s="7" t="inlineStr"/>
-      <c r="R45" s="7" t="inlineStr"/>
-      <c r="S45" s="5" t="n">
-        <v>43000</v>
-      </c>
-      <c r="T45" s="6" t="n">
-        <v>102.0930232558139</v>
-      </c>
-      <c r="U45" s="7" t="inlineStr"/>
-      <c r="V45" s="7" t="inlineStr"/>
+        <v>7388.400000000001</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>7304.8</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>7280</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="O45" s="7" t="inlineStr"/>
+      <c r="P45" s="7" t="inlineStr"/>
+      <c r="Q45" s="5" t="n">
+        <v>6560</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>22.86585365853659</v>
+      </c>
+      <c r="S45" s="7" t="inlineStr"/>
+      <c r="T45" s="7" t="inlineStr"/>
+      <c r="U45" s="5" t="n">
+        <v>5910</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>36.37901861252115</v>
+      </c>
       <c r="W45" s="7" t="inlineStr"/>
       <c r="X45" s="7" t="inlineStr"/>
       <c r="Y45" s="7" t="inlineStr"/>
@@ -3886,16 +4160,18 @@
       <c r="AB45" s="7" t="inlineStr"/>
       <c r="AC45" s="7" t="inlineStr"/>
       <c r="AD45" s="7" t="inlineStr"/>
+      <c r="AE45" s="7" t="inlineStr"/>
+      <c r="AF45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3910,48 +4186,52 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 64.3%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>103700</v>
+        <v>86900</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>102500</v>
+        <v>84800</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>108000</v>
+        <v>90800</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>102710</v>
+        <v>65667.5</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>82168</v>
+        <v>67730</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>81100</v>
-      </c>
-      <c r="L46" s="6" t="n">
-        <v>27.86683107274969</v>
-      </c>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
-      <c r="O46" s="5" t="n">
-        <v>73100</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v>41.86046511627907</v>
-      </c>
-      <c r="Q46" s="7" t="inlineStr"/>
-      <c r="R46" s="7" t="inlineStr"/>
-      <c r="S46" s="5" t="n">
-        <v>65900</v>
-      </c>
-      <c r="T46" s="6" t="n">
-        <v>57.35963581183612</v>
-      </c>
-      <c r="U46" s="7" t="inlineStr"/>
-      <c r="V46" s="7" t="inlineStr"/>
+        <v>52534</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>54184</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>52900</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>64.27221172022685</v>
+      </c>
+      <c r="O46" s="7" t="inlineStr"/>
+      <c r="P46" s="7" t="inlineStr"/>
+      <c r="Q46" s="5" t="n">
+        <v>47650</v>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v>82.37145855194123</v>
+      </c>
+      <c r="S46" s="7" t="inlineStr"/>
+      <c r="T46" s="7" t="inlineStr"/>
+      <c r="U46" s="5" t="n">
+        <v>42900</v>
+      </c>
+      <c r="V46" s="6" t="n">
+        <v>102.5641025641026</v>
+      </c>
       <c r="W46" s="7" t="inlineStr"/>
       <c r="X46" s="7" t="inlineStr"/>
       <c r="Y46" s="7" t="inlineStr"/>
@@ -3960,16 +4240,18 @@
       <c r="AB46" s="7" t="inlineStr"/>
       <c r="AC46" s="7" t="inlineStr"/>
       <c r="AD46" s="7" t="inlineStr"/>
+      <c r="AE46" s="7" t="inlineStr"/>
+      <c r="AF46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3984,48 +4266,52 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.1%</t>
+          <t>1차 매수선까지 27.9%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>167000</v>
+        <v>103700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>165100</v>
+        <v>102500</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>172400</v>
+        <v>108000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>182965</v>
+        <v>102710</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>146372</v>
+        <v>102450</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>143900</v>
-      </c>
-      <c r="L47" s="6" t="n">
-        <v>16.05281445448228</v>
-      </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-      <c r="O47" s="5" t="n">
-        <v>129700</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v>28.75867386276022</v>
-      </c>
-      <c r="Q47" s="7" t="inlineStr"/>
-      <c r="R47" s="7" t="inlineStr"/>
-      <c r="S47" s="5" t="n">
-        <v>116900</v>
-      </c>
-      <c r="T47" s="6" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="U47" s="7" t="inlineStr"/>
-      <c r="V47" s="7" t="inlineStr"/>
+        <v>82168</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>81960</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>81100</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>27.86683107274969</v>
+      </c>
+      <c r="O47" s="7" t="inlineStr"/>
+      <c r="P47" s="7" t="inlineStr"/>
+      <c r="Q47" s="5" t="n">
+        <v>73000</v>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v>42.05479452054794</v>
+      </c>
+      <c r="S47" s="7" t="inlineStr"/>
+      <c r="T47" s="7" t="inlineStr"/>
+      <c r="U47" s="5" t="n">
+        <v>65800</v>
+      </c>
+      <c r="V47" s="6" t="n">
+        <v>57.59878419452887</v>
+      </c>
       <c r="W47" s="7" t="inlineStr"/>
       <c r="X47" s="7" t="inlineStr"/>
       <c r="Y47" s="7" t="inlineStr"/>
@@ -4034,16 +4320,18 @@
       <c r="AB47" s="7" t="inlineStr"/>
       <c r="AC47" s="7" t="inlineStr"/>
       <c r="AD47" s="7" t="inlineStr"/>
+      <c r="AE47" s="7" t="inlineStr"/>
+      <c r="AF47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4058,48 +4346,52 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.6%</t>
+          <t>1차 매수선까지 16.1%</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>435500</v>
+        <v>167000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>430000</v>
+        <v>165100</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>436500</v>
+        <v>172400</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>434500</v>
+        <v>182965</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>347600</v>
+        <v>180915</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>344000</v>
-      </c>
-      <c r="L48" s="6" t="n">
-        <v>26.59883720930232</v>
-      </c>
-      <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
-      <c r="O48" s="5" t="n">
-        <v>310500</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>40.25764895330113</v>
-      </c>
-      <c r="Q48" s="7" t="inlineStr"/>
-      <c r="R48" s="7" t="inlineStr"/>
-      <c r="S48" s="5" t="n">
-        <v>280000</v>
-      </c>
-      <c r="T48" s="6" t="n">
-        <v>55.53571428571429</v>
-      </c>
-      <c r="U48" s="7" t="inlineStr"/>
-      <c r="V48" s="7" t="inlineStr"/>
+        <v>146372</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>144732</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>143900</v>
+      </c>
+      <c r="N48" s="6" t="n">
+        <v>16.05281445448228</v>
+      </c>
+      <c r="O48" s="7" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr"/>
+      <c r="Q48" s="5" t="n">
+        <v>129600</v>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v>28.85802469135803</v>
+      </c>
+      <c r="S48" s="7" t="inlineStr"/>
+      <c r="T48" s="7" t="inlineStr"/>
+      <c r="U48" s="5" t="n">
+        <v>116700</v>
+      </c>
+      <c r="V48" s="6" t="n">
+        <v>43.10197086546701</v>
+      </c>
       <c r="W48" s="7" t="inlineStr"/>
       <c r="X48" s="7" t="inlineStr"/>
       <c r="Y48" s="7" t="inlineStr"/>
@@ -4108,16 +4400,18 @@
       <c r="AB48" s="7" t="inlineStr"/>
       <c r="AC48" s="7" t="inlineStr"/>
       <c r="AD48" s="7" t="inlineStr"/>
+      <c r="AE48" s="7" t="inlineStr"/>
+      <c r="AF48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4132,48 +4426,52 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.6%</t>
+          <t>1차 매수선까지 26.6%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>21200</v>
+        <v>435500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>21050</v>
+        <v>430000</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>21850</v>
+        <v>436500</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>22647.5</v>
+        <v>434500</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>18118</v>
+        <v>434400</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>17880</v>
-      </c>
-      <c r="L49" s="6" t="n">
-        <v>18.56823266219239</v>
-      </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-      <c r="O49" s="5" t="n">
-        <v>16110</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v>31.59528243327126</v>
-      </c>
-      <c r="Q49" s="7" t="inlineStr"/>
-      <c r="R49" s="7" t="inlineStr"/>
-      <c r="S49" s="5" t="n">
-        <v>14510</v>
-      </c>
-      <c r="T49" s="6" t="n">
-        <v>46.10613370089594</v>
-      </c>
-      <c r="U49" s="7" t="inlineStr"/>
-      <c r="V49" s="7" t="inlineStr"/>
+        <v>347600</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>347520</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>344000</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>26.59883720930232</v>
+      </c>
+      <c r="O49" s="7" t="inlineStr"/>
+      <c r="P49" s="7" t="inlineStr"/>
+      <c r="Q49" s="5" t="n">
+        <v>310000</v>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v>40.48387096774194</v>
+      </c>
+      <c r="S49" s="7" t="inlineStr"/>
+      <c r="T49" s="7" t="inlineStr"/>
+      <c r="U49" s="5" t="n">
+        <v>279500</v>
+      </c>
+      <c r="V49" s="6" t="n">
+        <v>55.81395348837209</v>
+      </c>
       <c r="W49" s="7" t="inlineStr"/>
       <c r="X49" s="7" t="inlineStr"/>
       <c r="Y49" s="7" t="inlineStr"/>
@@ -4182,16 +4480,18 @@
       <c r="AB49" s="7" t="inlineStr"/>
       <c r="AC49" s="7" t="inlineStr"/>
       <c r="AD49" s="7" t="inlineStr"/>
+      <c r="AE49" s="7" t="inlineStr"/>
+      <c r="AF49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4206,48 +4506,52 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 18.6%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>22050</v>
+        <v>21200</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>21500</v>
+        <v>21050</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>22350</v>
+        <v>21850</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>21717</v>
+        <v>22647.5</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>17373.6</v>
+        <v>22505</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>17240</v>
-      </c>
-      <c r="L50" s="6" t="n">
-        <v>27.90023201856148</v>
-      </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
-      <c r="O50" s="5" t="n">
-        <v>15530</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v>41.98325820991629</v>
-      </c>
-      <c r="Q50" s="7" t="inlineStr"/>
-      <c r="R50" s="7" t="inlineStr"/>
-      <c r="S50" s="5" t="n">
-        <v>13990</v>
-      </c>
-      <c r="T50" s="6" t="n">
-        <v>57.61258041458185</v>
-      </c>
-      <c r="U50" s="7" t="inlineStr"/>
-      <c r="V50" s="7" t="inlineStr"/>
+        <v>18118</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>18004</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>17880</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>18.56823266219239</v>
+      </c>
+      <c r="O50" s="7" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr"/>
+      <c r="Q50" s="5" t="n">
+        <v>16100</v>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v>31.67701863354037</v>
+      </c>
+      <c r="S50" s="7" t="inlineStr"/>
+      <c r="T50" s="7" t="inlineStr"/>
+      <c r="U50" s="5" t="n">
+        <v>14500</v>
+      </c>
+      <c r="V50" s="6" t="n">
+        <v>46.20689655172414</v>
+      </c>
       <c r="W50" s="7" t="inlineStr"/>
       <c r="X50" s="7" t="inlineStr"/>
       <c r="Y50" s="7" t="inlineStr"/>
@@ -4256,16 +4560,18 @@
       <c r="AB50" s="7" t="inlineStr"/>
       <c r="AC50" s="7" t="inlineStr"/>
       <c r="AD50" s="7" t="inlineStr"/>
+      <c r="AE50" s="7" t="inlineStr"/>
+      <c r="AF50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4280,48 +4586,52 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 27.9%</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>53200</v>
+        <v>22050</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>52000</v>
+        <v>21500</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>54600</v>
+        <v>22350</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>51265</v>
+        <v>21717</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>41012</v>
+        <v>21789.5</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>40450</v>
-      </c>
-      <c r="L51" s="6" t="n">
-        <v>31.5203955500618</v>
-      </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
-      <c r="O51" s="5" t="n">
-        <v>36500</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v>45.75342465753425</v>
-      </c>
-      <c r="Q51" s="7" t="inlineStr"/>
-      <c r="R51" s="7" t="inlineStr"/>
-      <c r="S51" s="5" t="n">
-        <v>32900</v>
-      </c>
-      <c r="T51" s="6" t="n">
-        <v>61.70212765957447</v>
-      </c>
-      <c r="U51" s="7" t="inlineStr"/>
-      <c r="V51" s="7" t="inlineStr"/>
+        <v>17373.6</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>17431.6</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>17240</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>27.90023201856148</v>
+      </c>
+      <c r="O51" s="7" t="inlineStr"/>
+      <c r="P51" s="7" t="inlineStr"/>
+      <c r="Q51" s="5" t="n">
+        <v>15520</v>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v>42.07474226804123</v>
+      </c>
+      <c r="S51" s="7" t="inlineStr"/>
+      <c r="T51" s="7" t="inlineStr"/>
+      <c r="U51" s="5" t="n">
+        <v>13970</v>
+      </c>
+      <c r="V51" s="6" t="n">
+        <v>57.83822476735862</v>
+      </c>
       <c r="W51" s="7" t="inlineStr"/>
       <c r="X51" s="7" t="inlineStr"/>
       <c r="Y51" s="7" t="inlineStr"/>
@@ -4330,16 +4640,18 @@
       <c r="AB51" s="7" t="inlineStr"/>
       <c r="AC51" s="7" t="inlineStr"/>
       <c r="AD51" s="7" t="inlineStr"/>
+      <c r="AE51" s="7" t="inlineStr"/>
+      <c r="AF51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4354,48 +4666,52 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.0%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>49400</v>
+        <v>53200</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>48250</v>
+        <v>52000</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>50400</v>
+        <v>54600</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>47672.5</v>
+        <v>51265</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>38138</v>
+        <v>51190</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="L52" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="M52" s="7" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
-      <c r="O52" s="5" t="n">
-        <v>34250</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v>44.23357664233576</v>
-      </c>
-      <c r="Q52" s="7" t="inlineStr"/>
-      <c r="R52" s="7" t="inlineStr"/>
-      <c r="S52" s="5" t="n">
-        <v>30900</v>
-      </c>
-      <c r="T52" s="6" t="n">
-        <v>59.8705501618123</v>
-      </c>
-      <c r="U52" s="7" t="inlineStr"/>
-      <c r="V52" s="7" t="inlineStr"/>
+        <v>41012</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>40952</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>40450</v>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>31.5203955500618</v>
+      </c>
+      <c r="O52" s="7" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr"/>
+      <c r="Q52" s="5" t="n">
+        <v>36450</v>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v>45.95336076817559</v>
+      </c>
+      <c r="S52" s="7" t="inlineStr"/>
+      <c r="T52" s="7" t="inlineStr"/>
+      <c r="U52" s="5" t="n">
+        <v>32850</v>
+      </c>
+      <c r="V52" s="6" t="n">
+        <v>61.9482496194825</v>
+      </c>
       <c r="W52" s="7" t="inlineStr"/>
       <c r="X52" s="7" t="inlineStr"/>
       <c r="Y52" s="7" t="inlineStr"/>
@@ -4404,16 +4720,18 @@
       <c r="AB52" s="7" t="inlineStr"/>
       <c r="AC52" s="7" t="inlineStr"/>
       <c r="AD52" s="7" t="inlineStr"/>
+      <c r="AE52" s="7" t="inlineStr"/>
+      <c r="AF52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4428,48 +4746,52 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.3%</t>
+          <t>1차 매수선까지 30.0%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>22700</v>
+        <v>49400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>22000</v>
+        <v>48250</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>23100</v>
+        <v>50400</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>23712.5</v>
+        <v>47672.5</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>18970</v>
+        <v>48040</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>18720</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>21.26068376068376</v>
-      </c>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-      <c r="O53" s="5" t="n">
-        <v>16860</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v>34.63819691577699</v>
-      </c>
-      <c r="Q53" s="7" t="inlineStr"/>
-      <c r="R53" s="7" t="inlineStr"/>
-      <c r="S53" s="5" t="n">
-        <v>15190</v>
-      </c>
-      <c r="T53" s="6" t="n">
-        <v>49.44042132982226</v>
-      </c>
-      <c r="U53" s="7" t="inlineStr"/>
-      <c r="V53" s="7" t="inlineStr"/>
+        <v>38138</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>38432</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O53" s="7" t="inlineStr"/>
+      <c r="P53" s="7" t="inlineStr"/>
+      <c r="Q53" s="5" t="n">
+        <v>34250</v>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v>44.23357664233576</v>
+      </c>
+      <c r="S53" s="7" t="inlineStr"/>
+      <c r="T53" s="7" t="inlineStr"/>
+      <c r="U53" s="5" t="n">
+        <v>30850</v>
+      </c>
+      <c r="V53" s="6" t="n">
+        <v>60.12965964343599</v>
+      </c>
       <c r="W53" s="7" t="inlineStr"/>
       <c r="X53" s="7" t="inlineStr"/>
       <c r="Y53" s="7" t="inlineStr"/>
@@ -4478,16 +4800,18 @@
       <c r="AB53" s="7" t="inlineStr"/>
       <c r="AC53" s="7" t="inlineStr"/>
       <c r="AD53" s="7" t="inlineStr"/>
+      <c r="AE53" s="7" t="inlineStr"/>
+      <c r="AF53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4502,48 +4826,52 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.5%</t>
+          <t>1차 매수선까지 21.3%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>477000</v>
+        <v>22700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>451500</v>
+        <v>22000</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>484000</v>
+        <v>23100</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>436325</v>
+        <v>23712.5</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>349060</v>
+        <v>23595</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>347000</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>37.46397694524496</v>
-      </c>
-      <c r="M54" s="7" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
-      <c r="O54" s="5" t="n">
-        <v>313000</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>52.39616613418531</v>
-      </c>
-      <c r="Q54" s="7" t="inlineStr"/>
-      <c r="R54" s="7" t="inlineStr"/>
-      <c r="S54" s="5" t="n">
-        <v>282500</v>
-      </c>
-      <c r="T54" s="6" t="n">
-        <v>68.84955752212389</v>
-      </c>
-      <c r="U54" s="7" t="inlineStr"/>
-      <c r="V54" s="7" t="inlineStr"/>
+        <v>18970</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>18876</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>18720</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>21.26068376068376</v>
+      </c>
+      <c r="O54" s="7" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr"/>
+      <c r="Q54" s="5" t="n">
+        <v>16850</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>34.71810089020772</v>
+      </c>
+      <c r="S54" s="7" t="inlineStr"/>
+      <c r="T54" s="7" t="inlineStr"/>
+      <c r="U54" s="5" t="n">
+        <v>15170</v>
+      </c>
+      <c r="V54" s="6" t="n">
+        <v>49.63744232036915</v>
+      </c>
       <c r="W54" s="7" t="inlineStr"/>
       <c r="X54" s="7" t="inlineStr"/>
       <c r="Y54" s="7" t="inlineStr"/>
@@ -4552,16 +4880,18 @@
       <c r="AB54" s="7" t="inlineStr"/>
       <c r="AC54" s="7" t="inlineStr"/>
       <c r="AD54" s="7" t="inlineStr"/>
+      <c r="AE54" s="7" t="inlineStr"/>
+      <c r="AF54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4576,48 +4906,52 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 37.5%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>244000</v>
+        <v>477000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>232000</v>
+        <v>451500</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>246000</v>
+        <v>484000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>218130</v>
+        <v>436325</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>174504</v>
+        <v>440175</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>173700</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>40.4720782959125</v>
-      </c>
-      <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
-      <c r="O55" s="5" t="n">
-        <v>156500</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>55.91054313099042</v>
-      </c>
-      <c r="Q55" s="7" t="inlineStr"/>
-      <c r="R55" s="7" t="inlineStr"/>
-      <c r="S55" s="5" t="n">
-        <v>141000</v>
-      </c>
-      <c r="T55" s="6" t="n">
-        <v>73.04964539007092</v>
-      </c>
-      <c r="U55" s="7" t="inlineStr"/>
-      <c r="V55" s="7" t="inlineStr"/>
+        <v>349060</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>352140</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>347000</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>37.46397694524496</v>
+      </c>
+      <c r="O55" s="7" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr"/>
+      <c r="Q55" s="5" t="n">
+        <v>312500</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="S55" s="7" t="inlineStr"/>
+      <c r="T55" s="7" t="inlineStr"/>
+      <c r="U55" s="5" t="n">
+        <v>281500</v>
+      </c>
+      <c r="V55" s="6" t="n">
+        <v>69.44937833037301</v>
+      </c>
       <c r="W55" s="7" t="inlineStr"/>
       <c r="X55" s="7" t="inlineStr"/>
       <c r="Y55" s="7" t="inlineStr"/>
@@ -4626,16 +4960,18 @@
       <c r="AB55" s="7" t="inlineStr"/>
       <c r="AC55" s="7" t="inlineStr"/>
       <c r="AD55" s="7" t="inlineStr"/>
+      <c r="AE55" s="7" t="inlineStr"/>
+      <c r="AF55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4650,48 +4986,52 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 69.9%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>2300000</v>
+        <v>244000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>2102000</v>
+        <v>232000</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>2414000</v>
+        <v>246000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1691500</v>
+        <v>218130</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>1353200</v>
+        <v>220590</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>1354000</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>69.86706056129985</v>
-      </c>
-      <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
-      <c r="O56" s="5" t="n">
-        <v>1220000</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>88.52459016393442</v>
-      </c>
-      <c r="Q56" s="7" t="inlineStr"/>
-      <c r="R56" s="7" t="inlineStr"/>
-      <c r="S56" s="5" t="n">
-        <v>1099000</v>
-      </c>
-      <c r="T56" s="6" t="n">
-        <v>109.2811646951774</v>
-      </c>
-      <c r="U56" s="7" t="inlineStr"/>
-      <c r="V56" s="7" t="inlineStr"/>
+        <v>174504</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>176472</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>173700</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>40.4720782959125</v>
+      </c>
+      <c r="O56" s="7" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr"/>
+      <c r="Q56" s="5" t="n">
+        <v>156400</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>56.01023017902813</v>
+      </c>
+      <c r="S56" s="7" t="inlineStr"/>
+      <c r="T56" s="7" t="inlineStr"/>
+      <c r="U56" s="5" t="n">
+        <v>140800</v>
+      </c>
+      <c r="V56" s="6" t="n">
+        <v>73.29545454545455</v>
+      </c>
       <c r="W56" s="7" t="inlineStr"/>
       <c r="X56" s="7" t="inlineStr"/>
       <c r="Y56" s="7" t="inlineStr"/>
@@ -4700,16 +5040,18 @@
       <c r="AB56" s="7" t="inlineStr"/>
       <c r="AC56" s="7" t="inlineStr"/>
       <c r="AD56" s="7" t="inlineStr"/>
+      <c r="AE56" s="7" t="inlineStr"/>
+      <c r="AF56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4724,48 +5066,52 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.8%</t>
+          <t>1차 매수선까지 69.9%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>519000</v>
+        <v>2300000</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>510000</v>
+        <v>2102000</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>534000</v>
+        <v>2414000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>480675</v>
+        <v>1691500</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>384540</v>
+        <v>1739550</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>379500</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>36.75889328063241</v>
-      </c>
-      <c r="M57" s="7" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
-      <c r="O57" s="5" t="n">
-        <v>342500</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>51.53284671532846</v>
-      </c>
-      <c r="Q57" s="7" t="inlineStr"/>
-      <c r="R57" s="7" t="inlineStr"/>
-      <c r="S57" s="5" t="n">
-        <v>309000</v>
-      </c>
-      <c r="T57" s="6" t="n">
-        <v>67.96116504854369</v>
-      </c>
-      <c r="U57" s="7" t="inlineStr"/>
-      <c r="V57" s="7" t="inlineStr"/>
+        <v>1353200</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>1391640</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>1354000</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>69.86706056129985</v>
+      </c>
+      <c r="O57" s="7" t="inlineStr"/>
+      <c r="P57" s="7" t="inlineStr"/>
+      <c r="Q57" s="5" t="n">
+        <v>1219000</v>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v>88.67924528301887</v>
+      </c>
+      <c r="S57" s="7" t="inlineStr"/>
+      <c r="T57" s="7" t="inlineStr"/>
+      <c r="U57" s="5" t="n">
+        <v>1098000</v>
+      </c>
+      <c r="V57" s="6" t="n">
+        <v>109.471766848816</v>
+      </c>
       <c r="W57" s="7" t="inlineStr"/>
       <c r="X57" s="7" t="inlineStr"/>
       <c r="Y57" s="7" t="inlineStr"/>
@@ -4774,16 +5120,18 @@
       <c r="AB57" s="7" t="inlineStr"/>
       <c r="AC57" s="7" t="inlineStr"/>
       <c r="AD57" s="7" t="inlineStr"/>
+      <c r="AE57" s="7" t="inlineStr"/>
+      <c r="AF57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4798,48 +5146,52 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.8%</t>
+          <t>1차 매수선까지 36.8%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>41100</v>
+        <v>519000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>40750</v>
+        <v>510000</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>42000</v>
+        <v>534000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>41845</v>
+        <v>480675</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>33476</v>
+        <v>481175</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>33200</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>23.79518072289157</v>
-      </c>
-      <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
-      <c r="O58" s="5" t="n">
-        <v>29950</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>37.22871452420701</v>
-      </c>
-      <c r="Q58" s="7" t="inlineStr"/>
-      <c r="R58" s="7" t="inlineStr"/>
-      <c r="S58" s="5" t="n">
-        <v>27050</v>
-      </c>
-      <c r="T58" s="6" t="n">
-        <v>51.94085027726432</v>
-      </c>
-      <c r="U58" s="7" t="inlineStr"/>
-      <c r="V58" s="7" t="inlineStr"/>
+        <v>384540</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>384940</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>379500</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>36.75889328063241</v>
+      </c>
+      <c r="O58" s="7" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr"/>
+      <c r="Q58" s="5" t="n">
+        <v>342000</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>51.75438596491229</v>
+      </c>
+      <c r="S58" s="7" t="inlineStr"/>
+      <c r="T58" s="7" t="inlineStr"/>
+      <c r="U58" s="5" t="n">
+        <v>308000</v>
+      </c>
+      <c r="V58" s="6" t="n">
+        <v>68.5064935064935</v>
+      </c>
       <c r="W58" s="7" t="inlineStr"/>
       <c r="X58" s="7" t="inlineStr"/>
       <c r="Y58" s="7" t="inlineStr"/>
@@ -4848,16 +5200,18 @@
       <c r="AB58" s="7" t="inlineStr"/>
       <c r="AC58" s="7" t="inlineStr"/>
       <c r="AD58" s="7" t="inlineStr"/>
+      <c r="AE58" s="7" t="inlineStr"/>
+      <c r="AF58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4872,48 +5226,52 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.6%</t>
+          <t>1차 매수선까지 23.8%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>15900</v>
+        <v>41100</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>15540</v>
+        <v>40750</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>16070</v>
+        <v>42000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>17086.5</v>
+        <v>41845</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>13669.2</v>
+        <v>41892.5</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>13520</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>17.60355029585799</v>
-      </c>
-      <c r="M59" s="7" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
-      <c r="O59" s="5" t="n">
-        <v>12180</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v>30.54187192118227</v>
-      </c>
-      <c r="Q59" s="7" t="inlineStr"/>
-      <c r="R59" s="7" t="inlineStr"/>
-      <c r="S59" s="5" t="n">
-        <v>10980</v>
-      </c>
-      <c r="T59" s="6" t="n">
-        <v>44.80874316939891</v>
-      </c>
-      <c r="U59" s="7" t="inlineStr"/>
-      <c r="V59" s="7" t="inlineStr"/>
+        <v>33476</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>33514</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>33200</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>23.79518072289157</v>
+      </c>
+      <c r="O59" s="7" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr"/>
+      <c r="Q59" s="5" t="n">
+        <v>29900</v>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v>37.45819397993311</v>
+      </c>
+      <c r="S59" s="7" t="inlineStr"/>
+      <c r="T59" s="7" t="inlineStr"/>
+      <c r="U59" s="5" t="n">
+        <v>26950</v>
+      </c>
+      <c r="V59" s="6" t="n">
+        <v>52.50463821892394</v>
+      </c>
       <c r="W59" s="7" t="inlineStr"/>
       <c r="X59" s="7" t="inlineStr"/>
       <c r="Y59" s="7" t="inlineStr"/>
@@ -4922,16 +5280,18 @@
       <c r="AB59" s="7" t="inlineStr"/>
       <c r="AC59" s="7" t="inlineStr"/>
       <c r="AD59" s="7" t="inlineStr"/>
+      <c r="AE59" s="7" t="inlineStr"/>
+      <c r="AF59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4946,48 +5306,52 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.9%</t>
+          <t>1차 매수선까지 17.6%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>100900</v>
+        <v>15900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>92100</v>
+        <v>15540</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>101400</v>
+        <v>16070</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>91195</v>
+        <v>17086.5</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>72956</v>
+        <v>17014.5</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>72100</v>
-      </c>
-      <c r="L60" s="6" t="n">
-        <v>39.94452149791955</v>
-      </c>
-      <c r="M60" s="7" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
-      <c r="O60" s="5" t="n">
-        <v>65000</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v>55.23076923076923</v>
-      </c>
-      <c r="Q60" s="7" t="inlineStr"/>
-      <c r="R60" s="7" t="inlineStr"/>
-      <c r="S60" s="5" t="n">
-        <v>58600</v>
-      </c>
-      <c r="T60" s="6" t="n">
-        <v>72.18430034129693</v>
-      </c>
-      <c r="U60" s="7" t="inlineStr"/>
-      <c r="V60" s="7" t="inlineStr"/>
+        <v>13669.2</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>13611.6</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>13520</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>17.60355029585799</v>
+      </c>
+      <c r="O60" s="7" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr"/>
+      <c r="Q60" s="5" t="n">
+        <v>12170</v>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v>30.64913722267872</v>
+      </c>
+      <c r="S60" s="7" t="inlineStr"/>
+      <c r="T60" s="7" t="inlineStr"/>
+      <c r="U60" s="5" t="n">
+        <v>10960</v>
+      </c>
+      <c r="V60" s="6" t="n">
+        <v>45.07299270072993</v>
+      </c>
       <c r="W60" s="7" t="inlineStr"/>
       <c r="X60" s="7" t="inlineStr"/>
       <c r="Y60" s="7" t="inlineStr"/>
@@ -4996,16 +5360,18 @@
       <c r="AB60" s="7" t="inlineStr"/>
       <c r="AC60" s="7" t="inlineStr"/>
       <c r="AD60" s="7" t="inlineStr"/>
+      <c r="AE60" s="7" t="inlineStr"/>
+      <c r="AF60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5020,48 +5386,52 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.5%</t>
+          <t>1차 매수선까지 39.9%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>14680</v>
+        <v>100900</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>13830</v>
+        <v>92100</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>14950</v>
+        <v>101400</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>14425</v>
+        <v>91195</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>11540</v>
+        <v>91565</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>11420</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>28.54640980735552</v>
-      </c>
-      <c r="M61" s="7" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr"/>
-      <c r="O61" s="5" t="n">
-        <v>10290</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>42.66277939747328</v>
-      </c>
-      <c r="Q61" s="7" t="inlineStr"/>
-      <c r="R61" s="7" t="inlineStr"/>
-      <c r="S61" s="5" t="n">
-        <v>9280</v>
-      </c>
-      <c r="T61" s="6" t="n">
-        <v>58.18965517241379</v>
-      </c>
-      <c r="U61" s="7" t="inlineStr"/>
-      <c r="V61" s="7" t="inlineStr"/>
+        <v>72956</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>73252</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>72100</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>39.94452149791955</v>
+      </c>
+      <c r="O61" s="7" t="inlineStr"/>
+      <c r="P61" s="7" t="inlineStr"/>
+      <c r="Q61" s="5" t="n">
+        <v>64900</v>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v>55.46995377503852</v>
+      </c>
+      <c r="S61" s="7" t="inlineStr"/>
+      <c r="T61" s="7" t="inlineStr"/>
+      <c r="U61" s="5" t="n">
+        <v>58500</v>
+      </c>
+      <c r="V61" s="6" t="n">
+        <v>72.47863247863248</v>
+      </c>
       <c r="W61" s="7" t="inlineStr"/>
       <c r="X61" s="7" t="inlineStr"/>
       <c r="Y61" s="7" t="inlineStr"/>
@@ -5070,16 +5440,18 @@
       <c r="AB61" s="7" t="inlineStr"/>
       <c r="AC61" s="7" t="inlineStr"/>
       <c r="AD61" s="7" t="inlineStr"/>
+      <c r="AE61" s="7" t="inlineStr"/>
+      <c r="AF61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5094,48 +5466,52 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.1%</t>
+          <t>1차 매수선까지 28.5%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>74100</v>
+        <v>14680</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>73900</v>
+        <v>13830</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>76400</v>
+        <v>14950</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>77930</v>
+        <v>14425</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>62344</v>
+        <v>14429.5</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>61700</v>
-      </c>
-      <c r="L62" s="6" t="n">
-        <v>20.09724473257699</v>
-      </c>
-      <c r="M62" s="7" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
-      <c r="O62" s="5" t="n">
-        <v>55700</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v>33.03411131059246</v>
-      </c>
-      <c r="Q62" s="7" t="inlineStr"/>
-      <c r="R62" s="7" t="inlineStr"/>
-      <c r="S62" s="5" t="n">
-        <v>50300</v>
-      </c>
-      <c r="T62" s="6" t="n">
-        <v>47.31610337972167</v>
-      </c>
-      <c r="U62" s="7" t="inlineStr"/>
-      <c r="V62" s="7" t="inlineStr"/>
+        <v>11540</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>11543.6</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>11420</v>
+      </c>
+      <c r="N62" s="6" t="n">
+        <v>28.54640980735552</v>
+      </c>
+      <c r="O62" s="7" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr"/>
+      <c r="Q62" s="5" t="n">
+        <v>10280</v>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v>42.80155642023346</v>
+      </c>
+      <c r="S62" s="7" t="inlineStr"/>
+      <c r="T62" s="7" t="inlineStr"/>
+      <c r="U62" s="5" t="n">
+        <v>9260</v>
+      </c>
+      <c r="V62" s="6" t="n">
+        <v>58.53131749460043</v>
+      </c>
       <c r="W62" s="7" t="inlineStr"/>
       <c r="X62" s="7" t="inlineStr"/>
       <c r="Y62" s="7" t="inlineStr"/>
@@ -5144,16 +5520,18 @@
       <c r="AB62" s="7" t="inlineStr"/>
       <c r="AC62" s="7" t="inlineStr"/>
       <c r="AD62" s="7" t="inlineStr"/>
+      <c r="AE62" s="7" t="inlineStr"/>
+      <c r="AF62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5168,48 +5546,52 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 20.1%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>257000</v>
+        <v>74100</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>250500</v>
+        <v>73900</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>262500</v>
+        <v>76400</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>246825</v>
+        <v>77930</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>197460</v>
+        <v>77705</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>195400</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>31.52507676560901</v>
-      </c>
-      <c r="M63" s="7" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
-      <c r="O63" s="5" t="n">
-        <v>176000</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v>46.02272727272727</v>
-      </c>
-      <c r="Q63" s="7" t="inlineStr"/>
-      <c r="R63" s="7" t="inlineStr"/>
-      <c r="S63" s="5" t="n">
-        <v>158500</v>
-      </c>
-      <c r="T63" s="6" t="n">
-        <v>62.14511041009464</v>
-      </c>
-      <c r="U63" s="7" t="inlineStr"/>
-      <c r="V63" s="7" t="inlineStr"/>
+        <v>62344</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>62164</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>61700</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>20.09724473257699</v>
+      </c>
+      <c r="O63" s="7" t="inlineStr"/>
+      <c r="P63" s="7" t="inlineStr"/>
+      <c r="Q63" s="5" t="n">
+        <v>55600</v>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v>33.27338129496403</v>
+      </c>
+      <c r="S63" s="7" t="inlineStr"/>
+      <c r="T63" s="7" t="inlineStr"/>
+      <c r="U63" s="5" t="n">
+        <v>50100</v>
+      </c>
+      <c r="V63" s="6" t="n">
+        <v>47.90419161676647</v>
+      </c>
       <c r="W63" s="7" t="inlineStr"/>
       <c r="X63" s="7" t="inlineStr"/>
       <c r="Y63" s="7" t="inlineStr"/>
@@ -5218,16 +5600,18 @@
       <c r="AB63" s="7" t="inlineStr"/>
       <c r="AC63" s="7" t="inlineStr"/>
       <c r="AD63" s="7" t="inlineStr"/>
+      <c r="AE63" s="7" t="inlineStr"/>
+      <c r="AF63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5242,48 +5626,52 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.5%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>115900</v>
+        <v>257000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>113900</v>
+        <v>250500</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>118900</v>
+        <v>262500</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>106930</v>
+        <v>246825</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>85544</v>
+        <v>247225</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>84900</v>
-      </c>
-      <c r="L64" s="6" t="n">
-        <v>36.51354534746761</v>
-      </c>
-      <c r="M64" s="7" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
-      <c r="O64" s="5" t="n">
-        <v>76600</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v>51.30548302872062</v>
-      </c>
-      <c r="Q64" s="7" t="inlineStr"/>
-      <c r="R64" s="7" t="inlineStr"/>
-      <c r="S64" s="5" t="n">
-        <v>69100</v>
-      </c>
-      <c r="T64" s="6" t="n">
-        <v>67.72793053545585</v>
-      </c>
-      <c r="U64" s="7" t="inlineStr"/>
-      <c r="V64" s="7" t="inlineStr"/>
+        <v>197460</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>197780</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>195400</v>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>31.52507676560901</v>
+      </c>
+      <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr"/>
+      <c r="Q64" s="5" t="n">
+        <v>175900</v>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v>46.10574189880614</v>
+      </c>
+      <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="7" t="inlineStr"/>
+      <c r="U64" s="5" t="n">
+        <v>158400</v>
+      </c>
+      <c r="V64" s="6" t="n">
+        <v>62.24747474747475</v>
+      </c>
       <c r="W64" s="7" t="inlineStr"/>
       <c r="X64" s="7" t="inlineStr"/>
       <c r="Y64" s="7" t="inlineStr"/>
@@ -5292,16 +5680,18 @@
       <c r="AB64" s="7" t="inlineStr"/>
       <c r="AC64" s="7" t="inlineStr"/>
       <c r="AD64" s="7" t="inlineStr"/>
+      <c r="AE64" s="7" t="inlineStr"/>
+      <c r="AF64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5316,48 +5706,52 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 36.5%</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>989000</v>
+        <v>115900</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>976000</v>
+        <v>113900</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>1007000</v>
+        <v>118900</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>1009350</v>
+        <v>106930</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>807480</v>
+        <v>107640</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>798000</v>
-      </c>
-      <c r="L65" s="6" t="n">
-        <v>23.93483709273183</v>
-      </c>
-      <c r="M65" s="7" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr"/>
-      <c r="O65" s="5" t="n">
-        <v>720000</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v>37.36111111111111</v>
-      </c>
-      <c r="Q65" s="7" t="inlineStr"/>
-      <c r="R65" s="7" t="inlineStr"/>
-      <c r="S65" s="5" t="n">
-        <v>649000</v>
-      </c>
-      <c r="T65" s="6" t="n">
-        <v>52.38828967642527</v>
-      </c>
-      <c r="U65" s="7" t="inlineStr"/>
-      <c r="V65" s="7" t="inlineStr"/>
+        <v>85544</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>86112</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>84900</v>
+      </c>
+      <c r="N65" s="6" t="n">
+        <v>36.51354534746761</v>
+      </c>
+      <c r="O65" s="7" t="inlineStr"/>
+      <c r="P65" s="7" t="inlineStr"/>
+      <c r="Q65" s="5" t="n">
+        <v>76500</v>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v>51.5032679738562</v>
+      </c>
+      <c r="S65" s="7" t="inlineStr"/>
+      <c r="T65" s="7" t="inlineStr"/>
+      <c r="U65" s="5" t="n">
+        <v>68900</v>
+      </c>
+      <c r="V65" s="6" t="n">
+        <v>68.21480406386067</v>
+      </c>
       <c r="W65" s="7" t="inlineStr"/>
       <c r="X65" s="7" t="inlineStr"/>
       <c r="Y65" s="7" t="inlineStr"/>
@@ -5366,16 +5760,18 @@
       <c r="AB65" s="7" t="inlineStr"/>
       <c r="AC65" s="7" t="inlineStr"/>
       <c r="AD65" s="7" t="inlineStr"/>
+      <c r="AE65" s="7" t="inlineStr"/>
+      <c r="AF65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5390,48 +5786,52 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.4%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>30600</v>
+        <v>989000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>29800</v>
+        <v>976000</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>31250</v>
+        <v>1007000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>29765</v>
+        <v>1009350</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>23812</v>
+        <v>1005950</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>23650</v>
-      </c>
-      <c r="L66" s="6" t="n">
-        <v>29.38689217758985</v>
-      </c>
-      <c r="M66" s="7" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
-      <c r="O66" s="5" t="n">
-        <v>21350</v>
-      </c>
-      <c r="P66" s="6" t="n">
-        <v>43.32552693208431</v>
-      </c>
-      <c r="Q66" s="7" t="inlineStr"/>
-      <c r="R66" s="7" t="inlineStr"/>
-      <c r="S66" s="5" t="n">
-        <v>19230</v>
-      </c>
-      <c r="T66" s="6" t="n">
-        <v>59.12636505460218</v>
-      </c>
-      <c r="U66" s="7" t="inlineStr"/>
-      <c r="V66" s="7" t="inlineStr"/>
+        <v>807480</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>804760</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>798000</v>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>23.93483709273183</v>
+      </c>
+      <c r="O66" s="7" t="inlineStr"/>
+      <c r="P66" s="7" t="inlineStr"/>
+      <c r="Q66" s="5" t="n">
+        <v>719000</v>
+      </c>
+      <c r="R66" s="6" t="n">
+        <v>37.55215577190543</v>
+      </c>
+      <c r="S66" s="7" t="inlineStr"/>
+      <c r="T66" s="7" t="inlineStr"/>
+      <c r="U66" s="5" t="n">
+        <v>648000</v>
+      </c>
+      <c r="V66" s="6" t="n">
+        <v>52.62345679012346</v>
+      </c>
       <c r="W66" s="7" t="inlineStr"/>
       <c r="X66" s="7" t="inlineStr"/>
       <c r="Y66" s="7" t="inlineStr"/>
@@ -5440,16 +5840,18 @@
       <c r="AB66" s="7" t="inlineStr"/>
       <c r="AC66" s="7" t="inlineStr"/>
       <c r="AD66" s="7" t="inlineStr"/>
+      <c r="AE66" s="7" t="inlineStr"/>
+      <c r="AF66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5464,48 +5866,52 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.4%</t>
+          <t>1차 매수선까지 29.4%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>242000</v>
+        <v>30600</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>223500</v>
+        <v>29800</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>248000</v>
+        <v>31250</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>212260</v>
+        <v>29765</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>169808</v>
+        <v>29870</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>168700</v>
-      </c>
-      <c r="L67" s="6" t="n">
-        <v>43.44991108476586</v>
-      </c>
-      <c r="M67" s="7" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
-      <c r="O67" s="5" t="n">
-        <v>152000</v>
-      </c>
-      <c r="P67" s="6" t="n">
-        <v>59.21052631578947</v>
-      </c>
-      <c r="Q67" s="7" t="inlineStr"/>
-      <c r="R67" s="7" t="inlineStr"/>
-      <c r="S67" s="5" t="n">
-        <v>136900</v>
-      </c>
-      <c r="T67" s="6" t="n">
-        <v>76.77136596055514</v>
-      </c>
-      <c r="U67" s="7" t="inlineStr"/>
-      <c r="V67" s="7" t="inlineStr"/>
+        <v>23812</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>23896</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>23650</v>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>29.38689217758985</v>
+      </c>
+      <c r="O67" s="7" t="inlineStr"/>
+      <c r="P67" s="7" t="inlineStr"/>
+      <c r="Q67" s="5" t="n">
+        <v>21300</v>
+      </c>
+      <c r="R67" s="6" t="n">
+        <v>43.66197183098591</v>
+      </c>
+      <c r="S67" s="7" t="inlineStr"/>
+      <c r="T67" s="7" t="inlineStr"/>
+      <c r="U67" s="5" t="n">
+        <v>19180</v>
+      </c>
+      <c r="V67" s="6" t="n">
+        <v>59.54118873826904</v>
+      </c>
       <c r="W67" s="7" t="inlineStr"/>
       <c r="X67" s="7" t="inlineStr"/>
       <c r="Y67" s="7" t="inlineStr"/>
@@ -5514,16 +5920,18 @@
       <c r="AB67" s="7" t="inlineStr"/>
       <c r="AC67" s="7" t="inlineStr"/>
       <c r="AD67" s="7" t="inlineStr"/>
+      <c r="AE67" s="7" t="inlineStr"/>
+      <c r="AF67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5538,48 +5946,52 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.5%</t>
+          <t>1차 매수선까지 43.4%</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>49950</v>
+        <v>242000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>48850</v>
+        <v>223500</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>51500</v>
+        <v>248000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>52782.5</v>
+        <v>212260</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>42226</v>
+        <v>214465</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>41800</v>
-      </c>
-      <c r="L68" s="6" t="n">
-        <v>19.49760765550239</v>
-      </c>
-      <c r="M68" s="7" t="inlineStr"/>
-      <c r="N68" s="7" t="inlineStr"/>
-      <c r="O68" s="5" t="n">
-        <v>37700</v>
-      </c>
-      <c r="P68" s="6" t="n">
-        <v>32.49336870026525</v>
-      </c>
-      <c r="Q68" s="7" t="inlineStr"/>
-      <c r="R68" s="7" t="inlineStr"/>
-      <c r="S68" s="5" t="n">
-        <v>34000</v>
-      </c>
-      <c r="T68" s="6" t="n">
-        <v>46.91176470588236</v>
-      </c>
-      <c r="U68" s="7" t="inlineStr"/>
-      <c r="V68" s="7" t="inlineStr"/>
+        <v>169808</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>171572</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>168700</v>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>43.44991108476586</v>
+      </c>
+      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr"/>
+      <c r="Q68" s="5" t="n">
+        <v>151900</v>
+      </c>
+      <c r="R68" s="6" t="n">
+        <v>59.31533903884134</v>
+      </c>
+      <c r="S68" s="7" t="inlineStr"/>
+      <c r="T68" s="7" t="inlineStr"/>
+      <c r="U68" s="5" t="n">
+        <v>136800</v>
+      </c>
+      <c r="V68" s="6" t="n">
+        <v>76.90058479532163</v>
+      </c>
       <c r="W68" s="7" t="inlineStr"/>
       <c r="X68" s="7" t="inlineStr"/>
       <c r="Y68" s="7" t="inlineStr"/>
@@ -5588,16 +6000,18 @@
       <c r="AB68" s="7" t="inlineStr"/>
       <c r="AC68" s="7" t="inlineStr"/>
       <c r="AD68" s="7" t="inlineStr"/>
+      <c r="AE68" s="7" t="inlineStr"/>
+      <c r="AF68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5612,48 +6026,52 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.9%</t>
+          <t>1차 매수선까지 19.5%</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>15250</v>
+        <v>49950</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>15070</v>
+        <v>48850</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>16400</v>
+        <v>51500</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>15643.5</v>
+        <v>52782.5</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>12514.8</v>
+        <v>52630</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>12410</v>
-      </c>
-      <c r="L69" s="6" t="n">
-        <v>22.88477034649476</v>
-      </c>
-      <c r="M69" s="7" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
-      <c r="O69" s="5" t="n">
-        <v>11180</v>
-      </c>
-      <c r="P69" s="6" t="n">
-        <v>36.40429338103757</v>
-      </c>
-      <c r="Q69" s="7" t="inlineStr"/>
-      <c r="R69" s="7" t="inlineStr"/>
-      <c r="S69" s="5" t="n">
-        <v>10080</v>
-      </c>
-      <c r="T69" s="6" t="n">
-        <v>51.28968253968254</v>
-      </c>
-      <c r="U69" s="7" t="inlineStr"/>
-      <c r="V69" s="7" t="inlineStr"/>
+        <v>42226</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>42104</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>41800</v>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>19.49760765550239</v>
+      </c>
+      <c r="O69" s="7" t="inlineStr"/>
+      <c r="P69" s="7" t="inlineStr"/>
+      <c r="Q69" s="5" t="n">
+        <v>37650</v>
+      </c>
+      <c r="R69" s="6" t="n">
+        <v>32.66932270916335</v>
+      </c>
+      <c r="S69" s="7" t="inlineStr"/>
+      <c r="T69" s="7" t="inlineStr"/>
+      <c r="U69" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="V69" s="6" t="n">
+        <v>47.34513274336283</v>
+      </c>
       <c r="W69" s="7" t="inlineStr"/>
       <c r="X69" s="7" t="inlineStr"/>
       <c r="Y69" s="7" t="inlineStr"/>
@@ -5662,16 +6080,18 @@
       <c r="AB69" s="7" t="inlineStr"/>
       <c r="AC69" s="7" t="inlineStr"/>
       <c r="AD69" s="7" t="inlineStr"/>
+      <c r="AE69" s="7" t="inlineStr"/>
+      <c r="AF69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5686,48 +6106,52 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 22.9%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>28150</v>
+        <v>15250</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>27700</v>
+        <v>15070</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>28450</v>
+        <v>16400</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>29257.5</v>
+        <v>15643.5</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>23406</v>
+        <v>15649</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>23150</v>
-      </c>
-      <c r="L70" s="6" t="n">
-        <v>21.59827213822894</v>
-      </c>
-      <c r="M70" s="7" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
-      <c r="O70" s="5" t="n">
-        <v>20900</v>
-      </c>
-      <c r="P70" s="6" t="n">
-        <v>34.688995215311</v>
-      </c>
-      <c r="Q70" s="7" t="inlineStr"/>
-      <c r="R70" s="7" t="inlineStr"/>
-      <c r="S70" s="5" t="n">
-        <v>18820</v>
-      </c>
-      <c r="T70" s="6" t="n">
-        <v>49.57492029755579</v>
-      </c>
-      <c r="U70" s="7" t="inlineStr"/>
-      <c r="V70" s="7" t="inlineStr"/>
+        <v>12514.8</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>12519.2</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>12410</v>
+      </c>
+      <c r="N70" s="6" t="n">
+        <v>22.88477034649476</v>
+      </c>
+      <c r="O70" s="7" t="inlineStr"/>
+      <c r="P70" s="7" t="inlineStr"/>
+      <c r="Q70" s="5" t="n">
+        <v>11170</v>
+      </c>
+      <c r="R70" s="6" t="n">
+        <v>36.52641002685765</v>
+      </c>
+      <c r="S70" s="7" t="inlineStr"/>
+      <c r="T70" s="7" t="inlineStr"/>
+      <c r="U70" s="5" t="n">
+        <v>10060</v>
+      </c>
+      <c r="V70" s="6" t="n">
+        <v>51.59045725646123</v>
+      </c>
       <c r="W70" s="7" t="inlineStr"/>
       <c r="X70" s="7" t="inlineStr"/>
       <c r="Y70" s="7" t="inlineStr"/>
@@ -5736,16 +6160,18 @@
       <c r="AB70" s="7" t="inlineStr"/>
       <c r="AC70" s="7" t="inlineStr"/>
       <c r="AD70" s="7" t="inlineStr"/>
+      <c r="AE70" s="7" t="inlineStr"/>
+      <c r="AF70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5760,48 +6186,52 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.3%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>2415</v>
+        <v>28150</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>2410</v>
+        <v>27700</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>2535</v>
+        <v>28450</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>2433</v>
+        <v>29257.5</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>1946.4</v>
+        <v>29170</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>1927</v>
-      </c>
-      <c r="L71" s="6" t="n">
-        <v>25.32433834976648</v>
-      </c>
-      <c r="M71" s="7" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
-      <c r="O71" s="5" t="n">
-        <v>1736</v>
-      </c>
-      <c r="P71" s="6" t="n">
-        <v>39.11290322580645</v>
-      </c>
-      <c r="Q71" s="7" t="inlineStr"/>
-      <c r="R71" s="7" t="inlineStr"/>
-      <c r="S71" s="5" t="n">
-        <v>1564</v>
-      </c>
-      <c r="T71" s="6" t="n">
-        <v>54.41176470588235</v>
-      </c>
-      <c r="U71" s="7" t="inlineStr"/>
-      <c r="V71" s="7" t="inlineStr"/>
+        <v>23406</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>23336</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>23150</v>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>21.59827213822894</v>
+      </c>
+      <c r="O71" s="7" t="inlineStr"/>
+      <c r="P71" s="7" t="inlineStr"/>
+      <c r="Q71" s="5" t="n">
+        <v>20850</v>
+      </c>
+      <c r="R71" s="6" t="n">
+        <v>35.01199040767386</v>
+      </c>
+      <c r="S71" s="7" t="inlineStr"/>
+      <c r="T71" s="7" t="inlineStr"/>
+      <c r="U71" s="5" t="n">
+        <v>18770</v>
+      </c>
+      <c r="V71" s="6" t="n">
+        <v>49.97336174746936</v>
+      </c>
       <c r="W71" s="7" t="inlineStr"/>
       <c r="X71" s="7" t="inlineStr"/>
       <c r="Y71" s="7" t="inlineStr"/>
@@ -5810,16 +6240,18 @@
       <c r="AB71" s="7" t="inlineStr"/>
       <c r="AC71" s="7" t="inlineStr"/>
       <c r="AD71" s="7" t="inlineStr"/>
+      <c r="AE71" s="7" t="inlineStr"/>
+      <c r="AF71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5834,48 +6266,52 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.1%</t>
+          <t>1차 매수선까지 25.3%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>7110</v>
+        <v>2415</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>7030</v>
+        <v>2410</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>7480</v>
+        <v>2535</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>7043</v>
+        <v>2433</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>5634.400000000001</v>
+        <v>2432.5</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>5550</v>
-      </c>
-      <c r="L72" s="6" t="n">
-        <v>28.10810810810811</v>
-      </c>
-      <c r="M72" s="7" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr"/>
-      <c r="O72" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P72" s="6" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q72" s="7" t="inlineStr"/>
-      <c r="R72" s="7" t="inlineStr"/>
-      <c r="S72" s="5" t="n">
-        <v>4505</v>
-      </c>
-      <c r="T72" s="6" t="n">
-        <v>57.82463928967814</v>
-      </c>
-      <c r="U72" s="7" t="inlineStr"/>
-      <c r="V72" s="7" t="inlineStr"/>
+        <v>1946.4</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>1946</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>1927</v>
+      </c>
+      <c r="N72" s="6" t="n">
+        <v>25.32433834976648</v>
+      </c>
+      <c r="O72" s="7" t="inlineStr"/>
+      <c r="P72" s="7" t="inlineStr"/>
+      <c r="Q72" s="5" t="n">
+        <v>1735</v>
+      </c>
+      <c r="R72" s="6" t="n">
+        <v>39.19308357348703</v>
+      </c>
+      <c r="S72" s="7" t="inlineStr"/>
+      <c r="T72" s="7" t="inlineStr"/>
+      <c r="U72" s="5" t="n">
+        <v>1562</v>
+      </c>
+      <c r="V72" s="6" t="n">
+        <v>54.60947503201024</v>
+      </c>
       <c r="W72" s="7" t="inlineStr"/>
       <c r="X72" s="7" t="inlineStr"/>
       <c r="Y72" s="7" t="inlineStr"/>
@@ -5884,16 +6320,18 @@
       <c r="AB72" s="7" t="inlineStr"/>
       <c r="AC72" s="7" t="inlineStr"/>
       <c r="AD72" s="7" t="inlineStr"/>
+      <c r="AE72" s="7" t="inlineStr"/>
+      <c r="AF72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5908,48 +6346,52 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.8%</t>
+          <t>1차 매수선까지 28.1%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>146800</v>
+        <v>7110</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>140500</v>
+        <v>7030</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>146800</v>
+        <v>7480</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>141755</v>
+        <v>7043</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>113404</v>
+        <v>7009</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>112200</v>
-      </c>
-      <c r="L73" s="6" t="n">
-        <v>30.83778966131907</v>
-      </c>
-      <c r="M73" s="7" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
-      <c r="O73" s="5" t="n">
-        <v>101100</v>
-      </c>
-      <c r="P73" s="6" t="n">
-        <v>45.20276953511375</v>
-      </c>
-      <c r="Q73" s="7" t="inlineStr"/>
-      <c r="R73" s="7" t="inlineStr"/>
-      <c r="S73" s="5" t="n">
-        <v>91100</v>
-      </c>
-      <c r="T73" s="6" t="n">
-        <v>61.14160263446762</v>
-      </c>
-      <c r="U73" s="7" t="inlineStr"/>
-      <c r="V73" s="7" t="inlineStr"/>
+        <v>5634.400000000001</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>5607.200000000001</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>5550</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>28.10810810810811</v>
+      </c>
+      <c r="O73" s="7" t="inlineStr"/>
+      <c r="P73" s="7" t="inlineStr"/>
+      <c r="Q73" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="S73" s="7" t="inlineStr"/>
+      <c r="T73" s="7" t="inlineStr"/>
+      <c r="U73" s="5" t="n">
+        <v>4505</v>
+      </c>
+      <c r="V73" s="6" t="n">
+        <v>57.82463928967814</v>
+      </c>
       <c r="W73" s="7" t="inlineStr"/>
       <c r="X73" s="7" t="inlineStr"/>
       <c r="Y73" s="7" t="inlineStr"/>
@@ -5958,16 +6400,18 @@
       <c r="AB73" s="7" t="inlineStr"/>
       <c r="AC73" s="7" t="inlineStr"/>
       <c r="AD73" s="7" t="inlineStr"/>
+      <c r="AE73" s="7" t="inlineStr"/>
+      <c r="AF73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -5982,48 +6426,52 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.1%</t>
+          <t>1차 매수선까지 30.8%</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>35300</v>
+        <v>146800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>35000</v>
+        <v>140500</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>36000</v>
+        <v>146800</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>38007.5</v>
+        <v>141755</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>30406</v>
+        <v>141905</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>29900</v>
-      </c>
-      <c r="L74" s="6" t="n">
-        <v>18.06020066889632</v>
-      </c>
-      <c r="M74" s="7" t="inlineStr"/>
-      <c r="N74" s="7" t="inlineStr"/>
-      <c r="O74" s="5" t="n">
-        <v>27000</v>
-      </c>
-      <c r="P74" s="6" t="n">
-        <v>30.74074074074074</v>
-      </c>
-      <c r="Q74" s="7" t="inlineStr"/>
-      <c r="R74" s="7" t="inlineStr"/>
-      <c r="S74" s="5" t="n">
-        <v>24350</v>
-      </c>
-      <c r="T74" s="6" t="n">
-        <v>44.96919917864476</v>
-      </c>
-      <c r="U74" s="7" t="inlineStr"/>
-      <c r="V74" s="7" t="inlineStr"/>
+        <v>113404</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>113524</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>112200</v>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>30.83778966131907</v>
+      </c>
+      <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" s="7" t="inlineStr"/>
+      <c r="Q74" s="5" t="n">
+        <v>101000</v>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v>45.34653465346535</v>
+      </c>
+      <c r="S74" s="7" t="inlineStr"/>
+      <c r="T74" s="7" t="inlineStr"/>
+      <c r="U74" s="5" t="n">
+        <v>91000</v>
+      </c>
+      <c r="V74" s="6" t="n">
+        <v>61.31868131868132</v>
+      </c>
       <c r="W74" s="7" t="inlineStr"/>
       <c r="X74" s="7" t="inlineStr"/>
       <c r="Y74" s="7" t="inlineStr"/>
@@ -6032,16 +6480,18 @@
       <c r="AB74" s="7" t="inlineStr"/>
       <c r="AC74" s="7" t="inlineStr"/>
       <c r="AD74" s="7" t="inlineStr"/>
+      <c r="AE74" s="7" t="inlineStr"/>
+      <c r="AF74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6056,48 +6506,52 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.7%</t>
+          <t>1차 매수선까지 18.1%</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>8730</v>
+        <v>35300</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>8570</v>
+        <v>35000</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>8910</v>
+        <v>36000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>9764</v>
+        <v>38007.5</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>7811.200000000001</v>
+        <v>37600</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>7680</v>
-      </c>
-      <c r="L75" s="6" t="n">
-        <v>13.671875</v>
-      </c>
-      <c r="M75" s="7" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr"/>
-      <c r="O75" s="5" t="n">
-        <v>6930</v>
-      </c>
-      <c r="P75" s="6" t="n">
-        <v>25.97402597402597</v>
-      </c>
-      <c r="Q75" s="7" t="inlineStr"/>
-      <c r="R75" s="7" t="inlineStr"/>
-      <c r="S75" s="5" t="n">
-        <v>6250</v>
-      </c>
-      <c r="T75" s="6" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="U75" s="7" t="inlineStr"/>
-      <c r="V75" s="7" t="inlineStr"/>
+        <v>30406</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>30080</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>29900</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>18.06020066889632</v>
+      </c>
+      <c r="O75" s="7" t="inlineStr"/>
+      <c r="P75" s="7" t="inlineStr"/>
+      <c r="Q75" s="5" t="n">
+        <v>26950</v>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v>30.98330241187384</v>
+      </c>
+      <c r="S75" s="7" t="inlineStr"/>
+      <c r="T75" s="7" t="inlineStr"/>
+      <c r="U75" s="5" t="n">
+        <v>24300</v>
+      </c>
+      <c r="V75" s="6" t="n">
+        <v>45.26748971193415</v>
+      </c>
       <c r="W75" s="7" t="inlineStr"/>
       <c r="X75" s="7" t="inlineStr"/>
       <c r="Y75" s="7" t="inlineStr"/>
@@ -6106,16 +6560,18 @@
       <c r="AB75" s="7" t="inlineStr"/>
       <c r="AC75" s="7" t="inlineStr"/>
       <c r="AD75" s="7" t="inlineStr"/>
+      <c r="AE75" s="7" t="inlineStr"/>
+      <c r="AF75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6130,48 +6586,52 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.0%</t>
+          <t>1차 매수선까지 13.7%</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>260000</v>
+        <v>8730</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>251500</v>
+        <v>8570</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>283500</v>
+        <v>8910</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>251340</v>
+        <v>9764</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>201072</v>
+        <v>9646</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>201500</v>
-      </c>
-      <c r="L76" s="6" t="n">
-        <v>29.03225806451613</v>
-      </c>
-      <c r="M76" s="7" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
-      <c r="O76" s="5" t="n">
-        <v>181500</v>
-      </c>
-      <c r="P76" s="6" t="n">
-        <v>43.25068870523416</v>
-      </c>
-      <c r="Q76" s="7" t="inlineStr"/>
-      <c r="R76" s="7" t="inlineStr"/>
-      <c r="S76" s="5" t="n">
-        <v>163500</v>
-      </c>
-      <c r="T76" s="6" t="n">
-        <v>59.02140672782875</v>
-      </c>
-      <c r="U76" s="7" t="inlineStr"/>
-      <c r="V76" s="7" t="inlineStr"/>
+        <v>7811.200000000001</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>7716.8</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>7680</v>
+      </c>
+      <c r="N76" s="6" t="n">
+        <v>13.671875</v>
+      </c>
+      <c r="O76" s="7" t="inlineStr"/>
+      <c r="P76" s="7" t="inlineStr"/>
+      <c r="Q76" s="5" t="n">
+        <v>6920</v>
+      </c>
+      <c r="R76" s="6" t="n">
+        <v>26.15606936416185</v>
+      </c>
+      <c r="S76" s="7" t="inlineStr"/>
+      <c r="T76" s="7" t="inlineStr"/>
+      <c r="U76" s="5" t="n">
+        <v>6230</v>
+      </c>
+      <c r="V76" s="6" t="n">
+        <v>40.12841091492777</v>
+      </c>
       <c r="W76" s="7" t="inlineStr"/>
       <c r="X76" s="7" t="inlineStr"/>
       <c r="Y76" s="7" t="inlineStr"/>
@@ -6180,16 +6640,18 @@
       <c r="AB76" s="7" t="inlineStr"/>
       <c r="AC76" s="7" t="inlineStr"/>
       <c r="AD76" s="7" t="inlineStr"/>
+      <c r="AE76" s="7" t="inlineStr"/>
+      <c r="AF76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -6204,48 +6666,52 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.6%</t>
+          <t>1차 매수선까지 29.0%</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>311500</v>
+        <v>260000</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>310000</v>
+        <v>251500</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>318500</v>
+        <v>283500</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>295400</v>
+        <v>251340</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>236320</v>
+        <v>254450</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>235000</v>
-      </c>
-      <c r="L77" s="6" t="n">
-        <v>32.5531914893617</v>
-      </c>
-      <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
-      <c r="O77" s="5" t="n">
-        <v>212000</v>
-      </c>
-      <c r="P77" s="6" t="n">
-        <v>46.93396226415094</v>
-      </c>
-      <c r="Q77" s="7" t="inlineStr"/>
-      <c r="R77" s="7" t="inlineStr"/>
-      <c r="S77" s="5" t="n">
-        <v>190900</v>
-      </c>
-      <c r="T77" s="6" t="n">
-        <v>63.17443687794657</v>
-      </c>
-      <c r="U77" s="7" t="inlineStr"/>
-      <c r="V77" s="7" t="inlineStr"/>
+        <v>201072</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>203560</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>201500</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>29.03225806451613</v>
+      </c>
+      <c r="O77" s="7" t="inlineStr"/>
+      <c r="P77" s="7" t="inlineStr"/>
+      <c r="Q77" s="5" t="n">
+        <v>181400</v>
+      </c>
+      <c r="R77" s="6" t="n">
+        <v>43.32965821389195</v>
+      </c>
+      <c r="S77" s="7" t="inlineStr"/>
+      <c r="T77" s="7" t="inlineStr"/>
+      <c r="U77" s="5" t="n">
+        <v>163300</v>
+      </c>
+      <c r="V77" s="6" t="n">
+        <v>59.21616656460502</v>
+      </c>
       <c r="W77" s="7" t="inlineStr"/>
       <c r="X77" s="7" t="inlineStr"/>
       <c r="Y77" s="7" t="inlineStr"/>
@@ -6254,16 +6720,18 @@
       <c r="AB77" s="7" t="inlineStr"/>
       <c r="AC77" s="7" t="inlineStr"/>
       <c r="AD77" s="7" t="inlineStr"/>
+      <c r="AE77" s="7" t="inlineStr"/>
+      <c r="AF77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -6278,48 +6746,52 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.1%</t>
+          <t>1차 매수선까지 32.6%</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>100000</v>
+        <v>311500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>98900</v>
+        <v>310000</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>104400</v>
+        <v>318500</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>99740</v>
+        <v>295400</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>79792</v>
+        <v>297025</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>79300</v>
-      </c>
-      <c r="L78" s="6" t="n">
-        <v>26.10340479192938</v>
-      </c>
-      <c r="M78" s="7" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
-      <c r="O78" s="5" t="n">
-        <v>71500</v>
-      </c>
-      <c r="P78" s="6" t="n">
-        <v>39.86013986013986</v>
-      </c>
-      <c r="Q78" s="7" t="inlineStr"/>
-      <c r="R78" s="7" t="inlineStr"/>
-      <c r="S78" s="5" t="n">
-        <v>64500</v>
-      </c>
-      <c r="T78" s="6" t="n">
-        <v>55.03875968992248</v>
-      </c>
-      <c r="U78" s="7" t="inlineStr"/>
-      <c r="V78" s="7" t="inlineStr"/>
+        <v>236320</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>237620</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>235000</v>
+      </c>
+      <c r="N78" s="6" t="n">
+        <v>32.5531914893617</v>
+      </c>
+      <c r="O78" s="7" t="inlineStr"/>
+      <c r="P78" s="7" t="inlineStr"/>
+      <c r="Q78" s="5" t="n">
+        <v>212000</v>
+      </c>
+      <c r="R78" s="6" t="n">
+        <v>46.93396226415094</v>
+      </c>
+      <c r="S78" s="7" t="inlineStr"/>
+      <c r="T78" s="7" t="inlineStr"/>
+      <c r="U78" s="5" t="n">
+        <v>190900</v>
+      </c>
+      <c r="V78" s="6" t="n">
+        <v>63.17443687794657</v>
+      </c>
       <c r="W78" s="7" t="inlineStr"/>
       <c r="X78" s="7" t="inlineStr"/>
       <c r="Y78" s="7" t="inlineStr"/>
@@ -6328,16 +6800,18 @@
       <c r="AB78" s="7" t="inlineStr"/>
       <c r="AC78" s="7" t="inlineStr"/>
       <c r="AD78" s="7" t="inlineStr"/>
+      <c r="AE78" s="7" t="inlineStr"/>
+      <c r="AF78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6352,48 +6826,52 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.4%</t>
+          <t>1차 매수선까지 26.1%</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>96400</v>
+        <v>100000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>94500</v>
+        <v>98900</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>97900</v>
+        <v>104400</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>90180</v>
+        <v>99740</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>72144</v>
+        <v>100085</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>71700</v>
-      </c>
-      <c r="L79" s="6" t="n">
-        <v>34.44909344490934</v>
-      </c>
-      <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
-      <c r="O79" s="5" t="n">
-        <v>64700</v>
-      </c>
-      <c r="P79" s="6" t="n">
-        <v>48.99536321483771</v>
-      </c>
-      <c r="Q79" s="7" t="inlineStr"/>
-      <c r="R79" s="7" t="inlineStr"/>
-      <c r="S79" s="5" t="n">
-        <v>58400</v>
-      </c>
-      <c r="T79" s="6" t="n">
-        <v>65.06849315068493</v>
-      </c>
-      <c r="U79" s="7" t="inlineStr"/>
-      <c r="V79" s="7" t="inlineStr"/>
+        <v>79792</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>80068</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>79300</v>
+      </c>
+      <c r="N79" s="6" t="n">
+        <v>26.10340479192938</v>
+      </c>
+      <c r="O79" s="7" t="inlineStr"/>
+      <c r="P79" s="7" t="inlineStr"/>
+      <c r="Q79" s="5" t="n">
+        <v>71400</v>
+      </c>
+      <c r="R79" s="6" t="n">
+        <v>40.05602240896359</v>
+      </c>
+      <c r="S79" s="7" t="inlineStr"/>
+      <c r="T79" s="7" t="inlineStr"/>
+      <c r="U79" s="5" t="n">
+        <v>64300</v>
+      </c>
+      <c r="V79" s="6" t="n">
+        <v>55.52099533437014</v>
+      </c>
       <c r="W79" s="7" t="inlineStr"/>
       <c r="X79" s="7" t="inlineStr"/>
       <c r="Y79" s="7" t="inlineStr"/>
@@ -6402,16 +6880,18 @@
       <c r="AB79" s="7" t="inlineStr"/>
       <c r="AC79" s="7" t="inlineStr"/>
       <c r="AD79" s="7" t="inlineStr"/>
+      <c r="AE79" s="7" t="inlineStr"/>
+      <c r="AF79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -6426,48 +6906,52 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.7%</t>
+          <t>1차 매수선까지 34.4%</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>249000</v>
+        <v>96400</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>243000</v>
+        <v>94500</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>250000</v>
+        <v>97900</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>229025</v>
+        <v>90180</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>183220</v>
+        <v>90825</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>182200</v>
-      </c>
-      <c r="L80" s="6" t="n">
-        <v>36.66300768386389</v>
-      </c>
-      <c r="M80" s="7" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr"/>
-      <c r="O80" s="5" t="n">
-        <v>164100</v>
-      </c>
-      <c r="P80" s="6" t="n">
-        <v>51.73674588665448</v>
-      </c>
-      <c r="Q80" s="7" t="inlineStr"/>
-      <c r="R80" s="7" t="inlineStr"/>
-      <c r="S80" s="5" t="n">
-        <v>147800</v>
-      </c>
-      <c r="T80" s="6" t="n">
-        <v>68.47090663058187</v>
-      </c>
-      <c r="U80" s="7" t="inlineStr"/>
-      <c r="V80" s="7" t="inlineStr"/>
+        <v>72144</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>72660</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>71700</v>
+      </c>
+      <c r="N80" s="6" t="n">
+        <v>34.44909344490934</v>
+      </c>
+      <c r="O80" s="7" t="inlineStr"/>
+      <c r="P80" s="7" t="inlineStr"/>
+      <c r="Q80" s="5" t="n">
+        <v>64600</v>
+      </c>
+      <c r="R80" s="6" t="n">
+        <v>49.22600619195047</v>
+      </c>
+      <c r="S80" s="7" t="inlineStr"/>
+      <c r="T80" s="7" t="inlineStr"/>
+      <c r="U80" s="5" t="n">
+        <v>58200</v>
+      </c>
+      <c r="V80" s="6" t="n">
+        <v>65.63573883161511</v>
+      </c>
       <c r="W80" s="7" t="inlineStr"/>
       <c r="X80" s="7" t="inlineStr"/>
       <c r="Y80" s="7" t="inlineStr"/>
@@ -6476,16 +6960,18 @@
       <c r="AB80" s="7" t="inlineStr"/>
       <c r="AC80" s="7" t="inlineStr"/>
       <c r="AD80" s="7" t="inlineStr"/>
+      <c r="AE80" s="7" t="inlineStr"/>
+      <c r="AF80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6500,48 +6986,52 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.2%</t>
+          <t>1차 매수선까지 36.7%</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>129600</v>
+        <v>249000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>128500</v>
+        <v>243000</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>137200</v>
+        <v>250000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>117585</v>
+        <v>229025</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>94068</v>
+        <v>231025</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>93800</v>
-      </c>
-      <c r="L81" s="6" t="n">
-        <v>38.16631130063966</v>
-      </c>
-      <c r="M81" s="7" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
-      <c r="O81" s="5" t="n">
-        <v>84600</v>
-      </c>
-      <c r="P81" s="6" t="n">
-        <v>53.19148936170212</v>
-      </c>
-      <c r="Q81" s="7" t="inlineStr"/>
-      <c r="R81" s="7" t="inlineStr"/>
-      <c r="S81" s="5" t="n">
-        <v>76300</v>
-      </c>
-      <c r="T81" s="6" t="n">
-        <v>69.85583224115334</v>
-      </c>
-      <c r="U81" s="7" t="inlineStr"/>
-      <c r="V81" s="7" t="inlineStr"/>
+        <v>183220</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>184820</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>182200</v>
+      </c>
+      <c r="N81" s="6" t="n">
+        <v>36.66300768386389</v>
+      </c>
+      <c r="O81" s="7" t="inlineStr"/>
+      <c r="P81" s="7" t="inlineStr"/>
+      <c r="Q81" s="5" t="n">
+        <v>164000</v>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v>51.82926829268293</v>
+      </c>
+      <c r="S81" s="7" t="inlineStr"/>
+      <c r="T81" s="7" t="inlineStr"/>
+      <c r="U81" s="5" t="n">
+        <v>147700</v>
+      </c>
+      <c r="V81" s="6" t="n">
+        <v>68.58496953283684</v>
+      </c>
       <c r="W81" s="7" t="inlineStr"/>
       <c r="X81" s="7" t="inlineStr"/>
       <c r="Y81" s="7" t="inlineStr"/>
@@ -6550,6 +7040,88 @@
       <c r="AB81" s="7" t="inlineStr"/>
       <c r="AC81" s="7" t="inlineStr"/>
       <c r="AD81" s="7" t="inlineStr"/>
+      <c r="AE81" s="7" t="inlineStr"/>
+      <c r="AF81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 38.2%</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>129600</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>128500</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>137200</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>117585</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>118980</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>94068</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>95184</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>93800</v>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>38.16631130063966</v>
+      </c>
+      <c r="O82" s="7" t="inlineStr"/>
+      <c r="P82" s="7" t="inlineStr"/>
+      <c r="Q82" s="5" t="n">
+        <v>84500</v>
+      </c>
+      <c r="R82" s="6" t="n">
+        <v>53.37278106508876</v>
+      </c>
+      <c r="S82" s="7" t="inlineStr"/>
+      <c r="T82" s="7" t="inlineStr"/>
+      <c r="U82" s="5" t="n">
+        <v>76100</v>
+      </c>
+      <c r="V82" s="6" t="n">
+        <v>70.30223390275953</v>
+      </c>
+      <c r="W82" s="7" t="inlineStr"/>
+      <c r="X82" s="7" t="inlineStr"/>
+      <c r="Y82" s="7" t="inlineStr"/>
+      <c r="Z82" s="7" t="inlineStr"/>
+      <c r="AA82" s="7" t="inlineStr"/>
+      <c r="AB82" s="7" t="inlineStr"/>
+      <c r="AC82" s="7" t="inlineStr"/>
+      <c r="AD82" s="7" t="inlineStr"/>
+      <c r="AE82" s="7" t="inlineStr"/>
+      <c r="AF82" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -79,6 +80,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF82"/>
+  <dimension ref="A1:AF85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,51 +670,51 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.8%</t>
+          <t>1차 매수선까지 43.4%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>107700</v>
+        <v>111300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>101500</v>
+        <v>105500</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>109200</v>
+        <v>111500</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>95910</v>
+        <v>97250</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>97070</v>
+        <v>98620</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>76728</v>
+        <v>77800</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>77656</v>
+        <v>78896</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>76500</v>
+        <v>77600</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>40.78431372549019</v>
+        <v>43.4278350515464</v>
       </c>
       <c r="O2" s="7" t="inlineStr"/>
       <c r="P2" s="7" t="inlineStr"/>
       <c r="Q2" s="5" t="n">
-        <v>68900</v>
+        <v>69900</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>56.31349782293179</v>
+        <v>59.2274678111588</v>
       </c>
       <c r="S2" s="7" t="inlineStr"/>
       <c r="T2" s="7" t="inlineStr"/>
       <c r="U2" s="5" t="n">
-        <v>62100</v>
+        <v>63000</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>73.42995169082126</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="W2" s="7" t="inlineStr"/>
       <c r="X2" s="7" t="inlineStr"/>
@@ -746,51 +750,51 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.7%</t>
+          <t>1차 매수선까지 64.2%</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>560000</v>
+        <v>629000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>552000</v>
+        <v>553000</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>568000</v>
+        <v>630000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>463025</v>
+        <v>476925</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>473475</v>
+        <v>490975</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>370420</v>
+        <v>381540</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>378780</v>
+        <v>392780</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>371500</v>
+        <v>383000</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>50.74024226110363</v>
+        <v>64.22976501305483</v>
       </c>
       <c r="O3" s="7" t="inlineStr"/>
       <c r="P3" s="7" t="inlineStr"/>
       <c r="Q3" s="5" t="n">
-        <v>334500</v>
+        <v>345000</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>67.41405082212258</v>
+        <v>82.31884057971014</v>
       </c>
       <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="7" t="inlineStr"/>
       <c r="U3" s="5" t="n">
-        <v>301500</v>
+        <v>311000</v>
       </c>
       <c r="V3" s="6" t="n">
-        <v>85.7379767827529</v>
+        <v>102.2508038585209</v>
       </c>
       <c r="W3" s="7" t="inlineStr"/>
       <c r="X3" s="7" t="inlineStr"/>
@@ -826,51 +830,51 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.4%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>88800</v>
+        <v>89800</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>88200</v>
+        <v>88700</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>91500</v>
+        <v>90300</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>78450</v>
+        <v>79780</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>79730</v>
+        <v>81160</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>62760</v>
+        <v>63824</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>63784</v>
+        <v>64928</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>62800</v>
+        <v>63900</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>41.40127388535032</v>
+        <v>40.5320813771518</v>
       </c>
       <c r="O4" s="7" t="inlineStr"/>
       <c r="P4" s="7" t="inlineStr"/>
       <c r="Q4" s="5" t="n">
-        <v>56600</v>
+        <v>57600</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>56.8904593639576</v>
+        <v>55.90277777777778</v>
       </c>
       <c r="S4" s="7" t="inlineStr"/>
       <c r="T4" s="7" t="inlineStr"/>
       <c r="U4" s="5" t="n">
-        <v>51000</v>
+        <v>51900</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>74.11764705882354</v>
+        <v>73.02504816955684</v>
       </c>
       <c r="W4" s="7" t="inlineStr"/>
       <c r="X4" s="7" t="inlineStr"/>
@@ -906,51 +910,51 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.3%</t>
+          <t>1차 매수선까지 42.8%</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
+        <v>138800</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>137600</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>133700</v>
-      </c>
       <c r="H5" s="5" t="n">
-        <v>141600</v>
+        <v>144000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>120490</v>
+        <v>122070</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>122010</v>
+        <v>123495</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>96392</v>
+        <v>97656</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>97608</v>
+        <v>98796</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>96000</v>
+        <v>97200</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>43.33333333333334</v>
+        <v>42.79835390946502</v>
       </c>
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="5" t="n">
-        <v>86500</v>
+        <v>87500</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>59.07514450867052</v>
+        <v>58.62857142857143</v>
       </c>
       <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="7" t="inlineStr"/>
       <c r="U5" s="5" t="n">
-        <v>77900</v>
+        <v>78800</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>76.6367137355584</v>
+        <v>76.14213197969542</v>
       </c>
       <c r="W5" s="7" t="inlineStr"/>
       <c r="X5" s="7" t="inlineStr"/>
@@ -986,35 +990,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.6%</t>
+          <t>1차 매수선까지 34.1%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>270500</v>
+        <v>273500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>255500</v>
+        <v>271000</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>273500</v>
+        <v>287500</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>258250</v>
+        <v>258075</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>257925</v>
+        <v>258400</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>206600</v>
+        <v>206460</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>206340</v>
+        <v>206720</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>204000</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>32.59803921568628</v>
+        <v>34.06862745098039</v>
       </c>
       <c r="O6" s="7" t="inlineStr"/>
       <c r="P6" s="7" t="inlineStr"/>
@@ -1022,7 +1026,7 @@
         <v>183700</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>47.2509526401742</v>
+        <v>48.88405008165487</v>
       </c>
       <c r="S6" s="7" t="inlineStr"/>
       <c r="T6" s="7" t="inlineStr"/>
@@ -1030,7 +1034,7 @@
         <v>165400</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>63.54292623941959</v>
+        <v>65.35671100362757</v>
       </c>
       <c r="W6" s="7" t="inlineStr"/>
       <c r="X6" s="7" t="inlineStr"/>
@@ -1066,51 +1070,51 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.0%</t>
+          <t>1차 매수선까지 66.5%</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>323500</v>
+        <v>348000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>315500</v>
+        <v>320000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>329000</v>
+        <v>355000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>253975</v>
+        <v>261050</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>259825</v>
+        <v>268200</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>203180</v>
+        <v>208840</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>207860</v>
+        <v>214560</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>203500</v>
+        <v>209000</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>58.96805896805897</v>
+        <v>66.50717703349282</v>
       </c>
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="5" t="n">
-        <v>183200</v>
+        <v>188200</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>76.58296943231441</v>
+        <v>84.90967056323061</v>
       </c>
       <c r="S7" s="7" t="inlineStr"/>
       <c r="T7" s="7" t="inlineStr"/>
       <c r="U7" s="5" t="n">
-        <v>164900</v>
+        <v>169400</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>96.17950272892662</v>
+        <v>105.43093270366</v>
       </c>
       <c r="W7" s="7" t="inlineStr"/>
       <c r="X7" s="7" t="inlineStr"/>
@@ -1146,51 +1150,51 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.8%</t>
+          <t>1차 매수선까지 48.2%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>288000</v>
+        <v>291500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>267000</v>
+        <v>287000</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>294000</v>
+        <v>298000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>242925</v>
+        <v>246725</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>246550</v>
+        <v>250550</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>194340</v>
+        <v>197380</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>197240</v>
+        <v>200440</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>193500</v>
+        <v>196700</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>48.83720930232558</v>
+        <v>48.19522114895781</v>
       </c>
       <c r="O8" s="7" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr"/>
       <c r="Q8" s="5" t="n">
-        <v>174200</v>
+        <v>177100</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>65.32721010332951</v>
+        <v>64.59627329192547</v>
       </c>
       <c r="S8" s="7" t="inlineStr"/>
       <c r="T8" s="7" t="inlineStr"/>
       <c r="U8" s="5" t="n">
-        <v>156800</v>
+        <v>159400</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>83.67346938775511</v>
+        <v>82.8732747804266</v>
       </c>
       <c r="W8" s="7" t="inlineStr"/>
       <c r="X8" s="7" t="inlineStr"/>
@@ -1206,12 +1210,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>086520</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1226,51 +1230,51 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.5%</t>
+          <t>1차 매수선까지 65.9%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>141500</v>
+        <v>96200</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>138900</v>
+        <v>88100</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>144800</v>
+        <v>96200</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>132670</v>
+        <v>71872.5</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>135140</v>
+        <v>74310</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>106136</v>
+        <v>57498</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>108112</v>
+        <v>59448</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>106800</v>
+        <v>58000</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>32.49063670411985</v>
+        <v>65.86206896551724</v>
       </c>
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="5" t="n">
-        <v>96200</v>
+        <v>52300</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>47.08939708939709</v>
+        <v>83.93881453154876</v>
       </c>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="inlineStr"/>
       <c r="U9" s="5" t="n">
-        <v>86600</v>
+        <v>47100</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>63.39491916859122</v>
+        <v>104.2462845010616</v>
       </c>
       <c r="W9" s="7" t="inlineStr"/>
       <c r="X9" s="7" t="inlineStr"/>
@@ -1286,12 +1290,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>086520</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1306,51 +1310,51 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.8%</t>
+          <t>1차 매수선까지 30.6%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>89900</v>
+        <v>142000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>85500</v>
+        <v>138400</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>92300</v>
+        <v>143900</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>69475</v>
+        <v>135165</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>71557.5</v>
+        <v>137445</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>55580</v>
+        <v>108132</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>57246</v>
+        <v>109956</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>55900</v>
+        <v>108700</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>60.82289803220036</v>
+        <v>30.63477460901564</v>
       </c>
       <c r="O10" s="7" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr"/>
       <c r="Q10" s="5" t="n">
-        <v>50400</v>
+        <v>97900</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>78.37301587301587</v>
+        <v>45.04596527068438</v>
       </c>
       <c r="S10" s="7" t="inlineStr"/>
       <c r="T10" s="7" t="inlineStr"/>
       <c r="U10" s="5" t="n">
-        <v>45400</v>
+        <v>88200</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>98.01762114537445</v>
+        <v>60.99773242630386</v>
       </c>
       <c r="W10" s="7" t="inlineStr"/>
       <c r="X10" s="7" t="inlineStr"/>
@@ -1386,51 +1390,51 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 51.7%</t>
+          <t>1차 매수선까지 47.1%</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>29600</v>
+        <v>29150</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>29100</v>
+        <v>28850</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>30300</v>
+        <v>30200</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>24470</v>
+        <v>24860</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>24882.5</v>
+        <v>25220</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>19576</v>
+        <v>19888</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>19906</v>
+        <v>20176</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>19510</v>
+        <v>19810</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>51.71706817016914</v>
+        <v>47.14790509843513</v>
       </c>
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="5" t="n">
-        <v>17560</v>
+        <v>17830</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>68.56492027334852</v>
+        <v>63.48850252383623</v>
       </c>
       <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="7" t="inlineStr"/>
       <c r="U11" s="5" t="n">
-        <v>15810</v>
+        <v>16050</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>87.22327640733712</v>
+        <v>81.61993769470405</v>
       </c>
       <c r="W11" s="7" t="inlineStr"/>
       <c r="X11" s="7" t="inlineStr"/>
@@ -1466,51 +1470,51 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 35.5%</t>
+          <t>1차 매수선까지 33.5%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>65500</v>
+        <v>64900</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>62800</v>
+        <v>64000</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>66300</v>
+        <v>66900</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>61040</v>
+        <v>61245</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>61275</v>
+        <v>61510</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>48832</v>
+        <v>48996</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>49020</v>
+        <v>49208</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>48350</v>
+        <v>48600</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>35.47052740434333</v>
+        <v>33.53909465020576</v>
       </c>
       <c r="O12" s="7" t="inlineStr"/>
       <c r="P12" s="7" t="inlineStr"/>
       <c r="Q12" s="5" t="n">
-        <v>43550</v>
+        <v>43750</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>50.40183696900115</v>
+        <v>48.34285714285714</v>
       </c>
       <c r="S12" s="7" t="inlineStr"/>
       <c r="T12" s="7" t="inlineStr"/>
       <c r="U12" s="5" t="n">
-        <v>39200</v>
+        <v>39400</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>67.09183673469387</v>
+        <v>64.72081218274111</v>
       </c>
       <c r="W12" s="7" t="inlineStr"/>
       <c r="X12" s="7" t="inlineStr"/>
@@ -1546,51 +1550,51 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.8%</t>
+          <t>1차 매수선까지 44.2%</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>218000</v>
+        <v>225000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>212500</v>
+        <v>213000</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>223500</v>
+        <v>225000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>190435</v>
+        <v>194400</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>194050</v>
+        <v>198405</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>152348</v>
+        <v>155520</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>155240</v>
+        <v>158724</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>152700</v>
+        <v>156000</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>42.76358873608383</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="5" t="n">
-        <v>137500</v>
+        <v>140500</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>58.54545454545455</v>
+        <v>60.14234875444839</v>
       </c>
       <c r="S13" s="7" t="inlineStr"/>
       <c r="T13" s="7" t="inlineStr"/>
       <c r="U13" s="5" t="n">
-        <v>123800</v>
+        <v>126500</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>76.09046849757674</v>
+        <v>77.86561264822134</v>
       </c>
       <c r="W13" s="7" t="inlineStr"/>
       <c r="X13" s="7" t="inlineStr"/>
@@ -1626,51 +1630,51 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.1%</t>
+          <t>1차 매수선까지 42.2%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>162200</v>
+        <v>167900</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>157600</v>
+        <v>158500</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>164500</v>
+        <v>168200</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>144660</v>
+        <v>147265</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>146980</v>
+        <v>150015</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>115728</v>
+        <v>117812</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>117584</v>
+        <v>120012</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>115800</v>
+        <v>118100</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>40.06908462867012</v>
+        <v>42.16765453005927</v>
       </c>
       <c r="O14" s="7" t="inlineStr"/>
       <c r="P14" s="7" t="inlineStr"/>
       <c r="Q14" s="5" t="n">
-        <v>104300</v>
+        <v>106300</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>55.51294343240652</v>
+        <v>57.94920037629351</v>
       </c>
       <c r="S14" s="7" t="inlineStr"/>
       <c r="T14" s="7" t="inlineStr"/>
       <c r="U14" s="5" t="n">
-        <v>93900</v>
+        <v>95700</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>72.73695420660276</v>
+        <v>75.4440961337513</v>
       </c>
       <c r="W14" s="7" t="inlineStr"/>
       <c r="X14" s="7" t="inlineStr"/>
@@ -1706,51 +1710,51 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.9%</t>
+          <t>1차 매수선까지 40.4%</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>473500</v>
+        <v>483000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>469500</v>
+        <v>433000</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>491500</v>
+        <v>489000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>423625</v>
+        <v>430175</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>429700</v>
+        <v>436925</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>338900</v>
+        <v>344140</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>343760</v>
+        <v>349540</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>338500</v>
+        <v>344000</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>39.88183161004431</v>
+        <v>40.40697674418605</v>
       </c>
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="5" t="n">
-        <v>305000</v>
+        <v>310000</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>55.24590163934426</v>
+        <v>55.80645161290323</v>
       </c>
       <c r="S15" s="7" t="inlineStr"/>
       <c r="T15" s="7" t="inlineStr"/>
       <c r="U15" s="5" t="n">
-        <v>275000</v>
+        <v>279500</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>72.18181818181819</v>
+        <v>72.80858676207514</v>
       </c>
       <c r="W15" s="7" t="inlineStr"/>
       <c r="X15" s="7" t="inlineStr"/>
@@ -1766,12 +1770,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1786,51 +1790,51 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.7%</t>
+          <t>1차 매수선까지 72.1%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>84400</v>
+        <v>477500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>82100</v>
+        <v>427000</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>84900</v>
+        <v>500000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>75265</v>
+        <v>347875</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>76160</v>
+        <v>356425</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>60212</v>
+        <v>278300</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>60928</v>
+        <v>285140</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>60000</v>
+        <v>277500</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>40.66666666666666</v>
+        <v>72.07207207207207</v>
       </c>
       <c r="O16" s="7" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr"/>
       <c r="Q16" s="5" t="n">
-        <v>54100</v>
+        <v>250000</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>56.00739371534195</v>
+        <v>91</v>
       </c>
       <c r="S16" s="7" t="inlineStr"/>
       <c r="T16" s="7" t="inlineStr"/>
       <c r="U16" s="5" t="n">
-        <v>48700</v>
+        <v>225500</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>73.30595482546201</v>
+        <v>111.7516629711752</v>
       </c>
       <c r="W16" s="7" t="inlineStr"/>
       <c r="X16" s="7" t="inlineStr"/>
@@ -1846,12 +1850,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1866,51 +1870,51 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.4%</t>
+          <t>1차 매수선까지 76.2%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>123100</v>
+        <v>274500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>118200</v>
+        <v>220500</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>129100</v>
+        <v>282000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>103790</v>
+        <v>194975</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>106300</v>
+        <v>200665</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>83032</v>
+        <v>155980</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>85040</v>
+        <v>160532</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>83500</v>
+        <v>155800</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>47.4251497005988</v>
+        <v>76.18741976893453</v>
       </c>
       <c r="O17" s="7" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="5" t="n">
-        <v>75200</v>
+        <v>140300</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>63.69680851063831</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="S17" s="7" t="inlineStr"/>
       <c r="T17" s="7" t="inlineStr"/>
       <c r="U17" s="5" t="n">
-        <v>67700</v>
+        <v>126300</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>81.83161004431314</v>
+        <v>117.3396674584323</v>
       </c>
       <c r="W17" s="7" t="inlineStr"/>
       <c r="X17" s="7" t="inlineStr"/>
@@ -1926,12 +1930,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1946,51 +1950,51 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.6%</t>
+          <t>1차 매수선까지 42.5%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>397500</v>
+        <v>520000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>389000</v>
+        <v>485500</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>404000</v>
+        <v>527000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>341475</v>
+        <v>460275</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>347275</v>
+        <v>463500</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>273180</v>
+        <v>368220</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>277820</v>
+        <v>370800</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>273000</v>
+        <v>365000</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>45.60439560439561</v>
+        <v>42.46575342465754</v>
       </c>
       <c r="O18" s="7" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="5" t="n">
-        <v>246000</v>
+        <v>329000</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>61.58536585365854</v>
+        <v>58.05471124620061</v>
       </c>
       <c r="S18" s="7" t="inlineStr"/>
       <c r="T18" s="7" t="inlineStr"/>
       <c r="U18" s="5" t="n">
-        <v>221500</v>
+        <v>296500</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>79.45823927765237</v>
+        <v>75.37942664418212</v>
       </c>
       <c r="W18" s="7" t="inlineStr"/>
       <c r="X18" s="7" t="inlineStr"/>
@@ -2006,12 +2010,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2026,51 +2030,51 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.2%</t>
+          <t>1차 매수선까지 42.8%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>63800</v>
+        <v>86800</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>62200</v>
+        <v>82400</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>64900</v>
+        <v>87000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>58605</v>
+        <v>76280</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>59377.5</v>
+        <v>77300</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>46884</v>
+        <v>61024</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>47502</v>
+        <v>61840</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>46850</v>
+        <v>60800</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>36.17929562433298</v>
+        <v>42.76315789473684</v>
       </c>
       <c r="O19" s="7" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr"/>
       <c r="Q19" s="5" t="n">
-        <v>42200</v>
+        <v>54800</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>51.18483412322274</v>
+        <v>58.3941605839416</v>
       </c>
       <c r="S19" s="7" t="inlineStr"/>
       <c r="T19" s="7" t="inlineStr"/>
       <c r="U19" s="5" t="n">
-        <v>38000</v>
+        <v>49350</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>67.89473684210526</v>
+        <v>75.88652482269504</v>
       </c>
       <c r="W19" s="7" t="inlineStr"/>
       <c r="X19" s="7" t="inlineStr"/>
@@ -2086,12 +2090,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2106,51 +2110,51 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.8%</t>
+          <t>1차 매수선까지 47.1%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>42700</v>
+        <v>126100</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>42500</v>
+        <v>120000</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>43400</v>
+        <v>127500</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>40407.5</v>
+        <v>106450</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>40700</v>
+        <v>109070</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>32326</v>
+        <v>85160</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>32560</v>
+        <v>87256</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>32150</v>
+        <v>85700</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>32.8149300155521</v>
+        <v>47.1411901983664</v>
       </c>
       <c r="O20" s="7" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr"/>
       <c r="Q20" s="5" t="n">
-        <v>28950</v>
+        <v>77200</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>47.49568221070812</v>
+        <v>63.3419689119171</v>
       </c>
       <c r="S20" s="7" t="inlineStr"/>
       <c r="T20" s="7" t="inlineStr"/>
       <c r="U20" s="5" t="n">
-        <v>26100</v>
+        <v>69500</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>63.60153256704982</v>
+        <v>81.43884892086331</v>
       </c>
       <c r="W20" s="7" t="inlineStr"/>
       <c r="X20" s="7" t="inlineStr"/>
@@ -2166,12 +2170,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2186,51 +2190,51 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.0%</t>
+          <t>1차 매수선까지 42.8%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>120400</v>
+        <v>397000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>116000</v>
+        <v>385500</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>122600</v>
+        <v>402000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>110440</v>
+        <v>347250</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>111410</v>
+        <v>353175</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>88352</v>
+        <v>277800</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>89128</v>
+        <v>282540</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>87900</v>
+        <v>278000</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>36.97383390216154</v>
+        <v>42.80575539568346</v>
       </c>
       <c r="O21" s="7" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="5" t="n">
-        <v>79200</v>
+        <v>250500</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>52.02020202020202</v>
+        <v>58.48303393213573</v>
       </c>
       <c r="S21" s="7" t="inlineStr"/>
       <c r="T21" s="7" t="inlineStr"/>
       <c r="U21" s="5" t="n">
-        <v>71300</v>
+        <v>225500</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>68.86395511921458</v>
+        <v>76.05321507760532</v>
       </c>
       <c r="W21" s="7" t="inlineStr"/>
       <c r="X21" s="7" t="inlineStr"/>
@@ -2246,12 +2250,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2266,51 +2270,51 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.6%</t>
+          <t>1차 매수선까지 40.8%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>24300</v>
+        <v>67100</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>21050</v>
+        <v>62900</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>25400</v>
+        <v>67200</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>18154.5</v>
+        <v>59542.5</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>18613.5</v>
+        <v>60532.5</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>14523.6</v>
+        <v>47634</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>14890.8</v>
+        <v>48426</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>14500</v>
+        <v>47650</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>67.58620689655173</v>
+        <v>40.81846799580273</v>
       </c>
       <c r="O22" s="7" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr"/>
       <c r="Q22" s="5" t="n">
-        <v>13060</v>
+        <v>42900</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>86.06431852986218</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="S22" s="7" t="inlineStr"/>
       <c r="T22" s="7" t="inlineStr"/>
       <c r="U22" s="5" t="n">
-        <v>11760</v>
+        <v>38650</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>106.6326530612245</v>
+        <v>73.60931435963778</v>
       </c>
       <c r="W22" s="7" t="inlineStr"/>
       <c r="X22" s="7" t="inlineStr"/>
@@ -2326,12 +2330,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2346,51 +2350,51 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.9%</t>
+          <t>1차 매수선까지 40.4%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>434500</v>
+        <v>45700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>358000</v>
+        <v>42600</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>453500</v>
+        <v>45750</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>339700</v>
+        <v>40850</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>345725</v>
+        <v>41332.5</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>271760</v>
+        <v>32680</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>276580</v>
+        <v>33066</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>270000</v>
+        <v>32550</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>60.92592592592593</v>
+        <v>40.39938556067588</v>
       </c>
       <c r="O23" s="7" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr"/>
       <c r="Q23" s="5" t="n">
-        <v>243500</v>
+        <v>29300</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>78.43942505133469</v>
+        <v>55.97269624573379</v>
       </c>
       <c r="S23" s="7" t="inlineStr"/>
       <c r="T23" s="7" t="inlineStr"/>
       <c r="U23" s="5" t="n">
-        <v>219500</v>
+        <v>26400</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>97.9498861047836</v>
+        <v>73.10606060606061</v>
       </c>
       <c r="W23" s="7" t="inlineStr"/>
       <c r="X23" s="7" t="inlineStr"/>
@@ -2406,12 +2410,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2426,51 +2430,51 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 85.3%</t>
+          <t>1차 매수선까지 49.6%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>278000</v>
+        <v>46600</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>233500</v>
+        <v>41100</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>284500</v>
+        <v>49550</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>190200</v>
+        <v>38787.5</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>193850</v>
+        <v>39682.5</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>152160</v>
+        <v>31030</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>155080</v>
+        <v>31746</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>150000</v>
+        <v>31150</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>85.33333333333334</v>
+        <v>49.59871589085072</v>
       </c>
       <c r="O24" s="7" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr"/>
       <c r="Q24" s="5" t="n">
-        <v>135100</v>
+        <v>28050</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>105.7735011102887</v>
+        <v>66.1319073083779</v>
       </c>
       <c r="S24" s="7" t="inlineStr"/>
       <c r="T24" s="7" t="inlineStr"/>
       <c r="U24" s="5" t="n">
-        <v>121600</v>
+        <v>25250</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>128.6184210526316</v>
+        <v>84.55445544554455</v>
       </c>
       <c r="W24" s="7" t="inlineStr"/>
       <c r="X24" s="7" t="inlineStr"/>
@@ -2486,12 +2490,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2506,51 +2510,51 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.9%</t>
+          <t>1차 매수선까지 30.7%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>220500</v>
+        <v>1039000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>214000</v>
+        <v>981000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>235000</v>
+        <v>1056000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>189055</v>
+        <v>1008450</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>192275</v>
+        <v>1005050</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>151244</v>
+        <v>806760</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>153820</v>
+        <v>804040</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>151100</v>
+        <v>795000</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>45.92984778292521</v>
+        <v>30.69182389937107</v>
       </c>
       <c r="O25" s="7" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr"/>
       <c r="Q25" s="5" t="n">
-        <v>136000</v>
+        <v>716000</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>62.13235294117647</v>
+        <v>45.11173184357542</v>
       </c>
       <c r="S25" s="7" t="inlineStr"/>
       <c r="T25" s="7" t="inlineStr"/>
       <c r="U25" s="5" t="n">
-        <v>122500</v>
+        <v>645000</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>80</v>
+        <v>61.08527131782946</v>
       </c>
       <c r="W25" s="7" t="inlineStr"/>
       <c r="X25" s="7" t="inlineStr"/>
@@ -2566,12 +2570,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2586,51 +2590,51 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.3%</t>
+          <t>1차 매수선까지 33.7%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>59900</v>
+        <v>118500</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>58700</v>
+        <v>117500</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>64300</v>
+        <v>121700</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>56485</v>
+        <v>111315</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>56505</v>
+        <v>112195</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>45188</v>
+        <v>89052</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>45204</v>
+        <v>89756</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>44600</v>
+        <v>88600</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>34.30493273542601</v>
+        <v>33.74717832957111</v>
       </c>
       <c r="O26" s="7" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr"/>
       <c r="Q26" s="5" t="n">
-        <v>40150</v>
+        <v>79800</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>49.19053549190536</v>
+        <v>48.49624060150376</v>
       </c>
       <c r="S26" s="7" t="inlineStr"/>
       <c r="T26" s="7" t="inlineStr"/>
       <c r="U26" s="5" t="n">
-        <v>36150</v>
+        <v>71900</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>65.69847856154909</v>
+        <v>64.81223922114047</v>
       </c>
       <c r="W26" s="7" t="inlineStr"/>
       <c r="X26" s="7" t="inlineStr"/>
@@ -2646,12 +2650,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2666,51 +2670,51 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.0%</t>
+          <t>1차 매수선까지 69.3%</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>42700</v>
+        <v>25250</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>41700</v>
+        <v>24150</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>45000</v>
+        <v>25600</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>33670</v>
+        <v>18661</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>34347.5</v>
+        <v>19144.5</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>26936</v>
+        <v>14928.8</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>27478</v>
+        <v>15315.6</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>26850</v>
+        <v>14910</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>59.0316573556797</v>
+        <v>69.34942991281019</v>
       </c>
       <c r="O27" s="7" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr"/>
       <c r="Q27" s="5" t="n">
-        <v>24200</v>
+        <v>13420</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>76.44628099173553</v>
+        <v>88.15201192250373</v>
       </c>
       <c r="S27" s="7" t="inlineStr"/>
       <c r="T27" s="7" t="inlineStr"/>
       <c r="U27" s="5" t="n">
-        <v>21800</v>
+        <v>12080</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>95.87155963302753</v>
+        <v>109.023178807947</v>
       </c>
       <c r="W27" s="7" t="inlineStr"/>
       <c r="X27" s="7" t="inlineStr"/>
@@ -2726,12 +2730,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2746,51 +2750,51 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.7%</t>
+          <t>1차 매수선까지 82.6%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>70300</v>
+        <v>280000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>67000</v>
+        <v>264000</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>72100</v>
+        <v>281500</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>61060</v>
+        <v>193950</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>61830</v>
+        <v>197900</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>48848</v>
+        <v>155160</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>49464</v>
+        <v>158320</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>48600</v>
+        <v>153300</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>44.65020576131688</v>
+        <v>82.64840182648402</v>
       </c>
       <c r="O28" s="7" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr"/>
       <c r="Q28" s="5" t="n">
-        <v>43750</v>
+        <v>138000</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>60.68571428571429</v>
+        <v>102.8985507246377</v>
       </c>
       <c r="S28" s="7" t="inlineStr"/>
       <c r="T28" s="7" t="inlineStr"/>
       <c r="U28" s="5" t="n">
-        <v>39400</v>
+        <v>124300</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>78.42639593908629</v>
+        <v>125.2614641995173</v>
       </c>
       <c r="W28" s="7" t="inlineStr"/>
       <c r="X28" s="7" t="inlineStr"/>
@@ -2806,12 +2810,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2826,51 +2830,51 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.8%</t>
+          <t>1차 매수선까지 33.4%</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>488000</v>
+        <v>59500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>472000</v>
+        <v>58500</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>491500</v>
+        <v>62000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>457625</v>
+        <v>56485</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>458675</v>
+        <v>56485</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>366100</v>
+        <v>45188</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>366940</v>
+        <v>45188</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>362000</v>
+        <v>44600</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>34.80662983425415</v>
+        <v>33.40807174887892</v>
       </c>
       <c r="O29" s="7" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr"/>
       <c r="Q29" s="5" t="n">
-        <v>326000</v>
+        <v>40150</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>49.69325153374233</v>
+        <v>48.19427148194271</v>
       </c>
       <c r="S29" s="7" t="inlineStr"/>
       <c r="T29" s="7" t="inlineStr"/>
       <c r="U29" s="5" t="n">
-        <v>293500</v>
+        <v>36150</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>66.26916524701873</v>
+        <v>64.59197786998617</v>
       </c>
       <c r="W29" s="7" t="inlineStr"/>
       <c r="X29" s="7" t="inlineStr"/>
@@ -2886,12 +2890,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2906,51 +2910,51 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.8%</t>
+          <t>1차 매수선까지 59.5%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>28100</v>
+        <v>43850</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>27800</v>
+        <v>42250</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>29200</v>
+        <v>45200</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>27267.5</v>
+        <v>34405</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>27377.5</v>
+        <v>35172.5</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>21814</v>
+        <v>27524</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>21902</v>
+        <v>28138</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>21650</v>
+        <v>27500</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>29.79214780600462</v>
+        <v>59.45454545454546</v>
       </c>
       <c r="O30" s="7" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr"/>
       <c r="Q30" s="5" t="n">
-        <v>19490</v>
+        <v>24800</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>44.17650076962545</v>
+        <v>76.81451612903226</v>
       </c>
       <c r="S30" s="7" t="inlineStr"/>
       <c r="T30" s="7" t="inlineStr"/>
       <c r="U30" s="5" t="n">
-        <v>17550</v>
+        <v>22350</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>60.11396011396012</v>
+        <v>96.19686800894854</v>
       </c>
       <c r="W30" s="7" t="inlineStr"/>
       <c r="X30" s="7" t="inlineStr"/>
@@ -2966,12 +2970,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2986,51 +2990,51 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.7%</t>
+          <t>1차 매수선까지 36.9%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>232000</v>
+        <v>67300</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>226500</v>
+        <v>65400</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>238000</v>
+        <v>70900</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>222000</v>
+        <v>61680</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>222825</v>
+        <v>62330</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>177600</v>
+        <v>49344</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>178260</v>
+        <v>49864</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>176100</v>
+        <v>49150</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>31.74332765474163</v>
+        <v>36.92777212614445</v>
       </c>
       <c r="O31" s="7" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr"/>
       <c r="Q31" s="5" t="n">
-        <v>158500</v>
+        <v>44250</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>46.37223974763407</v>
+        <v>52.09039548022599</v>
       </c>
       <c r="S31" s="7" t="inlineStr"/>
       <c r="T31" s="7" t="inlineStr"/>
       <c r="U31" s="5" t="n">
-        <v>142700</v>
+        <v>39850</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>62.57883672039243</v>
+        <v>68.88331242158094</v>
       </c>
       <c r="W31" s="7" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr"/>
@@ -3046,12 +3050,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3066,51 +3070,51 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.4%</t>
+          <t>1차 매수선까지 26.6%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>966000</v>
+        <v>27400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>912000</v>
+        <v>27100</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>968000</v>
+        <v>28800</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>718100</v>
+        <v>27342.5</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>739750</v>
+        <v>27312.5</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>574480</v>
+        <v>21874</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>591800</v>
+        <v>21850</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>577000</v>
+        <v>21650</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>67.41767764298093</v>
+        <v>26.55889145496536</v>
       </c>
       <c r="O32" s="7" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr"/>
       <c r="Q32" s="5" t="n">
-        <v>520000</v>
+        <v>19490</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>85.76923076923076</v>
+        <v>40.58491534120062</v>
       </c>
       <c r="S32" s="7" t="inlineStr"/>
       <c r="T32" s="7" t="inlineStr"/>
       <c r="U32" s="5" t="n">
-        <v>468500</v>
+        <v>17550</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>106.1899679829242</v>
+        <v>56.12535612535613</v>
       </c>
       <c r="W32" s="7" t="inlineStr"/>
       <c r="X32" s="7" t="inlineStr"/>
@@ -3126,12 +3130,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3146,51 +3150,51 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.8%</t>
+          <t>1차 매수선까지 37.5%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>11820</v>
+        <v>243500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>11590</v>
+        <v>229000</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>12770</v>
+        <v>248000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>10962.5</v>
+        <v>223400</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>11111</v>
+        <v>224600</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>8770</v>
+        <v>178720</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>8888.800000000001</v>
+        <v>179680</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>8770</v>
+        <v>177100</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>34.77765108323831</v>
+        <v>37.49294184076793</v>
       </c>
       <c r="O33" s="7" t="inlineStr"/>
       <c r="P33" s="7" t="inlineStr"/>
       <c r="Q33" s="5" t="n">
-        <v>7900</v>
+        <v>159400</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>49.62025316455696</v>
+        <v>52.7603513174404</v>
       </c>
       <c r="S33" s="7" t="inlineStr"/>
       <c r="T33" s="7" t="inlineStr"/>
       <c r="U33" s="5" t="n">
-        <v>7120</v>
+        <v>143500</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>66.01123595505618</v>
+        <v>69.68641114982579</v>
       </c>
       <c r="W33" s="7" t="inlineStr"/>
       <c r="X33" s="7" t="inlineStr"/>
@@ -3206,12 +3210,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3226,51 +3230,51 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 66.8%</t>
+          <t>1차 매수선까지 70.6%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>209500</v>
+        <v>1017000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>163400</v>
+        <v>938000</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>209500</v>
+        <v>1025000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>158340</v>
+        <v>742300</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>161130</v>
+        <v>766050</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>126672</v>
+        <v>593840</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>128904</v>
+        <v>612840</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>125600</v>
+        <v>596000</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>66.79936305732484</v>
+        <v>70.63758389261746</v>
       </c>
       <c r="O34" s="7" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr"/>
       <c r="Q34" s="5" t="n">
-        <v>113100</v>
+        <v>537000</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>85.2343059239611</v>
+        <v>89.38547486033519</v>
       </c>
       <c r="S34" s="7" t="inlineStr"/>
       <c r="T34" s="7" t="inlineStr"/>
       <c r="U34" s="5" t="n">
-        <v>101800</v>
+        <v>483500</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>105.7956777996071</v>
+        <v>110.3412616339193</v>
       </c>
       <c r="W34" s="7" t="inlineStr"/>
       <c r="X34" s="7" t="inlineStr"/>
@@ -3286,12 +3290,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3306,51 +3310,51 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.4%</t>
+          <t>1차 매수선까지 36.1%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>126600</v>
+        <v>12170</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>114700</v>
+        <v>11650</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>131100</v>
+        <v>12800</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>109445</v>
+        <v>11128.5</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>110790</v>
+        <v>11330.5</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>87556</v>
+        <v>8902.800000000001</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>88632</v>
+        <v>9064.4</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>87100</v>
+        <v>8940</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>45.35017221584386</v>
+        <v>36.12975391498882</v>
       </c>
       <c r="O35" s="7" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr"/>
       <c r="Q35" s="5" t="n">
-        <v>78400</v>
+        <v>8050</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>61.47959183673469</v>
+        <v>51.18012422360248</v>
       </c>
       <c r="S35" s="7" t="inlineStr"/>
       <c r="T35" s="7" t="inlineStr"/>
       <c r="U35" s="5" t="n">
-        <v>70600</v>
+        <v>7250</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>79.3201133144476</v>
+        <v>67.86206896551724</v>
       </c>
       <c r="W35" s="7" t="inlineStr"/>
       <c r="X35" s="7" t="inlineStr"/>
@@ -3366,12 +3370,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>454910</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3386,51 +3390,51 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.6%</t>
+          <t>1차 매수선까지 60.9%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>425000</v>
+        <v>92500</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>389500</v>
+        <v>76700</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>435500</v>
+        <v>95500</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>367250</v>
+        <v>72225</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>368700</v>
+        <v>73560</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>293800</v>
+        <v>57780</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>294960</v>
+        <v>58848</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>290000</v>
+        <v>57500</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>46.55172413793103</v>
+        <v>60.86956521739131</v>
       </c>
       <c r="O36" s="7" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr"/>
       <c r="Q36" s="5" t="n">
-        <v>261500</v>
+        <v>51800</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>62.52390057361377</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="S36" s="7" t="inlineStr"/>
       <c r="T36" s="7" t="inlineStr"/>
       <c r="U36" s="5" t="n">
-        <v>235500</v>
+        <v>46650</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>80.46709129511677</v>
+        <v>98.28510182207931</v>
       </c>
       <c r="W36" s="7" t="inlineStr"/>
       <c r="X36" s="7" t="inlineStr"/>
@@ -3446,12 +3450,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3466,51 +3470,51 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.4%</t>
+          <t>1차 매수선까지 72.3%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>343000</v>
+        <v>54800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>321500</v>
+        <v>42200</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>345000</v>
+        <v>54800</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>286925</v>
+        <v>40007.5</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>290550</v>
+        <v>40882.5</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>229540</v>
+        <v>32006</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>232440</v>
+        <v>32706</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>228000</v>
+        <v>31800</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>50.43859649122807</v>
+        <v>72.32704402515722</v>
       </c>
       <c r="O37" s="7" t="inlineStr"/>
       <c r="P37" s="7" t="inlineStr"/>
       <c r="Q37" s="5" t="n">
-        <v>205500</v>
+        <v>28650</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>66.90997566909975</v>
+        <v>91.2739965095986</v>
       </c>
       <c r="S37" s="7" t="inlineStr"/>
       <c r="T37" s="7" t="inlineStr"/>
       <c r="U37" s="5" t="n">
-        <v>185000</v>
+        <v>25800</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>85.4054054054054</v>
+        <v>112.4031007751938</v>
       </c>
       <c r="W37" s="7" t="inlineStr"/>
       <c r="X37" s="7" t="inlineStr"/>
@@ -3526,12 +3530,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>090710</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3546,51 +3550,51 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.1%</t>
+          <t>1차 매수선까지 74.6%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>6450</v>
+        <v>224500</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>6090</v>
+        <v>209500</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>6500</v>
+        <v>245000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>4876.5</v>
+        <v>161880</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>5035</v>
+        <v>165445</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3901.2</v>
+        <v>129504</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>4028</v>
+        <v>132356</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>3930</v>
+        <v>128600</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>64.12213740458014</v>
+        <v>74.57231726283048</v>
       </c>
       <c r="O38" s="7" t="inlineStr"/>
       <c r="P38" s="7" t="inlineStr"/>
       <c r="Q38" s="5" t="n">
-        <v>3540</v>
+        <v>115800</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>82.20338983050848</v>
+        <v>93.86873920552678</v>
       </c>
       <c r="S38" s="7" t="inlineStr"/>
       <c r="T38" s="7" t="inlineStr"/>
       <c r="U38" s="5" t="n">
-        <v>3190</v>
+        <v>104300</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>102.1943573667712</v>
+        <v>115.2444870565676</v>
       </c>
       <c r="W38" s="7" t="inlineStr"/>
       <c r="X38" s="7" t="inlineStr"/>
@@ -3606,12 +3610,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3626,51 +3630,51 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.6%</t>
+          <t>1차 매수선까지 53.2%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>40600</v>
+        <v>135600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>40550</v>
+        <v>126100</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>45600</v>
+        <v>136800</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>37910</v>
+        <v>111240</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>38487.5</v>
+        <v>112955</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>30328</v>
+        <v>88992</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>30790</v>
+        <v>90364</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>30400</v>
+        <v>88500</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>33.55263157894737</v>
+        <v>53.22033898305085</v>
       </c>
       <c r="O39" s="7" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr"/>
       <c r="Q39" s="5" t="n">
-        <v>27400</v>
+        <v>79700</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>48.17518248175183</v>
+        <v>70.13801756587202</v>
       </c>
       <c r="S39" s="7" t="inlineStr"/>
       <c r="T39" s="7" t="inlineStr"/>
       <c r="U39" s="5" t="n">
-        <v>24700</v>
+        <v>71800</v>
       </c>
       <c r="V39" s="6" t="n">
-        <v>64.37246963562752</v>
+        <v>88.85793871866295</v>
       </c>
       <c r="W39" s="7" t="inlineStr"/>
       <c r="X39" s="7" t="inlineStr"/>
@@ -3686,12 +3690,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3706,51 +3710,51 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 24.2%</t>
+          <t>1차 매수선까지 46.5%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>23500</v>
+        <v>428500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>22550</v>
+        <v>410000</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>23800</v>
+        <v>432000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>24397.5</v>
+        <v>368875</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>23877.5</v>
+        <v>372075</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>19518</v>
+        <v>295100</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>19102</v>
+        <v>297660</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>18920</v>
+        <v>292500</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>24.20718816067653</v>
+        <v>46.49572649572649</v>
       </c>
       <c r="O40" s="7" t="inlineStr"/>
       <c r="P40" s="7" t="inlineStr"/>
       <c r="Q40" s="5" t="n">
-        <v>17030</v>
+        <v>263500</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>37.99177921315326</v>
+        <v>62.61859582542695</v>
       </c>
       <c r="S40" s="7" t="inlineStr"/>
       <c r="T40" s="7" t="inlineStr"/>
       <c r="U40" s="5" t="n">
-        <v>15330</v>
+        <v>237500</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>53.2941943900848</v>
+        <v>80.42105263157895</v>
       </c>
       <c r="W40" s="7" t="inlineStr"/>
       <c r="X40" s="7" t="inlineStr"/>
@@ -3766,12 +3770,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3786,51 +3790,51 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.0%</t>
+          <t>1차 매수선까지 48.2%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>9010</v>
+        <v>343000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>8890</v>
+        <v>337500</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>9080</v>
+        <v>362500</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>9852.5</v>
+        <v>290550</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>9685</v>
+        <v>294375</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>7882</v>
+        <v>232440</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>7748</v>
+        <v>235500</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>7700</v>
+        <v>231500</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>17.01298701298701</v>
+        <v>48.16414686825054</v>
       </c>
       <c r="O41" s="7" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr"/>
       <c r="Q41" s="5" t="n">
-        <v>6940</v>
+        <v>208500</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>29.82708933717579</v>
+        <v>64.5083932853717</v>
       </c>
       <c r="S41" s="7" t="inlineStr"/>
       <c r="T41" s="7" t="inlineStr"/>
       <c r="U41" s="5" t="n">
-        <v>6250</v>
+        <v>187700</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>44.16</v>
+        <v>82.73841236014917</v>
       </c>
       <c r="W41" s="7" t="inlineStr"/>
       <c r="X41" s="7" t="inlineStr"/>
@@ -3846,12 +3850,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3866,51 +3870,51 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.8%</t>
+          <t>1차 매수선까지 73.3%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>15950</v>
+        <v>7090</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>15860</v>
+        <v>6500</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>16250</v>
+        <v>7330</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>17111.5</v>
+        <v>5067</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>16909.5</v>
+        <v>5261.5</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>13689.2</v>
+        <v>4053.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>13527.6</v>
+        <v>4209.2</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>13430</v>
+        <v>4090</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>18.76396128071482</v>
+        <v>73.34963325183375</v>
       </c>
       <c r="O42" s="7" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr"/>
       <c r="Q42" s="5" t="n">
-        <v>12090</v>
+        <v>3685</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>31.92721257237386</v>
+        <v>92.40162822252374</v>
       </c>
       <c r="S42" s="7" t="inlineStr"/>
       <c r="T42" s="7" t="inlineStr"/>
       <c r="U42" s="5" t="n">
-        <v>10890</v>
+        <v>3320</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>46.46464646464646</v>
+        <v>113.5542168674699</v>
       </c>
       <c r="W42" s="7" t="inlineStr"/>
       <c r="X42" s="7" t="inlineStr"/>
@@ -3926,12 +3930,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3946,51 +3950,51 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.7%</t>
+          <t>1차 매수선까지 46.5%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>175800</v>
+        <v>27600</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>174500</v>
+        <v>24650</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>177300</v>
+        <v>28250</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>175300</v>
+        <v>24082.5</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>175160</v>
+        <v>23980</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>140240</v>
+        <v>19266</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>140128</v>
+        <v>19184</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>138700</v>
+        <v>18840</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>26.74837779379957</v>
+        <v>46.49681528662421</v>
       </c>
       <c r="O43" s="7" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr"/>
       <c r="Q43" s="5" t="n">
-        <v>124900</v>
+        <v>16960</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>40.75260208166534</v>
+        <v>62.73584905660378</v>
       </c>
       <c r="S43" s="7" t="inlineStr"/>
       <c r="T43" s="7" t="inlineStr"/>
       <c r="U43" s="5" t="n">
-        <v>112500</v>
+        <v>15270</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>56.26666666666667</v>
+        <v>80.74656188605108</v>
       </c>
       <c r="W43" s="7" t="inlineStr"/>
       <c r="X43" s="7" t="inlineStr"/>
@@ -4006,12 +4010,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -4026,51 +4030,51 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 16.4%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>234000</v>
+        <v>8820</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>221000</v>
+        <v>8770</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>238500</v>
+        <v>9190</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>210815</v>
+        <v>9675.5</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>211565</v>
+        <v>9528.5</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>168652</v>
+        <v>7740.400000000001</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>169252</v>
+        <v>7622.8</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>166600</v>
+        <v>7580</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>40.45618247298919</v>
+        <v>16.35883905013193</v>
       </c>
       <c r="O44" s="7" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr"/>
       <c r="Q44" s="5" t="n">
-        <v>150000</v>
+        <v>6830</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>56.00000000000001</v>
+        <v>29.13616398243045</v>
       </c>
       <c r="S44" s="7" t="inlineStr"/>
       <c r="T44" s="7" t="inlineStr"/>
       <c r="U44" s="5" t="n">
-        <v>135100</v>
+        <v>6150</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>73.20503330866025</v>
+        <v>43.41463414634146</v>
       </c>
       <c r="W44" s="7" t="inlineStr"/>
       <c r="X44" s="7" t="inlineStr"/>
@@ -4086,12 +4090,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -4106,51 +4110,51 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.7%</t>
+          <t>1차 매수선까지 17.1%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>8060</v>
+        <v>15580</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>8030</v>
+        <v>15400</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>8350</v>
+        <v>16430</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>9235.5</v>
+        <v>16891</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>9131</v>
+        <v>16747</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>7388.400000000001</v>
+        <v>13512.8</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>7304.8</v>
+        <v>13397.6</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>7280</v>
+        <v>13310</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>10.71428571428571</v>
+        <v>17.05484598046582</v>
       </c>
       <c r="O45" s="7" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr"/>
       <c r="Q45" s="5" t="n">
-        <v>6560</v>
+        <v>11980</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>22.86585365853659</v>
+        <v>30.05008347245409</v>
       </c>
       <c r="S45" s="7" t="inlineStr"/>
       <c r="T45" s="7" t="inlineStr"/>
       <c r="U45" s="5" t="n">
-        <v>5910</v>
+        <v>10790</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>36.37901861252115</v>
+        <v>44.39295644114921</v>
       </c>
       <c r="W45" s="7" t="inlineStr"/>
       <c r="X45" s="7" t="inlineStr"/>
@@ -4166,12 +4170,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4186,51 +4190,51 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.3%</t>
+          <t>1차 매수선까지 26.0%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>86900</v>
+        <v>174900</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>84800</v>
+        <v>173700</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>90800</v>
+        <v>176600</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>65667.5</v>
+        <v>175115</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>67730</v>
+        <v>175195</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>52534</v>
+        <v>140092</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>54184</v>
+        <v>140156</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>52900</v>
+        <v>138800</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>64.27221172022685</v>
+        <v>26.00864553314121</v>
       </c>
       <c r="O46" s="7" t="inlineStr"/>
       <c r="P46" s="7" t="inlineStr"/>
       <c r="Q46" s="5" t="n">
-        <v>47650</v>
+        <v>125000</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>82.37145855194123</v>
+        <v>39.92</v>
       </c>
       <c r="S46" s="7" t="inlineStr"/>
       <c r="T46" s="7" t="inlineStr"/>
       <c r="U46" s="5" t="n">
-        <v>42900</v>
+        <v>112600</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>102.5641025641026</v>
+        <v>55.32859680284192</v>
       </c>
       <c r="W46" s="7" t="inlineStr"/>
       <c r="X46" s="7" t="inlineStr"/>
@@ -4246,12 +4250,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4266,51 +4270,51 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 40.6%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>103700</v>
+        <v>235500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>102500</v>
+        <v>224000</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>108000</v>
+        <v>236000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>102710</v>
+        <v>211640</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>102450</v>
+        <v>212740</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>82168</v>
+        <v>169312</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>81960</v>
+        <v>170192</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>81100</v>
+        <v>167500</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27.86683107274969</v>
+        <v>40.59701492537313</v>
       </c>
       <c r="O47" s="7" t="inlineStr"/>
       <c r="P47" s="7" t="inlineStr"/>
       <c r="Q47" s="5" t="n">
-        <v>73000</v>
+        <v>150800</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>42.05479452054794</v>
+        <v>56.16710875331565</v>
       </c>
       <c r="S47" s="7" t="inlineStr"/>
       <c r="T47" s="7" t="inlineStr"/>
       <c r="U47" s="5" t="n">
-        <v>65800</v>
+        <v>135800</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>57.59878419452887</v>
+        <v>73.41678939617083</v>
       </c>
       <c r="W47" s="7" t="inlineStr"/>
       <c r="X47" s="7" t="inlineStr"/>
@@ -4326,12 +4330,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4341,56 +4345,56 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.1%</t>
+          <t>1차 매수선까지 9.6% (접근 중!)</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>167000</v>
+        <v>7880</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>165100</v>
+        <v>7720</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>172400</v>
+        <v>8220</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>182965</v>
+        <v>9122</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>180915</v>
+        <v>9021</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>146372</v>
+        <v>7297.6</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>144732</v>
+        <v>7216.8</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>143900</v>
+        <v>7190</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>16.05281445448228</v>
+        <v>9.596662030598054</v>
       </c>
       <c r="O48" s="7" t="inlineStr"/>
       <c r="P48" s="7" t="inlineStr"/>
       <c r="Q48" s="5" t="n">
-        <v>129600</v>
+        <v>6480</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>28.85802469135803</v>
+        <v>21.60493827160494</v>
       </c>
       <c r="S48" s="7" t="inlineStr"/>
       <c r="T48" s="7" t="inlineStr"/>
       <c r="U48" s="5" t="n">
-        <v>116700</v>
+        <v>5840</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>43.10197086546701</v>
+        <v>34.93150684931507</v>
       </c>
       <c r="W48" s="7" t="inlineStr"/>
       <c r="X48" s="7" t="inlineStr"/>
@@ -4406,12 +4410,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4426,51 +4430,51 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.6%</t>
+          <t>1차 매수선까지 83.9%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>435500</v>
+        <v>101700</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>430000</v>
+        <v>87500</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>436500</v>
+        <v>108000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>434500</v>
+        <v>68470</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>434400</v>
+        <v>71330</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>347600</v>
+        <v>54776</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>347520</v>
+        <v>57064</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>344000</v>
+        <v>55300</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>26.59883720930232</v>
+        <v>83.90596745027125</v>
       </c>
       <c r="O49" s="7" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr"/>
       <c r="Q49" s="5" t="n">
-        <v>310000</v>
+        <v>49800</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>40.48387096774194</v>
+        <v>104.2168674698795</v>
       </c>
       <c r="S49" s="7" t="inlineStr"/>
       <c r="T49" s="7" t="inlineStr"/>
       <c r="U49" s="5" t="n">
-        <v>279500</v>
+        <v>44850</v>
       </c>
       <c r="V49" s="6" t="n">
-        <v>55.81395348837209</v>
+        <v>126.7558528428094</v>
       </c>
       <c r="W49" s="7" t="inlineStr"/>
       <c r="X49" s="7" t="inlineStr"/>
@@ -4486,12 +4490,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4506,51 +4510,51 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.6%</t>
+          <t>1차 매수선까지 34.2%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>21200</v>
+        <v>108800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>21050</v>
+        <v>103200</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>21850</v>
+        <v>108900</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>22647.5</v>
+        <v>102705</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>22505</v>
+        <v>102745</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>18118</v>
+        <v>82164</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>18004</v>
+        <v>82196</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>17880</v>
+        <v>81100</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>18.56823266219239</v>
+        <v>34.1553637484587</v>
       </c>
       <c r="O50" s="7" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr"/>
       <c r="Q50" s="5" t="n">
-        <v>16100</v>
+        <v>73000</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>31.67701863354037</v>
+        <v>49.04109589041096</v>
       </c>
       <c r="S50" s="7" t="inlineStr"/>
       <c r="T50" s="7" t="inlineStr"/>
       <c r="U50" s="5" t="n">
-        <v>14500</v>
+        <v>65800</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>46.20689655172414</v>
+        <v>65.34954407294833</v>
       </c>
       <c r="W50" s="7" t="inlineStr"/>
       <c r="X50" s="7" t="inlineStr"/>
@@ -4566,12 +4570,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4586,51 +4590,51 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 27.5%</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>22050</v>
+        <v>181500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>21500</v>
+        <v>165700</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>22350</v>
+        <v>186500</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>21717</v>
+        <v>181640</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>21789.5</v>
+        <v>179790</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>17373.6</v>
+        <v>145312</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>17431.6</v>
+        <v>143832</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>17240</v>
+        <v>142300</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>27.90023201856148</v>
+        <v>27.5474349964863</v>
       </c>
       <c r="O51" s="7" t="inlineStr"/>
       <c r="P51" s="7" t="inlineStr"/>
       <c r="Q51" s="5" t="n">
-        <v>15520</v>
+        <v>128100</v>
       </c>
       <c r="R51" s="6" t="n">
-        <v>42.07474226804123</v>
+        <v>41.68618266978923</v>
       </c>
       <c r="S51" s="7" t="inlineStr"/>
       <c r="T51" s="7" t="inlineStr"/>
       <c r="U51" s="5" t="n">
-        <v>13970</v>
+        <v>115300</v>
       </c>
       <c r="V51" s="6" t="n">
-        <v>57.83822476735862</v>
+        <v>57.41543798785776</v>
       </c>
       <c r="W51" s="7" t="inlineStr"/>
       <c r="X51" s="7" t="inlineStr"/>
@@ -4646,12 +4650,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4666,51 +4670,51 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 25.1%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>53200</v>
+        <v>430500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>52000</v>
+        <v>429000</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>54600</v>
+        <v>438500</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>51265</v>
+        <v>434150</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>51190</v>
+        <v>434125</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>41012</v>
+        <v>347320</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>40952</v>
+        <v>347300</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>40450</v>
+        <v>344000</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>31.5203955500618</v>
+        <v>25.1453488372093</v>
       </c>
       <c r="O52" s="7" t="inlineStr"/>
       <c r="P52" s="7" t="inlineStr"/>
       <c r="Q52" s="5" t="n">
-        <v>36450</v>
+        <v>310000</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>45.95336076817559</v>
+        <v>38.87096774193549</v>
       </c>
       <c r="S52" s="7" t="inlineStr"/>
       <c r="T52" s="7" t="inlineStr"/>
       <c r="U52" s="5" t="n">
-        <v>32850</v>
+        <v>279500</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>61.9482496194825</v>
+        <v>54.02504472271914</v>
       </c>
       <c r="W52" s="7" t="inlineStr"/>
       <c r="X52" s="7" t="inlineStr"/>
@@ -4726,12 +4730,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4746,51 +4750,51 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.0%</t>
+          <t>1차 매수선까지 26.5%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>49400</v>
+        <v>22500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>48250</v>
+        <v>21350</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>50400</v>
+        <v>23150</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>47672.5</v>
+        <v>22570</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>48040</v>
+        <v>22470</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>38138</v>
+        <v>18056</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>38432</v>
+        <v>17976</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>38000</v>
+        <v>17790</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>30</v>
+        <v>26.47554806070826</v>
       </c>
       <c r="O53" s="7" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr"/>
       <c r="Q53" s="5" t="n">
-        <v>34250</v>
+        <v>16020</v>
       </c>
       <c r="R53" s="6" t="n">
-        <v>44.23357664233576</v>
+        <v>40.44943820224719</v>
       </c>
       <c r="S53" s="7" t="inlineStr"/>
       <c r="T53" s="7" t="inlineStr"/>
       <c r="U53" s="5" t="n">
-        <v>30850</v>
+        <v>14420</v>
       </c>
       <c r="V53" s="6" t="n">
-        <v>60.12965964343599</v>
+        <v>56.03328710124826</v>
       </c>
       <c r="W53" s="7" t="inlineStr"/>
       <c r="X53" s="7" t="inlineStr"/>
@@ -4806,12 +4810,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4826,51 +4830,51 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.3%</t>
+          <t>1차 매수선까지 27.5%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>22700</v>
+        <v>22000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>22000</v>
+        <v>21850</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>23100</v>
+        <v>22750</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>23712.5</v>
+        <v>21787</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>23595</v>
+        <v>21807</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>18970</v>
+        <v>17429.6</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>18876</v>
+        <v>17445.6</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>18720</v>
+        <v>17260</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>21.26068376068376</v>
+        <v>27.46234067207416</v>
       </c>
       <c r="O54" s="7" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr"/>
       <c r="Q54" s="5" t="n">
-        <v>16850</v>
+        <v>15540</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>34.71810089020772</v>
+        <v>41.57014157014157</v>
       </c>
       <c r="S54" s="7" t="inlineStr"/>
       <c r="T54" s="7" t="inlineStr"/>
       <c r="U54" s="5" t="n">
-        <v>15170</v>
+        <v>13990</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>49.63744232036915</v>
+        <v>57.25518227305218</v>
       </c>
       <c r="W54" s="7" t="inlineStr"/>
       <c r="X54" s="7" t="inlineStr"/>
@@ -4886,12 +4890,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4906,51 +4910,51 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.5%</t>
+          <t>1차 매수선까지 34.8%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>477000</v>
+        <v>54600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>451500</v>
+        <v>51800</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>484000</v>
+        <v>54800</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>436325</v>
+        <v>51260</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>440175</v>
+        <v>51285</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>349060</v>
+        <v>41008</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>352140</v>
+        <v>41028</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>347000</v>
+        <v>40500</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>37.46397694524496</v>
+        <v>34.81481481481482</v>
       </c>
       <c r="O55" s="7" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr"/>
       <c r="Q55" s="5" t="n">
-        <v>312500</v>
+        <v>36500</v>
       </c>
       <c r="R55" s="6" t="n">
-        <v>52.64</v>
+        <v>49.58904109589042</v>
       </c>
       <c r="S55" s="7" t="inlineStr"/>
       <c r="T55" s="7" t="inlineStr"/>
       <c r="U55" s="5" t="n">
-        <v>281500</v>
+        <v>32900</v>
       </c>
       <c r="V55" s="6" t="n">
-        <v>69.44937833037301</v>
+        <v>65.95744680851064</v>
       </c>
       <c r="W55" s="7" t="inlineStr"/>
       <c r="X55" s="7" t="inlineStr"/>
@@ -4966,12 +4970,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4986,51 +4990,51 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 33.9%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>244000</v>
+        <v>51200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>232000</v>
+        <v>49650</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>246000</v>
+        <v>53900</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>218130</v>
+        <v>48130</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>220590</v>
+        <v>48445</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>174504</v>
+        <v>38504</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>176472</v>
+        <v>38756</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>173700</v>
+        <v>38250</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>40.4720782959125</v>
+        <v>33.8562091503268</v>
       </c>
       <c r="O56" s="7" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr"/>
       <c r="Q56" s="5" t="n">
-        <v>156400</v>
+        <v>34450</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>56.01023017902813</v>
+        <v>48.62119013062409</v>
       </c>
       <c r="S56" s="7" t="inlineStr"/>
       <c r="T56" s="7" t="inlineStr"/>
       <c r="U56" s="5" t="n">
-        <v>140800</v>
+        <v>31050</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>73.29545454545455</v>
+        <v>64.89533011272141</v>
       </c>
       <c r="W56" s="7" t="inlineStr"/>
       <c r="X56" s="7" t="inlineStr"/>
@@ -5046,12 +5050,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -5066,51 +5070,51 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 69.9%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>2300000</v>
+        <v>22550</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2102000</v>
+        <v>22400</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>2414000</v>
+        <v>23250</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>1691500</v>
+        <v>23587.5</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>1739550</v>
+        <v>23387.5</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>1353200</v>
+        <v>18870</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>1391640</v>
+        <v>18710</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>1354000</v>
+        <v>18550</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>69.86706056129985</v>
+        <v>21.5633423180593</v>
       </c>
       <c r="O57" s="7" t="inlineStr"/>
       <c r="P57" s="7" t="inlineStr"/>
       <c r="Q57" s="5" t="n">
-        <v>1219000</v>
+        <v>16700</v>
       </c>
       <c r="R57" s="6" t="n">
-        <v>88.67924528301887</v>
+        <v>35.02994011976048</v>
       </c>
       <c r="S57" s="7" t="inlineStr"/>
       <c r="T57" s="7" t="inlineStr"/>
       <c r="U57" s="5" t="n">
-        <v>1098000</v>
+        <v>15040</v>
       </c>
       <c r="V57" s="6" t="n">
-        <v>109.471766848816</v>
+        <v>49.93351063829788</v>
       </c>
       <c r="W57" s="7" t="inlineStr"/>
       <c r="X57" s="7" t="inlineStr"/>
@@ -5126,12 +5130,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -5146,51 +5150,51 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.8%</t>
+          <t>1차 매수선까지 38.1%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>519000</v>
+        <v>483500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>510000</v>
+        <v>474000</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>534000</v>
+        <v>494500</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>480675</v>
+        <v>440500</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>481175</v>
+        <v>444150</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>384540</v>
+        <v>352400</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>384940</v>
+        <v>355320</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>379500</v>
+        <v>350000</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>36.75889328063241</v>
+        <v>38.14285714285715</v>
       </c>
       <c r="O58" s="7" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr"/>
       <c r="Q58" s="5" t="n">
-        <v>342000</v>
+        <v>315500</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>51.75438596491229</v>
+        <v>53.24881141045958</v>
       </c>
       <c r="S58" s="7" t="inlineStr"/>
       <c r="T58" s="7" t="inlineStr"/>
       <c r="U58" s="5" t="n">
-        <v>308000</v>
+        <v>284000</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>68.5064935064935</v>
+        <v>70.24647887323944</v>
       </c>
       <c r="W58" s="7" t="inlineStr"/>
       <c r="X58" s="7" t="inlineStr"/>
@@ -5206,12 +5210,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -5226,51 +5230,51 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.8%</t>
+          <t>1차 매수선까지 38.3%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>41100</v>
+        <v>242500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>40750</v>
+        <v>232500</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>42000</v>
+        <v>257000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>41845</v>
+        <v>220515</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>41892.5</v>
+        <v>222415</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>33476</v>
+        <v>176412</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>33514</v>
+        <v>177932</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>33200</v>
+        <v>175300</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>23.79518072289157</v>
+        <v>38.3342840844267</v>
       </c>
       <c r="O59" s="7" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr"/>
       <c r="Q59" s="5" t="n">
-        <v>29900</v>
+        <v>157800</v>
       </c>
       <c r="R59" s="6" t="n">
-        <v>37.45819397993311</v>
+        <v>53.67553865652725</v>
       </c>
       <c r="S59" s="7" t="inlineStr"/>
       <c r="T59" s="7" t="inlineStr"/>
       <c r="U59" s="5" t="n">
-        <v>26950</v>
+        <v>142100</v>
       </c>
       <c r="V59" s="6" t="n">
-        <v>52.50463821892394</v>
+        <v>70.65446868402533</v>
       </c>
       <c r="W59" s="7" t="inlineStr"/>
       <c r="X59" s="7" t="inlineStr"/>
@@ -5286,12 +5290,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -5306,51 +5310,51 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.6%</t>
+          <t>1차 매수선까지 68.1%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>15900</v>
+        <v>2346000</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>15540</v>
+        <v>2281000</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>16070</v>
+        <v>2419000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>17086.5</v>
+        <v>1741850</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>17014.5</v>
+        <v>1792050</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>13669.2</v>
+        <v>1393480</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>13611.6</v>
+        <v>1433640</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>13520</v>
+        <v>1396000</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>17.60355029585799</v>
+        <v>68.05157593123209</v>
       </c>
       <c r="O60" s="7" t="inlineStr"/>
       <c r="P60" s="7" t="inlineStr"/>
       <c r="Q60" s="5" t="n">
-        <v>12170</v>
+        <v>1257000</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>30.64913722267872</v>
+        <v>86.63484486873509</v>
       </c>
       <c r="S60" s="7" t="inlineStr"/>
       <c r="T60" s="7" t="inlineStr"/>
       <c r="U60" s="5" t="n">
-        <v>10960</v>
+        <v>1132000</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>45.07299270072993</v>
+        <v>107.243816254417</v>
       </c>
       <c r="W60" s="7" t="inlineStr"/>
       <c r="X60" s="7" t="inlineStr"/>
@@ -5366,12 +5370,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5386,51 +5390,51 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.9%</t>
+          <t>1차 매수선까지 39.6%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>100900</v>
+        <v>531000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>92100</v>
+        <v>515000</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>101400</v>
+        <v>534000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>91195</v>
+        <v>481775</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>91565</v>
+        <v>482675</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>72956</v>
+        <v>385420</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>73252</v>
+        <v>386140</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>72100</v>
+        <v>380500</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>39.94452149791955</v>
+        <v>39.55321944809461</v>
       </c>
       <c r="O61" s="7" t="inlineStr"/>
       <c r="P61" s="7" t="inlineStr"/>
       <c r="Q61" s="5" t="n">
-        <v>64900</v>
+        <v>342500</v>
       </c>
       <c r="R61" s="6" t="n">
-        <v>55.46995377503852</v>
+        <v>55.03649635036496</v>
       </c>
       <c r="S61" s="7" t="inlineStr"/>
       <c r="T61" s="7" t="inlineStr"/>
       <c r="U61" s="5" t="n">
-        <v>58500</v>
+        <v>308500</v>
       </c>
       <c r="V61" s="6" t="n">
-        <v>72.47863247863248</v>
+        <v>72.12317666126418</v>
       </c>
       <c r="W61" s="7" t="inlineStr"/>
       <c r="X61" s="7" t="inlineStr"/>
@@ -5446,12 +5450,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5466,51 +5470,51 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.5%</t>
+          <t>1차 매수선까지 20.6%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>14680</v>
+        <v>40050</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>13830</v>
+        <v>40000</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>14950</v>
+        <v>42100</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>14425</v>
+        <v>41840</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>14429.5</v>
+        <v>41812.5</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>11540</v>
+        <v>33472</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>11543.6</v>
+        <v>33450</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>11420</v>
+        <v>33200</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>28.54640980735552</v>
+        <v>20.63253012048193</v>
       </c>
       <c r="O62" s="7" t="inlineStr"/>
       <c r="P62" s="7" t="inlineStr"/>
       <c r="Q62" s="5" t="n">
-        <v>10280</v>
+        <v>29900</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>42.80155642023346</v>
+        <v>33.94648829431438</v>
       </c>
       <c r="S62" s="7" t="inlineStr"/>
       <c r="T62" s="7" t="inlineStr"/>
       <c r="U62" s="5" t="n">
-        <v>9260</v>
+        <v>26950</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>58.53131749460043</v>
+        <v>48.60853432282003</v>
       </c>
       <c r="W62" s="7" t="inlineStr"/>
       <c r="X62" s="7" t="inlineStr"/>
@@ -5526,12 +5530,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5546,51 +5550,51 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.1%</t>
+          <t>1차 매수선까지 15.8%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>74100</v>
+        <v>15560</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>73900</v>
+        <v>15560</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>76400</v>
+        <v>16060</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>77930</v>
+        <v>16997.5</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>77705</v>
+        <v>16897</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>62344</v>
+        <v>13598</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>62164</v>
+        <v>13517.6</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>61700</v>
+        <v>13440</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>20.09724473257699</v>
+        <v>15.77380952380952</v>
       </c>
       <c r="O63" s="7" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr"/>
       <c r="Q63" s="5" t="n">
-        <v>55600</v>
+        <v>12100</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>33.27338129496403</v>
+        <v>28.59504132231405</v>
       </c>
       <c r="S63" s="7" t="inlineStr"/>
       <c r="T63" s="7" t="inlineStr"/>
       <c r="U63" s="5" t="n">
-        <v>50100</v>
+        <v>10900</v>
       </c>
       <c r="V63" s="6" t="n">
-        <v>47.90419161676647</v>
+        <v>42.75229357798165</v>
       </c>
       <c r="W63" s="7" t="inlineStr"/>
       <c r="X63" s="7" t="inlineStr"/>
@@ -5606,12 +5610,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5626,51 +5630,51 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 42.1%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>257000</v>
+        <v>103200</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>250500</v>
+        <v>97800</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>262500</v>
+        <v>103400</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>246825</v>
+        <v>91680</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>247225</v>
+        <v>92240</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>197460</v>
+        <v>73344</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>197780</v>
+        <v>73792</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>195400</v>
+        <v>72600</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>31.52507676560901</v>
+        <v>42.14876033057851</v>
       </c>
       <c r="O64" s="7" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr"/>
       <c r="Q64" s="5" t="n">
-        <v>175900</v>
+        <v>65400</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>46.10574189880614</v>
+        <v>57.79816513761467</v>
       </c>
       <c r="S64" s="7" t="inlineStr"/>
       <c r="T64" s="7" t="inlineStr"/>
       <c r="U64" s="5" t="n">
-        <v>158400</v>
+        <v>58900</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>62.24747474747475</v>
+        <v>75.21222410865875</v>
       </c>
       <c r="W64" s="7" t="inlineStr"/>
       <c r="X64" s="7" t="inlineStr"/>
@@ -5686,12 +5690,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5706,51 +5710,51 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.5%</t>
+          <t>1차 매수선까지 27.3%</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>115900</v>
+        <v>14550</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>113900</v>
+        <v>14380</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>118900</v>
+        <v>15030</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>106930</v>
+        <v>14423</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>107640</v>
+        <v>14432</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>85544</v>
+        <v>11538.4</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>86112</v>
+        <v>11545.6</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>84900</v>
+        <v>11430</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>36.51354534746761</v>
+        <v>27.29658792650919</v>
       </c>
       <c r="O65" s="7" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr"/>
       <c r="Q65" s="5" t="n">
-        <v>76500</v>
+        <v>10290</v>
       </c>
       <c r="R65" s="6" t="n">
-        <v>51.5032679738562</v>
+        <v>41.39941690962099</v>
       </c>
       <c r="S65" s="7" t="inlineStr"/>
       <c r="T65" s="7" t="inlineStr"/>
       <c r="U65" s="5" t="n">
-        <v>68900</v>
+        <v>9270</v>
       </c>
       <c r="V65" s="6" t="n">
-        <v>68.21480406386067</v>
+        <v>56.957928802589</v>
       </c>
       <c r="W65" s="7" t="inlineStr"/>
       <c r="X65" s="7" t="inlineStr"/>
@@ -5766,12 +5770,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5786,51 +5790,51 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 10.1%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>989000</v>
+        <v>67300</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>976000</v>
+        <v>62200</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>1007000</v>
+        <v>70600</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>1009350</v>
+        <v>77365</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>1005950</v>
+        <v>76685</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>807480</v>
+        <v>61892</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>804760</v>
+        <v>61348</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>798000</v>
+        <v>61100</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>23.93483709273183</v>
+        <v>10.14729950900164</v>
       </c>
       <c r="O66" s="7" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr"/>
       <c r="Q66" s="5" t="n">
-        <v>719000</v>
+        <v>55000</v>
       </c>
       <c r="R66" s="6" t="n">
-        <v>37.55215577190543</v>
+        <v>22.36363636363636</v>
       </c>
       <c r="S66" s="7" t="inlineStr"/>
       <c r="T66" s="7" t="inlineStr"/>
       <c r="U66" s="5" t="n">
-        <v>648000</v>
+        <v>49550</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>52.62345679012346</v>
+        <v>35.82240161453078</v>
       </c>
       <c r="W66" s="7" t="inlineStr"/>
       <c r="X66" s="7" t="inlineStr"/>
@@ -5846,12 +5850,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5866,51 +5870,51 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.4%</t>
+          <t>1차 매수선까지 39.6%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>30600</v>
+        <v>274000</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>29800</v>
+        <v>256000</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>31250</v>
+        <v>274500</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>29765</v>
+        <v>248075</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>29870</v>
+        <v>249250</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>23812</v>
+        <v>198460</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>23896</v>
+        <v>199400</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>23650</v>
+        <v>196300</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>29.38689217758985</v>
+        <v>39.58227203260316</v>
       </c>
       <c r="O67" s="7" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr"/>
       <c r="Q67" s="5" t="n">
-        <v>21300</v>
+        <v>176700</v>
       </c>
       <c r="R67" s="6" t="n">
-        <v>43.66197183098591</v>
+        <v>55.06508205998868</v>
       </c>
       <c r="S67" s="7" t="inlineStr"/>
       <c r="T67" s="7" t="inlineStr"/>
       <c r="U67" s="5" t="n">
-        <v>19180</v>
+        <v>159100</v>
       </c>
       <c r="V67" s="6" t="n">
-        <v>59.54118873826904</v>
+        <v>72.21873035826523</v>
       </c>
       <c r="W67" s="7" t="inlineStr"/>
       <c r="X67" s="7" t="inlineStr"/>
@@ -5926,12 +5930,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5946,51 +5950,51 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.4%</t>
+          <t>1차 매수선까지 39.3%</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>242000</v>
+        <v>119400</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>223500</v>
+        <v>113100</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>248000</v>
+        <v>119600</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>212260</v>
+        <v>107815</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>214465</v>
+        <v>108715</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>169808</v>
+        <v>86252</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>171572</v>
+        <v>86972</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>168700</v>
+        <v>85700</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>43.44991108476586</v>
+        <v>39.32322053675612</v>
       </c>
       <c r="O68" s="7" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr"/>
       <c r="Q68" s="5" t="n">
-        <v>151900</v>
+        <v>77200</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>59.31533903884134</v>
+        <v>54.66321243523316</v>
       </c>
       <c r="S68" s="7" t="inlineStr"/>
       <c r="T68" s="7" t="inlineStr"/>
       <c r="U68" s="5" t="n">
-        <v>136800</v>
+        <v>69500</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>76.90058479532163</v>
+        <v>71.79856115107913</v>
       </c>
       <c r="W68" s="7" t="inlineStr"/>
       <c r="X68" s="7" t="inlineStr"/>
@@ -6006,12 +6010,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -6026,51 +6030,51 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.5%</t>
+          <t>1차 매수선까지 40.7%</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>49950</v>
+        <v>33550</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>48850</v>
+        <v>30850</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>51500</v>
+        <v>34050</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>52782.5</v>
+        <v>30017.5</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>52630</v>
+        <v>30275</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>42226</v>
+        <v>24014</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>42104</v>
+        <v>24220</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>41800</v>
+        <v>23850</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>19.49760765550239</v>
+        <v>40.67085953878406</v>
       </c>
       <c r="O69" s="7" t="inlineStr"/>
       <c r="P69" s="7" t="inlineStr"/>
       <c r="Q69" s="5" t="n">
-        <v>37650</v>
+        <v>21500</v>
       </c>
       <c r="R69" s="6" t="n">
-        <v>32.66932270916335</v>
+        <v>56.04651162790698</v>
       </c>
       <c r="S69" s="7" t="inlineStr"/>
       <c r="T69" s="7" t="inlineStr"/>
       <c r="U69" s="5" t="n">
-        <v>33900</v>
+        <v>19360</v>
       </c>
       <c r="V69" s="6" t="n">
-        <v>47.34513274336283</v>
+        <v>73.29545454545455</v>
       </c>
       <c r="W69" s="7" t="inlineStr"/>
       <c r="X69" s="7" t="inlineStr"/>
@@ -6086,12 +6090,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -6106,51 +6110,51 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.9%</t>
+          <t>1차 매수선까지 42.6%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>15250</v>
+        <v>243500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>15070</v>
+        <v>232500</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>16400</v>
+        <v>247000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>15643.5</v>
+        <v>214540</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>15649</v>
+        <v>217020</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>12514.8</v>
+        <v>171632</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>12519.2</v>
+        <v>173616</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>12410</v>
+        <v>170800</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>22.88477034649476</v>
+        <v>42.56440281030444</v>
       </c>
       <c r="O70" s="7" t="inlineStr"/>
       <c r="P70" s="7" t="inlineStr"/>
       <c r="Q70" s="5" t="n">
-        <v>11170</v>
+        <v>153800</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>36.52641002685765</v>
+        <v>58.32249674902471</v>
       </c>
       <c r="S70" s="7" t="inlineStr"/>
       <c r="T70" s="7" t="inlineStr"/>
       <c r="U70" s="5" t="n">
-        <v>10060</v>
+        <v>138500</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>51.59045725646123</v>
+        <v>75.81227436823104</v>
       </c>
       <c r="W70" s="7" t="inlineStr"/>
       <c r="X70" s="7" t="inlineStr"/>
@@ -6166,12 +6170,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -6186,51 +6190,51 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 19.7%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>28150</v>
+        <v>49850</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>27700</v>
+        <v>48550</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>28450</v>
+        <v>50400</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>29257.5</v>
+        <v>52625</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>29170</v>
+        <v>52467.5</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>23406</v>
+        <v>42100</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>23336</v>
+        <v>41974</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>23150</v>
+        <v>41650</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>21.59827213822894</v>
+        <v>19.68787515006002</v>
       </c>
       <c r="O71" s="7" t="inlineStr"/>
       <c r="P71" s="7" t="inlineStr"/>
       <c r="Q71" s="5" t="n">
-        <v>20850</v>
+        <v>37500</v>
       </c>
       <c r="R71" s="6" t="n">
-        <v>35.01199040767386</v>
+        <v>32.93333333333333</v>
       </c>
       <c r="S71" s="7" t="inlineStr"/>
       <c r="T71" s="7" t="inlineStr"/>
       <c r="U71" s="5" t="n">
-        <v>18770</v>
+        <v>33800</v>
       </c>
       <c r="V71" s="6" t="n">
-        <v>49.97336174746936</v>
+        <v>47.48520710059172</v>
       </c>
       <c r="W71" s="7" t="inlineStr"/>
       <c r="X71" s="7" t="inlineStr"/>
@@ -6246,12 +6250,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -6266,51 +6270,51 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.3%</t>
+          <t>1차 매수선까지 23.0%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>2415</v>
+        <v>15280</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>2410</v>
+        <v>15060</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>2535</v>
+        <v>15370</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>2433</v>
+        <v>15650.5</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2432.5</v>
+        <v>15661.5</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>1946.4</v>
+        <v>12520.4</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>1946</v>
+        <v>12529.2</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>1927</v>
+        <v>12420</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>25.32433834976648</v>
+        <v>23.02737520128824</v>
       </c>
       <c r="O72" s="7" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr"/>
       <c r="Q72" s="5" t="n">
-        <v>1735</v>
+        <v>11180</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>39.19308357348703</v>
+        <v>36.67262969588551</v>
       </c>
       <c r="S72" s="7" t="inlineStr"/>
       <c r="T72" s="7" t="inlineStr"/>
       <c r="U72" s="5" t="n">
-        <v>1562</v>
+        <v>10070</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>54.60947503201024</v>
+        <v>51.73783515392254</v>
       </c>
       <c r="W72" s="7" t="inlineStr"/>
       <c r="X72" s="7" t="inlineStr"/>
@@ -6326,12 +6330,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -6346,51 +6350,51 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.1%</t>
+          <t>1차 매수선까지 22.1%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>7110</v>
+        <v>28200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>7030</v>
+        <v>27800</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>7480</v>
+        <v>28950</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>7043</v>
+        <v>29172.5</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>7009</v>
+        <v>29100</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>5634.400000000001</v>
+        <v>23338</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>5607.200000000001</v>
+        <v>23280</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>5550</v>
+        <v>23100</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>28.10810810810811</v>
+        <v>22.07792207792208</v>
       </c>
       <c r="O73" s="7" t="inlineStr"/>
       <c r="P73" s="7" t="inlineStr"/>
       <c r="Q73" s="5" t="n">
-        <v>5000</v>
+        <v>20800</v>
       </c>
       <c r="R73" s="6" t="n">
-        <v>42.2</v>
+        <v>35.57692307692308</v>
       </c>
       <c r="S73" s="7" t="inlineStr"/>
       <c r="T73" s="7" t="inlineStr"/>
       <c r="U73" s="5" t="n">
-        <v>4505</v>
+        <v>18730</v>
       </c>
       <c r="V73" s="6" t="n">
-        <v>57.82463928967814</v>
+        <v>50.56059797116925</v>
       </c>
       <c r="W73" s="7" t="inlineStr"/>
       <c r="X73" s="7" t="inlineStr"/>
@@ -6406,12 +6410,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -6426,51 +6430,51 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.8%</t>
+          <t>1차 매수선까지 21.0%</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>146800</v>
+        <v>2330</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>140500</v>
+        <v>2320</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>146800</v>
+        <v>2425</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>141755</v>
+        <v>2428.25</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>141905</v>
+        <v>2426.05</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>113404</v>
+        <v>1942.6</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>113524</v>
+        <v>1940.84</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>112200</v>
+        <v>1925</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>30.83778966131907</v>
+        <v>21.03896103896104</v>
       </c>
       <c r="O74" s="7" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr"/>
       <c r="Q74" s="5" t="n">
-        <v>101000</v>
+        <v>1733</v>
       </c>
       <c r="R74" s="6" t="n">
-        <v>45.34653465346535</v>
+        <v>34.44893248701673</v>
       </c>
       <c r="S74" s="7" t="inlineStr"/>
       <c r="T74" s="7" t="inlineStr"/>
       <c r="U74" s="5" t="n">
-        <v>91000</v>
+        <v>1560</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>61.31868131868132</v>
+        <v>49.35897435897436</v>
       </c>
       <c r="W74" s="7" t="inlineStr"/>
       <c r="X74" s="7" t="inlineStr"/>
@@ -6486,12 +6490,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6506,51 +6510,51 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.1%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>35300</v>
+        <v>6840</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>35000</v>
+        <v>6760</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>36000</v>
+        <v>7500</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>38007.5</v>
+        <v>6995.5</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>37600</v>
+        <v>6962.5</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>30406</v>
+        <v>5596.400000000001</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>30080</v>
+        <v>5570</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>29900</v>
+        <v>5520</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>18.06020066889632</v>
+        <v>23.91304347826087</v>
       </c>
       <c r="O75" s="7" t="inlineStr"/>
       <c r="P75" s="7" t="inlineStr"/>
       <c r="Q75" s="5" t="n">
-        <v>26950</v>
+        <v>4970</v>
       </c>
       <c r="R75" s="6" t="n">
-        <v>30.98330241187384</v>
+        <v>37.62575452716298</v>
       </c>
       <c r="S75" s="7" t="inlineStr"/>
       <c r="T75" s="7" t="inlineStr"/>
       <c r="U75" s="5" t="n">
-        <v>24300</v>
+        <v>4475</v>
       </c>
       <c r="V75" s="6" t="n">
-        <v>45.26748971193415</v>
+        <v>52.84916201117319</v>
       </c>
       <c r="W75" s="7" t="inlineStr"/>
       <c r="X75" s="7" t="inlineStr"/>
@@ -6566,12 +6570,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6586,51 +6590,51 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.7%</t>
+          <t>1차 매수선까지 32.3%</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>8730</v>
+        <v>149000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>8570</v>
+        <v>143600</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>8910</v>
+        <v>149000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>9764</v>
+        <v>142015</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>9646</v>
+        <v>142475</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>7811.200000000001</v>
+        <v>113612</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>7716.8</v>
+        <v>113980</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>7680</v>
+        <v>112600</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>13.671875</v>
+        <v>32.32682060390763</v>
       </c>
       <c r="O76" s="7" t="inlineStr"/>
       <c r="P76" s="7" t="inlineStr"/>
       <c r="Q76" s="5" t="n">
-        <v>6920</v>
+        <v>101400</v>
       </c>
       <c r="R76" s="6" t="n">
-        <v>26.15606936416185</v>
+        <v>46.94280078895464</v>
       </c>
       <c r="S76" s="7" t="inlineStr"/>
       <c r="T76" s="7" t="inlineStr"/>
       <c r="U76" s="5" t="n">
-        <v>6230</v>
+        <v>91300</v>
       </c>
       <c r="V76" s="6" t="n">
-        <v>40.12841091492777</v>
+        <v>63.19824753559693</v>
       </c>
       <c r="W76" s="7" t="inlineStr"/>
       <c r="X76" s="7" t="inlineStr"/>
@@ -6646,12 +6650,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -6666,51 +6670,51 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.0%</t>
+          <t>1차 매수선까지 18.2%</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>260000</v>
+        <v>35050</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>251500</v>
+        <v>34750</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>283500</v>
+        <v>35950</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>251340</v>
+        <v>37587.5</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>254450</v>
+        <v>37320</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>201072</v>
+        <v>30070</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>203560</v>
+        <v>29856</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>201500</v>
+        <v>29650</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>29.03225806451613</v>
+        <v>18.21247892074199</v>
       </c>
       <c r="O77" s="7" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr"/>
       <c r="Q77" s="5" t="n">
-        <v>181400</v>
+        <v>26700</v>
       </c>
       <c r="R77" s="6" t="n">
-        <v>43.32965821389195</v>
+        <v>31.27340823970037</v>
       </c>
       <c r="S77" s="7" t="inlineStr"/>
       <c r="T77" s="7" t="inlineStr"/>
       <c r="U77" s="5" t="n">
-        <v>163300</v>
+        <v>24050</v>
       </c>
       <c r="V77" s="6" t="n">
-        <v>59.21616656460502</v>
+        <v>45.73804573804574</v>
       </c>
       <c r="W77" s="7" t="inlineStr"/>
       <c r="X77" s="7" t="inlineStr"/>
@@ -6726,12 +6730,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -6746,51 +6750,51 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.6%</t>
+          <t>1차 매수선까지 19.1%</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>311500</v>
+        <v>9040</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>310000</v>
+        <v>8740</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>318500</v>
+        <v>9360</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>295400</v>
+        <v>9661.5</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>297025</v>
+        <v>9552.5</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>236320</v>
+        <v>7729.200000000001</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>237620</v>
+        <v>7642</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>235000</v>
+        <v>7590</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>32.5531914893617</v>
+        <v>19.10408432147563</v>
       </c>
       <c r="O78" s="7" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr"/>
       <c r="Q78" s="5" t="n">
-        <v>212000</v>
+        <v>6840</v>
       </c>
       <c r="R78" s="6" t="n">
-        <v>46.93396226415094</v>
+        <v>32.16374269005848</v>
       </c>
       <c r="S78" s="7" t="inlineStr"/>
       <c r="T78" s="7" t="inlineStr"/>
       <c r="U78" s="5" t="n">
-        <v>190900</v>
+        <v>6160</v>
       </c>
       <c r="V78" s="6" t="n">
-        <v>63.17443687794657</v>
+        <v>46.75324675324675</v>
       </c>
       <c r="W78" s="7" t="inlineStr"/>
       <c r="X78" s="7" t="inlineStr"/>
@@ -6806,12 +6810,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6826,51 +6830,51 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.1%</t>
+          <t>1차 매수선까지 37.8%</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>100000</v>
+        <v>282500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>98900</v>
+        <v>250000</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>104400</v>
+        <v>285500</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>99740</v>
+        <v>255575</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>100085</v>
+        <v>259650</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>79792</v>
+        <v>204460</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>80068</v>
+        <v>207720</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>79300</v>
+        <v>205000</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>26.10340479192938</v>
+        <v>37.80487804878049</v>
       </c>
       <c r="O79" s="7" t="inlineStr"/>
       <c r="P79" s="7" t="inlineStr"/>
       <c r="Q79" s="5" t="n">
-        <v>71400</v>
+        <v>184600</v>
       </c>
       <c r="R79" s="6" t="n">
-        <v>40.05602240896359</v>
+        <v>53.03358613217768</v>
       </c>
       <c r="S79" s="7" t="inlineStr"/>
       <c r="T79" s="7" t="inlineStr"/>
       <c r="U79" s="5" t="n">
-        <v>64300</v>
+        <v>166200</v>
       </c>
       <c r="V79" s="6" t="n">
-        <v>55.52099533437014</v>
+        <v>69.97593261131168</v>
       </c>
       <c r="W79" s="7" t="inlineStr"/>
       <c r="X79" s="7" t="inlineStr"/>
@@ -6886,12 +6890,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -6906,51 +6910,51 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.4%</t>
+          <t>1차 매수선까지 33.4%</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>96400</v>
+        <v>315500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>94500</v>
+        <v>306000</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>97900</v>
+        <v>315500</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>90180</v>
+        <v>297225</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>90825</v>
+        <v>299175</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>72144</v>
+        <v>237780</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>72660</v>
+        <v>239340</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>71700</v>
+        <v>236500</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>34.44909344490934</v>
+        <v>33.40380549682875</v>
       </c>
       <c r="O80" s="7" t="inlineStr"/>
       <c r="P80" s="7" t="inlineStr"/>
       <c r="Q80" s="5" t="n">
-        <v>64600</v>
+        <v>213000</v>
       </c>
       <c r="R80" s="6" t="n">
-        <v>49.22600619195047</v>
+        <v>48.12206572769953</v>
       </c>
       <c r="S80" s="7" t="inlineStr"/>
       <c r="T80" s="7" t="inlineStr"/>
       <c r="U80" s="5" t="n">
-        <v>58200</v>
+        <v>191800</v>
       </c>
       <c r="V80" s="6" t="n">
-        <v>65.63573883161511</v>
+        <v>64.49426485922837</v>
       </c>
       <c r="W80" s="7" t="inlineStr"/>
       <c r="X80" s="7" t="inlineStr"/>
@@ -6966,12 +6970,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6986,51 +6990,51 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.7%</t>
+          <t>1차 매수선까지 25.4%</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>249000</v>
+        <v>99800</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>243000</v>
+        <v>97500</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>250000</v>
+        <v>100800</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>229025</v>
+        <v>100075</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>231025</v>
+        <v>100420</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>183220</v>
+        <v>80060</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>184820</v>
+        <v>80336</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>182200</v>
+        <v>79600</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>36.66300768386389</v>
+        <v>25.37688442211055</v>
       </c>
       <c r="O81" s="7" t="inlineStr"/>
       <c r="P81" s="7" t="inlineStr"/>
       <c r="Q81" s="5" t="n">
-        <v>164000</v>
+        <v>71700</v>
       </c>
       <c r="R81" s="6" t="n">
-        <v>51.82926829268293</v>
+        <v>39.1910739191074</v>
       </c>
       <c r="S81" s="7" t="inlineStr"/>
       <c r="T81" s="7" t="inlineStr"/>
       <c r="U81" s="5" t="n">
-        <v>147700</v>
+        <v>64600</v>
       </c>
       <c r="V81" s="6" t="n">
-        <v>68.58496953283684</v>
+        <v>54.4891640866873</v>
       </c>
       <c r="W81" s="7" t="inlineStr"/>
       <c r="X81" s="7" t="inlineStr"/>
@@ -7046,12 +7050,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -7066,51 +7070,51 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.2%</t>
+          <t>1차 매수선까지 35.7%</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>129600</v>
+        <v>98100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>128500</v>
+        <v>95600</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>137200</v>
+        <v>99700</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>117585</v>
+        <v>90910</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>118980</v>
+        <v>91575</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>94068</v>
+        <v>72728</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>95184</v>
+        <v>73260</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>93800</v>
+        <v>72300</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>38.16631130063966</v>
+        <v>35.68464730290457</v>
       </c>
       <c r="O82" s="7" t="inlineStr"/>
       <c r="P82" s="7" t="inlineStr"/>
       <c r="Q82" s="5" t="n">
-        <v>84500</v>
+        <v>65100</v>
       </c>
       <c r="R82" s="6" t="n">
-        <v>53.37278106508876</v>
+        <v>50.69124423963134</v>
       </c>
       <c r="S82" s="7" t="inlineStr"/>
       <c r="T82" s="7" t="inlineStr"/>
       <c r="U82" s="5" t="n">
-        <v>76100</v>
+        <v>58600</v>
       </c>
       <c r="V82" s="6" t="n">
-        <v>70.30223390275953</v>
+        <v>67.4061433447099</v>
       </c>
       <c r="W82" s="7" t="inlineStr"/>
       <c r="X82" s="7" t="inlineStr"/>
@@ -7122,6 +7126,268 @@
       <c r="AD82" s="7" t="inlineStr"/>
       <c r="AE82" s="7" t="inlineStr"/>
       <c r="AF82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>034730</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 37.8%</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>253500</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>244500</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>257000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>231250</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>233400</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>185000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>186720</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>184000</v>
+      </c>
+      <c r="N83" s="6" t="n">
+        <v>37.77173913043478</v>
+      </c>
+      <c r="O83" s="7" t="inlineStr"/>
+      <c r="P83" s="7" t="inlineStr"/>
+      <c r="Q83" s="5" t="n">
+        <v>165700</v>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v>52.98732649366325</v>
+      </c>
+      <c r="S83" s="7" t="inlineStr"/>
+      <c r="T83" s="7" t="inlineStr"/>
+      <c r="U83" s="5" t="n">
+        <v>149200</v>
+      </c>
+      <c r="V83" s="6" t="n">
+        <v>69.90616621983914</v>
+      </c>
+      <c r="W83" s="7" t="inlineStr"/>
+      <c r="X83" s="7" t="inlineStr"/>
+      <c r="Y83" s="7" t="inlineStr"/>
+      <c r="Z83" s="7" t="inlineStr"/>
+      <c r="AA83" s="7" t="inlineStr"/>
+      <c r="AB83" s="7" t="inlineStr"/>
+      <c r="AC83" s="7" t="inlineStr"/>
+      <c r="AD83" s="7" t="inlineStr"/>
+      <c r="AE83" s="7" t="inlineStr"/>
+      <c r="AF83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 34.7%</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>127800</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>124800</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>132300</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>118890</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>120265</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>95112</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>96212</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>94900</v>
+      </c>
+      <c r="N84" s="6" t="n">
+        <v>34.66807165437302</v>
+      </c>
+      <c r="O84" s="7" t="inlineStr"/>
+      <c r="P84" s="7" t="inlineStr"/>
+      <c r="Q84" s="5" t="n">
+        <v>85500</v>
+      </c>
+      <c r="R84" s="6" t="n">
+        <v>49.47368421052632</v>
+      </c>
+      <c r="S84" s="7" t="inlineStr"/>
+      <c r="T84" s="7" t="inlineStr"/>
+      <c r="U84" s="5" t="n">
+        <v>77000</v>
+      </c>
+      <c r="V84" s="6" t="n">
+        <v>65.97402597402598</v>
+      </c>
+      <c r="W84" s="7" t="inlineStr"/>
+      <c r="X84" s="7" t="inlineStr"/>
+      <c r="Y84" s="7" t="inlineStr"/>
+      <c r="Z84" s="7" t="inlineStr"/>
+      <c r="AA84" s="7" t="inlineStr"/>
+      <c r="AB84" s="7" t="inlineStr"/>
+      <c r="AC84" s="7" t="inlineStr"/>
+      <c r="AD84" s="7" t="inlineStr"/>
+      <c r="AE84" s="7" t="inlineStr"/>
+      <c r="AF84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>BOUGHT_1</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>READY_SELL1</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>+3% 매도선까지 1.9%</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>7400</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>7290</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>7780</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>9230</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>9148.5</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>7384</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>7318.8</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>7320</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>1.092896174863388</v>
+      </c>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="P85" s="5" t="n">
+        <v>7320</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <v>6590</v>
+      </c>
+      <c r="R85" s="6" t="n">
+        <v>12.29135053110774</v>
+      </c>
+      <c r="S85" s="7" t="inlineStr"/>
+      <c r="T85" s="7" t="inlineStr"/>
+      <c r="U85" s="5" t="n">
+        <v>5940</v>
+      </c>
+      <c r="V85" s="6" t="n">
+        <v>24.57912457912458</v>
+      </c>
+      <c r="W85" s="7" t="inlineStr"/>
+      <c r="X85" s="7" t="inlineStr"/>
+      <c r="Y85" s="5" t="n">
+        <v>7320</v>
+      </c>
+      <c r="Z85" s="5" t="n">
+        <v>7539.6</v>
+      </c>
+      <c r="AA85" s="6" t="n">
+        <v>-1.851557111783123</v>
+      </c>
+      <c r="AB85" s="5" t="n">
+        <v>7686</v>
+      </c>
+      <c r="AC85" s="6" t="n">
+        <v>-3.721051262034868</v>
+      </c>
+      <c r="AD85" s="5" t="n">
+        <v>7832.400000000001</v>
+      </c>
+      <c r="AE85" s="6" t="n">
+        <v>-5.520657780501513</v>
+      </c>
+      <c r="AF85" s="5" t="n">
+        <v>7780</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,7 +58,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -80,9 +79,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF85"/>
+  <dimension ref="A1:AF80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -670,51 +666,51 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.4%</t>
+          <t>1차 매수선까지 40.8%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>111300</v>
+        <v>107700</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>105500</v>
+        <v>101500</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>111500</v>
+        <v>109200</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>97250</v>
+        <v>95910</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>98620</v>
+        <v>97070</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>77800</v>
+        <v>76728</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>78896</v>
+        <v>77656</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>77600</v>
+        <v>76500</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>43.4278350515464</v>
+        <v>40.78431372549019</v>
       </c>
       <c r="O2" s="7" t="inlineStr"/>
       <c r="P2" s="7" t="inlineStr"/>
       <c r="Q2" s="5" t="n">
-        <v>69900</v>
+        <v>68900</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>59.2274678111588</v>
+        <v>56.31349782293179</v>
       </c>
       <c r="S2" s="7" t="inlineStr"/>
       <c r="T2" s="7" t="inlineStr"/>
       <c r="U2" s="5" t="n">
-        <v>63000</v>
+        <v>62100</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>76.66666666666667</v>
+        <v>73.42995169082126</v>
       </c>
       <c r="W2" s="7" t="inlineStr"/>
       <c r="X2" s="7" t="inlineStr"/>
@@ -750,51 +746,51 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.2%</t>
+          <t>1차 매수선까지 50.7%</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>629000</v>
+        <v>560000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>553000</v>
+        <v>552000</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>630000</v>
+        <v>568000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>476925</v>
+        <v>463025</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>490975</v>
+        <v>473475</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>381540</v>
+        <v>370420</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>392780</v>
+        <v>378780</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>383000</v>
+        <v>371500</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>64.22976501305483</v>
+        <v>50.74024226110363</v>
       </c>
       <c r="O3" s="7" t="inlineStr"/>
       <c r="P3" s="7" t="inlineStr"/>
       <c r="Q3" s="5" t="n">
-        <v>345000</v>
+        <v>334500</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>82.31884057971014</v>
+        <v>67.41405082212258</v>
       </c>
       <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="7" t="inlineStr"/>
       <c r="U3" s="5" t="n">
-        <v>311000</v>
+        <v>301500</v>
       </c>
       <c r="V3" s="6" t="n">
-        <v>102.2508038585209</v>
+        <v>85.7379767827529</v>
       </c>
       <c r="W3" s="7" t="inlineStr"/>
       <c r="X3" s="7" t="inlineStr"/>
@@ -830,51 +826,51 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 41.4%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>89800</v>
+        <v>88800</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>88700</v>
+        <v>88200</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>90300</v>
+        <v>91500</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>79780</v>
+        <v>78450</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>81160</v>
+        <v>79730</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>63824</v>
+        <v>62760</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>64928</v>
+        <v>63784</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>63900</v>
+        <v>62800</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>40.5320813771518</v>
+        <v>41.40127388535032</v>
       </c>
       <c r="O4" s="7" t="inlineStr"/>
       <c r="P4" s="7" t="inlineStr"/>
       <c r="Q4" s="5" t="n">
-        <v>57600</v>
+        <v>56600</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>55.90277777777778</v>
+        <v>56.8904593639576</v>
       </c>
       <c r="S4" s="7" t="inlineStr"/>
       <c r="T4" s="7" t="inlineStr"/>
       <c r="U4" s="5" t="n">
-        <v>51900</v>
+        <v>51000</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>73.02504816955684</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="W4" s="7" t="inlineStr"/>
       <c r="X4" s="7" t="inlineStr"/>
@@ -910,51 +906,51 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.8%</t>
+          <t>1차 매수선까지 43.3%</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>138800</v>
+        <v>137600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>137600</v>
+        <v>133700</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>144000</v>
+        <v>141600</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>122070</v>
+        <v>120490</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>123495</v>
+        <v>122010</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>97656</v>
+        <v>96392</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>98796</v>
+        <v>97608</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>97200</v>
+        <v>96000</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>42.79835390946502</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="5" t="n">
-        <v>87500</v>
+        <v>86500</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>58.62857142857143</v>
+        <v>59.07514450867052</v>
       </c>
       <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="7" t="inlineStr"/>
       <c r="U5" s="5" t="n">
-        <v>78800</v>
+        <v>77900</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>76.14213197969542</v>
+        <v>76.6367137355584</v>
       </c>
       <c r="W5" s="7" t="inlineStr"/>
       <c r="X5" s="7" t="inlineStr"/>
@@ -990,35 +986,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.1%</t>
+          <t>1차 매수선까지 32.6%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
+        <v>270500</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>255500</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>273500</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>271000</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>287500</v>
-      </c>
       <c r="I6" s="5" t="n">
-        <v>258075</v>
+        <v>258250</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>258400</v>
+        <v>257925</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>206460</v>
+        <v>206600</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>206720</v>
+        <v>206340</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>204000</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>34.06862745098039</v>
+        <v>32.59803921568628</v>
       </c>
       <c r="O6" s="7" t="inlineStr"/>
       <c r="P6" s="7" t="inlineStr"/>
@@ -1026,7 +1022,7 @@
         <v>183700</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>48.88405008165487</v>
+        <v>47.2509526401742</v>
       </c>
       <c r="S6" s="7" t="inlineStr"/>
       <c r="T6" s="7" t="inlineStr"/>
@@ -1034,7 +1030,7 @@
         <v>165400</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>65.35671100362757</v>
+        <v>63.54292623941959</v>
       </c>
       <c r="W6" s="7" t="inlineStr"/>
       <c r="X6" s="7" t="inlineStr"/>
@@ -1070,51 +1066,51 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 66.5%</t>
+          <t>1차 매수선까지 59.0%</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>348000</v>
+        <v>323500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>320000</v>
+        <v>315500</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>355000</v>
+        <v>329000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>261050</v>
+        <v>253975</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>268200</v>
+        <v>259825</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>208840</v>
+        <v>203180</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>214560</v>
+        <v>207860</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>209000</v>
+        <v>203500</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>66.50717703349282</v>
+        <v>58.96805896805897</v>
       </c>
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="5" t="n">
-        <v>188200</v>
+        <v>183200</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>84.90967056323061</v>
+        <v>76.58296943231441</v>
       </c>
       <c r="S7" s="7" t="inlineStr"/>
       <c r="T7" s="7" t="inlineStr"/>
       <c r="U7" s="5" t="n">
-        <v>169400</v>
+        <v>164900</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>105.43093270366</v>
+        <v>96.17950272892662</v>
       </c>
       <c r="W7" s="7" t="inlineStr"/>
       <c r="X7" s="7" t="inlineStr"/>
@@ -1150,51 +1146,51 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.2%</t>
+          <t>1차 매수선까지 48.8%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>291500</v>
+        <v>288000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>287000</v>
+        <v>267000</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>298000</v>
+        <v>294000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>246725</v>
+        <v>242925</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>250550</v>
+        <v>246550</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>197380</v>
+        <v>194340</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>200440</v>
+        <v>197240</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>196700</v>
+        <v>193500</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>48.19522114895781</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="O8" s="7" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr"/>
       <c r="Q8" s="5" t="n">
-        <v>177100</v>
+        <v>174200</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>64.59627329192547</v>
+        <v>65.32721010332951</v>
       </c>
       <c r="S8" s="7" t="inlineStr"/>
       <c r="T8" s="7" t="inlineStr"/>
       <c r="U8" s="5" t="n">
-        <v>159400</v>
+        <v>156800</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>82.8732747804266</v>
+        <v>83.67346938775511</v>
       </c>
       <c r="W8" s="7" t="inlineStr"/>
       <c r="X8" s="7" t="inlineStr"/>
@@ -1210,12 +1206,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>086520</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1230,51 +1226,51 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 65.9%</t>
+          <t>1차 매수선까지 32.5%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>96200</v>
+        <v>141500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>88100</v>
+        <v>138900</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>96200</v>
+        <v>144800</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>71872.5</v>
+        <v>132670</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>74310</v>
+        <v>135140</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>57498</v>
+        <v>106136</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>59448</v>
+        <v>108112</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>58000</v>
+        <v>106800</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>65.86206896551724</v>
+        <v>32.49063670411985</v>
       </c>
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="5" t="n">
-        <v>52300</v>
+        <v>96200</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>83.93881453154876</v>
+        <v>47.08939708939709</v>
       </c>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="inlineStr"/>
       <c r="U9" s="5" t="n">
-        <v>47100</v>
+        <v>86600</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>104.2462845010616</v>
+        <v>63.39491916859122</v>
       </c>
       <c r="W9" s="7" t="inlineStr"/>
       <c r="X9" s="7" t="inlineStr"/>
@@ -1290,12 +1286,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>086520</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1310,51 +1306,51 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.6%</t>
+          <t>1차 매수선까지 60.8%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>142000</v>
+        <v>89900</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>138400</v>
+        <v>85500</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>143900</v>
+        <v>92300</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>135165</v>
+        <v>69475</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>137445</v>
+        <v>71557.5</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>108132</v>
+        <v>55580</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>109956</v>
+        <v>57246</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>108700</v>
+        <v>55900</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>30.63477460901564</v>
+        <v>60.82289803220036</v>
       </c>
       <c r="O10" s="7" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr"/>
       <c r="Q10" s="5" t="n">
-        <v>97900</v>
+        <v>50400</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>45.04596527068438</v>
+        <v>78.37301587301587</v>
       </c>
       <c r="S10" s="7" t="inlineStr"/>
       <c r="T10" s="7" t="inlineStr"/>
       <c r="U10" s="5" t="n">
-        <v>88200</v>
+        <v>45400</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>60.99773242630386</v>
+        <v>98.01762114537445</v>
       </c>
       <c r="W10" s="7" t="inlineStr"/>
       <c r="X10" s="7" t="inlineStr"/>
@@ -1390,51 +1386,51 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.1%</t>
+          <t>1차 매수선까지 51.7%</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>29150</v>
+        <v>29600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>28850</v>
+        <v>29100</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>30200</v>
+        <v>30300</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>24860</v>
+        <v>24470</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>25220</v>
+        <v>24882.5</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>19888</v>
+        <v>19576</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>20176</v>
+        <v>19906</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>19810</v>
+        <v>19510</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>47.14790509843513</v>
+        <v>51.71706817016914</v>
       </c>
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="5" t="n">
-        <v>17830</v>
+        <v>17560</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>63.48850252383623</v>
+        <v>68.56492027334852</v>
       </c>
       <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="7" t="inlineStr"/>
       <c r="U11" s="5" t="n">
-        <v>16050</v>
+        <v>15810</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>81.61993769470405</v>
+        <v>87.22327640733712</v>
       </c>
       <c r="W11" s="7" t="inlineStr"/>
       <c r="X11" s="7" t="inlineStr"/>
@@ -1470,51 +1466,51 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.5%</t>
+          <t>1차 매수선까지 35.5%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>64900</v>
+        <v>65500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>64000</v>
+        <v>62800</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>66900</v>
+        <v>66300</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>61245</v>
+        <v>61040</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>61510</v>
+        <v>61275</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>48996</v>
+        <v>48832</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>49208</v>
+        <v>49020</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>48600</v>
+        <v>48350</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>33.53909465020576</v>
+        <v>35.47052740434333</v>
       </c>
       <c r="O12" s="7" t="inlineStr"/>
       <c r="P12" s="7" t="inlineStr"/>
       <c r="Q12" s="5" t="n">
-        <v>43750</v>
+        <v>43550</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>48.34285714285714</v>
+        <v>50.40183696900115</v>
       </c>
       <c r="S12" s="7" t="inlineStr"/>
       <c r="T12" s="7" t="inlineStr"/>
       <c r="U12" s="5" t="n">
-        <v>39400</v>
+        <v>39200</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>64.72081218274111</v>
+        <v>67.09183673469387</v>
       </c>
       <c r="W12" s="7" t="inlineStr"/>
       <c r="X12" s="7" t="inlineStr"/>
@@ -1550,51 +1546,51 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.2%</t>
+          <t>1차 매수선까지 42.8%</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>225000</v>
+        <v>218000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>213000</v>
+        <v>212500</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>225000</v>
+        <v>223500</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>194400</v>
+        <v>190435</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>198405</v>
+        <v>194050</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>155520</v>
+        <v>152348</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>158724</v>
+        <v>155240</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>156000</v>
+        <v>152700</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>44.23076923076923</v>
+        <v>42.76358873608383</v>
       </c>
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="5" t="n">
-        <v>140500</v>
+        <v>137500</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>60.14234875444839</v>
+        <v>58.54545454545455</v>
       </c>
       <c r="S13" s="7" t="inlineStr"/>
       <c r="T13" s="7" t="inlineStr"/>
       <c r="U13" s="5" t="n">
-        <v>126500</v>
+        <v>123800</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>77.86561264822134</v>
+        <v>76.09046849757674</v>
       </c>
       <c r="W13" s="7" t="inlineStr"/>
       <c r="X13" s="7" t="inlineStr"/>
@@ -1630,51 +1626,51 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.2%</t>
+          <t>1차 매수선까지 40.1%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>167900</v>
+        <v>162200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>158500</v>
+        <v>157600</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>168200</v>
+        <v>164500</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>147265</v>
+        <v>144660</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>150015</v>
+        <v>146980</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>117812</v>
+        <v>115728</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>120012</v>
+        <v>117584</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>118100</v>
+        <v>115800</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>42.16765453005927</v>
+        <v>40.06908462867012</v>
       </c>
       <c r="O14" s="7" t="inlineStr"/>
       <c r="P14" s="7" t="inlineStr"/>
       <c r="Q14" s="5" t="n">
-        <v>106300</v>
+        <v>104300</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>57.94920037629351</v>
+        <v>55.51294343240652</v>
       </c>
       <c r="S14" s="7" t="inlineStr"/>
       <c r="T14" s="7" t="inlineStr"/>
       <c r="U14" s="5" t="n">
-        <v>95700</v>
+        <v>93900</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>75.4440961337513</v>
+        <v>72.73695420660276</v>
       </c>
       <c r="W14" s="7" t="inlineStr"/>
       <c r="X14" s="7" t="inlineStr"/>
@@ -1710,51 +1706,51 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.4%</t>
+          <t>1차 매수선까지 39.9%</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>483000</v>
+        <v>473500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>433000</v>
+        <v>469500</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>489000</v>
+        <v>491500</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>430175</v>
+        <v>423625</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>436925</v>
+        <v>429700</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>344140</v>
+        <v>338900</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>349540</v>
+        <v>343760</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>344000</v>
+        <v>338500</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>40.40697674418605</v>
+        <v>39.88183161004431</v>
       </c>
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="5" t="n">
-        <v>310000</v>
+        <v>305000</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>55.80645161290323</v>
+        <v>55.24590163934426</v>
       </c>
       <c r="S15" s="7" t="inlineStr"/>
       <c r="T15" s="7" t="inlineStr"/>
       <c r="U15" s="5" t="n">
-        <v>279500</v>
+        <v>275000</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>72.80858676207514</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="W15" s="7" t="inlineStr"/>
       <c r="X15" s="7" t="inlineStr"/>
@@ -1770,12 +1766,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1790,51 +1786,51 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 72.1%</t>
+          <t>1차 매수선까지 40.7%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>477500</v>
+        <v>84400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>427000</v>
+        <v>82100</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>500000</v>
+        <v>84900</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>347875</v>
+        <v>75265</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>356425</v>
+        <v>76160</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>278300</v>
+        <v>60212</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>285140</v>
+        <v>60928</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>277500</v>
+        <v>60000</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>72.07207207207207</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="O16" s="7" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr"/>
       <c r="Q16" s="5" t="n">
-        <v>250000</v>
+        <v>54100</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>91</v>
+        <v>56.00739371534195</v>
       </c>
       <c r="S16" s="7" t="inlineStr"/>
       <c r="T16" s="7" t="inlineStr"/>
       <c r="U16" s="5" t="n">
-        <v>225500</v>
+        <v>48700</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>111.7516629711752</v>
+        <v>73.30595482546201</v>
       </c>
       <c r="W16" s="7" t="inlineStr"/>
       <c r="X16" s="7" t="inlineStr"/>
@@ -1850,12 +1846,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1870,51 +1866,51 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 76.2%</t>
+          <t>1차 매수선까지 47.4%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>274500</v>
+        <v>123100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>220500</v>
+        <v>118200</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>282000</v>
+        <v>129100</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>194975</v>
+        <v>103790</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>200665</v>
+        <v>106300</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>155980</v>
+        <v>83032</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>160532</v>
+        <v>85040</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>155800</v>
+        <v>83500</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>76.18741976893453</v>
+        <v>47.4251497005988</v>
       </c>
       <c r="O17" s="7" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="5" t="n">
-        <v>140300</v>
+        <v>75200</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>95.65217391304348</v>
+        <v>63.69680851063831</v>
       </c>
       <c r="S17" s="7" t="inlineStr"/>
       <c r="T17" s="7" t="inlineStr"/>
       <c r="U17" s="5" t="n">
-        <v>126300</v>
+        <v>67700</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>117.3396674584323</v>
+        <v>81.83161004431314</v>
       </c>
       <c r="W17" s="7" t="inlineStr"/>
       <c r="X17" s="7" t="inlineStr"/>
@@ -1930,12 +1926,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1950,51 +1946,51 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.5%</t>
+          <t>1차 매수선까지 45.6%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>520000</v>
+        <v>397500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>485500</v>
+        <v>389000</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>527000</v>
+        <v>404000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>460275</v>
+        <v>341475</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>463500</v>
+        <v>347275</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>368220</v>
+        <v>273180</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>370800</v>
+        <v>277820</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>365000</v>
+        <v>273000</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>42.46575342465754</v>
+        <v>45.60439560439561</v>
       </c>
       <c r="O18" s="7" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="5" t="n">
-        <v>329000</v>
+        <v>246000</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>58.05471124620061</v>
+        <v>61.58536585365854</v>
       </c>
       <c r="S18" s="7" t="inlineStr"/>
       <c r="T18" s="7" t="inlineStr"/>
       <c r="U18" s="5" t="n">
-        <v>296500</v>
+        <v>221500</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>75.37942664418212</v>
+        <v>79.45823927765237</v>
       </c>
       <c r="W18" s="7" t="inlineStr"/>
       <c r="X18" s="7" t="inlineStr"/>
@@ -2010,12 +2006,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2030,51 +2026,51 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.8%</t>
+          <t>1차 매수선까지 36.2%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>86800</v>
+        <v>63800</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>82400</v>
+        <v>62200</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>87000</v>
+        <v>64900</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>76280</v>
+        <v>58605</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>77300</v>
+        <v>59377.5</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>61024</v>
+        <v>46884</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>61840</v>
+        <v>47502</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>60800</v>
+        <v>46850</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>42.76315789473684</v>
+        <v>36.17929562433298</v>
       </c>
       <c r="O19" s="7" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr"/>
       <c r="Q19" s="5" t="n">
-        <v>54800</v>
+        <v>42200</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>58.3941605839416</v>
+        <v>51.18483412322274</v>
       </c>
       <c r="S19" s="7" t="inlineStr"/>
       <c r="T19" s="7" t="inlineStr"/>
       <c r="U19" s="5" t="n">
-        <v>49350</v>
+        <v>38000</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>75.88652482269504</v>
+        <v>67.89473684210526</v>
       </c>
       <c r="W19" s="7" t="inlineStr"/>
       <c r="X19" s="7" t="inlineStr"/>
@@ -2090,12 +2086,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2110,51 +2106,51 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.1%</t>
+          <t>1차 매수선까지 32.8%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>126100</v>
+        <v>42700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>120000</v>
+        <v>42500</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>127500</v>
+        <v>43400</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>106450</v>
+        <v>40407.5</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>109070</v>
+        <v>40700</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>85160</v>
+        <v>32326</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>87256</v>
+        <v>32560</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>85700</v>
+        <v>32150</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>47.1411901983664</v>
+        <v>32.8149300155521</v>
       </c>
       <c r="O20" s="7" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr"/>
       <c r="Q20" s="5" t="n">
-        <v>77200</v>
+        <v>28950</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>63.3419689119171</v>
+        <v>47.49568221070812</v>
       </c>
       <c r="S20" s="7" t="inlineStr"/>
       <c r="T20" s="7" t="inlineStr"/>
       <c r="U20" s="5" t="n">
-        <v>69500</v>
+        <v>26100</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>81.43884892086331</v>
+        <v>63.60153256704982</v>
       </c>
       <c r="W20" s="7" t="inlineStr"/>
       <c r="X20" s="7" t="inlineStr"/>
@@ -2170,12 +2166,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2190,51 +2186,51 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.8%</t>
+          <t>1차 매수선까지 37.0%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>397000</v>
+        <v>120400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>385500</v>
+        <v>116000</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>402000</v>
+        <v>122600</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>347250</v>
+        <v>110440</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>353175</v>
+        <v>111410</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>277800</v>
+        <v>88352</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>282540</v>
+        <v>89128</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>278000</v>
+        <v>87900</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>42.80575539568346</v>
+        <v>36.97383390216154</v>
       </c>
       <c r="O21" s="7" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="5" t="n">
-        <v>250500</v>
+        <v>79200</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>58.48303393213573</v>
+        <v>52.02020202020202</v>
       </c>
       <c r="S21" s="7" t="inlineStr"/>
       <c r="T21" s="7" t="inlineStr"/>
       <c r="U21" s="5" t="n">
-        <v>225500</v>
+        <v>71300</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>76.05321507760532</v>
+        <v>68.86395511921458</v>
       </c>
       <c r="W21" s="7" t="inlineStr"/>
       <c r="X21" s="7" t="inlineStr"/>
@@ -2250,12 +2246,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2270,51 +2266,51 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.8%</t>
+          <t>1차 매수선까지 67.6%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>67100</v>
+        <v>24300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>62900</v>
+        <v>21050</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>67200</v>
+        <v>25400</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>59542.5</v>
+        <v>18154.5</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>60532.5</v>
+        <v>18613.5</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>47634</v>
+        <v>14523.6</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>48426</v>
+        <v>14890.8</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>47650</v>
+        <v>14500</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>40.81846799580273</v>
+        <v>67.58620689655173</v>
       </c>
       <c r="O22" s="7" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr"/>
       <c r="Q22" s="5" t="n">
-        <v>42900</v>
+        <v>13060</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>56.41025641025641</v>
+        <v>86.06431852986218</v>
       </c>
       <c r="S22" s="7" t="inlineStr"/>
       <c r="T22" s="7" t="inlineStr"/>
       <c r="U22" s="5" t="n">
-        <v>38650</v>
+        <v>11760</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>73.60931435963778</v>
+        <v>106.6326530612245</v>
       </c>
       <c r="W22" s="7" t="inlineStr"/>
       <c r="X22" s="7" t="inlineStr"/>
@@ -2330,12 +2326,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2350,51 +2346,51 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.4%</t>
+          <t>1차 매수선까지 60.9%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>45700</v>
+        <v>434500</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>42600</v>
+        <v>358000</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>45750</v>
+        <v>453500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>40850</v>
+        <v>339700</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>41332.5</v>
+        <v>345725</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>32680</v>
+        <v>271760</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>33066</v>
+        <v>276580</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>32550</v>
+        <v>270000</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>40.39938556067588</v>
+        <v>60.92592592592593</v>
       </c>
       <c r="O23" s="7" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr"/>
       <c r="Q23" s="5" t="n">
-        <v>29300</v>
+        <v>243500</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>55.97269624573379</v>
+        <v>78.43942505133469</v>
       </c>
       <c r="S23" s="7" t="inlineStr"/>
       <c r="T23" s="7" t="inlineStr"/>
       <c r="U23" s="5" t="n">
-        <v>26400</v>
+        <v>219500</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>73.10606060606061</v>
+        <v>97.9498861047836</v>
       </c>
       <c r="W23" s="7" t="inlineStr"/>
       <c r="X23" s="7" t="inlineStr"/>
@@ -2410,12 +2406,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2430,51 +2426,51 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 49.6%</t>
+          <t>1차 매수선까지 85.3%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>46600</v>
+        <v>278000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>41100</v>
+        <v>233500</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>49550</v>
+        <v>284500</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>38787.5</v>
+        <v>190200</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>39682.5</v>
+        <v>193850</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>31030</v>
+        <v>152160</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>31746</v>
+        <v>155080</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>31150</v>
+        <v>150000</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>49.59871589085072</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="O24" s="7" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr"/>
       <c r="Q24" s="5" t="n">
-        <v>28050</v>
+        <v>135100</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>66.1319073083779</v>
+        <v>105.7735011102887</v>
       </c>
       <c r="S24" s="7" t="inlineStr"/>
       <c r="T24" s="7" t="inlineStr"/>
       <c r="U24" s="5" t="n">
-        <v>25250</v>
+        <v>121600</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>84.55445544554455</v>
+        <v>128.6184210526316</v>
       </c>
       <c r="W24" s="7" t="inlineStr"/>
       <c r="X24" s="7" t="inlineStr"/>
@@ -2490,12 +2486,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2510,51 +2506,51 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.7%</t>
+          <t>1차 매수선까지 45.9%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1039000</v>
+        <v>220500</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>981000</v>
+        <v>214000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1056000</v>
+        <v>235000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1008450</v>
+        <v>189055</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1005050</v>
+        <v>192275</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>806760</v>
+        <v>151244</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>804040</v>
+        <v>153820</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>795000</v>
+        <v>151100</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>30.69182389937107</v>
+        <v>45.92984778292521</v>
       </c>
       <c r="O25" s="7" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr"/>
       <c r="Q25" s="5" t="n">
-        <v>716000</v>
+        <v>136000</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>45.11173184357542</v>
+        <v>62.13235294117647</v>
       </c>
       <c r="S25" s="7" t="inlineStr"/>
       <c r="T25" s="7" t="inlineStr"/>
       <c r="U25" s="5" t="n">
-        <v>645000</v>
+        <v>122500</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>61.08527131782946</v>
+        <v>80</v>
       </c>
       <c r="W25" s="7" t="inlineStr"/>
       <c r="X25" s="7" t="inlineStr"/>
@@ -2570,12 +2566,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2590,51 +2586,51 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.7%</t>
+          <t>1차 매수선까지 34.3%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>118500</v>
+        <v>59900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>117500</v>
+        <v>58700</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>121700</v>
+        <v>64300</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>111315</v>
+        <v>56485</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>112195</v>
+        <v>56505</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>89052</v>
+        <v>45188</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>89756</v>
+        <v>45204</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>88600</v>
+        <v>44600</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>33.74717832957111</v>
+        <v>34.30493273542601</v>
       </c>
       <c r="O26" s="7" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr"/>
       <c r="Q26" s="5" t="n">
-        <v>79800</v>
+        <v>40150</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>48.49624060150376</v>
+        <v>49.19053549190536</v>
       </c>
       <c r="S26" s="7" t="inlineStr"/>
       <c r="T26" s="7" t="inlineStr"/>
       <c r="U26" s="5" t="n">
-        <v>71900</v>
+        <v>36150</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>64.81223922114047</v>
+        <v>65.69847856154909</v>
       </c>
       <c r="W26" s="7" t="inlineStr"/>
       <c r="X26" s="7" t="inlineStr"/>
@@ -2650,12 +2646,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2670,51 +2666,51 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 69.3%</t>
+          <t>1차 매수선까지 59.0%</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>25250</v>
+        <v>42700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>24150</v>
+        <v>41700</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>25600</v>
+        <v>45000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>18661</v>
+        <v>33670</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>19144.5</v>
+        <v>34347.5</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>14928.8</v>
+        <v>26936</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>15315.6</v>
+        <v>27478</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>14910</v>
+        <v>26850</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>69.34942991281019</v>
+        <v>59.0316573556797</v>
       </c>
       <c r="O27" s="7" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr"/>
       <c r="Q27" s="5" t="n">
-        <v>13420</v>
+        <v>24200</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>88.15201192250373</v>
+        <v>76.44628099173553</v>
       </c>
       <c r="S27" s="7" t="inlineStr"/>
       <c r="T27" s="7" t="inlineStr"/>
       <c r="U27" s="5" t="n">
-        <v>12080</v>
+        <v>21800</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>109.023178807947</v>
+        <v>95.87155963302753</v>
       </c>
       <c r="W27" s="7" t="inlineStr"/>
       <c r="X27" s="7" t="inlineStr"/>
@@ -2730,12 +2726,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2750,51 +2746,51 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 82.6%</t>
+          <t>1차 매수선까지 44.7%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>280000</v>
+        <v>70300</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>264000</v>
+        <v>67000</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>281500</v>
+        <v>72100</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>193950</v>
+        <v>61060</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>197900</v>
+        <v>61830</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>155160</v>
+        <v>48848</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>158320</v>
+        <v>49464</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>153300</v>
+        <v>48600</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>82.64840182648402</v>
+        <v>44.65020576131688</v>
       </c>
       <c r="O28" s="7" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr"/>
       <c r="Q28" s="5" t="n">
-        <v>138000</v>
+        <v>43750</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>102.8985507246377</v>
+        <v>60.68571428571429</v>
       </c>
       <c r="S28" s="7" t="inlineStr"/>
       <c r="T28" s="7" t="inlineStr"/>
       <c r="U28" s="5" t="n">
-        <v>124300</v>
+        <v>39400</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>125.2614641995173</v>
+        <v>78.42639593908629</v>
       </c>
       <c r="W28" s="7" t="inlineStr"/>
       <c r="X28" s="7" t="inlineStr"/>
@@ -2810,12 +2806,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2830,51 +2826,51 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.4%</t>
+          <t>1차 매수선까지 34.8%</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>59500</v>
+        <v>488000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>58500</v>
+        <v>472000</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>62000</v>
+        <v>491500</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>56485</v>
+        <v>457625</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>56485</v>
+        <v>458675</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>45188</v>
+        <v>366100</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>45188</v>
+        <v>366940</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>44600</v>
+        <v>362000</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>33.40807174887892</v>
+        <v>34.80662983425415</v>
       </c>
       <c r="O29" s="7" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr"/>
       <c r="Q29" s="5" t="n">
-        <v>40150</v>
+        <v>326000</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>48.19427148194271</v>
+        <v>49.69325153374233</v>
       </c>
       <c r="S29" s="7" t="inlineStr"/>
       <c r="T29" s="7" t="inlineStr"/>
       <c r="U29" s="5" t="n">
-        <v>36150</v>
+        <v>293500</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>64.59197786998617</v>
+        <v>66.26916524701873</v>
       </c>
       <c r="W29" s="7" t="inlineStr"/>
       <c r="X29" s="7" t="inlineStr"/>
@@ -2890,12 +2886,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2910,51 +2906,51 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.5%</t>
+          <t>1차 매수선까지 29.8%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>43850</v>
+        <v>28100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>42250</v>
+        <v>27800</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>45200</v>
+        <v>29200</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>34405</v>
+        <v>27267.5</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>35172.5</v>
+        <v>27377.5</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>27524</v>
+        <v>21814</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>28138</v>
+        <v>21902</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>27500</v>
+        <v>21650</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>59.45454545454546</v>
+        <v>29.79214780600462</v>
       </c>
       <c r="O30" s="7" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr"/>
       <c r="Q30" s="5" t="n">
-        <v>24800</v>
+        <v>19490</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>76.81451612903226</v>
+        <v>44.17650076962545</v>
       </c>
       <c r="S30" s="7" t="inlineStr"/>
       <c r="T30" s="7" t="inlineStr"/>
       <c r="U30" s="5" t="n">
-        <v>22350</v>
+        <v>17550</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>96.19686800894854</v>
+        <v>60.11396011396012</v>
       </c>
       <c r="W30" s="7" t="inlineStr"/>
       <c r="X30" s="7" t="inlineStr"/>
@@ -2970,12 +2966,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2990,51 +2986,51 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.9%</t>
+          <t>1차 매수선까지 31.7%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>67300</v>
+        <v>232000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>65400</v>
+        <v>226500</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>70900</v>
+        <v>238000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>61680</v>
+        <v>222000</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>62330</v>
+        <v>222825</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>49344</v>
+        <v>177600</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>49864</v>
+        <v>178260</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>49150</v>
+        <v>176100</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>36.92777212614445</v>
+        <v>31.74332765474163</v>
       </c>
       <c r="O31" s="7" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr"/>
       <c r="Q31" s="5" t="n">
-        <v>44250</v>
+        <v>158500</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>52.09039548022599</v>
+        <v>46.37223974763407</v>
       </c>
       <c r="S31" s="7" t="inlineStr"/>
       <c r="T31" s="7" t="inlineStr"/>
       <c r="U31" s="5" t="n">
-        <v>39850</v>
+        <v>142700</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>68.88331242158094</v>
+        <v>62.57883672039243</v>
       </c>
       <c r="W31" s="7" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr"/>
@@ -3050,12 +3046,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3070,51 +3066,51 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.6%</t>
+          <t>1차 매수선까지 67.4%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>27400</v>
+        <v>966000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>27100</v>
+        <v>912000</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>28800</v>
+        <v>968000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>27342.5</v>
+        <v>718100</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>27312.5</v>
+        <v>739750</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>21874</v>
+        <v>574480</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>21850</v>
+        <v>591800</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>21650</v>
+        <v>577000</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>26.55889145496536</v>
+        <v>67.41767764298093</v>
       </c>
       <c r="O32" s="7" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr"/>
       <c r="Q32" s="5" t="n">
-        <v>19490</v>
+        <v>520000</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>40.58491534120062</v>
+        <v>85.76923076923076</v>
       </c>
       <c r="S32" s="7" t="inlineStr"/>
       <c r="T32" s="7" t="inlineStr"/>
       <c r="U32" s="5" t="n">
-        <v>17550</v>
+        <v>468500</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>56.12535612535613</v>
+        <v>106.1899679829242</v>
       </c>
       <c r="W32" s="7" t="inlineStr"/>
       <c r="X32" s="7" t="inlineStr"/>
@@ -3130,12 +3126,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3150,51 +3146,51 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.5%</t>
+          <t>1차 매수선까지 34.8%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>243500</v>
+        <v>11820</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>229000</v>
+        <v>11590</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>248000</v>
+        <v>12770</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>223400</v>
+        <v>10962.5</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>224600</v>
+        <v>11111</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>178720</v>
+        <v>8770</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>179680</v>
+        <v>8888.800000000001</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>177100</v>
+        <v>8770</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>37.49294184076793</v>
+        <v>34.77765108323831</v>
       </c>
       <c r="O33" s="7" t="inlineStr"/>
       <c r="P33" s="7" t="inlineStr"/>
       <c r="Q33" s="5" t="n">
-        <v>159400</v>
+        <v>7900</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>52.7603513174404</v>
+        <v>49.62025316455696</v>
       </c>
       <c r="S33" s="7" t="inlineStr"/>
       <c r="T33" s="7" t="inlineStr"/>
       <c r="U33" s="5" t="n">
-        <v>143500</v>
+        <v>7120</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>69.68641114982579</v>
+        <v>66.01123595505618</v>
       </c>
       <c r="W33" s="7" t="inlineStr"/>
       <c r="X33" s="7" t="inlineStr"/>
@@ -3210,12 +3206,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3230,51 +3226,51 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 70.6%</t>
+          <t>1차 매수선까지 66.8%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1017000</v>
+        <v>209500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>938000</v>
+        <v>163400</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1025000</v>
+        <v>209500</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>742300</v>
+        <v>158340</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>766050</v>
+        <v>161130</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>593840</v>
+        <v>126672</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>612840</v>
+        <v>128904</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>596000</v>
+        <v>125600</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>70.63758389261746</v>
+        <v>66.79936305732484</v>
       </c>
       <c r="O34" s="7" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr"/>
       <c r="Q34" s="5" t="n">
-        <v>537000</v>
+        <v>113100</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>89.38547486033519</v>
+        <v>85.2343059239611</v>
       </c>
       <c r="S34" s="7" t="inlineStr"/>
       <c r="T34" s="7" t="inlineStr"/>
       <c r="U34" s="5" t="n">
-        <v>483500</v>
+        <v>101800</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>110.3412616339193</v>
+        <v>105.7956777996071</v>
       </c>
       <c r="W34" s="7" t="inlineStr"/>
       <c r="X34" s="7" t="inlineStr"/>
@@ -3290,12 +3286,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3310,51 +3306,51 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.1%</t>
+          <t>1차 매수선까지 45.4%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>12170</v>
+        <v>126600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>11650</v>
+        <v>114700</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>12800</v>
+        <v>131100</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>11128.5</v>
+        <v>109445</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>11330.5</v>
+        <v>110790</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>8902.800000000001</v>
+        <v>87556</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>9064.4</v>
+        <v>88632</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>8940</v>
+        <v>87100</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>36.12975391498882</v>
+        <v>45.35017221584386</v>
       </c>
       <c r="O35" s="7" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr"/>
       <c r="Q35" s="5" t="n">
-        <v>8050</v>
+        <v>78400</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>51.18012422360248</v>
+        <v>61.47959183673469</v>
       </c>
       <c r="S35" s="7" t="inlineStr"/>
       <c r="T35" s="7" t="inlineStr"/>
       <c r="U35" s="5" t="n">
-        <v>7250</v>
+        <v>70600</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>67.86206896551724</v>
+        <v>79.3201133144476</v>
       </c>
       <c r="W35" s="7" t="inlineStr"/>
       <c r="X35" s="7" t="inlineStr"/>
@@ -3370,12 +3366,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>454910</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3390,51 +3386,51 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.9%</t>
+          <t>1차 매수선까지 46.6%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>92500</v>
+        <v>425000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>76700</v>
+        <v>389500</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>95500</v>
+        <v>435500</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>72225</v>
+        <v>367250</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>73560</v>
+        <v>368700</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>57780</v>
+        <v>293800</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>58848</v>
+        <v>294960</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>57500</v>
+        <v>290000</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>60.86956521739131</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="O36" s="7" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr"/>
       <c r="Q36" s="5" t="n">
-        <v>51800</v>
+        <v>261500</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>78.57142857142857</v>
+        <v>62.52390057361377</v>
       </c>
       <c r="S36" s="7" t="inlineStr"/>
       <c r="T36" s="7" t="inlineStr"/>
       <c r="U36" s="5" t="n">
-        <v>46650</v>
+        <v>235500</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>98.28510182207931</v>
+        <v>80.46709129511677</v>
       </c>
       <c r="W36" s="7" t="inlineStr"/>
       <c r="X36" s="7" t="inlineStr"/>
@@ -3450,12 +3446,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>161580</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3470,51 +3466,51 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 72.3%</t>
+          <t>1차 매수선까지 50.4%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>54800</v>
+        <v>343000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>42200</v>
+        <v>321500</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>54800</v>
+        <v>345000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>40007.5</v>
+        <v>286925</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>40882.5</v>
+        <v>290550</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>32006</v>
+        <v>229540</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>32706</v>
+        <v>232440</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>31800</v>
+        <v>228000</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>72.32704402515722</v>
+        <v>50.43859649122807</v>
       </c>
       <c r="O37" s="7" t="inlineStr"/>
       <c r="P37" s="7" t="inlineStr"/>
       <c r="Q37" s="5" t="n">
-        <v>28650</v>
+        <v>205500</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>91.2739965095986</v>
+        <v>66.90997566909975</v>
       </c>
       <c r="S37" s="7" t="inlineStr"/>
       <c r="T37" s="7" t="inlineStr"/>
       <c r="U37" s="5" t="n">
-        <v>25800</v>
+        <v>185000</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>112.4031007751938</v>
+        <v>85.4054054054054</v>
       </c>
       <c r="W37" s="7" t="inlineStr"/>
       <c r="X37" s="7" t="inlineStr"/>
@@ -3530,12 +3526,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3550,51 +3546,51 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 74.6%</t>
+          <t>1차 매수선까지 64.1%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>224500</v>
+        <v>6450</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>209500</v>
+        <v>6090</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>245000</v>
+        <v>6500</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>161880</v>
+        <v>4876.5</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>165445</v>
+        <v>5035</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>129504</v>
+        <v>3901.2</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>132356</v>
+        <v>4028</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>128600</v>
+        <v>3930</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>74.57231726283048</v>
+        <v>64.12213740458014</v>
       </c>
       <c r="O38" s="7" t="inlineStr"/>
       <c r="P38" s="7" t="inlineStr"/>
       <c r="Q38" s="5" t="n">
-        <v>115800</v>
+        <v>3540</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>93.86873920552678</v>
+        <v>82.20338983050848</v>
       </c>
       <c r="S38" s="7" t="inlineStr"/>
       <c r="T38" s="7" t="inlineStr"/>
       <c r="U38" s="5" t="n">
-        <v>104300</v>
+        <v>3190</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>115.2444870565676</v>
+        <v>102.1943573667712</v>
       </c>
       <c r="W38" s="7" t="inlineStr"/>
       <c r="X38" s="7" t="inlineStr"/>
@@ -3610,12 +3606,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3630,51 +3626,51 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 53.2%</t>
+          <t>1차 매수선까지 33.6%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>135600</v>
+        <v>40600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>126100</v>
+        <v>40550</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>136800</v>
+        <v>45600</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>111240</v>
+        <v>37910</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>112955</v>
+        <v>38487.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>88992</v>
+        <v>30328</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>90364</v>
+        <v>30790</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>88500</v>
+        <v>30400</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>53.22033898305085</v>
+        <v>33.55263157894737</v>
       </c>
       <c r="O39" s="7" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr"/>
       <c r="Q39" s="5" t="n">
-        <v>79700</v>
+        <v>27400</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>70.13801756587202</v>
+        <v>48.17518248175183</v>
       </c>
       <c r="S39" s="7" t="inlineStr"/>
       <c r="T39" s="7" t="inlineStr"/>
       <c r="U39" s="5" t="n">
-        <v>71800</v>
+        <v>24700</v>
       </c>
       <c r="V39" s="6" t="n">
-        <v>88.85793871866295</v>
+        <v>64.37246963562752</v>
       </c>
       <c r="W39" s="7" t="inlineStr"/>
       <c r="X39" s="7" t="inlineStr"/>
@@ -3690,12 +3686,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3710,51 +3706,51 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.5%</t>
+          <t>1차 매수선까지 17.0%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>428500</v>
+        <v>9010</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>410000</v>
+        <v>8890</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>432000</v>
+        <v>9080</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>368875</v>
+        <v>9852.5</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>372075</v>
+        <v>9685</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>295100</v>
+        <v>7882</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>297660</v>
+        <v>7748</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>292500</v>
+        <v>7700</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>46.49572649572649</v>
+        <v>17.01298701298701</v>
       </c>
       <c r="O40" s="7" t="inlineStr"/>
       <c r="P40" s="7" t="inlineStr"/>
       <c r="Q40" s="5" t="n">
-        <v>263500</v>
+        <v>6940</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>62.61859582542695</v>
+        <v>29.82708933717579</v>
       </c>
       <c r="S40" s="7" t="inlineStr"/>
       <c r="T40" s="7" t="inlineStr"/>
       <c r="U40" s="5" t="n">
-        <v>237500</v>
+        <v>6250</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>80.42105263157895</v>
+        <v>44.16</v>
       </c>
       <c r="W40" s="7" t="inlineStr"/>
       <c r="X40" s="7" t="inlineStr"/>
@@ -3770,12 +3766,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3790,51 +3786,51 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.2%</t>
+          <t>1차 매수선까지 18.8%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>343000</v>
+        <v>15950</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>337500</v>
+        <v>15860</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>362500</v>
+        <v>16250</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>290550</v>
+        <v>17111.5</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>294375</v>
+        <v>16909.5</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>232440</v>
+        <v>13689.2</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>235500</v>
+        <v>13527.6</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>231500</v>
+        <v>13430</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>48.16414686825054</v>
+        <v>18.76396128071482</v>
       </c>
       <c r="O41" s="7" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr"/>
       <c r="Q41" s="5" t="n">
-        <v>208500</v>
+        <v>12090</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>64.5083932853717</v>
+        <v>31.92721257237386</v>
       </c>
       <c r="S41" s="7" t="inlineStr"/>
       <c r="T41" s="7" t="inlineStr"/>
       <c r="U41" s="5" t="n">
-        <v>187700</v>
+        <v>10890</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>82.73841236014917</v>
+        <v>46.46464646464646</v>
       </c>
       <c r="W41" s="7" t="inlineStr"/>
       <c r="X41" s="7" t="inlineStr"/>
@@ -3850,12 +3846,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>090710</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3870,51 +3866,51 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 73.3%</t>
+          <t>1차 매수선까지 26.7%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>7090</v>
+        <v>175800</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>6500</v>
+        <v>174500</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>7330</v>
+        <v>177300</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>5067</v>
+        <v>175300</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>5261.5</v>
+        <v>175160</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>4053.6</v>
+        <v>140240</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>4209.2</v>
+        <v>140128</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>4090</v>
+        <v>138700</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>73.34963325183375</v>
+        <v>26.74837779379957</v>
       </c>
       <c r="O42" s="7" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr"/>
       <c r="Q42" s="5" t="n">
-        <v>3685</v>
+        <v>124900</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>92.40162822252374</v>
+        <v>40.75260208166534</v>
       </c>
       <c r="S42" s="7" t="inlineStr"/>
       <c r="T42" s="7" t="inlineStr"/>
       <c r="U42" s="5" t="n">
-        <v>3320</v>
+        <v>112500</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>113.5542168674699</v>
+        <v>56.26666666666667</v>
       </c>
       <c r="W42" s="7" t="inlineStr"/>
       <c r="X42" s="7" t="inlineStr"/>
@@ -3930,12 +3926,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>일동제약</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3950,51 +3946,51 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.5%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>27600</v>
+        <v>234000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>24650</v>
+        <v>221000</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>28250</v>
+        <v>238500</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>24082.5</v>
+        <v>210815</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>23980</v>
+        <v>211565</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>19266</v>
+        <v>168652</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>19184</v>
+        <v>169252</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>18840</v>
+        <v>166600</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>46.49681528662421</v>
+        <v>40.45618247298919</v>
       </c>
       <c r="O43" s="7" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr"/>
       <c r="Q43" s="5" t="n">
-        <v>16960</v>
+        <v>150000</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>62.73584905660378</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="S43" s="7" t="inlineStr"/>
       <c r="T43" s="7" t="inlineStr"/>
       <c r="U43" s="5" t="n">
-        <v>15270</v>
+        <v>135100</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>80.74656188605108</v>
+        <v>73.20503330866025</v>
       </c>
       <c r="W43" s="7" t="inlineStr"/>
       <c r="X43" s="7" t="inlineStr"/>
@@ -4010,12 +4006,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -4030,51 +4026,51 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 16.4%</t>
+          <t>1차 매수선까지 10.7%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>8820</v>
+        <v>8060</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>8770</v>
+        <v>8030</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>9190</v>
+        <v>8350</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>9675.5</v>
+        <v>9235.5</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>9528.5</v>
+        <v>9131</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>7740.400000000001</v>
+        <v>7388.400000000001</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>7622.8</v>
+        <v>7304.8</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>7580</v>
+        <v>7280</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>16.35883905013193</v>
+        <v>10.71428571428571</v>
       </c>
       <c r="O44" s="7" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr"/>
       <c r="Q44" s="5" t="n">
-        <v>6830</v>
+        <v>6560</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>29.13616398243045</v>
+        <v>22.86585365853659</v>
       </c>
       <c r="S44" s="7" t="inlineStr"/>
       <c r="T44" s="7" t="inlineStr"/>
       <c r="U44" s="5" t="n">
-        <v>6150</v>
+        <v>5910</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>43.41463414634146</v>
+        <v>36.37901861252115</v>
       </c>
       <c r="W44" s="7" t="inlineStr"/>
       <c r="X44" s="7" t="inlineStr"/>
@@ -4090,12 +4086,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -4110,51 +4106,51 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.1%</t>
+          <t>1차 매수선까지 64.3%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>15580</v>
+        <v>86900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>15400</v>
+        <v>84800</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>16430</v>
+        <v>90800</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>16891</v>
+        <v>65667.5</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>16747</v>
+        <v>67730</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>13512.8</v>
+        <v>52534</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>13397.6</v>
+        <v>54184</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>13310</v>
+        <v>52900</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>17.05484598046582</v>
+        <v>64.27221172022685</v>
       </c>
       <c r="O45" s="7" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr"/>
       <c r="Q45" s="5" t="n">
-        <v>11980</v>
+        <v>47650</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>30.05008347245409</v>
+        <v>82.37145855194123</v>
       </c>
       <c r="S45" s="7" t="inlineStr"/>
       <c r="T45" s="7" t="inlineStr"/>
       <c r="U45" s="5" t="n">
-        <v>10790</v>
+        <v>42900</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>44.39295644114921</v>
+        <v>102.5641025641026</v>
       </c>
       <c r="W45" s="7" t="inlineStr"/>
       <c r="X45" s="7" t="inlineStr"/>
@@ -4170,12 +4166,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4190,51 +4186,51 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.0%</t>
+          <t>1차 매수선까지 27.9%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>174900</v>
+        <v>103700</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>173700</v>
+        <v>102500</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>176600</v>
+        <v>108000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>175115</v>
+        <v>102710</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>175195</v>
+        <v>102450</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>140092</v>
+        <v>82168</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>140156</v>
+        <v>81960</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>138800</v>
+        <v>81100</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>26.00864553314121</v>
+        <v>27.86683107274969</v>
       </c>
       <c r="O46" s="7" t="inlineStr"/>
       <c r="P46" s="7" t="inlineStr"/>
       <c r="Q46" s="5" t="n">
-        <v>125000</v>
+        <v>73000</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>39.92</v>
+        <v>42.05479452054794</v>
       </c>
       <c r="S46" s="7" t="inlineStr"/>
       <c r="T46" s="7" t="inlineStr"/>
       <c r="U46" s="5" t="n">
-        <v>112600</v>
+        <v>65800</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>55.32859680284192</v>
+        <v>57.59878419452887</v>
       </c>
       <c r="W46" s="7" t="inlineStr"/>
       <c r="X46" s="7" t="inlineStr"/>
@@ -4250,12 +4246,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4270,51 +4266,51 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.6%</t>
+          <t>1차 매수선까지 26.6%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>235500</v>
+        <v>435500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>224000</v>
+        <v>430000</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>236000</v>
+        <v>436500</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>211640</v>
+        <v>434500</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>212740</v>
+        <v>434400</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>169312</v>
+        <v>347600</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>170192</v>
+        <v>347520</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>167500</v>
+        <v>344000</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>40.59701492537313</v>
+        <v>26.59883720930232</v>
       </c>
       <c r="O47" s="7" t="inlineStr"/>
       <c r="P47" s="7" t="inlineStr"/>
       <c r="Q47" s="5" t="n">
-        <v>150800</v>
+        <v>310000</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>56.16710875331565</v>
+        <v>40.48387096774194</v>
       </c>
       <c r="S47" s="7" t="inlineStr"/>
       <c r="T47" s="7" t="inlineStr"/>
       <c r="U47" s="5" t="n">
-        <v>135800</v>
+        <v>279500</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>73.41678939617083</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="W47" s="7" t="inlineStr"/>
       <c r="X47" s="7" t="inlineStr"/>
@@ -4330,12 +4326,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4345,56 +4341,56 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>READY_BUY1</t>
+          <t>WATCHING</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 9.6% (접근 중!)</t>
+          <t>1차 매수선까지 18.6%</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>7880</v>
+        <v>21200</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>7720</v>
+        <v>21050</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>8220</v>
+        <v>21850</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>9122</v>
+        <v>22647.5</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>9021</v>
+        <v>22505</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>7297.6</v>
+        <v>18118</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>7216.8</v>
+        <v>18004</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>7190</v>
+        <v>17880</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>9.596662030598054</v>
+        <v>18.56823266219239</v>
       </c>
       <c r="O48" s="7" t="inlineStr"/>
       <c r="P48" s="7" t="inlineStr"/>
       <c r="Q48" s="5" t="n">
-        <v>6480</v>
+        <v>16100</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>21.60493827160494</v>
+        <v>31.67701863354037</v>
       </c>
       <c r="S48" s="7" t="inlineStr"/>
       <c r="T48" s="7" t="inlineStr"/>
       <c r="U48" s="5" t="n">
-        <v>5840</v>
+        <v>14500</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>34.93150684931507</v>
+        <v>46.20689655172414</v>
       </c>
       <c r="W48" s="7" t="inlineStr"/>
       <c r="X48" s="7" t="inlineStr"/>
@@ -4410,12 +4406,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4430,51 +4426,51 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 83.9%</t>
+          <t>1차 매수선까지 27.9%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>101700</v>
+        <v>22050</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>87500</v>
+        <v>21500</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>108000</v>
+        <v>22350</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>68470</v>
+        <v>21717</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>71330</v>
+        <v>21789.5</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>54776</v>
+        <v>17373.6</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>57064</v>
+        <v>17431.6</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>55300</v>
+        <v>17240</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>83.90596745027125</v>
+        <v>27.90023201856148</v>
       </c>
       <c r="O49" s="7" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr"/>
       <c r="Q49" s="5" t="n">
-        <v>49800</v>
+        <v>15520</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>104.2168674698795</v>
+        <v>42.07474226804123</v>
       </c>
       <c r="S49" s="7" t="inlineStr"/>
       <c r="T49" s="7" t="inlineStr"/>
       <c r="U49" s="5" t="n">
-        <v>44850</v>
+        <v>13970</v>
       </c>
       <c r="V49" s="6" t="n">
-        <v>126.7558528428094</v>
+        <v>57.83822476735862</v>
       </c>
       <c r="W49" s="7" t="inlineStr"/>
       <c r="X49" s="7" t="inlineStr"/>
@@ -4490,12 +4486,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4510,51 +4506,51 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.2%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>108800</v>
+        <v>53200</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>103200</v>
+        <v>52000</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>108900</v>
+        <v>54600</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>102705</v>
+        <v>51265</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>102745</v>
+        <v>51190</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>82164</v>
+        <v>41012</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>82196</v>
+        <v>40952</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>81100</v>
+        <v>40450</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>34.1553637484587</v>
+        <v>31.5203955500618</v>
       </c>
       <c r="O50" s="7" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr"/>
       <c r="Q50" s="5" t="n">
-        <v>73000</v>
+        <v>36450</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>49.04109589041096</v>
+        <v>45.95336076817559</v>
       </c>
       <c r="S50" s="7" t="inlineStr"/>
       <c r="T50" s="7" t="inlineStr"/>
       <c r="U50" s="5" t="n">
-        <v>65800</v>
+        <v>32850</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>65.34954407294833</v>
+        <v>61.9482496194825</v>
       </c>
       <c r="W50" s="7" t="inlineStr"/>
       <c r="X50" s="7" t="inlineStr"/>
@@ -4570,12 +4566,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4590,51 +4586,51 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.5%</t>
+          <t>1차 매수선까지 30.0%</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>181500</v>
+        <v>49400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>165700</v>
+        <v>48250</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>186500</v>
+        <v>50400</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>181640</v>
+        <v>47672.5</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>179790</v>
+        <v>48040</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>145312</v>
+        <v>38138</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>143832</v>
+        <v>38432</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>142300</v>
+        <v>38000</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>27.5474349964863</v>
+        <v>30</v>
       </c>
       <c r="O51" s="7" t="inlineStr"/>
       <c r="P51" s="7" t="inlineStr"/>
       <c r="Q51" s="5" t="n">
-        <v>128100</v>
+        <v>34250</v>
       </c>
       <c r="R51" s="6" t="n">
-        <v>41.68618266978923</v>
+        <v>44.23357664233576</v>
       </c>
       <c r="S51" s="7" t="inlineStr"/>
       <c r="T51" s="7" t="inlineStr"/>
       <c r="U51" s="5" t="n">
-        <v>115300</v>
+        <v>30850</v>
       </c>
       <c r="V51" s="6" t="n">
-        <v>57.41543798785776</v>
+        <v>60.12965964343599</v>
       </c>
       <c r="W51" s="7" t="inlineStr"/>
       <c r="X51" s="7" t="inlineStr"/>
@@ -4650,12 +4646,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4670,51 +4666,51 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.1%</t>
+          <t>1차 매수선까지 21.3%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>430500</v>
+        <v>22700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>429000</v>
+        <v>22000</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>438500</v>
+        <v>23100</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>434150</v>
+        <v>23712.5</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>434125</v>
+        <v>23595</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>347320</v>
+        <v>18970</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>347300</v>
+        <v>18876</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>344000</v>
+        <v>18720</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>25.1453488372093</v>
+        <v>21.26068376068376</v>
       </c>
       <c r="O52" s="7" t="inlineStr"/>
       <c r="P52" s="7" t="inlineStr"/>
       <c r="Q52" s="5" t="n">
-        <v>310000</v>
+        <v>16850</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>38.87096774193549</v>
+        <v>34.71810089020772</v>
       </c>
       <c r="S52" s="7" t="inlineStr"/>
       <c r="T52" s="7" t="inlineStr"/>
       <c r="U52" s="5" t="n">
-        <v>279500</v>
+        <v>15170</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>54.02504472271914</v>
+        <v>49.63744232036915</v>
       </c>
       <c r="W52" s="7" t="inlineStr"/>
       <c r="X52" s="7" t="inlineStr"/>
@@ -4730,12 +4726,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4750,51 +4746,51 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.5%</t>
+          <t>1차 매수선까지 37.5%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>22500</v>
+        <v>477000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>21350</v>
+        <v>451500</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>23150</v>
+        <v>484000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>22570</v>
+        <v>436325</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>22470</v>
+        <v>440175</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>18056</v>
+        <v>349060</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>17976</v>
+        <v>352140</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>17790</v>
+        <v>347000</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>26.47554806070826</v>
+        <v>37.46397694524496</v>
       </c>
       <c r="O53" s="7" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr"/>
       <c r="Q53" s="5" t="n">
-        <v>16020</v>
+        <v>312500</v>
       </c>
       <c r="R53" s="6" t="n">
-        <v>40.44943820224719</v>
+        <v>52.64</v>
       </c>
       <c r="S53" s="7" t="inlineStr"/>
       <c r="T53" s="7" t="inlineStr"/>
       <c r="U53" s="5" t="n">
-        <v>14420</v>
+        <v>281500</v>
       </c>
       <c r="V53" s="6" t="n">
-        <v>56.03328710124826</v>
+        <v>69.44937833037301</v>
       </c>
       <c r="W53" s="7" t="inlineStr"/>
       <c r="X53" s="7" t="inlineStr"/>
@@ -4810,12 +4806,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4830,51 +4826,51 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.5%</t>
+          <t>1차 매수선까지 40.5%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>22000</v>
+        <v>244000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>21850</v>
+        <v>232000</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>22750</v>
+        <v>246000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>21787</v>
+        <v>218130</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>21807</v>
+        <v>220590</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>17429.6</v>
+        <v>174504</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>17445.6</v>
+        <v>176472</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>17260</v>
+        <v>173700</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>27.46234067207416</v>
+        <v>40.4720782959125</v>
       </c>
       <c r="O54" s="7" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr"/>
       <c r="Q54" s="5" t="n">
-        <v>15540</v>
+        <v>156400</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>41.57014157014157</v>
+        <v>56.01023017902813</v>
       </c>
       <c r="S54" s="7" t="inlineStr"/>
       <c r="T54" s="7" t="inlineStr"/>
       <c r="U54" s="5" t="n">
-        <v>13990</v>
+        <v>140800</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>57.25518227305218</v>
+        <v>73.29545454545455</v>
       </c>
       <c r="W54" s="7" t="inlineStr"/>
       <c r="X54" s="7" t="inlineStr"/>
@@ -4890,12 +4886,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4910,51 +4906,51 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.8%</t>
+          <t>1차 매수선까지 69.9%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>54600</v>
+        <v>2300000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>51800</v>
+        <v>2102000</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>54800</v>
+        <v>2414000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>51260</v>
+        <v>1691500</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>51285</v>
+        <v>1739550</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>41008</v>
+        <v>1353200</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>41028</v>
+        <v>1391640</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>40500</v>
+        <v>1354000</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>34.81481481481482</v>
+        <v>69.86706056129985</v>
       </c>
       <c r="O55" s="7" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr"/>
       <c r="Q55" s="5" t="n">
-        <v>36500</v>
+        <v>1219000</v>
       </c>
       <c r="R55" s="6" t="n">
-        <v>49.58904109589042</v>
+        <v>88.67924528301887</v>
       </c>
       <c r="S55" s="7" t="inlineStr"/>
       <c r="T55" s="7" t="inlineStr"/>
       <c r="U55" s="5" t="n">
-        <v>32900</v>
+        <v>1098000</v>
       </c>
       <c r="V55" s="6" t="n">
-        <v>65.95744680851064</v>
+        <v>109.471766848816</v>
       </c>
       <c r="W55" s="7" t="inlineStr"/>
       <c r="X55" s="7" t="inlineStr"/>
@@ -4970,12 +4966,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4990,51 +4986,51 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.9%</t>
+          <t>1차 매수선까지 36.8%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>51200</v>
+        <v>519000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>49650</v>
+        <v>510000</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>53900</v>
+        <v>534000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>48130</v>
+        <v>480675</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>48445</v>
+        <v>481175</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>38504</v>
+        <v>384540</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>38756</v>
+        <v>384940</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>38250</v>
+        <v>379500</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>33.8562091503268</v>
+        <v>36.75889328063241</v>
       </c>
       <c r="O56" s="7" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr"/>
       <c r="Q56" s="5" t="n">
-        <v>34450</v>
+        <v>342000</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>48.62119013062409</v>
+        <v>51.75438596491229</v>
       </c>
       <c r="S56" s="7" t="inlineStr"/>
       <c r="T56" s="7" t="inlineStr"/>
       <c r="U56" s="5" t="n">
-        <v>31050</v>
+        <v>308000</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>64.89533011272141</v>
+        <v>68.5064935064935</v>
       </c>
       <c r="W56" s="7" t="inlineStr"/>
       <c r="X56" s="7" t="inlineStr"/>
@@ -5050,12 +5046,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -5070,51 +5066,51 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 23.8%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>22550</v>
+        <v>41100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>22400</v>
+        <v>40750</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>23250</v>
+        <v>42000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>23587.5</v>
+        <v>41845</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>23387.5</v>
+        <v>41892.5</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>18870</v>
+        <v>33476</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>18710</v>
+        <v>33514</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>18550</v>
+        <v>33200</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>21.5633423180593</v>
+        <v>23.79518072289157</v>
       </c>
       <c r="O57" s="7" t="inlineStr"/>
       <c r="P57" s="7" t="inlineStr"/>
       <c r="Q57" s="5" t="n">
-        <v>16700</v>
+        <v>29900</v>
       </c>
       <c r="R57" s="6" t="n">
-        <v>35.02994011976048</v>
+        <v>37.45819397993311</v>
       </c>
       <c r="S57" s="7" t="inlineStr"/>
       <c r="T57" s="7" t="inlineStr"/>
       <c r="U57" s="5" t="n">
-        <v>15040</v>
+        <v>26950</v>
       </c>
       <c r="V57" s="6" t="n">
-        <v>49.93351063829788</v>
+        <v>52.50463821892394</v>
       </c>
       <c r="W57" s="7" t="inlineStr"/>
       <c r="X57" s="7" t="inlineStr"/>
@@ -5130,12 +5126,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -5150,51 +5146,51 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.1%</t>
+          <t>1차 매수선까지 17.6%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>483500</v>
+        <v>15900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>474000</v>
+        <v>15540</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>494500</v>
+        <v>16070</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>440500</v>
+        <v>17086.5</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>444150</v>
+        <v>17014.5</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>352400</v>
+        <v>13669.2</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>355320</v>
+        <v>13611.6</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>350000</v>
+        <v>13520</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>38.14285714285715</v>
+        <v>17.60355029585799</v>
       </c>
       <c r="O58" s="7" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr"/>
       <c r="Q58" s="5" t="n">
-        <v>315500</v>
+        <v>12170</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>53.24881141045958</v>
+        <v>30.64913722267872</v>
       </c>
       <c r="S58" s="7" t="inlineStr"/>
       <c r="T58" s="7" t="inlineStr"/>
       <c r="U58" s="5" t="n">
-        <v>284000</v>
+        <v>10960</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>70.24647887323944</v>
+        <v>45.07299270072993</v>
       </c>
       <c r="W58" s="7" t="inlineStr"/>
       <c r="X58" s="7" t="inlineStr"/>
@@ -5210,12 +5206,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -5230,51 +5226,51 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.3%</t>
+          <t>1차 매수선까지 39.9%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>242500</v>
+        <v>100900</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>232500</v>
+        <v>92100</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>257000</v>
+        <v>101400</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>220515</v>
+        <v>91195</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>222415</v>
+        <v>91565</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>176412</v>
+        <v>72956</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>177932</v>
+        <v>73252</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>175300</v>
+        <v>72100</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>38.3342840844267</v>
+        <v>39.94452149791955</v>
       </c>
       <c r="O59" s="7" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr"/>
       <c r="Q59" s="5" t="n">
-        <v>157800</v>
+        <v>64900</v>
       </c>
       <c r="R59" s="6" t="n">
-        <v>53.67553865652725</v>
+        <v>55.46995377503852</v>
       </c>
       <c r="S59" s="7" t="inlineStr"/>
       <c r="T59" s="7" t="inlineStr"/>
       <c r="U59" s="5" t="n">
-        <v>142100</v>
+        <v>58500</v>
       </c>
       <c r="V59" s="6" t="n">
-        <v>70.65446868402533</v>
+        <v>72.47863247863248</v>
       </c>
       <c r="W59" s="7" t="inlineStr"/>
       <c r="X59" s="7" t="inlineStr"/>
@@ -5290,12 +5286,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -5310,51 +5306,51 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 68.1%</t>
+          <t>1차 매수선까지 28.5%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>2346000</v>
+        <v>14680</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>2281000</v>
+        <v>13830</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>2419000</v>
+        <v>14950</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>1741850</v>
+        <v>14425</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>1792050</v>
+        <v>14429.5</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>1393480</v>
+        <v>11540</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>1433640</v>
+        <v>11543.6</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>1396000</v>
+        <v>11420</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>68.05157593123209</v>
+        <v>28.54640980735552</v>
       </c>
       <c r="O60" s="7" t="inlineStr"/>
       <c r="P60" s="7" t="inlineStr"/>
       <c r="Q60" s="5" t="n">
-        <v>1257000</v>
+        <v>10280</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>86.63484486873509</v>
+        <v>42.80155642023346</v>
       </c>
       <c r="S60" s="7" t="inlineStr"/>
       <c r="T60" s="7" t="inlineStr"/>
       <c r="U60" s="5" t="n">
-        <v>1132000</v>
+        <v>9260</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>107.243816254417</v>
+        <v>58.53131749460043</v>
       </c>
       <c r="W60" s="7" t="inlineStr"/>
       <c r="X60" s="7" t="inlineStr"/>
@@ -5370,12 +5366,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5390,51 +5386,51 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.6%</t>
+          <t>1차 매수선까지 20.1%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>531000</v>
+        <v>74100</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>515000</v>
+        <v>73900</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>534000</v>
+        <v>76400</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>481775</v>
+        <v>77930</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>482675</v>
+        <v>77705</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>385420</v>
+        <v>62344</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>386140</v>
+        <v>62164</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>380500</v>
+        <v>61700</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>39.55321944809461</v>
+        <v>20.09724473257699</v>
       </c>
       <c r="O61" s="7" t="inlineStr"/>
       <c r="P61" s="7" t="inlineStr"/>
       <c r="Q61" s="5" t="n">
-        <v>342500</v>
+        <v>55600</v>
       </c>
       <c r="R61" s="6" t="n">
-        <v>55.03649635036496</v>
+        <v>33.27338129496403</v>
       </c>
       <c r="S61" s="7" t="inlineStr"/>
       <c r="T61" s="7" t="inlineStr"/>
       <c r="U61" s="5" t="n">
-        <v>308500</v>
+        <v>50100</v>
       </c>
       <c r="V61" s="6" t="n">
-        <v>72.12317666126418</v>
+        <v>47.90419161676647</v>
       </c>
       <c r="W61" s="7" t="inlineStr"/>
       <c r="X61" s="7" t="inlineStr"/>
@@ -5450,12 +5446,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5470,51 +5466,51 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.6%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>40050</v>
+        <v>257000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>40000</v>
+        <v>250500</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>42100</v>
+        <v>262500</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>41840</v>
+        <v>246825</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>41812.5</v>
+        <v>247225</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>33472</v>
+        <v>197460</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>33450</v>
+        <v>197780</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>33200</v>
+        <v>195400</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>20.63253012048193</v>
+        <v>31.52507676560901</v>
       </c>
       <c r="O62" s="7" t="inlineStr"/>
       <c r="P62" s="7" t="inlineStr"/>
       <c r="Q62" s="5" t="n">
-        <v>29900</v>
+        <v>175900</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>33.94648829431438</v>
+        <v>46.10574189880614</v>
       </c>
       <c r="S62" s="7" t="inlineStr"/>
       <c r="T62" s="7" t="inlineStr"/>
       <c r="U62" s="5" t="n">
-        <v>26950</v>
+        <v>158400</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>48.60853432282003</v>
+        <v>62.24747474747475</v>
       </c>
       <c r="W62" s="7" t="inlineStr"/>
       <c r="X62" s="7" t="inlineStr"/>
@@ -5530,12 +5526,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5550,51 +5546,51 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 15.8%</t>
+          <t>1차 매수선까지 36.5%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>15560</v>
+        <v>115900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>15560</v>
+        <v>113900</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>16060</v>
+        <v>118900</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>16997.5</v>
+        <v>106930</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>16897</v>
+        <v>107640</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>13598</v>
+        <v>85544</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>13517.6</v>
+        <v>86112</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>13440</v>
+        <v>84900</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>15.77380952380952</v>
+        <v>36.51354534746761</v>
       </c>
       <c r="O63" s="7" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr"/>
       <c r="Q63" s="5" t="n">
-        <v>12100</v>
+        <v>76500</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>28.59504132231405</v>
+        <v>51.5032679738562</v>
       </c>
       <c r="S63" s="7" t="inlineStr"/>
       <c r="T63" s="7" t="inlineStr"/>
       <c r="U63" s="5" t="n">
-        <v>10900</v>
+        <v>68900</v>
       </c>
       <c r="V63" s="6" t="n">
-        <v>42.75229357798165</v>
+        <v>68.21480406386067</v>
       </c>
       <c r="W63" s="7" t="inlineStr"/>
       <c r="X63" s="7" t="inlineStr"/>
@@ -5610,12 +5606,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5630,51 +5626,51 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.1%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>103200</v>
+        <v>989000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>97800</v>
+        <v>976000</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>103400</v>
+        <v>1007000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>91680</v>
+        <v>1009350</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>92240</v>
+        <v>1005950</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>73344</v>
+        <v>807480</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>73792</v>
+        <v>804760</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>72600</v>
+        <v>798000</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>42.14876033057851</v>
+        <v>23.93483709273183</v>
       </c>
       <c r="O64" s="7" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr"/>
       <c r="Q64" s="5" t="n">
-        <v>65400</v>
+        <v>719000</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>57.79816513761467</v>
+        <v>37.55215577190543</v>
       </c>
       <c r="S64" s="7" t="inlineStr"/>
       <c r="T64" s="7" t="inlineStr"/>
       <c r="U64" s="5" t="n">
-        <v>58900</v>
+        <v>648000</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>75.21222410865875</v>
+        <v>52.62345679012346</v>
       </c>
       <c r="W64" s="7" t="inlineStr"/>
       <c r="X64" s="7" t="inlineStr"/>
@@ -5690,12 +5686,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5710,51 +5706,51 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.3%</t>
+          <t>1차 매수선까지 29.4%</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>14550</v>
+        <v>30600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>14380</v>
+        <v>29800</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>15030</v>
+        <v>31250</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>14423</v>
+        <v>29765</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>14432</v>
+        <v>29870</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>11538.4</v>
+        <v>23812</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>11545.6</v>
+        <v>23896</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>11430</v>
+        <v>23650</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>27.29658792650919</v>
+        <v>29.38689217758985</v>
       </c>
       <c r="O65" s="7" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr"/>
       <c r="Q65" s="5" t="n">
-        <v>10290</v>
+        <v>21300</v>
       </c>
       <c r="R65" s="6" t="n">
-        <v>41.39941690962099</v>
+        <v>43.66197183098591</v>
       </c>
       <c r="S65" s="7" t="inlineStr"/>
       <c r="T65" s="7" t="inlineStr"/>
       <c r="U65" s="5" t="n">
-        <v>9270</v>
+        <v>19180</v>
       </c>
       <c r="V65" s="6" t="n">
-        <v>56.957928802589</v>
+        <v>59.54118873826904</v>
       </c>
       <c r="W65" s="7" t="inlineStr"/>
       <c r="X65" s="7" t="inlineStr"/>
@@ -5770,12 +5766,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5790,51 +5786,51 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.1%</t>
+          <t>1차 매수선까지 43.4%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>67300</v>
+        <v>242000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>62200</v>
+        <v>223500</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>70600</v>
+        <v>248000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>77365</v>
+        <v>212260</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>76685</v>
+        <v>214465</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>61892</v>
+        <v>169808</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>61348</v>
+        <v>171572</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>61100</v>
+        <v>168700</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>10.14729950900164</v>
+        <v>43.44991108476586</v>
       </c>
       <c r="O66" s="7" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr"/>
       <c r="Q66" s="5" t="n">
-        <v>55000</v>
+        <v>151900</v>
       </c>
       <c r="R66" s="6" t="n">
-        <v>22.36363636363636</v>
+        <v>59.31533903884134</v>
       </c>
       <c r="S66" s="7" t="inlineStr"/>
       <c r="T66" s="7" t="inlineStr"/>
       <c r="U66" s="5" t="n">
-        <v>49550</v>
+        <v>136800</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>35.82240161453078</v>
+        <v>76.90058479532163</v>
       </c>
       <c r="W66" s="7" t="inlineStr"/>
       <c r="X66" s="7" t="inlineStr"/>
@@ -5850,12 +5846,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5870,51 +5866,51 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.6%</t>
+          <t>1차 매수선까지 19.5%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>274000</v>
+        <v>49950</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>256000</v>
+        <v>48850</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>274500</v>
+        <v>51500</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>248075</v>
+        <v>52782.5</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>249250</v>
+        <v>52630</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>198460</v>
+        <v>42226</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>199400</v>
+        <v>42104</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>196300</v>
+        <v>41800</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>39.58227203260316</v>
+        <v>19.49760765550239</v>
       </c>
       <c r="O67" s="7" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr"/>
       <c r="Q67" s="5" t="n">
-        <v>176700</v>
+        <v>37650</v>
       </c>
       <c r="R67" s="6" t="n">
-        <v>55.06508205998868</v>
+        <v>32.66932270916335</v>
       </c>
       <c r="S67" s="7" t="inlineStr"/>
       <c r="T67" s="7" t="inlineStr"/>
       <c r="U67" s="5" t="n">
-        <v>159100</v>
+        <v>33900</v>
       </c>
       <c r="V67" s="6" t="n">
-        <v>72.21873035826523</v>
+        <v>47.34513274336283</v>
       </c>
       <c r="W67" s="7" t="inlineStr"/>
       <c r="X67" s="7" t="inlineStr"/>
@@ -5930,12 +5926,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5950,51 +5946,51 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.3%</t>
+          <t>1차 매수선까지 22.9%</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>119400</v>
+        <v>15250</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>113100</v>
+        <v>15070</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>119600</v>
+        <v>16400</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>107815</v>
+        <v>15643.5</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>108715</v>
+        <v>15649</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>86252</v>
+        <v>12514.8</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>86972</v>
+        <v>12519.2</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>85700</v>
+        <v>12410</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>39.32322053675612</v>
+        <v>22.88477034649476</v>
       </c>
       <c r="O68" s="7" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr"/>
       <c r="Q68" s="5" t="n">
-        <v>77200</v>
+        <v>11170</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>54.66321243523316</v>
+        <v>36.52641002685765</v>
       </c>
       <c r="S68" s="7" t="inlineStr"/>
       <c r="T68" s="7" t="inlineStr"/>
       <c r="U68" s="5" t="n">
-        <v>69500</v>
+        <v>10060</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>71.79856115107913</v>
+        <v>51.59045725646123</v>
       </c>
       <c r="W68" s="7" t="inlineStr"/>
       <c r="X68" s="7" t="inlineStr"/>
@@ -6010,12 +6006,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -6030,51 +6026,51 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.7%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>33550</v>
+        <v>28150</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>30850</v>
+        <v>27700</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>34050</v>
+        <v>28450</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>30017.5</v>
+        <v>29257.5</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>30275</v>
+        <v>29170</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>24014</v>
+        <v>23406</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>24220</v>
+        <v>23336</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>23850</v>
+        <v>23150</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>40.67085953878406</v>
+        <v>21.59827213822894</v>
       </c>
       <c r="O69" s="7" t="inlineStr"/>
       <c r="P69" s="7" t="inlineStr"/>
       <c r="Q69" s="5" t="n">
-        <v>21500</v>
+        <v>20850</v>
       </c>
       <c r="R69" s="6" t="n">
-        <v>56.04651162790698</v>
+        <v>35.01199040767386</v>
       </c>
       <c r="S69" s="7" t="inlineStr"/>
       <c r="T69" s="7" t="inlineStr"/>
       <c r="U69" s="5" t="n">
-        <v>19360</v>
+        <v>18770</v>
       </c>
       <c r="V69" s="6" t="n">
-        <v>73.29545454545455</v>
+        <v>49.97336174746936</v>
       </c>
       <c r="W69" s="7" t="inlineStr"/>
       <c r="X69" s="7" t="inlineStr"/>
@@ -6090,12 +6086,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -6110,51 +6106,51 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.6%</t>
+          <t>1차 매수선까지 25.3%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>243500</v>
+        <v>2415</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>232500</v>
+        <v>2410</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>247000</v>
+        <v>2535</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>214540</v>
+        <v>2433</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>217020</v>
+        <v>2432.5</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>171632</v>
+        <v>1946.4</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>173616</v>
+        <v>1946</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>170800</v>
+        <v>1927</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>42.56440281030444</v>
+        <v>25.32433834976648</v>
       </c>
       <c r="O70" s="7" t="inlineStr"/>
       <c r="P70" s="7" t="inlineStr"/>
       <c r="Q70" s="5" t="n">
-        <v>153800</v>
+        <v>1735</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>58.32249674902471</v>
+        <v>39.19308357348703</v>
       </c>
       <c r="S70" s="7" t="inlineStr"/>
       <c r="T70" s="7" t="inlineStr"/>
       <c r="U70" s="5" t="n">
-        <v>138500</v>
+        <v>1562</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>75.81227436823104</v>
+        <v>54.60947503201024</v>
       </c>
       <c r="W70" s="7" t="inlineStr"/>
       <c r="X70" s="7" t="inlineStr"/>
@@ -6170,12 +6166,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -6190,51 +6186,51 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.7%</t>
+          <t>1차 매수선까지 28.1%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>49850</v>
+        <v>7110</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>48550</v>
+        <v>7030</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>50400</v>
+        <v>7480</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>52625</v>
+        <v>7043</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>52467.5</v>
+        <v>7009</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>42100</v>
+        <v>5634.400000000001</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>41974</v>
+        <v>5607.200000000001</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>41650</v>
+        <v>5550</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>19.68787515006002</v>
+        <v>28.10810810810811</v>
       </c>
       <c r="O71" s="7" t="inlineStr"/>
       <c r="P71" s="7" t="inlineStr"/>
       <c r="Q71" s="5" t="n">
-        <v>37500</v>
+        <v>5000</v>
       </c>
       <c r="R71" s="6" t="n">
-        <v>32.93333333333333</v>
+        <v>42.2</v>
       </c>
       <c r="S71" s="7" t="inlineStr"/>
       <c r="T71" s="7" t="inlineStr"/>
       <c r="U71" s="5" t="n">
-        <v>33800</v>
+        <v>4505</v>
       </c>
       <c r="V71" s="6" t="n">
-        <v>47.48520710059172</v>
+        <v>57.82463928967814</v>
       </c>
       <c r="W71" s="7" t="inlineStr"/>
       <c r="X71" s="7" t="inlineStr"/>
@@ -6250,12 +6246,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -6270,51 +6266,51 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.0%</t>
+          <t>1차 매수선까지 30.8%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>15280</v>
+        <v>146800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>15060</v>
+        <v>140500</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>15370</v>
+        <v>146800</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>15650.5</v>
+        <v>141755</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>15661.5</v>
+        <v>141905</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>12520.4</v>
+        <v>113404</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>12529.2</v>
+        <v>113524</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>12420</v>
+        <v>112200</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>23.02737520128824</v>
+        <v>30.83778966131907</v>
       </c>
       <c r="O72" s="7" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr"/>
       <c r="Q72" s="5" t="n">
-        <v>11180</v>
+        <v>101000</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>36.67262969588551</v>
+        <v>45.34653465346535</v>
       </c>
       <c r="S72" s="7" t="inlineStr"/>
       <c r="T72" s="7" t="inlineStr"/>
       <c r="U72" s="5" t="n">
-        <v>10070</v>
+        <v>91000</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>51.73783515392254</v>
+        <v>61.31868131868132</v>
       </c>
       <c r="W72" s="7" t="inlineStr"/>
       <c r="X72" s="7" t="inlineStr"/>
@@ -6330,12 +6326,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -6350,51 +6346,51 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.1%</t>
+          <t>1차 매수선까지 18.1%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>28200</v>
+        <v>35300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>27800</v>
+        <v>35000</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>28950</v>
+        <v>36000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>29172.5</v>
+        <v>38007.5</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>29100</v>
+        <v>37600</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>23338</v>
+        <v>30406</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>23280</v>
+        <v>30080</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>23100</v>
+        <v>29900</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>22.07792207792208</v>
+        <v>18.06020066889632</v>
       </c>
       <c r="O73" s="7" t="inlineStr"/>
       <c r="P73" s="7" t="inlineStr"/>
       <c r="Q73" s="5" t="n">
-        <v>20800</v>
+        <v>26950</v>
       </c>
       <c r="R73" s="6" t="n">
-        <v>35.57692307692308</v>
+        <v>30.98330241187384</v>
       </c>
       <c r="S73" s="7" t="inlineStr"/>
       <c r="T73" s="7" t="inlineStr"/>
       <c r="U73" s="5" t="n">
-        <v>18730</v>
+        <v>24300</v>
       </c>
       <c r="V73" s="6" t="n">
-        <v>50.56059797116925</v>
+        <v>45.26748971193415</v>
       </c>
       <c r="W73" s="7" t="inlineStr"/>
       <c r="X73" s="7" t="inlineStr"/>
@@ -6410,12 +6406,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -6430,51 +6426,51 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.0%</t>
+          <t>1차 매수선까지 13.7%</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>2330</v>
+        <v>8730</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2320</v>
+        <v>8570</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>2425</v>
+        <v>8910</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>2428.25</v>
+        <v>9764</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2426.05</v>
+        <v>9646</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>1942.6</v>
+        <v>7811.200000000001</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>1940.84</v>
+        <v>7716.8</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>1925</v>
+        <v>7680</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>21.03896103896104</v>
+        <v>13.671875</v>
       </c>
       <c r="O74" s="7" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr"/>
       <c r="Q74" s="5" t="n">
-        <v>1733</v>
+        <v>6920</v>
       </c>
       <c r="R74" s="6" t="n">
-        <v>34.44893248701673</v>
+        <v>26.15606936416185</v>
       </c>
       <c r="S74" s="7" t="inlineStr"/>
       <c r="T74" s="7" t="inlineStr"/>
       <c r="U74" s="5" t="n">
-        <v>1560</v>
+        <v>6230</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>49.35897435897436</v>
+        <v>40.12841091492777</v>
       </c>
       <c r="W74" s="7" t="inlineStr"/>
       <c r="X74" s="7" t="inlineStr"/>
@@ -6490,12 +6486,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6510,51 +6506,51 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 29.0%</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>6840</v>
+        <v>260000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>6760</v>
+        <v>251500</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>7500</v>
+        <v>283500</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>6995.5</v>
+        <v>251340</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>6962.5</v>
+        <v>254450</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>5596.400000000001</v>
+        <v>201072</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>5570</v>
+        <v>203560</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>5520</v>
+        <v>201500</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>23.91304347826087</v>
+        <v>29.03225806451613</v>
       </c>
       <c r="O75" s="7" t="inlineStr"/>
       <c r="P75" s="7" t="inlineStr"/>
       <c r="Q75" s="5" t="n">
-        <v>4970</v>
+        <v>181400</v>
       </c>
       <c r="R75" s="6" t="n">
-        <v>37.62575452716298</v>
+        <v>43.32965821389195</v>
       </c>
       <c r="S75" s="7" t="inlineStr"/>
       <c r="T75" s="7" t="inlineStr"/>
       <c r="U75" s="5" t="n">
-        <v>4475</v>
+        <v>163300</v>
       </c>
       <c r="V75" s="6" t="n">
-        <v>52.84916201117319</v>
+        <v>59.21616656460502</v>
       </c>
       <c r="W75" s="7" t="inlineStr"/>
       <c r="X75" s="7" t="inlineStr"/>
@@ -6570,12 +6566,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6590,51 +6586,51 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.3%</t>
+          <t>1차 매수선까지 32.6%</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>149000</v>
+        <v>311500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>143600</v>
+        <v>310000</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>149000</v>
+        <v>318500</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>142015</v>
+        <v>295400</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>142475</v>
+        <v>297025</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>113612</v>
+        <v>236320</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>113980</v>
+        <v>237620</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>112600</v>
+        <v>235000</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>32.32682060390763</v>
+        <v>32.5531914893617</v>
       </c>
       <c r="O76" s="7" t="inlineStr"/>
       <c r="P76" s="7" t="inlineStr"/>
       <c r="Q76" s="5" t="n">
-        <v>101400</v>
+        <v>212000</v>
       </c>
       <c r="R76" s="6" t="n">
-        <v>46.94280078895464</v>
+        <v>46.93396226415094</v>
       </c>
       <c r="S76" s="7" t="inlineStr"/>
       <c r="T76" s="7" t="inlineStr"/>
       <c r="U76" s="5" t="n">
-        <v>91300</v>
+        <v>190900</v>
       </c>
       <c r="V76" s="6" t="n">
-        <v>63.19824753559693</v>
+        <v>63.17443687794657</v>
       </c>
       <c r="W76" s="7" t="inlineStr"/>
       <c r="X76" s="7" t="inlineStr"/>
@@ -6650,12 +6646,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -6670,51 +6666,51 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.2%</t>
+          <t>1차 매수선까지 26.1%</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>35050</v>
+        <v>100000</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>34750</v>
+        <v>98900</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>35950</v>
+        <v>104400</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>37587.5</v>
+        <v>99740</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>37320</v>
+        <v>100085</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>30070</v>
+        <v>79792</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>29856</v>
+        <v>80068</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>29650</v>
+        <v>79300</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>18.21247892074199</v>
+        <v>26.10340479192938</v>
       </c>
       <c r="O77" s="7" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr"/>
       <c r="Q77" s="5" t="n">
-        <v>26700</v>
+        <v>71400</v>
       </c>
       <c r="R77" s="6" t="n">
-        <v>31.27340823970037</v>
+        <v>40.05602240896359</v>
       </c>
       <c r="S77" s="7" t="inlineStr"/>
       <c r="T77" s="7" t="inlineStr"/>
       <c r="U77" s="5" t="n">
-        <v>24050</v>
+        <v>64300</v>
       </c>
       <c r="V77" s="6" t="n">
-        <v>45.73804573804574</v>
+        <v>55.52099533437014</v>
       </c>
       <c r="W77" s="7" t="inlineStr"/>
       <c r="X77" s="7" t="inlineStr"/>
@@ -6730,12 +6726,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -6750,51 +6746,51 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.1%</t>
+          <t>1차 매수선까지 34.4%</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>9040</v>
+        <v>96400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>8740</v>
+        <v>94500</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>9360</v>
+        <v>97900</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>9661.5</v>
+        <v>90180</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>9552.5</v>
+        <v>90825</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>7729.200000000001</v>
+        <v>72144</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>7642</v>
+        <v>72660</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>7590</v>
+        <v>71700</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>19.10408432147563</v>
+        <v>34.44909344490934</v>
       </c>
       <c r="O78" s="7" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr"/>
       <c r="Q78" s="5" t="n">
-        <v>6840</v>
+        <v>64600</v>
       </c>
       <c r="R78" s="6" t="n">
-        <v>32.16374269005848</v>
+        <v>49.22600619195047</v>
       </c>
       <c r="S78" s="7" t="inlineStr"/>
       <c r="T78" s="7" t="inlineStr"/>
       <c r="U78" s="5" t="n">
-        <v>6160</v>
+        <v>58200</v>
       </c>
       <c r="V78" s="6" t="n">
-        <v>46.75324675324675</v>
+        <v>65.63573883161511</v>
       </c>
       <c r="W78" s="7" t="inlineStr"/>
       <c r="X78" s="7" t="inlineStr"/>
@@ -6810,12 +6806,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6830,51 +6826,51 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.8%</t>
+          <t>1차 매수선까지 36.7%</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>282500</v>
+        <v>249000</v>
       </c>
       <c r="G79" s="5" t="n">
+        <v>243000</v>
+      </c>
+      <c r="H79" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="H79" s="5" t="n">
-        <v>285500</v>
-      </c>
       <c r="I79" s="5" t="n">
-        <v>255575</v>
+        <v>229025</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>259650</v>
+        <v>231025</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>204460</v>
+        <v>183220</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>207720</v>
+        <v>184820</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>205000</v>
+        <v>182200</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>37.80487804878049</v>
+        <v>36.66300768386389</v>
       </c>
       <c r="O79" s="7" t="inlineStr"/>
       <c r="P79" s="7" t="inlineStr"/>
       <c r="Q79" s="5" t="n">
-        <v>184600</v>
+        <v>164000</v>
       </c>
       <c r="R79" s="6" t="n">
-        <v>53.03358613217768</v>
+        <v>51.82926829268293</v>
       </c>
       <c r="S79" s="7" t="inlineStr"/>
       <c r="T79" s="7" t="inlineStr"/>
       <c r="U79" s="5" t="n">
-        <v>166200</v>
+        <v>147700</v>
       </c>
       <c r="V79" s="6" t="n">
-        <v>69.97593261131168</v>
+        <v>68.58496953283684</v>
       </c>
       <c r="W79" s="7" t="inlineStr"/>
       <c r="X79" s="7" t="inlineStr"/>
@@ -6890,12 +6886,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -6910,51 +6906,51 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.4%</t>
+          <t>1차 매수선까지 38.2%</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>315500</v>
+        <v>129600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>306000</v>
+        <v>128500</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>315500</v>
+        <v>137200</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>297225</v>
+        <v>117585</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>299175</v>
+        <v>118980</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>237780</v>
+        <v>94068</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>239340</v>
+        <v>95184</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>236500</v>
+        <v>93800</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>33.40380549682875</v>
+        <v>38.16631130063966</v>
       </c>
       <c r="O80" s="7" t="inlineStr"/>
       <c r="P80" s="7" t="inlineStr"/>
       <c r="Q80" s="5" t="n">
-        <v>213000</v>
+        <v>84500</v>
       </c>
       <c r="R80" s="6" t="n">
-        <v>48.12206572769953</v>
+        <v>53.37278106508876</v>
       </c>
       <c r="S80" s="7" t="inlineStr"/>
       <c r="T80" s="7" t="inlineStr"/>
       <c r="U80" s="5" t="n">
-        <v>191800</v>
+        <v>76100</v>
       </c>
       <c r="V80" s="6" t="n">
-        <v>64.49426485922837</v>
+        <v>70.30223390275953</v>
       </c>
       <c r="W80" s="7" t="inlineStr"/>
       <c r="X80" s="7" t="inlineStr"/>
@@ -6966,428 +6962,6 @@
       <c r="AD80" s="7" t="inlineStr"/>
       <c r="AE80" s="7" t="inlineStr"/>
       <c r="AF80" s="7" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>267270</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>HD현대건설기계</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>WATCHING</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>1차 매수선까지 25.4%</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>99800</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>97500</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>100800</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>100075</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>100420</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>80060</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>80336</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>79600</v>
-      </c>
-      <c r="N81" s="6" t="n">
-        <v>25.37688442211055</v>
-      </c>
-      <c r="O81" s="7" t="inlineStr"/>
-      <c r="P81" s="7" t="inlineStr"/>
-      <c r="Q81" s="5" t="n">
-        <v>71700</v>
-      </c>
-      <c r="R81" s="6" t="n">
-        <v>39.1910739191074</v>
-      </c>
-      <c r="S81" s="7" t="inlineStr"/>
-      <c r="T81" s="7" t="inlineStr"/>
-      <c r="U81" s="5" t="n">
-        <v>64600</v>
-      </c>
-      <c r="V81" s="6" t="n">
-        <v>54.4891640866873</v>
-      </c>
-      <c r="W81" s="7" t="inlineStr"/>
-      <c r="X81" s="7" t="inlineStr"/>
-      <c r="Y81" s="7" t="inlineStr"/>
-      <c r="Z81" s="7" t="inlineStr"/>
-      <c r="AA81" s="7" t="inlineStr"/>
-      <c r="AB81" s="7" t="inlineStr"/>
-      <c r="AC81" s="7" t="inlineStr"/>
-      <c r="AD81" s="7" t="inlineStr"/>
-      <c r="AE81" s="7" t="inlineStr"/>
-      <c r="AF81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>000880</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>한화</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>WATCHING</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>1차 매수선까지 35.7%</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>98100</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>95600</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>99700</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>90910</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>91575</v>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>72728</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>73260</v>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v>72300</v>
-      </c>
-      <c r="N82" s="6" t="n">
-        <v>35.68464730290457</v>
-      </c>
-      <c r="O82" s="7" t="inlineStr"/>
-      <c r="P82" s="7" t="inlineStr"/>
-      <c r="Q82" s="5" t="n">
-        <v>65100</v>
-      </c>
-      <c r="R82" s="6" t="n">
-        <v>50.69124423963134</v>
-      </c>
-      <c r="S82" s="7" t="inlineStr"/>
-      <c r="T82" s="7" t="inlineStr"/>
-      <c r="U82" s="5" t="n">
-        <v>58600</v>
-      </c>
-      <c r="V82" s="6" t="n">
-        <v>67.4061433447099</v>
-      </c>
-      <c r="W82" s="7" t="inlineStr"/>
-      <c r="X82" s="7" t="inlineStr"/>
-      <c r="Y82" s="7" t="inlineStr"/>
-      <c r="Z82" s="7" t="inlineStr"/>
-      <c r="AA82" s="7" t="inlineStr"/>
-      <c r="AB82" s="7" t="inlineStr"/>
-      <c r="AC82" s="7" t="inlineStr"/>
-      <c r="AD82" s="7" t="inlineStr"/>
-      <c r="AE82" s="7" t="inlineStr"/>
-      <c r="AF82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>034730</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>WATCHING</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>1차 매수선까지 37.8%</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>253500</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>244500</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>257000</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>231250</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>233400</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>185000</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>186720</v>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v>184000</v>
-      </c>
-      <c r="N83" s="6" t="n">
-        <v>37.77173913043478</v>
-      </c>
-      <c r="O83" s="7" t="inlineStr"/>
-      <c r="P83" s="7" t="inlineStr"/>
-      <c r="Q83" s="5" t="n">
-        <v>165700</v>
-      </c>
-      <c r="R83" s="6" t="n">
-        <v>52.98732649366325</v>
-      </c>
-      <c r="S83" s="7" t="inlineStr"/>
-      <c r="T83" s="7" t="inlineStr"/>
-      <c r="U83" s="5" t="n">
-        <v>149200</v>
-      </c>
-      <c r="V83" s="6" t="n">
-        <v>69.90616621983914</v>
-      </c>
-      <c r="W83" s="7" t="inlineStr"/>
-      <c r="X83" s="7" t="inlineStr"/>
-      <c r="Y83" s="7" t="inlineStr"/>
-      <c r="Z83" s="7" t="inlineStr"/>
-      <c r="AA83" s="7" t="inlineStr"/>
-      <c r="AB83" s="7" t="inlineStr"/>
-      <c r="AC83" s="7" t="inlineStr"/>
-      <c r="AD83" s="7" t="inlineStr"/>
-      <c r="AE83" s="7" t="inlineStr"/>
-      <c r="AF83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>096770</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>WATCHING</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>1차 매수선까지 34.7%</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>127800</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>124800</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>132300</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>118890</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>120265</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>95112</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>96212</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>94900</v>
-      </c>
-      <c r="N84" s="6" t="n">
-        <v>34.66807165437302</v>
-      </c>
-      <c r="O84" s="7" t="inlineStr"/>
-      <c r="P84" s="7" t="inlineStr"/>
-      <c r="Q84" s="5" t="n">
-        <v>85500</v>
-      </c>
-      <c r="R84" s="6" t="n">
-        <v>49.47368421052632</v>
-      </c>
-      <c r="S84" s="7" t="inlineStr"/>
-      <c r="T84" s="7" t="inlineStr"/>
-      <c r="U84" s="5" t="n">
-        <v>77000</v>
-      </c>
-      <c r="V84" s="6" t="n">
-        <v>65.97402597402598</v>
-      </c>
-      <c r="W84" s="7" t="inlineStr"/>
-      <c r="X84" s="7" t="inlineStr"/>
-      <c r="Y84" s="7" t="inlineStr"/>
-      <c r="Z84" s="7" t="inlineStr"/>
-      <c r="AA84" s="7" t="inlineStr"/>
-      <c r="AB84" s="7" t="inlineStr"/>
-      <c r="AC84" s="7" t="inlineStr"/>
-      <c r="AD84" s="7" t="inlineStr"/>
-      <c r="AE84" s="7" t="inlineStr"/>
-      <c r="AF84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>025980</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>아난티</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>BOUGHT_1</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>READY_SELL1</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>+3% 매도선까지 1.9%</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>7400</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>7290</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>7780</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>9230</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>9148.5</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>7384</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>7318.8</v>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v>7320</v>
-      </c>
-      <c r="N85" s="6" t="n">
-        <v>1.092896174863388</v>
-      </c>
-      <c r="O85" s="8" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="P85" s="5" t="n">
-        <v>7320</v>
-      </c>
-      <c r="Q85" s="5" t="n">
-        <v>6590</v>
-      </c>
-      <c r="R85" s="6" t="n">
-        <v>12.29135053110774</v>
-      </c>
-      <c r="S85" s="7" t="inlineStr"/>
-      <c r="T85" s="7" t="inlineStr"/>
-      <c r="U85" s="5" t="n">
-        <v>5940</v>
-      </c>
-      <c r="V85" s="6" t="n">
-        <v>24.57912457912458</v>
-      </c>
-      <c r="W85" s="7" t="inlineStr"/>
-      <c r="X85" s="7" t="inlineStr"/>
-      <c r="Y85" s="5" t="n">
-        <v>7320</v>
-      </c>
-      <c r="Z85" s="5" t="n">
-        <v>7539.6</v>
-      </c>
-      <c r="AA85" s="6" t="n">
-        <v>-1.851557111783123</v>
-      </c>
-      <c r="AB85" s="5" t="n">
-        <v>7686</v>
-      </c>
-      <c r="AC85" s="6" t="n">
-        <v>-3.721051262034868</v>
-      </c>
-      <c r="AD85" s="5" t="n">
-        <v>7832.400000000001</v>
-      </c>
-      <c r="AE85" s="6" t="n">
-        <v>-5.520657780501513</v>
-      </c>
-      <c r="AF85" s="5" t="n">
-        <v>7780</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/trading_signals.xlsx
+++ b/output/trading_signals.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -79,6 +80,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF80"/>
+  <dimension ref="A1:AF86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,51 +670,51 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.8%</t>
+          <t>1차 매수선까지 27.3%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>107700</v>
+        <v>100300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>101500</v>
+        <v>96700</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>109200</v>
+        <v>103800</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>95910</v>
+        <v>98960</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>97070</v>
+        <v>99510</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>76728</v>
+        <v>79168</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>77656</v>
+        <v>79608</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>76500</v>
+        <v>78800</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>40.78431372549019</v>
+        <v>27.28426395939086</v>
       </c>
       <c r="O2" s="7" t="inlineStr"/>
       <c r="P2" s="7" t="inlineStr"/>
       <c r="Q2" s="5" t="n">
-        <v>68900</v>
+        <v>71000</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>56.31349782293179</v>
+        <v>41.26760563380282</v>
       </c>
       <c r="S2" s="7" t="inlineStr"/>
       <c r="T2" s="7" t="inlineStr"/>
       <c r="U2" s="5" t="n">
-        <v>62100</v>
+        <v>64000</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>73.42995169082126</v>
+        <v>56.71874999999999</v>
       </c>
       <c r="W2" s="7" t="inlineStr"/>
       <c r="X2" s="7" t="inlineStr"/>
@@ -746,51 +750,51 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.7%</t>
+          <t>1차 매수선까지 45.0%</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>560000</v>
+        <v>580000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>552000</v>
+        <v>532000</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>568000</v>
+        <v>588000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>463025</v>
+        <v>499575</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>473475</v>
+        <v>508700</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>370420</v>
+        <v>399660</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>378780</v>
+        <v>406960</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>371500</v>
+        <v>400000</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>50.74024226110363</v>
+        <v>45</v>
       </c>
       <c r="O3" s="7" t="inlineStr"/>
       <c r="P3" s="7" t="inlineStr"/>
       <c r="Q3" s="5" t="n">
-        <v>334500</v>
+        <v>360500</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>67.41405082212258</v>
+        <v>60.88765603328709</v>
       </c>
       <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="7" t="inlineStr"/>
       <c r="U3" s="5" t="n">
-        <v>301500</v>
+        <v>324500</v>
       </c>
       <c r="V3" s="6" t="n">
-        <v>85.7379767827529</v>
+        <v>78.73651771956857</v>
       </c>
       <c r="W3" s="7" t="inlineStr"/>
       <c r="X3" s="7" t="inlineStr"/>
@@ -826,51 +830,51 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 41.4%</t>
+          <t>1차 매수선까지 23.9%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>88800</v>
+        <v>81300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>88200</v>
+        <v>79200</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>91500</v>
+        <v>88000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>78450</v>
+        <v>81940</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>79730</v>
+        <v>82755</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>62760</v>
+        <v>65552</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>63784</v>
+        <v>66204</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>62800</v>
+        <v>65600</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>41.40127388535032</v>
+        <v>23.93292682926829</v>
       </c>
       <c r="O4" s="7" t="inlineStr"/>
       <c r="P4" s="7" t="inlineStr"/>
       <c r="Q4" s="5" t="n">
-        <v>56600</v>
+        <v>59100</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>56.8904593639576</v>
+        <v>37.56345177664975</v>
       </c>
       <c r="S4" s="7" t="inlineStr"/>
       <c r="T4" s="7" t="inlineStr"/>
       <c r="U4" s="5" t="n">
-        <v>51000</v>
+        <v>53200</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>74.11764705882354</v>
+        <v>52.81954887218046</v>
       </c>
       <c r="W4" s="7" t="inlineStr"/>
       <c r="X4" s="7" t="inlineStr"/>
@@ -906,51 +910,51 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.3%</t>
+          <t>1차 매수선까지 27.8%</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>137600</v>
+        <v>126400</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>133700</v>
+        <v>120000</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>141600</v>
+        <v>136000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>120490</v>
+        <v>124170</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>122010</v>
+        <v>124940</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>96392</v>
+        <v>99336</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>97608</v>
+        <v>99952</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>96000</v>
+        <v>98900</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>43.33333333333334</v>
+        <v>27.80586450960566</v>
       </c>
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="5" t="n">
-        <v>86500</v>
+        <v>89100</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>59.07514450867052</v>
+        <v>41.86307519640853</v>
       </c>
       <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="7" t="inlineStr"/>
       <c r="U5" s="5" t="n">
-        <v>77900</v>
+        <v>80200</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>76.6367137355584</v>
+        <v>57.60598503740648</v>
       </c>
       <c r="W5" s="7" t="inlineStr"/>
       <c r="X5" s="7" t="inlineStr"/>
@@ -986,51 +990,51 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.6%</t>
+          <t>1차 매수선까지 34.1%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>270500</v>
+        <v>275500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>255500</v>
+        <v>256500</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>273500</v>
+        <v>280000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>258250</v>
+        <v>258950</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>257925</v>
+        <v>260050</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>206600</v>
+        <v>207160</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>206340</v>
+        <v>208040</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>204000</v>
+        <v>205500</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>32.59803921568628</v>
+        <v>34.0632603406326</v>
       </c>
       <c r="O6" s="7" t="inlineStr"/>
       <c r="P6" s="7" t="inlineStr"/>
       <c r="Q6" s="5" t="n">
-        <v>183700</v>
+        <v>185000</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>47.2509526401742</v>
+        <v>48.91891891891892</v>
       </c>
       <c r="S6" s="7" t="inlineStr"/>
       <c r="T6" s="7" t="inlineStr"/>
       <c r="U6" s="5" t="n">
-        <v>165400</v>
+        <v>166600</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>63.54292623941959</v>
+        <v>65.36614645858343</v>
       </c>
       <c r="W6" s="7" t="inlineStr"/>
       <c r="X6" s="7" t="inlineStr"/>
@@ -1066,51 +1070,51 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.0%</t>
+          <t>1차 매수선까지 46.2%</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>323500</v>
+        <v>321000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>315500</v>
+        <v>310000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>329000</v>
+        <v>333500</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>253975</v>
+        <v>273575</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>259825</v>
+        <v>279200</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>203180</v>
+        <v>218860</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>207860</v>
+        <v>223360</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>203500</v>
+        <v>219500</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>58.96805896805897</v>
+        <v>46.24145785876993</v>
       </c>
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="5" t="n">
-        <v>183200</v>
+        <v>197600</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>76.58296943231441</v>
+        <v>62.44939271255061</v>
       </c>
       <c r="S7" s="7" t="inlineStr"/>
       <c r="T7" s="7" t="inlineStr"/>
       <c r="U7" s="5" t="n">
-        <v>164900</v>
+        <v>177900</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>96.17950272892662</v>
+        <v>80.43844856661046</v>
       </c>
       <c r="W7" s="7" t="inlineStr"/>
       <c r="X7" s="7" t="inlineStr"/>
@@ -1146,51 +1150,51 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 48.8%</t>
+          <t>1차 매수선까지 34.0%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>288000</v>
+        <v>270000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>267000</v>
+        <v>259000</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>294000</v>
+        <v>275000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>242925</v>
+        <v>252350</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>246550</v>
+        <v>254850</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>194340</v>
+        <v>201880</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>197240</v>
+        <v>203880</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>193500</v>
+        <v>201500</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>48.83720930232558</v>
+        <v>33.99503722084367</v>
       </c>
       <c r="O8" s="7" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr"/>
       <c r="Q8" s="5" t="n">
-        <v>174200</v>
+        <v>181400</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>65.32721010332951</v>
+        <v>48.84233737596472</v>
       </c>
       <c r="S8" s="7" t="inlineStr"/>
       <c r="T8" s="7" t="inlineStr"/>
       <c r="U8" s="5" t="n">
-        <v>156800</v>
+        <v>163300</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>83.67346938775511</v>
+        <v>65.3398652786283</v>
       </c>
       <c r="W8" s="7" t="inlineStr"/>
       <c r="X8" s="7" t="inlineStr"/>
@@ -1206,12 +1210,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>086520</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1226,51 +1230,51 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.5%</t>
+          <t>1차 매수선까지 50.2%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>141500</v>
+        <v>92800</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>138900</v>
+        <v>87300</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>144800</v>
+        <v>96300</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>132670</v>
+        <v>76490</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>135140</v>
+        <v>78745</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>106136</v>
+        <v>61192</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>108112</v>
+        <v>62996</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>106800</v>
+        <v>61800</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>32.49063670411985</v>
+        <v>50.16181229773463</v>
       </c>
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="5" t="n">
-        <v>96200</v>
+        <v>55700</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>47.08939708939709</v>
+        <v>66.6068222621185</v>
       </c>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="inlineStr"/>
       <c r="U9" s="5" t="n">
-        <v>86600</v>
+        <v>50200</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>63.39491916859122</v>
+        <v>84.86055776892431</v>
       </c>
       <c r="W9" s="7" t="inlineStr"/>
       <c r="X9" s="7" t="inlineStr"/>
@@ -1286,12 +1290,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>086520</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1306,51 +1310,51 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.8%</t>
+          <t>1차 매수선까지 19.2%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>89900</v>
+        <v>133100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>85500</v>
+        <v>125900</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>92300</v>
+        <v>136100</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>69475</v>
+        <v>139045</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>71557.5</v>
+        <v>140685</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>55580</v>
+        <v>111236</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>57246</v>
+        <v>112548</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>55900</v>
+        <v>111700</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>60.82289803220036</v>
+        <v>19.15846016114592</v>
       </c>
       <c r="O10" s="7" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr"/>
       <c r="Q10" s="5" t="n">
-        <v>50400</v>
+        <v>100600</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>78.37301587301587</v>
+        <v>32.30616302186879</v>
       </c>
       <c r="S10" s="7" t="inlineStr"/>
       <c r="T10" s="7" t="inlineStr"/>
       <c r="U10" s="5" t="n">
-        <v>45400</v>
+        <v>90600</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>98.01762114537445</v>
+        <v>46.90949227373068</v>
       </c>
       <c r="W10" s="7" t="inlineStr"/>
       <c r="X10" s="7" t="inlineStr"/>
@@ -1386,51 +1390,51 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 51.7%</t>
+          <t>1차 매수선까지 34.9%</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>29600</v>
+        <v>27450</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>29100</v>
+        <v>26500</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>30300</v>
+        <v>28450</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>24470</v>
+        <v>25467.5</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>24882.5</v>
+        <v>25745</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>19576</v>
+        <v>20374</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>19906</v>
+        <v>20596</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>19510</v>
+        <v>20350</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>51.71706817016914</v>
+        <v>34.88943488943489</v>
       </c>
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="5" t="n">
-        <v>17560</v>
+        <v>18320</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>68.56492027334852</v>
+        <v>49.83624454148472</v>
       </c>
       <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="7" t="inlineStr"/>
       <c r="U11" s="5" t="n">
-        <v>15810</v>
+        <v>16490</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>87.22327640733712</v>
+        <v>66.46452395391145</v>
       </c>
       <c r="W11" s="7" t="inlineStr"/>
       <c r="X11" s="7" t="inlineStr"/>
@@ -1466,51 +1470,51 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 35.5%</t>
+          <t>1차 매수선까지 28.4%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>65500</v>
+        <v>62700</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>62800</v>
+        <v>60500</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>66300</v>
+        <v>65600</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>61040</v>
+        <v>61585</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>61275</v>
+        <v>61715</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>48832</v>
+        <v>49268</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>49020</v>
+        <v>49372</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>48350</v>
+        <v>48850</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>35.47052740434333</v>
+        <v>28.35209825997953</v>
       </c>
       <c r="O12" s="7" t="inlineStr"/>
       <c r="P12" s="7" t="inlineStr"/>
       <c r="Q12" s="5" t="n">
-        <v>43550</v>
+        <v>44000</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>50.40183696900115</v>
+        <v>42.5</v>
       </c>
       <c r="S12" s="7" t="inlineStr"/>
       <c r="T12" s="7" t="inlineStr"/>
       <c r="U12" s="5" t="n">
-        <v>39200</v>
+        <v>39650</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>67.09183673469387</v>
+        <v>58.13366960907944</v>
       </c>
       <c r="W12" s="7" t="inlineStr"/>
       <c r="X12" s="7" t="inlineStr"/>
@@ -1546,51 +1550,51 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 42.8%</t>
+          <t>1차 매수선까지 32.1%</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>218000</v>
+        <v>213500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>212500</v>
+        <v>203000</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>223500</v>
+        <v>218750</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>190435</v>
+        <v>201250</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>194050</v>
+        <v>204545</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>152348</v>
+        <v>161000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>155240</v>
+        <v>163636</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>152700</v>
+        <v>161600</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>42.76358873608383</v>
+        <v>32.11633663366337</v>
       </c>
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="5" t="n">
-        <v>137500</v>
+        <v>145500</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>58.54545454545455</v>
+        <v>46.73539518900343</v>
       </c>
       <c r="S13" s="7" t="inlineStr"/>
       <c r="T13" s="7" t="inlineStr"/>
       <c r="U13" s="5" t="n">
-        <v>123800</v>
+        <v>131000</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>76.09046849757674</v>
+        <v>62.97709923664122</v>
       </c>
       <c r="W13" s="7" t="inlineStr"/>
       <c r="X13" s="7" t="inlineStr"/>
@@ -1626,51 +1630,51 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.1%</t>
+          <t>1차 매수선까지 29.9%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>162200</v>
+        <v>158300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>157600</v>
+        <v>150500</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>164500</v>
+        <v>161900</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>144660</v>
+        <v>151960</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>146980</v>
+        <v>154085</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>115728</v>
+        <v>121568</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>117584</v>
+        <v>123268</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>115800</v>
+        <v>121900</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>40.06908462867012</v>
+        <v>29.86054142739951</v>
       </c>
       <c r="O14" s="7" t="inlineStr"/>
       <c r="P14" s="7" t="inlineStr"/>
       <c r="Q14" s="5" t="n">
-        <v>104300</v>
+        <v>109800</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>55.51294343240652</v>
+        <v>44.17122040072859</v>
       </c>
       <c r="S14" s="7" t="inlineStr"/>
       <c r="T14" s="7" t="inlineStr"/>
       <c r="U14" s="5" t="n">
-        <v>93900</v>
+        <v>98900</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>72.73695420660276</v>
+        <v>60.06066734074823</v>
       </c>
       <c r="W14" s="7" t="inlineStr"/>
       <c r="X14" s="7" t="inlineStr"/>
@@ -1686,12 +1690,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1706,51 +1710,51 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.9%</t>
+          <t>1차 매수선까지 53.7%</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>473500</v>
+        <v>446500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>469500</v>
+        <v>431000</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>491500</v>
+        <v>494000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>423625</v>
+        <v>363675</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>429700</v>
+        <v>370625</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>338900</v>
+        <v>290940</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>343760</v>
+        <v>296500</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>338500</v>
+        <v>290500</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>39.88183161004431</v>
+        <v>53.70051635111876</v>
       </c>
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="5" t="n">
-        <v>305000</v>
+        <v>261500</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>55.24590163934426</v>
+        <v>70.74569789674953</v>
       </c>
       <c r="S15" s="7" t="inlineStr"/>
       <c r="T15" s="7" t="inlineStr"/>
       <c r="U15" s="5" t="n">
-        <v>275000</v>
+        <v>235500</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>72.18181818181819</v>
+        <v>89.59660297239915</v>
       </c>
       <c r="W15" s="7" t="inlineStr"/>
       <c r="X15" s="7" t="inlineStr"/>
@@ -1766,12 +1770,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1786,51 +1790,51 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.7%</t>
+          <t>1차 매수선까지 42.0%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>84400</v>
+        <v>526000</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>82100</v>
+        <v>511000</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>84900</v>
+        <v>557000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>75265</v>
+        <v>467975</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>76160</v>
+        <v>470725</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>60212</v>
+        <v>374380</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>60928</v>
+        <v>376580</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>60000</v>
+        <v>370500</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>40.66666666666666</v>
+        <v>41.97031039136302</v>
       </c>
       <c r="O16" s="7" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr"/>
       <c r="Q16" s="5" t="n">
-        <v>54100</v>
+        <v>333500</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>56.00739371534195</v>
+        <v>57.72113943028486</v>
       </c>
       <c r="S16" s="7" t="inlineStr"/>
       <c r="T16" s="7" t="inlineStr"/>
       <c r="U16" s="5" t="n">
-        <v>48700</v>
+        <v>300500</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>73.30595482546201</v>
+        <v>75.04159733777038</v>
       </c>
       <c r="W16" s="7" t="inlineStr"/>
       <c r="X16" s="7" t="inlineStr"/>
@@ -1846,12 +1850,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1866,51 +1870,51 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 47.4%</t>
+          <t>1차 매수선까지 26.2%</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>123100</v>
+        <v>78000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>118200</v>
+        <v>74300</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>129100</v>
+        <v>79600</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>103790</v>
+        <v>77560</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>106300</v>
+        <v>77960</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>83032</v>
+        <v>62048</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>85040</v>
+        <v>62368</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>83500</v>
+        <v>61800</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>47.4251497005988</v>
+        <v>26.21359223300971</v>
       </c>
       <c r="O17" s="7" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="5" t="n">
-        <v>75200</v>
+        <v>55700</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>63.69680851063831</v>
+        <v>40.0359066427289</v>
       </c>
       <c r="S17" s="7" t="inlineStr"/>
       <c r="T17" s="7" t="inlineStr"/>
       <c r="U17" s="5" t="n">
-        <v>67700</v>
+        <v>50200</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>81.83161004431314</v>
+        <v>55.37848605577689</v>
       </c>
       <c r="W17" s="7" t="inlineStr"/>
       <c r="X17" s="7" t="inlineStr"/>
@@ -1926,12 +1930,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1946,51 +1950,51 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.6%</t>
+          <t>1차 매수선까지 34.5%</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>397500</v>
+        <v>476000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>389000</v>
+        <v>452000</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>404000</v>
+        <v>482000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>341475</v>
+        <v>442625</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>347275</v>
+        <v>448225</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>273180</v>
+        <v>354100</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>277820</v>
+        <v>358580</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>273000</v>
+        <v>354000</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>45.60439560439561</v>
+        <v>34.46327683615819</v>
       </c>
       <c r="O18" s="7" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="5" t="n">
-        <v>246000</v>
+        <v>319000</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>61.58536585365854</v>
+        <v>49.21630094043887</v>
       </c>
       <c r="S18" s="7" t="inlineStr"/>
       <c r="T18" s="7" t="inlineStr"/>
       <c r="U18" s="5" t="n">
-        <v>221500</v>
+        <v>287500</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>79.45823927765237</v>
+        <v>65.56521739130434</v>
       </c>
       <c r="W18" s="7" t="inlineStr"/>
       <c r="X18" s="7" t="inlineStr"/>
@@ -2006,12 +2010,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2026,51 +2030,51 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.2%</t>
+          <t>1차 매수선까지 48.0%</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>63800</v>
+        <v>242500</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>62200</v>
+        <v>239500</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>64900</v>
+        <v>265000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>58605</v>
+        <v>204315</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>59377.5</v>
+        <v>208600</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>46884</v>
+        <v>163452</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>47502</v>
+        <v>166880</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>46850</v>
+        <v>163800</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>36.17929562433298</v>
+        <v>48.04639804639805</v>
       </c>
       <c r="O19" s="7" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr"/>
       <c r="Q19" s="5" t="n">
-        <v>42200</v>
+        <v>147500</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>51.18483412322274</v>
+        <v>64.40677966101694</v>
       </c>
       <c r="S19" s="7" t="inlineStr"/>
       <c r="T19" s="7" t="inlineStr"/>
       <c r="U19" s="5" t="n">
-        <v>38000</v>
+        <v>132800</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>67.89473684210526</v>
+        <v>82.60542168674698</v>
       </c>
       <c r="W19" s="7" t="inlineStr"/>
       <c r="X19" s="7" t="inlineStr"/>
@@ -2086,12 +2090,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2106,51 +2110,51 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.8%</t>
+          <t>1차 매수선까지 41.2%</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>42700</v>
+        <v>126900</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>42500</v>
+        <v>115500</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>43400</v>
+        <v>127800</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>40407.5</v>
+        <v>111460</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>40700</v>
+        <v>114135</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>32326</v>
+        <v>89168</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>32560</v>
+        <v>91308</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>32150</v>
+        <v>89900</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>32.8149300155521</v>
+        <v>41.15684093437152</v>
       </c>
       <c r="O20" s="7" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr"/>
       <c r="Q20" s="5" t="n">
-        <v>28950</v>
+        <v>81000</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>47.49568221070812</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="S20" s="7" t="inlineStr"/>
       <c r="T20" s="7" t="inlineStr"/>
       <c r="U20" s="5" t="n">
-        <v>26100</v>
+        <v>73000</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>63.60153256704982</v>
+        <v>73.83561643835617</v>
       </c>
       <c r="W20" s="7" t="inlineStr"/>
       <c r="X20" s="7" t="inlineStr"/>
@@ -2166,12 +2170,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2186,51 +2190,51 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.0%</t>
+          <t>1차 매수선까지 34.0%</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>120400</v>
+        <v>384500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>116000</v>
+        <v>373000</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>122600</v>
+        <v>401000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>110440</v>
+        <v>357875</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>111410</v>
+        <v>363100</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>88352</v>
+        <v>286300</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>89128</v>
+        <v>290480</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>87900</v>
+        <v>287000</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>36.97383390216154</v>
+        <v>33.97212543554006</v>
       </c>
       <c r="O21" s="7" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="5" t="n">
-        <v>79200</v>
+        <v>258500</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>52.02020202020202</v>
+        <v>48.74274661508704</v>
       </c>
       <c r="S21" s="7" t="inlineStr"/>
       <c r="T21" s="7" t="inlineStr"/>
       <c r="U21" s="5" t="n">
-        <v>71300</v>
+        <v>233000</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>68.86395511921458</v>
+        <v>65.02145922746782</v>
       </c>
       <c r="W21" s="7" t="inlineStr"/>
       <c r="X21" s="7" t="inlineStr"/>
@@ -2246,12 +2250,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2266,51 +2270,51 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.6%</t>
+          <t>1차 매수선까지 26.5%</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>24300</v>
+        <v>62000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>21050</v>
+        <v>60000</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>25400</v>
+        <v>65500</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>18154.5</v>
+        <v>61185</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>18613.5</v>
+        <v>61895</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>14523.6</v>
+        <v>48948</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>14890.8</v>
+        <v>49516</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>14500</v>
+        <v>49000</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>67.58620689655173</v>
+        <v>26.53061224489796</v>
       </c>
       <c r="O22" s="7" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr"/>
       <c r="Q22" s="5" t="n">
-        <v>13060</v>
+        <v>44150</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>86.06431852986218</v>
+        <v>40.43035107587769</v>
       </c>
       <c r="S22" s="7" t="inlineStr"/>
       <c r="T22" s="7" t="inlineStr"/>
       <c r="U22" s="5" t="n">
-        <v>11760</v>
+        <v>39750</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>106.6326530612245</v>
+        <v>55.9748427672956</v>
       </c>
       <c r="W22" s="7" t="inlineStr"/>
       <c r="X22" s="7" t="inlineStr"/>
@@ -2326,12 +2330,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>277810</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2346,51 +2350,51 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 60.9%</t>
+          <t>1차 매수선까지 30.8%</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>434500</v>
+        <v>43500</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>358000</v>
+        <v>41800</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>453500</v>
+        <v>45150</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>339700</v>
+        <v>41675</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>345725</v>
+        <v>42070</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>271760</v>
+        <v>33340</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>276580</v>
+        <v>33656</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>270000</v>
+        <v>33250</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>60.92592592592593</v>
+        <v>30.82706766917293</v>
       </c>
       <c r="O23" s="7" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr"/>
       <c r="Q23" s="5" t="n">
-        <v>243500</v>
+        <v>29950</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>78.43942505133469</v>
+        <v>45.24207011686144</v>
       </c>
       <c r="S23" s="7" t="inlineStr"/>
       <c r="T23" s="7" t="inlineStr"/>
       <c r="U23" s="5" t="n">
-        <v>219500</v>
+        <v>27000</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>97.9498861047836</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="W23" s="7" t="inlineStr"/>
       <c r="X23" s="7" t="inlineStr"/>
@@ -2406,12 +2410,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>347850</t>
+          <t>249420</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2426,51 +2430,51 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 85.3%</t>
+          <t>1차 매수선까지 51.1%</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>278000</v>
+        <v>28400</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>233500</v>
+        <v>27400</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>284500</v>
+        <v>31550</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>190200</v>
+        <v>23897.5</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>193850</v>
+        <v>23957.5</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>152160</v>
+        <v>19118</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>155080</v>
+        <v>19166</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>150000</v>
+        <v>18790</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>85.33333333333334</v>
+        <v>51.14422565194252</v>
       </c>
       <c r="O24" s="7" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr"/>
       <c r="Q24" s="5" t="n">
-        <v>135100</v>
+        <v>16920</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>105.7735011102887</v>
+        <v>67.84869976359337</v>
       </c>
       <c r="S24" s="7" t="inlineStr"/>
       <c r="T24" s="7" t="inlineStr"/>
       <c r="U24" s="5" t="n">
-        <v>121600</v>
+        <v>15230</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>128.6184210526316</v>
+        <v>86.47406434668417</v>
       </c>
       <c r="W24" s="7" t="inlineStr"/>
       <c r="X24" s="7" t="inlineStr"/>
@@ -2486,12 +2490,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2506,51 +2510,51 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.9%</t>
+          <t>1차 매수선까지 18.9%</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>220500</v>
+        <v>28600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>214000</v>
+        <v>28200</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>235000</v>
+        <v>33500</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>189055</v>
+        <v>30277.5</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>192275</v>
+        <v>30267.5</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>151244</v>
+        <v>24222</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>153820</v>
+        <v>24214</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>151100</v>
+        <v>24050</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>45.92984778292521</v>
+        <v>18.91891891891892</v>
       </c>
       <c r="O25" s="7" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr"/>
       <c r="Q25" s="5" t="n">
-        <v>136000</v>
+        <v>21650</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>62.13235294117647</v>
+        <v>32.10161662817552</v>
       </c>
       <c r="S25" s="7" t="inlineStr"/>
       <c r="T25" s="7" t="inlineStr"/>
       <c r="U25" s="5" t="n">
-        <v>122500</v>
+        <v>19490</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>80</v>
+        <v>46.74191893278604</v>
       </c>
       <c r="W25" s="7" t="inlineStr"/>
       <c r="X25" s="7" t="inlineStr"/>
@@ -2566,12 +2570,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>466100</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2586,51 +2590,51 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.3%</t>
+          <t>1차 매수선까지 28.5%</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>59900</v>
+        <v>41700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>58700</v>
+        <v>40250</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>64300</v>
+        <v>44550</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>56485</v>
+        <v>40347.5</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>56505</v>
+        <v>41025</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>45188</v>
+        <v>32278</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>45204</v>
+        <v>32820</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>44600</v>
+        <v>32450</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>34.30493273542601</v>
+        <v>28.50539291217257</v>
       </c>
       <c r="O26" s="7" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr"/>
       <c r="Q26" s="5" t="n">
-        <v>40150</v>
+        <v>29250</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>49.19053549190536</v>
+        <v>42.56410256410256</v>
       </c>
       <c r="S26" s="7" t="inlineStr"/>
       <c r="T26" s="7" t="inlineStr"/>
       <c r="U26" s="5" t="n">
-        <v>36150</v>
+        <v>26350</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>65.69847856154909</v>
+        <v>58.25426944971537</v>
       </c>
       <c r="W26" s="7" t="inlineStr"/>
       <c r="X26" s="7" t="inlineStr"/>
@@ -2646,12 +2650,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2666,51 +2670,51 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 59.0%</t>
+          <t>1차 매수선까지 22.2%</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>42700</v>
+        <v>959000</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>41700</v>
+        <v>923000</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>45000</v>
+        <v>1011000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>33670</v>
+        <v>996900</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>34347.5</v>
+        <v>989950</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>26936</v>
+        <v>797520</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>27478</v>
+        <v>791960</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>26850</v>
+        <v>785000</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>59.0316573556797</v>
+        <v>22.1656050955414</v>
       </c>
       <c r="O27" s="7" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr"/>
       <c r="Q27" s="5" t="n">
-        <v>24200</v>
+        <v>707000</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>76.44628099173553</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="S27" s="7" t="inlineStr"/>
       <c r="T27" s="7" t="inlineStr"/>
       <c r="U27" s="5" t="n">
-        <v>21800</v>
+        <v>637000</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>95.87155963302753</v>
+        <v>50.54945054945055</v>
       </c>
       <c r="W27" s="7" t="inlineStr"/>
       <c r="X27" s="7" t="inlineStr"/>
@@ -2726,12 +2730,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2746,51 +2750,51 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 44.7%</t>
+          <t>1차 매수선까지 24.1%</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>70300</v>
+        <v>111100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>67000</v>
+        <v>109400</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>72100</v>
+        <v>114600</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>61060</v>
+        <v>112480</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>61830</v>
+        <v>112845</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>48848</v>
+        <v>89984</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>49464</v>
+        <v>90276</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>48600</v>
+        <v>89500</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>44.65020576131688</v>
+        <v>24.1340782122905</v>
       </c>
       <c r="O28" s="7" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr"/>
       <c r="Q28" s="5" t="n">
-        <v>43750</v>
+        <v>80600</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>60.68571428571429</v>
+        <v>37.84119106699752</v>
       </c>
       <c r="S28" s="7" t="inlineStr"/>
       <c r="T28" s="7" t="inlineStr"/>
       <c r="U28" s="5" t="n">
-        <v>39400</v>
+        <v>72600</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>78.42639593908629</v>
+        <v>53.03030303030303</v>
       </c>
       <c r="W28" s="7" t="inlineStr"/>
       <c r="X28" s="7" t="inlineStr"/>
@@ -2806,12 +2810,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2826,51 +2830,51 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.8%</t>
+          <t>1차 매수선까지 66.5%</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>488000</v>
+        <v>26300</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>472000</v>
+        <v>24550</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>491500</v>
+        <v>27000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>457625</v>
+        <v>19751.5</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>458675</v>
+        <v>20265</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>366100</v>
+        <v>15801.2</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>366940</v>
+        <v>16212</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>362000</v>
+        <v>15800</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>34.80662983425415</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="O29" s="7" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr"/>
       <c r="Q29" s="5" t="n">
-        <v>326000</v>
+        <v>14230</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>49.69325153374233</v>
+        <v>84.8208011243851</v>
       </c>
       <c r="S29" s="7" t="inlineStr"/>
       <c r="T29" s="7" t="inlineStr"/>
       <c r="U29" s="5" t="n">
-        <v>293500</v>
+        <v>12810</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>66.26916524701873</v>
+        <v>105.3083528493365</v>
       </c>
       <c r="W29" s="7" t="inlineStr"/>
       <c r="X29" s="7" t="inlineStr"/>
@@ -2886,12 +2890,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>097230</t>
+          <t>347850</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2906,51 +2910,51 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.8%</t>
+          <t>1차 매수선까지 97.0%</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>28100</v>
+        <v>320000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>27800</v>
+        <v>270500</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>29200</v>
+        <v>326000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>27267.5</v>
+        <v>204875</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>27377.5</v>
+        <v>210850</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>21814</v>
+        <v>163900</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>21902</v>
+        <v>168680</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>21650</v>
+        <v>162400</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>29.79214780600462</v>
+        <v>97.04433497536947</v>
       </c>
       <c r="O30" s="7" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr"/>
       <c r="Q30" s="5" t="n">
-        <v>19490</v>
+        <v>146200</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>44.17650076962545</v>
+        <v>118.8782489740082</v>
       </c>
       <c r="S30" s="7" t="inlineStr"/>
       <c r="T30" s="7" t="inlineStr"/>
       <c r="U30" s="5" t="n">
-        <v>17550</v>
+        <v>131600</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>60.11396011396012</v>
+        <v>143.161094224924</v>
       </c>
       <c r="W30" s="7" t="inlineStr"/>
       <c r="X30" s="7" t="inlineStr"/>
@@ -2966,12 +2970,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2986,51 +2990,51 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.7%</t>
+          <t>1차 매수선까지 23.2%</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>232000</v>
+        <v>54500</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>226500</v>
+        <v>52700</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>238000</v>
+        <v>58400</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>222000</v>
+        <v>56105</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>222825</v>
+        <v>55825</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>177600</v>
+        <v>44884</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>178260</v>
+        <v>44660</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>176100</v>
+        <v>44250</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>31.74332765474163</v>
+        <v>23.16384180790961</v>
       </c>
       <c r="O31" s="7" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr"/>
       <c r="Q31" s="5" t="n">
-        <v>158500</v>
+        <v>39850</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>46.37223974763407</v>
+        <v>36.76286072772898</v>
       </c>
       <c r="S31" s="7" t="inlineStr"/>
       <c r="T31" s="7" t="inlineStr"/>
       <c r="U31" s="5" t="n">
-        <v>142700</v>
+        <v>35900</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>62.57883672039243</v>
+        <v>51.81058495821726</v>
       </c>
       <c r="W31" s="7" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr"/>
@@ -3046,12 +3050,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3066,51 +3070,51 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 67.4%</t>
+          <t>1차 매수선까지 44.5%</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>966000</v>
+        <v>41250</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>912000</v>
+        <v>38475</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>968000</v>
+        <v>41700</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>718100</v>
+        <v>35770</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>739750</v>
+        <v>36297.5</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>574480</v>
+        <v>28616</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>591800</v>
+        <v>29038</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>577000</v>
+        <v>28550</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>67.41767764298093</v>
+        <v>44.48336252189142</v>
       </c>
       <c r="O32" s="7" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr"/>
       <c r="Q32" s="5" t="n">
-        <v>520000</v>
+        <v>25700</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>85.76923076923076</v>
+        <v>60.50583657587548</v>
       </c>
       <c r="S32" s="7" t="inlineStr"/>
       <c r="T32" s="7" t="inlineStr"/>
       <c r="U32" s="5" t="n">
-        <v>468500</v>
+        <v>23150</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>106.1899679829242</v>
+        <v>78.18574514038878</v>
       </c>
       <c r="W32" s="7" t="inlineStr"/>
       <c r="X32" s="7" t="inlineStr"/>
@@ -3126,12 +3130,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>한라캐스트</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3146,51 +3150,51 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.8%</t>
+          <t>1차 매수선까지 28.7%</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>11820</v>
+        <v>64300</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>11590</v>
+        <v>63100</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>12770</v>
+        <v>67100</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>10962.5</v>
+        <v>62695</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>11111</v>
+        <v>63130</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>8770</v>
+        <v>50156</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>8888.800000000001</v>
+        <v>50504</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>8770</v>
+        <v>49950</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>34.77765108323831</v>
+        <v>28.72872872872873</v>
       </c>
       <c r="O33" s="7" t="inlineStr"/>
       <c r="P33" s="7" t="inlineStr"/>
       <c r="Q33" s="5" t="n">
-        <v>7900</v>
+        <v>45000</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>49.62025316455696</v>
+        <v>42.88888888888889</v>
       </c>
       <c r="S33" s="7" t="inlineStr"/>
       <c r="T33" s="7" t="inlineStr"/>
       <c r="U33" s="5" t="n">
-        <v>7120</v>
+        <v>40550</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>66.01123595505618</v>
+        <v>58.56966707768188</v>
       </c>
       <c r="W33" s="7" t="inlineStr"/>
       <c r="X33" s="7" t="inlineStr"/>
@@ -3206,12 +3210,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>097230</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3226,51 +3230,51 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 66.8%</t>
+          <t>1차 매수선까지 17.2%</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>209500</v>
+        <v>25250</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>163400</v>
+        <v>24350</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>209500</v>
+        <v>26050</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>158340</v>
+        <v>27152.5</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>161130</v>
+        <v>27082.5</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>126672</v>
+        <v>21722</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>128904</v>
+        <v>21666</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>125600</v>
+        <v>21550</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>66.79936305732484</v>
+        <v>17.16937354988399</v>
       </c>
       <c r="O34" s="7" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr"/>
       <c r="Q34" s="5" t="n">
-        <v>113100</v>
+        <v>19400</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>85.2343059239611</v>
+        <v>30.15463917525773</v>
       </c>
       <c r="S34" s="7" t="inlineStr"/>
       <c r="T34" s="7" t="inlineStr"/>
       <c r="U34" s="5" t="n">
-        <v>101800</v>
+        <v>17470</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>105.7956777996071</v>
+        <v>44.53348597595878</v>
       </c>
       <c r="W34" s="7" t="inlineStr"/>
       <c r="X34" s="7" t="inlineStr"/>
@@ -3286,12 +3290,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3306,51 +3310,51 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 45.4%</t>
+          <t>1차 매수선까지 22.0%</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>126600</v>
+        <v>216000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>114700</v>
+        <v>209500</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>131100</v>
+        <v>231000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>109445</v>
+        <v>223650</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>110790</v>
+        <v>223175</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>87556</v>
+        <v>178920</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>88632</v>
+        <v>178540</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>87100</v>
+        <v>177000</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>45.35017221584386</v>
+        <v>22.03389830508474</v>
       </c>
       <c r="O35" s="7" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr"/>
       <c r="Q35" s="5" t="n">
-        <v>78400</v>
+        <v>159400</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>61.47959183673469</v>
+        <v>35.5081555834379</v>
       </c>
       <c r="S35" s="7" t="inlineStr"/>
       <c r="T35" s="7" t="inlineStr"/>
       <c r="U35" s="5" t="n">
-        <v>70600</v>
+        <v>143500</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>79.3201133144476</v>
+        <v>50.52264808362369</v>
       </c>
       <c r="W35" s="7" t="inlineStr"/>
       <c r="X35" s="7" t="inlineStr"/>
@@ -3366,12 +3370,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3386,51 +3390,51 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 46.6%</t>
+          <t>1차 매수선까지 45.8%</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>425000</v>
+        <v>913000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>389500</v>
+        <v>869000</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>435500</v>
+        <v>978000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>367250</v>
+        <v>780800</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>368700</v>
+        <v>796800</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>293800</v>
+        <v>624640</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>294960</v>
+        <v>637440</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>290000</v>
+        <v>626000</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>46.55172413793103</v>
+        <v>45.84664536741214</v>
       </c>
       <c r="O36" s="7" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr"/>
       <c r="Q36" s="5" t="n">
-        <v>261500</v>
+        <v>564000</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>62.52390057361377</v>
+        <v>61.87943262411347</v>
       </c>
       <c r="S36" s="7" t="inlineStr"/>
       <c r="T36" s="7" t="inlineStr"/>
       <c r="U36" s="5" t="n">
-        <v>235500</v>
+        <v>508000</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>80.46709129511677</v>
+        <v>79.7244094488189</v>
       </c>
       <c r="W36" s="7" t="inlineStr"/>
       <c r="X36" s="7" t="inlineStr"/>
@@ -3446,12 +3450,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3466,51 +3470,51 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 50.4%</t>
+          <t>1차 매수선까지 15.8%</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>343000</v>
+        <v>10650</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>321500</v>
+        <v>10340</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>345000</v>
+        <v>11330</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>286925</v>
+        <v>11419</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>290550</v>
+        <v>11566.5</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>229540</v>
+        <v>9135.200000000001</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>232440</v>
+        <v>9253.200000000001</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>228000</v>
+        <v>9200</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>50.43859649122807</v>
+        <v>15.76086956521739</v>
       </c>
       <c r="O37" s="7" t="inlineStr"/>
       <c r="P37" s="7" t="inlineStr"/>
       <c r="Q37" s="5" t="n">
-        <v>205500</v>
+        <v>8290</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>66.90997566909975</v>
+        <v>28.46803377563329</v>
       </c>
       <c r="S37" s="7" t="inlineStr"/>
       <c r="T37" s="7" t="inlineStr"/>
       <c r="U37" s="5" t="n">
-        <v>185000</v>
+        <v>7470</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>85.4054054054054</v>
+        <v>42.570281124498</v>
       </c>
       <c r="W37" s="7" t="inlineStr"/>
       <c r="X37" s="7" t="inlineStr"/>
@@ -3526,12 +3530,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>090710</t>
+          <t>064400</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3546,51 +3550,51 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.1%</t>
+          <t>1차 매수선까지 15.8%</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>6450</v>
+        <v>58600</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>6090</v>
+        <v>57000</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>6500</v>
+        <v>61700</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>4876.5</v>
+        <v>63920</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>5035</v>
+        <v>63620</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3901.2</v>
+        <v>51136</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>4028</v>
+        <v>50896</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>3930</v>
+        <v>50600</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>64.12213740458014</v>
+        <v>15.8102766798419</v>
       </c>
       <c r="O38" s="7" t="inlineStr"/>
       <c r="P38" s="7" t="inlineStr"/>
       <c r="Q38" s="5" t="n">
-        <v>3540</v>
+        <v>45550</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>82.20338983050848</v>
+        <v>28.64983534577388</v>
       </c>
       <c r="S38" s="7" t="inlineStr"/>
       <c r="T38" s="7" t="inlineStr"/>
       <c r="U38" s="5" t="n">
-        <v>3190</v>
+        <v>41000</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>102.1943573667712</v>
+        <v>42.92682926829269</v>
       </c>
       <c r="W38" s="7" t="inlineStr"/>
       <c r="X38" s="7" t="inlineStr"/>
@@ -3606,12 +3610,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>267260</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3626,51 +3630,51 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 33.6%</t>
+          <t>1차 매수선까지 43.2%</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>40600</v>
+        <v>872000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>40550</v>
+        <v>828000</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>45600</v>
+        <v>919000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>37910</v>
+        <v>761450</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>38487.5</v>
+        <v>773900</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>30328</v>
+        <v>609160</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>30790</v>
+        <v>619120</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>30400</v>
+        <v>609000</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>33.55263157894737</v>
+        <v>43.18555008210181</v>
       </c>
       <c r="O39" s="7" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr"/>
       <c r="Q39" s="5" t="n">
-        <v>27400</v>
+        <v>549000</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>48.17518248175183</v>
+        <v>58.83424408014572</v>
       </c>
       <c r="S39" s="7" t="inlineStr"/>
       <c r="T39" s="7" t="inlineStr"/>
       <c r="U39" s="5" t="n">
-        <v>24700</v>
+        <v>494500</v>
       </c>
       <c r="V39" s="6" t="n">
-        <v>64.37246963562752</v>
+        <v>76.33973710819009</v>
       </c>
       <c r="W39" s="7" t="inlineStr"/>
       <c r="X39" s="7" t="inlineStr"/>
@@ -3686,12 +3690,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>454910</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3706,51 +3710,51 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.0%</t>
+          <t>1차 매수선까지 37.5%</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>9010</v>
+        <v>81100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>8890</v>
+        <v>78000</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>9080</v>
+        <v>88000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>9852.5</v>
+        <v>74110</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>9685</v>
+        <v>74845</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>7882</v>
+        <v>59288</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>7748</v>
+        <v>59876</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>7700</v>
+        <v>59000</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>17.01298701298701</v>
+        <v>37.45762711864407</v>
       </c>
       <c r="O40" s="7" t="inlineStr"/>
       <c r="P40" s="7" t="inlineStr"/>
       <c r="Q40" s="5" t="n">
-        <v>6940</v>
+        <v>53200</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>29.82708933717579</v>
+        <v>52.44360902255639</v>
       </c>
       <c r="S40" s="7" t="inlineStr"/>
       <c r="T40" s="7" t="inlineStr"/>
       <c r="U40" s="5" t="n">
-        <v>6250</v>
+        <v>47900</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>44.16</v>
+        <v>69.31106471816284</v>
       </c>
       <c r="W40" s="7" t="inlineStr"/>
       <c r="X40" s="7" t="inlineStr"/>
@@ -3766,12 +3770,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>060250</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>NHN KCP</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3786,51 +3790,51 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.8%</t>
+          <t>1차 매수선까지 57.1%</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>15950</v>
+        <v>52000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>15860</v>
+        <v>50000</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>16250</v>
+        <v>55000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>17111.5</v>
+        <v>41580</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>16909.5</v>
+        <v>42277.5</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>13689.2</v>
+        <v>33264</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>13527.6</v>
+        <v>33822</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>13430</v>
+        <v>33100</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>18.76396128071482</v>
+        <v>57.09969788519638</v>
       </c>
       <c r="O41" s="7" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr"/>
       <c r="Q41" s="5" t="n">
-        <v>12090</v>
+        <v>29800</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>31.92721257237386</v>
+        <v>74.49664429530202</v>
       </c>
       <c r="S41" s="7" t="inlineStr"/>
       <c r="T41" s="7" t="inlineStr"/>
       <c r="U41" s="5" t="n">
-        <v>10890</v>
+        <v>26850</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>46.46464646464646</v>
+        <v>93.66852886405958</v>
       </c>
       <c r="W41" s="7" t="inlineStr"/>
       <c r="X41" s="7" t="inlineStr"/>
@@ -3846,12 +3850,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3866,51 +3870,51 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.7%</t>
+          <t>1차 매수선까지 55.9%</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>175800</v>
+        <v>208500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>174500</v>
+        <v>203500</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>177300</v>
+        <v>222500</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>175300</v>
+        <v>168040</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>175160</v>
+        <v>170800</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>140240</v>
+        <v>134432</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>140128</v>
+        <v>136640</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>138700</v>
+        <v>133700</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>26.74837779379957</v>
+        <v>55.94614809274495</v>
       </c>
       <c r="O42" s="7" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr"/>
       <c r="Q42" s="5" t="n">
-        <v>124900</v>
+        <v>120400</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>40.75260208166534</v>
+        <v>73.17275747508306</v>
       </c>
       <c r="S42" s="7" t="inlineStr"/>
       <c r="T42" s="7" t="inlineStr"/>
       <c r="U42" s="5" t="n">
-        <v>112500</v>
+        <v>108400</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>56.26666666666667</v>
+        <v>92.34317343173431</v>
       </c>
       <c r="W42" s="7" t="inlineStr"/>
       <c r="X42" s="7" t="inlineStr"/>
@@ -3926,12 +3930,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3946,51 +3950,51 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 37.2%</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>234000</v>
+        <v>124200</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>221000</v>
+        <v>118900</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>238500</v>
+        <v>129000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>210815</v>
+        <v>113740</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>211565</v>
+        <v>114755</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>168652</v>
+        <v>90992</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>169252</v>
+        <v>91804</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>166600</v>
+        <v>90500</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>40.45618247298919</v>
+        <v>37.23756906077348</v>
       </c>
       <c r="O43" s="7" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr"/>
       <c r="Q43" s="5" t="n">
-        <v>150000</v>
+        <v>81500</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>56.00000000000001</v>
+        <v>52.39263803680981</v>
       </c>
       <c r="S43" s="7" t="inlineStr"/>
       <c r="T43" s="7" t="inlineStr"/>
       <c r="U43" s="5" t="n">
-        <v>135100</v>
+        <v>73400</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>73.20503330866025</v>
+        <v>69.20980926430518</v>
       </c>
       <c r="W43" s="7" t="inlineStr"/>
       <c r="X43" s="7" t="inlineStr"/>
@@ -4006,12 +4010,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>064260</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>다날</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -4026,51 +4030,51 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 10.7%</t>
+          <t>1차 매수선까지 52.2%</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>8060</v>
+        <v>457500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>8030</v>
+        <v>443000</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>8350</v>
+        <v>481000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>9235.5</v>
+        <v>377800</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>9131</v>
+        <v>382900</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>7388.400000000001</v>
+        <v>302240</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>7304.8</v>
+        <v>306320</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>7280</v>
+        <v>300500</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>10.71428571428571</v>
+        <v>52.24625623960066</v>
       </c>
       <c r="O44" s="7" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr"/>
       <c r="Q44" s="5" t="n">
-        <v>6560</v>
+        <v>270500</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>22.86585365853659</v>
+        <v>69.13123844731977</v>
       </c>
       <c r="S44" s="7" t="inlineStr"/>
       <c r="T44" s="7" t="inlineStr"/>
       <c r="U44" s="5" t="n">
-        <v>5910</v>
+        <v>243500</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>36.37901861252115</v>
+        <v>87.88501026694045</v>
       </c>
       <c r="W44" s="7" t="inlineStr"/>
       <c r="X44" s="7" t="inlineStr"/>
@@ -4086,12 +4090,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -4106,51 +4110,51 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 64.3%</t>
+          <t>1차 매수선까지 40.2%</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>86900</v>
+        <v>331500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>84800</v>
+        <v>322000</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>90800</v>
+        <v>339000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>65667.5</v>
+        <v>297075</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>67730</v>
+        <v>300175</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>52534</v>
+        <v>237660</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>54184</v>
+        <v>240140</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>52900</v>
+        <v>236500</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>64.27221172022685</v>
+        <v>40.169133192389</v>
       </c>
       <c r="O45" s="7" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr"/>
       <c r="Q45" s="5" t="n">
-        <v>47650</v>
+        <v>213000</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>82.37145855194123</v>
+        <v>55.63380281690142</v>
       </c>
       <c r="S45" s="7" t="inlineStr"/>
       <c r="T45" s="7" t="inlineStr"/>
       <c r="U45" s="5" t="n">
-        <v>42900</v>
+        <v>191800</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>102.5641025641026</v>
+        <v>72.83628779979145</v>
       </c>
       <c r="W45" s="7" t="inlineStr"/>
       <c r="X45" s="7" t="inlineStr"/>
@@ -4166,12 +4170,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>090710</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4186,51 +4190,51 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 66.2%</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>103700</v>
+        <v>7380</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>102500</v>
+        <v>6340</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>108000</v>
+        <v>7830</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>102710</v>
+        <v>5485.25</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>102450</v>
+        <v>5694.75</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>82168</v>
+        <v>4388.2</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>81960</v>
+        <v>4555.8</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>81100</v>
+        <v>4440</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>27.86683107274969</v>
+        <v>66.21621621621621</v>
       </c>
       <c r="O46" s="7" t="inlineStr"/>
       <c r="P46" s="7" t="inlineStr"/>
       <c r="Q46" s="5" t="n">
-        <v>73000</v>
+        <v>4000</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>42.05479452054794</v>
+        <v>84.5</v>
       </c>
       <c r="S46" s="7" t="inlineStr"/>
       <c r="T46" s="7" t="inlineStr"/>
       <c r="U46" s="5" t="n">
-        <v>65800</v>
+        <v>3605</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>57.59878419452887</v>
+        <v>104.7156726768377</v>
       </c>
       <c r="W46" s="7" t="inlineStr"/>
       <c r="X46" s="7" t="inlineStr"/>
@@ -4246,12 +4250,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>041190</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4266,51 +4270,51 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.6%</t>
+          <t>1차 매수선까지 16.0%</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>435500</v>
+        <v>8550</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>430000</v>
+        <v>8120</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>436500</v>
+        <v>8750</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>434500</v>
+        <v>9386</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>434400</v>
+        <v>9270.5</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>347600</v>
+        <v>7508.8</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>347520</v>
+        <v>7416.400000000001</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>344000</v>
+        <v>7370</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>26.59883720930232</v>
+        <v>16.01085481682497</v>
       </c>
       <c r="O47" s="7" t="inlineStr"/>
       <c r="P47" s="7" t="inlineStr"/>
       <c r="Q47" s="5" t="n">
-        <v>310000</v>
+        <v>6640</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>40.48387096774194</v>
+        <v>28.76506024096386</v>
       </c>
       <c r="S47" s="7" t="inlineStr"/>
       <c r="T47" s="7" t="inlineStr"/>
       <c r="U47" s="5" t="n">
-        <v>279500</v>
+        <v>5980</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>55.81395348837209</v>
+        <v>42.97658862876254</v>
       </c>
       <c r="W47" s="7" t="inlineStr"/>
       <c r="X47" s="7" t="inlineStr"/>
@@ -4326,12 +4330,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>060250</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>SK오션플랜트</t>
+          <t>NHN KCP</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4346,51 +4350,51 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.6%</t>
+          <t>1차 매수선까지 16.2%</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>21200</v>
+        <v>15210</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>21050</v>
+        <v>14640</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>21850</v>
+        <v>15600</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>22647.5</v>
+        <v>16604</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>22505</v>
+        <v>16458.5</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>18118</v>
+        <v>13283.2</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>18004</v>
+        <v>13166.8</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>17880</v>
+        <v>13090</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>18.56823266219239</v>
+        <v>16.19556913674561</v>
       </c>
       <c r="O48" s="7" t="inlineStr"/>
       <c r="P48" s="7" t="inlineStr"/>
       <c r="Q48" s="5" t="n">
-        <v>16100</v>
+        <v>11790</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>31.67701863354037</v>
+        <v>29.00763358778626</v>
       </c>
       <c r="S48" s="7" t="inlineStr"/>
       <c r="T48" s="7" t="inlineStr"/>
       <c r="U48" s="5" t="n">
-        <v>14500</v>
+        <v>10620</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>46.20689655172414</v>
+        <v>43.22033898305085</v>
       </c>
       <c r="W48" s="7" t="inlineStr"/>
       <c r="X48" s="7" t="inlineStr"/>
@@ -4406,12 +4410,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4426,51 +4430,51 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 27.9%</t>
+          <t>1차 매수선까지 25.6%</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>22050</v>
+        <v>174300</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>21500</v>
+        <v>172500</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>22350</v>
+        <v>181000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>21717</v>
+        <v>175225</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>21789.5</v>
+        <v>175170</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>17373.6</v>
+        <v>140180</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>17431.6</v>
+        <v>140136</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>17240</v>
+        <v>138800</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>27.90023201856148</v>
+        <v>25.57636887608069</v>
       </c>
       <c r="O49" s="7" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr"/>
       <c r="Q49" s="5" t="n">
-        <v>15520</v>
+        <v>125000</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>42.07474226804123</v>
+        <v>39.44</v>
       </c>
       <c r="S49" s="7" t="inlineStr"/>
       <c r="T49" s="7" t="inlineStr"/>
       <c r="U49" s="5" t="n">
-        <v>13970</v>
+        <v>112600</v>
       </c>
       <c r="V49" s="6" t="n">
-        <v>57.83822476735862</v>
+        <v>54.79573712255773</v>
       </c>
       <c r="W49" s="7" t="inlineStr"/>
       <c r="X49" s="7" t="inlineStr"/>
@@ -4486,12 +4490,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>000250</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4506,51 +4510,51 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 37.6%</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>53200</v>
+        <v>233000</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>52000</v>
+        <v>225000</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>54600</v>
+        <v>247000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>51265</v>
+        <v>213915</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>51190</v>
+        <v>214790</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>41012</v>
+        <v>171132</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>40952</v>
+        <v>171832</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>40450</v>
+        <v>169300</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>31.5203955500618</v>
+        <v>37.62551683402244</v>
       </c>
       <c r="O50" s="7" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr"/>
       <c r="Q50" s="5" t="n">
-        <v>36450</v>
+        <v>152400</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>45.95336076817559</v>
+        <v>52.88713910761155</v>
       </c>
       <c r="S50" s="7" t="inlineStr"/>
       <c r="T50" s="7" t="inlineStr"/>
       <c r="U50" s="5" t="n">
-        <v>32850</v>
+        <v>137200</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>61.9482496194825</v>
+        <v>69.82507288629738</v>
       </c>
       <c r="W50" s="7" t="inlineStr"/>
       <c r="X50" s="7" t="inlineStr"/>
@@ -4566,12 +4570,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>064260</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>다날</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4581,56 +4585,56 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.0%</t>
+          <t>1차 매수선까지 8.3% (접근 중!)</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>49400</v>
+        <v>7590</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>48250</v>
+        <v>7380</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>50400</v>
+        <v>7740</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>47672.5</v>
+        <v>8906.5</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>48040</v>
+        <v>8786.5</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>38138</v>
+        <v>7125.200000000001</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>38432</v>
+        <v>7029.200000000001</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>38000</v>
+        <v>7010</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>30</v>
+        <v>8.273894436519258</v>
       </c>
       <c r="O51" s="7" t="inlineStr"/>
       <c r="P51" s="7" t="inlineStr"/>
       <c r="Q51" s="5" t="n">
-        <v>34250</v>
+        <v>6310</v>
       </c>
       <c r="R51" s="6" t="n">
-        <v>44.23357664233576</v>
+        <v>20.28526148969889</v>
       </c>
       <c r="S51" s="7" t="inlineStr"/>
       <c r="T51" s="7" t="inlineStr"/>
       <c r="U51" s="5" t="n">
-        <v>30850</v>
+        <v>5680</v>
       </c>
       <c r="V51" s="6" t="n">
-        <v>60.12965964343599</v>
+        <v>33.62676056338028</v>
       </c>
       <c r="W51" s="7" t="inlineStr"/>
       <c r="X51" s="7" t="inlineStr"/>
@@ -4646,12 +4650,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>현대힘스</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4666,51 +4670,51 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.3%</t>
+          <t>1차 매수선까지 49.9%</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>22700</v>
+        <v>88900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>22000</v>
+        <v>81000</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>23100</v>
+        <v>92500</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>23712.5</v>
+        <v>73227.5</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>23595</v>
+        <v>75535</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>18970</v>
+        <v>58582</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>18876</v>
+        <v>60428</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>18720</v>
+        <v>59300</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>21.26068376068376</v>
+        <v>49.91568296795953</v>
       </c>
       <c r="O52" s="7" t="inlineStr"/>
       <c r="P52" s="7" t="inlineStr"/>
       <c r="Q52" s="5" t="n">
-        <v>16850</v>
+        <v>53400</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>34.71810089020772</v>
+        <v>66.47940074906367</v>
       </c>
       <c r="S52" s="7" t="inlineStr"/>
       <c r="T52" s="7" t="inlineStr"/>
       <c r="U52" s="5" t="n">
-        <v>15170</v>
+        <v>48100</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>49.63744232036915</v>
+        <v>84.82328482328482</v>
       </c>
       <c r="W52" s="7" t="inlineStr"/>
       <c r="X52" s="7" t="inlineStr"/>
@@ -4726,12 +4730,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4746,51 +4750,51 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 37.5%</t>
+          <t>1차 매수선까지 23.2%</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>477000</v>
+        <v>99700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>451500</v>
+        <v>99100</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>484000</v>
+        <v>107500</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>436325</v>
+        <v>102285</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>440175</v>
+        <v>101970</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>349060</v>
+        <v>81828</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>352140</v>
+        <v>81576</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>347000</v>
+        <v>80900</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>37.46397694524496</v>
+        <v>23.23856613102596</v>
       </c>
       <c r="O53" s="7" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr"/>
       <c r="Q53" s="5" t="n">
-        <v>312500</v>
+        <v>72900</v>
       </c>
       <c r="R53" s="6" t="n">
-        <v>52.64</v>
+        <v>36.76268861454047</v>
       </c>
       <c r="S53" s="7" t="inlineStr"/>
       <c r="T53" s="7" t="inlineStr"/>
       <c r="U53" s="5" t="n">
-        <v>281500</v>
+        <v>65700</v>
       </c>
       <c r="V53" s="6" t="n">
-        <v>69.44937833037301</v>
+        <v>51.7503805175038</v>
       </c>
       <c r="W53" s="7" t="inlineStr"/>
       <c r="X53" s="7" t="inlineStr"/>
@@ -4806,12 +4810,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>010620</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>HD현대미포</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4826,51 +4830,51 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 40.5%</t>
+          <t>1차 매수선까지 31.3%</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>244000</v>
+        <v>61700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>232000</v>
+        <v>61500</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>246000</v>
+        <v>73300</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>218130</v>
+        <v>59735</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>220590</v>
+        <v>59476.65</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>174504</v>
+        <v>47788</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>176472</v>
+        <v>47581.32000000001</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>173700</v>
+        <v>47000</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>40.4720782959125</v>
+        <v>31.27659574468085</v>
       </c>
       <c r="O54" s="7" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr"/>
       <c r="Q54" s="5" t="n">
-        <v>156400</v>
+        <v>42350</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>56.01023017902813</v>
+        <v>45.69067296340024</v>
       </c>
       <c r="S54" s="7" t="inlineStr"/>
       <c r="T54" s="7" t="inlineStr"/>
       <c r="U54" s="5" t="n">
-        <v>140800</v>
+        <v>38150</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>73.29545454545455</v>
+        <v>61.73001310615989</v>
       </c>
       <c r="W54" s="7" t="inlineStr"/>
       <c r="X54" s="7" t="inlineStr"/>
@@ -4886,12 +4890,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4906,51 +4910,51 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 69.9%</t>
+          <t>1차 매수선까지 26.1%</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>2300000</v>
+        <v>433000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2102000</v>
+        <v>422500</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>2414000</v>
+        <v>444500</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>1691500</v>
+        <v>434150</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>1739550</v>
+        <v>433475</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>1353200</v>
+        <v>347320</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>1391640</v>
+        <v>346780</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>1354000</v>
+        <v>343500</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>69.86706056129985</v>
+        <v>26.05531295487627</v>
       </c>
       <c r="O55" s="7" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr"/>
       <c r="Q55" s="5" t="n">
-        <v>1219000</v>
+        <v>309500</v>
       </c>
       <c r="R55" s="6" t="n">
-        <v>88.67924528301887</v>
+        <v>39.90306946688207</v>
       </c>
       <c r="S55" s="7" t="inlineStr"/>
       <c r="T55" s="7" t="inlineStr"/>
       <c r="U55" s="5" t="n">
-        <v>1098000</v>
+        <v>279000</v>
       </c>
       <c r="V55" s="6" t="n">
-        <v>109.471766848816</v>
+        <v>55.19713261648745</v>
       </c>
       <c r="W55" s="7" t="inlineStr"/>
       <c r="X55" s="7" t="inlineStr"/>
@@ -4966,12 +4970,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>LIG넥스원</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4986,51 +4990,51 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.8%</t>
+          <t>1차 매수선까지 17.1%</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>519000</v>
+        <v>20500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>510000</v>
+        <v>19970</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>534000</v>
+        <v>21750</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>480675</v>
+        <v>22212.5</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>481175</v>
+        <v>22035</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>384540</v>
+        <v>17770</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>384940</v>
+        <v>17628</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>379500</v>
+        <v>17510</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>36.75889328063241</v>
+        <v>17.07595659623072</v>
       </c>
       <c r="O56" s="7" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr"/>
       <c r="Q56" s="5" t="n">
-        <v>342000</v>
+        <v>15760</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>51.75438596491229</v>
+        <v>30.07614213197969</v>
       </c>
       <c r="S56" s="7" t="inlineStr"/>
       <c r="T56" s="7" t="inlineStr"/>
       <c r="U56" s="5" t="n">
-        <v>308000</v>
+        <v>14190</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>68.5064935064935</v>
+        <v>44.46793516560958</v>
       </c>
       <c r="W56" s="7" t="inlineStr"/>
       <c r="X56" s="7" t="inlineStr"/>
@@ -5046,12 +5050,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>0008Z0</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -5066,51 +5070,51 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.8%</t>
+          <t>1차 매수선까지 18.6%</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>41100</v>
+        <v>20450</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>40750</v>
+        <v>19760</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>41845</v>
+        <v>21727</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>41892.5</v>
+        <v>21704.5</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>33476</v>
+        <v>17381.6</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>33514</v>
+        <v>17363.6</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>33200</v>
+        <v>17240</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>23.79518072289157</v>
+        <v>18.61948955916473</v>
       </c>
       <c r="O57" s="7" t="inlineStr"/>
       <c r="P57" s="7" t="inlineStr"/>
       <c r="Q57" s="5" t="n">
-        <v>29900</v>
+        <v>15520</v>
       </c>
       <c r="R57" s="6" t="n">
-        <v>37.45819397993311</v>
+        <v>31.76546391752577</v>
       </c>
       <c r="S57" s="7" t="inlineStr"/>
       <c r="T57" s="7" t="inlineStr"/>
       <c r="U57" s="5" t="n">
-        <v>26950</v>
+        <v>13970</v>
       </c>
       <c r="V57" s="6" t="n">
-        <v>52.50463821892394</v>
+        <v>46.38511095204009</v>
       </c>
       <c r="W57" s="7" t="inlineStr"/>
       <c r="X57" s="7" t="inlineStr"/>
@@ -5126,12 +5130,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>삼양컴텍</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -5146,51 +5150,51 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 17.6%</t>
+          <t>1차 매수선까지 41.3%</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>15900</v>
+        <v>58000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>15540</v>
+        <v>54700</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>16070</v>
+        <v>60800</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>17086.5</v>
+        <v>51760</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>17014.5</v>
+        <v>52160</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>13669.2</v>
+        <v>41408</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>13611.6</v>
+        <v>41728</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>13520</v>
+        <v>41050</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>17.60355029585799</v>
+        <v>41.29110840438489</v>
       </c>
       <c r="O58" s="7" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr"/>
       <c r="Q58" s="5" t="n">
-        <v>12170</v>
+        <v>36950</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>30.64913722267872</v>
+        <v>56.96887686062247</v>
       </c>
       <c r="S58" s="7" t="inlineStr"/>
       <c r="T58" s="7" t="inlineStr"/>
       <c r="U58" s="5" t="n">
-        <v>10960</v>
+        <v>33300</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>45.07299270072993</v>
+        <v>74.17417417417418</v>
       </c>
       <c r="W58" s="7" t="inlineStr"/>
       <c r="X58" s="7" t="inlineStr"/>
@@ -5206,12 +5210,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -5226,51 +5230,51 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 39.9%</t>
+          <t>1차 매수선까지 19.6%</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>100900</v>
+        <v>45500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>92100</v>
+        <v>44650</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>101400</v>
+        <v>47700</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>91195</v>
+        <v>48097.5</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>91565</v>
+        <v>47932.5</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>72956</v>
+        <v>38478</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>73252</v>
+        <v>38346</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>72100</v>
+        <v>38050</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>39.94452149791955</v>
+        <v>19.57950065703022</v>
       </c>
       <c r="O59" s="7" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr"/>
       <c r="Q59" s="5" t="n">
-        <v>64900</v>
+        <v>34250</v>
       </c>
       <c r="R59" s="6" t="n">
-        <v>55.46995377503852</v>
+        <v>32.84671532846716</v>
       </c>
       <c r="S59" s="7" t="inlineStr"/>
       <c r="T59" s="7" t="inlineStr"/>
       <c r="U59" s="5" t="n">
-        <v>58500</v>
+        <v>30850</v>
       </c>
       <c r="V59" s="6" t="n">
-        <v>72.47863247863248</v>
+        <v>47.48784440842788</v>
       </c>
       <c r="W59" s="7" t="inlineStr"/>
       <c r="X59" s="7" t="inlineStr"/>
@@ -5286,12 +5290,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대힘스</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -5306,51 +5310,51 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.5%</t>
+          <t>1차 매수선까지 15.0%</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>14680</v>
+        <v>20900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>13830</v>
+        <v>20400</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>14950</v>
+        <v>21900</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>14425</v>
+        <v>23082.5</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>14429.5</v>
+        <v>22860</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>11540</v>
+        <v>18466</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>11543.6</v>
+        <v>18288</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>11420</v>
+        <v>18180</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>28.54640980735552</v>
+        <v>14.96149614961496</v>
       </c>
       <c r="O60" s="7" t="inlineStr"/>
       <c r="P60" s="7" t="inlineStr"/>
       <c r="Q60" s="5" t="n">
-        <v>10280</v>
+        <v>16370</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>42.80155642023346</v>
+        <v>27.67257177764203</v>
       </c>
       <c r="S60" s="7" t="inlineStr"/>
       <c r="T60" s="7" t="inlineStr"/>
       <c r="U60" s="5" t="n">
-        <v>9260</v>
+        <v>14740</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>58.53131749460043</v>
+        <v>41.7910447761194</v>
       </c>
       <c r="W60" s="7" t="inlineStr"/>
       <c r="X60" s="7" t="inlineStr"/>
@@ -5366,12 +5370,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5386,51 +5390,51 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 20.1%</t>
+          <t>1차 매수선까지 21.6%</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>74100</v>
+        <v>428500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>73900</v>
+        <v>424500</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>76400</v>
+        <v>457000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>77930</v>
+        <v>443400</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>77705</v>
+        <v>444150</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>62344</v>
+        <v>354720</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>62164</v>
+        <v>355320</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>61700</v>
+        <v>352500</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>20.09724473257699</v>
+        <v>21.56028368794326</v>
       </c>
       <c r="O61" s="7" t="inlineStr"/>
       <c r="P61" s="7" t="inlineStr"/>
       <c r="Q61" s="5" t="n">
-        <v>55600</v>
+        <v>317500</v>
       </c>
       <c r="R61" s="6" t="n">
-        <v>33.27338129496403</v>
+        <v>34.96062992125984</v>
       </c>
       <c r="S61" s="7" t="inlineStr"/>
       <c r="T61" s="7" t="inlineStr"/>
       <c r="U61" s="5" t="n">
-        <v>50100</v>
+        <v>286000</v>
       </c>
       <c r="V61" s="6" t="n">
-        <v>47.90419161676647</v>
+        <v>49.82517482517482</v>
       </c>
       <c r="W61" s="7" t="inlineStr"/>
       <c r="X61" s="7" t="inlineStr"/>
@@ -5446,12 +5450,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>010620</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>HD현대미포</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5466,51 +5470,51 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 31.5%</t>
+          <t>1차 매수선까지 20.9%</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>257000</v>
+        <v>213000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>250500</v>
+        <v>208500</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>262500</v>
+        <v>224000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>246825</v>
+        <v>221740</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>247225</v>
+        <v>222065</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>197460</v>
+        <v>177392</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>197780</v>
+        <v>177652</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>195400</v>
+        <v>176200</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>31.52507676560901</v>
+        <v>20.88535754824063</v>
       </c>
       <c r="O62" s="7" t="inlineStr"/>
       <c r="P62" s="7" t="inlineStr"/>
       <c r="Q62" s="5" t="n">
-        <v>175900</v>
+        <v>158600</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>46.10574189880614</v>
+        <v>34.30012610340479</v>
       </c>
       <c r="S62" s="7" t="inlineStr"/>
       <c r="T62" s="7" t="inlineStr"/>
       <c r="U62" s="5" t="n">
-        <v>158400</v>
+        <v>142800</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>62.24747474747475</v>
+        <v>49.15966386554621</v>
       </c>
       <c r="W62" s="7" t="inlineStr"/>
       <c r="X62" s="7" t="inlineStr"/>
@@ -5526,12 +5530,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5546,51 +5550,51 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.5%</t>
+          <t>1차 매수선까지 52.2%</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>115900</v>
+        <v>2234000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>113900</v>
+        <v>2100000</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>118900</v>
+        <v>2278000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>106930</v>
+        <v>1831550</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>107640</v>
+        <v>1872500</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>85544</v>
+        <v>1465240</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>86112</v>
+        <v>1498000</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>84900</v>
+        <v>1468000</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>36.51354534746761</v>
+        <v>52.17983651226158</v>
       </c>
       <c r="O63" s="7" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr"/>
       <c r="Q63" s="5" t="n">
-        <v>76500</v>
+        <v>1322000</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>51.5032679738562</v>
+        <v>68.98638426626323</v>
       </c>
       <c r="S63" s="7" t="inlineStr"/>
       <c r="T63" s="7" t="inlineStr"/>
       <c r="U63" s="5" t="n">
-        <v>68900</v>
+        <v>1190000</v>
       </c>
       <c r="V63" s="6" t="n">
-        <v>68.21480406386067</v>
+        <v>87.73109243697479</v>
       </c>
       <c r="W63" s="7" t="inlineStr"/>
       <c r="X63" s="7" t="inlineStr"/>
@@ -5606,12 +5610,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>LIG넥스원</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5626,51 +5630,51 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 23.9%</t>
+          <t>1차 매수선까지 27.1%</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>989000</v>
+        <v>482500</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>976000</v>
+        <v>462000</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>1007000</v>
+        <v>512000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>1009350</v>
+        <v>480600</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>1005950</v>
+        <v>479425</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>807480</v>
+        <v>384480</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>804760</v>
+        <v>383540</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>798000</v>
+        <v>379500</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>23.93483709273183</v>
+        <v>27.14097496706193</v>
       </c>
       <c r="O64" s="7" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr"/>
       <c r="Q64" s="5" t="n">
-        <v>719000</v>
+        <v>342000</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>37.55215577190543</v>
+        <v>41.08187134502924</v>
       </c>
       <c r="S64" s="7" t="inlineStr"/>
       <c r="T64" s="7" t="inlineStr"/>
       <c r="U64" s="5" t="n">
-        <v>648000</v>
+        <v>308000</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>52.62345679012346</v>
+        <v>56.65584415584416</v>
       </c>
       <c r="W64" s="7" t="inlineStr"/>
       <c r="X64" s="7" t="inlineStr"/>
@@ -5686,12 +5690,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>0008Z0</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5701,56 +5705,56 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.4%</t>
+          <t>1차 매수선까지 9.7% (접근 중!)</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>30600</v>
+        <v>36100</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>29800</v>
+        <v>35200</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>31250</v>
+        <v>38250</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>29765</v>
+        <v>41510</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>29870</v>
+        <v>41277.5</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>23812</v>
+        <v>33208</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>23896</v>
+        <v>33022</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>23650</v>
+        <v>32900</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>29.38689217758985</v>
+        <v>9.72644376899696</v>
       </c>
       <c r="O65" s="7" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr"/>
       <c r="Q65" s="5" t="n">
-        <v>21300</v>
+        <v>29650</v>
       </c>
       <c r="R65" s="6" t="n">
-        <v>43.66197183098591</v>
+        <v>21.75379426644182</v>
       </c>
       <c r="S65" s="7" t="inlineStr"/>
       <c r="T65" s="7" t="inlineStr"/>
       <c r="U65" s="5" t="n">
-        <v>19180</v>
+        <v>26700</v>
       </c>
       <c r="V65" s="6" t="n">
-        <v>59.54118873826904</v>
+        <v>35.2059925093633</v>
       </c>
       <c r="W65" s="7" t="inlineStr"/>
       <c r="X65" s="7" t="inlineStr"/>
@@ -5766,12 +5770,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>484590</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼양컴텍</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5786,51 +5790,51 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 43.4%</t>
+          <t>1차 매수선까지 12.0%</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>242000</v>
+        <v>14790</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>223500</v>
+        <v>14150</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>248000</v>
+        <v>15200</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>212260</v>
+        <v>16733.5</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>214465</v>
+        <v>16584</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>169808</v>
+        <v>13386.8</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>171572</v>
+        <v>13267.2</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>168700</v>
+        <v>13210</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>43.44991108476586</v>
+        <v>11.96063588190765</v>
       </c>
       <c r="O66" s="7" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr"/>
       <c r="Q66" s="5" t="n">
-        <v>151900</v>
+        <v>11890</v>
       </c>
       <c r="R66" s="6" t="n">
-        <v>59.31533903884134</v>
+        <v>24.39024390243902</v>
       </c>
       <c r="S66" s="7" t="inlineStr"/>
       <c r="T66" s="7" t="inlineStr"/>
       <c r="U66" s="5" t="n">
-        <v>136800</v>
+        <v>10710</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>76.90058479532163</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="W66" s="7" t="inlineStr"/>
       <c r="X66" s="7" t="inlineStr"/>
@@ -5846,12 +5850,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5866,51 +5870,51 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 19.5%</t>
+          <t>1차 매수선까지 40.3%</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>49950</v>
+        <v>103100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>48850</v>
+        <v>101400</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>51500</v>
+        <v>113300</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>52782.5</v>
+        <v>92980</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>52630</v>
+        <v>93355</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>42226</v>
+        <v>74384</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>42104</v>
+        <v>74684</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>41800</v>
+        <v>73500</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>19.49760765550239</v>
+        <v>40.27210884353741</v>
       </c>
       <c r="O67" s="7" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr"/>
       <c r="Q67" s="5" t="n">
-        <v>37650</v>
+        <v>66200</v>
       </c>
       <c r="R67" s="6" t="n">
-        <v>32.66932270916335</v>
+        <v>55.74018126888217</v>
       </c>
       <c r="S67" s="7" t="inlineStr"/>
       <c r="T67" s="7" t="inlineStr"/>
       <c r="U67" s="5" t="n">
-        <v>33900</v>
+        <v>59600</v>
       </c>
       <c r="V67" s="6" t="n">
-        <v>47.34513274336283</v>
+        <v>72.98657718120806</v>
       </c>
       <c r="W67" s="7" t="inlineStr"/>
       <c r="X67" s="7" t="inlineStr"/>
@@ -5926,12 +5930,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>042670</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>HD현대인프라코어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5946,51 +5950,51 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 22.9%</t>
+          <t>1차 매수선까지 23.0%</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>15250</v>
+        <v>14030</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>15070</v>
+        <v>13640</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>16400</v>
+        <v>14620</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>15643.5</v>
+        <v>14411</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>15649</v>
+        <v>14384.5</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>12514.8</v>
+        <v>11528.8</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>12519.2</v>
+        <v>11507.6</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>12410</v>
+        <v>11410</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>22.88477034649476</v>
+        <v>22.96231375985977</v>
       </c>
       <c r="O68" s="7" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr"/>
       <c r="Q68" s="5" t="n">
-        <v>11170</v>
+        <v>10270</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>36.52641002685765</v>
+        <v>36.61148977604674</v>
       </c>
       <c r="S68" s="7" t="inlineStr"/>
       <c r="T68" s="7" t="inlineStr"/>
       <c r="U68" s="5" t="n">
-        <v>10060</v>
+        <v>9250</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>51.59045725646123</v>
+        <v>51.67567567567568</v>
       </c>
       <c r="W68" s="7" t="inlineStr"/>
       <c r="X68" s="7" t="inlineStr"/>
@@ -6006,12 +6010,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -6021,56 +6025,56 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>WATCHING</t>
+          <t>READY_BUY1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 21.6%</t>
+          <t>1차 매수선까지 2.3% (접근 중!)</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>28150</v>
+        <v>61100</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>27700</v>
+        <v>60300</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>28450</v>
+        <v>64900</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>29257.5</v>
+        <v>75610</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>29170</v>
+        <v>74675</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>23406</v>
+        <v>60488</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>23336</v>
+        <v>59740</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>23150</v>
+        <v>59700</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>21.59827213822894</v>
+        <v>2.345058626465661</v>
       </c>
       <c r="O69" s="7" t="inlineStr"/>
       <c r="P69" s="7" t="inlineStr"/>
       <c r="Q69" s="5" t="n">
-        <v>20850</v>
+        <v>53800</v>
       </c>
       <c r="R69" s="6" t="n">
-        <v>35.01199040767386</v>
+        <v>13.56877323420074</v>
       </c>
       <c r="S69" s="7" t="inlineStr"/>
       <c r="T69" s="7" t="inlineStr"/>
       <c r="U69" s="5" t="n">
-        <v>18770</v>
+        <v>48450</v>
       </c>
       <c r="V69" s="6" t="n">
-        <v>49.97336174746936</v>
+        <v>26.109391124871</v>
       </c>
       <c r="W69" s="7" t="inlineStr"/>
       <c r="X69" s="7" t="inlineStr"/>
@@ -6086,12 +6090,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -6106,51 +6110,51 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 25.3%</t>
+          <t>1차 매수선까지 31.5%</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>2415</v>
+        <v>259000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>2410</v>
+        <v>254500</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>2535</v>
+        <v>275500</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>2433</v>
+        <v>249025</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2432.5</v>
+        <v>249250</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>1946.4</v>
+        <v>199220</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>1946</v>
+        <v>199400</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>1927</v>
+        <v>197000</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>25.32433834976648</v>
+        <v>31.47208121827411</v>
       </c>
       <c r="O70" s="7" t="inlineStr"/>
       <c r="P70" s="7" t="inlineStr"/>
       <c r="Q70" s="5" t="n">
-        <v>1735</v>
+        <v>177400</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>39.19308357348703</v>
+        <v>45.9977452085682</v>
       </c>
       <c r="S70" s="7" t="inlineStr"/>
       <c r="T70" s="7" t="inlineStr"/>
       <c r="U70" s="5" t="n">
-        <v>1562</v>
+        <v>159700</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>54.60947503201024</v>
+        <v>62.17908578584846</v>
       </c>
       <c r="W70" s="7" t="inlineStr"/>
       <c r="X70" s="7" t="inlineStr"/>
@@ -6166,12 +6170,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>037270</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>YG PLUS</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -6186,51 +6190,51 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 28.1%</t>
+          <t>1차 매수선까지 36.0%</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>7110</v>
+        <v>118200</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>7030</v>
+        <v>117700</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>7480</v>
+        <v>128900</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>7043</v>
+        <v>109445</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>7009</v>
+        <v>110125</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>5634.400000000001</v>
+        <v>87556</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>5607.200000000001</v>
+        <v>88100</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>5550</v>
+        <v>86900</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>28.10810810810811</v>
+        <v>36.01841196777906</v>
       </c>
       <c r="O71" s="7" t="inlineStr"/>
       <c r="P71" s="7" t="inlineStr"/>
       <c r="Q71" s="5" t="n">
-        <v>5000</v>
+        <v>78300</v>
       </c>
       <c r="R71" s="6" t="n">
-        <v>42.2</v>
+        <v>50.95785440613027</v>
       </c>
       <c r="S71" s="7" t="inlineStr"/>
       <c r="T71" s="7" t="inlineStr"/>
       <c r="U71" s="5" t="n">
-        <v>4505</v>
+        <v>70500</v>
       </c>
       <c r="V71" s="6" t="n">
-        <v>57.82463928967814</v>
+        <v>67.65957446808511</v>
       </c>
       <c r="W71" s="7" t="inlineStr"/>
       <c r="X71" s="7" t="inlineStr"/>
@@ -6246,12 +6250,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -6266,51 +6270,51 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 30.8%</t>
+          <t>1차 매수선까지 31.7%</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>146800</v>
+        <v>229000</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>140500</v>
+        <v>219500</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>146800</v>
+        <v>235000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>141755</v>
+        <v>218355</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>141905</v>
+        <v>220045</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>113404</v>
+        <v>174684</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>113524</v>
+        <v>176036</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>112200</v>
+        <v>173900</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>30.83778966131907</v>
+        <v>31.68487636572743</v>
       </c>
       <c r="O72" s="7" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr"/>
       <c r="Q72" s="5" t="n">
-        <v>101000</v>
+        <v>156600</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>45.34653465346535</v>
+        <v>46.23243933588761</v>
       </c>
       <c r="S72" s="7" t="inlineStr"/>
       <c r="T72" s="7" t="inlineStr"/>
       <c r="U72" s="5" t="n">
-        <v>91000</v>
+        <v>141000</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>61.31868131868132</v>
+        <v>62.4113475177305</v>
       </c>
       <c r="W72" s="7" t="inlineStr"/>
       <c r="X72" s="7" t="inlineStr"/>
@@ -6326,12 +6330,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>294570</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>쿠콘</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -6346,51 +6350,51 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 18.1%</t>
+          <t>1차 매수선까지 13.0%</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>35300</v>
+        <v>46600</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>35000</v>
+        <v>46400</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>36000</v>
+        <v>49550</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>38007.5</v>
+        <v>52145</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>37600</v>
+        <v>51795</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>30406</v>
+        <v>41716</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>30080</v>
+        <v>41436</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>29900</v>
+        <v>41250</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>18.06020066889632</v>
+        <v>12.96969696969697</v>
       </c>
       <c r="O73" s="7" t="inlineStr"/>
       <c r="P73" s="7" t="inlineStr"/>
       <c r="Q73" s="5" t="n">
-        <v>26950</v>
+        <v>37150</v>
       </c>
       <c r="R73" s="6" t="n">
-        <v>30.98330241187384</v>
+        <v>25.43741588156124</v>
       </c>
       <c r="S73" s="7" t="inlineStr"/>
       <c r="T73" s="7" t="inlineStr"/>
       <c r="U73" s="5" t="n">
-        <v>24300</v>
+        <v>33450</v>
       </c>
       <c r="V73" s="6" t="n">
-        <v>45.26748971193415</v>
+        <v>39.31240657698057</v>
       </c>
       <c r="W73" s="7" t="inlineStr"/>
       <c r="X73" s="7" t="inlineStr"/>
@@ -6406,12 +6410,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>042670</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>HD현대인프라코어</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -6426,51 +6430,51 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 13.7%</t>
+          <t>1차 매수선까지 13.8%</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>8730</v>
+        <v>14080</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>8570</v>
+        <v>13700</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>8910</v>
+        <v>14750</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>9764</v>
+        <v>15586.5</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>9646</v>
+        <v>15547.5</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>7811.200000000001</v>
+        <v>12469.2</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>7716.8</v>
+        <v>12438</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>7680</v>
+        <v>12370</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>13.671875</v>
+        <v>13.82376717865804</v>
       </c>
       <c r="O74" s="7" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr"/>
       <c r="Q74" s="5" t="n">
-        <v>6920</v>
+        <v>11140</v>
       </c>
       <c r="R74" s="6" t="n">
-        <v>26.15606936416185</v>
+        <v>26.39138240574506</v>
       </c>
       <c r="S74" s="7" t="inlineStr"/>
       <c r="T74" s="7" t="inlineStr"/>
       <c r="U74" s="5" t="n">
-        <v>6230</v>
+        <v>10030</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>40.12841091492777</v>
+        <v>40.37886340977069</v>
       </c>
       <c r="W74" s="7" t="inlineStr"/>
       <c r="X74" s="7" t="inlineStr"/>
@@ -6486,12 +6490,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6506,51 +6510,51 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 29.0%</t>
+          <t>1차 매수선까지 17.2%</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>260000</v>
+        <v>26850</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>251500</v>
+        <v>26000</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>283500</v>
+        <v>27750</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>251340</v>
+        <v>28925</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>254450</v>
+        <v>28785</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>201072</v>
+        <v>23140</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>203560</v>
+        <v>23028</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>201500</v>
+        <v>22900</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>29.03225806451613</v>
+        <v>17.24890829694323</v>
       </c>
       <c r="O75" s="7" t="inlineStr"/>
       <c r="P75" s="7" t="inlineStr"/>
       <c r="Q75" s="5" t="n">
-        <v>181400</v>
+        <v>20650</v>
       </c>
       <c r="R75" s="6" t="n">
-        <v>43.32965821389195</v>
+        <v>30.02421307506054</v>
       </c>
       <c r="S75" s="7" t="inlineStr"/>
       <c r="T75" s="7" t="inlineStr"/>
       <c r="U75" s="5" t="n">
-        <v>163300</v>
+        <v>18590</v>
       </c>
       <c r="V75" s="6" t="n">
-        <v>59.21616656460502</v>
+        <v>44.43249058633674</v>
       </c>
       <c r="W75" s="7" t="inlineStr"/>
       <c r="X75" s="7" t="inlineStr"/>
@@ -6566,12 +6570,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>008970</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6586,51 +6590,51 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 32.6%</t>
+          <t>1차 매수선까지 17.7%</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>311500</v>
+        <v>2260</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>310000</v>
+        <v>2220</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>318500</v>
+        <v>2340</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>295400</v>
+        <v>2421.8</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>297025</v>
+        <v>2416.1</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>236320</v>
+        <v>1937.44</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>237620</v>
+        <v>1932.88</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>235000</v>
+        <v>1920</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>32.5531914893617</v>
+        <v>17.70833333333334</v>
       </c>
       <c r="O76" s="7" t="inlineStr"/>
       <c r="P76" s="7" t="inlineStr"/>
       <c r="Q76" s="5" t="n">
-        <v>212000</v>
+        <v>1729</v>
       </c>
       <c r="R76" s="6" t="n">
-        <v>46.93396226415094</v>
+        <v>30.71139386928861</v>
       </c>
       <c r="S76" s="7" t="inlineStr"/>
       <c r="T76" s="7" t="inlineStr"/>
       <c r="U76" s="5" t="n">
-        <v>190900</v>
+        <v>1557</v>
       </c>
       <c r="V76" s="6" t="n">
-        <v>63.17443687794657</v>
+        <v>45.15093127809891</v>
       </c>
       <c r="W76" s="7" t="inlineStr"/>
       <c r="X76" s="7" t="inlineStr"/>
@@ -6646,12 +6650,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>037270</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>YG PLUS</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -6666,51 +6670,51 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 26.1%</t>
+          <t>1차 매수선까지 22.9%</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>100000</v>
+        <v>6720</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>98900</v>
+        <v>6550</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>104400</v>
+        <v>6940</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>99740</v>
+        <v>6931</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>100085</v>
+        <v>6893.5</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>79792</v>
+        <v>5544.8</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>80068</v>
+        <v>5514.8</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>79300</v>
+        <v>5470</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>26.10340479192938</v>
+        <v>22.85191956124314</v>
       </c>
       <c r="O77" s="7" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr"/>
       <c r="Q77" s="5" t="n">
-        <v>71400</v>
+        <v>4925</v>
       </c>
       <c r="R77" s="6" t="n">
-        <v>40.05602240896359</v>
+        <v>36.44670050761422</v>
       </c>
       <c r="S77" s="7" t="inlineStr"/>
       <c r="T77" s="7" t="inlineStr"/>
       <c r="U77" s="5" t="n">
-        <v>64300</v>
+        <v>4435</v>
       </c>
       <c r="V77" s="6" t="n">
-        <v>55.52099533437014</v>
+        <v>51.52198421645998</v>
       </c>
       <c r="W77" s="7" t="inlineStr"/>
       <c r="X77" s="7" t="inlineStr"/>
@@ -6726,12 +6730,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -6746,51 +6750,51 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 34.4%</t>
+          <t>1차 매수선까지 33.7%</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>96400</v>
+        <v>150900</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>94500</v>
+        <v>146100</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>97900</v>
+        <v>160400</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>90180</v>
+        <v>143025</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>90825</v>
+        <v>142970</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>72144</v>
+        <v>114420</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>72660</v>
+        <v>114376</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>71700</v>
+        <v>112900</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>34.44909344490934</v>
+        <v>33.65810451727192</v>
       </c>
       <c r="O78" s="7" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr"/>
       <c r="Q78" s="5" t="n">
-        <v>64600</v>
+        <v>101700</v>
       </c>
       <c r="R78" s="6" t="n">
-        <v>49.22600619195047</v>
+        <v>48.37758112094395</v>
       </c>
       <c r="S78" s="7" t="inlineStr"/>
       <c r="T78" s="7" t="inlineStr"/>
       <c r="U78" s="5" t="n">
-        <v>58200</v>
+        <v>91600</v>
       </c>
       <c r="V78" s="6" t="n">
-        <v>65.63573883161511</v>
+        <v>64.73799126637554</v>
       </c>
       <c r="W78" s="7" t="inlineStr"/>
       <c r="X78" s="7" t="inlineStr"/>
@@ -6806,12 +6810,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>294570</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>쿠콘</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6826,51 +6830,51 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 36.7%</t>
+          <t>1차 매수선까지 17.5%</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>249000</v>
+        <v>34500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>243000</v>
+        <v>33000</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>250000</v>
+        <v>34750</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>229025</v>
+        <v>37097.5</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>231025</v>
+        <v>36905</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>183220</v>
+        <v>29678</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>184820</v>
+        <v>29524</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>182200</v>
+        <v>29350</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>36.66300768386389</v>
+        <v>17.54684838160136</v>
       </c>
       <c r="O79" s="7" t="inlineStr"/>
       <c r="P79" s="7" t="inlineStr"/>
       <c r="Q79" s="5" t="n">
-        <v>164000</v>
+        <v>26450</v>
       </c>
       <c r="R79" s="6" t="n">
-        <v>51.82926829268293</v>
+        <v>30.43478260869566</v>
       </c>
       <c r="S79" s="7" t="inlineStr"/>
       <c r="T79" s="7" t="inlineStr"/>
       <c r="U79" s="5" t="n">
-        <v>147700</v>
+        <v>23850</v>
       </c>
       <c r="V79" s="6" t="n">
-        <v>68.58496953283684</v>
+        <v>44.65408805031446</v>
       </c>
       <c r="W79" s="7" t="inlineStr"/>
       <c r="X79" s="7" t="inlineStr"/>
@@ -6886,12 +6890,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -6906,51 +6910,51 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1차 매수선까지 38.2%</t>
+          <t>1차 매수선까지 20.8%</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>129600</v>
+        <v>8960</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>128500</v>
+        <v>8660</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>137200</v>
+        <v>9290</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>117585</v>
+        <v>9445</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>118980</v>
+        <v>9341</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>94068</v>
+        <v>7556</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>95184</v>
+        <v>7472.8</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>93800</v>
+        <v>7420</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>38.16631130063966</v>
+        <v>20.75471698113208</v>
       </c>
       <c r="O80" s="7" t="inlineStr"/>
       <c r="P80" s="7" t="inlineStr"/>
       <c r="Q80" s="5" t="n">
-        <v>84500</v>
+        <v>6680</v>
       </c>
       <c r="R80" s="6" t="n">
-        <v>53.37278106508876</v>
+        <v>34.13173652694611</v>
       </c>
       <c r="S80" s="7" t="inlineStr"/>
       <c r="T80" s="7" t="inlineStr"/>
       <c r="U80" s="5" t="n">
-        <v>76100</v>
+        <v>6020</v>
       </c>
       <c r="V80" s="6" t="n">
-        <v>70.30223390275953</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="W80" s="7" t="inlineStr"/>
       <c r="X80" s="7" t="inlineStr"/>
@@ -6962,6 +6966,486 @@
       <c r="AD80" s="7" t="inlineStr"/>
       <c r="AE80" s="7" t="inlineStr"/>
       <c r="AF80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>402340</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 24.7%</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>241000</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>267000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>261900</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>263150</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>209520</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>210520</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>208500</v>
+      </c>
+      <c r="N81" s="6" t="n">
+        <v>24.70023980815348</v>
+      </c>
+      <c r="O81" s="7" t="inlineStr"/>
+      <c r="P81" s="7" t="inlineStr"/>
+      <c r="Q81" s="5" t="n">
+        <v>187700</v>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v>38.51891315929675</v>
+      </c>
+      <c r="S81" s="7" t="inlineStr"/>
+      <c r="T81" s="7" t="inlineStr"/>
+      <c r="U81" s="5" t="n">
+        <v>169000</v>
+      </c>
+      <c r="V81" s="6" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="W81" s="7" t="inlineStr"/>
+      <c r="X81" s="7" t="inlineStr"/>
+      <c r="Y81" s="7" t="inlineStr"/>
+      <c r="Z81" s="7" t="inlineStr"/>
+      <c r="AA81" s="7" t="inlineStr"/>
+      <c r="AB81" s="7" t="inlineStr"/>
+      <c r="AC81" s="7" t="inlineStr"/>
+      <c r="AD81" s="7" t="inlineStr"/>
+      <c r="AE81" s="7" t="inlineStr"/>
+      <c r="AF81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>005490</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 26.8%</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>303000</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>295000</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>312000</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>300350</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>301750</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>240280</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>241400</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>239000</v>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>26.77824267782427</v>
+      </c>
+      <c r="O82" s="7" t="inlineStr"/>
+      <c r="P82" s="7" t="inlineStr"/>
+      <c r="Q82" s="5" t="n">
+        <v>215500</v>
+      </c>
+      <c r="R82" s="6" t="n">
+        <v>40.60324825986079</v>
+      </c>
+      <c r="S82" s="7" t="inlineStr"/>
+      <c r="T82" s="7" t="inlineStr"/>
+      <c r="U82" s="5" t="n">
+        <v>194000</v>
+      </c>
+      <c r="V82" s="6" t="n">
+        <v>56.18556701030928</v>
+      </c>
+      <c r="W82" s="7" t="inlineStr"/>
+      <c r="X82" s="7" t="inlineStr"/>
+      <c r="Y82" s="7" t="inlineStr"/>
+      <c r="Z82" s="7" t="inlineStr"/>
+      <c r="AA82" s="7" t="inlineStr"/>
+      <c r="AB82" s="7" t="inlineStr"/>
+      <c r="AC82" s="7" t="inlineStr"/>
+      <c r="AD82" s="7" t="inlineStr"/>
+      <c r="AE82" s="7" t="inlineStr"/>
+      <c r="AF82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>267270</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>HD현대건설기계</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 17.7%</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>93900</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>92400</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>97600</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>100385</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>100410</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>80308</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>80328</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>79800</v>
+      </c>
+      <c r="N83" s="6" t="n">
+        <v>17.66917293233083</v>
+      </c>
+      <c r="O83" s="7" t="inlineStr"/>
+      <c r="P83" s="7" t="inlineStr"/>
+      <c r="Q83" s="5" t="n">
+        <v>71900</v>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v>30.5980528511822</v>
+      </c>
+      <c r="S83" s="7" t="inlineStr"/>
+      <c r="T83" s="7" t="inlineStr"/>
+      <c r="U83" s="5" t="n">
+        <v>64800</v>
+      </c>
+      <c r="V83" s="6" t="n">
+        <v>44.9074074074074</v>
+      </c>
+      <c r="W83" s="7" t="inlineStr"/>
+      <c r="X83" s="7" t="inlineStr"/>
+      <c r="Y83" s="7" t="inlineStr"/>
+      <c r="Z83" s="7" t="inlineStr"/>
+      <c r="AA83" s="7" t="inlineStr"/>
+      <c r="AB83" s="7" t="inlineStr"/>
+      <c r="AC83" s="7" t="inlineStr"/>
+      <c r="AD83" s="7" t="inlineStr"/>
+      <c r="AE83" s="7" t="inlineStr"/>
+      <c r="AF83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>000880</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 22.6%</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>89100</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>85500</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>93000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>91520</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>91670</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>73216</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>73336</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>72700</v>
+      </c>
+      <c r="N84" s="6" t="n">
+        <v>22.55845942228336</v>
+      </c>
+      <c r="O84" s="7" t="inlineStr"/>
+      <c r="P84" s="7" t="inlineStr"/>
+      <c r="Q84" s="5" t="n">
+        <v>65500</v>
+      </c>
+      <c r="R84" s="6" t="n">
+        <v>36.03053435114504</v>
+      </c>
+      <c r="S84" s="7" t="inlineStr"/>
+      <c r="T84" s="7" t="inlineStr"/>
+      <c r="U84" s="5" t="n">
+        <v>59000</v>
+      </c>
+      <c r="V84" s="6" t="n">
+        <v>51.01694915254237</v>
+      </c>
+      <c r="W84" s="7" t="inlineStr"/>
+      <c r="X84" s="7" t="inlineStr"/>
+      <c r="Y84" s="7" t="inlineStr"/>
+      <c r="Z84" s="7" t="inlineStr"/>
+      <c r="AA84" s="7" t="inlineStr"/>
+      <c r="AB84" s="7" t="inlineStr"/>
+      <c r="AC84" s="7" t="inlineStr"/>
+      <c r="AD84" s="7" t="inlineStr"/>
+      <c r="AE84" s="7" t="inlineStr"/>
+      <c r="AF84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>034730</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 27.5%</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>237500</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>230500</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>247000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>234625</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>235400</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>187700</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>188320</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>186300</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>27.4825550187869</v>
+      </c>
+      <c r="O85" s="7" t="inlineStr"/>
+      <c r="P85" s="7" t="inlineStr"/>
+      <c r="Q85" s="5" t="n">
+        <v>167700</v>
+      </c>
+      <c r="R85" s="6" t="n">
+        <v>41.62194394752534</v>
+      </c>
+      <c r="S85" s="7" t="inlineStr"/>
+      <c r="T85" s="7" t="inlineStr"/>
+      <c r="U85" s="5" t="n">
+        <v>151000</v>
+      </c>
+      <c r="V85" s="6" t="n">
+        <v>57.28476821192054</v>
+      </c>
+      <c r="W85" s="7" t="inlineStr"/>
+      <c r="X85" s="7" t="inlineStr"/>
+      <c r="Y85" s="7" t="inlineStr"/>
+      <c r="Z85" s="7" t="inlineStr"/>
+      <c r="AA85" s="7" t="inlineStr"/>
+      <c r="AB85" s="7" t="inlineStr"/>
+      <c r="AC85" s="7" t="inlineStr"/>
+      <c r="AD85" s="7" t="inlineStr"/>
+      <c r="AE85" s="7" t="inlineStr"/>
+      <c r="AF85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>WATCHING</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>1차 매수선까지 25.5%</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>121200</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>117900</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>125500</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>121165</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>121970</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>96932</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>97576</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>96600</v>
+      </c>
+      <c r="N86" s="6" t="n">
+        <v>25.46583850931677</v>
+      </c>
+      <c r="O86" s="7" t="inlineStr"/>
+      <c r="P86" s="7" t="inlineStr"/>
+      <c r="Q86" s="5" t="n">
+        <v>87000</v>
+      </c>
+      <c r="R86" s="6" t="n">
+        <v>39.31034482758621</v>
+      </c>
+      <c r="S86" s="7" t="inlineStr"/>
+      <c r="T86" s="7" t="inlineStr"/>
+      <c r="U86" s="5" t="n">
+        <v>78400</v>
+      </c>
+      <c r="V86" s="6" t="n">
+        <v>54.59183673469388</v>
+      </c>
+      <c r="W86" s="7" t="inlineStr"/>
+      <c r="X86" s="7" t="inlineStr"/>
+      <c r="Y86" s="7" t="inlineStr"/>
+      <c r="Z86" s="7" t="inlineStr"/>
+      <c r="AA86" s="7" t="inlineStr"/>
+      <c r="AB86" s="7" t="inlineStr"/>
+      <c r="AC86" s="7" t="inlineStr"/>
+      <c r="AD86" s="7" t="inlineStr"/>
+      <c r="AE86" s="7" t="inlineStr"/>
+      <c r="AF86" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6974,14 +7458,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="n"/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>티커</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>매수상태</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>알람상태</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>상태메시지</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>저가</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>고가</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>20일선(당일)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>20일선(익일)</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>-20%엔벨로프(당일)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>-20%엔벨로프(익일)</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수선(익일)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수선이격도(%)</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수일</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>1차매수가(당일)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수선(익일)</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수선이격도(%)</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수일</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>2차매수가(당일)</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수선(익일)</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수선이격도(%)</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수일</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>3차매수가(당일)</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>평균매수가</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>1차매도선(+3%)</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>1차매도선이격도(%)</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>2차매도선(+5%)</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>2차매도선이격도(%)</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>3차매도선(+7%)</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>3차매도선이격도(%)</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>최고도달선</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>종료사유</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>실현수익률(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>매도 완료</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>7490</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>7310</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>7870</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>9074</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>8954</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>7259.200000000001</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>7163.200000000001</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>7150</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>4.755244755244755</v>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="n"/>
+      <c r="Q2" s="5" t="n">
+        <v>6440</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>16.30434782608696</v>
+      </c>
+      <c r="S2" s="7" t="n"/>
+      <c r="T2" s="7" t="n"/>
+      <c r="U2" s="5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>29.13793103448276</v>
+      </c>
+      <c r="W2" s="7" t="n"/>
+      <c r="X2" s="7" t="n"/>
+      <c r="Y2" s="5" t="n">
+        <v>7320</v>
+      </c>
+      <c r="Z2" s="5" t="n">
+        <v>7539.6</v>
+      </c>
+      <c r="AA2" s="6" t="n">
+        <v>-0.657859833412918</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>7686</v>
+      </c>
+      <c r="AC2" s="6" t="n">
+        <v>-2.550091074681239</v>
+      </c>
+      <c r="AD2" s="5" t="n">
+        <v>7832.400000000001</v>
+      </c>
+      <c r="AE2" s="6" t="n">
+        <v>-4.371584699453559</v>
+      </c>
+      <c r="AF2" s="5" t="n">
+        <v>7870</v>
+      </c>
+      <c r="AG2" s="8" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>+7% 도달 → 전량 매도</t>
+        </is>
+      </c>
+      <c r="AI2" s="6" t="n">
+        <v>2.3224043715847</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
